--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="1374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="1375">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95473098754883</t>
+    <t xml:space="preserve">1.95473074913025</t>
   </si>
   <si>
     <t xml:space="preserve">FM.MI</t>
@@ -53,25 +53,25 @@
     <t xml:space="preserve">1.8558669090271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86453926563263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68415582180023</t>
+    <t xml:space="preserve">1.86453914642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68415570259094</t>
   </si>
   <si>
     <t xml:space="preserve">1.76914405822754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74486184120178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69542980194092</t>
+    <t xml:space="preserve">1.74486172199249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69542992115021</t>
   </si>
   <si>
     <t xml:space="preserve">1.61824655532837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52285146713257</t>
+    <t xml:space="preserve">1.52285158634186</t>
   </si>
   <si>
     <t xml:space="preserve">1.47949004173279</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">1.45434057712555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55233716964722</t>
+    <t xml:space="preserve">1.55233728885651</t>
   </si>
   <si>
     <t xml:space="preserve">1.48989689350128</t>
@@ -92,13 +92,13 @@
     <t xml:space="preserve">1.54366493225098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.595698595047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51331210136414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53325831890106</t>
+    <t xml:space="preserve">1.59569847583771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51331198215485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53325808048248</t>
   </si>
   <si>
     <t xml:space="preserve">1.49943625926971</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">1.4300582408905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40751016139984</t>
+    <t xml:space="preserve">1.40751028060913</t>
   </si>
   <si>
     <t xml:space="preserve">1.38582956790924</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">1.28349673748016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17682766914368</t>
+    <t xml:space="preserve">1.17682778835297</t>
   </si>
   <si>
     <t xml:space="preserve">1.24186980724335</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">1.20718061923981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23059582710266</t>
+    <t xml:space="preserve">1.23059594631195</t>
   </si>
   <si>
     <t xml:space="preserve">1.43873047828674</t>
@@ -143,10 +143,10 @@
     <t xml:space="preserve">1.46561455726624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52111709117889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51678073406219</t>
+    <t xml:space="preserve">1.5211169719696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51678085327148</t>
   </si>
   <si>
     <t xml:space="preserve">1.4942330121994</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">1.47515392303467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5098432302475</t>
+    <t xml:space="preserve">1.50984311103821</t>
   </si>
   <si>
     <t xml:space="preserve">1.56014227867126</t>
@@ -167,22 +167,22 @@
     <t xml:space="preserve">1.58702635765076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55754041671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52805471420288</t>
+    <t xml:space="preserve">1.55754053592682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52805495262146</t>
   </si>
   <si>
     <t xml:space="preserve">1.54279780387878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51244461536407</t>
+    <t xml:space="preserve">1.51244473457336</t>
   </si>
   <si>
     <t xml:space="preserve">1.55147004127502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61651194095612</t>
+    <t xml:space="preserve">1.61651206016541</t>
   </si>
   <si>
     <t xml:space="preserve">1.67374908924103</t>
@@ -194,37 +194,37 @@
     <t xml:space="preserve">1.67808520793915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65467000007629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63298940658569</t>
+    <t xml:space="preserve">1.65467011928558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63298952579498</t>
   </si>
   <si>
     <t xml:space="preserve">1.6061053276062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53499269485474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49770200252533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49683451652527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48122441768646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41791701316833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39970517158508</t>
+    <t xml:space="preserve">1.53499257564545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49770176410675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49683463573456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48122453689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41791689395905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39970529079437</t>
   </si>
   <si>
     <t xml:space="preserve">1.35200762748718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39190018177032</t>
+    <t xml:space="preserve">1.39190006256104</t>
   </si>
   <si>
     <t xml:space="preserve">1.46041119098663</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">1.62952041625977</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60437095165253</t>
+    <t xml:space="preserve">1.60437083244324</t>
   </si>
   <si>
     <t xml:space="preserve">1.60870695114136</t>
@@ -254,16 +254,16 @@
     <t xml:space="preserve">1.55407166481018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60090184211731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58876073360443</t>
+    <t xml:space="preserve">1.6009019613266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58876085281372</t>
   </si>
   <si>
     <t xml:space="preserve">1.49249851703644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45780944824219</t>
+    <t xml:space="preserve">1.4578093290329</t>
   </si>
   <si>
     <t xml:space="preserve">1.47775566577911</t>
@@ -272,22 +272,22 @@
     <t xml:space="preserve">1.47428679466248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46908330917358</t>
+    <t xml:space="preserve">1.46908342838287</t>
   </si>
   <si>
     <t xml:space="preserve">1.56794726848602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53932893276215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53065645694733</t>
+    <t xml:space="preserve">1.53932869434357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53065657615662</t>
   </si>
   <si>
     <t xml:space="preserve">1.54106330871582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5696816444397</t>
+    <t xml:space="preserve">1.56968176364899</t>
   </si>
   <si>
     <t xml:space="preserve">1.5471339225769</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">1.56708025932312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5740180015564</t>
+    <t xml:space="preserve">1.57401788234711</t>
   </si>
   <si>
     <t xml:space="preserve">1.5107102394104</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">1.45000445842743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38929855823517</t>
+    <t xml:space="preserve">1.38929843902588</t>
   </si>
   <si>
     <t xml:space="preserve">1.40057241916656</t>
@@ -326,40 +326,40 @@
     <t xml:space="preserve">1.38756394386292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44740283489227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49163126945496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48382616043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32338929176331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3294597864151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3884311914444</t>
+    <t xml:space="preserve">1.44740271568298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49163138866425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4838262796402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32338917255402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32945966720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38843107223511</t>
   </si>
   <si>
     <t xml:space="preserve">1.39016568660736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35981261730194</t>
+    <t xml:space="preserve">1.35981285572052</t>
   </si>
   <si>
     <t xml:space="preserve">1.33726489543915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31124794483185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30084121227264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30257558822632</t>
+    <t xml:space="preserve">1.31124806404114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30084133148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30257570743561</t>
   </si>
   <si>
     <t xml:space="preserve">1.36154723167419</t>
@@ -374,10 +374,10 @@
     <t xml:space="preserve">1.39623630046844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.377157330513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40490853786469</t>
+    <t xml:space="preserve">1.37715744972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4049084186554</t>
   </si>
   <si>
     <t xml:space="preserve">1.39450192451477</t>
@@ -386,19 +386,19 @@
     <t xml:space="preserve">1.4040412902832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.393634557724</t>
+    <t xml:space="preserve">1.39363467693329</t>
   </si>
   <si>
     <t xml:space="preserve">1.42225313186646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42832362651825</t>
+    <t xml:space="preserve">1.42832350730896</t>
   </si>
   <si>
     <t xml:space="preserve">1.37889182567596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38062620162964</t>
+    <t xml:space="preserve">1.38062632083893</t>
   </si>
   <si>
     <t xml:space="preserve">1.36588335037231</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">1.35460937023163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34333550930023</t>
+    <t xml:space="preserve">1.34333539009094</t>
   </si>
   <si>
     <t xml:space="preserve">1.33119416236877</t>
@@ -422,10 +422,10 @@
     <t xml:space="preserve">1.30170857906342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3077791929245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34767162799835</t>
+    <t xml:space="preserve">1.30777907371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34767150878906</t>
   </si>
   <si>
     <t xml:space="preserve">1.34506988525391</t>
@@ -434,46 +434,46 @@
     <t xml:space="preserve">1.33379578590393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37108671665192</t>
+    <t xml:space="preserve">1.37108659744263</t>
   </si>
   <si>
     <t xml:space="preserve">1.35547661781311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34940588474274</t>
+    <t xml:space="preserve">1.34940600395203</t>
   </si>
   <si>
     <t xml:space="preserve">1.33813202381134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34853875637054</t>
+    <t xml:space="preserve">1.34853863716125</t>
   </si>
   <si>
     <t xml:space="preserve">1.41704976558685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40317416191101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39536893367767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41097915172577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36501610279083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38322794437408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36761772632599</t>
+    <t xml:space="preserve">1.40317404270172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39536905288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41097903251648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36501598358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38322782516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36761784553528</t>
   </si>
   <si>
     <t xml:space="preserve">1.38149344921112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39797067642212</t>
+    <t xml:space="preserve">1.39797079563141</t>
   </si>
   <si>
     <t xml:space="preserve">1.37455558776855</t>
@@ -482,16 +482,16 @@
     <t xml:space="preserve">1.41358077526093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42138588428497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41271352767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40924465656281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42572212219238</t>
+    <t xml:space="preserve">1.42138600349426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41271364688873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40924453735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42572200298309</t>
   </si>
   <si>
     <t xml:space="preserve">1.35114049911499</t>
@@ -512,16 +512,16 @@
     <t xml:space="preserve">1.33032703399658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32078754901886</t>
+    <t xml:space="preserve">1.32078742980957</t>
   </si>
   <si>
     <t xml:space="preserve">1.3190530538559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31992018222809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3129825592041</t>
+    <t xml:space="preserve">1.31992030143738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31298243999481</t>
   </si>
   <si>
     <t xml:space="preserve">1.17942941188812</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">1.29216909408569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23146307468414</t>
+    <t xml:space="preserve">1.23146319389343</t>
   </si>
   <si>
     <t xml:space="preserve">1.2175874710083</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">1.2488077878952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22886157035828</t>
+    <t xml:space="preserve">1.22886145114899</t>
   </si>
   <si>
     <t xml:space="preserve">1.18550002574921</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">1.15774881839752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11872339248657</t>
+    <t xml:space="preserve">1.11872351169586</t>
   </si>
   <si>
     <t xml:space="preserve">1.13086462020874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12305951118469</t>
+    <t xml:space="preserve">1.12305963039398</t>
   </si>
   <si>
     <t xml:space="preserve">1.13346636295319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11438739299774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11612176895142</t>
+    <t xml:space="preserve">1.11438727378845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11612188816071</t>
   </si>
   <si>
     <t xml:space="preserve">1.11525452136993</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">1.09791004657745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09270656108856</t>
+    <t xml:space="preserve">1.09270668029785</t>
   </si>
   <si>
     <t xml:space="preserve">1.07536208629608</t>
@@ -584,31 +584,31 @@
     <t xml:space="preserve">1.07276034355164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10398066043854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1542797088623</t>
+    <t xml:space="preserve">1.10398054122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15427982807159</t>
   </si>
   <si>
     <t xml:space="preserve">1.16295206546783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16208481788635</t>
+    <t xml:space="preserve">1.16208493709564</t>
   </si>
   <si>
     <t xml:space="preserve">1.17856216430664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18289828300476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20544624328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23493206501007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24533867835999</t>
+    <t xml:space="preserve">1.18289840221405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20544612407684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23493194580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2453385591507</t>
   </si>
   <si>
     <t xml:space="preserve">1.21845459938049</t>
@@ -617,31 +617,31 @@
     <t xml:space="preserve">1.19937562942505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20111012458801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22799408435822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22192347049713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23666656017303</t>
+    <t xml:space="preserve">1.20111000537872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2279942035675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22192358970642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23666632175446</t>
   </si>
   <si>
     <t xml:space="preserve">1.26875388622284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38409507274628</t>
+    <t xml:space="preserve">1.38409495353699</t>
   </si>
   <si>
     <t xml:space="preserve">1.39883804321289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38669681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35721099376678</t>
+    <t xml:space="preserve">1.38669669628143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35721123218536</t>
   </si>
   <si>
     <t xml:space="preserve">1.34593713283539</t>
@@ -650,28 +650,28 @@
     <t xml:space="preserve">1.33292865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28869986534119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25747978687286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23319756984711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24447154998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22712695598602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25661277770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22365808486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22279071807861</t>
+    <t xml:space="preserve">1.28870010375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25747990608215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23319745063782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2444714307785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22712707519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25661265850067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2236579656601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2227908372879</t>
   </si>
   <si>
     <t xml:space="preserve">1.25314378738403</t>
@@ -680,19 +680,19 @@
     <t xml:space="preserve">1.22625970840454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21325147151947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20891523361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20457899570465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21585297584534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21672010421753</t>
+    <t xml:space="preserve">1.21325135231018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20891535282135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20457911491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21585285663605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21672022342682</t>
   </si>
   <si>
     <t xml:space="preserve">1.19070339202881</t>
@@ -701,10 +701,10 @@
     <t xml:space="preserve">1.20197737216949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18810176849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.191570520401</t>
+    <t xml:space="preserve">1.18810164928436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19157063961029</t>
   </si>
   <si>
     <t xml:space="preserve">1.20284450054169</t>
@@ -719,46 +719,46 @@
     <t xml:space="preserve">1.27742612361908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27222287654877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29823958873749</t>
+    <t xml:space="preserve">1.27222275733948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2982394695282</t>
   </si>
   <si>
     <t xml:space="preserve">1.26355040073395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24273705482483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23579907417297</t>
+    <t xml:space="preserve">1.24273693561554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23579919338226</t>
   </si>
   <si>
     <t xml:space="preserve">1.22018897533417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24794030189514</t>
+    <t xml:space="preserve">1.24794042110443</t>
   </si>
   <si>
     <t xml:space="preserve">1.24967479705811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29043447971344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2930361032486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31818580627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30691182613373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27308988571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24013519287109</t>
+    <t xml:space="preserve">1.29043459892273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29303634166718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31818568706512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30691194534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27309000492096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24013531208038</t>
   </si>
   <si>
     <t xml:space="preserve">1.27916049957275</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">1.2704883813858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26528477668762</t>
+    <t xml:space="preserve">1.2652850151062</t>
   </si>
   <si>
     <t xml:space="preserve">1.28436398506165</t>
@@ -776,22 +776,22 @@
     <t xml:space="preserve">1.27482438087463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26441776752472</t>
+    <t xml:space="preserve">1.26441764831543</t>
   </si>
   <si>
     <t xml:space="preserve">1.28523111343384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28696548938751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3398665189743</t>
+    <t xml:space="preserve">1.2869656085968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33986639976501</t>
   </si>
   <si>
     <t xml:space="preserve">1.33899927139282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41184639930725</t>
+    <t xml:space="preserve">1.41184651851654</t>
   </si>
   <si>
     <t xml:space="preserve">1.57835412025452</t>
@@ -800,16 +800,16 @@
     <t xml:space="preserve">1.51851534843445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54019594192505</t>
+    <t xml:space="preserve">1.54019606113434</t>
   </si>
   <si>
     <t xml:space="preserve">1.49856913089752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50724136829376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50203812122345</t>
+    <t xml:space="preserve">1.50724148750305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50203800201416</t>
   </si>
   <si>
     <t xml:space="preserve">1.4786229133606</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">1.47168505191803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48729515075684</t>
+    <t xml:space="preserve">1.48729526996613</t>
   </si>
   <si>
     <t xml:space="preserve">1.47602117061615</t>
@@ -836,16 +836,16 @@
     <t xml:space="preserve">1.45694220066071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46821618080139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45867657661438</t>
+    <t xml:space="preserve">1.4682160615921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45867669582367</t>
   </si>
   <si>
     <t xml:space="preserve">1.45954382419586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45607495307922</t>
+    <t xml:space="preserve">1.45607507228851</t>
   </si>
   <si>
     <t xml:space="preserve">1.49076402187347</t>
@@ -854,55 +854,55 @@
     <t xml:space="preserve">1.47341954708099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52892220020294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50637412071228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57488524913788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58269035816193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56187665462494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53585982322693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48642790317535</t>
+    <t xml:space="preserve">1.52892208099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50637423992157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5748850107193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58269023895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56187677383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53585994243622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48642802238464</t>
   </si>
   <si>
     <t xml:space="preserve">1.49510014057159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51157760620117</t>
+    <t xml:space="preserve">1.51157748699188</t>
   </si>
   <si>
     <t xml:space="preserve">1.48902952671051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48035740852356</t>
+    <t xml:space="preserve">1.48035728931427</t>
   </si>
   <si>
     <t xml:space="preserve">1.48816251754761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51591372489929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56881463527679</t>
+    <t xml:space="preserve">1.51591360569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5688145160675</t>
   </si>
   <si>
     <t xml:space="preserve">1.57054901123047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64686501026154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78648853302002</t>
+    <t xml:space="preserve">1.64686512947083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78648865222931</t>
   </si>
   <si>
     <t xml:space="preserve">1.7604718208313</t>
@@ -920,73 +920,73 @@
     <t xml:space="preserve">2.15245890617371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9998265504837</t>
+    <t xml:space="preserve">1.99982643127441</t>
   </si>
   <si>
     <t xml:space="preserve">2.05879807472229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00329566001892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9512619972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05186009407043</t>
+    <t xml:space="preserve">2.00329542160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95126187801361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05186033248901</t>
   </si>
   <si>
     <t xml:space="preserve">2.01543664932251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98074758052826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90443193912506</t>
+    <t xml:space="preserve">1.98074769973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90443181991577</t>
   </si>
   <si>
     <t xml:space="preserve">1.90790057182312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91657269001007</t>
+    <t xml:space="preserve">1.91657280921936</t>
   </si>
   <si>
     <t xml:space="preserve">1.90616595745087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84892892837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87321150302887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83158457279205</t>
+    <t xml:space="preserve">1.84892904758453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87321138381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83158445358276</t>
   </si>
   <si>
     <t xml:space="preserve">1.84719467163086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93218290805817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93738615512848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92524492740631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94258952140808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97727859020233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02063989639282</t>
+    <t xml:space="preserve">1.93218266963959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93738627433777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9252450466156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94258987903595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97727882862091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0206401348114</t>
   </si>
   <si>
     <t xml:space="preserve">2.06920480728149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.011967420578</t>
+    <t xml:space="preserve">2.01196789741516</t>
   </si>
   <si>
     <t xml:space="preserve">2.03971886634827</t>
@@ -995,19 +995,19 @@
     <t xml:space="preserve">2.01370239257812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99462342262268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94432413578033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90269720554352</t>
+    <t xml:space="preserve">1.99462306499481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94432425498962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90269732475281</t>
   </si>
   <si>
     <t xml:space="preserve">1.82117760181427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91310393810272</t>
+    <t xml:space="preserve">1.91310381889343</t>
   </si>
   <si>
     <t xml:space="preserve">1.72144663333893</t>
@@ -1016,22 +1016,22 @@
     <t xml:space="preserve">1.67114746570587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69976592063904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68762469291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67895257472992</t>
+    <t xml:space="preserve">1.69976603984833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68762457370758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67895245552063</t>
   </si>
   <si>
     <t xml:space="preserve">1.63992714881897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64773225784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62865316867828</t>
+    <t xml:space="preserve">1.64773213863373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62865328788757</t>
   </si>
   <si>
     <t xml:space="preserve">1.62691879272461</t>
@@ -1046,13 +1046,13 @@
     <t xml:space="preserve">1.63905990123749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6485995054245</t>
+    <t xml:space="preserve">1.64859938621521</t>
   </si>
   <si>
     <t xml:space="preserve">1.6650767326355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6910936832428</t>
+    <t xml:space="preserve">1.69109380245209</t>
   </si>
   <si>
     <t xml:space="preserve">1.72925162315369</t>
@@ -1064,22 +1064,22 @@
     <t xml:space="preserve">1.65640449523926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63038778305054</t>
+    <t xml:space="preserve">1.63038766384125</t>
   </si>
   <si>
     <t xml:space="preserve">1.66681122779846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68155419826508</t>
+    <t xml:space="preserve">1.68155407905579</t>
   </si>
   <si>
     <t xml:space="preserve">1.68935918807983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67721796035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63385653495789</t>
+    <t xml:space="preserve">1.67721807956696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63385665416718</t>
   </si>
   <si>
     <t xml:space="preserve">1.62171542644501</t>
@@ -1103,10 +1103,10 @@
     <t xml:space="preserve">1.72578275203705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72751724720001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71190702915192</t>
+    <t xml:space="preserve">1.72751712799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71190714836121</t>
   </si>
   <si>
     <t xml:space="preserve">1.74312722682953</t>
@@ -1115,10 +1115,10 @@
     <t xml:space="preserve">1.77781629562378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77348017692566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80383324623108</t>
+    <t xml:space="preserve">1.77348029613495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80383312702179</t>
   </si>
   <si>
     <t xml:space="preserve">1.93391740322113</t>
@@ -1127,34 +1127,34 @@
     <t xml:space="preserve">1.88188374042511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95559823513031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88621962070465</t>
+    <t xml:space="preserve">1.95559811592102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88621973991394</t>
   </si>
   <si>
     <t xml:space="preserve">1.81684160232544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89489221572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8081693649292</t>
+    <t xml:space="preserve">1.89489197731018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80816924571991</t>
   </si>
   <si>
     <t xml:space="preserve">1.82984983921051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85153090953827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78215253353119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81250548362732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79082489013672</t>
+    <t xml:space="preserve">1.8515305519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78215265274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81250536441803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79082477092743</t>
   </si>
   <si>
     <t xml:space="preserve">1.73445498943329</t>
@@ -1166,13 +1166,13 @@
     <t xml:space="preserve">1.96860635280609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89922821521759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89055597782135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87754738330841</t>
+    <t xml:space="preserve">1.89922833442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89055609703064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8775475025177</t>
   </si>
   <si>
     <t xml:space="preserve">1.83418619632721</t>
@@ -1187,22 +1187,22 @@
     <t xml:space="preserve">1.83852219581604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86020302772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97294282913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98161494731903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92958116531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98595094680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0466570854187</t>
+    <t xml:space="preserve">1.86020278930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97294235229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98161482810974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92958092689514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98595106601715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04665684700012</t>
   </si>
   <si>
     <t xml:space="preserve">2.03364849090576</t>
@@ -1211,10 +1211,10 @@
     <t xml:space="preserve">2.042320728302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07267379760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08134627342224</t>
+    <t xml:space="preserve">2.072674036026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08134603500366</t>
   </si>
   <si>
     <t xml:space="preserve">2.1116988658905</t>
@@ -1223,10 +1223,10 @@
     <t xml:space="preserve">2.15072417259216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05532884597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18541312217712</t>
+    <t xml:space="preserve">2.05532932281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1854133605957</t>
   </si>
   <si>
     <t xml:space="preserve">2.33717799186707</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">2.3024890422821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28080821037292</t>
+    <t xml:space="preserve">2.2808084487915</t>
   </si>
   <si>
     <t xml:space="preserve">2.21143007278442</t>
@@ -1244,19 +1244,19 @@
     <t xml:space="preserve">2.30682516098022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28514432907104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44991779327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48894309997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59300994873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38921189308167</t>
+    <t xml:space="preserve">2.28514456748962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44991755485535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48894286155701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59301018714905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38921213150024</t>
   </si>
   <si>
     <t xml:space="preserve">2.49761557579041</t>
@@ -1268,19 +1268,19 @@
     <t xml:space="preserve">2.62769937515259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71442198753357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76645588874817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83583402633667</t>
+    <t xml:space="preserve">2.71442246437073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76645565032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83583378791809</t>
   </si>
   <si>
     <t xml:space="preserve">2.91388440132141</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92255640029907</t>
+    <t xml:space="preserve">2.92255663871765</t>
   </si>
   <si>
     <t xml:space="preserve">2.93122911453247</t>
@@ -1304,22 +1304,22 @@
     <t xml:space="preserve">3.21741390228271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25643944740295</t>
+    <t xml:space="preserve">3.25643920898438</t>
   </si>
   <si>
     <t xml:space="preserve">3.36050653457642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20874190330505</t>
+    <t xml:space="preserve">3.20874166488647</t>
   </si>
   <si>
     <t xml:space="preserve">3.36917877197266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26511168479919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22175025939941</t>
+    <t xml:space="preserve">3.26511144638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22175002098083</t>
   </si>
   <si>
     <t xml:space="preserve">3.33882570266724</t>
@@ -1331,7 +1331,7 @@
     <t xml:space="preserve">3.34749817848206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50793552398682</t>
+    <t xml:space="preserve">3.50793528556824</t>
   </si>
   <si>
     <t xml:space="preserve">3.48625445365906</t>
@@ -1340,43 +1340,43 @@
     <t xml:space="preserve">3.55563259124756</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51227140426636</t>
+    <t xml:space="preserve">3.51227164268494</t>
   </si>
   <si>
     <t xml:space="preserve">3.62934684753418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6640362739563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73341417312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80712866783142</t>
+    <t xml:space="preserve">3.66403603553772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7334144115448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80712890625</t>
   </si>
   <si>
     <t xml:space="preserve">3.90686011314392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07596921920776</t>
+    <t xml:space="preserve">4.07596874237061</t>
   </si>
   <si>
     <t xml:space="preserve">4.0456166267395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09764957427979</t>
+    <t xml:space="preserve">4.09765005111694</t>
   </si>
   <si>
     <t xml:space="preserve">3.86783480644226</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04127979278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94588565826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97190189361572</t>
+    <t xml:space="preserve">4.0412802696228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94588470458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9719021320343</t>
   </si>
   <si>
     <t xml:space="preserve">3.7117338180542</t>
@@ -1391,13 +1391,13 @@
     <t xml:space="preserve">4.24941492080688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25375080108643</t>
+    <t xml:space="preserve">4.25375127792358</t>
   </si>
   <si>
     <t xml:space="preserve">4.28410387039185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62232255935669</t>
+    <t xml:space="preserve">4.62232303619385</t>
   </si>
   <si>
     <t xml:space="preserve">4.57896137237549</t>
@@ -1406,28 +1406,28 @@
     <t xml:space="preserve">4.74373388290405</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75240707397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05593585968018</t>
+    <t xml:space="preserve">4.75240659713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05593633651733</t>
   </si>
   <si>
     <t xml:space="preserve">4.98655796051025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95186948776245</t>
+    <t xml:space="preserve">4.95186901092529</t>
   </si>
   <si>
     <t xml:space="preserve">4.87381839752197</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31879281997681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80444049835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97788619995117</t>
+    <t xml:space="preserve">4.31879329681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80444002151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97788572311401</t>
   </si>
   <si>
     <t xml:space="preserve">5.01257514953613</t>
@@ -1436,22 +1436,22 @@
     <t xml:space="preserve">5.03859186172485</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91717958450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82178497314453</t>
+    <t xml:space="preserve">4.91718006134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82178449630737</t>
   </si>
   <si>
     <t xml:space="preserve">4.85647392272949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89116287231445</t>
+    <t xml:space="preserve">4.89116334915161</t>
   </si>
   <si>
     <t xml:space="preserve">4.83045721054077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76107835769653</t>
+    <t xml:space="preserve">4.76107931137085</t>
   </si>
   <si>
     <t xml:space="preserve">4.54427194595337</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">4.60497808456421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58763313293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64833927154541</t>
+    <t xml:space="preserve">4.58763360977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64833974838257</t>
   </si>
   <si>
     <t xml:space="preserve">4.61365032196045</t>
@@ -1475,76 +1475,76 @@
     <t xml:space="preserve">4.53560018539429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47489356994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40551567077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18437242507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1887092590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24074268341064</t>
+    <t xml:space="preserve">4.47489404678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40551614761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1843729019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18870878219604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24074220657349</t>
   </si>
   <si>
     <t xml:space="preserve">4.084641456604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92854022979736</t>
+    <t xml:space="preserve">3.92854070663452</t>
   </si>
   <si>
     <t xml:space="preserve">3.91553211212158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85916233062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7811119556427</t>
+    <t xml:space="preserve">3.85916185379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78111219406128</t>
   </si>
   <si>
     <t xml:space="preserve">4.14101123809814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62501096725464</t>
+    <t xml:space="preserve">3.62501072883606</t>
   </si>
   <si>
     <t xml:space="preserve">3.31280899047852</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28679227828979</t>
+    <t xml:space="preserve">3.28679203987122</t>
   </si>
   <si>
     <t xml:space="preserve">3.14369964599609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00927925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09166622161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03529644012451</t>
+    <t xml:space="preserve">3.00927972793579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09166598320007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03529620170593</t>
   </si>
   <si>
     <t xml:space="preserve">3.04830479621887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07865786552429</t>
+    <t xml:space="preserve">3.07865738868713</t>
   </si>
   <si>
     <t xml:space="preserve">2.96158170700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89653968811035</t>
+    <t xml:space="preserve">2.89653992652893</t>
   </si>
   <si>
     <t xml:space="preserve">2.90521216392517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02662420272827</t>
+    <t xml:space="preserve">3.02662396430969</t>
   </si>
   <si>
     <t xml:space="preserve">2.75344729423523</t>
@@ -1553,37 +1553,37 @@
     <t xml:space="preserve">2.80548095703125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88786745071411</t>
+    <t xml:space="preserve">2.88786768913269</t>
   </si>
   <si>
     <t xml:space="preserve">3.04396843910217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26077556610107</t>
+    <t xml:space="preserve">3.2607753276825</t>
   </si>
   <si>
     <t xml:space="preserve">3.24343085289001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19139719009399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4255485534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43855714797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39519596099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20440554618835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06998538970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86618685722351</t>
+    <t xml:space="preserve">3.19139695167542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42554879188538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43855690956116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39519548416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20440578460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06998515129089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86618709564209</t>
   </si>
   <si>
     <t xml:space="preserve">2.93990135192871</t>
@@ -1592,13 +1592,13 @@
     <t xml:space="preserve">2.88353133201599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97459030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02228784561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3821873664856</t>
+    <t xml:space="preserve">2.97459053993225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02228760719299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38218760490417</t>
   </si>
   <si>
     <t xml:space="preserve">3.32148122787476</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">3.15670824050903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11768269538879</t>
+    <t xml:space="preserve">3.11768293380737</t>
   </si>
   <si>
     <t xml:space="preserve">3.08732986450195</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">3.06564927101135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81848931312561</t>
+    <t xml:space="preserve">2.81848907470703</t>
   </si>
   <si>
     <t xml:space="preserve">2.68840503692627</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">2.73176670074463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63203573226929</t>
+    <t xml:space="preserve">2.63203525543213</t>
   </si>
   <si>
     <t xml:space="preserve">2.98759865760803</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">3.17838883399963</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10467433929443</t>
+    <t xml:space="preserve">3.10467457771301</t>
   </si>
   <si>
     <t xml:space="preserve">3.16104435920715</t>
@@ -1655,16 +1655,16 @@
     <t xml:space="preserve">3.46023774147034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5903217792511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88517904281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9025239944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8548264503479</t>
+    <t xml:space="preserve">3.59032154083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8851797580719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90252375602722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85482621192932</t>
   </si>
   <si>
     <t xml:space="preserve">4.11499452590942</t>
@@ -1673,31 +1673,31 @@
     <t xml:space="preserve">4.27543163299561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10198593139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14534759521484</t>
+    <t xml:space="preserve">4.10198640823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.145348072052</t>
   </si>
   <si>
     <t xml:space="preserve">4.1323390007019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95889377593994</t>
+    <t xml:space="preserve">3.95889401435852</t>
   </si>
   <si>
     <t xml:space="preserve">3.82447338104248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96756529808044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9415488243103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99791884422302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00659132003784</t>
+    <t xml:space="preserve">3.9675657749176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94154906272888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9979190826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00659084320068</t>
   </si>
   <si>
     <t xml:space="preserve">4.06296062469482</t>
@@ -1709,46 +1709,46 @@
     <t xml:space="preserve">4.01526355743408</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0933141708374</t>
+    <t xml:space="preserve">4.09331369400024</t>
   </si>
   <si>
     <t xml:space="preserve">4.03260803222656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98924684524536</t>
+    <t xml:space="preserve">3.98924612998962</t>
   </si>
   <si>
     <t xml:space="preserve">3.9242045879364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82880926132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75943160057068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74642300605774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56864094734192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77677607536316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24507856369019</t>
+    <t xml:space="preserve">3.8288094997406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75943112373352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74642276763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5686411857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.776775598526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24507904052734</t>
   </si>
   <si>
     <t xml:space="preserve">4.17136430740356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0889778137207</t>
+    <t xml:space="preserve">4.08897733688354</t>
   </si>
   <si>
     <t xml:space="preserve">4.06729698181152</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16269254684448</t>
+    <t xml:space="preserve">4.16269207000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.21906185150146</t>
@@ -1760,16 +1760,16 @@
     <t xml:space="preserve">4.20171737670898</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68302869796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88249111175537</t>
+    <t xml:space="preserve">4.68302822113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88249063491821</t>
   </si>
   <si>
     <t xml:space="preserve">4.76975107192993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72638988494873</t>
+    <t xml:space="preserve">4.72638940811157</t>
   </si>
   <si>
     <t xml:space="preserve">4.63966703414917</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">4.39684343338013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91119647026062</t>
+    <t xml:space="preserve">3.91119623184204</t>
   </si>
   <si>
     <t xml:space="preserve">4.04995250701904</t>
@@ -1799,22 +1799,22 @@
     <t xml:space="preserve">4.01130485534668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91760349273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22547912597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00684261322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83282613754272</t>
+    <t xml:space="preserve">3.91760301589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2254786491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00684213638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8328263759613</t>
   </si>
   <si>
     <t xml:space="preserve">3.85513591766357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85959792137146</t>
+    <t xml:space="preserve">3.85959768295288</t>
   </si>
   <si>
     <t xml:space="preserve">3.93098950386047</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">4.03807640075684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95776081085205</t>
+    <t xml:space="preserve">3.95776104927063</t>
   </si>
   <si>
     <t xml:space="preserve">3.79266834259033</t>
@@ -1856,16 +1856,16 @@
     <t xml:space="preserve">3.67219519615173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59634232521057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58741807937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64096140861511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64988589286804</t>
+    <t xml:space="preserve">3.59634208679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5874183177948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64096164703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64988565444946</t>
   </si>
   <si>
     <t xml:space="preserve">3.5115647315979</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">3.41786336898804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44909715652466</t>
+    <t xml:space="preserve">3.44909739494324</t>
   </si>
   <si>
     <t xml:space="preserve">3.4223256111145</t>
@@ -1889,7 +1889,7 @@
     <t xml:space="preserve">3.47140717506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50710296630859</t>
+    <t xml:space="preserve">3.50710272789001</t>
   </si>
   <si>
     <t xml:space="preserve">3.41340160369873</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">3.36878204345703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34647226333618</t>
+    <t xml:space="preserve">3.3464720249176</t>
   </si>
   <si>
     <t xml:space="preserve">3.31523823738098</t>
@@ -1910,16 +1910,16 @@
     <t xml:space="preserve">3.32862424850464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36432027816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39555358886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35539603233337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31077671051025</t>
+    <t xml:space="preserve">3.36432003974915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39555382728577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35539627075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31077647209167</t>
   </si>
   <si>
     <t xml:space="preserve">3.27954268455505</t>
@@ -1931,7 +1931,7 @@
     <t xml:space="preserve">3.38216781616211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40001583099365</t>
+    <t xml:space="preserve">3.40001559257507</t>
   </si>
   <si>
     <t xml:space="preserve">3.30631422996521</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">3.33308625221252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35093426704407</t>
+    <t xml:space="preserve">3.35093402862549</t>
   </si>
   <si>
     <t xml:space="preserve">3.52941250801086</t>
@@ -1958,16 +1958,16 @@
     <t xml:space="preserve">3.8105161190033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80605459213257</t>
+    <t xml:space="preserve">3.80605435371399</t>
   </si>
   <si>
     <t xml:space="preserve">3.76589632034302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6008038520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5561842918396</t>
+    <t xml:space="preserve">3.60080409049988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55618453025818</t>
   </si>
   <si>
     <t xml:space="preserve">3.4669451713562</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">3.70789122581482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6766574382782</t>
+    <t xml:space="preserve">3.67665719985962</t>
   </si>
   <si>
     <t xml:space="preserve">3.73912501335144</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">3.66773366928101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69896745681763</t>
+    <t xml:space="preserve">3.69896721839905</t>
   </si>
   <si>
     <t xml:space="preserve">3.7212769985199</t>
@@ -2018,13 +2018,13 @@
     <t xml:space="preserve">3.56957030296326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96668553352356</t>
+    <t xml:space="preserve">3.96668529510498</t>
   </si>
   <si>
     <t xml:space="preserve">3.73466277122498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69450497627258</t>
+    <t xml:space="preserve">3.69450521469116</t>
   </si>
   <si>
     <t xml:space="preserve">3.70342922210693</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">3.56510829925537</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93991351127625</t>
+    <t xml:space="preserve">3.93991327285767</t>
   </si>
   <si>
     <t xml:space="preserve">4.06038618087769</t>
@@ -2051,25 +2051,25 @@
     <t xml:space="preserve">3.91314172744751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98899459838867</t>
+    <t xml:space="preserve">3.98899435997009</t>
   </si>
   <si>
     <t xml:space="preserve">3.98007082939148</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12731552124023</t>
+    <t xml:space="preserve">4.12731599807739</t>
   </si>
   <si>
     <t xml:space="preserve">4.05146217346191</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09161996841431</t>
+    <t xml:space="preserve">4.09161949157715</t>
   </si>
   <si>
     <t xml:space="preserve">4.03361415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92652702331543</t>
+    <t xml:space="preserve">3.92652726173401</t>
   </si>
   <si>
     <t xml:space="preserve">3.90867972373962</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">3.90421748161316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0425386428833</t>
+    <t xml:space="preserve">4.04253911972046</t>
   </si>
   <si>
     <t xml:space="preserve">3.93545126914978</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">4.07823419570923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19424486160278</t>
+    <t xml:space="preserve">4.19424438476562</t>
   </si>
   <si>
     <t xml:space="preserve">4.00238037109375</t>
@@ -2099,7 +2099,7 @@
     <t xml:space="preserve">4.1763973236084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.087158203125</t>
+    <t xml:space="preserve">4.08715772628784</t>
   </si>
   <si>
     <t xml:space="preserve">4.21655464172363</t>
@@ -2108,10 +2108,10 @@
     <t xml:space="preserve">4.46196269989014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53335428237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64044094085693</t>
+    <t xml:space="preserve">4.53335475921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64044141769409</t>
   </si>
   <si>
     <t xml:space="preserve">4.58689785003662</t>
@@ -2123,25 +2123,25 @@
     <t xml:space="preserve">4.7564525604248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78322410583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68506097793579</t>
+    <t xml:space="preserve">4.78322458267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68506050109863</t>
   </si>
   <si>
     <t xml:space="preserve">4.83676767349243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81892013549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90815877914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00632286071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89923524856567</t>
+    <t xml:space="preserve">4.81891965866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90815925598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00632238388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89923477172852</t>
   </si>
   <si>
     <t xml:space="preserve">4.85461568832397</t>
@@ -2171,19 +2171,19 @@
     <t xml:space="preserve">4.82784414291382</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80999565124512</t>
+    <t xml:space="preserve">4.80999612808228</t>
   </si>
   <si>
     <t xml:space="preserve">4.94385480880737</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06878995895386</t>
+    <t xml:space="preserve">5.0687894821167</t>
   </si>
   <si>
     <t xml:space="preserve">4.99739837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23834419250488</t>
+    <t xml:space="preserve">5.23834466934204</t>
   </si>
   <si>
     <t xml:space="preserve">5.45251893997192</t>
@@ -2201,10 +2201,10 @@
     <t xml:space="preserve">5.15802907943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88138675689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70290851593018</t>
+    <t xml:space="preserve">4.88138723373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70290899276733</t>
   </si>
   <si>
     <t xml:space="preserve">4.71183300018311</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">4.63151741027832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67613649368286</t>
+    <t xml:space="preserve">4.67613697052002</t>
   </si>
   <si>
     <t xml:space="preserve">4.56012630462646</t>
@@ -2231,13 +2231,13 @@
     <t xml:space="preserve">4.02022886276245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98453330993652</t>
+    <t xml:space="preserve">3.98453307151794</t>
   </si>
   <si>
     <t xml:space="preserve">3.94883728027344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80159258842468</t>
+    <t xml:space="preserve">3.80159282684326</t>
   </si>
   <si>
     <t xml:space="preserve">3.12783622741699</t>
@@ -2252,25 +2252,25 @@
     <t xml:space="preserve">2.72625946998596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75749278068542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44961762428284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45854163169861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14174199104309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99895942211151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10604619979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25775337219238</t>
+    <t xml:space="preserve">2.757493019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44961738586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45854187011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14174222946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9989595413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10604643821716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2577531337738</t>
   </si>
   <si>
     <t xml:space="preserve">2.34699273109436</t>
@@ -2285,13 +2285,13 @@
     <t xml:space="preserve">2.40053629875183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48085141181946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45407938957214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46300363540649</t>
+    <t xml:space="preserve">2.48085117340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45407962799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46300339698792</t>
   </si>
   <si>
     <t xml:space="preserve">2.56116652488708</t>
@@ -2300,13 +2300,13 @@
     <t xml:space="preserve">2.73964524269104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23938512802124</t>
+    <t xml:space="preserve">3.23938488960266</t>
   </si>
   <si>
     <t xml:space="preserve">3.20368933677673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10998797416687</t>
+    <t xml:space="preserve">3.10998821258545</t>
   </si>
   <si>
     <t xml:space="preserve">2.91812372207642</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">2.99843907356262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9359712600708</t>
+    <t xml:space="preserve">2.93597149848938</t>
   </si>
   <si>
     <t xml:space="preserve">2.94489550590515</t>
@@ -2330,13 +2330,13 @@
     <t xml:space="preserve">2.97612929344177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85565638542175</t>
+    <t xml:space="preserve">2.85565614700317</t>
   </si>
   <si>
     <t xml:space="preserve">2.98059105873108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00290083885193</t>
+    <t xml:space="preserve">3.00290107727051</t>
   </si>
   <si>
     <t xml:space="preserve">3.13229775428772</t>
@@ -4134,6 +4134,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.55999994277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46000003814697</t>
   </si>
 </sst>
 </file>
@@ -69108,7 +69111,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6493981481</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>49787</v>
@@ -69129,6 +69132,32 @@
         <v>1373</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6494328704</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>46882</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>7.65000009536743</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>7.42000007629395</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>7.57999992370605</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>7.46000003814697</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>1374</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95473074913025</t>
+    <t xml:space="preserve">1.95473062992096</t>
   </si>
   <si>
     <t xml:space="preserve">FM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95993411540985</t>
+    <t xml:space="preserve">1.95993423461914</t>
   </si>
   <si>
     <t xml:space="preserve">1.9096348285675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85586678981781</t>
+    <t xml:space="preserve">1.8558669090271</t>
   </si>
   <si>
     <t xml:space="preserve">1.86453914642334</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">1.76914405822754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74486184120178</t>
+    <t xml:space="preserve">1.74486172199249</t>
   </si>
   <si>
     <t xml:space="preserve">1.69542968273163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61824655532837</t>
+    <t xml:space="preserve">1.61824667453766</t>
   </si>
   <si>
     <t xml:space="preserve">1.52285146713257</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">1.23059582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43873035907745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39710342884064</t>
+    <t xml:space="preserve">1.43873047828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39710354804993</t>
   </si>
   <si>
     <t xml:space="preserve">1.50030362606049</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">1.48295903205872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46561443805695</t>
+    <t xml:space="preserve">1.46561455726624</t>
   </si>
   <si>
     <t xml:space="preserve">1.52111709117889</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">1.51678085327148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49423313140869</t>
+    <t xml:space="preserve">1.4942330121994</t>
   </si>
   <si>
     <t xml:space="preserve">1.47688841819763</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">1.47515392303467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5098432302475</t>
+    <t xml:space="preserve">1.50984311103821</t>
   </si>
   <si>
     <t xml:space="preserve">1.56014239788055</t>
@@ -215,19 +215,19 @@
     <t xml:space="preserve">1.48122453689575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41791713237762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39970517158508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35200762748718</t>
+    <t xml:space="preserve">1.41791701316833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39970505237579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35200774669647</t>
   </si>
   <si>
     <t xml:space="preserve">1.39190006256104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46041107177734</t>
+    <t xml:space="preserve">1.46041119098663</t>
   </si>
   <si>
     <t xml:space="preserve">1.57228338718414</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">1.60437095165253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60870695114136</t>
+    <t xml:space="preserve">1.60870683193207</t>
   </si>
   <si>
     <t xml:space="preserve">1.62518429756165</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">1.58876073360443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49249851703644</t>
+    <t xml:space="preserve">1.49249839782715</t>
   </si>
   <si>
     <t xml:space="preserve">1.45780944824219</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">1.55060279369354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56708014011383</t>
+    <t xml:space="preserve">1.56708002090454</t>
   </si>
   <si>
     <t xml:space="preserve">1.5740180015564</t>
@@ -317,10 +317,10 @@
     <t xml:space="preserve">1.45000445842743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38929843902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40057241916656</t>
+    <t xml:space="preserve">1.38929855823517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40057253837585</t>
   </si>
   <si>
     <t xml:space="preserve">1.3875640630722</t>
@@ -332,19 +332,19 @@
     <t xml:space="preserve">1.49163126945496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48382616043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32338929176331</t>
+    <t xml:space="preserve">1.4838262796402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32338917255402</t>
   </si>
   <si>
     <t xml:space="preserve">1.3294597864151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3884311914444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39016580581665</t>
+    <t xml:space="preserve">1.38843107223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39016568660736</t>
   </si>
   <si>
     <t xml:space="preserve">1.35981273651123</t>
@@ -359,22 +359,22 @@
     <t xml:space="preserve">1.30084133148193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30257558822632</t>
+    <t xml:space="preserve">1.30257570743561</t>
   </si>
   <si>
     <t xml:space="preserve">1.36154723167419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37802445888519</t>
+    <t xml:space="preserve">1.3780243396759</t>
   </si>
   <si>
     <t xml:space="preserve">1.38236057758331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39623630046844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.377157330513</t>
+    <t xml:space="preserve">1.39623618125916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37715744972229</t>
   </si>
   <si>
     <t xml:space="preserve">1.40490853786469</t>
@@ -389,13 +389,13 @@
     <t xml:space="preserve">1.393634557724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42225301265717</t>
+    <t xml:space="preserve">1.42225313186646</t>
   </si>
   <si>
     <t xml:space="preserve">1.42832362651825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37889170646667</t>
+    <t xml:space="preserve">1.37889182567596</t>
   </si>
   <si>
     <t xml:space="preserve">1.38062620162964</t>
@@ -404,13 +404,13 @@
     <t xml:space="preserve">1.36588335037231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35634386539459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35460937023163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34333550930023</t>
+    <t xml:space="preserve">1.3563437461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35460925102234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34333539009094</t>
   </si>
   <si>
     <t xml:space="preserve">1.33119428157806</t>
@@ -419,28 +419,28 @@
     <t xml:space="preserve">1.32685804367065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30170857906342</t>
+    <t xml:space="preserve">1.30170845985413</t>
   </si>
   <si>
     <t xml:space="preserve">1.3077791929245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34767162799835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34506988525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33379578590393</t>
+    <t xml:space="preserve">1.34767174720764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34506976604462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33379590511322</t>
   </si>
   <si>
     <t xml:space="preserve">1.37108671665192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35547649860382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34940588474274</t>
+    <t xml:space="preserve">1.35547661781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34940600395203</t>
   </si>
   <si>
     <t xml:space="preserve">1.33813202381134</t>
@@ -449,46 +449,46 @@
     <t xml:space="preserve">1.34853863716125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41704964637756</t>
+    <t xml:space="preserve">1.41704976558685</t>
   </si>
   <si>
     <t xml:space="preserve">1.40317416191101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39536893367767</t>
+    <t xml:space="preserve">1.39536905288696</t>
   </si>
   <si>
     <t xml:space="preserve">1.41097915172577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36501610279083</t>
+    <t xml:space="preserve">1.36501598358154</t>
   </si>
   <si>
     <t xml:space="preserve">1.38322794437408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36761784553528</t>
+    <t xml:space="preserve">1.36761796474457</t>
   </si>
   <si>
     <t xml:space="preserve">1.38149344921112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39797079563141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37455570697784</t>
+    <t xml:space="preserve">1.39797067642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37455558776855</t>
   </si>
   <si>
     <t xml:space="preserve">1.41358077526093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42138588428497</t>
+    <t xml:space="preserve">1.42138576507568</t>
   </si>
   <si>
     <t xml:space="preserve">1.41271352767944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40924465656281</t>
+    <t xml:space="preserve">1.40924477577209</t>
   </si>
   <si>
     <t xml:space="preserve">1.42572212219238</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">1.35894548892975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34680438041687</t>
+    <t xml:space="preserve">1.34680426120758</t>
   </si>
   <si>
     <t xml:space="preserve">1.36414885520935</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">1.31992018222809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3129825592041</t>
+    <t xml:space="preserve">1.31298243999481</t>
   </si>
   <si>
     <t xml:space="preserve">1.17942941188812</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">1.12305963039398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13346636295319</t>
+    <t xml:space="preserve">1.13346648216248</t>
   </si>
   <si>
     <t xml:space="preserve">1.11438727378845</t>
@@ -569,22 +569,22 @@
     <t xml:space="preserve">1.11612176895142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11525452136993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09791004657745</t>
+    <t xml:space="preserve">1.11525464057922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09790992736816</t>
   </si>
   <si>
     <t xml:space="preserve">1.09270668029785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07536208629608</t>
+    <t xml:space="preserve">1.07536220550537</t>
   </si>
   <si>
     <t xml:space="preserve">1.07276034355164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10398066043854</t>
+    <t xml:space="preserve">1.10398054122925</t>
   </si>
   <si>
     <t xml:space="preserve">1.1542797088623</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">1.16208481788635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17856216430664</t>
+    <t xml:space="preserve">1.17856204509735</t>
   </si>
   <si>
     <t xml:space="preserve">1.18289828300476</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">1.20544624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23493206501007</t>
+    <t xml:space="preserve">1.23493194580078</t>
   </si>
   <si>
     <t xml:space="preserve">1.24533867835999</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">1.22192347049713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23666656017303</t>
+    <t xml:space="preserve">1.23666644096375</t>
   </si>
   <si>
     <t xml:space="preserve">1.26875388622284</t>
@@ -635,28 +635,28 @@
     <t xml:space="preserve">1.38409507274628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3988379240036</t>
+    <t xml:space="preserve">1.39883804321289</t>
   </si>
   <si>
     <t xml:space="preserve">1.38669681549072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35721099376678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34593713283539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33292865753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28869986534119</t>
+    <t xml:space="preserve">1.35721111297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34593725204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33292853832245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28869998455048</t>
   </si>
   <si>
     <t xml:space="preserve">1.25747990608215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2331976890564</t>
+    <t xml:space="preserve">1.23319756984711</t>
   </si>
   <si>
     <t xml:space="preserve">1.2444714307785</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">1.22712695598602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25661277770996</t>
+    <t xml:space="preserve">1.25661265850067</t>
   </si>
   <si>
     <t xml:space="preserve">1.22365808486938</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">1.22625970840454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21325147151947</t>
+    <t xml:space="preserve">1.21325135231018</t>
   </si>
   <si>
     <t xml:space="preserve">1.20891511440277</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">1.21585297584534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21672022342682</t>
+    <t xml:space="preserve">1.21672010421753</t>
   </si>
   <si>
     <t xml:space="preserve">1.19070339202881</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">1.27222275733948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29823958873749</t>
+    <t xml:space="preserve">1.2982394695282</t>
   </si>
   <si>
     <t xml:space="preserve">1.26355040073395</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">1.24967479705811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29043447971344</t>
+    <t xml:space="preserve">1.29043459892273</t>
   </si>
   <si>
     <t xml:space="preserve">1.29303622245789</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">1.2704883813858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26528477668762</t>
+    <t xml:space="preserve">1.26528489589691</t>
   </si>
   <si>
     <t xml:space="preserve">1.28436398506165</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">1.28523099422455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28696548938751</t>
+    <t xml:space="preserve">1.2869656085968</t>
   </si>
   <si>
     <t xml:space="preserve">1.3398665189743</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">1.33899927139282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41184639930725</t>
+    <t xml:space="preserve">1.41184628009796</t>
   </si>
   <si>
     <t xml:space="preserve">1.57835412025452</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">1.49856913089752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50724136829376</t>
+    <t xml:space="preserve">1.50724148750305</t>
   </si>
   <si>
     <t xml:space="preserve">1.50203800201416</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">1.47168505191803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48729515075684</t>
+    <t xml:space="preserve">1.48729526996613</t>
   </si>
   <si>
     <t xml:space="preserve">1.47602117061615</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">1.53585982322693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48642802238464</t>
+    <t xml:space="preserve">1.48642790317535</t>
   </si>
   <si>
     <t xml:space="preserve">1.49510014057159</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">1.48035740852356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48816251754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51591372489929</t>
+    <t xml:space="preserve">1.48816239833832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51591360569</t>
   </si>
   <si>
     <t xml:space="preserve">1.5688145160675</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">1.57054901123047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64686512947083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78648853302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7604718208313</t>
+    <t xml:space="preserve">1.64686501026154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78648841381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76047170162201</t>
   </si>
   <si>
     <t xml:space="preserve">1.85933589935303</t>
@@ -917,10 +917,10 @@
     <t xml:space="preserve">1.84199142456055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15245890617371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9998265504837</t>
+    <t xml:space="preserve">2.15245866775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99982666969299</t>
   </si>
   <si>
     <t xml:space="preserve">2.05879807472229</t>
@@ -929,19 +929,19 @@
     <t xml:space="preserve">2.00329542160034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9512619972229</t>
+    <t xml:space="preserve">1.95126187801361</t>
   </si>
   <si>
     <t xml:space="preserve">2.05186009407043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01543664932251</t>
+    <t xml:space="preserve">2.01543641090393</t>
   </si>
   <si>
     <t xml:space="preserve">1.98074758052826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90443181991577</t>
+    <t xml:space="preserve">1.90443170070648</t>
   </si>
   <si>
     <t xml:space="preserve">1.90790033340454</t>
@@ -953,13 +953,13 @@
     <t xml:space="preserve">1.90616607666016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84892892837524</t>
+    <t xml:space="preserve">1.84892904758453</t>
   </si>
   <si>
     <t xml:space="preserve">1.87321162223816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83158457279205</t>
+    <t xml:space="preserve">1.83158445358276</t>
   </si>
   <si>
     <t xml:space="preserve">1.84719467163086</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">1.93218290805817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93738615512848</t>
+    <t xml:space="preserve">1.93738627433777</t>
   </si>
   <si>
     <t xml:space="preserve">1.92524516582489</t>
@@ -977,13 +977,13 @@
     <t xml:space="preserve">1.94258952140808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97727859020233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02063989639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06920480728149</t>
+    <t xml:space="preserve">1.97727870941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0206401348114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06920456886292</t>
   </si>
   <si>
     <t xml:space="preserve">2.01196765899658</t>
@@ -995,16 +995,16 @@
     <t xml:space="preserve">2.01370239257812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9946231842041</t>
+    <t xml:space="preserve">1.99462306499481</t>
   </si>
   <si>
     <t xml:space="preserve">1.94432413578033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90269708633423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82117760181427</t>
+    <t xml:space="preserve">1.90269696712494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82117772102356</t>
   </si>
   <si>
     <t xml:space="preserve">1.91310405731201</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">1.72144663333893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67114746570587</t>
+    <t xml:space="preserve">1.67114758491516</t>
   </si>
   <si>
     <t xml:space="preserve">1.69976592063904</t>
@@ -1025,16 +1025,16 @@
     <t xml:space="preserve">1.67895245552063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63992714881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64773225784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62865328788757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6269189119339</t>
+    <t xml:space="preserve">1.63992726802826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64773237705231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62865316867828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62691879272461</t>
   </si>
   <si>
     <t xml:space="preserve">1.60350370407104</t>
@@ -1046,19 +1046,19 @@
     <t xml:space="preserve">1.63905990123749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6485995054245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66507685184479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6910936832428</t>
+    <t xml:space="preserve">1.64859938621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6650767326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69109380245209</t>
   </si>
   <si>
     <t xml:space="preserve">1.7292515039444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6754834651947</t>
+    <t xml:space="preserve">1.67548358440399</t>
   </si>
   <si>
     <t xml:space="preserve">1.65640449523926</t>
@@ -1067,16 +1067,16 @@
     <t xml:space="preserve">1.63038766384125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66681134700775</t>
+    <t xml:space="preserve">1.66681122779846</t>
   </si>
   <si>
     <t xml:space="preserve">1.68155419826508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68935906887054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67721796035767</t>
+    <t xml:space="preserve">1.68935918807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67721807956696</t>
   </si>
   <si>
     <t xml:space="preserve">1.63385653495789</t>
@@ -1088,10 +1088,10 @@
     <t xml:space="preserve">1.65727174282074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71537601947784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66854584217072</t>
+    <t xml:space="preserve">1.71537590026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66854572296143</t>
   </si>
   <si>
     <t xml:space="preserve">1.71711039543152</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">1.72751712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71190714836121</t>
+    <t xml:space="preserve">1.71190702915192</t>
   </si>
   <si>
     <t xml:space="preserve">1.74312722682953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77781629562378</t>
+    <t xml:space="preserve">1.77781641483307</t>
   </si>
   <si>
     <t xml:space="preserve">1.77348029613495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80383324623108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93391740322113</t>
+    <t xml:space="preserve">1.80383312702179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93391752243042</t>
   </si>
   <si>
     <t xml:space="preserve">1.88188374042511</t>
@@ -1136,19 +1136,19 @@
     <t xml:space="preserve">1.81684172153473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89489209651947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8081693649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82984983921051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85153090953827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78215253353119</t>
+    <t xml:space="preserve">1.89489197731018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80816924571991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82984972000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85153079032898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7821524143219</t>
   </si>
   <si>
     <t xml:space="preserve">1.81250536441803</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">1.79082489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73445498943329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.764808177948</t>
+    <t xml:space="preserve">1.73445510864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76480805873871</t>
   </si>
   <si>
     <t xml:space="preserve">1.96860635280609</t>
@@ -1172,10 +1172,10 @@
     <t xml:space="preserve">1.89055597782135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87754738330841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83418607711792</t>
+    <t xml:space="preserve">1.8775475025177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83418619632721</t>
   </si>
   <si>
     <t xml:space="preserve">1.84285831451416</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">1.97294282913208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98161470890045</t>
+    <t xml:space="preserve">1.98161494731903</t>
   </si>
   <si>
     <t xml:space="preserve">1.92958116531372</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">2.072674036026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08134603500366</t>
+    <t xml:space="preserve">2.08134579658508</t>
   </si>
   <si>
     <t xml:space="preserve">2.1116988658905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15072417259216</t>
+    <t xml:space="preserve">2.15072441101074</t>
   </si>
   <si>
     <t xml:space="preserve">2.05532884597778</t>
@@ -1238,13 +1238,13 @@
     <t xml:space="preserve">2.2808084487915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21143007278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30682516098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28514432907104</t>
+    <t xml:space="preserve">2.21142983436584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3068253993988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28514456748962</t>
   </si>
   <si>
     <t xml:space="preserve">2.44991755485535</t>
@@ -1268,13 +1268,13 @@
     <t xml:space="preserve">2.62769937515259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71442198753357</t>
+    <t xml:space="preserve">2.71442222595215</t>
   </si>
   <si>
     <t xml:space="preserve">2.76645588874817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83583426475525</t>
+    <t xml:space="preserve">2.83583402633667</t>
   </si>
   <si>
     <t xml:space="preserve">2.91388440132141</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">2.92255663871765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93122887611389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87052297592163</t>
+    <t xml:space="preserve">2.93122911453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87052273750305</t>
   </si>
   <si>
     <t xml:space="preserve">2.92689275741577</t>
@@ -1295,13 +1295,13 @@
     <t xml:space="preserve">3.10033845901489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23909449577332</t>
+    <t xml:space="preserve">3.23909473419189</t>
   </si>
   <si>
     <t xml:space="preserve">3.25210309028625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21741390228271</t>
+    <t xml:space="preserve">3.21741366386414</t>
   </si>
   <si>
     <t xml:space="preserve">3.25643944740295</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">3.20874190330505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36917877197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26511168479919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22175025939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33882570266724</t>
+    <t xml:space="preserve">3.36917901039124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26511144638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22175002098083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33882594108582</t>
   </si>
   <si>
     <t xml:space="preserve">3.27811980247498</t>
@@ -1337,19 +1337,19 @@
     <t xml:space="preserve">3.48625445365906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55563259124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51227140426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62934708595276</t>
+    <t xml:space="preserve">3.55563282966614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51227164268494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62934684753418</t>
   </si>
   <si>
     <t xml:space="preserve">3.6640362739563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7334144115448</t>
+    <t xml:space="preserve">3.73341464996338</t>
   </si>
   <si>
     <t xml:space="preserve">3.80712866783142</t>
@@ -1361,16 +1361,16 @@
     <t xml:space="preserve">4.07596921920776</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04561614990234</t>
+    <t xml:space="preserve">4.0456166267395</t>
   </si>
   <si>
     <t xml:space="preserve">4.09764957427979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86783480644226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04127979278564</t>
+    <t xml:space="preserve">3.86783504486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0412802696228</t>
   </si>
   <si>
     <t xml:space="preserve">3.94588565826416</t>
@@ -1379,16 +1379,16 @@
     <t xml:space="preserve">3.97190237045288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71173357963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9198682308197</t>
+    <t xml:space="preserve">3.7117338180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91986846923828</t>
   </si>
   <si>
     <t xml:space="preserve">4.07163333892822</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24941492080688</t>
+    <t xml:space="preserve">4.24941444396973</t>
   </si>
   <si>
     <t xml:space="preserve">4.25375080108643</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">4.28410387039185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62232255935669</t>
+    <t xml:space="preserve">4.62232208251953</t>
   </si>
   <si>
     <t xml:space="preserve">4.57896137237549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74373388290405</t>
+    <t xml:space="preserve">4.74373435974121</t>
   </si>
   <si>
     <t xml:space="preserve">4.75240707397461</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">5.03859186172485</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91717958450317</t>
+    <t xml:space="preserve">4.91718006134033</t>
   </si>
   <si>
     <t xml:space="preserve">4.82178497314453</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">4.89116287231445</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83045673370361</t>
+    <t xml:space="preserve">4.83045721054077</t>
   </si>
   <si>
     <t xml:space="preserve">4.76107883453369</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">4.54427194595337</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70904588699341</t>
+    <t xml:space="preserve">4.70904541015625</t>
   </si>
   <si>
     <t xml:space="preserve">4.60497760772705</t>
@@ -1469,10 +1469,10 @@
     <t xml:space="preserve">4.64833927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61365032196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53560018539429</t>
+    <t xml:space="preserve">4.61365079879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53559970855713</t>
   </si>
   <si>
     <t xml:space="preserve">4.47489356994629</t>
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">4.08464097976685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92854070663452</t>
+    <t xml:space="preserve">3.92854046821594</t>
   </si>
   <si>
     <t xml:space="preserve">3.91553211212158</t>
@@ -1523,19 +1523,19 @@
     <t xml:space="preserve">3.00927948951721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09166622161865</t>
+    <t xml:space="preserve">3.09166598320007</t>
   </si>
   <si>
     <t xml:space="preserve">3.03529644012451</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04830503463745</t>
+    <t xml:space="preserve">3.04830479621887</t>
   </si>
   <si>
     <t xml:space="preserve">3.07865762710571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96158194541931</t>
+    <t xml:space="preserve">2.96158170700073</t>
   </si>
   <si>
     <t xml:space="preserve">2.89653968811035</t>
@@ -1550,10 +1550,10 @@
     <t xml:space="preserve">2.75344729423523</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80548095703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88786745071411</t>
+    <t xml:space="preserve">2.80548071861267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88786768913269</t>
   </si>
   <si>
     <t xml:space="preserve">3.04396843910217</t>
@@ -1568,13 +1568,13 @@
     <t xml:space="preserve">3.19139719009399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4255485534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43855714797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39519596099854</t>
+    <t xml:space="preserve">3.42554879188538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43855690956116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39519572257996</t>
   </si>
   <si>
     <t xml:space="preserve">3.20440554618835</t>
@@ -1592,13 +1592,13 @@
     <t xml:space="preserve">2.88353133201599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97459030151367</t>
+    <t xml:space="preserve">2.97459053993225</t>
   </si>
   <si>
     <t xml:space="preserve">3.02228784561157</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3821873664856</t>
+    <t xml:space="preserve">3.38218760490417</t>
   </si>
   <si>
     <t xml:space="preserve">3.32148122787476</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">3.06564927101135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81848931312561</t>
+    <t xml:space="preserve">2.81848955154419</t>
   </si>
   <si>
     <t xml:space="preserve">2.68840527534485</t>
@@ -1625,10 +1625,10 @@
     <t xml:space="preserve">2.73176670074463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63203549385071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98759865760803</t>
+    <t xml:space="preserve">2.63203573226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98759889602661</t>
   </si>
   <si>
     <t xml:space="preserve">3.17405247688293</t>
@@ -1637,10 +1637,10 @@
     <t xml:space="preserve">3.3041365146637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30847311019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17838883399963</t>
+    <t xml:space="preserve">3.3084728717804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17838859558105</t>
   </si>
   <si>
     <t xml:space="preserve">3.10467433929443</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">3.16104435920715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33015370368958</t>
+    <t xml:space="preserve">3.330153465271</t>
   </si>
   <si>
     <t xml:space="preserve">3.46023774147034</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">3.88517904281616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9025239944458</t>
+    <t xml:space="preserve">3.90252375602722</t>
   </si>
   <si>
     <t xml:space="preserve">3.8548264503479</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">4.11499452590942</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27543163299561</t>
+    <t xml:space="preserve">4.27543115615845</t>
   </si>
   <si>
     <t xml:space="preserve">4.10198640823364</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">4.1323390007019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95889377593994</t>
+    <t xml:space="preserve">3.95889401435852</t>
   </si>
   <si>
     <t xml:space="preserve">3.82447338104248</t>
@@ -1694,7 +1694,7 @@
     <t xml:space="preserve">3.9415488243103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99791884422302</t>
+    <t xml:space="preserve">3.99791860580444</t>
   </si>
   <si>
     <t xml:space="preserve">4.00659084320068</t>
@@ -1715,13 +1715,13 @@
     <t xml:space="preserve">4.03260803222656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9892463684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9242045879364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82880902290344</t>
+    <t xml:space="preserve">3.98924612998962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92420434951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82880878448486</t>
   </si>
   <si>
     <t xml:space="preserve">3.75943160057068</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">3.56864094734192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.776775598526</t>
+    <t xml:space="preserve">3.77677583694458</t>
   </si>
   <si>
     <t xml:space="preserve">4.24507856369019</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">4.06729698181152</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16269207000732</t>
+    <t xml:space="preserve">4.16269159317017</t>
   </si>
   <si>
     <t xml:space="preserve">4.21906137466431</t>
@@ -1763,25 +1763,25 @@
     <t xml:space="preserve">4.68302869796753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88249158859253</t>
+    <t xml:space="preserve">4.88249111175537</t>
   </si>
   <si>
     <t xml:space="preserve">4.76975107192993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72638940811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63966703414917</t>
+    <t xml:space="preserve">4.72638988494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63966751098633</t>
   </si>
   <si>
     <t xml:space="preserve">4.55294466018677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44887733459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39684343338013</t>
+    <t xml:space="preserve">4.44887685775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39684391021729</t>
   </si>
   <si>
     <t xml:space="preserve">3.91119599342346</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">4.12285375595093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01130485534668</t>
+    <t xml:space="preserve">4.01130437850952</t>
   </si>
   <si>
     <t xml:space="preserve">3.91760349273682</t>
@@ -1805,19 +1805,19 @@
     <t xml:space="preserve">4.22547912597656</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00684261322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83282613754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85513591766357</t>
+    <t xml:space="preserve">4.00684213638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8328263759613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85513615608215</t>
   </si>
   <si>
     <t xml:space="preserve">3.8595974445343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93098950386047</t>
+    <t xml:space="preserve">3.93098974227905</t>
   </si>
   <si>
     <t xml:space="preserve">3.83728837966919</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">4.03807640075684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95776128768921</t>
+    <t xml:space="preserve">3.95776081085205</t>
   </si>
   <si>
     <t xml:space="preserve">3.79266858100891</t>
@@ -1841,22 +1841,22 @@
     <t xml:space="preserve">3.76143479347229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61419034004211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68111944198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52048850059509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48479270935059</t>
+    <t xml:space="preserve">3.61419010162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6811192035675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52048873901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48479294776917</t>
   </si>
   <si>
     <t xml:space="preserve">3.67219519615173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59634232521057</t>
+    <t xml:space="preserve">3.59634208679199</t>
   </si>
   <si>
     <t xml:space="preserve">3.58741807937622</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">3.64096164703369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64988565444946</t>
+    <t xml:space="preserve">3.64988589286804</t>
   </si>
   <si>
     <t xml:space="preserve">3.5115647315979</t>
@@ -1886,7 +1886,7 @@
     <t xml:space="preserve">3.4223256111145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47140717506409</t>
+    <t xml:space="preserve">3.47140693664551</t>
   </si>
   <si>
     <t xml:space="preserve">3.50710296630859</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">3.41340160369873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42678737640381</t>
+    <t xml:space="preserve">3.42678761482239</t>
   </si>
   <si>
     <t xml:space="preserve">3.36878204345703</t>
@@ -1934,40 +1934,40 @@
     <t xml:space="preserve">3.40001559257507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30631422996521</t>
+    <t xml:space="preserve">3.30631446838379</t>
   </si>
   <si>
     <t xml:space="preserve">3.28400492668152</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33308625221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35093426704407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52941250801086</t>
+    <t xml:space="preserve">3.33308601379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35093402862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52941274642944</t>
   </si>
   <si>
     <t xml:space="preserve">3.65880942344666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71235299110413</t>
+    <t xml:space="preserve">3.71235322952271</t>
   </si>
   <si>
     <t xml:space="preserve">3.81051635742188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80605435371399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76589632034302</t>
+    <t xml:space="preserve">3.80605411529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7658965587616</t>
   </si>
   <si>
     <t xml:space="preserve">3.6008038520813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5561842918396</t>
+    <t xml:space="preserve">3.55618405342102</t>
   </si>
   <si>
     <t xml:space="preserve">3.4669451713562</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">3.66773343086243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69896721839905</t>
+    <t xml:space="preserve">3.69896697998047</t>
   </si>
   <si>
     <t xml:space="preserve">3.7212769985199</t>
@@ -2018,10 +2018,10 @@
     <t xml:space="preserve">3.56957030296326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9666850566864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73466324806213</t>
+    <t xml:space="preserve">3.96668481826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73466300964355</t>
   </si>
   <si>
     <t xml:space="preserve">3.69450497627258</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">3.60526609420776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57849454879761</t>
+    <t xml:space="preserve">3.57849431037903</t>
   </si>
   <si>
     <t xml:space="preserve">3.56510806083679</t>
@@ -2048,10 +2048,10 @@
     <t xml:space="preserve">4.06038665771484</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91314172744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98899459838867</t>
+    <t xml:space="preserve">3.91314196586609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98899435997009</t>
   </si>
   <si>
     <t xml:space="preserve">3.98007082939148</t>
@@ -2069,10 +2069,10 @@
     <t xml:space="preserve">4.03361415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92652702331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90867924690247</t>
+    <t xml:space="preserve">3.92652750015259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90867972373962</t>
   </si>
   <si>
     <t xml:space="preserve">3.90421748161316</t>
@@ -2081,22 +2081,22 @@
     <t xml:space="preserve">4.0425386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93545126914978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8908314704895</t>
+    <t xml:space="preserve">3.93545150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89083194732666</t>
   </si>
   <si>
     <t xml:space="preserve">4.07823419570923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19424486160278</t>
+    <t xml:space="preserve">4.19424438476562</t>
   </si>
   <si>
     <t xml:space="preserve">4.00238084793091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17639684677124</t>
+    <t xml:space="preserve">4.1763973236084</t>
   </si>
   <si>
     <t xml:space="preserve">4.08715772628784</t>
@@ -2108,28 +2108,28 @@
     <t xml:space="preserve">4.46196269989014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53335380554199</t>
+    <t xml:space="preserve">4.53335428237915</t>
   </si>
   <si>
     <t xml:space="preserve">4.64044094085693</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58689737319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64936542510986</t>
+    <t xml:space="preserve">4.58689785003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64936494827271</t>
   </si>
   <si>
     <t xml:space="preserve">4.7564525604248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78322410583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68506145477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83676767349243</t>
+    <t xml:space="preserve">4.78322458267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68506097793579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83676815032959</t>
   </si>
   <si>
     <t xml:space="preserve">4.81892013549805</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">4.89923477172852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85461568832397</t>
+    <t xml:space="preserve">4.85461521148682</t>
   </si>
   <si>
     <t xml:space="preserve">4.9795503616333</t>
@@ -2156,10 +2156,10 @@
     <t xml:space="preserve">5.04201793670654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89031171798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95277881622314</t>
+    <t xml:space="preserve">4.8903112411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9527792930603</t>
   </si>
   <si>
     <t xml:space="preserve">4.8456916809082</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">4.997398853302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23834419250488</t>
+    <t xml:space="preserve">5.23834466934204</t>
   </si>
   <si>
     <t xml:space="preserve">5.45251846313477</t>
@@ -2201,13 +2201,13 @@
     <t xml:space="preserve">5.15802955627441</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88138723373413</t>
+    <t xml:space="preserve">4.88138675689697</t>
   </si>
   <si>
     <t xml:space="preserve">4.70290899276733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71183252334595</t>
+    <t xml:space="preserve">4.71183300018311</t>
   </si>
   <si>
     <t xml:space="preserve">4.73860454559326</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">4.63151741027832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67613649368286</t>
+    <t xml:space="preserve">4.67613697052002</t>
   </si>
   <si>
     <t xml:space="preserve">4.56012630462646</t>
@@ -2225,16 +2225,16 @@
     <t xml:space="preserve">4.41734313964844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14516353607178</t>
+    <t xml:space="preserve">4.14516401290894</t>
   </si>
   <si>
     <t xml:space="preserve">4.02022886276245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98453283309937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94883728027344</t>
+    <t xml:space="preserve">3.98453259468079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94883704185486</t>
   </si>
   <si>
     <t xml:space="preserve">3.8015923500061</t>
@@ -2252,25 +2252,25 @@
     <t xml:space="preserve">2.72625923156738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.757493019104</t>
+    <t xml:space="preserve">2.75749325752258</t>
   </si>
   <si>
     <t xml:space="preserve">2.44961738586426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45854139328003</t>
+    <t xml:space="preserve">2.45854163169861</t>
   </si>
   <si>
     <t xml:space="preserve">2.14174222946167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99895942211151</t>
+    <t xml:space="preserve">1.99895930290222</t>
   </si>
   <si>
     <t xml:space="preserve">2.10604619979858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25775337219238</t>
+    <t xml:space="preserve">2.2577531337738</t>
   </si>
   <si>
     <t xml:space="preserve">2.34699249267578</t>
@@ -2279,25 +2279,25 @@
     <t xml:space="preserve">2.4228458404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54331874847412</t>
+    <t xml:space="preserve">2.54331851005554</t>
   </si>
   <si>
     <t xml:space="preserve">2.40053606033325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48085141181946</t>
+    <t xml:space="preserve">2.48085117340088</t>
   </si>
   <si>
     <t xml:space="preserve">2.45407962799072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46300363540649</t>
+    <t xml:space="preserve">2.46300339698792</t>
   </si>
   <si>
     <t xml:space="preserve">2.56116652488708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73964500427246</t>
+    <t xml:space="preserve">2.73964524269104</t>
   </si>
   <si>
     <t xml:space="preserve">3.23938512802124</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">3.20368933677673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10998797416687</t>
+    <t xml:space="preserve">3.10998773574829</t>
   </si>
   <si>
     <t xml:space="preserve">2.91812372207642</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">2.94489550590515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89135217666626</t>
+    <t xml:space="preserve">2.89135193824768</t>
   </si>
   <si>
     <t xml:space="preserve">2.97612929344177</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">2.85565638542175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98059105873108</t>
+    <t xml:space="preserve">2.98059129714966</t>
   </si>
   <si>
     <t xml:space="preserve">3.00290107727051</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">3.13229775428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01182508468628</t>
+    <t xml:space="preserve">3.0118248462677</t>
   </si>
   <si>
     <t xml:space="preserve">2.98862147331238</t>
@@ -2795,9 +2795,6 @@
     <t xml:space="preserve">3.10463929176331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0118248462677</t>
-  </si>
-  <si>
     <t xml:space="preserve">3.11392092704773</t>
   </si>
   <si>
@@ -4146,6 +4143,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.3600001335144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44000005722046</t>
   </si>
 </sst>
 </file>
@@ -38978,7 +38978,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1327" t="s">
-        <v>927</v>
+        <v>776</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -39056,7 +39056,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1330" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -39082,7 +39082,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1331" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -39108,7 +39108,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1332" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -39134,7 +39134,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1333" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -39160,7 +39160,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1334" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -39186,7 +39186,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1335" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -39238,7 +39238,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1337" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -39264,7 +39264,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1338" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -39290,7 +39290,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1339" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -39316,7 +39316,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G1340" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -39342,7 +39342,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1341" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -39368,7 +39368,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1342" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -39394,7 +39394,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1343" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -39420,7 +39420,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1344" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -39446,7 +39446,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1345" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -39472,7 +39472,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1346" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -39498,7 +39498,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1347" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -39524,7 +39524,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1348" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -39550,7 +39550,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1349" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -39576,7 +39576,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1350" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -39602,7 +39602,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1351" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -39628,7 +39628,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1352" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -39654,7 +39654,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1353" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -39680,7 +39680,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1354" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -39706,7 +39706,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1355" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -39758,7 +39758,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1357" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -39784,7 +39784,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1358" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -39810,7 +39810,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1359" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -39836,7 +39836,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1360" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -39862,7 +39862,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1361" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -39888,7 +39888,7 @@
         <v>3.375</v>
       </c>
       <c r="G1362" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -39914,7 +39914,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1363" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -39940,7 +39940,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1364" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -39966,7 +39966,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1365" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -39992,7 +39992,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1366" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -40018,7 +40018,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1367" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -40044,7 +40044,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1368" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -40070,7 +40070,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1369" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -40096,7 +40096,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1370" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -40148,7 +40148,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1372" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -40174,7 +40174,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1373" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -40200,7 +40200,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1374" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -40226,7 +40226,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1375" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -40252,7 +40252,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1376" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -40278,7 +40278,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1377" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -40304,7 +40304,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1378" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -40330,7 +40330,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G1379" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -40356,7 +40356,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G1380" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -40382,7 +40382,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1381" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -40408,7 +40408,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1382" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -40434,7 +40434,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1383" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -40460,7 +40460,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G1384" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -40486,7 +40486,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1385" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -40512,7 +40512,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1386" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -40538,7 +40538,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1387" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -40564,7 +40564,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1388" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -40590,7 +40590,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G1389" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -40616,7 +40616,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G1390" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -40642,7 +40642,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1391" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -40668,7 +40668,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1392" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -40694,7 +40694,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G1393" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -40720,7 +40720,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1394" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -40746,7 +40746,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1395" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -40772,7 +40772,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1396" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -40798,7 +40798,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1397" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -40824,7 +40824,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1398" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -40850,7 +40850,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1399" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -40876,7 +40876,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1400" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -40902,7 +40902,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1401" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -40928,7 +40928,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1402" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -40954,7 +40954,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1403" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -40980,7 +40980,7 @@
         <v>3.5</v>
       </c>
       <c r="G1404" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -41032,7 +41032,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1406" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -41110,7 +41110,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1409" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -41136,7 +41136,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1410" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -41162,7 +41162,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1411" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -41214,7 +41214,7 @@
         <v>3.375</v>
       </c>
       <c r="G1413" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -41292,7 +41292,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1416" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -41318,7 +41318,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1417" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -41448,7 +41448,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1422" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -41474,7 +41474,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1423" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -41500,7 +41500,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1424" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -41526,7 +41526,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1425" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -41552,7 +41552,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1426" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -41578,7 +41578,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1427" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -41604,7 +41604,7 @@
         <v>3.5</v>
       </c>
       <c r="G1428" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -41630,7 +41630,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1429" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -41656,7 +41656,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1430" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -41682,7 +41682,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1431" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -41708,7 +41708,7 @@
         <v>3.375</v>
       </c>
       <c r="G1432" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -41734,7 +41734,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1433" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -41760,7 +41760,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1434" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -41812,7 +41812,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1436" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -41838,7 +41838,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1437" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -41864,7 +41864,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1438" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -41890,7 +41890,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1439" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -41916,7 +41916,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1440" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -41942,7 +41942,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G1441" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -41968,7 +41968,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1442" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -41994,7 +41994,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1443" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -42020,7 +42020,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1444" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -42046,7 +42046,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1445" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -42098,7 +42098,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1447" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -42124,7 +42124,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1448" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -42150,7 +42150,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1449" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -42176,7 +42176,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1450" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -42202,7 +42202,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1451" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -42228,7 +42228,7 @@
         <v>3.625</v>
       </c>
       <c r="G1452" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -42254,7 +42254,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1453" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -42306,7 +42306,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1455" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -42332,7 +42332,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1456" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -42358,7 +42358,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1457" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -42384,7 +42384,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G1458" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -42410,7 +42410,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1459" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -42436,7 +42436,7 @@
         <v>3.625</v>
       </c>
       <c r="G1460" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -42462,7 +42462,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1461" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -42488,7 +42488,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1462" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -42514,7 +42514,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1463" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -42540,7 +42540,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1464" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -42566,7 +42566,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1465" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -42592,7 +42592,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1466" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -42618,7 +42618,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1467" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -42644,7 +42644,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1468" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -42670,7 +42670,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1469" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -42696,7 +42696,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1470" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -42722,7 +42722,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1471" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -42748,7 +42748,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1472" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -42774,7 +42774,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1473" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -42800,7 +42800,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1474" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -42826,7 +42826,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1475" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -42852,7 +42852,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1476" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -42878,7 +42878,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1477" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -42904,7 +42904,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1478" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -42930,7 +42930,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G1479" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -42982,7 +42982,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1481" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -43034,7 +43034,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1483" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -43060,7 +43060,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G1484" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -43086,7 +43086,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1485" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -43112,7 +43112,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1486" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -43138,7 +43138,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1487" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -43164,7 +43164,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1488" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -43190,7 +43190,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1489" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -43216,7 +43216,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1490" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -43242,7 +43242,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1491" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -43268,7 +43268,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1492" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -43294,7 +43294,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1493" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -43320,7 +43320,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1494" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -43346,7 +43346,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1495" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -43372,7 +43372,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1496" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -43398,7 +43398,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1497" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -43424,7 +43424,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1498" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -43450,7 +43450,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1499" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -43502,7 +43502,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1501" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -43554,7 +43554,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1503" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -43580,7 +43580,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1504" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -43606,7 +43606,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1505" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -43658,7 +43658,7 @@
         <v>3.25</v>
       </c>
       <c r="G1507" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -43736,7 +43736,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1510" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -43762,7 +43762,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1511" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -43788,7 +43788,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1512" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -43814,7 +43814,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1513" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -43866,7 +43866,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1515" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -43892,7 +43892,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1516" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -43970,7 +43970,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1519" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -43996,7 +43996,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1520" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -44022,7 +44022,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1521" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -44048,7 +44048,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1522" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -44074,7 +44074,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1523" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -44100,7 +44100,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1524" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -44126,7 +44126,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1525" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -44152,7 +44152,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1526" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -44178,7 +44178,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1527" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -44204,7 +44204,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -44256,7 +44256,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1530" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -44282,7 +44282,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1531" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -44360,7 +44360,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G1534" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -44386,7 +44386,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1535" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -44438,7 +44438,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1537" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -44464,7 +44464,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1538" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -44516,7 +44516,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1540" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -44542,7 +44542,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1541" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -44568,7 +44568,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1542" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -44750,7 +44750,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1549" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -44776,7 +44776,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1550" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -44828,7 +44828,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1552" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -44854,7 +44854,7 @@
         <v>3.375</v>
       </c>
       <c r="G1553" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -44880,7 +44880,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1554" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -44932,7 +44932,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1556" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -44984,7 +44984,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1558" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -45010,7 +45010,7 @@
         <v>3.375</v>
       </c>
       <c r="G1559" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -45088,7 +45088,7 @@
         <v>3.25</v>
       </c>
       <c r="G1562" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -45218,7 +45218,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1567" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -45244,7 +45244,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1568" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -45426,7 +45426,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G1575" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -45478,7 +45478,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1577" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -45530,7 +45530,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1579" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -45556,7 +45556,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1580" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -45660,7 +45660,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1584" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -45738,7 +45738,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G1587" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -45790,7 +45790,7 @@
         <v>3.375</v>
       </c>
       <c r="G1589" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -45816,7 +45816,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1590" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -45946,7 +45946,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1595" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -46050,7 +46050,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G1599" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -46128,7 +46128,7 @@
         <v>3.375</v>
       </c>
       <c r="G1602" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -46154,7 +46154,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1603" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -46232,7 +46232,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1606" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -46284,7 +46284,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1608" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -46336,7 +46336,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1610" t="s">
-        <v>927</v>
+        <v>776</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -46362,7 +46362,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1611" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -46388,7 +46388,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1612" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -46518,7 +46518,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1617" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -46570,7 +46570,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1619" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -46596,7 +46596,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1620" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -46622,7 +46622,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1621" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -46726,7 +46726,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1625" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -46752,7 +46752,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1626" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -46856,7 +46856,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1630" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -46882,7 +46882,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G1631" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -47038,7 +47038,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1637" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -47116,7 +47116,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1640" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -47168,7 +47168,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1642" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -47194,7 +47194,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1643" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -47246,7 +47246,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1645" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -47298,7 +47298,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1647" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -47350,7 +47350,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1649" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -47428,7 +47428,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1652" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -47480,7 +47480,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1654" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -47844,7 +47844,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1668" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -48000,7 +48000,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1674" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -48026,7 +48026,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1675" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -48182,7 +48182,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1681" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -48208,7 +48208,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1682" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -48234,7 +48234,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1683" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -48312,7 +48312,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1686" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -48468,7 +48468,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1692" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -48494,7 +48494,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1693" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -48572,7 +48572,7 @@
         <v>3.125</v>
       </c>
       <c r="G1696" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -48624,7 +48624,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1698" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -48676,7 +48676,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1700" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -48702,7 +48702,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1701" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -48754,7 +48754,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1703" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -48858,7 +48858,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1707" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -48884,7 +48884,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1708" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -48910,7 +48910,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1709" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -48962,7 +48962,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1711" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -48988,7 +48988,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G1712" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -49040,7 +49040,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1714" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -49196,7 +49196,7 @@
         <v>3.125</v>
       </c>
       <c r="G1720" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -49222,7 +49222,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1721" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -49274,7 +49274,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1723" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -49378,7 +49378,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1727" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -49560,7 +49560,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1734" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -49768,7 +49768,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1742" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -49846,7 +49846,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G1745" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -49898,7 +49898,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1747" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -49924,7 +49924,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1748" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -50054,7 +50054,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1753" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -50132,7 +50132,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1756" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -50210,7 +50210,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1759" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -50262,7 +50262,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1761" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -50392,7 +50392,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1766" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -50418,7 +50418,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1767" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -50470,7 +50470,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1769" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -50574,7 +50574,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1773" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -50626,7 +50626,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1775" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -50652,7 +50652,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1776" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -50678,7 +50678,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1777" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -50834,7 +50834,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1783" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -50860,7 +50860,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1784" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -50886,7 +50886,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1785" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -50938,7 +50938,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1787" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -51068,7 +51068,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1792" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -51172,7 +51172,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1796" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -51250,7 +51250,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1799" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -51380,7 +51380,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1804" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -51484,7 +51484,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1808" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -51510,7 +51510,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1809" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -51692,7 +51692,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1816" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -51770,7 +51770,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1819" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -51822,7 +51822,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1821" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -52030,7 +52030,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1829" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -52212,7 +52212,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1836" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -52264,7 +52264,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1838" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -52316,7 +52316,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1840" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -52368,7 +52368,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1842" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -52446,7 +52446,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1845" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -52524,7 +52524,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1848" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -52732,7 +52732,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1856" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -52758,7 +52758,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G1857" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -52810,7 +52810,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1859" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -52836,7 +52836,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1860" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -52888,7 +52888,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1862" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -52914,7 +52914,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1863" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -53070,7 +53070,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1869" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -53096,7 +53096,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1870" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -53122,7 +53122,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1871" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -53148,7 +53148,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1872" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -53278,7 +53278,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1877" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -53330,7 +53330,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1879" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -53408,7 +53408,7 @@
         <v>2.625</v>
       </c>
       <c r="G1882" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -53486,7 +53486,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G1885" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -53538,7 +53538,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G1887" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -53590,7 +53590,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1889" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -53616,7 +53616,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1890" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -53668,7 +53668,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1892" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -53694,7 +53694,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1893" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -53720,7 +53720,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G1894" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -53746,7 +53746,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G1895" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -53772,7 +53772,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1896" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -53798,7 +53798,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G1897" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -53824,7 +53824,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1898" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -53850,7 +53850,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1899" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -53876,7 +53876,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1900" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -53902,7 +53902,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G1901" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -53928,7 +53928,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G1902" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -54006,7 +54006,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1905" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -54032,7 +54032,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G1906" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -54084,7 +54084,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1908" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -54162,7 +54162,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1911" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -54214,7 +54214,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1913" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -54240,7 +54240,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1914" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -54266,7 +54266,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1915" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -54292,7 +54292,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1916" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -54318,7 +54318,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1917" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -54344,7 +54344,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1918" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -54370,7 +54370,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1919" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -54396,7 +54396,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1920" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -54422,7 +54422,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1921" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -54448,7 +54448,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G1922" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -54526,7 +54526,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1925" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -54552,7 +54552,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G1926" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -54630,7 +54630,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1929" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -54682,7 +54682,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1931" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -54734,7 +54734,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1933" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -54760,7 +54760,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1934" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -54786,7 +54786,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1935" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -54812,7 +54812,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1936" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -54838,7 +54838,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1937" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -54864,7 +54864,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1938" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -54890,7 +54890,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1939" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -54916,7 +54916,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1940" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -54942,7 +54942,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1941" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -54968,7 +54968,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1942" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -54994,7 +54994,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1943" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -55020,7 +55020,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1944" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -55046,7 +55046,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1945" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -55072,7 +55072,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G1946" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -55098,7 +55098,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1947" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -55124,7 +55124,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1948" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -55150,7 +55150,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1949" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -55202,7 +55202,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G1951" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -55228,7 +55228,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1952" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -55254,7 +55254,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1953" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -55280,7 +55280,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1954" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -55358,7 +55358,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1957" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -55384,7 +55384,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1958" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -55410,7 +55410,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1959" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -55436,7 +55436,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1960" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -55462,7 +55462,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1961" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -55514,7 +55514,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1963" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -55618,7 +55618,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1967" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -55670,7 +55670,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1969" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -55696,7 +55696,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1970" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -55722,7 +55722,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1971" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -55748,7 +55748,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1972" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -55774,7 +55774,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G1973" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -55800,7 +55800,7 @@
         <v>1.9539999961853</v>
       </c>
       <c r="G1974" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -55826,7 +55826,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1975" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -55852,7 +55852,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1976" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -55878,7 +55878,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1977" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -55904,7 +55904,7 @@
         <v>1.96599996089935</v>
       </c>
       <c r="G1978" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -55930,7 +55930,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G1979" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -55956,7 +55956,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1980" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -55982,7 +55982,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G1981" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -56008,7 +56008,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1982" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -56034,7 +56034,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G1983" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -56060,7 +56060,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1984" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -56086,7 +56086,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G1985" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -56112,7 +56112,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1986" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -56138,7 +56138,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1987" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -56164,7 +56164,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G1988" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -56190,7 +56190,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G1989" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -56216,7 +56216,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1990" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -56242,7 +56242,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1991" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -56268,7 +56268,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1992" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -56294,7 +56294,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G1993" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -56320,7 +56320,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G1994" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -56346,7 +56346,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1995" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -56372,7 +56372,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1996" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -56398,7 +56398,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G1997" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -56424,7 +56424,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1998" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -56450,7 +56450,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1999" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -56476,7 +56476,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2000" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -56502,7 +56502,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2001" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -56528,7 +56528,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G2002" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -56554,7 +56554,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2003" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -56580,7 +56580,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G2004" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -56606,7 +56606,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G2005" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -56788,7 +56788,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G2012" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -56814,7 +56814,7 @@
         <v>2.375</v>
       </c>
       <c r="G2013" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -56918,7 +56918,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G2017" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -57074,7 +57074,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2023" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -57126,7 +57126,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G2025" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -57204,7 +57204,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2028" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -57256,7 +57256,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G2030" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -57282,7 +57282,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G2031" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -57308,7 +57308,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G2032" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -57386,7 +57386,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G2035" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -57438,7 +57438,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G2037" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -57516,7 +57516,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G2040" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -57698,7 +57698,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G2047" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -57802,7 +57802,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G2051" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -57854,7 +57854,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G2053" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -58114,7 +58114,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G2063" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -58504,7 +58504,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2078" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -58530,7 +58530,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2079" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -58582,7 +58582,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G2081" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -58634,7 +58634,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2083" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -58660,7 +58660,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G2084" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -58686,7 +58686,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2085" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -58764,7 +58764,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G2088" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -58790,7 +58790,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2089" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -58816,7 +58816,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G2090" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -58842,7 +58842,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G2091" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -58868,7 +58868,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G2092" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -58894,7 +58894,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G2093" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -58946,7 +58946,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2095" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -58972,7 +58972,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G2096" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -58998,7 +58998,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G2097" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -59024,7 +59024,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G2098" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -59050,7 +59050,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G2099" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -59076,7 +59076,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G2100" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -59102,7 +59102,7 @@
         <v>4.125</v>
       </c>
       <c r="G2101" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -59128,7 +59128,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2102" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -59154,7 +59154,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2103" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -59180,7 +59180,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2104" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -59206,7 +59206,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2105" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -59232,7 +59232,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G2106" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -59258,7 +59258,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G2107" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -59284,7 +59284,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G2108" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -59310,7 +59310,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2109" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -59336,7 +59336,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G2110" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -59362,7 +59362,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G2111" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -59388,7 +59388,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G2112" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -59414,7 +59414,7 @@
         <v>3.625</v>
       </c>
       <c r="G2113" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -59440,7 +59440,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2114" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -59466,7 +59466,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G2115" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -59492,7 +59492,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2116" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -59518,7 +59518,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G2117" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -59544,7 +59544,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G2118" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -59570,7 +59570,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G2119" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -59596,7 +59596,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G2120" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -59622,7 +59622,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G2121" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -59648,7 +59648,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2122" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -59674,7 +59674,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G2123" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -59700,7 +59700,7 @@
         <v>3.75</v>
       </c>
       <c r="G2124" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -59726,7 +59726,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G2125" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -59752,7 +59752,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G2126" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -59778,7 +59778,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G2127" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -59804,7 +59804,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G2128" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -59830,7 +59830,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G2129" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -59856,7 +59856,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G2130" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -59882,7 +59882,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2131" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -59908,7 +59908,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G2132" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -59934,7 +59934,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G2133" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -59960,7 +59960,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G2134" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -59986,7 +59986,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G2135" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -60012,7 +60012,7 @@
         <v>3.75</v>
       </c>
       <c r="G2136" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -60038,7 +60038,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G2137" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -60064,7 +60064,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2138" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -60090,7 +60090,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G2139" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -60116,7 +60116,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G2140" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -60142,7 +60142,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2141" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -60168,7 +60168,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G2142" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -60194,7 +60194,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G2143" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -60220,7 +60220,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G2144" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -60246,7 +60246,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G2145" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -60272,7 +60272,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2146" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -60298,7 +60298,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G2147" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -60324,7 +60324,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G2148" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -60350,7 +60350,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G2149" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -60376,7 +60376,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G2150" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -60402,7 +60402,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G2151" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -60428,7 +60428,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G2152" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -60454,7 +60454,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G2153" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -60480,7 +60480,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G2154" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -60506,7 +60506,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G2155" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -60532,7 +60532,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2156" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -60558,7 +60558,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G2157" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -60584,7 +60584,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G2158" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -60610,7 +60610,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G2159" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -60636,7 +60636,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G2160" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -60662,7 +60662,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G2161" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -60688,7 +60688,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G2162" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -60714,7 +60714,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2163" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -60740,7 +60740,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2164" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -60766,7 +60766,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G2165" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -60792,7 +60792,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G2166" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -60818,7 +60818,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G2167" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -60844,7 +60844,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G2168" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -60870,7 +60870,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G2169" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -60896,7 +60896,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G2170" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -60922,7 +60922,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G2171" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -60948,7 +60948,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2172" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -60974,7 +60974,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G2173" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -61000,7 +61000,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G2174" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -61026,7 +61026,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2175" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -61052,7 +61052,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2176" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -61078,7 +61078,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2177" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -61104,7 +61104,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G2178" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -61130,7 +61130,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2179" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -61156,7 +61156,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G2180" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -61182,7 +61182,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2181" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -61208,7 +61208,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G2182" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -61234,7 +61234,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G2183" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -61260,7 +61260,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G2184" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -61286,7 +61286,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G2185" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -61312,7 +61312,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G2186" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -61338,7 +61338,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G2187" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -61364,7 +61364,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G2188" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -61390,7 +61390,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G2189" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -61416,7 +61416,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G2190" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -61442,7 +61442,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G2191" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -61468,7 +61468,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G2192" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -61494,7 +61494,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G2193" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -61520,7 +61520,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G2194" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -61546,7 +61546,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G2195" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -61572,7 +61572,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G2196" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -61598,7 +61598,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2197" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -61624,7 +61624,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G2198" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -61650,7 +61650,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G2199" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -61676,7 +61676,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2200" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -61702,7 +61702,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G2201" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -61728,7 +61728,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G2202" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -61754,7 +61754,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G2203" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -61780,7 +61780,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G2204" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -61806,7 +61806,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G2205" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -61832,7 +61832,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2206" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -61858,7 +61858,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G2207" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -61884,7 +61884,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G2208" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -61910,7 +61910,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G2209" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -61936,7 +61936,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G2210" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -61962,7 +61962,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G2211" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -61988,7 +61988,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G2212" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -62014,7 +62014,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G2213" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -62040,7 +62040,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G2214" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -62066,7 +62066,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G2215" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -62092,7 +62092,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G2216" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -62118,7 +62118,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G2217" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -62144,7 +62144,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G2218" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -62170,7 +62170,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G2219" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -62196,7 +62196,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G2220" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -62222,7 +62222,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G2221" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -62248,7 +62248,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G2222" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -62274,7 +62274,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G2223" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -62300,7 +62300,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G2224" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -62326,7 +62326,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G2225" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -62352,7 +62352,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G2226" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -62378,7 +62378,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G2227" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -62404,7 +62404,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G2228" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -62430,7 +62430,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G2229" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -62456,7 +62456,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2230" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -62482,7 +62482,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G2231" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -62508,7 +62508,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G2232" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -62534,7 +62534,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G2233" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -62560,7 +62560,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G2234" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -62586,7 +62586,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G2235" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -62612,7 +62612,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G2236" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -62638,7 +62638,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G2237" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -62664,7 +62664,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G2238" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -62690,7 +62690,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G2239" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -62716,7 +62716,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G2240" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -62742,7 +62742,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G2241" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -62768,7 +62768,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2242" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -62794,7 +62794,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2243" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -62820,7 +62820,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2244" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -62846,7 +62846,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2245" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -62872,7 +62872,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G2246" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -62898,7 +62898,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G2247" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -62924,7 +62924,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G2248" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -62950,7 +62950,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2249" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -62976,7 +62976,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2250" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -63002,7 +63002,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G2251" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -63028,7 +63028,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G2252" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -63054,7 +63054,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G2253" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -63080,7 +63080,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G2254" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -63106,7 +63106,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G2255" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -63132,7 +63132,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2256" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -63158,7 +63158,7 @@
         <v>4.125</v>
       </c>
       <c r="G2257" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -63184,7 +63184,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2258" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -63210,7 +63210,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G2259" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -63236,7 +63236,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G2260" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -63262,7 +63262,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G2261" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -63288,7 +63288,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G2262" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -63314,7 +63314,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2263" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -63340,7 +63340,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G2264" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -63366,7 +63366,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G2265" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -63392,7 +63392,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G2266" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -63418,7 +63418,7 @@
         <v>4</v>
       </c>
       <c r="G2267" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -63444,7 +63444,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2268" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63470,7 +63470,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2269" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63496,7 +63496,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2270" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63522,7 +63522,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G2271" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63548,7 +63548,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2272" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63574,7 +63574,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G2273" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -63600,7 +63600,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G2274" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63626,7 +63626,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2275" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -63652,7 +63652,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G2276" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -63678,7 +63678,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2277" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -63704,7 +63704,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2278" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -63730,7 +63730,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G2279" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -63756,7 +63756,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G2280" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -63782,7 +63782,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2281" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -63808,7 +63808,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G2282" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -63834,7 +63834,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G2283" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -63860,7 +63860,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2284" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -63886,7 +63886,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G2285" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -63912,7 +63912,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G2286" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -63938,7 +63938,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G2287" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -63964,7 +63964,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G2288" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -63990,7 +63990,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2289" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -64016,7 +64016,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2290" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -64042,7 +64042,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2291" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -64068,7 +64068,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2292" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64094,7 +64094,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G2293" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64120,7 +64120,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G2294" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64146,7 +64146,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G2295" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64172,7 +64172,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G2296" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64198,7 +64198,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2297" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64224,7 +64224,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2298" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64250,7 +64250,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G2299" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64276,7 +64276,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G2300" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64302,7 +64302,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2301" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64328,7 +64328,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2302" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64354,7 +64354,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G2303" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64380,7 +64380,7 @@
         <v>4.375</v>
       </c>
       <c r="G2304" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64406,7 +64406,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G2305" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64432,7 +64432,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G2306" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64458,7 +64458,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2307" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64484,7 +64484,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G2308" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64510,7 +64510,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2309" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64536,7 +64536,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G2310" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64562,7 +64562,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G2311" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64588,7 +64588,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G2312" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64614,7 +64614,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G2313" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64640,7 +64640,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G2314" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64666,7 +64666,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G2315" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -64692,7 +64692,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G2316" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -64718,7 +64718,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2317" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -64744,7 +64744,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G2318" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64770,7 +64770,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G2319" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64796,7 +64796,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G2320" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -64822,7 +64822,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2321" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -64848,7 +64848,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G2322" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -64874,7 +64874,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G2323" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -64900,7 +64900,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2324" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -64926,7 +64926,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G2325" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -64952,7 +64952,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2326" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -64978,7 +64978,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G2327" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -65004,7 +65004,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G2328" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -65030,7 +65030,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2329" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -65056,7 +65056,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G2330" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65082,7 +65082,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G2331" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65108,7 +65108,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G2332" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65134,7 +65134,7 @@
         <v>4.90500020980835</v>
       </c>
       <c r="G2333" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65160,7 +65160,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G2334" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65186,7 +65186,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G2335" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65212,7 +65212,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G2336" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65238,7 +65238,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G2337" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65264,7 +65264,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G2338" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65290,7 +65290,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G2339" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65316,7 +65316,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G2340" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65342,7 +65342,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G2341" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65368,7 +65368,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65394,7 +65394,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G2343" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65420,7 +65420,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G2344" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65446,7 +65446,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2345" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65472,7 +65472,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2346" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65498,7 +65498,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G2347" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65524,7 +65524,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2348" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65550,7 +65550,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2349" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65576,7 +65576,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G2350" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65602,7 +65602,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G2351" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65628,7 +65628,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2352" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65654,7 +65654,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G2353" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -65680,7 +65680,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G2354" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -65706,7 +65706,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G2355" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -65732,7 +65732,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2356" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -65758,7 +65758,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G2357" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -65784,7 +65784,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2358" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -65810,7 +65810,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2359" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -65836,7 +65836,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G2360" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -65862,7 +65862,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2361" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -65888,7 +65888,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G2362" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -65914,7 +65914,7 @@
         <v>4.91499996185303</v>
       </c>
       <c r="G2363" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -65940,7 +65940,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G2364" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -65966,7 +65966,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G2365" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -65992,7 +65992,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G2366" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -66018,7 +66018,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2367" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -66044,7 +66044,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G2368" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -66070,7 +66070,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G2369" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66096,7 +66096,7 @@
         <v>5.25</v>
       </c>
       <c r="G2370" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66122,7 +66122,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G2371" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66148,7 +66148,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G2372" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66174,7 +66174,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G2373" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66200,7 +66200,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G2374" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66226,7 +66226,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G2375" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66252,7 +66252,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2376" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66278,7 +66278,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G2377" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66304,7 +66304,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G2378" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66330,7 +66330,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G2379" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66356,7 +66356,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2380" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66382,7 +66382,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G2381" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66408,7 +66408,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G2382" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66434,7 +66434,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G2383" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66460,7 +66460,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G2384" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66486,7 +66486,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2385" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66512,7 +66512,7 @@
         <v>5.75</v>
       </c>
       <c r="G2386" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66538,7 +66538,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2387" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66564,7 +66564,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G2388" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66590,7 +66590,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2389" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66616,7 +66616,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2390" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66642,7 +66642,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G2391" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66668,7 +66668,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G2392" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66694,7 +66694,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G2393" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66720,7 +66720,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G2394" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66746,7 +66746,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G2395" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66772,7 +66772,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G2396" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66798,7 +66798,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G2397" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66824,7 +66824,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2398" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66850,7 +66850,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G2399" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66876,7 +66876,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G2400" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66902,7 +66902,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G2401" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66928,7 +66928,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G2402" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66954,7 +66954,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2403" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66980,7 +66980,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G2404" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -67006,7 +67006,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G2405" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -67032,7 +67032,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G2406" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -67058,7 +67058,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2407" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67084,7 +67084,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G2408" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67110,7 +67110,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2409" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67136,7 +67136,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2410" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67162,7 +67162,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G2411" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67188,7 +67188,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G2412" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67214,7 +67214,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G2413" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67240,7 +67240,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G2414" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67266,7 +67266,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2415" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67292,7 +67292,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G2416" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67318,7 +67318,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G2417" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67344,7 +67344,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2418" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67370,7 +67370,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2419" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67396,7 +67396,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2420" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67422,7 +67422,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2421" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67448,7 +67448,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G2422" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67474,7 +67474,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G2423" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67500,7 +67500,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G2424" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67526,7 +67526,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2425" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67552,7 +67552,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G2426" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67578,7 +67578,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G2427" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67604,7 +67604,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G2428" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67630,7 +67630,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G2429" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67656,7 +67656,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G2430" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67682,7 +67682,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G2431" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67708,7 +67708,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G2432" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67734,7 +67734,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G2433" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67760,7 +67760,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G2434" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67786,7 +67786,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G2435" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67812,7 +67812,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G2436" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67838,7 +67838,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G2437" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67864,7 +67864,7 @@
         <v>6.5</v>
       </c>
       <c r="G2438" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67890,7 +67890,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G2439" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67916,7 +67916,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G2440" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67942,7 +67942,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G2441" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67968,7 +67968,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G2442" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67994,7 +67994,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G2443" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -68020,7 +68020,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G2444" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -68046,7 +68046,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G2445" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -68072,7 +68072,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G2446" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68098,7 +68098,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G2447" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68124,7 +68124,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G2448" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68150,7 +68150,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G2449" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68176,7 +68176,7 @@
         <v>7</v>
       </c>
       <c r="G2450" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68202,7 +68202,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G2451" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68228,7 +68228,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G2452" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68254,7 +68254,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G2453" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68280,7 +68280,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2454" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68306,7 +68306,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G2455" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68332,7 +68332,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G2456" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68358,7 +68358,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G2457" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68384,7 +68384,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G2458" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68410,7 +68410,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G2459" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68436,7 +68436,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G2460" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68462,7 +68462,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G2461" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68488,7 +68488,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G2462" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68514,7 +68514,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G2463" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68540,7 +68540,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G2464" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68566,7 +68566,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2465" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68592,7 +68592,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2466" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68618,7 +68618,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G2467" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68644,7 +68644,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G2468" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68670,7 +68670,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G2469" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68696,7 +68696,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2470" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68722,7 +68722,7 @@
         <v>7.25</v>
       </c>
       <c r="G2471" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68748,7 +68748,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G2472" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68774,7 +68774,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G2473" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68800,7 +68800,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G2474" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68826,7 +68826,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G2475" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68852,7 +68852,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2476" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68878,7 +68878,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G2477" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68904,7 +68904,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G2478" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68930,7 +68930,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G2479" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68956,7 +68956,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G2480" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68982,7 +68982,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G2481" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -69008,7 +69008,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2482" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -69034,7 +69034,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G2483" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -69060,7 +69060,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2484" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69086,7 +69086,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G2485" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69112,7 +69112,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G2486" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69138,7 +69138,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2487" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -69164,7 +69164,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2488" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -69190,7 +69190,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G2489" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -69198,7 +69198,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6496064815</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>99522</v>
@@ -69216,9 +69216,35 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G2490" t="s">
+        <v>1376</v>
+      </c>
+      <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6493634259</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>37915</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>7.46999979019165</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>7.30999994277954</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>7.38000011444092</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>7.44000005722046</v>
+      </c>
+      <c r="G2491" t="s">
         <v>1377</v>
       </c>
-      <c r="H2490" t="s">
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="1382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="1383">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -4158,6 +4158,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80999994277954</t>
   </si>
 </sst>
 </file>
@@ -69366,7 +69369,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6493518519</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>49373</v>
@@ -69387,6 +69390,32 @@
         <v>1381</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6495833333</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>182572</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>7.90000009536743</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>7.59000015258789</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>7.80999994277954</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>1382</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="1388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="1389">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -4176,6 +4176,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.92000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8600001335144</t>
   </si>
 </sst>
 </file>
@@ -69514,7 +69517,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6912268518</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>63127</v>
@@ -69535,6 +69538,32 @@
         <v>1387</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.691087963</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>46676</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>7.82000017166138</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>7.96000003814697</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>7.8600001335144</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1388</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95473074913025</t>
+    <t xml:space="preserve">1.95473062992096</t>
   </si>
   <si>
     <t xml:space="preserve">FM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95993411540985</t>
+    <t xml:space="preserve">1.95993399620056</t>
   </si>
   <si>
     <t xml:space="preserve">1.9096348285675</t>
@@ -68,31 +68,31 @@
     <t xml:space="preserve">1.69542992115021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61824655532837</t>
+    <t xml:space="preserve">1.61824667453766</t>
   </si>
   <si>
     <t xml:space="preserve">1.52285158634186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47949004173279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34420263767242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45434057712555</t>
+    <t xml:space="preserve">1.47949016094208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34420251846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45434045791626</t>
   </si>
   <si>
     <t xml:space="preserve">1.55233716964722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48989689350128</t>
+    <t xml:space="preserve">1.48989677429199</t>
   </si>
   <si>
     <t xml:space="preserve">1.54366493225098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.595698595047</t>
+    <t xml:space="preserve">1.59569871425629</t>
   </si>
   <si>
     <t xml:space="preserve">1.51331210136414</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">1.53325819969177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.499436378479</t>
+    <t xml:space="preserve">1.49943625926971</t>
   </si>
   <si>
     <t xml:space="preserve">1.43005812168121</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">1.38582956790924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28349685668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17682766914368</t>
+    <t xml:space="preserve">1.28349673748016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17682754993439</t>
   </si>
   <si>
     <t xml:space="preserve">1.24186980724335</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">1.23059582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43873059749603</t>
+    <t xml:space="preserve">1.43873047828674</t>
   </si>
   <si>
     <t xml:space="preserve">1.39710354804993</t>
@@ -137,13 +137,13 @@
     <t xml:space="preserve">1.50030362606049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48295915126801</t>
+    <t xml:space="preserve">1.48295903205872</t>
   </si>
   <si>
     <t xml:space="preserve">1.46561455726624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5211169719696</t>
+    <t xml:space="preserve">1.52111709117889</t>
   </si>
   <si>
     <t xml:space="preserve">1.51678073406219</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">1.47515392303467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5098432302475</t>
+    <t xml:space="preserve">1.50984311103821</t>
   </si>
   <si>
     <t xml:space="preserve">1.56014239788055</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">1.55754065513611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52805495262146</t>
+    <t xml:space="preserve">1.52805483341217</t>
   </si>
   <si>
     <t xml:space="preserve">1.54279780387878</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">1.61651206016541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67374908924103</t>
+    <t xml:space="preserve">1.67374897003174</t>
   </si>
   <si>
     <t xml:space="preserve">1.70843827724457</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">1.67808520793915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65467011928558</t>
+    <t xml:space="preserve">1.65467000007629</t>
   </si>
   <si>
     <t xml:space="preserve">1.63298940658569</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">1.60610520839691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53499269485474</t>
+    <t xml:space="preserve">1.53499257564545</t>
   </si>
   <si>
     <t xml:space="preserve">1.49770188331604</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">1.48122441768646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41791701316833</t>
+    <t xml:space="preserve">1.41791713237762</t>
   </si>
   <si>
     <t xml:space="preserve">1.39970517158508</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">1.35200774669647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39190006256104</t>
+    <t xml:space="preserve">1.39190018177032</t>
   </si>
   <si>
     <t xml:space="preserve">1.46041107177734</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">1.57228350639343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62952053546906</t>
+    <t xml:space="preserve">1.62952041625977</t>
   </si>
   <si>
     <t xml:space="preserve">1.60437095165253</t>
@@ -242,19 +242,19 @@
     <t xml:space="preserve">1.60870707035065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62518441677094</t>
+    <t xml:space="preserve">1.62518429756165</t>
   </si>
   <si>
     <t xml:space="preserve">1.65987348556519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58615899085999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55407178401947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60090184211731</t>
+    <t xml:space="preserve">1.58615911006927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55407166481018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6009019613266</t>
   </si>
   <si>
     <t xml:space="preserve">1.58876085281372</t>
@@ -269,19 +269,19 @@
     <t xml:space="preserve">1.47775566577911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47428691387177</t>
+    <t xml:space="preserve">1.47428679466248</t>
   </si>
   <si>
     <t xml:space="preserve">1.46908342838287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56794726848602</t>
+    <t xml:space="preserve">1.56794714927673</t>
   </si>
   <si>
     <t xml:space="preserve">1.53932881355286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53065645694733</t>
+    <t xml:space="preserve">1.53065657615662</t>
   </si>
   <si>
     <t xml:space="preserve">1.54106318950653</t>
@@ -290,55 +290,55 @@
     <t xml:space="preserve">1.56968176364899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54713380336761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55060267448425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56708025932312</t>
+    <t xml:space="preserve">1.5471339225769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55060279369354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56708014011383</t>
   </si>
   <si>
     <t xml:space="preserve">1.5740180015564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51071012020111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59136235713959</t>
+    <t xml:space="preserve">1.5107102394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59136247634888</t>
   </si>
   <si>
     <t xml:space="preserve">1.56100940704346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54453229904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45000433921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38929855823517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40057229995728</t>
+    <t xml:space="preserve">1.54453217983246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45000445842743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38929843902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40057241916656</t>
   </si>
   <si>
     <t xml:space="preserve">1.3875640630722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44740283489227</t>
+    <t xml:space="preserve">1.44740271568298</t>
   </si>
   <si>
     <t xml:space="preserve">1.49163138866425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4838262796402</t>
+    <t xml:space="preserve">1.48382616043091</t>
   </si>
   <si>
     <t xml:space="preserve">1.32338917255402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32945966720581</t>
+    <t xml:space="preserve">1.3294597864151</t>
   </si>
   <si>
     <t xml:space="preserve">1.3884311914444</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">1.30084121227264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30257570743561</t>
+    <t xml:space="preserve">1.30257558822632</t>
   </si>
   <si>
     <t xml:space="preserve">1.3615471124649</t>
@@ -368,31 +368,31 @@
     <t xml:space="preserve">1.37802445888519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38236057758331</t>
+    <t xml:space="preserve">1.3823606967926</t>
   </si>
   <si>
     <t xml:space="preserve">1.39623630046844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.377157330513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4049084186554</t>
+    <t xml:space="preserve">1.37715721130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40490853786469</t>
   </si>
   <si>
     <t xml:space="preserve">1.39450180530548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40404140949249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39363467693329</t>
+    <t xml:space="preserve">1.4040412902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.393634557724</t>
   </si>
   <si>
     <t xml:space="preserve">1.42225301265717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42832362651825</t>
+    <t xml:space="preserve">1.42832350730896</t>
   </si>
   <si>
     <t xml:space="preserve">1.37889182567596</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">1.38062620162964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36588335037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3563437461853</t>
+    <t xml:space="preserve">1.3658834695816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35634386539459</t>
   </si>
   <si>
     <t xml:space="preserve">1.35460937023163</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">1.34333550930023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33119416236877</t>
+    <t xml:space="preserve">1.33119428157806</t>
   </si>
   <si>
     <t xml:space="preserve">1.32685804367065</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">1.41704976558685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40317416191101</t>
+    <t xml:space="preserve">1.40317404270172</t>
   </si>
   <si>
     <t xml:space="preserve">1.39536905288696</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">1.41097915172577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36501598358154</t>
+    <t xml:space="preserve">1.36501610279083</t>
   </si>
   <si>
     <t xml:space="preserve">1.38322782516479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36761772632599</t>
+    <t xml:space="preserve">1.3676176071167</t>
   </si>
   <si>
     <t xml:space="preserve">1.38149356842041</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">1.39797067642212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37455558776855</t>
+    <t xml:space="preserve">1.37455570697784</t>
   </si>
   <si>
     <t xml:space="preserve">1.41358077526093</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">1.42138588428497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41271352767944</t>
+    <t xml:space="preserve">1.41271340847015</t>
   </si>
   <si>
     <t xml:space="preserve">1.40924465656281</t>
@@ -494,25 +494,25 @@
     <t xml:space="preserve">1.42572212219238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35114049911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35894560813904</t>
+    <t xml:space="preserve">1.3511403799057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35894548892975</t>
   </si>
   <si>
     <t xml:space="preserve">1.34680426120758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36414897441864</t>
+    <t xml:space="preserve">1.36414885520935</t>
   </si>
   <si>
     <t xml:space="preserve">1.36241436004639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33032703399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32078742980957</t>
+    <t xml:space="preserve">1.33032715320587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32078754901886</t>
   </si>
   <si>
     <t xml:space="preserve">1.3190530538559</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">1.3129825592041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17942941188812</t>
+    <t xml:space="preserve">1.17942953109741</t>
   </si>
   <si>
     <t xml:space="preserve">1.26181614398956</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">1.29216909408569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23146307468414</t>
+    <t xml:space="preserve">1.23146295547485</t>
   </si>
   <si>
     <t xml:space="preserve">1.21758759021759</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">1.11872339248657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13086462020874</t>
+    <t xml:space="preserve">1.13086473941803</t>
   </si>
   <si>
     <t xml:space="preserve">1.12305951118469</t>
@@ -563,19 +563,19 @@
     <t xml:space="preserve">1.13346636295319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11438727378845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11612176895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11525464057922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09791016578674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09270679950714</t>
+    <t xml:space="preserve">1.11438739299774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11612164974213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11525452136993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09791004657745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09270668029785</t>
   </si>
   <si>
     <t xml:space="preserve">1.07536208629608</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">1.07276034355164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10398054122925</t>
+    <t xml:space="preserve">1.10398066043854</t>
   </si>
   <si>
     <t xml:space="preserve">1.1542797088623</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">1.17856216430664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18289828300476</t>
+    <t xml:space="preserve">1.18289816379547</t>
   </si>
   <si>
     <t xml:space="preserve">1.20544612407684</t>
@@ -608,28 +608,28 @@
     <t xml:space="preserve">1.23493194580078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2453385591507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21845471858978</t>
+    <t xml:space="preserve">1.24533867835999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21845459938049</t>
   </si>
   <si>
     <t xml:space="preserve">1.19937562942505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20111000537872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22799408435822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22192358970642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23666632175446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26875388622284</t>
+    <t xml:space="preserve">1.20111012458801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2279942035675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22192347049713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23666644096375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26875400543213</t>
   </si>
   <si>
     <t xml:space="preserve">1.38409507274628</t>
@@ -647,13 +647,13 @@
     <t xml:space="preserve">1.34593713283539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33292865753174</t>
+    <t xml:space="preserve">1.33292853832245</t>
   </si>
   <si>
     <t xml:space="preserve">1.28870010375977</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25747990608215</t>
+    <t xml:space="preserve">1.25747978687286</t>
   </si>
   <si>
     <t xml:space="preserve">1.23319756984711</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">1.25661265850067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2236579656601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2227908372879</t>
+    <t xml:space="preserve">1.22365808486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22279071807861</t>
   </si>
   <si>
     <t xml:space="preserve">1.25314390659332</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">1.22625982761383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21325135231018</t>
+    <t xml:space="preserve">1.21325123310089</t>
   </si>
   <si>
     <t xml:space="preserve">1.20891523361206</t>
@@ -707,13 +707,13 @@
     <t xml:space="preserve">1.191570520401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20284461975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19243776798248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2340646982193</t>
+    <t xml:space="preserve">1.20284450054169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19243788719177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23406481742859</t>
   </si>
   <si>
     <t xml:space="preserve">1.27742624282837</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">1.29823958873749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26355051994324</t>
+    <t xml:space="preserve">1.26355040073395</t>
   </si>
   <si>
     <t xml:space="preserve">1.24273693561554</t>
@@ -737,22 +737,22 @@
     <t xml:space="preserve">1.22018897533417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24794054031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24967467784882</t>
+    <t xml:space="preserve">1.24794042110443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24967479705811</t>
   </si>
   <si>
     <t xml:space="preserve">1.29043447971344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29303634166718</t>
+    <t xml:space="preserve">1.29303622245789</t>
   </si>
   <si>
     <t xml:space="preserve">1.31818580627441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30691194534302</t>
+    <t xml:space="preserve">1.30691182613373</t>
   </si>
   <si>
     <t xml:space="preserve">1.27309000492096</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">1.24013531208038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27916049957275</t>
+    <t xml:space="preserve">1.27916061878204</t>
   </si>
   <si>
     <t xml:space="preserve">1.2704883813858</t>
@@ -779,28 +779,28 @@
     <t xml:space="preserve">1.26441752910614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28523111343384</t>
+    <t xml:space="preserve">1.28523123264313</t>
   </si>
   <si>
     <t xml:space="preserve">1.2869656085968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33986639976501</t>
+    <t xml:space="preserve">1.3398665189743</t>
   </si>
   <si>
     <t xml:space="preserve">1.33899927139282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41184651851654</t>
+    <t xml:space="preserve">1.41184639930725</t>
   </si>
   <si>
     <t xml:space="preserve">1.57835412025452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51851546764374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54019606113434</t>
+    <t xml:space="preserve">1.51851534843445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54019618034363</t>
   </si>
   <si>
     <t xml:space="preserve">1.49856925010681</t>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">1.50724148750305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50203788280487</t>
+    <t xml:space="preserve">1.50203800201416</t>
   </si>
   <si>
     <t xml:space="preserve">1.47862303256989</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">1.48729515075684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47602117061615</t>
+    <t xml:space="preserve">1.47602128982544</t>
   </si>
   <si>
     <t xml:space="preserve">1.45694220066071</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">1.49076402187347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47341954708099</t>
+    <t xml:space="preserve">1.4734194278717</t>
   </si>
   <si>
     <t xml:space="preserve">1.52892208099365</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">1.57488524913788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58269011974335</t>
+    <t xml:space="preserve">1.58269023895264</t>
   </si>
   <si>
     <t xml:space="preserve">1.56187665462494</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">1.48642790317535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49510014057159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51157748699188</t>
+    <t xml:space="preserve">1.49510025978088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51157760620117</t>
   </si>
   <si>
     <t xml:space="preserve">1.4890296459198</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">1.64686512947083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78648865222931</t>
+    <t xml:space="preserve">1.78648853302002</t>
   </si>
   <si>
     <t xml:space="preserve">1.7604718208313</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">1.84199130535126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15245890617371</t>
+    <t xml:space="preserve">2.15245866775513</t>
   </si>
   <si>
     <t xml:space="preserve">1.99982666969299</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.05186033248901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01543641090393</t>
+    <t xml:space="preserve">2.01543664932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.98074746131897</t>
@@ -947,10 +947,10 @@
     <t xml:space="preserve">1.90790045261383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91657304763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90616583824158</t>
+    <t xml:space="preserve">1.91657292842865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90616571903229</t>
   </si>
   <si>
     <t xml:space="preserve">1.84892892837524</t>
@@ -959,25 +959,25 @@
     <t xml:space="preserve">1.87321150302887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83158445358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84719455242157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93218290805817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93738603591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9252450466156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94258964061737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97727859020233</t>
+    <t xml:space="preserve">1.83158433437347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84719467163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93218278884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93738615512848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92524492740631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94258952140808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97727870941162</t>
   </si>
   <si>
     <t xml:space="preserve">2.0206401348114</t>
@@ -986,7 +986,7 @@
     <t xml:space="preserve">2.06920456886292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01196789741516</t>
+    <t xml:space="preserve">2.01196765899658</t>
   </si>
   <si>
     <t xml:space="preserve">2.03971886634827</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">2.01370215415955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99462330341339</t>
+    <t xml:space="preserve">1.9946231842041</t>
   </si>
   <si>
     <t xml:space="preserve">1.94432425498962</t>
@@ -1007,22 +1007,22 @@
     <t xml:space="preserve">1.82117760181427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91310381889343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72144663333893</t>
+    <t xml:space="preserve">1.91310393810272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72144675254822</t>
   </si>
   <si>
     <t xml:space="preserve">1.67114746570587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69976603984833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68762457370758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67895233631134</t>
+    <t xml:space="preserve">1.69976592063904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68762469291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67895245552063</t>
   </si>
   <si>
     <t xml:space="preserve">1.63992726802826</t>
@@ -1031,10 +1031,10 @@
     <t xml:space="preserve">1.64773225784302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62865328788757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62691867351532</t>
+    <t xml:space="preserve">1.62865316867828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62691879272461</t>
   </si>
   <si>
     <t xml:space="preserve">1.60350358486176</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">1.6485995054245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66507685184479</t>
+    <t xml:space="preserve">1.6650767326355</t>
   </si>
   <si>
     <t xml:space="preserve">1.6910936832428</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">1.67548358440399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65640449523926</t>
+    <t xml:space="preserve">1.65640461444855</t>
   </si>
   <si>
     <t xml:space="preserve">1.63038766384125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66681122779846</t>
+    <t xml:space="preserve">1.66681134700775</t>
   </si>
   <si>
     <t xml:space="preserve">1.68155407905579</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">1.65727162361145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71537613868713</t>
+    <t xml:space="preserve">1.71537601947784</t>
   </si>
   <si>
     <t xml:space="preserve">1.66854584217072</t>
@@ -1100,13 +1100,13 @@
     <t xml:space="preserve">1.7067037820816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72578275203705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72751712799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71190702915192</t>
+    <t xml:space="preserve">1.72578263282776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72751724720001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71190714836121</t>
   </si>
   <si>
     <t xml:space="preserve">1.74312734603882</t>
@@ -1121,10 +1121,10 @@
     <t xml:space="preserve">1.80383312702179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93391764163971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88188374042511</t>
+    <t xml:space="preserve">1.93391752243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88188362121582</t>
   </si>
   <si>
     <t xml:space="preserve">1.9555983543396</t>
@@ -1133,13 +1133,13 @@
     <t xml:space="preserve">1.88621973991394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81684160232544</t>
+    <t xml:space="preserve">1.81684172153473</t>
   </si>
   <si>
     <t xml:space="preserve">1.89489221572876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80816948413849</t>
+    <t xml:space="preserve">1.80816960334778</t>
   </si>
   <si>
     <t xml:space="preserve">1.8298499584198</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">1.85153079032898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78215253353119</t>
+    <t xml:space="preserve">1.78215265274048</t>
   </si>
   <si>
     <t xml:space="preserve">1.81250536441803</t>
@@ -1166,19 +1166,19 @@
     <t xml:space="preserve">1.96860635280609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89922845363617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89055597782135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8775475025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83418619632721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84285831451416</t>
+    <t xml:space="preserve">1.89922833442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89055585861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87754762172699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8341863155365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84285843372345</t>
   </si>
   <si>
     <t xml:space="preserve">1.82551383972168</t>
@@ -1187,16 +1187,16 @@
     <t xml:space="preserve">1.83852219581604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86020290851593</t>
+    <t xml:space="preserve">1.86020302772522</t>
   </si>
   <si>
     <t xml:space="preserve">1.9729425907135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98161482810974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92958116531372</t>
+    <t xml:space="preserve">1.98161494731903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92958104610443</t>
   </si>
   <si>
     <t xml:space="preserve">1.98595082759857</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">2.03364849090576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.042320728302</t>
+    <t xml:space="preserve">2.04232096672058</t>
   </si>
   <si>
     <t xml:space="preserve">2.072674036026</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">2.08134627342224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11169862747192</t>
+    <t xml:space="preserve">2.1116988658905</t>
   </si>
   <si>
     <t xml:space="preserve">2.15072417259216</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">2.05532908439636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18541359901428</t>
+    <t xml:space="preserve">2.1854133605957</t>
   </si>
   <si>
     <t xml:space="preserve">2.33717823028564</t>
@@ -1235,19 +1235,19 @@
     <t xml:space="preserve">2.30248880386353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2808084487915</t>
+    <t xml:space="preserve">2.28080868721008</t>
   </si>
   <si>
     <t xml:space="preserve">2.21143007278442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30682492256165</t>
+    <t xml:space="preserve">2.30682516098022</t>
   </si>
   <si>
     <t xml:space="preserve">2.28514432907104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44991779327393</t>
+    <t xml:space="preserve">2.44991755485535</t>
   </si>
   <si>
     <t xml:space="preserve">2.48894286155701</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">2.76645565032959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83583402633667</t>
+    <t xml:space="preserve">2.83583426475525</t>
   </si>
   <si>
     <t xml:space="preserve">2.91388440132141</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">2.87052297592163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92689275741577</t>
+    <t xml:space="preserve">2.92689299583435</t>
   </si>
   <si>
     <t xml:space="preserve">3.10033845901489</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">3.23909449577332</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25210309028625</t>
+    <t xml:space="preserve">3.25210332870483</t>
   </si>
   <si>
     <t xml:space="preserve">3.21741414070129</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">3.36917877197266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26511168479919</t>
+    <t xml:space="preserve">3.26511144638062</t>
   </si>
   <si>
     <t xml:space="preserve">3.22175002098083</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">3.27811980247498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34749817848206</t>
+    <t xml:space="preserve">3.34749794006348</t>
   </si>
   <si>
     <t xml:space="preserve">3.50793504714966</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">3.62934708595276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6640362739563</t>
+    <t xml:space="preserve">3.66403603553772</t>
   </si>
   <si>
     <t xml:space="preserve">3.73341417312622</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">4.09764957427979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86783528327942</t>
+    <t xml:space="preserve">3.86783504486084</t>
   </si>
   <si>
     <t xml:space="preserve">4.0412802696228</t>
@@ -1382,7 +1382,7 @@
     <t xml:space="preserve">3.71173405647278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9198682308197</t>
+    <t xml:space="preserve">3.91986799240112</t>
   </si>
   <si>
     <t xml:space="preserve">4.07163286209106</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">4.284104347229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62232303619385</t>
+    <t xml:space="preserve">4.62232255935669</t>
   </si>
   <si>
     <t xml:space="preserve">4.57896137237549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74373435974121</t>
+    <t xml:space="preserve">4.74373483657837</t>
   </si>
   <si>
     <t xml:space="preserve">4.75240707397461</t>
@@ -1412,19 +1412,19 @@
     <t xml:space="preserve">5.05593633651733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98655796051025</t>
+    <t xml:space="preserve">4.98655843734741</t>
   </si>
   <si>
     <t xml:space="preserve">4.95186853408813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87381887435913</t>
+    <t xml:space="preserve">4.87381839752197</t>
   </si>
   <si>
     <t xml:space="preserve">4.31879281997681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80444002151489</t>
+    <t xml:space="preserve">4.80444049835205</t>
   </si>
   <si>
     <t xml:space="preserve">4.97788572311401</t>
@@ -1445,13 +1445,13 @@
     <t xml:space="preserve">4.85647392272949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89116334915161</t>
+    <t xml:space="preserve">4.89116287231445</t>
   </si>
   <si>
     <t xml:space="preserve">4.83045768737793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76107883453369</t>
+    <t xml:space="preserve">4.76107835769653</t>
   </si>
   <si>
     <t xml:space="preserve">4.54427194595337</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">4.64833927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61364984512329</t>
+    <t xml:space="preserve">4.61365032196045</t>
   </si>
   <si>
     <t xml:space="preserve">4.53560018539429</t>
@@ -1484,25 +1484,25 @@
     <t xml:space="preserve">4.18437242507935</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18870830535889</t>
+    <t xml:space="preserve">4.18870878219604</t>
   </si>
   <si>
     <t xml:space="preserve">4.24074220657349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.084641456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92854070663452</t>
+    <t xml:space="preserve">4.08464193344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9285409450531</t>
   </si>
   <si>
     <t xml:space="preserve">3.91553211212158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85916233062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7811119556427</t>
+    <t xml:space="preserve">3.85916209220886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78111171722412</t>
   </si>
   <si>
     <t xml:space="preserve">4.14101123809814</t>
@@ -1511,13 +1511,13 @@
     <t xml:space="preserve">3.62501072883606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31280899047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28679203987122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14369964599609</t>
+    <t xml:space="preserve">3.31280922889709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28679227828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14369940757751</t>
   </si>
   <si>
     <t xml:space="preserve">3.00927948951721</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">3.03529620170593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04830455780029</t>
+    <t xml:space="preserve">3.04830479621887</t>
   </si>
   <si>
     <t xml:space="preserve">3.07865762710571</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">2.96158194541931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89653992652893</t>
+    <t xml:space="preserve">2.89653968811035</t>
   </si>
   <si>
     <t xml:space="preserve">2.90521216392517</t>
@@ -1547,7 +1547,7 @@
     <t xml:space="preserve">3.02662420272827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75344753265381</t>
+    <t xml:space="preserve">2.75344729423523</t>
   </si>
   <si>
     <t xml:space="preserve">2.80548071861267</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">3.24343061447144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19139719009399</t>
+    <t xml:space="preserve">3.19139742851257</t>
   </si>
   <si>
     <t xml:space="preserve">3.42554879188538</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">3.20440554618835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06998538970947</t>
+    <t xml:space="preserve">3.06998515129089</t>
   </si>
   <si>
     <t xml:space="preserve">2.86618685722351</t>
@@ -1589,7 +1589,7 @@
     <t xml:space="preserve">2.93990135192871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88353157043457</t>
+    <t xml:space="preserve">2.88353133201599</t>
   </si>
   <si>
     <t xml:space="preserve">2.97459030151367</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">3.3821873664856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32148146629333</t>
+    <t xml:space="preserve">3.32148122787476</t>
   </si>
   <si>
     <t xml:space="preserve">3.15670824050903</t>
@@ -1613,16 +1613,16 @@
     <t xml:space="preserve">3.08732986450195</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06564927101135</t>
+    <t xml:space="preserve">3.06564950942993</t>
   </si>
   <si>
     <t xml:space="preserve">2.81848931312561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68840527534485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73176670074463</t>
+    <t xml:space="preserve">2.68840503692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73176693916321</t>
   </si>
   <si>
     <t xml:space="preserve">2.63203549385071</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">3.17405271530151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3041365146637</t>
+    <t xml:space="preserve">3.30413675308228</t>
   </si>
   <si>
     <t xml:space="preserve">3.3084728717804</t>
@@ -1646,10 +1646,10 @@
     <t xml:space="preserve">3.10467433929443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16104435920715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33015370368958</t>
+    <t xml:space="preserve">3.16104412078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.330153465271</t>
   </si>
   <si>
     <t xml:space="preserve">3.46023797988892</t>
@@ -1658,13 +1658,13 @@
     <t xml:space="preserve">3.5903217792511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88517928123474</t>
+    <t xml:space="preserve">3.88517904281616</t>
   </si>
   <si>
     <t xml:space="preserve">3.90252375602722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85482621192932</t>
+    <t xml:space="preserve">3.8548264503479</t>
   </si>
   <si>
     <t xml:space="preserve">4.11499452590942</t>
@@ -1679,10 +1679,10 @@
     <t xml:space="preserve">4.145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1323390007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95889353752136</t>
+    <t xml:space="preserve">4.13233852386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95889377593994</t>
   </si>
   <si>
     <t xml:space="preserve">3.82447338104248</t>
@@ -1694,7 +1694,7 @@
     <t xml:space="preserve">3.94154858589172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9979190826416</t>
+    <t xml:space="preserve">3.99791884422302</t>
   </si>
   <si>
     <t xml:space="preserve">4.00659132003784</t>
@@ -1715,16 +1715,16 @@
     <t xml:space="preserve">4.0326075553894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98924660682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9242045879364</t>
+    <t xml:space="preserve">3.9892463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92420434951782</t>
   </si>
   <si>
     <t xml:space="preserve">3.8288094997406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75943112373352</t>
+    <t xml:space="preserve">3.7594313621521</t>
   </si>
   <si>
     <t xml:space="preserve">3.74642300605774</t>
@@ -1736,13 +1736,13 @@
     <t xml:space="preserve">3.77677583694458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24507904052734</t>
+    <t xml:space="preserve">4.24507856369019</t>
   </si>
   <si>
     <t xml:space="preserve">4.17136430740356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08897733688354</t>
+    <t xml:space="preserve">4.0889778137207</t>
   </si>
   <si>
     <t xml:space="preserve">4.06729698181152</t>
@@ -1751,7 +1751,7 @@
     <t xml:space="preserve">4.16269254684448</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21906137466431</t>
+    <t xml:space="preserve">4.21906185150146</t>
   </si>
   <si>
     <t xml:space="preserve">4.23206996917725</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">4.88249111175537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76975107192993</t>
+    <t xml:space="preserve">4.76975154876709</t>
   </si>
   <si>
     <t xml:space="preserve">4.72638940811157</t>
@@ -1775,10 +1775,10 @@
     <t xml:space="preserve">4.63966751098633</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55294466018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44887733459473</t>
+    <t xml:space="preserve">4.55294418334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44887685775757</t>
   </si>
   <si>
     <t xml:space="preserve">4.39684343338013</t>
@@ -69569,7 +69569,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6910416667</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>71563</v>
@@ -69590,6 +69590,32 @@
         <v>1388</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6911805556</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>94575</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>7.94999980926514</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="1389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="1390">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95473062992096</t>
+    <t xml:space="preserve">1.95473086833954</t>
   </si>
   <si>
     <t xml:space="preserve">FM.MI</t>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">1.95993399620056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9096348285675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85586702823639</t>
+    <t xml:space="preserve">1.90963470935822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8558669090271</t>
   </si>
   <si>
     <t xml:space="preserve">1.86453914642334</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">1.52285158634186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47949016094208</t>
+    <t xml:space="preserve">1.47949004173279</t>
   </si>
   <si>
     <t xml:space="preserve">1.34420251846313</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">1.53325819969177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49943625926971</t>
+    <t xml:space="preserve">1.499436378479</t>
   </si>
   <si>
     <t xml:space="preserve">1.43005812168121</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">1.38582956790924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28349673748016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17682754993439</t>
+    <t xml:space="preserve">1.28349661827087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17682766914368</t>
   </si>
   <si>
     <t xml:space="preserve">1.24186980724335</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">1.48295903205872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46561455726624</t>
+    <t xml:space="preserve">1.46561443805695</t>
   </si>
   <si>
     <t xml:space="preserve">1.52111709117889</t>
@@ -152,10 +152,10 @@
     <t xml:space="preserve">1.4942330121994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47688841819763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47515392303467</t>
+    <t xml:space="preserve">1.47688853740692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47515404224396</t>
   </si>
   <si>
     <t xml:space="preserve">1.50984311103821</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">1.54279780387878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51244473457336</t>
+    <t xml:space="preserve">1.51244485378265</t>
   </si>
   <si>
     <t xml:space="preserve">1.55147004127502</t>
@@ -188,22 +188,22 @@
     <t xml:space="preserve">1.67374897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70843827724457</t>
+    <t xml:space="preserve">1.70843815803528</t>
   </si>
   <si>
     <t xml:space="preserve">1.67808520793915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65467000007629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63298940658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60610520839691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53499257564545</t>
+    <t xml:space="preserve">1.65467011928558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63298952579498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6061053276062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53499269485474</t>
   </si>
   <si>
     <t xml:space="preserve">1.49770188331604</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">1.48122441768646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41791713237762</t>
+    <t xml:space="preserve">1.41791701316833</t>
   </si>
   <si>
     <t xml:space="preserve">1.39970517158508</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">1.39190018177032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46041107177734</t>
+    <t xml:space="preserve">1.46041119098663</t>
   </si>
   <si>
     <t xml:space="preserve">1.57228350639343</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">1.58876085281372</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49249863624573</t>
+    <t xml:space="preserve">1.49249851703644</t>
   </si>
   <si>
     <t xml:space="preserve">1.4578093290329</t>
@@ -281,28 +281,28 @@
     <t xml:space="preserve">1.53932881355286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53065657615662</t>
+    <t xml:space="preserve">1.53065645694733</t>
   </si>
   <si>
     <t xml:space="preserve">1.54106318950653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56968176364899</t>
+    <t xml:space="preserve">1.5696816444397</t>
   </si>
   <si>
     <t xml:space="preserve">1.5471339225769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55060279369354</t>
+    <t xml:space="preserve">1.55060267448425</t>
   </si>
   <si>
     <t xml:space="preserve">1.56708014011383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5740180015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5107102394104</t>
+    <t xml:space="preserve">1.57401812076569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51071035861969</t>
   </si>
   <si>
     <t xml:space="preserve">1.59136247634888</t>
@@ -311,16 +311,16 @@
     <t xml:space="preserve">1.56100940704346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54453217983246</t>
+    <t xml:space="preserve">1.54453229904175</t>
   </si>
   <si>
     <t xml:space="preserve">1.45000445842743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38929843902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40057241916656</t>
+    <t xml:space="preserve">1.38929855823517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40057253837585</t>
   </si>
   <si>
     <t xml:space="preserve">1.3875640630722</t>
@@ -329,16 +329,16 @@
     <t xml:space="preserve">1.44740271568298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49163138866425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48382616043091</t>
+    <t xml:space="preserve">1.49163126945496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4838262796402</t>
   </si>
   <si>
     <t xml:space="preserve">1.32338917255402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3294597864151</t>
+    <t xml:space="preserve">1.32945990562439</t>
   </si>
   <si>
     <t xml:space="preserve">1.3884311914444</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">1.35981273651123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33726501464844</t>
+    <t xml:space="preserve">1.33726489543915</t>
   </si>
   <si>
     <t xml:space="preserve">1.31124794483185</t>
@@ -359,10 +359,10 @@
     <t xml:space="preserve">1.30084121227264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30257558822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3615471124649</t>
+    <t xml:space="preserve">1.30257570743561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36154723167419</t>
   </si>
   <si>
     <t xml:space="preserve">1.37802445888519</t>
@@ -374,16 +374,16 @@
     <t xml:space="preserve">1.39623630046844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37715721130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40490853786469</t>
+    <t xml:space="preserve">1.377157330513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4049084186554</t>
   </si>
   <si>
     <t xml:space="preserve">1.39450180530548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4040412902832</t>
+    <t xml:space="preserve">1.40404140949249</t>
   </si>
   <si>
     <t xml:space="preserve">1.393634557724</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">1.42225301265717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42832350730896</t>
+    <t xml:space="preserve">1.42832362651825</t>
   </si>
   <si>
     <t xml:space="preserve">1.37889182567596</t>
@@ -404,13 +404,13 @@
     <t xml:space="preserve">1.3658834695816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35634386539459</t>
+    <t xml:space="preserve">1.3563437461853</t>
   </si>
   <si>
     <t xml:space="preserve">1.35460937023163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34333550930023</t>
+    <t xml:space="preserve">1.34333539009094</t>
   </si>
   <si>
     <t xml:space="preserve">1.33119428157806</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">1.32685804367065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30170857906342</t>
+    <t xml:space="preserve">1.30170845985413</t>
   </si>
   <si>
     <t xml:space="preserve">1.30777907371521</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">1.34506988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33379590511322</t>
+    <t xml:space="preserve">1.33379578590393</t>
   </si>
   <si>
     <t xml:space="preserve">1.37108659744263</t>
@@ -443,16 +443,16 @@
     <t xml:space="preserve">1.34940600395203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33813190460205</t>
+    <t xml:space="preserve">1.33813202381134</t>
   </si>
   <si>
     <t xml:space="preserve">1.34853875637054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41704976558685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40317404270172</t>
+    <t xml:space="preserve">1.41704964637756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40317416191101</t>
   </si>
   <si>
     <t xml:space="preserve">1.39536905288696</t>
@@ -461,16 +461,16 @@
     <t xml:space="preserve">1.41097915172577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36501610279083</t>
+    <t xml:space="preserve">1.36501622200012</t>
   </si>
   <si>
     <t xml:space="preserve">1.38322782516479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3676176071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38149356842041</t>
+    <t xml:space="preserve">1.36761772632599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38149344921112</t>
   </si>
   <si>
     <t xml:space="preserve">1.39797067642212</t>
@@ -485,10 +485,10 @@
     <t xml:space="preserve">1.42138588428497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41271340847015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40924465656281</t>
+    <t xml:space="preserve">1.41271352767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40924477577209</t>
   </si>
   <si>
     <t xml:space="preserve">1.42572212219238</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">1.3129825592041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17942953109741</t>
+    <t xml:space="preserve">1.17942941188812</t>
   </si>
   <si>
     <t xml:space="preserve">1.26181614398956</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">1.29216909408569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23146295547485</t>
+    <t xml:space="preserve">1.23146307468414</t>
   </si>
   <si>
     <t xml:space="preserve">1.21758759021759</t>
@@ -554,10 +554,10 @@
     <t xml:space="preserve">1.11872339248657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13086473941803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12305951118469</t>
+    <t xml:space="preserve">1.13086462020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12305963039398</t>
   </si>
   <si>
     <t xml:space="preserve">1.13346636295319</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">1.09270668029785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07536208629608</t>
+    <t xml:space="preserve">1.07536220550537</t>
   </si>
   <si>
     <t xml:space="preserve">1.07276034355164</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">1.1542797088623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16295206546783</t>
+    <t xml:space="preserve">1.16295194625854</t>
   </si>
   <si>
     <t xml:space="preserve">1.16208481788635</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">1.17856216430664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18289816379547</t>
+    <t xml:space="preserve">1.18289828300476</t>
   </si>
   <si>
     <t xml:space="preserve">1.20544612407684</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">1.24533867835999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21845459938049</t>
+    <t xml:space="preserve">1.21845471858978</t>
   </si>
   <si>
     <t xml:space="preserve">1.19937562942505</t>
@@ -644,7 +644,7 @@
     <t xml:space="preserve">1.35721111297607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34593713283539</t>
+    <t xml:space="preserve">1.3459370136261</t>
   </si>
   <si>
     <t xml:space="preserve">1.33292853832245</t>
@@ -653,22 +653,22 @@
     <t xml:space="preserve">1.28870010375977</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25747978687286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23319756984711</t>
+    <t xml:space="preserve">1.25747990608215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2331976890564</t>
   </si>
   <si>
     <t xml:space="preserve">1.2444714307785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22712695598602</t>
+    <t xml:space="preserve">1.22712683677673</t>
   </si>
   <si>
     <t xml:space="preserve">1.25661265850067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22365808486938</t>
+    <t xml:space="preserve">1.2236579656601</t>
   </si>
   <si>
     <t xml:space="preserve">1.22279071807861</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">1.20457899570465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21585285663605</t>
+    <t xml:space="preserve">1.21585297584534</t>
   </si>
   <si>
     <t xml:space="preserve">1.21672022342682</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">1.20197737216949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18810176849365</t>
+    <t xml:space="preserve">1.18810164928436</t>
   </si>
   <si>
     <t xml:space="preserve">1.191570520401</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">1.19243788719177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23406481742859</t>
+    <t xml:space="preserve">1.2340646982193</t>
   </si>
   <si>
     <t xml:space="preserve">1.27742624282837</t>
@@ -722,16 +722,16 @@
     <t xml:space="preserve">1.27222263813019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29823958873749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26355040073395</t>
+    <t xml:space="preserve">1.2982394695282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26355051994324</t>
   </si>
   <si>
     <t xml:space="preserve">1.24273693561554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23579919338226</t>
+    <t xml:space="preserve">1.23579907417297</t>
   </si>
   <si>
     <t xml:space="preserve">1.22018897533417</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">1.24967479705811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29043447971344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29303622245789</t>
+    <t xml:space="preserve">1.29043459892273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29303634166718</t>
   </si>
   <si>
     <t xml:space="preserve">1.31818580627441</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">1.30691182613373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27309000492096</t>
+    <t xml:space="preserve">1.27308988571167</t>
   </si>
   <si>
     <t xml:space="preserve">1.24013531208038</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">1.28436386585236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27482450008392</t>
+    <t xml:space="preserve">1.27482438087463</t>
   </si>
   <si>
     <t xml:space="preserve">1.26441752910614</t>
@@ -800,10 +800,10 @@
     <t xml:space="preserve">1.51851534843445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54019618034363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49856925010681</t>
+    <t xml:space="preserve">1.54019606113434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49856913089752</t>
   </si>
   <si>
     <t xml:space="preserve">1.50724148750305</t>
@@ -821,19 +821,19 @@
     <t xml:space="preserve">1.40577578544617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38496232032776</t>
+    <t xml:space="preserve">1.38496220111847</t>
   </si>
   <si>
     <t xml:space="preserve">1.47168505191803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48729515075684</t>
+    <t xml:space="preserve">1.48729526996613</t>
   </si>
   <si>
     <t xml:space="preserve">1.47602128982544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45694220066071</t>
+    <t xml:space="preserve">1.45694208145142</t>
   </si>
   <si>
     <t xml:space="preserve">1.46821618080139</t>
@@ -842,16 +842,16 @@
     <t xml:space="preserve">1.45867669582367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45954394340515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45607507228851</t>
+    <t xml:space="preserve">1.45954382419586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45607495307922</t>
   </si>
   <si>
     <t xml:space="preserve">1.49076402187347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4734194278717</t>
+    <t xml:space="preserve">1.47341954708099</t>
   </si>
   <si>
     <t xml:space="preserve">1.52892208099365</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">1.50637412071228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57488524913788</t>
+    <t xml:space="preserve">1.57488512992859</t>
   </si>
   <si>
     <t xml:space="preserve">1.58269023895264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56187665462494</t>
+    <t xml:space="preserve">1.56187677383423</t>
   </si>
   <si>
     <t xml:space="preserve">1.53585994243622</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">1.48642790317535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49510025978088</t>
+    <t xml:space="preserve">1.49510014057159</t>
   </si>
   <si>
     <t xml:space="preserve">1.51157760620117</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">1.5688145160675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57054889202118</t>
+    <t xml:space="preserve">1.57054901123047</t>
   </si>
   <si>
     <t xml:space="preserve">1.64686512947083</t>
@@ -905,10 +905,10 @@
     <t xml:space="preserve">1.78648853302002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7604718208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85933601856232</t>
+    <t xml:space="preserve">1.76047170162201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85933589935303</t>
   </si>
   <si>
     <t xml:space="preserve">1.86627352237701</t>
@@ -938,19 +938,19 @@
     <t xml:space="preserve">2.01543664932251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98074746131897</t>
+    <t xml:space="preserve">1.98074769973755</t>
   </si>
   <si>
     <t xml:space="preserve">1.90443181991577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90790045261383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91657292842865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90616571903229</t>
+    <t xml:space="preserve">1.90790057182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91657280921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90616595745087</t>
   </si>
   <si>
     <t xml:space="preserve">1.84892892837524</t>
@@ -962,16 +962,16 @@
     <t xml:space="preserve">1.83158433437347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84719467163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93218278884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93738615512848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92524492740631</t>
+    <t xml:space="preserve">1.84719455242157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93218290805817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93738603591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9252450466156</t>
   </si>
   <si>
     <t xml:space="preserve">1.94258952140808</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">2.0206401348114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06920456886292</t>
+    <t xml:space="preserve">2.06920480728149</t>
   </si>
   <si>
     <t xml:space="preserve">2.01196765899658</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">1.94432425498962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90269720554352</t>
+    <t xml:space="preserve">1.90269732475281</t>
   </si>
   <si>
     <t xml:space="preserve">1.82117760181427</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">1.91310393810272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72144675254822</t>
+    <t xml:space="preserve">1.72144663333893</t>
   </si>
   <si>
     <t xml:space="preserve">1.67114746570587</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">1.63992726802826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64773225784302</t>
+    <t xml:space="preserve">1.64773213863373</t>
   </si>
   <si>
     <t xml:space="preserve">1.62865316867828</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">1.6910936832428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72925162315369</t>
+    <t xml:space="preserve">1.72925174236298</t>
   </si>
   <si>
     <t xml:space="preserve">1.67548358440399</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">1.68155407905579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68935918807983</t>
+    <t xml:space="preserve">1.68935906887054</t>
   </si>
   <si>
     <t xml:space="preserve">1.67721807956696</t>
@@ -1082,10 +1082,10 @@
     <t xml:space="preserve">1.63385665416718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62171530723572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65727162361145</t>
+    <t xml:space="preserve">1.62171542644501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65727174282074</t>
   </si>
   <si>
     <t xml:space="preserve">1.71537601947784</t>
@@ -1100,13 +1100,13 @@
     <t xml:space="preserve">1.7067037820816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72578263282776</t>
+    <t xml:space="preserve">1.72578275203705</t>
   </si>
   <si>
     <t xml:space="preserve">1.72751724720001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71190714836121</t>
+    <t xml:space="preserve">1.71190702915192</t>
   </si>
   <si>
     <t xml:space="preserve">1.74312734603882</t>
@@ -1115,16 +1115,16 @@
     <t xml:space="preserve">1.77781629562378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77348029613495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80383312702179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93391752243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88188362121582</t>
+    <t xml:space="preserve">1.77348041534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80383324623108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93391728401184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8818838596344</t>
   </si>
   <si>
     <t xml:space="preserve">1.9555983543396</t>
@@ -1139,19 +1139,19 @@
     <t xml:space="preserve">1.89489221572876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80816960334778</t>
+    <t xml:space="preserve">1.80816948413849</t>
   </si>
   <si>
     <t xml:space="preserve">1.8298499584198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85153079032898</t>
+    <t xml:space="preserve">1.85153090953827</t>
   </si>
   <si>
     <t xml:space="preserve">1.78215265274048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81250536441803</t>
+    <t xml:space="preserve">1.81250548362732</t>
   </si>
   <si>
     <t xml:space="preserve">1.79082489013672</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">1.73445498943329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76480805873871</t>
+    <t xml:space="preserve">1.764808177948</t>
   </si>
   <si>
     <t xml:space="preserve">1.96860635280609</t>
@@ -1172,10 +1172,10 @@
     <t xml:space="preserve">1.89055585861206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87754762172699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8341863155365</t>
+    <t xml:space="preserve">1.8775475025177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83418619632721</t>
   </si>
   <si>
     <t xml:space="preserve">1.84285843372345</t>
@@ -1208,43 +1208,43 @@
     <t xml:space="preserve">2.03364849090576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04232096672058</t>
+    <t xml:space="preserve">2.042320728302</t>
   </si>
   <si>
     <t xml:space="preserve">2.072674036026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08134627342224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1116988658905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15072417259216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05532908439636</t>
+    <t xml:space="preserve">2.08134603500366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11169910430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15072441101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05532932281494</t>
   </si>
   <si>
     <t xml:space="preserve">2.1854133605957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33717823028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30248880386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28080868721008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21143007278442</t>
+    <t xml:space="preserve">2.33717799186707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3024890422821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2808084487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.211430311203</t>
   </si>
   <si>
     <t xml:space="preserve">2.30682516098022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28514432907104</t>
+    <t xml:space="preserve">2.28514456748962</t>
   </si>
   <si>
     <t xml:space="preserve">2.44991755485535</t>
@@ -1274,25 +1274,25 @@
     <t xml:space="preserve">2.76645565032959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83583426475525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91388440132141</t>
+    <t xml:space="preserve">2.83583402633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91388416290283</t>
   </si>
   <si>
     <t xml:space="preserve">2.92255663871765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93122911453247</t>
+    <t xml:space="preserve">2.93122887611389</t>
   </si>
   <si>
     <t xml:space="preserve">2.87052297592163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92689299583435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10033845901489</t>
+    <t xml:space="preserve">2.92689275741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10033822059631</t>
   </si>
   <si>
     <t xml:space="preserve">3.23909449577332</t>
@@ -1331,7 +1331,7 @@
     <t xml:space="preserve">3.34749794006348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50793504714966</t>
+    <t xml:space="preserve">3.50793528556824</t>
   </si>
   <si>
     <t xml:space="preserve">3.48625469207764</t>
@@ -1343,13 +1343,13 @@
     <t xml:space="preserve">3.51227164268494</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62934708595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66403603553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73341417312622</t>
+    <t xml:space="preserve">3.62934684753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6640362739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73341393470764</t>
   </si>
   <si>
     <t xml:space="preserve">3.80712842941284</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">4.0456166267395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09764957427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86783504486084</t>
+    <t xml:space="preserve">4.09765005111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86783456802368</t>
   </si>
   <si>
     <t xml:space="preserve">4.0412802696228</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">3.97190165519714</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71173405647278</t>
+    <t xml:space="preserve">3.7117338180542</t>
   </si>
   <si>
     <t xml:space="preserve">3.91986799240112</t>
@@ -1400,25 +1400,25 @@
     <t xml:space="preserve">4.62232255935669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57896137237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74373483657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75240707397461</t>
+    <t xml:space="preserve">4.57896184921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74373435974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75240659713745</t>
   </si>
   <si>
     <t xml:space="preserve">5.05593633651733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98655843734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95186853408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87381839752197</t>
+    <t xml:space="preserve">4.98655796051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95186901092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87381887435913</t>
   </si>
   <si>
     <t xml:space="preserve">4.31879281997681</t>
@@ -1448,10 +1448,10 @@
     <t xml:space="preserve">4.89116287231445</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83045768737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76107835769653</t>
+    <t xml:space="preserve">4.83045721054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76107883453369</t>
   </si>
   <si>
     <t xml:space="preserve">4.54427194595337</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">4.70904541015625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60497760772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58763360977173</t>
+    <t xml:space="preserve">4.60497808456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58763313293457</t>
   </si>
   <si>
     <t xml:space="preserve">4.64833927154541</t>
@@ -1478,19 +1478,19 @@
     <t xml:space="preserve">4.47489356994629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40551567077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18437242507935</t>
+    <t xml:space="preserve">4.40551519393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1843729019165</t>
   </si>
   <si>
     <t xml:space="preserve">4.18870878219604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24074220657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08464193344116</t>
+    <t xml:space="preserve">4.24074172973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.084641456604</t>
   </si>
   <si>
     <t xml:space="preserve">3.9285409450531</t>
@@ -1508,7 +1508,7 @@
     <t xml:space="preserve">4.14101123809814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62501072883606</t>
+    <t xml:space="preserve">3.62501096725464</t>
   </si>
   <si>
     <t xml:space="preserve">3.31280922889709</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">2.96158194541931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89653968811035</t>
+    <t xml:space="preserve">2.89653992652893</t>
   </si>
   <si>
     <t xml:space="preserve">2.90521216392517</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">2.80548071861267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88786768913269</t>
+    <t xml:space="preserve">2.88786745071411</t>
   </si>
   <si>
     <t xml:space="preserve">3.04396867752075</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">3.2607753276825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24343061447144</t>
+    <t xml:space="preserve">3.24343085289001</t>
   </si>
   <si>
     <t xml:space="preserve">3.19139742851257</t>
@@ -1580,22 +1580,22 @@
     <t xml:space="preserve">3.20440554618835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06998515129089</t>
+    <t xml:space="preserve">3.06998538970947</t>
   </si>
   <si>
     <t xml:space="preserve">2.86618685722351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93990135192871</t>
+    <t xml:space="preserve">2.93990159034729</t>
   </si>
   <si>
     <t xml:space="preserve">2.88353133201599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97459030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02228784561157</t>
+    <t xml:space="preserve">2.97459053993225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02228760719299</t>
   </si>
   <si>
     <t xml:space="preserve">3.3821873664856</t>
@@ -1613,10 +1613,10 @@
     <t xml:space="preserve">3.08732986450195</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06564950942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81848931312561</t>
+    <t xml:space="preserve">3.06564927101135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81848955154419</t>
   </si>
   <si>
     <t xml:space="preserve">2.68840503692627</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">3.3084728717804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17838883399963</t>
+    <t xml:space="preserve">3.17838859558105</t>
   </si>
   <si>
     <t xml:space="preserve">3.10467433929443</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">3.46023797988892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5903217792511</t>
+    <t xml:space="preserve">3.59032154083252</t>
   </si>
   <si>
     <t xml:space="preserve">3.88517904281616</t>
@@ -1664,10 +1664,10 @@
     <t xml:space="preserve">3.90252375602722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8548264503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11499452590942</t>
+    <t xml:space="preserve">3.85482597351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11499404907227</t>
   </si>
   <si>
     <t xml:space="preserve">4.27543115615845</t>
@@ -1679,19 +1679,19 @@
     <t xml:space="preserve">4.145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13233852386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95889377593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82447338104248</t>
+    <t xml:space="preserve">4.1323390007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95889329910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82447361946106</t>
   </si>
   <si>
     <t xml:space="preserve">3.9675657749176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94154858589172</t>
+    <t xml:space="preserve">3.94154906272888</t>
   </si>
   <si>
     <t xml:space="preserve">3.99791884422302</t>
@@ -1721,7 +1721,7 @@
     <t xml:space="preserve">3.92420434951782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8288094997406</t>
+    <t xml:space="preserve">3.82880973815918</t>
   </si>
   <si>
     <t xml:space="preserve">3.7594313621521</t>
@@ -1730,7 +1730,7 @@
     <t xml:space="preserve">3.74642300605774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56864094734192</t>
+    <t xml:space="preserve">3.5686411857605</t>
   </si>
   <si>
     <t xml:space="preserve">3.77677583694458</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">4.06729698181152</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16269254684448</t>
+    <t xml:space="preserve">4.16269207000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.21906185150146</t>
@@ -1757,10 +1757,10 @@
     <t xml:space="preserve">4.23206996917725</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20171737670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68302822113037</t>
+    <t xml:space="preserve">4.20171689987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68302869796753</t>
   </si>
   <si>
     <t xml:space="preserve">4.88249111175537</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">4.72638940811157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63966751098633</t>
+    <t xml:space="preserve">4.63966703414917</t>
   </si>
   <si>
     <t xml:space="preserve">4.55294418334961</t>
@@ -1796,13 +1796,13 @@
     <t xml:space="preserve">4.12285375595093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01130485534668</t>
+    <t xml:space="preserve">4.01130437850952</t>
   </si>
   <si>
     <t xml:space="preserve">3.91760301589966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2254786491394</t>
+    <t xml:space="preserve">4.22547912597656</t>
   </si>
   <si>
     <t xml:space="preserve">4.00684213638306</t>
@@ -1814,10 +1814,10 @@
     <t xml:space="preserve">3.85513615608215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85959768295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93098950386047</t>
+    <t xml:space="preserve">3.85959792137146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93098926544189</t>
   </si>
   <si>
     <t xml:space="preserve">3.83728814125061</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">4.03807640075684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95776104927063</t>
+    <t xml:space="preserve">3.95776081085205</t>
   </si>
   <si>
     <t xml:space="preserve">3.79266834259033</t>
@@ -1838,13 +1838,13 @@
     <t xml:space="preserve">3.74358701705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76143479347229</t>
+    <t xml:space="preserve">3.76143455505371</t>
   </si>
   <si>
     <t xml:space="preserve">3.61419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68111944198608</t>
+    <t xml:space="preserve">3.6811192035675</t>
   </si>
   <si>
     <t xml:space="preserve">3.52048873901367</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">3.48479294776917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67219519615173</t>
+    <t xml:space="preserve">3.67219543457031</t>
   </si>
   <si>
     <t xml:space="preserve">3.59634208679199</t>
@@ -1865,10 +1865,10 @@
     <t xml:space="preserve">3.64096164703369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64988565444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51156449317932</t>
+    <t xml:space="preserve">3.64988589286804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5115647315979</t>
   </si>
   <si>
     <t xml:space="preserve">3.49817895889282</t>
@@ -1910,7 +1910,7 @@
     <t xml:space="preserve">3.32862448692322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36431980133057</t>
+    <t xml:space="preserve">3.36432003974915</t>
   </si>
   <si>
     <t xml:space="preserve">3.39555382728577</t>
@@ -1952,10 +1952,10 @@
     <t xml:space="preserve">3.65880942344666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71235299110413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81051635742188</t>
+    <t xml:space="preserve">3.71235322952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81051659584045</t>
   </si>
   <si>
     <t xml:space="preserve">3.80605435371399</t>
@@ -1967,19 +1967,19 @@
     <t xml:space="preserve">3.6008038520813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5561842918396</t>
+    <t xml:space="preserve">3.55618405342102</t>
   </si>
   <si>
     <t xml:space="preserve">3.4669451713562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62757587432861</t>
+    <t xml:space="preserve">3.62757611274719</t>
   </si>
   <si>
     <t xml:space="preserve">3.78374433517456</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69004344940186</t>
+    <t xml:space="preserve">3.69004368782043</t>
   </si>
   <si>
     <t xml:space="preserve">3.70789122581482</t>
@@ -2000,19 +2000,19 @@
     <t xml:space="preserve">3.69896721839905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72127747535706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72573924064636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62311387062073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60972785949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58295631408691</t>
+    <t xml:space="preserve">3.72127723693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72573947906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62311363220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60972809791565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58295607566833</t>
   </si>
   <si>
     <t xml:space="preserve">3.56957030296326</t>
@@ -2021,19 +2021,19 @@
     <t xml:space="preserve">3.99791860580444</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96668529510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73466300964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69450521469116</t>
+    <t xml:space="preserve">3.96668481826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73466277122498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69450497627258</t>
   </si>
   <si>
     <t xml:space="preserve">3.70342922210693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6320378780365</t>
+    <t xml:space="preserve">3.63203811645508</t>
   </si>
   <si>
     <t xml:space="preserve">3.60526609420776</t>
@@ -2045,34 +2045,34 @@
     <t xml:space="preserve">3.56510829925537</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93991327285767</t>
+    <t xml:space="preserve">3.93991351127625</t>
   </si>
   <si>
     <t xml:space="preserve">4.06038618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91314172744751</t>
+    <t xml:space="preserve">3.91314196586609</t>
   </si>
   <si>
     <t xml:space="preserve">3.98899483680725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98007130622864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12731599807739</t>
+    <t xml:space="preserve">3.98007082939148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12731552124023</t>
   </si>
   <si>
     <t xml:space="preserve">4.05146217346191</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09161949157715</t>
+    <t xml:space="preserve">4.09161996841431</t>
   </si>
   <si>
     <t xml:space="preserve">4.03361415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92652726173401</t>
+    <t xml:space="preserve">3.92652750015259</t>
   </si>
   <si>
     <t xml:space="preserve">3.90867972373962</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">4.0425386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93545126914978</t>
+    <t xml:space="preserve">3.93545150756836</t>
   </si>
   <si>
     <t xml:space="preserve">3.8908314704895</t>
@@ -2105,16 +2105,16 @@
     <t xml:space="preserve">4.08715772628784</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21655464172363</t>
+    <t xml:space="preserve">4.21655511856079</t>
   </si>
   <si>
     <t xml:space="preserve">4.46196317672729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53335428237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64044141769409</t>
+    <t xml:space="preserve">4.53335380554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64044094085693</t>
   </si>
   <si>
     <t xml:space="preserve">4.58689785003662</t>
@@ -2135,19 +2135,19 @@
     <t xml:space="preserve">4.83676767349243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81891965866089</t>
+    <t xml:space="preserve">4.81892013549805</t>
   </si>
   <si>
     <t xml:space="preserve">4.90815925598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00632238388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89923477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85461616516113</t>
+    <t xml:space="preserve">5.00632190704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89923524856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85461568832397</t>
   </si>
   <si>
     <t xml:space="preserve">4.9795503616333</t>
@@ -2159,10 +2159,10 @@
     <t xml:space="preserve">5.04201793670654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89031171798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95277881622314</t>
+    <t xml:space="preserve">4.8903112411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9527792930603</t>
   </si>
   <si>
     <t xml:space="preserve">4.8456916809082</t>
@@ -2174,13 +2174,13 @@
     <t xml:space="preserve">4.82784366607666</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80999612808228</t>
+    <t xml:space="preserve">4.80999565124512</t>
   </si>
   <si>
     <t xml:space="preserve">4.94385480880737</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0687894821167</t>
+    <t xml:space="preserve">5.06878995895386</t>
   </si>
   <si>
     <t xml:space="preserve">4.99739837646484</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">5.45251893997192</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83624792098999</t>
+    <t xml:space="preserve">5.83624744415283</t>
   </si>
   <si>
     <t xml:space="preserve">5.67561721801758</t>
@@ -2204,31 +2204,31 @@
     <t xml:space="preserve">5.15802955627441</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88138771057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70290851593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71183300018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7386040687561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63151741027832</t>
+    <t xml:space="preserve">4.88138723373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70290899276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71183347702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73860454559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63151788711548</t>
   </si>
   <si>
     <t xml:space="preserve">4.67613697052002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56012630462646</t>
+    <t xml:space="preserve">4.56012582778931</t>
   </si>
   <si>
     <t xml:space="preserve">4.41734313964844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14516305923462</t>
+    <t xml:space="preserve">4.14516353607178</t>
   </si>
   <si>
     <t xml:space="preserve">4.02022838592529</t>
@@ -2237,16 +2237,16 @@
     <t xml:space="preserve">3.98453307151794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94883728027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80159258842468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12783598899841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15906953811646</t>
+    <t xml:space="preserve">3.94883751869202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8015923500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12783575057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15906977653503</t>
   </si>
   <si>
     <t xml:space="preserve">3.25277090072632</t>
@@ -2258,13 +2258,13 @@
     <t xml:space="preserve">2.757493019104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961738586426</t>
+    <t xml:space="preserve">2.44961762428284</t>
   </si>
   <si>
     <t xml:space="preserve">2.45854163169861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14174246788025</t>
+    <t xml:space="preserve">2.14174222946167</t>
   </si>
   <si>
     <t xml:space="preserve">1.99895930290222</t>
@@ -2276,16 +2276,16 @@
     <t xml:space="preserve">2.2577531337738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34699273109436</t>
+    <t xml:space="preserve">2.34699249267578</t>
   </si>
   <si>
     <t xml:space="preserve">2.4228458404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54331874847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40053629875183</t>
+    <t xml:space="preserve">2.54331851005554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40053606033325</t>
   </si>
   <si>
     <t xml:space="preserve">2.48085117340088</t>
@@ -2303,22 +2303,22 @@
     <t xml:space="preserve">2.73964524269104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23938512802124</t>
+    <t xml:space="preserve">3.23938536643982</t>
   </si>
   <si>
     <t xml:space="preserve">3.20368933677673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10998821258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.918123960495</t>
+    <t xml:space="preserve">3.10998797416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91812372207642</t>
   </si>
   <si>
     <t xml:space="preserve">2.85119438171387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99843907356262</t>
+    <t xml:space="preserve">2.99843883514404</t>
   </si>
   <si>
     <t xml:space="preserve">2.93597173690796</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">2.94489550590515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89135193824768</t>
+    <t xml:space="preserve">2.8913516998291</t>
   </si>
   <si>
     <t xml:space="preserve">2.97612929344177</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">2.85565638542175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98059105873108</t>
+    <t xml:space="preserve">2.98059129714966</t>
   </si>
   <si>
     <t xml:space="preserve">3.00290107727051</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">3.1322979927063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01182508468628</t>
+    <t xml:space="preserve">3.0118248462677</t>
   </si>
   <si>
     <t xml:space="preserve">2.98862147331238</t>
@@ -2360,22 +2360,22 @@
     <t xml:space="preserve">2.951495885849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8772439956665</t>
+    <t xml:space="preserve">2.87724423408508</t>
   </si>
   <si>
     <t xml:space="preserve">2.88652563095093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85404062271118</t>
+    <t xml:space="preserve">2.85404086112976</t>
   </si>
   <si>
     <t xml:space="preserve">2.7473042011261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71481895446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96077704429626</t>
+    <t xml:space="preserve">2.71481919288635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96077728271484</t>
   </si>
   <si>
     <t xml:space="preserve">2.75658559799194</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">2.78442978858948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83547806739807</t>
+    <t xml:space="preserve">2.83547782897949</t>
   </si>
   <si>
     <t xml:space="preserve">3.08607649803162</t>
@@ -2408,19 +2408,19 @@
     <t xml:space="preserve">3.31347155570984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35059714317322</t>
+    <t xml:space="preserve">3.3505973815918</t>
   </si>
   <si>
     <t xml:space="preserve">3.27634596824646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28098678588867</t>
+    <t xml:space="preserve">3.28098654747009</t>
   </si>
   <si>
     <t xml:space="preserve">3.34595656394958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07215428352356</t>
+    <t xml:space="preserve">3.07215452194214</t>
   </si>
   <si>
     <t xml:space="preserve">3.07679510116577</t>
@@ -2429,13 +2429,13 @@
     <t xml:space="preserve">3.09999847412109</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16032814979553</t>
+    <t xml:space="preserve">3.16032791137695</t>
   </si>
   <si>
     <t xml:space="preserve">3.09535789489746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05359125137329</t>
+    <t xml:space="preserve">3.05359148979187</t>
   </si>
   <si>
     <t xml:space="preserve">3.03502869606018</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">2.99326205253601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85868144035339</t>
+    <t xml:space="preserve">2.85868120193481</t>
   </si>
   <si>
     <t xml:space="preserve">2.83083701133728</t>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">2.82155561447144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84940004348755</t>
+    <t xml:space="preserve">2.84939980506897</t>
   </si>
   <si>
     <t xml:space="preserve">2.81227421760559</t>
@@ -2465,7 +2465,7 @@
     <t xml:space="preserve">2.88188505172729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7937114238739</t>
+    <t xml:space="preserve">2.79371118545532</t>
   </si>
   <si>
     <t xml:space="preserve">2.76122617721558</t>
@@ -2483,13 +2483,13 @@
     <t xml:space="preserve">2.90972924232483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86332201957703</t>
+    <t xml:space="preserve">2.86332225799561</t>
   </si>
   <si>
     <t xml:space="preserve">2.78907084465027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69161558151245</t>
+    <t xml:space="preserve">2.69161581993103</t>
   </si>
   <si>
     <t xml:space="preserve">2.59416055679321</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">2.16257381439209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13472938537598</t>
+    <t xml:space="preserve">2.13472962379456</t>
   </si>
   <si>
     <t xml:space="preserve">2.24610686302185</t>
@@ -2519,16 +2519,16 @@
     <t xml:space="preserve">2.40389108657837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58951997756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55703496932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60808253288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55239391326904</t>
+    <t xml:space="preserve">2.589519739151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55703473091125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60808277130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55239415168762</t>
   </si>
   <si>
     <t xml:space="preserve">2.57559776306152</t>
@@ -2543,13 +2543,13 @@
     <t xml:space="preserve">2.40853190422058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35748410224915</t>
+    <t xml:space="preserve">2.35748386383057</t>
   </si>
   <si>
     <t xml:space="preserve">2.54311275482178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45029854774475</t>
+    <t xml:space="preserve">2.45029830932617</t>
   </si>
   <si>
     <t xml:space="preserve">2.41781330108643</t>
@@ -2558,7 +2558,7 @@
     <t xml:space="preserve">2.45957970619202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44565749168396</t>
+    <t xml:space="preserve">2.44565773010254</t>
   </si>
   <si>
     <t xml:space="preserve">2.46422052383423</t>
@@ -2570,7 +2570,7 @@
     <t xml:space="preserve">2.4317352771759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49670577049255</t>
+    <t xml:space="preserve">2.49670553207397</t>
   </si>
   <si>
     <t xml:space="preserve">2.47814273834229</t>
@@ -2579,28 +2579,28 @@
     <t xml:space="preserve">2.51990914344788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50134611129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52919030189514</t>
+    <t xml:space="preserve">2.50134634971619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52919054031372</t>
   </si>
   <si>
     <t xml:space="preserve">2.56167554855347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5663161277771</t>
+    <t xml:space="preserve">2.56631636619568</t>
   </si>
   <si>
     <t xml:space="preserve">2.3017954826355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29715442657471</t>
+    <t xml:space="preserve">2.29715466499329</t>
   </si>
   <si>
     <t xml:space="preserve">2.29251408576965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2785918712616</t>
+    <t xml:space="preserve">2.27859163284302</t>
   </si>
   <si>
     <t xml:space="preserve">2.23218464851379</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">2.19969964027405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17185544967651</t>
+    <t xml:space="preserve">2.17185521125793</t>
   </si>
   <si>
     <t xml:space="preserve">2.26931023597717</t>
@@ -2621,13 +2621,13 @@
     <t xml:space="preserve">2.24146604537964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22754383087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19505906105042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12544822692871</t>
+    <t xml:space="preserve">2.22754406929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19505882263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12544798851013</t>
   </si>
   <si>
     <t xml:space="preserve">2.01407098770142</t>
@@ -2642,13 +2642,13 @@
     <t xml:space="preserve">2.0744001865387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97230446338654</t>
+    <t xml:space="preserve">1.97230458259583</t>
   </si>
   <si>
     <t xml:space="preserve">1.96766364574432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.944460272789</t>
+    <t xml:space="preserve">1.94446015357971</t>
   </si>
   <si>
     <t xml:space="preserve">1.87020885944366</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">1.81730461120605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79688549041748</t>
+    <t xml:space="preserve">1.79688537120819</t>
   </si>
   <si>
     <t xml:space="preserve">1.80059802532196</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">1.88413095474243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03263401985168</t>
+    <t xml:space="preserve">2.03263378143311</t>
   </si>
   <si>
     <t xml:space="preserve">2.50598692893982</t>
@@ -2693,10 +2693,10 @@
     <t xml:space="preserve">2.77978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71946001052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70553755760193</t>
+    <t xml:space="preserve">2.71945977210999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70553779602051</t>
   </si>
   <si>
     <t xml:space="preserve">2.7241005897522</t>
@@ -2708,10 +2708,10 @@
     <t xml:space="preserve">2.64056777954102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68233418464661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76586723327637</t>
+    <t xml:space="preserve">2.68233442306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76586699485779</t>
   </si>
   <si>
     <t xml:space="preserve">2.58023834228516</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">2.6127233505249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59880113601685</t>
+    <t xml:space="preserve">2.59880137443542</t>
   </si>
   <si>
     <t xml:space="preserve">2.62664556503296</t>
@@ -2741,10 +2741,10 @@
     <t xml:space="preserve">2.39925050735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27395105361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32963967323303</t>
+    <t xml:space="preserve">2.27395129203796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32963991165161</t>
   </si>
   <si>
     <t xml:space="preserve">2.3482027053833</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">2.35284328460693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39460968971252</t>
+    <t xml:space="preserve">2.39460945129395</t>
   </si>
   <si>
     <t xml:space="preserve">2.46886134147644</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">2.64520835876465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7008969783783</t>
+    <t xml:space="preserve">2.70089721679688</t>
   </si>
   <si>
     <t xml:space="preserve">2.71017861366272</t>
@@ -2786,16 +2786,16 @@
     <t xml:space="preserve">2.93757343292236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9979031085968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09071731567383</t>
+    <t xml:space="preserve">2.99790287017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09071707725525</t>
   </si>
   <si>
     <t xml:space="preserve">3.04895091056824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10463953018188</t>
+    <t xml:space="preserve">3.10463929176331</t>
   </si>
   <si>
     <t xml:space="preserve">3.11392092704773</t>
@@ -2804,19 +2804,19 @@
     <t xml:space="preserve">3.2392201423645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24386072158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21601629257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25314259529114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29026818275452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29954957962036</t>
+    <t xml:space="preserve">3.24386096000671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2160165309906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25314235687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29026794433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29954934120178</t>
   </si>
   <si>
     <t xml:space="preserve">3.31811237335205</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">3.61975908279419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49910044670105</t>
+    <t xml:space="preserve">3.49910020828247</t>
   </si>
   <si>
     <t xml:space="preserve">3.62904047966003</t>
@@ -2846,19 +2846,19 @@
     <t xml:space="preserve">3.41092658042908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34131574630737</t>
+    <t xml:space="preserve">3.34131598472595</t>
   </si>
   <si>
     <t xml:space="preserve">3.3273937702179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44805216789246</t>
+    <t xml:space="preserve">3.44805240631104</t>
   </si>
   <si>
     <t xml:space="preserve">3.38772320747375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41556739807129</t>
+    <t xml:space="preserve">3.41556763648987</t>
   </si>
   <si>
     <t xml:space="preserve">3.29490876197815</t>
@@ -2873,19 +2873,19 @@
     <t xml:space="preserve">3.13248372077942</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17889070510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18353176116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28562712669373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3738009929657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43413019180298</t>
+    <t xml:space="preserve">3.17889094352722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18353152275085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2856273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37380075454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43413043022156</t>
   </si>
   <si>
     <t xml:space="preserve">3.47589659690857</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">3.50838160514832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63368105888367</t>
+    <t xml:space="preserve">3.63368082046509</t>
   </si>
   <si>
     <t xml:space="preserve">3.60583686828613</t>
@@ -2906,28 +2906,28 @@
     <t xml:space="preserve">3.54550743103027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69865107536316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55478858947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53622603416443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4434118270874</t>
+    <t xml:space="preserve">3.69865083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55478882789612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53622579574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44341158866882</t>
   </si>
   <si>
     <t xml:space="preserve">3.52230405807495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54086661338806</t>
+    <t xml:space="preserve">3.54086685180664</t>
   </si>
   <si>
     <t xml:space="preserve">3.46197438240051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47125601768494</t>
+    <t xml:space="preserve">3.47125577926636</t>
   </si>
   <si>
     <t xml:space="preserve">3.50374102592468</t>
@@ -2939,16 +2939,16 @@
     <t xml:space="preserve">3.22993874549866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26706457138062</t>
+    <t xml:space="preserve">3.26706433296204</t>
   </si>
   <si>
     <t xml:space="preserve">3.33203434944153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39236354827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37844157218933</t>
+    <t xml:space="preserve">3.39236378669739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37844181060791</t>
   </si>
   <si>
     <t xml:space="preserve">3.30883097648621</t>
@@ -2969,13 +2969,13 @@
     <t xml:space="preserve">3.05823230743408</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13712453842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11856150627136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96541786193848</t>
+    <t xml:space="preserve">3.13712430000305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11856126785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9654176235199</t>
   </si>
   <si>
     <t xml:space="preserve">3.30419015884399</t>
@@ -2984,7 +2984,7 @@
     <t xml:space="preserve">3.17425012588501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12784290313721</t>
+    <t xml:space="preserve">3.12784266471863</t>
   </si>
   <si>
     <t xml:space="preserve">3.19745373725891</t>
@@ -3005,16 +3005,16 @@
     <t xml:space="preserve">3.36451935768127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45269322395325</t>
+    <t xml:space="preserve">3.45269298553467</t>
   </si>
   <si>
     <t xml:space="preserve">3.42020797729492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42484879493713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32275319099426</t>
+    <t xml:space="preserve">3.42484903335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32275295257568</t>
   </si>
   <si>
     <t xml:space="preserve">3.33667516708374</t>
@@ -3023,13 +3023,13 @@
     <t xml:space="preserve">3.38308238983154</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36916017532349</t>
+    <t xml:space="preserve">3.36916041374207</t>
   </si>
   <si>
     <t xml:space="preserve">3.16496872901917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01646566390991</t>
+    <t xml:space="preserve">3.01646590232849</t>
   </si>
   <si>
     <t xml:space="preserve">3.1696093082428</t>
@@ -3038,7 +3038,7 @@
     <t xml:space="preserve">3.06751370429993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0211067199707</t>
+    <t xml:space="preserve">3.02110648155212</t>
   </si>
   <si>
     <t xml:space="preserve">3.15568733215332</t>
@@ -3047,10 +3047,10 @@
     <t xml:space="preserve">3.14176511764526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.123202085495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03966927528381</t>
+    <t xml:space="preserve">3.12320232391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03966951370239</t>
   </si>
   <si>
     <t xml:space="preserve">3.14640593528748</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">2.58487915992737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77050757408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86796259880066</t>
+    <t xml:space="preserve">2.7705078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86796283721924</t>
   </si>
   <si>
     <t xml:space="preserve">2.94685482978821</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">2.98398065567017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02574706077576</t>
+    <t xml:space="preserve">3.02574729919434</t>
   </si>
   <si>
     <t xml:space="preserve">2.97934007644653</t>
@@ -3086,16 +3086,16 @@
     <t xml:space="preserve">2.80299282073975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84475922584534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9282922744751</t>
+    <t xml:space="preserve">2.84475946426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92829203605652</t>
   </si>
   <si>
     <t xml:space="preserve">2.87260365486145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89116621017456</t>
+    <t xml:space="preserve">2.89116644859314</t>
   </si>
   <si>
     <t xml:space="preserve">3.03038787841797</t>
@@ -3104,16 +3104,16 @@
     <t xml:space="preserve">2.8169150352478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68697500228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69625639915466</t>
+    <t xml:space="preserve">2.68697476387024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69625616073608</t>
   </si>
   <si>
     <t xml:space="preserve">2.62200474739075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79835200309753</t>
+    <t xml:space="preserve">2.79835224151611</t>
   </si>
   <si>
     <t xml:space="preserve">2.91901063919067</t>
@@ -3125,7 +3125,7 @@
     <t xml:space="preserve">2.9050886631012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95613646507263</t>
+    <t xml:space="preserve">2.95613622665405</t>
   </si>
   <si>
     <t xml:space="preserve">2.80763363838196</t>
@@ -3143,31 +3143,31 @@
     <t xml:space="preserve">2.74266338348389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63128638267517</t>
+    <t xml:space="preserve">2.63128614425659</t>
   </si>
   <si>
     <t xml:space="preserve">2.49206471443176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53847169876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54775333404541</t>
+    <t xml:space="preserve">2.53847193717957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54775309562683</t>
   </si>
   <si>
     <t xml:space="preserve">2.48742413520813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44101715087891</t>
+    <t xml:space="preserve">2.44101691246033</t>
   </si>
   <si>
     <t xml:space="preserve">2.47350192070007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43637609481812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38996887207031</t>
+    <t xml:space="preserve">2.43637633323669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38996911048889</t>
   </si>
   <si>
     <t xml:space="preserve">2.3249990940094</t>
@@ -3179,19 +3179,19 @@
     <t xml:space="preserve">2.31107687950134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28323245048523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28787326812744</t>
+    <t xml:space="preserve">2.28323268890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28787302970886</t>
   </si>
   <si>
     <t xml:space="preserve">2.26002883911133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33428072929382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33892107009888</t>
+    <t xml:space="preserve">2.33428049087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33892130851746</t>
   </si>
   <si>
     <t xml:space="preserve">2.30643606185913</t>
@@ -3221,13 +3221,13 @@
     <t xml:space="preserve">2.18113660812378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22290325164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18577766418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11616683006287</t>
+    <t xml:space="preserve">2.22290301322937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18577742576599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11616659164429</t>
   </si>
   <si>
     <t xml:space="preserve">2.0976037979126</t>
@@ -3245,22 +3245,22 @@
     <t xml:space="preserve">2.04191517829895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02335262298584</t>
+    <t xml:space="preserve">2.02335238456726</t>
   </si>
   <si>
     <t xml:space="preserve">2.00014877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98158586025238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97694540023804</t>
+    <t xml:space="preserve">1.98158597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97694528102875</t>
   </si>
   <si>
     <t xml:space="preserve">1.99086737632751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99550807476044</t>
+    <t xml:space="preserve">1.99550831317902</t>
   </si>
   <si>
     <t xml:space="preserve">2.00478959083557</t>
@@ -3275,10 +3275,10 @@
     <t xml:space="preserve">2.05119657516479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00943040847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02799296379089</t>
+    <t xml:space="preserve">2.0094301700592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02799320220947</t>
   </si>
   <si>
     <t xml:space="preserve">1.95838224887848</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">1.93981945514679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91197526454926</t>
+    <t xml:space="preserve">1.91197514533997</t>
   </si>
   <si>
     <t xml:space="preserve">1.90269374847412</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">1.75419080257416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73562800884247</t>
+    <t xml:space="preserve">1.73562788963318</t>
   </si>
   <si>
     <t xml:space="preserve">1.82472968101501</t>
@@ -3317,16 +3317,16 @@
     <t xml:space="preserve">1.80431056022644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77646625041962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.793172955513</t>
+    <t xml:space="preserve">1.77646636962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79317283630371</t>
   </si>
   <si>
     <t xml:space="preserve">1.7950291633606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76904118061066</t>
+    <t xml:space="preserve">1.76904106140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75047838687897</t>
@@ -3356,7 +3356,7 @@
     <t xml:space="preserve">1.81916093826294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287335395813</t>
+    <t xml:space="preserve">1.82287347316742</t>
   </si>
   <si>
     <t xml:space="preserve">2.01871156692505</t>
@@ -3371,22 +3371,22 @@
     <t xml:space="preserve">2.37604665756226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38532829284668</t>
+    <t xml:space="preserve">2.3853280544281</t>
   </si>
   <si>
     <t xml:space="preserve">2.3714063167572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60344219207764</t>
+    <t xml:space="preserve">2.60344195365906</t>
   </si>
   <si>
     <t xml:space="preserve">3.56407022476196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64296245574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57799243927002</t>
+    <t xml:space="preserve">3.64296221733093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5779926776886</t>
   </si>
   <si>
     <t xml:space="preserve">3.55942964553833</t>
@@ -3395,19 +3395,19 @@
     <t xml:space="preserve">3.82859110832214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90748333930969</t>
+    <t xml:space="preserve">3.90748310089111</t>
   </si>
   <si>
     <t xml:space="preserve">4.00029754638672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81466913223267</t>
+    <t xml:space="preserve">3.81466889381409</t>
   </si>
   <si>
     <t xml:space="preserve">3.48517823219299</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42948961257935</t>
+    <t xml:space="preserve">3.42948937416077</t>
   </si>
   <si>
     <t xml:space="preserve">3.45733380317688</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">3.35987877845764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58727383613586</t>
+    <t xml:space="preserve">3.58727407455444</t>
   </si>
   <si>
     <t xml:space="preserve">3.52694439888</t>
@@ -4179,6 +4179,9 @@
   </si>
   <si>
     <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88000011444092</t>
   </si>
 </sst>
 </file>
@@ -69595,7 +69598,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6911805556</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>94575</v>
@@ -69616,6 +69619,32 @@
         <v>1384</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6910763889</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>38093</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>7.94000005722046</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>7.84999990463257</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>7.88000011444092</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1389</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="1392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="1393">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95473062992096</t>
+    <t xml:space="preserve">1.95473086833954</t>
   </si>
   <si>
     <t xml:space="preserve">FM.MI</t>
@@ -53,16 +53,16 @@
     <t xml:space="preserve">1.8558669090271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86453902721405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68415570259094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76914393901825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74486172199249</t>
+    <t xml:space="preserve">1.86453914642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68415582180023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76914405822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74486184120178</t>
   </si>
   <si>
     <t xml:space="preserve">1.69542992115021</t>
@@ -74,28 +74,28 @@
     <t xml:space="preserve">1.52285158634186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47949016094208</t>
+    <t xml:space="preserve">1.47949004173279</t>
   </si>
   <si>
     <t xml:space="preserve">1.34420251846313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45434057712555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55233728885651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48989689350128</t>
+    <t xml:space="preserve">1.45434045791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55233716964722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48989677429199</t>
   </si>
   <si>
     <t xml:space="preserve">1.54366493225098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.595698595047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51331198215485</t>
+    <t xml:space="preserve">1.59569871425629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51331210136414</t>
   </si>
   <si>
     <t xml:space="preserve">1.53325819969177</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">1.38582956790924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28349673748016</t>
+    <t xml:space="preserve">1.28349661827087</t>
   </si>
   <si>
     <t xml:space="preserve">1.17682766914368</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">1.24186980724335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2071807384491</t>
+    <t xml:space="preserve">1.20718061923981</t>
   </si>
   <si>
     <t xml:space="preserve">1.23059582710266</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">1.43873047828674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39710342884064</t>
+    <t xml:space="preserve">1.39710354804993</t>
   </si>
   <si>
     <t xml:space="preserve">1.50030362606049</t>
@@ -140,28 +140,28 @@
     <t xml:space="preserve">1.48295903205872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46561455726624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5211169719696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51678085327148</t>
+    <t xml:space="preserve">1.46561443805695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52111709117889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51678073406219</t>
   </si>
   <si>
     <t xml:space="preserve">1.4942330121994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47688841819763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47515392303467</t>
+    <t xml:space="preserve">1.47688853740692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47515404224396</t>
   </si>
   <si>
     <t xml:space="preserve">1.50984311103821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56014227867126</t>
+    <t xml:space="preserve">1.56014239788055</t>
   </si>
   <si>
     <t xml:space="preserve">1.58702635765076</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">1.54279780387878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51244461536407</t>
+    <t xml:space="preserve">1.51244485378265</t>
   </si>
   <si>
     <t xml:space="preserve">1.55147004127502</t>
@@ -191,28 +191,28 @@
     <t xml:space="preserve">1.70843815803528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67808532714844</t>
+    <t xml:space="preserve">1.67808520793915</t>
   </si>
   <si>
     <t xml:space="preserve">1.65467011928558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63298940658569</t>
+    <t xml:space="preserve">1.63298952579498</t>
   </si>
   <si>
     <t xml:space="preserve">1.6061053276062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53499257564545</t>
+    <t xml:space="preserve">1.53499269485474</t>
   </si>
   <si>
     <t xml:space="preserve">1.49770188331604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49683475494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48122453689575</t>
+    <t xml:space="preserve">1.49683463573456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48122441768646</t>
   </si>
   <si>
     <t xml:space="preserve">1.41791701316833</t>
@@ -236,13 +236,13 @@
     <t xml:space="preserve">1.62952041625977</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60437083244324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60870718955994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62518441677094</t>
+    <t xml:space="preserve">1.60437095165253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60870707035065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62518429756165</t>
   </si>
   <si>
     <t xml:space="preserve">1.65987348556519</t>
@@ -260,10 +260,10 @@
     <t xml:space="preserve">1.58876085281372</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49249839782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45780944824219</t>
+    <t xml:space="preserve">1.49249851703644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4578093290329</t>
   </si>
   <si>
     <t xml:space="preserve">1.47775566577911</t>
@@ -272,52 +272,52 @@
     <t xml:space="preserve">1.47428679466248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46908330917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56794726848602</t>
+    <t xml:space="preserve">1.46908342838287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56794714927673</t>
   </si>
   <si>
     <t xml:space="preserve">1.53932881355286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53065657615662</t>
+    <t xml:space="preserve">1.53065645694733</t>
   </si>
   <si>
     <t xml:space="preserve">1.54106318950653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56968176364899</t>
+    <t xml:space="preserve">1.5696816444397</t>
   </si>
   <si>
     <t xml:space="preserve">1.5471339225769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55060279369354</t>
+    <t xml:space="preserve">1.55060267448425</t>
   </si>
   <si>
     <t xml:space="preserve">1.56708014011383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5740180015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5107102394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59136259555817</t>
+    <t xml:space="preserve">1.57401812076569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51071035861969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59136247634888</t>
   </si>
   <si>
     <t xml:space="preserve">1.56100940704346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54453217983246</t>
+    <t xml:space="preserve">1.54453229904175</t>
   </si>
   <si>
     <t xml:space="preserve">1.45000445842743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38929843902588</t>
+    <t xml:space="preserve">1.38929855823517</t>
   </si>
   <si>
     <t xml:space="preserve">1.40057253837585</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">1.32338917255402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3294597864151</t>
+    <t xml:space="preserve">1.32945990562439</t>
   </si>
   <si>
     <t xml:space="preserve">1.3884311914444</t>
@@ -365,10 +365,10 @@
     <t xml:space="preserve">1.36154723167419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37802457809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38236057758331</t>
+    <t xml:space="preserve">1.37802445888519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3823606967926</t>
   </si>
   <si>
     <t xml:space="preserve">1.39623630046844</t>
@@ -377,19 +377,19 @@
     <t xml:space="preserve">1.377157330513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40490853786469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39450192451477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4040412902832</t>
+    <t xml:space="preserve">1.4049084186554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39450180530548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40404140949249</t>
   </si>
   <si>
     <t xml:space="preserve">1.393634557724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42225313186646</t>
+    <t xml:space="preserve">1.42225301265717</t>
   </si>
   <si>
     <t xml:space="preserve">1.42832362651825</t>
@@ -401,13 +401,13 @@
     <t xml:space="preserve">1.38062620162964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36588335037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35634386539459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35460948944092</t>
+    <t xml:space="preserve">1.3658834695816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3563437461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35460937023163</t>
   </si>
   <si>
     <t xml:space="preserve">1.34333539009094</t>
@@ -419,10 +419,10 @@
     <t xml:space="preserve">1.32685804367065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30170857906342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30777895450592</t>
+    <t xml:space="preserve">1.30170845985413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30777907371521</t>
   </si>
   <si>
     <t xml:space="preserve">1.34767150878906</t>
@@ -431,10 +431,10 @@
     <t xml:space="preserve">1.34506988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33379590511322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37108671665192</t>
+    <t xml:space="preserve">1.33379578590393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37108659744263</t>
   </si>
   <si>
     <t xml:space="preserve">1.35547661781311</t>
@@ -443,16 +443,16 @@
     <t xml:space="preserve">1.34940600395203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33813214302063</t>
+    <t xml:space="preserve">1.33813202381134</t>
   </si>
   <si>
     <t xml:space="preserve">1.34853875637054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41704976558685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40317404270172</t>
+    <t xml:space="preserve">1.41704964637756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40317416191101</t>
   </si>
   <si>
     <t xml:space="preserve">1.39536905288696</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">1.41097915172577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36501610279083</t>
+    <t xml:space="preserve">1.36501622200012</t>
   </si>
   <si>
     <t xml:space="preserve">1.38322782516479</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">1.38149344921112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39797079563141</t>
+    <t xml:space="preserve">1.39797067642212</t>
   </si>
   <si>
     <t xml:space="preserve">1.37455570697784</t>
@@ -482,19 +482,19 @@
     <t xml:space="preserve">1.41358077526093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42138600349426</t>
+    <t xml:space="preserve">1.42138588428497</t>
   </si>
   <si>
     <t xml:space="preserve">1.41271352767944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40924465656281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42572200298309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35114049911499</t>
+    <t xml:space="preserve">1.40924477577209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42572212219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3511403799057</t>
   </si>
   <si>
     <t xml:space="preserve">1.35894548892975</t>
@@ -509,10 +509,10 @@
     <t xml:space="preserve">1.36241436004639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33032703399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32078742980957</t>
+    <t xml:space="preserve">1.33032715320587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32078754901886</t>
   </si>
   <si>
     <t xml:space="preserve">1.3190530538559</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">1.17942941188812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26181602478027</t>
+    <t xml:space="preserve">1.26181614398956</t>
   </si>
   <si>
     <t xml:space="preserve">1.29216909408569</t>
@@ -536,16 +536,16 @@
     <t xml:space="preserve">1.23146307468414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2175874710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2488077878952</t>
+    <t xml:space="preserve">1.21758759021759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24880766868591</t>
   </si>
   <si>
     <t xml:space="preserve">1.2288613319397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18549990653992</t>
+    <t xml:space="preserve">1.18550002574921</t>
   </si>
   <si>
     <t xml:space="preserve">1.15774881839752</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">1.11872339248657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13086473941803</t>
+    <t xml:space="preserve">1.13086462020874</t>
   </si>
   <si>
     <t xml:space="preserve">1.12305963039398</t>
@@ -575,10 +575,10 @@
     <t xml:space="preserve">1.09791004657745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09270656108856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07536208629608</t>
+    <t xml:space="preserve">1.09270668029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07536220550537</t>
   </si>
   <si>
     <t xml:space="preserve">1.07276034355164</t>
@@ -587,22 +587,22 @@
     <t xml:space="preserve">1.10398066043854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15427982807159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16295218467712</t>
+    <t xml:space="preserve">1.1542797088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16295194625854</t>
   </si>
   <si>
     <t xml:space="preserve">1.16208481788635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17856204509735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18289840221405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20544624328613</t>
+    <t xml:space="preserve">1.17856216430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18289828300476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20544612407684</t>
   </si>
   <si>
     <t xml:space="preserve">1.23493194580078</t>
@@ -611,10 +611,10 @@
     <t xml:space="preserve">1.24533867835999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21845459938049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19937574863434</t>
+    <t xml:space="preserve">1.21845471858978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19937562942505</t>
   </si>
   <si>
     <t xml:space="preserve">1.20111012458801</t>
@@ -644,7 +644,7 @@
     <t xml:space="preserve">1.35721111297607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34593713283539</t>
+    <t xml:space="preserve">1.3459370136261</t>
   </si>
   <si>
     <t xml:space="preserve">1.33292853832245</t>
@@ -656,25 +656,25 @@
     <t xml:space="preserve">1.25747990608215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23319756984711</t>
+    <t xml:space="preserve">1.2331976890564</t>
   </si>
   <si>
     <t xml:space="preserve">1.2444714307785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22712695598602</t>
+    <t xml:space="preserve">1.22712683677673</t>
   </si>
   <si>
     <t xml:space="preserve">1.25661265850067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22365808486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2227908372879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25314378738403</t>
+    <t xml:space="preserve">1.2236579656601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22279071807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25314390659332</t>
   </si>
   <si>
     <t xml:space="preserve">1.22625982761383</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">1.20197737216949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18810176849365</t>
+    <t xml:space="preserve">1.18810164928436</t>
   </si>
   <si>
     <t xml:space="preserve">1.191570520401</t>
@@ -710,28 +710,28 @@
     <t xml:space="preserve">1.20284450054169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19243776798248</t>
+    <t xml:space="preserve">1.19243788719177</t>
   </si>
   <si>
     <t xml:space="preserve">1.2340646982193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27742612361908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27222275733948</t>
+    <t xml:space="preserve">1.27742624282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27222263813019</t>
   </si>
   <si>
     <t xml:space="preserve">1.2982394695282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26355040073395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24273705482483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23579919338226</t>
+    <t xml:space="preserve">1.26355051994324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24273693561554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23579907417297</t>
   </si>
   <si>
     <t xml:space="preserve">1.22018897533417</t>
@@ -740,10 +740,10 @@
     <t xml:space="preserve">1.24794042110443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2496749162674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29043447971344</t>
+    <t xml:space="preserve">1.24967479705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29043459892273</t>
   </si>
   <si>
     <t xml:space="preserve">1.29303634166718</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">1.31818580627441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30691170692444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27309000492096</t>
+    <t xml:space="preserve">1.30691182613373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27308988571167</t>
   </si>
   <si>
     <t xml:space="preserve">1.24013531208038</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">1.2704883813858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2652850151062</t>
+    <t xml:space="preserve">1.26528489589691</t>
   </si>
   <si>
     <t xml:space="preserve">1.28436386585236</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">1.2869656085968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33986639976501</t>
+    <t xml:space="preserve">1.3398665189743</t>
   </si>
   <si>
     <t xml:space="preserve">1.33899927139282</t>
@@ -794,13 +794,13 @@
     <t xml:space="preserve">1.41184639930725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57835400104523</t>
+    <t xml:space="preserve">1.57835412025452</t>
   </si>
   <si>
     <t xml:space="preserve">1.51851534843445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54019618034363</t>
+    <t xml:space="preserve">1.54019606113434</t>
   </si>
   <si>
     <t xml:space="preserve">1.49856913089752</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">1.50203800201416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4786229133606</t>
+    <t xml:space="preserve">1.47862303256989</t>
   </si>
   <si>
     <t xml:space="preserve">1.43352711200714</t>
@@ -830,13 +830,13 @@
     <t xml:space="preserve">1.48729526996613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47602117061615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45694220066071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4682160615921</t>
+    <t xml:space="preserve">1.47602128982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45694208145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46821618080139</t>
   </si>
   <si>
     <t xml:space="preserve">1.45867669582367</t>
@@ -857,58 +857,58 @@
     <t xml:space="preserve">1.52892208099365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50637423992157</t>
+    <t xml:space="preserve">1.50637412071228</t>
   </si>
   <si>
     <t xml:space="preserve">1.57488512992859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58269035816193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56187665462494</t>
+    <t xml:space="preserve">1.58269023895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56187677383423</t>
   </si>
   <si>
     <t xml:space="preserve">1.53585994243622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48642802238464</t>
+    <t xml:space="preserve">1.48642790317535</t>
   </si>
   <si>
     <t xml:space="preserve">1.49510014057159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51157748699188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48902952671051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48035740852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48816251754761</t>
+    <t xml:space="preserve">1.51157760620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4890296459198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48035728931427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48816239833832</t>
   </si>
   <si>
     <t xml:space="preserve">1.51591360569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56881463527679</t>
+    <t xml:space="preserve">1.5688145160675</t>
   </si>
   <si>
     <t xml:space="preserve">1.57054901123047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64686501026154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78648865222931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7604718208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85933601856232</t>
+    <t xml:space="preserve">1.64686512947083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78648853302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76047170162201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85933589935303</t>
   </si>
   <si>
     <t xml:space="preserve">1.86627352237701</t>
@@ -938,43 +938,43 @@
     <t xml:space="preserve">2.01543664932251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98074746131897</t>
+    <t xml:space="preserve">1.98074769973755</t>
   </si>
   <si>
     <t xml:space="preserve">1.90443181991577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90790033340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91657269001007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90616583824158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84892904758453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87321138381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83158445358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84719467163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93218278884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93738639354706</t>
+    <t xml:space="preserve">1.90790057182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91657280921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90616595745087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84892892837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87321150302887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83158433437347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84719455242157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93218290805817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93738603591919</t>
   </si>
   <si>
     <t xml:space="preserve">1.9252450466156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94258964061737</t>
+    <t xml:space="preserve">1.94258952140808</t>
   </si>
   <si>
     <t xml:space="preserve">1.97727870941162</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">2.0206401348114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06920504570007</t>
+    <t xml:space="preserve">2.06920480728149</t>
   </si>
   <si>
     <t xml:space="preserve">2.01196765899658</t>
@@ -995,22 +995,22 @@
     <t xml:space="preserve">2.01370215415955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99462294578552</t>
+    <t xml:space="preserve">1.9946231842041</t>
   </si>
   <si>
     <t xml:space="preserve">1.94432425498962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90269720554352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82117748260498</t>
+    <t xml:space="preserve">1.90269732475281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82117760181427</t>
   </si>
   <si>
     <t xml:space="preserve">1.91310393810272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72144675254822</t>
+    <t xml:space="preserve">1.72144663333893</t>
   </si>
   <si>
     <t xml:space="preserve">1.67114746570587</t>
@@ -1019,28 +1019,28 @@
     <t xml:space="preserve">1.69976592063904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68762481212616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67895257472992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63992714881897</t>
+    <t xml:space="preserve">1.68762469291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67895245552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63992726802826</t>
   </si>
   <si>
     <t xml:space="preserve">1.64773213863373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62865328788757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6269189119339</t>
+    <t xml:space="preserve">1.62865316867828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62691879272461</t>
   </si>
   <si>
     <t xml:space="preserve">1.60350358486176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59656572341919</t>
+    <t xml:space="preserve">1.59656584262848</t>
   </si>
   <si>
     <t xml:space="preserve">1.63905990123749</t>
@@ -1055,19 +1055,19 @@
     <t xml:space="preserve">1.6910936832428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72925162315369</t>
+    <t xml:space="preserve">1.72925174236298</t>
   </si>
   <si>
     <t xml:space="preserve">1.67548358440399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65640449523926</t>
+    <t xml:space="preserve">1.65640461444855</t>
   </si>
   <si>
     <t xml:space="preserve">1.63038766384125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66681122779846</t>
+    <t xml:space="preserve">1.66681134700775</t>
   </si>
   <si>
     <t xml:space="preserve">1.68155407905579</t>
@@ -1097,19 +1097,19 @@
     <t xml:space="preserve">1.71711039543152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70670366287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72578263282776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72751712799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71190714836121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74312722682953</t>
+    <t xml:space="preserve">1.7067037820816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72578275203705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72751724720001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71190702915192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74312734603882</t>
   </si>
   <si>
     <t xml:space="preserve">1.77781629562378</t>
@@ -1118,16 +1118,16 @@
     <t xml:space="preserve">1.77348041534424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80383312702179</t>
+    <t xml:space="preserve">1.80383324623108</t>
   </si>
   <si>
     <t xml:space="preserve">1.93391728401184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88188362121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95559811592102</t>
+    <t xml:space="preserve">1.8818838596344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9555983543396</t>
   </si>
   <si>
     <t xml:space="preserve">1.88621973991394</t>
@@ -1136,22 +1136,22 @@
     <t xml:space="preserve">1.81684172153473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89489197731018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8081693649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82984983921051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85153067111969</t>
+    <t xml:space="preserve">1.89489221572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80816948413849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8298499584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85153090953827</t>
   </si>
   <si>
     <t xml:space="preserve">1.78215265274048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81250536441803</t>
+    <t xml:space="preserve">1.81250548362732</t>
   </si>
   <si>
     <t xml:space="preserve">1.79082489013672</t>
@@ -1169,22 +1169,22 @@
     <t xml:space="preserve">1.89922833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89055609703064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87754774093628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8341863155365</t>
+    <t xml:space="preserve">1.89055585861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8775475025177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83418619632721</t>
   </si>
   <si>
     <t xml:space="preserve">1.84285843372345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82551395893097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83852207660675</t>
+    <t xml:space="preserve">1.82551383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83852219581604</t>
   </si>
   <si>
     <t xml:space="preserve">1.86020302772522</t>
@@ -1196,37 +1196,37 @@
     <t xml:space="preserve">1.98161494731903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92958092689514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98595106601715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04665660858154</t>
+    <t xml:space="preserve">1.92958104610443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98595082759857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04665684700012</t>
   </si>
   <si>
     <t xml:space="preserve">2.03364849090576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04232096672058</t>
+    <t xml:space="preserve">2.042320728302</t>
   </si>
   <si>
     <t xml:space="preserve">2.072674036026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08134579658508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1116988658905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15072417259216</t>
+    <t xml:space="preserve">2.08134603500366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11169910430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15072441101074</t>
   </si>
   <si>
     <t xml:space="preserve">2.05532932281494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18541312217712</t>
+    <t xml:space="preserve">2.1854133605957</t>
   </si>
   <si>
     <t xml:space="preserve">2.33717799186707</t>
@@ -1235,16 +1235,16 @@
     <t xml:space="preserve">2.3024890422821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28080868721008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21143007278442</t>
+    <t xml:space="preserve">2.2808084487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.211430311203</t>
   </si>
   <si>
     <t xml:space="preserve">2.30682516098022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28514432907104</t>
+    <t xml:space="preserve">2.28514456748962</t>
   </si>
   <si>
     <t xml:space="preserve">2.44991755485535</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">2.38921189308167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49761557579041</t>
+    <t xml:space="preserve">2.49761533737183</t>
   </si>
   <si>
     <t xml:space="preserve">2.57566571235657</t>
@@ -1277,31 +1277,31 @@
     <t xml:space="preserve">2.83583402633667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91388440132141</t>
+    <t xml:space="preserve">2.91388416290283</t>
   </si>
   <si>
     <t xml:space="preserve">2.92255663871765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93122911453247</t>
+    <t xml:space="preserve">2.93122887611389</t>
   </si>
   <si>
     <t xml:space="preserve">2.87052297592163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92689299583435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10033845901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23909473419189</t>
+    <t xml:space="preserve">2.92689275741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10033822059631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23909449577332</t>
   </si>
   <si>
     <t xml:space="preserve">3.25210332870483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21741437911987</t>
+    <t xml:space="preserve">3.21741414070129</t>
   </si>
   <si>
     <t xml:space="preserve">3.25643944740295</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">3.36050653457642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20874166488647</t>
+    <t xml:space="preserve">3.20874190330505</t>
   </si>
   <si>
     <t xml:space="preserve">3.36917877197266</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">3.50793528556824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48625445365906</t>
+    <t xml:space="preserve">3.48625469207764</t>
   </si>
   <si>
     <t xml:space="preserve">3.55563259124756</t>
@@ -1346,16 +1346,16 @@
     <t xml:space="preserve">3.62934684753418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66403603553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73341417312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80712890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90686011314392</t>
+    <t xml:space="preserve">3.6640362739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73341393470764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80712842941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90685963630676</t>
   </si>
   <si>
     <t xml:space="preserve">4.07596921920776</t>
@@ -1364,7 +1364,7 @@
     <t xml:space="preserve">4.0456166267395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09764957427979</t>
+    <t xml:space="preserve">4.09765005111694</t>
   </si>
   <si>
     <t xml:space="preserve">3.86783456802368</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">3.945885181427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9719021320343</t>
+    <t xml:space="preserve">3.97190165519714</t>
   </si>
   <si>
     <t xml:space="preserve">3.7117338180542</t>
@@ -1385,10 +1385,10 @@
     <t xml:space="preserve">3.91986799240112</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07163333892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24941492080688</t>
+    <t xml:space="preserve">4.07163286209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24941539764404</t>
   </si>
   <si>
     <t xml:space="preserve">4.25375127792358</t>
@@ -1400,16 +1400,16 @@
     <t xml:space="preserve">4.62232255935669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57896137237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74373388290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75240707397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05593585968018</t>
+    <t xml:space="preserve">4.57896184921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74373435974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75240659713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05593633651733</t>
   </si>
   <si>
     <t xml:space="preserve">4.98655796051025</t>
@@ -1418,10 +1418,10 @@
     <t xml:space="preserve">4.95186901092529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87381839752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31879329681396</t>
+    <t xml:space="preserve">4.87381887435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31879281997681</t>
   </si>
   <si>
     <t xml:space="preserve">4.80444049835205</t>
@@ -1430,7 +1430,7 @@
     <t xml:space="preserve">4.97788572311401</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01257514953613</t>
+    <t xml:space="preserve">5.01257562637329</t>
   </si>
   <si>
     <t xml:space="preserve">5.03859186172485</t>
@@ -1439,13 +1439,13 @@
     <t xml:space="preserve">4.91718006134033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82178497314453</t>
+    <t xml:space="preserve">4.82178449630737</t>
   </si>
   <si>
     <t xml:space="preserve">4.85647392272949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89116334915161</t>
+    <t xml:space="preserve">4.89116287231445</t>
   </si>
   <si>
     <t xml:space="preserve">4.83045721054077</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">4.76107883453369</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54427146911621</t>
+    <t xml:space="preserve">4.54427194595337</t>
   </si>
   <si>
     <t xml:space="preserve">4.70904541015625</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">4.60497808456421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58763360977173</t>
+    <t xml:space="preserve">4.58763313293457</t>
   </si>
   <si>
     <t xml:space="preserve">4.64833927154541</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">4.47489356994629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40551567077637</t>
+    <t xml:space="preserve">4.40551519393921</t>
   </si>
   <si>
     <t xml:space="preserve">4.1843729019165</t>
@@ -1487,10 +1487,10 @@
     <t xml:space="preserve">4.18870878219604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24074220657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08464193344116</t>
+    <t xml:space="preserve">4.24074172973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.084641456604</t>
   </si>
   <si>
     <t xml:space="preserve">3.9285409450531</t>
@@ -1499,19 +1499,19 @@
     <t xml:space="preserve">3.91553211212158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85916185379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78111219406128</t>
+    <t xml:space="preserve">3.85916209220886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78111171722412</t>
   </si>
   <si>
     <t xml:space="preserve">4.14101123809814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62501072883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31280899047852</t>
+    <t xml:space="preserve">3.62501096725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31280922889709</t>
   </si>
   <si>
     <t xml:space="preserve">3.28679227828979</t>
@@ -1538,25 +1538,25 @@
     <t xml:space="preserve">2.96158194541931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89653968811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90521192550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02662396430969</t>
+    <t xml:space="preserve">2.89653992652893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90521216392517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02662420272827</t>
   </si>
   <si>
     <t xml:space="preserve">2.75344729423523</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80548095703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88786768913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04396843910217</t>
+    <t xml:space="preserve">2.80548071861267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88786745071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04396867752075</t>
   </si>
   <si>
     <t xml:space="preserve">3.2607753276825</t>
@@ -1565,28 +1565,28 @@
     <t xml:space="preserve">3.24343085289001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19139719009399</t>
+    <t xml:space="preserve">3.19139742851257</t>
   </si>
   <si>
     <t xml:space="preserve">3.42554879188538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43855667114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39519572257996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20440578460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06998515129089</t>
+    <t xml:space="preserve">3.43855690956116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39519548416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20440554618835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06998538970947</t>
   </si>
   <si>
     <t xml:space="preserve">2.86618685722351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93990135192871</t>
+    <t xml:space="preserve">2.93990159034729</t>
   </si>
   <si>
     <t xml:space="preserve">2.88353133201599</t>
@@ -1604,7 +1604,7 @@
     <t xml:space="preserve">3.32148122787476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15670800209045</t>
+    <t xml:space="preserve">3.15670824050903</t>
   </si>
   <si>
     <t xml:space="preserve">3.11768293380737</t>
@@ -1613,16 +1613,16 @@
     <t xml:space="preserve">3.08732986450195</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06564950942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81848931312561</t>
+    <t xml:space="preserve">3.06564927101135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81848955154419</t>
   </si>
   <si>
     <t xml:space="preserve">2.68840503692627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73176670074463</t>
+    <t xml:space="preserve">2.73176693916321</t>
   </si>
   <si>
     <t xml:space="preserve">2.63203549385071</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">3.17405271530151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30413699150085</t>
+    <t xml:space="preserve">3.30413675308228</t>
   </si>
   <si>
     <t xml:space="preserve">3.3084728717804</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">3.17838859558105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10467457771301</t>
+    <t xml:space="preserve">3.10467433929443</t>
   </si>
   <si>
     <t xml:space="preserve">3.16104412078857</t>
@@ -1652,28 +1652,28 @@
     <t xml:space="preserve">3.330153465271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46023774147034</t>
+    <t xml:space="preserve">3.46023797988892</t>
   </si>
   <si>
     <t xml:space="preserve">3.59032154083252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88517928123474</t>
+    <t xml:space="preserve">3.88517904281616</t>
   </si>
   <si>
     <t xml:space="preserve">3.90252375602722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85482668876648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11499452590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27543163299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10198640823364</t>
+    <t xml:space="preserve">3.85482597351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11499404907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27543115615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10198593139648</t>
   </si>
   <si>
     <t xml:space="preserve">4.145348072052</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">3.95889329910278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82447338104248</t>
+    <t xml:space="preserve">3.82447361946106</t>
   </si>
   <si>
     <t xml:space="preserve">3.9675657749176</t>
@@ -1694,13 +1694,13 @@
     <t xml:space="preserve">3.94154906272888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99791932106018</t>
+    <t xml:space="preserve">3.99791884422302</t>
   </si>
   <si>
     <t xml:space="preserve">4.00659132003784</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06296014785767</t>
+    <t xml:space="preserve">4.06296062469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.05862474441528</t>
@@ -1709,13 +1709,13 @@
     <t xml:space="preserve">4.01526355743408</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09331321716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03260803222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98924589157104</t>
+    <t xml:space="preserve">4.09331369400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0326075553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9892463684082</t>
   </si>
   <si>
     <t xml:space="preserve">3.92420434951782</t>
@@ -1724,13 +1724,13 @@
     <t xml:space="preserve">3.82880973815918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75943088531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74642276763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56864094734192</t>
+    <t xml:space="preserve">3.7594313621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74642300605774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5686411857605</t>
   </si>
   <si>
     <t xml:space="preserve">3.77677583694458</t>
@@ -1742,19 +1742,19 @@
     <t xml:space="preserve">4.17136430740356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08897733688354</t>
+    <t xml:space="preserve">4.0889778137207</t>
   </si>
   <si>
     <t xml:space="preserve">4.06729698181152</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16269159317017</t>
+    <t xml:space="preserve">4.16269207000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.21906185150146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2320704460144</t>
+    <t xml:space="preserve">4.23206996917725</t>
   </si>
   <si>
     <t xml:space="preserve">4.20171689987183</t>
@@ -1763,10 +1763,10 @@
     <t xml:space="preserve">4.68302869796753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88249063491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76975107192993</t>
+    <t xml:space="preserve">4.88249111175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76975154876709</t>
   </si>
   <si>
     <t xml:space="preserve">4.72638940811157</t>
@@ -1778,13 +1778,13 @@
     <t xml:space="preserve">4.55294418334961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44887733459473</t>
+    <t xml:space="preserve">4.44887685775757</t>
   </si>
   <si>
     <t xml:space="preserve">4.39684343338013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91119623184204</t>
+    <t xml:space="preserve">3.9111967086792</t>
   </si>
   <si>
     <t xml:space="preserve">4.04995250701904</t>
@@ -1796,31 +1796,31 @@
     <t xml:space="preserve">4.12285375595093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01130485534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91760349273682</t>
+    <t xml:space="preserve">4.01130437850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91760301589966</t>
   </si>
   <si>
     <t xml:space="preserve">4.22547912597656</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00684261322021</t>
+    <t xml:space="preserve">4.00684213638306</t>
   </si>
   <si>
     <t xml:space="preserve">3.83282613754272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85513591766357</t>
+    <t xml:space="preserve">3.85513615608215</t>
   </si>
   <si>
     <t xml:space="preserve">3.85959792137146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93098950386047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83728790283203</t>
+    <t xml:space="preserve">3.93098926544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83728814125061</t>
   </si>
   <si>
     <t xml:space="preserve">4.01576662063599</t>
@@ -1838,31 +1838,31 @@
     <t xml:space="preserve">3.74358701705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76143503189087</t>
+    <t xml:space="preserve">3.76143455505371</t>
   </si>
   <si>
     <t xml:space="preserve">3.61419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68111944198608</t>
+    <t xml:space="preserve">3.6811192035675</t>
   </si>
   <si>
     <t xml:space="preserve">3.52048873901367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48479270935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67219519615173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59634232521057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58741807937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64096140861511</t>
+    <t xml:space="preserve">3.48479294776917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67219543457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59634208679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5874183177948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64096164703369</t>
   </si>
   <si>
     <t xml:space="preserve">3.64988589286804</t>
@@ -1880,13 +1880,13 @@
     <t xml:space="preserve">3.41786336898804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44909715652466</t>
+    <t xml:space="preserve">3.44909739494324</t>
   </si>
   <si>
     <t xml:space="preserve">3.4223256111145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47140717506409</t>
+    <t xml:space="preserve">3.47140693664551</t>
   </si>
   <si>
     <t xml:space="preserve">3.50710296630859</t>
@@ -1898,7 +1898,7 @@
     <t xml:space="preserve">3.42678737640381</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36878204345703</t>
+    <t xml:space="preserve">3.36878228187561</t>
   </si>
   <si>
     <t xml:space="preserve">3.34647226333618</t>
@@ -1907,19 +1907,19 @@
     <t xml:space="preserve">3.31523823738098</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32862424850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36432027816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39555358886719</t>
+    <t xml:space="preserve">3.32862448692322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36432003974915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39555382728577</t>
   </si>
   <si>
     <t xml:space="preserve">3.35539603233337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31077671051025</t>
+    <t xml:space="preserve">3.31077647209167</t>
   </si>
   <si>
     <t xml:space="preserve">3.27954268455505</t>
@@ -1931,16 +1931,16 @@
     <t xml:space="preserve">3.38216781616211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40001583099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30631422996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28400468826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33308625221252</t>
+    <t xml:space="preserve">3.40001559257507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30631446838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28400492668152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33308601379395</t>
   </si>
   <si>
     <t xml:space="preserve">3.35093426704407</t>
@@ -1952,40 +1952,40 @@
     <t xml:space="preserve">3.65880942344666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71235299110413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8105161190033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80605459213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76589632034302</t>
+    <t xml:space="preserve">3.71235322952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81051659584045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80605435371399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7658965587616</t>
   </si>
   <si>
     <t xml:space="preserve">3.6008038520813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5561842918396</t>
+    <t xml:space="preserve">3.55618405342102</t>
   </si>
   <si>
     <t xml:space="preserve">3.4669451713562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62757587432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78374409675598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69004344940186</t>
+    <t xml:space="preserve">3.62757611274719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78374433517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69004368782043</t>
   </si>
   <si>
     <t xml:space="preserve">3.70789122581482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6766574382782</t>
+    <t xml:space="preserve">3.67665719985962</t>
   </si>
   <si>
     <t xml:space="preserve">3.73912501335144</t>
@@ -1997,16 +1997,16 @@
     <t xml:space="preserve">3.66773366928101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69896745681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7212769985199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72573924064636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62311387062073</t>
+    <t xml:space="preserve">3.69896721839905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72127723693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72573947906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62311363220215</t>
   </si>
   <si>
     <t xml:space="preserve">3.60972809791565</t>
@@ -2018,10 +2018,10 @@
     <t xml:space="preserve">3.56957030296326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99791884422302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96668553352356</t>
+    <t xml:space="preserve">3.99791860580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96668481826782</t>
   </si>
   <si>
     <t xml:space="preserve">3.73466277122498</t>
@@ -2036,10 +2036,10 @@
     <t xml:space="preserve">3.63203811645508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60526585578918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57849454879761</t>
+    <t xml:space="preserve">3.60526609420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57849431037903</t>
   </si>
   <si>
     <t xml:space="preserve">3.56510829925537</t>
@@ -2051,10 +2051,10 @@
     <t xml:space="preserve">4.06038618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91314172744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98899459838867</t>
+    <t xml:space="preserve">3.91314196586609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98899483680725</t>
   </si>
   <si>
     <t xml:space="preserve">3.98007082939148</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">4.03361415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92652702331543</t>
+    <t xml:space="preserve">3.92652750015259</t>
   </si>
   <si>
     <t xml:space="preserve">3.90867972373962</t>
@@ -2084,10 +2084,10 @@
     <t xml:space="preserve">4.0425386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93545126914978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89083194732666</t>
+    <t xml:space="preserve">3.93545150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8908314704895</t>
   </si>
   <si>
     <t xml:space="preserve">4.07823419570923</t>
@@ -2096,22 +2096,22 @@
     <t xml:space="preserve">4.19424486160278</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00238037109375</t>
+    <t xml:space="preserve">4.00238084793091</t>
   </si>
   <si>
     <t xml:space="preserve">4.1763973236084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.087158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21655464172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46196269989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53335428237915</t>
+    <t xml:space="preserve">4.08715772628784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21655511856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46196317672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53335380554199</t>
   </si>
   <si>
     <t xml:space="preserve">4.64044094085693</t>
@@ -2138,10 +2138,10 @@
     <t xml:space="preserve">4.81892013549805</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90815877914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00632286071777</t>
+    <t xml:space="preserve">4.90815925598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00632190704346</t>
   </si>
   <si>
     <t xml:space="preserve">4.89923524856567</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">4.85461568832397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97955083847046</t>
+    <t xml:space="preserve">4.9795503616333</t>
   </si>
   <si>
     <t xml:space="preserve">5.12233304977417</t>
@@ -2159,10 +2159,10 @@
     <t xml:space="preserve">5.04201793670654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89031171798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95277881622314</t>
+    <t xml:space="preserve">4.8903112411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9527792930603</t>
   </si>
   <si>
     <t xml:space="preserve">4.8456916809082</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">4.76537656784058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82784414291382</t>
+    <t xml:space="preserve">4.82784366607666</t>
   </si>
   <si>
     <t xml:space="preserve">4.80999565124512</t>
@@ -2186,7 +2186,7 @@
     <t xml:space="preserve">4.99739837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23834419250488</t>
+    <t xml:space="preserve">5.23834466934204</t>
   </si>
   <si>
     <t xml:space="preserve">5.45251893997192</t>
@@ -2201,52 +2201,52 @@
     <t xml:space="preserve">5.42574691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15802907943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88138675689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70290851593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71183300018311</t>
+    <t xml:space="preserve">5.15802955627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88138723373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70290899276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71183347702026</t>
   </si>
   <si>
     <t xml:space="preserve">4.73860454559326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63151741027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67613649368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56012630462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41734266281128</t>
+    <t xml:space="preserve">4.63151788711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67613697052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56012582778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41734313964844</t>
   </si>
   <si>
     <t xml:space="preserve">4.14516353607178</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02022886276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98453330993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94883728027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80159258842468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12783622741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15906953811646</t>
+    <t xml:space="preserve">4.02022838592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98453307151794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94883751869202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8015923500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12783575057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15906977653503</t>
   </si>
   <si>
     <t xml:space="preserve">3.25277090072632</t>
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">2.72625946998596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75749278068542</t>
+    <t xml:space="preserve">2.757493019104</t>
   </si>
   <si>
     <t xml:space="preserve">2.44961762428284</t>
@@ -2264,34 +2264,34 @@
     <t xml:space="preserve">2.45854163169861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14174199104309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99895942211151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10604619979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25775337219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34699273109436</t>
+    <t xml:space="preserve">2.14174222946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99895930290222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10604643821716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2577531337738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34699249267578</t>
   </si>
   <si>
     <t xml:space="preserve">2.4228458404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54331874847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40053629875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48085141181946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45407938957214</t>
+    <t xml:space="preserve">2.54331851005554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40053606033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48085117340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45407962799072</t>
   </si>
   <si>
     <t xml:space="preserve">2.46300363540649</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">2.73964524269104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23938512802124</t>
+    <t xml:space="preserve">3.23938536643982</t>
   </si>
   <si>
     <t xml:space="preserve">3.20368933677673</t>
@@ -2318,16 +2318,16 @@
     <t xml:space="preserve">2.85119438171387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99843907356262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9359712600708</t>
+    <t xml:space="preserve">2.99843883514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93597173690796</t>
   </si>
   <si>
     <t xml:space="preserve">2.94489550590515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89135193824768</t>
+    <t xml:space="preserve">2.8913516998291</t>
   </si>
   <si>
     <t xml:space="preserve">2.97612929344177</t>
@@ -2336,16 +2336,16 @@
     <t xml:space="preserve">2.85565638542175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98059105873108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00290083885193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13229775428772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01182508468628</t>
+    <t xml:space="preserve">2.98059129714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00290107727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1322979927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0118248462677</t>
   </si>
   <si>
     <t xml:space="preserve">2.98862147331238</t>
@@ -2360,22 +2360,22 @@
     <t xml:space="preserve">2.951495885849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8772439956665</t>
+    <t xml:space="preserve">2.87724423408508</t>
   </si>
   <si>
     <t xml:space="preserve">2.88652563095093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85404062271118</t>
+    <t xml:space="preserve">2.85404086112976</t>
   </si>
   <si>
     <t xml:space="preserve">2.7473042011261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71481895446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96077704429626</t>
+    <t xml:space="preserve">2.71481919288635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96077728271484</t>
   </si>
   <si>
     <t xml:space="preserve">2.75658559799194</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">2.78442978858948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83547806739807</t>
+    <t xml:space="preserve">2.83547782897949</t>
   </si>
   <si>
     <t xml:space="preserve">3.08607649803162</t>
@@ -2408,19 +2408,19 @@
     <t xml:space="preserve">3.31347155570984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35059714317322</t>
+    <t xml:space="preserve">3.3505973815918</t>
   </si>
   <si>
     <t xml:space="preserve">3.27634596824646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28098678588867</t>
+    <t xml:space="preserve">3.28098654747009</t>
   </si>
   <si>
     <t xml:space="preserve">3.34595656394958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07215428352356</t>
+    <t xml:space="preserve">3.07215452194214</t>
   </si>
   <si>
     <t xml:space="preserve">3.07679510116577</t>
@@ -2429,13 +2429,13 @@
     <t xml:space="preserve">3.09999847412109</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16032814979553</t>
+    <t xml:space="preserve">3.16032791137695</t>
   </si>
   <si>
     <t xml:space="preserve">3.09535789489746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05359125137329</t>
+    <t xml:space="preserve">3.05359148979187</t>
   </si>
   <si>
     <t xml:space="preserve">3.03502869606018</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">2.99326205253601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85868144035339</t>
+    <t xml:space="preserve">2.85868120193481</t>
   </si>
   <si>
     <t xml:space="preserve">2.83083701133728</t>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">2.82155561447144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84940004348755</t>
+    <t xml:space="preserve">2.84939980506897</t>
   </si>
   <si>
     <t xml:space="preserve">2.81227421760559</t>
@@ -2465,7 +2465,7 @@
     <t xml:space="preserve">2.88188505172729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7937114238739</t>
+    <t xml:space="preserve">2.79371118545532</t>
   </si>
   <si>
     <t xml:space="preserve">2.76122617721558</t>
@@ -2483,13 +2483,13 @@
     <t xml:space="preserve">2.90972924232483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86332201957703</t>
+    <t xml:space="preserve">2.86332225799561</t>
   </si>
   <si>
     <t xml:space="preserve">2.78907084465027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69161558151245</t>
+    <t xml:space="preserve">2.69161581993103</t>
   </si>
   <si>
     <t xml:space="preserve">2.59416055679321</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">2.16257381439209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13472938537598</t>
+    <t xml:space="preserve">2.13472962379456</t>
   </si>
   <si>
     <t xml:space="preserve">2.24610686302185</t>
@@ -2519,16 +2519,16 @@
     <t xml:space="preserve">2.40389108657837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58951997756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55703496932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60808253288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55239391326904</t>
+    <t xml:space="preserve">2.589519739151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55703473091125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60808277130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55239415168762</t>
   </si>
   <si>
     <t xml:space="preserve">2.57559776306152</t>
@@ -2543,13 +2543,13 @@
     <t xml:space="preserve">2.40853190422058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35748410224915</t>
+    <t xml:space="preserve">2.35748386383057</t>
   </si>
   <si>
     <t xml:space="preserve">2.54311275482178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45029854774475</t>
+    <t xml:space="preserve">2.45029830932617</t>
   </si>
   <si>
     <t xml:space="preserve">2.41781330108643</t>
@@ -2558,7 +2558,7 @@
     <t xml:space="preserve">2.45957970619202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44565749168396</t>
+    <t xml:space="preserve">2.44565773010254</t>
   </si>
   <si>
     <t xml:space="preserve">2.46422052383423</t>
@@ -2570,7 +2570,7 @@
     <t xml:space="preserve">2.4317352771759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49670577049255</t>
+    <t xml:space="preserve">2.49670553207397</t>
   </si>
   <si>
     <t xml:space="preserve">2.47814273834229</t>
@@ -2579,28 +2579,28 @@
     <t xml:space="preserve">2.51990914344788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50134611129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52919030189514</t>
+    <t xml:space="preserve">2.50134634971619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52919054031372</t>
   </si>
   <si>
     <t xml:space="preserve">2.56167554855347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5663161277771</t>
+    <t xml:space="preserve">2.56631636619568</t>
   </si>
   <si>
     <t xml:space="preserve">2.3017954826355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29715442657471</t>
+    <t xml:space="preserve">2.29715466499329</t>
   </si>
   <si>
     <t xml:space="preserve">2.29251408576965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2785918712616</t>
+    <t xml:space="preserve">2.27859163284302</t>
   </si>
   <si>
     <t xml:space="preserve">2.23218464851379</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">2.19969964027405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17185544967651</t>
+    <t xml:space="preserve">2.17185521125793</t>
   </si>
   <si>
     <t xml:space="preserve">2.26931023597717</t>
@@ -2621,13 +2621,13 @@
     <t xml:space="preserve">2.24146604537964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22754383087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19505906105042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12544822692871</t>
+    <t xml:space="preserve">2.22754406929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19505882263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12544798851013</t>
   </si>
   <si>
     <t xml:space="preserve">2.01407098770142</t>
@@ -2642,13 +2642,13 @@
     <t xml:space="preserve">2.0744001865387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97230446338654</t>
+    <t xml:space="preserve">1.97230458259583</t>
   </si>
   <si>
     <t xml:space="preserve">1.96766364574432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.944460272789</t>
+    <t xml:space="preserve">1.94446015357971</t>
   </si>
   <si>
     <t xml:space="preserve">1.87020885944366</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">1.81730461120605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79688549041748</t>
+    <t xml:space="preserve">1.79688537120819</t>
   </si>
   <si>
     <t xml:space="preserve">1.80059802532196</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">1.88413095474243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03263401985168</t>
+    <t xml:space="preserve">2.03263378143311</t>
   </si>
   <si>
     <t xml:space="preserve">2.50598692893982</t>
@@ -2693,10 +2693,10 @@
     <t xml:space="preserve">2.77978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71946001052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70553755760193</t>
+    <t xml:space="preserve">2.71945977210999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70553779602051</t>
   </si>
   <si>
     <t xml:space="preserve">2.7241005897522</t>
@@ -2708,10 +2708,10 @@
     <t xml:space="preserve">2.64056777954102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68233418464661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76586723327637</t>
+    <t xml:space="preserve">2.68233442306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76586699485779</t>
   </si>
   <si>
     <t xml:space="preserve">2.58023834228516</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">2.6127233505249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59880113601685</t>
+    <t xml:space="preserve">2.59880137443542</t>
   </si>
   <si>
     <t xml:space="preserve">2.62664556503296</t>
@@ -2741,10 +2741,10 @@
     <t xml:space="preserve">2.39925050735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27395105361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32963967323303</t>
+    <t xml:space="preserve">2.27395129203796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32963991165161</t>
   </si>
   <si>
     <t xml:space="preserve">2.3482027053833</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">2.35284328460693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39460968971252</t>
+    <t xml:space="preserve">2.39460945129395</t>
   </si>
   <si>
     <t xml:space="preserve">2.46886134147644</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">2.64520835876465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7008969783783</t>
+    <t xml:space="preserve">2.70089721679688</t>
   </si>
   <si>
     <t xml:space="preserve">2.71017861366272</t>
@@ -2786,16 +2786,16 @@
     <t xml:space="preserve">2.93757343292236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9979031085968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09071731567383</t>
+    <t xml:space="preserve">2.99790287017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09071707725525</t>
   </si>
   <si>
     <t xml:space="preserve">3.04895091056824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10463953018188</t>
+    <t xml:space="preserve">3.10463929176331</t>
   </si>
   <si>
     <t xml:space="preserve">3.11392092704773</t>
@@ -2804,19 +2804,19 @@
     <t xml:space="preserve">3.2392201423645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24386072158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21601629257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25314259529114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29026818275452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29954957962036</t>
+    <t xml:space="preserve">3.24386096000671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2160165309906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25314235687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29026794433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29954934120178</t>
   </si>
   <si>
     <t xml:space="preserve">3.31811237335205</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">3.61975908279419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49910044670105</t>
+    <t xml:space="preserve">3.49910020828247</t>
   </si>
   <si>
     <t xml:space="preserve">3.62904047966003</t>
@@ -2846,19 +2846,19 @@
     <t xml:space="preserve">3.41092658042908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34131574630737</t>
+    <t xml:space="preserve">3.34131598472595</t>
   </si>
   <si>
     <t xml:space="preserve">3.3273937702179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44805216789246</t>
+    <t xml:space="preserve">3.44805240631104</t>
   </si>
   <si>
     <t xml:space="preserve">3.38772320747375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41556739807129</t>
+    <t xml:space="preserve">3.41556763648987</t>
   </si>
   <si>
     <t xml:space="preserve">3.29490876197815</t>
@@ -2873,19 +2873,19 @@
     <t xml:space="preserve">3.13248372077942</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17889070510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18353176116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28562712669373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3738009929657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43413019180298</t>
+    <t xml:space="preserve">3.17889094352722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18353152275085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2856273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37380075454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43413043022156</t>
   </si>
   <si>
     <t xml:space="preserve">3.47589659690857</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">3.50838160514832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63368105888367</t>
+    <t xml:space="preserve">3.63368082046509</t>
   </si>
   <si>
     <t xml:space="preserve">3.60583686828613</t>
@@ -2906,28 +2906,28 @@
     <t xml:space="preserve">3.54550743103027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69865107536316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55478858947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53622603416443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4434118270874</t>
+    <t xml:space="preserve">3.69865083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55478882789612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53622579574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44341158866882</t>
   </si>
   <si>
     <t xml:space="preserve">3.52230405807495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54086661338806</t>
+    <t xml:space="preserve">3.54086685180664</t>
   </si>
   <si>
     <t xml:space="preserve">3.46197438240051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47125601768494</t>
+    <t xml:space="preserve">3.47125577926636</t>
   </si>
   <si>
     <t xml:space="preserve">3.50374102592468</t>
@@ -2939,16 +2939,16 @@
     <t xml:space="preserve">3.22993874549866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26706457138062</t>
+    <t xml:space="preserve">3.26706433296204</t>
   </si>
   <si>
     <t xml:space="preserve">3.33203434944153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39236354827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37844157218933</t>
+    <t xml:space="preserve">3.39236378669739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37844181060791</t>
   </si>
   <si>
     <t xml:space="preserve">3.30883097648621</t>
@@ -2969,13 +2969,13 @@
     <t xml:space="preserve">3.05823230743408</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13712453842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11856150627136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96541786193848</t>
+    <t xml:space="preserve">3.13712430000305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11856126785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9654176235199</t>
   </si>
   <si>
     <t xml:space="preserve">3.30419015884399</t>
@@ -2984,7 +2984,7 @@
     <t xml:space="preserve">3.17425012588501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12784290313721</t>
+    <t xml:space="preserve">3.12784266471863</t>
   </si>
   <si>
     <t xml:space="preserve">3.19745373725891</t>
@@ -3005,16 +3005,16 @@
     <t xml:space="preserve">3.36451935768127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45269322395325</t>
+    <t xml:space="preserve">3.45269298553467</t>
   </si>
   <si>
     <t xml:space="preserve">3.42020797729492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42484879493713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32275319099426</t>
+    <t xml:space="preserve">3.42484903335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32275295257568</t>
   </si>
   <si>
     <t xml:space="preserve">3.33667516708374</t>
@@ -3023,13 +3023,13 @@
     <t xml:space="preserve">3.38308238983154</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36916017532349</t>
+    <t xml:space="preserve">3.36916041374207</t>
   </si>
   <si>
     <t xml:space="preserve">3.16496872901917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01646566390991</t>
+    <t xml:space="preserve">3.01646590232849</t>
   </si>
   <si>
     <t xml:space="preserve">3.1696093082428</t>
@@ -3038,7 +3038,7 @@
     <t xml:space="preserve">3.06751370429993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0211067199707</t>
+    <t xml:space="preserve">3.02110648155212</t>
   </si>
   <si>
     <t xml:space="preserve">3.15568733215332</t>
@@ -3047,10 +3047,10 @@
     <t xml:space="preserve">3.14176511764526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.123202085495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03966927528381</t>
+    <t xml:space="preserve">3.12320232391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03966951370239</t>
   </si>
   <si>
     <t xml:space="preserve">3.14640593528748</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">2.58487915992737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77050757408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86796259880066</t>
+    <t xml:space="preserve">2.7705078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86796283721924</t>
   </si>
   <si>
     <t xml:space="preserve">2.94685482978821</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">2.98398065567017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02574706077576</t>
+    <t xml:space="preserve">3.02574729919434</t>
   </si>
   <si>
     <t xml:space="preserve">2.97934007644653</t>
@@ -3086,16 +3086,16 @@
     <t xml:space="preserve">2.80299282073975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84475922584534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9282922744751</t>
+    <t xml:space="preserve">2.84475946426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92829203605652</t>
   </si>
   <si>
     <t xml:space="preserve">2.87260365486145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89116621017456</t>
+    <t xml:space="preserve">2.89116644859314</t>
   </si>
   <si>
     <t xml:space="preserve">3.03038787841797</t>
@@ -3104,16 +3104,16 @@
     <t xml:space="preserve">2.8169150352478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68697500228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69625639915466</t>
+    <t xml:space="preserve">2.68697476387024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69625616073608</t>
   </si>
   <si>
     <t xml:space="preserve">2.62200474739075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79835200309753</t>
+    <t xml:space="preserve">2.79835224151611</t>
   </si>
   <si>
     <t xml:space="preserve">2.91901063919067</t>
@@ -3125,7 +3125,7 @@
     <t xml:space="preserve">2.9050886631012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95613646507263</t>
+    <t xml:space="preserve">2.95613622665405</t>
   </si>
   <si>
     <t xml:space="preserve">2.80763363838196</t>
@@ -3143,31 +3143,31 @@
     <t xml:space="preserve">2.74266338348389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63128638267517</t>
+    <t xml:space="preserve">2.63128614425659</t>
   </si>
   <si>
     <t xml:space="preserve">2.49206471443176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53847169876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54775333404541</t>
+    <t xml:space="preserve">2.53847193717957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54775309562683</t>
   </si>
   <si>
     <t xml:space="preserve">2.48742413520813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44101715087891</t>
+    <t xml:space="preserve">2.44101691246033</t>
   </si>
   <si>
     <t xml:space="preserve">2.47350192070007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43637609481812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38996887207031</t>
+    <t xml:space="preserve">2.43637633323669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38996911048889</t>
   </si>
   <si>
     <t xml:space="preserve">2.3249990940094</t>
@@ -3179,19 +3179,19 @@
     <t xml:space="preserve">2.31107687950134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28323245048523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28787326812744</t>
+    <t xml:space="preserve">2.28323268890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28787302970886</t>
   </si>
   <si>
     <t xml:space="preserve">2.26002883911133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33428072929382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33892107009888</t>
+    <t xml:space="preserve">2.33428049087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33892130851746</t>
   </si>
   <si>
     <t xml:space="preserve">2.30643606185913</t>
@@ -3221,13 +3221,13 @@
     <t xml:space="preserve">2.18113660812378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22290325164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18577766418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11616683006287</t>
+    <t xml:space="preserve">2.22290301322937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18577742576599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11616659164429</t>
   </si>
   <si>
     <t xml:space="preserve">2.0976037979126</t>
@@ -3245,22 +3245,22 @@
     <t xml:space="preserve">2.04191517829895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02335262298584</t>
+    <t xml:space="preserve">2.02335238456726</t>
   </si>
   <si>
     <t xml:space="preserve">2.00014877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98158586025238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97694540023804</t>
+    <t xml:space="preserve">1.98158597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97694528102875</t>
   </si>
   <si>
     <t xml:space="preserve">1.99086737632751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99550807476044</t>
+    <t xml:space="preserve">1.99550831317902</t>
   </si>
   <si>
     <t xml:space="preserve">2.00478959083557</t>
@@ -3275,10 +3275,10 @@
     <t xml:space="preserve">2.05119657516479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00943040847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02799296379089</t>
+    <t xml:space="preserve">2.0094301700592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02799320220947</t>
   </si>
   <si>
     <t xml:space="preserve">1.95838224887848</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">1.93981945514679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91197526454926</t>
+    <t xml:space="preserve">1.91197514533997</t>
   </si>
   <si>
     <t xml:space="preserve">1.90269374847412</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">1.75419080257416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73562800884247</t>
+    <t xml:space="preserve">1.73562788963318</t>
   </si>
   <si>
     <t xml:space="preserve">1.82472968101501</t>
@@ -3317,16 +3317,16 @@
     <t xml:space="preserve">1.80431056022644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77646625041962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.793172955513</t>
+    <t xml:space="preserve">1.77646636962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79317283630371</t>
   </si>
   <si>
     <t xml:space="preserve">1.7950291633606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76904118061066</t>
+    <t xml:space="preserve">1.76904106140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75047838687897</t>
@@ -3356,7 +3356,7 @@
     <t xml:space="preserve">1.81916093826294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287335395813</t>
+    <t xml:space="preserve">1.82287347316742</t>
   </si>
   <si>
     <t xml:space="preserve">2.01871156692505</t>
@@ -3371,22 +3371,22 @@
     <t xml:space="preserve">2.37604665756226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38532829284668</t>
+    <t xml:space="preserve">2.3853280544281</t>
   </si>
   <si>
     <t xml:space="preserve">2.3714063167572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60344219207764</t>
+    <t xml:space="preserve">2.60344195365906</t>
   </si>
   <si>
     <t xml:space="preserve">3.56407022476196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64296245574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57799243927002</t>
+    <t xml:space="preserve">3.64296221733093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5779926776886</t>
   </si>
   <si>
     <t xml:space="preserve">3.55942964553833</t>
@@ -3395,19 +3395,19 @@
     <t xml:space="preserve">3.82859110832214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90748333930969</t>
+    <t xml:space="preserve">3.90748310089111</t>
   </si>
   <si>
     <t xml:space="preserve">4.00029754638672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81466913223267</t>
+    <t xml:space="preserve">3.81466889381409</t>
   </si>
   <si>
     <t xml:space="preserve">3.48517823219299</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42948961257935</t>
+    <t xml:space="preserve">3.42948937416077</t>
   </si>
   <si>
     <t xml:space="preserve">3.45733380317688</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">3.35987877845764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58727383613586</t>
+    <t xml:space="preserve">3.58727407455444</t>
   </si>
   <si>
     <t xml:space="preserve">3.52694439888</t>
@@ -4188,6 +4188,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.76000022888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78999996185303</t>
   </si>
 </sst>
 </file>
@@ -69734,7 +69737,7 @@
     </row>
     <row r="2509">
       <c r="A2509" s="1" t="n">
-        <v>45972.6911921296</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2509" t="n">
         <v>163939</v>
@@ -69755,6 +69758,32 @@
         <v>1387</v>
       </c>
       <c r="H2509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>45973.6911805556</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>56558</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>7.96000003814697</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>7.76000022888184</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>7.96000003814697</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>7.78999996185303</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H2510" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95473074913025</t>
+    <t xml:space="preserve">1.95473086833954</t>
   </si>
   <si>
     <t xml:space="preserve">FM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95993411540985</t>
+    <t xml:space="preserve">1.95993423461914</t>
   </si>
   <si>
     <t xml:space="preserve">1.9096348285675</t>
@@ -65,13 +65,13 @@
     <t xml:space="preserve">1.74486172199249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69542992115021</t>
+    <t xml:space="preserve">1.69542980194092</t>
   </si>
   <si>
     <t xml:space="preserve">1.61824655532837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52285158634186</t>
+    <t xml:space="preserve">1.52285146713257</t>
   </si>
   <si>
     <t xml:space="preserve">1.47949004173279</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">1.34420263767242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45434057712555</t>
+    <t xml:space="preserve">1.45434045791626</t>
   </si>
   <si>
     <t xml:space="preserve">1.55233728885651</t>
@@ -89,61 +89,61 @@
     <t xml:space="preserve">1.48989689350128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54366493225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59569847583771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51331198215485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53325819969177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.499436378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43005812168121</t>
+    <t xml:space="preserve">1.54366505146027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.595698595047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51331210136414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53325831890106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49943625926971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4300582408905</t>
   </si>
   <si>
     <t xml:space="preserve">1.40751028060913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38582956790924</t>
+    <t xml:space="preserve">1.38582968711853</t>
   </si>
   <si>
     <t xml:space="preserve">1.28349673748016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17682778835297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24186980724335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2071807384491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23059594631195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43873059749603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39710342884064</t>
+    <t xml:space="preserve">1.17682766914368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24186968803406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20718061923981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23059582710266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43873047828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39710354804993</t>
   </si>
   <si>
     <t xml:space="preserve">1.50030362606049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48295915126801</t>
+    <t xml:space="preserve">1.48295903205872</t>
   </si>
   <si>
     <t xml:space="preserve">1.46561455726624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5211169719696</t>
+    <t xml:space="preserve">1.52111709117889</t>
   </si>
   <si>
     <t xml:space="preserve">1.51678085327148</t>
@@ -161,34 +161,34 @@
     <t xml:space="preserve">1.5098432302475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56014227867126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58702635765076</t>
+    <t xml:space="preserve">1.56014239788055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58702623844147</t>
   </si>
   <si>
     <t xml:space="preserve">1.55754053592682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52805495262146</t>
+    <t xml:space="preserve">1.52805483341217</t>
   </si>
   <si>
     <t xml:space="preserve">1.54279780387878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51244461536407</t>
+    <t xml:space="preserve">1.51244473457336</t>
   </si>
   <si>
     <t xml:space="preserve">1.55147004127502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61651206016541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67374908924103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70843815803528</t>
+    <t xml:space="preserve">1.61651194095612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67374897003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70843827724457</t>
   </si>
   <si>
     <t xml:space="preserve">1.67808520793915</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">1.6061053276062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53499269485474</t>
+    <t xml:space="preserve">1.53499281406403</t>
   </si>
   <si>
     <t xml:space="preserve">1.49770188331604</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">1.39970517158508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35200762748718</t>
+    <t xml:space="preserve">1.35200774669647</t>
   </si>
   <si>
     <t xml:space="preserve">1.39190018177032</t>
@@ -230,61 +230,61 @@
     <t xml:space="preserve">1.46041107177734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57228350639343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62952053546906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60437095165253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60870707035065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62518441677094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65987348556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58615899085999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55407178401947</t>
+    <t xml:space="preserve">1.57228338718414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62952041625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60437083244324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60870695114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62518429756165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65987360477448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58615911006927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55407166481018</t>
   </si>
   <si>
     <t xml:space="preserve">1.60090184211731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58876085281372</t>
+    <t xml:space="preserve">1.58876073360443</t>
   </si>
   <si>
     <t xml:space="preserve">1.49249851703644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45780944824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47775566577911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47428691387177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46908342838287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56794726848602</t>
+    <t xml:space="preserve">1.4578093290329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47775554656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47428667545319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46908330917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56794738769531</t>
   </si>
   <si>
     <t xml:space="preserve">1.53932881355286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53065657615662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54106318950653</t>
+    <t xml:space="preserve">1.53065645694733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54106330871582</t>
   </si>
   <si>
     <t xml:space="preserve">1.56968176364899</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">1.5471339225769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55060267448425</t>
+    <t xml:space="preserve">1.55060279369354</t>
   </si>
   <si>
     <t xml:space="preserve">1.56708014011383</t>
@@ -302,31 +302,31 @@
     <t xml:space="preserve">1.57401788234711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51071012020111</t>
+    <t xml:space="preserve">1.5107102394104</t>
   </si>
   <si>
     <t xml:space="preserve">1.59136247634888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56100940704346</t>
+    <t xml:space="preserve">1.56100952625275</t>
   </si>
   <si>
     <t xml:space="preserve">1.54453229904175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45000433921814</t>
+    <t xml:space="preserve">1.45000445842743</t>
   </si>
   <si>
     <t xml:space="preserve">1.38929855823517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40057241916656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38756394386292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44740271568298</t>
+    <t xml:space="preserve">1.40057253837585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3875640630722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44740283489227</t>
   </si>
   <si>
     <t xml:space="preserve">1.49163126945496</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">1.4838262796402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32338929176331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32945966720581</t>
+    <t xml:space="preserve">1.32338917255402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3294597864151</t>
   </si>
   <si>
     <t xml:space="preserve">1.3884311914444</t>
@@ -350,25 +350,25 @@
     <t xml:space="preserve">1.35981273651123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33726501464844</t>
+    <t xml:space="preserve">1.33726489543915</t>
   </si>
   <si>
     <t xml:space="preserve">1.31124806404114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30084121227264</t>
+    <t xml:space="preserve">1.30084133148193</t>
   </si>
   <si>
     <t xml:space="preserve">1.30257570743561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3615471124649</t>
+    <t xml:space="preserve">1.36154723167419</t>
   </si>
   <si>
     <t xml:space="preserve">1.37802445888519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38236057758331</t>
+    <t xml:space="preserve">1.3823606967926</t>
   </si>
   <si>
     <t xml:space="preserve">1.39623630046844</t>
@@ -377,10 +377,10 @@
     <t xml:space="preserve">1.37715744972229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4049084186554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39450180530548</t>
+    <t xml:space="preserve">1.40490853786469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39450192451477</t>
   </si>
   <si>
     <t xml:space="preserve">1.4040412902832</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">1.38062620162964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36588335037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35634386539459</t>
+    <t xml:space="preserve">1.3658834695816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3563437461853</t>
   </si>
   <si>
     <t xml:space="preserve">1.35460937023163</t>
@@ -413,28 +413,28 @@
     <t xml:space="preserve">1.34333539009094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33119416236877</t>
+    <t xml:space="preserve">1.33119428157806</t>
   </si>
   <si>
     <t xml:space="preserve">1.32685804367065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30170857906342</t>
+    <t xml:space="preserve">1.30170845985413</t>
   </si>
   <si>
     <t xml:space="preserve">1.30777907371521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34767150878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34506976604462</t>
+    <t xml:space="preserve">1.34767162799835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34506988525391</t>
   </si>
   <si>
     <t xml:space="preserve">1.33379590511322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37108659744263</t>
+    <t xml:space="preserve">1.37108671665192</t>
   </si>
   <si>
     <t xml:space="preserve">1.35547661781311</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">1.34853875637054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41704976558685</t>
+    <t xml:space="preserve">1.41704964637756</t>
   </si>
   <si>
     <t xml:space="preserve">1.40317416191101</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">1.41097903251648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36501598358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38322782516479</t>
+    <t xml:space="preserve">1.36501610279083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38322794437408</t>
   </si>
   <si>
     <t xml:space="preserve">1.36761784553528</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">1.38149344921112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39797079563141</t>
+    <t xml:space="preserve">1.39797067642212</t>
   </si>
   <si>
     <t xml:space="preserve">1.37455558776855</t>
@@ -482,22 +482,22 @@
     <t xml:space="preserve">1.41358077526093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42138600349426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41271364688873</t>
+    <t xml:space="preserve">1.42138576507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41271340847015</t>
   </si>
   <si>
     <t xml:space="preserve">1.40924465656281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42572200298309</t>
+    <t xml:space="preserve">1.42572212219238</t>
   </si>
   <si>
     <t xml:space="preserve">1.35114049911499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35894560813904</t>
+    <t xml:space="preserve">1.35894548892975</t>
   </si>
   <si>
     <t xml:space="preserve">1.34680426120758</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">1.36414885520935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36241436004639</t>
+    <t xml:space="preserve">1.36241447925568</t>
   </si>
   <si>
     <t xml:space="preserve">1.33032703399658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32078742980957</t>
+    <t xml:space="preserve">1.32078754901886</t>
   </si>
   <si>
     <t xml:space="preserve">1.3190530538559</t>
@@ -521,22 +521,22 @@
     <t xml:space="preserve">1.31992018222809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3129825592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17942929267883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26181614398956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29216909408569</t>
+    <t xml:space="preserve">1.31298243999481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17942941188812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26181590557098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2921689748764</t>
   </si>
   <si>
     <t xml:space="preserve">1.23146307468414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2175874710083</t>
+    <t xml:space="preserve">1.21758759021759</t>
   </si>
   <si>
     <t xml:space="preserve">1.24880766868591</t>
@@ -545,10 +545,10 @@
     <t xml:space="preserve">1.22886145114899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18550002574921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15774881839752</t>
+    <t xml:space="preserve">1.18549990653992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15774869918823</t>
   </si>
   <si>
     <t xml:space="preserve">1.11872339248657</t>
@@ -557,10 +557,10 @@
     <t xml:space="preserve">1.13086462020874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12305963039398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13346636295319</t>
+    <t xml:space="preserve">1.12305951118469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13346648216248</t>
   </si>
   <si>
     <t xml:space="preserve">1.11438727378845</t>
@@ -569,22 +569,22 @@
     <t xml:space="preserve">1.11612176895142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11525464057922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09791016578674</t>
+    <t xml:space="preserve">1.11525452136993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09790992736816</t>
   </si>
   <si>
     <t xml:space="preserve">1.09270668029785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07536220550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07276046276093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10398042201996</t>
+    <t xml:space="preserve">1.07536208629608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07276034355164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10398054122925</t>
   </si>
   <si>
     <t xml:space="preserve">1.1542797088623</t>
@@ -593,31 +593,31 @@
     <t xml:space="preserve">1.16295206546783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16208493709564</t>
+    <t xml:space="preserve">1.16208481788635</t>
   </si>
   <si>
     <t xml:space="preserve">1.17856216430664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18289840221405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20544612407684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23493194580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24533867835999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21845471858978</t>
+    <t xml:space="preserve">1.18289828300476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20544624328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23493206501007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2453385591507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21845459938049</t>
   </si>
   <si>
     <t xml:space="preserve">1.19937562942505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20111000537872</t>
+    <t xml:space="preserve">1.20111012458801</t>
   </si>
   <si>
     <t xml:space="preserve">1.2279942035675</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">1.22192358970642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23666632175446</t>
+    <t xml:space="preserve">1.23666644096375</t>
   </si>
   <si>
     <t xml:space="preserve">1.26875388622284</t>
@@ -635,22 +635,22 @@
     <t xml:space="preserve">1.38409507274628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39883816242218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38669669628143</t>
+    <t xml:space="preserve">1.39883804321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38669681549072</t>
   </si>
   <si>
     <t xml:space="preserve">1.35721111297607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34593713283539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33292865753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28870010375977</t>
+    <t xml:space="preserve">1.34593725204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33292853832245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28869998455048</t>
   </si>
   <si>
     <t xml:space="preserve">1.25747990608215</t>
@@ -665,13 +665,13 @@
     <t xml:space="preserve">1.22712695598602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25661265850067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2236579656601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2227908372879</t>
+    <t xml:space="preserve">1.25661253929138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22365808486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22279071807861</t>
   </si>
   <si>
     <t xml:space="preserve">1.25314378738403</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">1.21325135231018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20891523361206</t>
+    <t xml:space="preserve">1.20891511440277</t>
   </si>
   <si>
     <t xml:space="preserve">1.20457911491394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21585285663605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21672022342682</t>
+    <t xml:space="preserve">1.21585297584534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21672010421753</t>
   </si>
   <si>
     <t xml:space="preserve">1.19070339202881</t>
@@ -707,13 +707,13 @@
     <t xml:space="preserve">1.191570520401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20284461975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19243776798248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23406457901001</t>
+    <t xml:space="preserve">1.20284450054169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19243788719177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2340646982193</t>
   </si>
   <si>
     <t xml:space="preserve">1.27742612361908</t>
@@ -725,10 +725,10 @@
     <t xml:space="preserve">1.2982394695282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26355051994324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24273705482483</t>
+    <t xml:space="preserve">1.26355040073395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24273693561554</t>
   </si>
   <si>
     <t xml:space="preserve">1.23579919338226</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">1.22018897533417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24794042110443</t>
+    <t xml:space="preserve">1.24794030189514</t>
   </si>
   <si>
     <t xml:space="preserve">1.24967479705811</t>
@@ -746,16 +746,16 @@
     <t xml:space="preserve">1.29043447971344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29303634166718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31818580627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30691194534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27309012413025</t>
+    <t xml:space="preserve">1.29303622245789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31818568706512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30691182613373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27309000492096</t>
   </si>
   <si>
     <t xml:space="preserve">1.24013531208038</t>
@@ -764,10 +764,10 @@
     <t xml:space="preserve">1.27916049957275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2704883813858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26528489589691</t>
+    <t xml:space="preserve">1.27048826217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26528477668762</t>
   </si>
   <si>
     <t xml:space="preserve">1.28436386585236</t>
@@ -779,19 +779,19 @@
     <t xml:space="preserve">1.26441764831543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28523111343384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2869656085968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33986639976501</t>
+    <t xml:space="preserve">1.28523099422455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28696548938751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3398665189743</t>
   </si>
   <si>
     <t xml:space="preserve">1.33899927139282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41184639930725</t>
+    <t xml:space="preserve">1.41184628009796</t>
   </si>
   <si>
     <t xml:space="preserve">1.57835412025452</t>
@@ -803,13 +803,13 @@
     <t xml:space="preserve">1.54019606113434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49856913089752</t>
+    <t xml:space="preserve">1.49856925010681</t>
   </si>
   <si>
     <t xml:space="preserve">1.50724148750305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50203800201416</t>
+    <t xml:space="preserve">1.50203812122345</t>
   </si>
   <si>
     <t xml:space="preserve">1.47862303256989</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">1.40577578544617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38496220111847</t>
+    <t xml:space="preserve">1.38496243953705</t>
   </si>
   <si>
     <t xml:space="preserve">1.47168505191803</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">1.45867669582367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45954394340515</t>
+    <t xml:space="preserve">1.45954382419586</t>
   </si>
   <si>
     <t xml:space="preserve">1.45607495307922</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">1.57488512992859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58269023895264</t>
+    <t xml:space="preserve">1.58269011974335</t>
   </si>
   <si>
     <t xml:space="preserve">1.56187677383423</t>
@@ -878,46 +878,46 @@
     <t xml:space="preserve">1.49510014057159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51157748699188</t>
+    <t xml:space="preserve">1.51157760620117</t>
   </si>
   <si>
     <t xml:space="preserve">1.48902952671051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48035728931427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48816251754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51591360569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56881463527679</t>
+    <t xml:space="preserve">1.48035740852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48816239833832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51591372489929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5688145160675</t>
   </si>
   <si>
     <t xml:space="preserve">1.57054901123047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64686512947083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78648865222931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7604718208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85933589935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86627352237701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84199130535126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15245890617371</t>
+    <t xml:space="preserve">1.64686501026154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78648841381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76047170162201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85933578014374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86627340316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84199142456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15245866775513</t>
   </si>
   <si>
     <t xml:space="preserve">1.99982666969299</t>
@@ -926,43 +926,43 @@
     <t xml:space="preserve">2.05879807472229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00329566001892</t>
+    <t xml:space="preserve">2.00329542160034</t>
   </si>
   <si>
     <t xml:space="preserve">1.95126187801361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05186033248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01543641090393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98074769973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90443181991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90790045261383</t>
+    <t xml:space="preserve">2.05186009407043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01543664932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98074734210968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90443170070648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90790033340454</t>
   </si>
   <si>
     <t xml:space="preserve">1.91657280921936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90616583824158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84892904758453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87321138381958</t>
+    <t xml:space="preserve">1.90616595745087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84892892837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87321150302887</t>
   </si>
   <si>
     <t xml:space="preserve">1.83158445358276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84719467163086</t>
+    <t xml:space="preserve">1.84719479084015</t>
   </si>
   <si>
     <t xml:space="preserve">1.93218290805817</t>
@@ -974,22 +974,22 @@
     <t xml:space="preserve">1.9252450466156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94258987903595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97727859020233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0206401348114</t>
+    <t xml:space="preserve">1.94258952140808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97727870941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02063989639282</t>
   </si>
   <si>
     <t xml:space="preserve">2.06920480728149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01196789741516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03971886634827</t>
+    <t xml:space="preserve">2.01196765899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03971910476685</t>
   </si>
   <si>
     <t xml:space="preserve">2.01370239257812</t>
@@ -998,37 +998,37 @@
     <t xml:space="preserve">1.99462330341339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94432425498962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90269720554352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82117760181427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91310381889343</t>
+    <t xml:space="preserve">1.94432413578033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90269696712494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82117772102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91310393810272</t>
   </si>
   <si>
     <t xml:space="preserve">1.72144663333893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67114734649658</t>
+    <t xml:space="preserve">1.67114758491516</t>
   </si>
   <si>
     <t xml:space="preserve">1.69976603984833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68762457370758</t>
+    <t xml:space="preserve">1.68762469291687</t>
   </si>
   <si>
     <t xml:space="preserve">1.67895245552063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63992714881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64773213863373</t>
+    <t xml:space="preserve">1.63992726802826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64773225784302</t>
   </si>
   <si>
     <t xml:space="preserve">1.62865328788757</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">1.62691879272461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60350358486176</t>
+    <t xml:space="preserve">1.60350370407104</t>
   </si>
   <si>
     <t xml:space="preserve">1.59656572341919</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">1.6485995054245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66507685184479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6910936832428</t>
+    <t xml:space="preserve">1.6650767326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69109380245209</t>
   </si>
   <si>
     <t xml:space="preserve">1.72925162315369</t>
@@ -1064,13 +1064,13 @@
     <t xml:space="preserve">1.65640449523926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63038778305054</t>
+    <t xml:space="preserve">1.63038766384125</t>
   </si>
   <si>
     <t xml:space="preserve">1.66681122779846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68155407905579</t>
+    <t xml:space="preserve">1.68155419826508</t>
   </si>
   <si>
     <t xml:space="preserve">1.68935918807983</t>
@@ -1079,10 +1079,10 @@
     <t xml:space="preserve">1.67721807956696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63385665416718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62171530723572</t>
+    <t xml:space="preserve">1.6338564157486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62171542644501</t>
   </si>
   <si>
     <t xml:space="preserve">1.65727174282074</t>
@@ -1097,19 +1097,19 @@
     <t xml:space="preserve">1.71711051464081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70670366287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72578275203705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72751700878143</t>
+    <t xml:space="preserve">1.7067037820816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72578287124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72751712799072</t>
   </si>
   <si>
     <t xml:space="preserve">1.71190702915192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74312734603882</t>
+    <t xml:space="preserve">1.74312722682953</t>
   </si>
   <si>
     <t xml:space="preserve">1.77781629562378</t>
@@ -1121,22 +1121,22 @@
     <t xml:space="preserve">1.80383312702179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93391740322113</t>
+    <t xml:space="preserve">1.93391728401184</t>
   </si>
   <si>
     <t xml:space="preserve">1.88188374042511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95559811592102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88621973991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81684160232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89489197731018</t>
+    <t xml:space="preserve">1.95559799671173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88621962070465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81684172153473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89489209651947</t>
   </si>
   <si>
     <t xml:space="preserve">1.80816924571991</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">1.82984983921051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85153067111969</t>
+    <t xml:space="preserve">1.85153079032898</t>
   </si>
   <si>
     <t xml:space="preserve">1.78215253353119</t>
@@ -1157,22 +1157,22 @@
     <t xml:space="preserve">1.79082489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73445498943329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.764808177948</t>
+    <t xml:space="preserve">1.73445510864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76480805873871</t>
   </si>
   <si>
     <t xml:space="preserve">1.96860635280609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89922845363617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89055609703064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8775475025177</t>
+    <t xml:space="preserve">1.89922821521759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89055597782135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87754738330841</t>
   </si>
   <si>
     <t xml:space="preserve">1.83418619632721</t>
@@ -1184,7 +1184,7 @@
     <t xml:space="preserve">1.82551395893097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83852207660675</t>
+    <t xml:space="preserve">1.83852231502533</t>
   </si>
   <si>
     <t xml:space="preserve">1.86020290851593</t>
@@ -1193,13 +1193,13 @@
     <t xml:space="preserve">1.9729425907135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98161482810974</t>
+    <t xml:space="preserve">1.98161494731903</t>
   </si>
   <si>
     <t xml:space="preserve">1.92958116531372</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98595082759857</t>
+    <t xml:space="preserve">1.98595094680786</t>
   </si>
   <si>
     <t xml:space="preserve">2.04665684700012</t>
@@ -1217,31 +1217,31 @@
     <t xml:space="preserve">2.08134603500366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11169862747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15072441101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05532932281494</t>
+    <t xml:space="preserve">2.1116988658905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15072417259216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05532908439636</t>
   </si>
   <si>
     <t xml:space="preserve">2.1854133605957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33717823028564</t>
+    <t xml:space="preserve">2.33717799186707</t>
   </si>
   <si>
     <t xml:space="preserve">2.3024890422821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2808084487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21143007278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30682516098022</t>
+    <t xml:space="preserve">2.28080821037292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21142983436584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3068253993988</t>
   </si>
   <si>
     <t xml:space="preserve">2.28514456748962</t>
@@ -1253,25 +1253,25 @@
     <t xml:space="preserve">2.48894286155701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59301018714905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38921213150024</t>
+    <t xml:space="preserve">2.59300994873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38921189308167</t>
   </si>
   <si>
     <t xml:space="preserve">2.49761533737183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57566595077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62769961357117</t>
+    <t xml:space="preserve">2.57566571235657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62769937515259</t>
   </si>
   <si>
     <t xml:space="preserve">2.71442222595215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76645565032959</t>
+    <t xml:space="preserve">2.76645588874817</t>
   </si>
   <si>
     <t xml:space="preserve">2.83583378791809</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">2.93122911453247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87052297592163</t>
+    <t xml:space="preserve">2.87052273750305</t>
   </si>
   <si>
     <t xml:space="preserve">2.92689275741577</t>
@@ -1298,25 +1298,25 @@
     <t xml:space="preserve">3.23909473419189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25210285186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21741414070129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25643920898438</t>
+    <t xml:space="preserve">3.25210309028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21741390228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25643944740295</t>
   </si>
   <si>
     <t xml:space="preserve">3.36050653457642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20874190330505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36917877197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26511168479919</t>
+    <t xml:space="preserve">3.20874166488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36917901039124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26511144638062</t>
   </si>
   <si>
     <t xml:space="preserve">3.22175002098083</t>
@@ -1328,13 +1328,13 @@
     <t xml:space="preserve">3.27811980247498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34749817848206</t>
+    <t xml:space="preserve">3.34749794006348</t>
   </si>
   <si>
     <t xml:space="preserve">3.50793528556824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48625469207764</t>
+    <t xml:space="preserve">3.48625445365906</t>
   </si>
   <si>
     <t xml:space="preserve">3.55563259124756</t>
@@ -1349,16 +1349,16 @@
     <t xml:space="preserve">3.6640362739563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73341417312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80712842941284</t>
+    <t xml:space="preserve">3.7334144115448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80712866783142</t>
   </si>
   <si>
     <t xml:space="preserve">3.90686011314392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07596874237061</t>
+    <t xml:space="preserve">4.07596921920776</t>
   </si>
   <si>
     <t xml:space="preserve">4.0456166267395</t>
@@ -1367,22 +1367,22 @@
     <t xml:space="preserve">4.09764957427979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86783480644226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0412802696228</t>
+    <t xml:space="preserve">3.86783456802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04127979278564</t>
   </si>
   <si>
     <t xml:space="preserve">3.945885181427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97190165519714</t>
+    <t xml:space="preserve">3.97190189361572</t>
   </si>
   <si>
     <t xml:space="preserve">3.71173405647278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9198682308197</t>
+    <t xml:space="preserve">3.91986846923828</t>
   </si>
   <si>
     <t xml:space="preserve">4.07163333892822</t>
@@ -1391,13 +1391,13 @@
     <t xml:space="preserve">4.24941492080688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25375127792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28410387039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62232303619385</t>
+    <t xml:space="preserve">4.25375080108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.284104347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62232208251953</t>
   </si>
   <si>
     <t xml:space="preserve">4.57896137237549</t>
@@ -1412,19 +1412,19 @@
     <t xml:space="preserve">5.05593585968018</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98655796051025</t>
+    <t xml:space="preserve">4.9865574836731</t>
   </si>
   <si>
     <t xml:space="preserve">4.95186901092529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87381887435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31879329681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80444002151489</t>
+    <t xml:space="preserve">4.87381839752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31879281997681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80444049835205</t>
   </si>
   <si>
     <t xml:space="preserve">4.97788572311401</t>
@@ -1439,19 +1439,19 @@
     <t xml:space="preserve">4.91718006134033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82178449630737</t>
+    <t xml:space="preserve">4.82178497314453</t>
   </si>
   <si>
     <t xml:space="preserve">4.85647392272949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89116334915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83045721054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76107883453369</t>
+    <t xml:space="preserve">4.89116287231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83045768737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76107835769653</t>
   </si>
   <si>
     <t xml:space="preserve">4.54427194595337</t>
@@ -1463,49 +1463,49 @@
     <t xml:space="preserve">4.60497808456421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58763360977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64833974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61365032196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53560018539429</t>
+    <t xml:space="preserve">4.58763313293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64833927154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61365079879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53559970855713</t>
   </si>
   <si>
     <t xml:space="preserve">4.47489356994629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40551614761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18437242507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18870878219604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24074268341064</t>
+    <t xml:space="preserve">4.40551567077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1843729019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1887092590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2407431602478</t>
   </si>
   <si>
     <t xml:space="preserve">4.084641456604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92854118347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91553211212158</t>
+    <t xml:space="preserve">3.92854046821594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91553258895874</t>
   </si>
   <si>
     <t xml:space="preserve">3.85916233062744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78111219406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14101123809814</t>
+    <t xml:space="preserve">3.7811119556427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14101076126099</t>
   </si>
   <si>
     <t xml:space="preserve">3.62501072883606</t>
@@ -1514,22 +1514,22 @@
     <t xml:space="preserve">3.31280899047852</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28679203987122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14369988441467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00927972793579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09166598320007</t>
+    <t xml:space="preserve">3.28679227828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14369964599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00927948951721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09166622161865</t>
   </si>
   <si>
     <t xml:space="preserve">3.03529620170593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04830455780029</t>
+    <t xml:space="preserve">3.04830479621887</t>
   </si>
   <si>
     <t xml:space="preserve">3.07865762710571</t>
@@ -1538,13 +1538,13 @@
     <t xml:space="preserve">2.96158170700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89653992652893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90521216392517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02662396430969</t>
+    <t xml:space="preserve">2.89653968811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90521192550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02662420272827</t>
   </si>
   <si>
     <t xml:space="preserve">2.75344729423523</t>
@@ -1553,43 +1553,43 @@
     <t xml:space="preserve">2.80548071861267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88786768913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04396843910217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26077556610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24343061447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19139695167542</t>
+    <t xml:space="preserve">2.88786745071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04396867752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2607753276825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24343085289001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19139719009399</t>
   </si>
   <si>
     <t xml:space="preserve">3.42554879188538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43855667114258</t>
+    <t xml:space="preserve">3.43855714797974</t>
   </si>
   <si>
     <t xml:space="preserve">3.39519572257996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20440578460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06998538970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86618709564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93990111351013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88353157043457</t>
+    <t xml:space="preserve">3.20440554618835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06998562812805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86618685722351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93990135192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88353133201599</t>
   </si>
   <si>
     <t xml:space="preserve">2.97459053993225</t>
@@ -1598,22 +1598,22 @@
     <t xml:space="preserve">3.02228784561157</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3821873664856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32148146629333</t>
+    <t xml:space="preserve">3.38218760490417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32148122787476</t>
   </si>
   <si>
     <t xml:space="preserve">3.15670824050903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11768293380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08732986450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06564903259277</t>
+    <t xml:space="preserve">3.11768269538879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08733010292053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06564927101135</t>
   </si>
   <si>
     <t xml:space="preserve">2.81848931312561</t>
@@ -1622,19 +1622,19 @@
     <t xml:space="preserve">2.68840527534485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73176670074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63203549385071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98759865760803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17405271530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3041365146637</t>
+    <t xml:space="preserve">2.73176693916321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63203573226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98759889602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17405247688293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30413675308228</t>
   </si>
   <si>
     <t xml:space="preserve">3.3084728717804</t>
@@ -1646,10 +1646,10 @@
     <t xml:space="preserve">3.10467457771301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16104435920715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33015370368958</t>
+    <t xml:space="preserve">3.16104412078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.330153465271</t>
   </si>
   <si>
     <t xml:space="preserve">3.46023774147034</t>
@@ -1658,46 +1658,46 @@
     <t xml:space="preserve">3.5903217792511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8851797580719</t>
+    <t xml:space="preserve">3.88517904281616</t>
   </si>
   <si>
     <t xml:space="preserve">3.90252375602722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85482621192932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11499500274658</t>
+    <t xml:space="preserve">3.8548264503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11499452590942</t>
   </si>
   <si>
     <t xml:space="preserve">4.27543163299561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10198593139648</t>
+    <t xml:space="preserve">4.10198640823364</t>
   </si>
   <si>
     <t xml:space="preserve">4.145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13233947753906</t>
+    <t xml:space="preserve">4.1323390007019</t>
   </si>
   <si>
     <t xml:space="preserve">3.95889353752136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82447338104248</t>
+    <t xml:space="preserve">3.8244731426239</t>
   </si>
   <si>
     <t xml:space="preserve">3.9675657749176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94154906272888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9979190826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00659132003784</t>
+    <t xml:space="preserve">3.9415488243103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99791860580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00659084320068</t>
   </si>
   <si>
     <t xml:space="preserve">4.06296062469482</t>
@@ -1706,7 +1706,7 @@
     <t xml:space="preserve">4.05862474441528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01526355743408</t>
+    <t xml:space="preserve">4.01526403427124</t>
   </si>
   <si>
     <t xml:space="preserve">4.09331369400024</t>
@@ -1718,22 +1718,22 @@
     <t xml:space="preserve">3.98924660682678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9242045879364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8288094997406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75943112373352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74642276763916</t>
+    <t xml:space="preserve">3.92420482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82880926132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75943160057068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74642300605774</t>
   </si>
   <si>
     <t xml:space="preserve">3.56864094734192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77677583694458</t>
+    <t xml:space="preserve">3.77677607536316</t>
   </si>
   <si>
     <t xml:space="preserve">4.24507904052734</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">4.17136430740356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08897733688354</t>
+    <t xml:space="preserve">4.0889778137207</t>
   </si>
   <si>
     <t xml:space="preserve">4.06729698181152</t>
@@ -1751,7 +1751,7 @@
     <t xml:space="preserve">4.16269207000732</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21906185150146</t>
+    <t xml:space="preserve">4.21906137466431</t>
   </si>
   <si>
     <t xml:space="preserve">4.2320704460144</t>
@@ -1760,31 +1760,31 @@
     <t xml:space="preserve">4.20171689987183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68302822113037</t>
+    <t xml:space="preserve">4.68302869796753</t>
   </si>
   <si>
     <t xml:space="preserve">4.88249111175537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76975107192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72638940811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63966703414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55294418334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44887733459473</t>
+    <t xml:space="preserve">4.76975154876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72638988494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63966751098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55294466018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44887685775757</t>
   </si>
   <si>
     <t xml:space="preserve">4.39684343338013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91119623184204</t>
+    <t xml:space="preserve">3.91119599342346</t>
   </si>
   <si>
     <t xml:space="preserve">4.04995250701904</t>
@@ -1796,31 +1796,31 @@
     <t xml:space="preserve">4.12285375595093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01130485534668</t>
+    <t xml:space="preserve">4.01130437850952</t>
   </si>
   <si>
     <t xml:space="preserve">3.91760301589966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2254786491394</t>
+    <t xml:space="preserve">4.22547912597656</t>
   </si>
   <si>
     <t xml:space="preserve">4.00684213638306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8328263759613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85513591766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85959768295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93098950386047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83728790283203</t>
+    <t xml:space="preserve">3.83282613754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85513615608215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85959792137146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93098926544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83728814125061</t>
   </si>
   <si>
     <t xml:space="preserve">4.01576662063599</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">4.03807640075684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95776104927063</t>
+    <t xml:space="preserve">3.95776081085205</t>
   </si>
   <si>
     <t xml:space="preserve">3.79266834259033</t>
@@ -1838,22 +1838,22 @@
     <t xml:space="preserve">3.74358701705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76143503189087</t>
+    <t xml:space="preserve">3.76143455505371</t>
   </si>
   <si>
     <t xml:space="preserve">3.61419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68111944198608</t>
+    <t xml:space="preserve">3.6811192035675</t>
   </si>
   <si>
     <t xml:space="preserve">3.52048873901367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48479270935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67219519615173</t>
+    <t xml:space="preserve">3.48479294776917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67219543457031</t>
   </si>
   <si>
     <t xml:space="preserve">3.59634208679199</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">3.64096164703369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64988565444946</t>
+    <t xml:space="preserve">3.64988589286804</t>
   </si>
   <si>
     <t xml:space="preserve">3.5115647315979</t>
@@ -1886,10 +1886,10 @@
     <t xml:space="preserve">3.4223256111145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47140717506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50710272789001</t>
+    <t xml:space="preserve">3.47140693664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50710296630859</t>
   </si>
   <si>
     <t xml:space="preserve">3.41340160369873</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">3.42678737640381</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36878204345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3464720249176</t>
+    <t xml:space="preserve">3.36878228187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34647226333618</t>
   </si>
   <si>
     <t xml:space="preserve">3.31523823738098</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32862424850464</t>
+    <t xml:space="preserve">3.32862448692322</t>
   </si>
   <si>
     <t xml:space="preserve">3.36432003974915</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">3.39555382728577</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35539627075195</t>
+    <t xml:space="preserve">3.35539603233337</t>
   </si>
   <si>
     <t xml:space="preserve">3.31077647209167</t>
@@ -1934,16 +1934,16 @@
     <t xml:space="preserve">3.40001559257507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30631422996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28400468826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33308625221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35093402862549</t>
+    <t xml:space="preserve">3.30631446838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28400492668152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33308601379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35093426704407</t>
   </si>
   <si>
     <t xml:space="preserve">3.52941250801086</t>
@@ -1952,34 +1952,34 @@
     <t xml:space="preserve">3.65880942344666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71235299110413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8105161190033</t>
+    <t xml:space="preserve">3.71235322952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81051659584045</t>
   </si>
   <si>
     <t xml:space="preserve">3.80605435371399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76589632034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60080409049988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55618453025818</t>
+    <t xml:space="preserve">3.7658965587616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6008038520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55618405342102</t>
   </si>
   <si>
     <t xml:space="preserve">3.4669451713562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62757587432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78374409675598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69004344940186</t>
+    <t xml:space="preserve">3.62757611274719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78374433517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69004368782043</t>
   </si>
   <si>
     <t xml:space="preserve">3.70789122581482</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">3.69896721839905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7212769985199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72573924064636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62311387062073</t>
+    <t xml:space="preserve">3.72127723693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72573947906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62311363220215</t>
   </si>
   <si>
     <t xml:space="preserve">3.60972809791565</t>
@@ -2018,13 +2018,13 @@
     <t xml:space="preserve">3.56957030296326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96668529510498</t>
+    <t xml:space="preserve">3.96668481826782</t>
   </si>
   <si>
     <t xml:space="preserve">3.73466277122498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69450521469116</t>
+    <t xml:space="preserve">3.69450497627258</t>
   </si>
   <si>
     <t xml:space="preserve">3.70342922210693</t>
@@ -2033,43 +2033,43 @@
     <t xml:space="preserve">3.63203811645508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60526585578918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57849454879761</t>
+    <t xml:space="preserve">3.60526609420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57849431037903</t>
   </si>
   <si>
     <t xml:space="preserve">3.56510829925537</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93991327285767</t>
+    <t xml:space="preserve">3.93991351127625</t>
   </si>
   <si>
     <t xml:space="preserve">4.06038618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91314172744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98899435997009</t>
+    <t xml:space="preserve">3.91314196586609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98899483680725</t>
   </si>
   <si>
     <t xml:space="preserve">3.98007082939148</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12731599807739</t>
+    <t xml:space="preserve">4.12731552124023</t>
   </si>
   <si>
     <t xml:space="preserve">4.05146217346191</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09161949157715</t>
+    <t xml:space="preserve">4.09161996841431</t>
   </si>
   <si>
     <t xml:space="preserve">4.03361415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92652726173401</t>
+    <t xml:space="preserve">3.92652750015259</t>
   </si>
   <si>
     <t xml:space="preserve">3.90867972373962</t>
@@ -2078,22 +2078,22 @@
     <t xml:space="preserve">3.90421748161316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04253911972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93545126914978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89083194732666</t>
+    <t xml:space="preserve">4.0425386428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93545150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8908314704895</t>
   </si>
   <si>
     <t xml:space="preserve">4.07823419570923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19424438476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00238037109375</t>
+    <t xml:space="preserve">4.19424486160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00238084793091</t>
   </si>
   <si>
     <t xml:space="preserve">4.1763973236084</t>
@@ -2102,16 +2102,16 @@
     <t xml:space="preserve">4.08715772628784</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21655464172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46196269989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53335475921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64044141769409</t>
+    <t xml:space="preserve">4.21655511856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46196317672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53335380554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64044094085693</t>
   </si>
   <si>
     <t xml:space="preserve">4.58689785003662</t>
@@ -2123,31 +2123,31 @@
     <t xml:space="preserve">4.7564525604248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78322458267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68506050109863</t>
+    <t xml:space="preserve">4.78322410583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68506097793579</t>
   </si>
   <si>
     <t xml:space="preserve">4.83676767349243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81891965866089</t>
+    <t xml:space="preserve">4.81892013549805</t>
   </si>
   <si>
     <t xml:space="preserve">4.90815925598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00632238388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89923477172852</t>
+    <t xml:space="preserve">5.00632190704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89923524856567</t>
   </si>
   <si>
     <t xml:space="preserve">4.85461568832397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97955083847046</t>
+    <t xml:space="preserve">4.9795503616333</t>
   </si>
   <si>
     <t xml:space="preserve">5.12233304977417</t>
@@ -2156,10 +2156,10 @@
     <t xml:space="preserve">5.04201793670654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89031171798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95277881622314</t>
+    <t xml:space="preserve">4.8903112411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9527792930603</t>
   </si>
   <si>
     <t xml:space="preserve">4.8456916809082</t>
@@ -2168,16 +2168,16 @@
     <t xml:space="preserve">4.76537656784058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82784414291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80999612808228</t>
+    <t xml:space="preserve">4.82784366607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80999565124512</t>
   </si>
   <si>
     <t xml:space="preserve">4.94385480880737</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0687894821167</t>
+    <t xml:space="preserve">5.06878995895386</t>
   </si>
   <si>
     <t xml:space="preserve">4.99739837646484</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">5.42574691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15802907943726</t>
+    <t xml:space="preserve">5.15802955627441</t>
   </si>
   <si>
     <t xml:space="preserve">4.88138723373413</t>
@@ -2207,43 +2207,43 @@
     <t xml:space="preserve">4.70290899276733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71183300018311</t>
+    <t xml:space="preserve">4.71183347702026</t>
   </si>
   <si>
     <t xml:space="preserve">4.73860454559326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63151741027832</t>
+    <t xml:space="preserve">4.63151788711548</t>
   </si>
   <si>
     <t xml:space="preserve">4.67613697052002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56012630462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41734266281128</t>
+    <t xml:space="preserve">4.56012582778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41734313964844</t>
   </si>
   <si>
     <t xml:space="preserve">4.14516353607178</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02022886276245</t>
+    <t xml:space="preserve">4.02022838592529</t>
   </si>
   <si>
     <t xml:space="preserve">3.98453307151794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94883728027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80159282684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12783622741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15906953811646</t>
+    <t xml:space="preserve">3.94883751869202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8015923500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12783575057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15906977653503</t>
   </si>
   <si>
     <t xml:space="preserve">3.25277090072632</t>
@@ -2255,16 +2255,16 @@
     <t xml:space="preserve">2.757493019104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961738586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45854187011719</t>
+    <t xml:space="preserve">2.44961762428284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45854163169861</t>
   </si>
   <si>
     <t xml:space="preserve">2.14174222946167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9989595413208</t>
+    <t xml:space="preserve">1.99895930290222</t>
   </si>
   <si>
     <t xml:space="preserve">2.10604643821716</t>
@@ -2273,16 +2273,16 @@
     <t xml:space="preserve">2.2577531337738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34699273109436</t>
+    <t xml:space="preserve">2.34699249267578</t>
   </si>
   <si>
     <t xml:space="preserve">2.4228458404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54331874847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40053629875183</t>
+    <t xml:space="preserve">2.54331851005554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40053606033325</t>
   </si>
   <si>
     <t xml:space="preserve">2.48085117340088</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">2.45407962799072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46300339698792</t>
+    <t xml:space="preserve">2.46300363540649</t>
   </si>
   <si>
     <t xml:space="preserve">2.56116652488708</t>
@@ -2300,13 +2300,13 @@
     <t xml:space="preserve">2.73964524269104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23938488960266</t>
+    <t xml:space="preserve">3.23938536643982</t>
   </si>
   <si>
     <t xml:space="preserve">3.20368933677673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10998821258545</t>
+    <t xml:space="preserve">3.10998797416687</t>
   </si>
   <si>
     <t xml:space="preserve">2.91812372207642</t>
@@ -2315,34 +2315,34 @@
     <t xml:space="preserve">2.85119438171387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99843907356262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93597149848938</t>
+    <t xml:space="preserve">2.99843883514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93597173690796</t>
   </si>
   <si>
     <t xml:space="preserve">2.94489550590515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89135193824768</t>
+    <t xml:space="preserve">2.8913516998291</t>
   </si>
   <si>
     <t xml:space="preserve">2.97612929344177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85565614700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98059105873108</t>
+    <t xml:space="preserve">2.85565638542175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98059129714966</t>
   </si>
   <si>
     <t xml:space="preserve">3.00290107727051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13229775428772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01182508468628</t>
+    <t xml:space="preserve">3.1322979927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0118248462677</t>
   </si>
   <si>
     <t xml:space="preserve">2.98862147331238</t>
@@ -2357,22 +2357,22 @@
     <t xml:space="preserve">2.951495885849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8772439956665</t>
+    <t xml:space="preserve">2.87724423408508</t>
   </si>
   <si>
     <t xml:space="preserve">2.88652563095093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85404062271118</t>
+    <t xml:space="preserve">2.85404086112976</t>
   </si>
   <si>
     <t xml:space="preserve">2.7473042011261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71481895446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96077704429626</t>
+    <t xml:space="preserve">2.71481919288635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96077728271484</t>
   </si>
   <si>
     <t xml:space="preserve">2.75658559799194</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">2.78442978858948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83547806739807</t>
+    <t xml:space="preserve">2.83547782897949</t>
   </si>
   <si>
     <t xml:space="preserve">3.08607649803162</t>
@@ -2405,19 +2405,19 @@
     <t xml:space="preserve">3.31347155570984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35059714317322</t>
+    <t xml:space="preserve">3.3505973815918</t>
   </si>
   <si>
     <t xml:space="preserve">3.27634596824646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28098678588867</t>
+    <t xml:space="preserve">3.28098654747009</t>
   </si>
   <si>
     <t xml:space="preserve">3.34595656394958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07215428352356</t>
+    <t xml:space="preserve">3.07215452194214</t>
   </si>
   <si>
     <t xml:space="preserve">3.07679510116577</t>
@@ -2426,13 +2426,13 @@
     <t xml:space="preserve">3.09999847412109</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16032814979553</t>
+    <t xml:space="preserve">3.16032791137695</t>
   </si>
   <si>
     <t xml:space="preserve">3.09535789489746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05359125137329</t>
+    <t xml:space="preserve">3.05359148979187</t>
   </si>
   <si>
     <t xml:space="preserve">3.03502869606018</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">2.99326205253601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85868144035339</t>
+    <t xml:space="preserve">2.85868120193481</t>
   </si>
   <si>
     <t xml:space="preserve">2.83083701133728</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">2.82155561447144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84940004348755</t>
+    <t xml:space="preserve">2.84939980506897</t>
   </si>
   <si>
     <t xml:space="preserve">2.81227421760559</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">2.88188505172729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7937114238739</t>
+    <t xml:space="preserve">2.79371118545532</t>
   </si>
   <si>
     <t xml:space="preserve">2.76122617721558</t>
@@ -2480,13 +2480,13 @@
     <t xml:space="preserve">2.90972924232483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86332201957703</t>
+    <t xml:space="preserve">2.86332225799561</t>
   </si>
   <si>
     <t xml:space="preserve">2.78907084465027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69161558151245</t>
+    <t xml:space="preserve">2.69161581993103</t>
   </si>
   <si>
     <t xml:space="preserve">2.59416055679321</t>
@@ -2507,7 +2507,7 @@
     <t xml:space="preserve">2.16257381439209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13472938537598</t>
+    <t xml:space="preserve">2.13472962379456</t>
   </si>
   <si>
     <t xml:space="preserve">2.24610686302185</t>
@@ -2516,16 +2516,16 @@
     <t xml:space="preserve">2.40389108657837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58951997756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55703496932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60808253288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55239391326904</t>
+    <t xml:space="preserve">2.589519739151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55703473091125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60808277130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55239415168762</t>
   </si>
   <si>
     <t xml:space="preserve">2.57559776306152</t>
@@ -2540,13 +2540,13 @@
     <t xml:space="preserve">2.40853190422058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35748410224915</t>
+    <t xml:space="preserve">2.35748386383057</t>
   </si>
   <si>
     <t xml:space="preserve">2.54311275482178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45029854774475</t>
+    <t xml:space="preserve">2.45029830932617</t>
   </si>
   <si>
     <t xml:space="preserve">2.41781330108643</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">2.45957970619202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44565749168396</t>
+    <t xml:space="preserve">2.44565773010254</t>
   </si>
   <si>
     <t xml:space="preserve">2.46422052383423</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">2.4317352771759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49670577049255</t>
+    <t xml:space="preserve">2.49670553207397</t>
   </si>
   <si>
     <t xml:space="preserve">2.47814273834229</t>
@@ -2576,28 +2576,28 @@
     <t xml:space="preserve">2.51990914344788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50134611129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52919030189514</t>
+    <t xml:space="preserve">2.50134634971619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52919054031372</t>
   </si>
   <si>
     <t xml:space="preserve">2.56167554855347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5663161277771</t>
+    <t xml:space="preserve">2.56631636619568</t>
   </si>
   <si>
     <t xml:space="preserve">2.3017954826355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29715442657471</t>
+    <t xml:space="preserve">2.29715466499329</t>
   </si>
   <si>
     <t xml:space="preserve">2.29251408576965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2785918712616</t>
+    <t xml:space="preserve">2.27859163284302</t>
   </si>
   <si>
     <t xml:space="preserve">2.23218464851379</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">2.19969964027405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17185544967651</t>
+    <t xml:space="preserve">2.17185521125793</t>
   </si>
   <si>
     <t xml:space="preserve">2.26931023597717</t>
@@ -2618,13 +2618,13 @@
     <t xml:space="preserve">2.24146604537964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22754383087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19505906105042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12544822692871</t>
+    <t xml:space="preserve">2.22754406929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19505882263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12544798851013</t>
   </si>
   <si>
     <t xml:space="preserve">2.01407098770142</t>
@@ -2639,13 +2639,13 @@
     <t xml:space="preserve">2.0744001865387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97230446338654</t>
+    <t xml:space="preserve">1.97230458259583</t>
   </si>
   <si>
     <t xml:space="preserve">1.96766364574432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.944460272789</t>
+    <t xml:space="preserve">1.94446015357971</t>
   </si>
   <si>
     <t xml:space="preserve">1.87020885944366</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">1.81730461120605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79688549041748</t>
+    <t xml:space="preserve">1.79688537120819</t>
   </si>
   <si>
     <t xml:space="preserve">1.80059802532196</t>
@@ -2669,7 +2669,7 @@
     <t xml:space="preserve">1.88413095474243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03263401985168</t>
+    <t xml:space="preserve">2.03263378143311</t>
   </si>
   <si>
     <t xml:space="preserve">2.50598692893982</t>
@@ -2690,10 +2690,10 @@
     <t xml:space="preserve">2.77978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71946001052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70553755760193</t>
+    <t xml:space="preserve">2.71945977210999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70553779602051</t>
   </si>
   <si>
     <t xml:space="preserve">2.7241005897522</t>
@@ -2705,10 +2705,10 @@
     <t xml:space="preserve">2.64056777954102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68233418464661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76586723327637</t>
+    <t xml:space="preserve">2.68233442306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76586699485779</t>
   </si>
   <si>
     <t xml:space="preserve">2.58023834228516</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">2.6127233505249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59880113601685</t>
+    <t xml:space="preserve">2.59880137443542</t>
   </si>
   <si>
     <t xml:space="preserve">2.62664556503296</t>
@@ -2738,10 +2738,10 @@
     <t xml:space="preserve">2.39925050735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27395105361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32963967323303</t>
+    <t xml:space="preserve">2.27395129203796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32963991165161</t>
   </si>
   <si>
     <t xml:space="preserve">2.3482027053833</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">2.35284328460693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39460968971252</t>
+    <t xml:space="preserve">2.39460945129395</t>
   </si>
   <si>
     <t xml:space="preserve">2.46886134147644</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">2.64520835876465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7008969783783</t>
+    <t xml:space="preserve">2.70089721679688</t>
   </si>
   <si>
     <t xml:space="preserve">2.71017861366272</t>
@@ -2783,16 +2783,16 @@
     <t xml:space="preserve">2.93757343292236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9979031085968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09071731567383</t>
+    <t xml:space="preserve">2.99790287017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09071707725525</t>
   </si>
   <si>
     <t xml:space="preserve">3.04895091056824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10463953018188</t>
+    <t xml:space="preserve">3.10463929176331</t>
   </si>
   <si>
     <t xml:space="preserve">3.11392092704773</t>
@@ -2801,19 +2801,19 @@
     <t xml:space="preserve">3.2392201423645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24386072158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21601629257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25314259529114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29026818275452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29954957962036</t>
+    <t xml:space="preserve">3.24386096000671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2160165309906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25314235687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29026794433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29954934120178</t>
   </si>
   <si>
     <t xml:space="preserve">3.31811237335205</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">3.61975908279419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49910044670105</t>
+    <t xml:space="preserve">3.49910020828247</t>
   </si>
   <si>
     <t xml:space="preserve">3.62904047966003</t>
@@ -2843,19 +2843,19 @@
     <t xml:space="preserve">3.41092658042908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34131574630737</t>
+    <t xml:space="preserve">3.34131598472595</t>
   </si>
   <si>
     <t xml:space="preserve">3.3273937702179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44805216789246</t>
+    <t xml:space="preserve">3.44805240631104</t>
   </si>
   <si>
     <t xml:space="preserve">3.38772320747375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41556739807129</t>
+    <t xml:space="preserve">3.41556763648987</t>
   </si>
   <si>
     <t xml:space="preserve">3.29490876197815</t>
@@ -2870,19 +2870,19 @@
     <t xml:space="preserve">3.13248372077942</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17889070510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18353176116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28562712669373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3738009929657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43413019180298</t>
+    <t xml:space="preserve">3.17889094352722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18353152275085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2856273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37380075454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43413043022156</t>
   </si>
   <si>
     <t xml:space="preserve">3.47589659690857</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">3.50838160514832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63368105888367</t>
+    <t xml:space="preserve">3.63368082046509</t>
   </si>
   <si>
     <t xml:space="preserve">3.60583686828613</t>
@@ -2903,28 +2903,28 @@
     <t xml:space="preserve">3.54550743103027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69865107536316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55478858947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53622603416443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4434118270874</t>
+    <t xml:space="preserve">3.69865083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55478882789612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53622579574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44341158866882</t>
   </si>
   <si>
     <t xml:space="preserve">3.52230405807495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54086661338806</t>
+    <t xml:space="preserve">3.54086685180664</t>
   </si>
   <si>
     <t xml:space="preserve">3.46197438240051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47125601768494</t>
+    <t xml:space="preserve">3.47125577926636</t>
   </si>
   <si>
     <t xml:space="preserve">3.50374102592468</t>
@@ -2936,16 +2936,16 @@
     <t xml:space="preserve">3.22993874549866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26706457138062</t>
+    <t xml:space="preserve">3.26706433296204</t>
   </si>
   <si>
     <t xml:space="preserve">3.33203434944153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39236354827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37844157218933</t>
+    <t xml:space="preserve">3.39236378669739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37844181060791</t>
   </si>
   <si>
     <t xml:space="preserve">3.30883097648621</t>
@@ -2966,13 +2966,13 @@
     <t xml:space="preserve">3.05823230743408</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13712453842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11856150627136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96541786193848</t>
+    <t xml:space="preserve">3.13712430000305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11856126785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9654176235199</t>
   </si>
   <si>
     <t xml:space="preserve">3.30419015884399</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">3.17425012588501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12784290313721</t>
+    <t xml:space="preserve">3.12784266471863</t>
   </si>
   <si>
     <t xml:space="preserve">3.19745373725891</t>
@@ -3002,16 +3002,16 @@
     <t xml:space="preserve">3.36451935768127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45269322395325</t>
+    <t xml:space="preserve">3.45269298553467</t>
   </si>
   <si>
     <t xml:space="preserve">3.42020797729492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42484879493713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32275319099426</t>
+    <t xml:space="preserve">3.42484903335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32275295257568</t>
   </si>
   <si>
     <t xml:space="preserve">3.33667516708374</t>
@@ -3020,13 +3020,13 @@
     <t xml:space="preserve">3.38308238983154</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36916017532349</t>
+    <t xml:space="preserve">3.36916041374207</t>
   </si>
   <si>
     <t xml:space="preserve">3.16496872901917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01646566390991</t>
+    <t xml:space="preserve">3.01646590232849</t>
   </si>
   <si>
     <t xml:space="preserve">3.1696093082428</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">3.06751370429993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0211067199707</t>
+    <t xml:space="preserve">3.02110648155212</t>
   </si>
   <si>
     <t xml:space="preserve">3.15568733215332</t>
@@ -3044,10 +3044,10 @@
     <t xml:space="preserve">3.14176511764526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.123202085495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03966927528381</t>
+    <t xml:space="preserve">3.12320232391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03966951370239</t>
   </si>
   <si>
     <t xml:space="preserve">3.14640593528748</t>
@@ -3062,10 +3062,10 @@
     <t xml:space="preserve">2.58487915992737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77050757408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86796259880066</t>
+    <t xml:space="preserve">2.7705078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86796283721924</t>
   </si>
   <si>
     <t xml:space="preserve">2.94685482978821</t>
@@ -3074,7 +3074,7 @@
     <t xml:space="preserve">2.98398065567017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02574706077576</t>
+    <t xml:space="preserve">3.02574729919434</t>
   </si>
   <si>
     <t xml:space="preserve">2.97934007644653</t>
@@ -3083,16 +3083,16 @@
     <t xml:space="preserve">2.80299282073975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84475922584534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9282922744751</t>
+    <t xml:space="preserve">2.84475946426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92829203605652</t>
   </si>
   <si>
     <t xml:space="preserve">2.87260365486145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89116621017456</t>
+    <t xml:space="preserve">2.89116644859314</t>
   </si>
   <si>
     <t xml:space="preserve">3.03038787841797</t>
@@ -3101,16 +3101,16 @@
     <t xml:space="preserve">2.8169150352478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68697500228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69625639915466</t>
+    <t xml:space="preserve">2.68697476387024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69625616073608</t>
   </si>
   <si>
     <t xml:space="preserve">2.62200474739075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79835200309753</t>
+    <t xml:space="preserve">2.79835224151611</t>
   </si>
   <si>
     <t xml:space="preserve">2.91901063919067</t>
@@ -3122,7 +3122,7 @@
     <t xml:space="preserve">2.9050886631012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95613646507263</t>
+    <t xml:space="preserve">2.95613622665405</t>
   </si>
   <si>
     <t xml:space="preserve">2.80763363838196</t>
@@ -3140,31 +3140,31 @@
     <t xml:space="preserve">2.74266338348389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63128638267517</t>
+    <t xml:space="preserve">2.63128614425659</t>
   </si>
   <si>
     <t xml:space="preserve">2.49206471443176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53847169876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54775333404541</t>
+    <t xml:space="preserve">2.53847193717957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54775309562683</t>
   </si>
   <si>
     <t xml:space="preserve">2.48742413520813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44101715087891</t>
+    <t xml:space="preserve">2.44101691246033</t>
   </si>
   <si>
     <t xml:space="preserve">2.47350192070007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43637609481812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38996887207031</t>
+    <t xml:space="preserve">2.43637633323669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38996911048889</t>
   </si>
   <si>
     <t xml:space="preserve">2.3249990940094</t>
@@ -3176,19 +3176,19 @@
     <t xml:space="preserve">2.31107687950134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28323245048523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28787326812744</t>
+    <t xml:space="preserve">2.28323268890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28787302970886</t>
   </si>
   <si>
     <t xml:space="preserve">2.26002883911133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33428072929382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33892107009888</t>
+    <t xml:space="preserve">2.33428049087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33892130851746</t>
   </si>
   <si>
     <t xml:space="preserve">2.30643606185913</t>
@@ -3218,13 +3218,13 @@
     <t xml:space="preserve">2.18113660812378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22290325164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18577766418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11616683006287</t>
+    <t xml:space="preserve">2.22290301322937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18577742576599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11616659164429</t>
   </si>
   <si>
     <t xml:space="preserve">2.0976037979126</t>
@@ -3242,22 +3242,22 @@
     <t xml:space="preserve">2.04191517829895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02335262298584</t>
+    <t xml:space="preserve">2.02335238456726</t>
   </si>
   <si>
     <t xml:space="preserve">2.00014877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98158586025238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97694540023804</t>
+    <t xml:space="preserve">1.98158597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97694528102875</t>
   </si>
   <si>
     <t xml:space="preserve">1.99086737632751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99550807476044</t>
+    <t xml:space="preserve">1.99550831317902</t>
   </si>
   <si>
     <t xml:space="preserve">2.00478959083557</t>
@@ -3272,10 +3272,10 @@
     <t xml:space="preserve">2.05119657516479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00943040847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02799296379089</t>
+    <t xml:space="preserve">2.0094301700592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02799320220947</t>
   </si>
   <si>
     <t xml:space="preserve">1.95838224887848</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">1.93981945514679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91197526454926</t>
+    <t xml:space="preserve">1.91197514533997</t>
   </si>
   <si>
     <t xml:space="preserve">1.90269374847412</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">1.75419080257416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73562800884247</t>
+    <t xml:space="preserve">1.73562788963318</t>
   </si>
   <si>
     <t xml:space="preserve">1.82472968101501</t>
@@ -3314,16 +3314,16 @@
     <t xml:space="preserve">1.80431056022644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77646625041962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.793172955513</t>
+    <t xml:space="preserve">1.77646636962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79317283630371</t>
   </si>
   <si>
     <t xml:space="preserve">1.7950291633606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76904118061066</t>
+    <t xml:space="preserve">1.76904106140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75047838687897</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">1.81916093826294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287335395813</t>
+    <t xml:space="preserve">1.82287347316742</t>
   </si>
   <si>
     <t xml:space="preserve">2.01871156692505</t>
@@ -3368,22 +3368,22 @@
     <t xml:space="preserve">2.37604665756226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38532829284668</t>
+    <t xml:space="preserve">2.3853280544281</t>
   </si>
   <si>
     <t xml:space="preserve">2.3714063167572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60344219207764</t>
+    <t xml:space="preserve">2.60344195365906</t>
   </si>
   <si>
     <t xml:space="preserve">3.56407022476196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64296245574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57799243927002</t>
+    <t xml:space="preserve">3.64296221733093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5779926776886</t>
   </si>
   <si>
     <t xml:space="preserve">3.55942964553833</t>
@@ -3392,19 +3392,19 @@
     <t xml:space="preserve">3.82859110832214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90748333930969</t>
+    <t xml:space="preserve">3.90748310089111</t>
   </si>
   <si>
     <t xml:space="preserve">4.00029754638672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81466913223267</t>
+    <t xml:space="preserve">3.81466889381409</t>
   </si>
   <si>
     <t xml:space="preserve">3.48517823219299</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42948961257935</t>
+    <t xml:space="preserve">3.42948937416077</t>
   </si>
   <si>
     <t xml:space="preserve">3.45733380317688</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">3.35987877845764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58727383613586</t>
+    <t xml:space="preserve">3.58727407455444</t>
   </si>
   <si>
     <t xml:space="preserve">3.52694439888</t>
@@ -69786,7 +69786,7 @@
     </row>
     <row r="2511">
       <c r="A2511" s="1" t="n">
-        <v>45974.691412037</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B2511" t="n">
         <v>354988</v>
@@ -69807,6 +69807,32 @@
         <v>1365</v>
       </c>
       <c r="H2511" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" s="1" t="n">
+        <v>45975.6909837963</v>
+      </c>
+      <c r="B2512" t="n">
+        <v>172083</v>
+      </c>
+      <c r="C2512" t="n">
+        <v>7.42000007629395</v>
+      </c>
+      <c r="D2512" t="n">
+        <v>7.05999994277954</v>
+      </c>
+      <c r="E2512" t="n">
+        <v>7.3600001335144</v>
+      </c>
+      <c r="F2512" t="n">
+        <v>7.34000015258789</v>
+      </c>
+      <c r="G2512" t="s">
+        <v>1369</v>
+      </c>
+      <c r="H2512" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="1394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="1395">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95473062992096</t>
+    <t xml:space="preserve">1.95473086833954</t>
   </si>
   <si>
     <t xml:space="preserve">FM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95993423461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9096348285675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85586702823639</t>
+    <t xml:space="preserve">1.95993399620056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90963470935822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85586678981781</t>
   </si>
   <si>
     <t xml:space="preserve">1.86453926563263</t>
@@ -65,37 +65,37 @@
     <t xml:space="preserve">1.74486184120178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69542968273163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61824667453766</t>
+    <t xml:space="preserve">1.69542992115021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61824655532837</t>
   </si>
   <si>
     <t xml:space="preserve">1.52285158634186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47949004173279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34420263767242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45434057712555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55233728885651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48989689350128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54366505146027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.595698595047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51331210136414</t>
+    <t xml:space="preserve">1.47949016094208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34420251846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45434045791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55233716964722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48989677429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54366493225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59569871425629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51331198215485</t>
   </si>
   <si>
     <t xml:space="preserve">1.53325819969177</t>
@@ -104,13 +104,13 @@
     <t xml:space="preserve">1.499436378479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4300582408905</t>
+    <t xml:space="preserve">1.43005812168121</t>
   </si>
   <si>
     <t xml:space="preserve">1.40751039981842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38582968711853</t>
+    <t xml:space="preserve">1.38582956790924</t>
   </si>
   <si>
     <t xml:space="preserve">1.28349673748016</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">1.17682766914368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24186968803406</t>
+    <t xml:space="preserve">1.24186980724335</t>
   </si>
   <si>
     <t xml:space="preserve">1.20718061923981</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">1.23059582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43873059749603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39710354804993</t>
+    <t xml:space="preserve">1.43873047828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39710342884064</t>
   </si>
   <si>
     <t xml:space="preserve">1.50030362606049</t>
@@ -140,28 +140,28 @@
     <t xml:space="preserve">1.48295903205872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46561455726624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52111709117889</t>
+    <t xml:space="preserve">1.46561443805695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5211169719696</t>
   </si>
   <si>
     <t xml:space="preserve">1.51678085327148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49423289299011</t>
+    <t xml:space="preserve">1.4942330121994</t>
   </si>
   <si>
     <t xml:space="preserve">1.47688841819763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47515392303467</t>
+    <t xml:space="preserve">1.47515404224396</t>
   </si>
   <si>
     <t xml:space="preserve">1.50984311103821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56014239788055</t>
+    <t xml:space="preserve">1.56014227867126</t>
   </si>
   <si>
     <t xml:space="preserve">1.58702635765076</t>
@@ -173,10 +173,10 @@
     <t xml:space="preserve">1.52805483341217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54279768466949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51244473457336</t>
+    <t xml:space="preserve">1.54279780387878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51244485378265</t>
   </si>
   <si>
     <t xml:space="preserve">1.55147004127502</t>
@@ -188,16 +188,16 @@
     <t xml:space="preserve">1.67374897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70843827724457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67808520793915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65467011928558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63298940658569</t>
+    <t xml:space="preserve">1.70843815803528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67808508872986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65467000007629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63298952579498</t>
   </si>
   <si>
     <t xml:space="preserve">1.6061053276062</t>
@@ -206,16 +206,16 @@
     <t xml:space="preserve">1.53499269485474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49770188331604</t>
+    <t xml:space="preserve">1.49770176410675</t>
   </si>
   <si>
     <t xml:space="preserve">1.49683463573456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48122453689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41791689395905</t>
+    <t xml:space="preserve">1.48122441768646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41791701316833</t>
   </si>
   <si>
     <t xml:space="preserve">1.39970517158508</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">1.46041119098663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57228338718414</t>
+    <t xml:space="preserve">1.57228350639343</t>
   </si>
   <si>
     <t xml:space="preserve">1.62952041625977</t>
@@ -242,22 +242,22 @@
     <t xml:space="preserve">1.60870707035065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62518429756165</t>
+    <t xml:space="preserve">1.62518441677094</t>
   </si>
   <si>
     <t xml:space="preserve">1.65987360477448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58615911006927</t>
+    <t xml:space="preserve">1.58615899085999</t>
   </si>
   <si>
     <t xml:space="preserve">1.55407166481018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6009019613266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58876073360443</t>
+    <t xml:space="preserve">1.60090208053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58876085281372</t>
   </si>
   <si>
     <t xml:space="preserve">1.49249851703644</t>
@@ -269,25 +269,25 @@
     <t xml:space="preserve">1.47775566577911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47428667545319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46908330917358</t>
+    <t xml:space="preserve">1.47428679466248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46908342838287</t>
   </si>
   <si>
     <t xml:space="preserve">1.56794726848602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53932869434357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53065645694733</t>
+    <t xml:space="preserve">1.53932881355286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53065657615662</t>
   </si>
   <si>
     <t xml:space="preserve">1.54106318950653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56968176364899</t>
+    <t xml:space="preserve">1.5696816444397</t>
   </si>
   <si>
     <t xml:space="preserve">1.5471339225769</t>
@@ -299,16 +299,16 @@
     <t xml:space="preserve">1.56708014011383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57401788234711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5107102394104</t>
+    <t xml:space="preserve">1.5740180015564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51071035861969</t>
   </si>
   <si>
     <t xml:space="preserve">1.59136247634888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56100940704346</t>
+    <t xml:space="preserve">1.56100952625275</t>
   </si>
   <si>
     <t xml:space="preserve">1.54453229904175</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">1.45000445842743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38929855823517</t>
+    <t xml:space="preserve">1.38929843902588</t>
   </si>
   <si>
     <t xml:space="preserve">1.40057241916656</t>
@@ -326,10 +326,10 @@
     <t xml:space="preserve">1.3875640630722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44740283489227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49163138866425</t>
+    <t xml:space="preserve">1.44740271568298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49163126945496</t>
   </si>
   <si>
     <t xml:space="preserve">1.4838262796402</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">1.3294597864151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3884311914444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39016556739807</t>
+    <t xml:space="preserve">1.38843107223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39016568660736</t>
   </si>
   <si>
     <t xml:space="preserve">1.35981273651123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33726489543915</t>
+    <t xml:space="preserve">1.33726477622986</t>
   </si>
   <si>
     <t xml:space="preserve">1.31124806404114</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">1.30257570743561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3615471124649</t>
+    <t xml:space="preserve">1.36154723167419</t>
   </si>
   <si>
     <t xml:space="preserve">1.37802445888519</t>
@@ -383,25 +383,25 @@
     <t xml:space="preserve">1.39450180530548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4040412902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39363467693329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42225313186646</t>
+    <t xml:space="preserve">1.40404140949249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.393634557724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42225301265717</t>
   </si>
   <si>
     <t xml:space="preserve">1.42832362651825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37889170646667</t>
+    <t xml:space="preserve">1.37889182567596</t>
   </si>
   <si>
     <t xml:space="preserve">1.38062620162964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3658834695816</t>
+    <t xml:space="preserve">1.36588335037231</t>
   </si>
   <si>
     <t xml:space="preserve">1.3563437461853</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">1.35460937023163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34333539009094</t>
+    <t xml:space="preserve">1.34333550930023</t>
   </si>
   <si>
     <t xml:space="preserve">1.33119428157806</t>
@@ -422,37 +422,37 @@
     <t xml:space="preserve">1.30170845985413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3077791929245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34767150878906</t>
+    <t xml:space="preserve">1.30777907371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34767162799835</t>
   </si>
   <si>
     <t xml:space="preserve">1.34506988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33379590511322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37108671665192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35547649860382</t>
+    <t xml:space="preserve">1.33379578590393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37108659744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35547661781311</t>
   </si>
   <si>
     <t xml:space="preserve">1.34940600395203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33813190460205</t>
+    <t xml:space="preserve">1.33813202381134</t>
   </si>
   <si>
     <t xml:space="preserve">1.34853875637054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41704976558685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40317416191101</t>
+    <t xml:space="preserve">1.41704964637756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40317404270172</t>
   </si>
   <si>
     <t xml:space="preserve">1.39536905288696</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">1.36501610279083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38322782516479</t>
+    <t xml:space="preserve">1.38322794437408</t>
   </si>
   <si>
     <t xml:space="preserve">1.36761772632599</t>
@@ -476,37 +476,37 @@
     <t xml:space="preserve">1.39797067642212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37455558776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41358089447021</t>
+    <t xml:space="preserve">1.37455570697784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41358077526093</t>
   </si>
   <si>
     <t xml:space="preserve">1.42138588428497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41271340847015</t>
+    <t xml:space="preserve">1.41271352767944</t>
   </si>
   <si>
     <t xml:space="preserve">1.40924477577209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42572212219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35114049911499</t>
+    <t xml:space="preserve">1.42572200298309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3511403799057</t>
   </si>
   <si>
     <t xml:space="preserve">1.35894548892975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34680426120758</t>
+    <t xml:space="preserve">1.34680438041687</t>
   </si>
   <si>
     <t xml:space="preserve">1.36414885520935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36241447925568</t>
+    <t xml:space="preserve">1.36241436004639</t>
   </si>
   <si>
     <t xml:space="preserve">1.33032703399658</t>
@@ -518,19 +518,19 @@
     <t xml:space="preserve">1.3190530538559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31992018222809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31298243999481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17942941188812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26181602478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29216909408569</t>
+    <t xml:space="preserve">1.31992030143738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3129825592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17942929267883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26181614398956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2921689748764</t>
   </si>
   <si>
     <t xml:space="preserve">1.23146307468414</t>
@@ -539,37 +539,37 @@
     <t xml:space="preserve">1.21758759021759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2488077878952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22886145114899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18549990653992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15774869918823</t>
+    <t xml:space="preserve">1.24880766868591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2288613319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18550002574921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15774881839752</t>
   </si>
   <si>
     <t xml:space="preserve">1.11872339248657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13086462020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12305951118469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13346648216248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11438727378845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11612176895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11525464057922</t>
+    <t xml:space="preserve">1.13086473941803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12305974960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13346636295319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11438739299774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11612164974213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11525452136993</t>
   </si>
   <si>
     <t xml:space="preserve">1.09791004657745</t>
@@ -584,58 +584,58 @@
     <t xml:space="preserve">1.07276034355164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10398054122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1542797088623</t>
+    <t xml:space="preserve">1.10398066043854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15427982807159</t>
   </si>
   <si>
     <t xml:space="preserve">1.16295206546783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16208481788635</t>
+    <t xml:space="preserve">1.16208493709564</t>
   </si>
   <si>
     <t xml:space="preserve">1.17856216430664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18289816379547</t>
+    <t xml:space="preserve">1.18289840221405</t>
   </si>
   <si>
     <t xml:space="preserve">1.20544612407684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23493194580078</t>
+    <t xml:space="preserve">1.23493206501007</t>
   </si>
   <si>
     <t xml:space="preserve">1.24533867835999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21845459938049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19937562942505</t>
+    <t xml:space="preserve">1.21845471858978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19937574863434</t>
   </si>
   <si>
     <t xml:space="preserve">1.20111012458801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22799408435822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22192347049713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23666632175446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26875400543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38409507274628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3988379240036</t>
+    <t xml:space="preserve">1.2279942035675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22192358970642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23666644096375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26875388622284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38409519195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39883804321289</t>
   </si>
   <si>
     <t xml:space="preserve">1.38669669628143</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">1.33292853832245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28869998455048</t>
+    <t xml:space="preserve">1.28870010375977</t>
   </si>
   <si>
     <t xml:space="preserve">1.25747990608215</t>
@@ -662,25 +662,25 @@
     <t xml:space="preserve">1.2444714307785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22712683677673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25661253929138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22365808486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22279071807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25314378738403</t>
+    <t xml:space="preserve">1.22712695598602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25661265850067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2236579656601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2227908372879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25314390659332</t>
   </si>
   <si>
     <t xml:space="preserve">1.22625982761383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21325135231018</t>
+    <t xml:space="preserve">1.21325123310089</t>
   </si>
   <si>
     <t xml:space="preserve">1.20891511440277</t>
@@ -692,16 +692,16 @@
     <t xml:space="preserve">1.21585297584534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21672010421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19070327281952</t>
+    <t xml:space="preserve">1.21672022342682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1907035112381</t>
   </si>
   <si>
     <t xml:space="preserve">1.20197737216949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18810176849365</t>
+    <t xml:space="preserve">1.18810164928436</t>
   </si>
   <si>
     <t xml:space="preserve">1.191570520401</t>
@@ -716,10 +716,10 @@
     <t xml:space="preserve">1.2340646982193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27742624282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27222275733948</t>
+    <t xml:space="preserve">1.27742612361908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27222263813019</t>
   </si>
   <si>
     <t xml:space="preserve">1.2982394695282</t>
@@ -740,52 +740,52 @@
     <t xml:space="preserve">1.24794042110443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24967479705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29043447971344</t>
+    <t xml:space="preserve">1.2496749162674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29043459892273</t>
   </si>
   <si>
     <t xml:space="preserve">1.29303622245789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31818568706512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30691182613373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27309000492096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24013531208038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27916049957275</t>
+    <t xml:space="preserve">1.31818580627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30691170692444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27308988571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24013519287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27916073799133</t>
   </si>
   <si>
     <t xml:space="preserve">1.2704883813858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26528477668762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28436398506165</t>
+    <t xml:space="preserve">1.26528489589691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28436386585236</t>
   </si>
   <si>
     <t xml:space="preserve">1.27482438087463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26441764831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28523111343384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28696548938751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33986639976501</t>
+    <t xml:space="preserve">1.26441752910614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28523123264313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28696572780609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33986663818359</t>
   </si>
   <si>
     <t xml:space="preserve">1.33899927139282</t>
@@ -797,13 +797,13 @@
     <t xml:space="preserve">1.57835412025452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51851546764374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54019606113434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49856925010681</t>
+    <t xml:space="preserve">1.51851534843445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54019618034363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49856913089752</t>
   </si>
   <si>
     <t xml:space="preserve">1.50724148750305</t>
@@ -815,16 +815,16 @@
     <t xml:space="preserve">1.47862303256989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43352711200714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40577578544617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38496232032776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47168505191803</t>
+    <t xml:space="preserve">1.43352699279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40577590465546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38496220111847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47168517112732</t>
   </si>
   <si>
     <t xml:space="preserve">1.48729526996613</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">1.45954382419586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45607507228851</t>
+    <t xml:space="preserve">1.45607495307922</t>
   </si>
   <si>
     <t xml:space="preserve">1.49076402187347</t>
@@ -860,10 +860,10 @@
     <t xml:space="preserve">1.50637412071228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57488524913788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58269011974335</t>
+    <t xml:space="preserve">1.57488512992859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58269023895264</t>
   </si>
   <si>
     <t xml:space="preserve">1.56187677383423</t>
@@ -872,31 +872,31 @@
     <t xml:space="preserve">1.53585994243622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48642778396606</t>
+    <t xml:space="preserve">1.48642790317535</t>
   </si>
   <si>
     <t xml:space="preserve">1.49510014057159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51157748699188</t>
+    <t xml:space="preserve">1.51157760620117</t>
   </si>
   <si>
     <t xml:space="preserve">1.48902952671051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48035728931427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48816227912903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51591360569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56881439685822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57054889202118</t>
+    <t xml:space="preserve">1.48035740852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48816239833832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51591372489929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56881463527679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57054901123047</t>
   </si>
   <si>
     <t xml:space="preserve">1.64686501026154</t>
@@ -905,19 +905,19 @@
     <t xml:space="preserve">1.78648853302002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76047170162201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85933589935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86627340316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84199142456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15245890617371</t>
+    <t xml:space="preserve">1.7604718208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85933566093445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8662736415863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84199130535126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15245866775513</t>
   </si>
   <si>
     <t xml:space="preserve">1.99982666969299</t>
@@ -926,10 +926,10 @@
     <t xml:space="preserve">2.05879807472229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00329542160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95126163959503</t>
+    <t xml:space="preserve">2.00329566001892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95126187801361</t>
   </si>
   <si>
     <t xml:space="preserve">2.05186033248901</t>
@@ -938,13 +938,13 @@
     <t xml:space="preserve">2.01543664932251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98074734210968</t>
+    <t xml:space="preserve">1.98074769973755</t>
   </si>
   <si>
     <t xml:space="preserve">1.90443170070648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90790033340454</t>
+    <t xml:space="preserve">1.90790057182312</t>
   </si>
   <si>
     <t xml:space="preserve">1.91657280921936</t>
@@ -959,10 +959,10 @@
     <t xml:space="preserve">1.87321150302887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83158433437347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84719467163086</t>
+    <t xml:space="preserve">1.83158445358276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84719455242157</t>
   </si>
   <si>
     <t xml:space="preserve">1.93218290805817</t>
@@ -974,34 +974,34 @@
     <t xml:space="preserve">1.9252450466156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94258975982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97727882862091</t>
+    <t xml:space="preserve">1.94258952140808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97727847099304</t>
   </si>
   <si>
     <t xml:space="preserve">2.0206401348114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06920456886292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01196765899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03971910476685</t>
+    <t xml:space="preserve">2.06920504570007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01196789741516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03971886634827</t>
   </si>
   <si>
     <t xml:space="preserve">2.01370215415955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99462306499481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94432413578033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90269720554352</t>
+    <t xml:space="preserve">1.99462342262268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94432425498962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90269708633423</t>
   </si>
   <si>
     <t xml:space="preserve">1.82117772102356</t>
@@ -1010,34 +1010,34 @@
     <t xml:space="preserve">1.91310393810272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72144663333893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67114758491516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69976603984833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68762457370758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67895233631134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63992738723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64773225784302</t>
+    <t xml:space="preserve">1.72144675254822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67114734649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69976592063904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68762481212616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67895245552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63992726802826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64773213863373</t>
   </si>
   <si>
     <t xml:space="preserve">1.62865328788757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62691867351532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60350370407104</t>
+    <t xml:space="preserve">1.6269189119339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60350358486176</t>
   </si>
   <si>
     <t xml:space="preserve">1.59656584262848</t>
@@ -1049,28 +1049,28 @@
     <t xml:space="preserve">1.6485995054245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6650767326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69109380245209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72925162315369</t>
+    <t xml:space="preserve">1.66507685184479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6910936832428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72925174236298</t>
   </si>
   <si>
     <t xml:space="preserve">1.67548358440399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65640449523926</t>
+    <t xml:space="preserve">1.65640461444855</t>
   </si>
   <si>
     <t xml:space="preserve">1.63038766384125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66681122779846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68155419826508</t>
+    <t xml:space="preserve">1.66681134700775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68155407905579</t>
   </si>
   <si>
     <t xml:space="preserve">1.68935918807983</t>
@@ -1082,28 +1082,28 @@
     <t xml:space="preserve">1.63385653495789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62171542644501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65727174282074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71537601947784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66854572296143</t>
+    <t xml:space="preserve">1.62171530723572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65727186203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71537590026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66854584217072</t>
   </si>
   <si>
     <t xml:space="preserve">1.71711039543152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7067037820816</t>
+    <t xml:space="preserve">1.70670366287231</t>
   </si>
   <si>
     <t xml:space="preserve">1.72578275203705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72751712799072</t>
+    <t xml:space="preserve">1.72751724720001</t>
   </si>
   <si>
     <t xml:space="preserve">1.71190702915192</t>
@@ -1118,37 +1118,37 @@
     <t xml:space="preserve">1.77348041534424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80383312702179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93391752243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88188374042511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95559823513031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88621962070465</t>
+    <t xml:space="preserve">1.80383324623108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93391728401184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8818838596344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95559811592102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88621973991394</t>
   </si>
   <si>
     <t xml:space="preserve">1.81684160232544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89489209651947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80816948413849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82985007762909</t>
+    <t xml:space="preserve">1.89489221572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8081693649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8298499584198</t>
   </si>
   <si>
     <t xml:space="preserve">1.85153079032898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78215265274048</t>
+    <t xml:space="preserve">1.78215253353119</t>
   </si>
   <si>
     <t xml:space="preserve">1.81250548362732</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">1.79082489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73445510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76480805873871</t>
+    <t xml:space="preserve">1.73445498943329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.764808177948</t>
   </si>
   <si>
     <t xml:space="preserve">1.96860635280609</t>
@@ -1169,79 +1169,79 @@
     <t xml:space="preserve">1.89922833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89055597782135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87754762172699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8341863155365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84285831451416</t>
+    <t xml:space="preserve">1.89055609703064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8775475025177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83418619632721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84285855293274</t>
   </si>
   <si>
     <t xml:space="preserve">1.82551383972168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83852219581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86020290851593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9729425907135</t>
+    <t xml:space="preserve">1.83852207660675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86020302772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97294282913208</t>
   </si>
   <si>
     <t xml:space="preserve">1.98161494731903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92958092689514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98595070838928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04665684700012</t>
+    <t xml:space="preserve">1.92958104610443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98595082759857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04665660858154</t>
   </si>
   <si>
     <t xml:space="preserve">2.03364849090576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04232096672058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07267379760742</t>
+    <t xml:space="preserve">2.042320728302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.072674036026</t>
   </si>
   <si>
     <t xml:space="preserve">2.08134603500366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1116988658905</t>
+    <t xml:space="preserve">2.11169910430908</t>
   </si>
   <si>
     <t xml:space="preserve">2.15072417259216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05532908439636</t>
+    <t xml:space="preserve">2.05532932281494</t>
   </si>
   <si>
     <t xml:space="preserve">2.1854133605957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33717799186707</t>
+    <t xml:space="preserve">2.33717823028564</t>
   </si>
   <si>
     <t xml:space="preserve">2.3024890422821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28080821037292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21143007278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30682516098022</t>
+    <t xml:space="preserve">2.2808084487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.211430311203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3068253993988</t>
   </si>
   <si>
     <t xml:space="preserve">2.28514456748962</t>
@@ -1253,13 +1253,13 @@
     <t xml:space="preserve">2.48894286155701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59300994873047</t>
+    <t xml:space="preserve">2.59301018714905</t>
   </si>
   <si>
     <t xml:space="preserve">2.38921189308167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49761557579041</t>
+    <t xml:space="preserve">2.49761533737183</t>
   </si>
   <si>
     <t xml:space="preserve">2.57566571235657</t>
@@ -1271,31 +1271,31 @@
     <t xml:space="preserve">2.71442222595215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76645565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83583378791809</t>
+    <t xml:space="preserve">2.76645588874817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83583402633667</t>
   </si>
   <si>
     <t xml:space="preserve">2.91388416290283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92255663871765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93122911453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87052273750305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92689299583435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10033822059631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23909473419189</t>
+    <t xml:space="preserve">2.92255640029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93122887611389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87052321434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92689275741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10033845901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23909449577332</t>
   </si>
   <si>
     <t xml:space="preserve">3.25210332870483</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">3.21741414070129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25643944740295</t>
+    <t xml:space="preserve">3.25643920898438</t>
   </si>
   <si>
     <t xml:space="preserve">3.36050653457642</t>
@@ -1313,13 +1313,13 @@
     <t xml:space="preserve">3.20874190330505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36917901039124</t>
+    <t xml:space="preserve">3.36917877197266</t>
   </si>
   <si>
     <t xml:space="preserve">3.26511144638062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22175002098083</t>
+    <t xml:space="preserve">3.22175025939941</t>
   </si>
   <si>
     <t xml:space="preserve">3.33882594108582</t>
@@ -1352,73 +1352,73 @@
     <t xml:space="preserve">3.73341393470764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80712866783142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90685963630676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07596921920776</t>
+    <t xml:space="preserve">3.80712890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90686011314392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07596874237061</t>
   </si>
   <si>
     <t xml:space="preserve">4.0456166267395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09765005111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86783504486084</t>
+    <t xml:space="preserve">4.09764957427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86783456802368</t>
   </si>
   <si>
     <t xml:space="preserve">4.0412802696228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.945885181427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97190141677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71173405647278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91986846923828</t>
+    <t xml:space="preserve">3.94588565826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97190165519714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71173357963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91986799240112</t>
   </si>
   <si>
     <t xml:space="preserve">4.07163286209106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24941492080688</t>
+    <t xml:space="preserve">4.24941539764404</t>
   </si>
   <si>
     <t xml:space="preserve">4.25375127792358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.284104347229</t>
+    <t xml:space="preserve">4.28410387039185</t>
   </si>
   <si>
     <t xml:space="preserve">4.62232255935669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57896184921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74373435974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75240707397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05593585968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9865574836731</t>
+    <t xml:space="preserve">4.57896137237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74373388290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75240659713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05593633651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98655796051025</t>
   </si>
   <si>
     <t xml:space="preserve">4.95186901092529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87381839752197</t>
+    <t xml:space="preserve">4.87381887435913</t>
   </si>
   <si>
     <t xml:space="preserve">4.31879281997681</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">4.97788572311401</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01257514953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03859233856201</t>
+    <t xml:space="preserve">5.01257562637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0385913848877</t>
   </si>
   <si>
     <t xml:space="preserve">4.91718006134033</t>
@@ -1442,13 +1442,13 @@
     <t xml:space="preserve">4.82178449630737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85647344589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89116287231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83045768737793</t>
+    <t xml:space="preserve">4.85647439956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89116334915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83045721054077</t>
   </si>
   <si>
     <t xml:space="preserve">4.76107835769653</t>
@@ -1466,13 +1466,13 @@
     <t xml:space="preserve">4.58763313293457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64833927154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61365032196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53560018539429</t>
+    <t xml:space="preserve">4.64833974838257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61365079879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53559970855713</t>
   </si>
   <si>
     <t xml:space="preserve">4.47489356994629</t>
@@ -1484,25 +1484,25 @@
     <t xml:space="preserve">4.1843729019165</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18870878219604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24074268341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08464193344116</t>
+    <t xml:space="preserve">4.1887092590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24074220657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.084641456604</t>
   </si>
   <si>
     <t xml:space="preserve">3.9285409450531</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91553211212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85916185379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7811119556427</t>
+    <t xml:space="preserve">3.91553163528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85916209220886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78111219406128</t>
   </si>
   <si>
     <t xml:space="preserve">4.14101123809814</t>
@@ -1511,40 +1511,40 @@
     <t xml:space="preserve">3.62501096725464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31280899047852</t>
+    <t xml:space="preserve">3.31280922889709</t>
   </si>
   <si>
     <t xml:space="preserve">3.28679227828979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14369964599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00927948951721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09166598320007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03529596328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04830455780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07865738868713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96158194541931</t>
+    <t xml:space="preserve">3.14369940757751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00927972793579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09166622161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03529620170593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04830479621887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07865762710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96158170700073</t>
   </si>
   <si>
     <t xml:space="preserve">2.89653992652893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90521192550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02662420272827</t>
+    <t xml:space="preserve">2.90521216392517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02662396430969</t>
   </si>
   <si>
     <t xml:space="preserve">2.75344729423523</t>
@@ -1553,25 +1553,25 @@
     <t xml:space="preserve">2.80548071861267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88786745071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04396867752075</t>
+    <t xml:space="preserve">2.88786768913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04396843910217</t>
   </si>
   <si>
     <t xml:space="preserve">3.2607753276825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24343085289001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19139719009399</t>
+    <t xml:space="preserve">3.24343061447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19139742851257</t>
   </si>
   <si>
     <t xml:space="preserve">3.42554879188538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43855714797974</t>
+    <t xml:space="preserve">3.43855690956116</t>
   </si>
   <si>
     <t xml:space="preserve">3.39519548416138</t>
@@ -1589,28 +1589,28 @@
     <t xml:space="preserve">2.93990159034729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88353157043457</t>
+    <t xml:space="preserve">2.88353133201599</t>
   </si>
   <si>
     <t xml:space="preserve">2.97459053993225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02228784561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38218760490417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32148122787476</t>
+    <t xml:space="preserve">3.02228736877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3821873664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32148146629333</t>
   </si>
   <si>
     <t xml:space="preserve">3.15670824050903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11768269538879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08733010292053</t>
+    <t xml:space="preserve">3.11768293380737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08732986450195</t>
   </si>
   <si>
     <t xml:space="preserve">3.06564927101135</t>
@@ -1619,16 +1619,16 @@
     <t xml:space="preserve">2.81848955154419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68840527534485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73176693916321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63203573226929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98759889602661</t>
+    <t xml:space="preserve">2.68840503692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73176670074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63203549385071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98759865760803</t>
   </si>
   <si>
     <t xml:space="preserve">3.17405271530151</t>
@@ -1637,19 +1637,19 @@
     <t xml:space="preserve">3.30413675308228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3084728717804</t>
+    <t xml:space="preserve">3.30847311019897</t>
   </si>
   <si>
     <t xml:space="preserve">3.17838859558105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10467457771301</t>
+    <t xml:space="preserve">3.10467433929443</t>
   </si>
   <si>
     <t xml:space="preserve">3.16104412078857</t>
   </si>
   <si>
-    <t xml:space="preserve">3.330153465271</t>
+    <t xml:space="preserve">3.33015370368958</t>
   </si>
   <si>
     <t xml:space="preserve">3.46023774147034</t>
@@ -1658,13 +1658,13 @@
     <t xml:space="preserve">3.59032154083252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88517951965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90252327919006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8548264503479</t>
+    <t xml:space="preserve">3.88517904281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90252375602722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85482597351074</t>
   </si>
   <si>
     <t xml:space="preserve">4.11499404907227</t>
@@ -1676,13 +1676,13 @@
     <t xml:space="preserve">4.10198593139648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14534759521484</t>
+    <t xml:space="preserve">4.145348072052</t>
   </si>
   <si>
     <t xml:space="preserve">4.1323390007019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95889353752136</t>
+    <t xml:space="preserve">3.95889329910278</t>
   </si>
   <si>
     <t xml:space="preserve">3.82447361946106</t>
@@ -1691,55 +1691,55 @@
     <t xml:space="preserve">3.9675657749176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9415488243103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9979190826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00659084320068</t>
+    <t xml:space="preserve">3.94154906272888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99791884422302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00659132003784</t>
   </si>
   <si>
     <t xml:space="preserve">4.06296062469482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05862426757812</t>
+    <t xml:space="preserve">4.05862474441528</t>
   </si>
   <si>
     <t xml:space="preserve">4.01526355743408</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09331369400024</t>
+    <t xml:space="preserve">4.09331321716309</t>
   </si>
   <si>
     <t xml:space="preserve">4.0326075553894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98924612998962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92420482635498</t>
+    <t xml:space="preserve">3.98924684524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92420434951782</t>
   </si>
   <si>
     <t xml:space="preserve">3.82880973815918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75943112373352</t>
+    <t xml:space="preserve">3.7594313621521</t>
   </si>
   <si>
     <t xml:space="preserve">3.74642300605774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5686411857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.776775598526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24507904052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17136383056641</t>
+    <t xml:space="preserve">3.56864094734192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77677583694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24507856369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17136430740356</t>
   </si>
   <si>
     <t xml:space="preserve">4.0889778137207</t>
@@ -1751,10 +1751,10 @@
     <t xml:space="preserve">4.16269207000732</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21906137466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23206996917725</t>
+    <t xml:space="preserve">4.21906185150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2320704460144</t>
   </si>
   <si>
     <t xml:space="preserve">4.20171689987183</t>
@@ -1769,28 +1769,28 @@
     <t xml:space="preserve">4.76975154876709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72638988494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63966751098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55294466018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44887685775757</t>
+    <t xml:space="preserve">4.72638940811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63966703414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55294418334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44887733459473</t>
   </si>
   <si>
     <t xml:space="preserve">4.39684343338013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91119647026062</t>
+    <t xml:space="preserve">3.91119623184204</t>
   </si>
   <si>
     <t xml:space="preserve">4.04995250701904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2700982093811</t>
+    <t xml:space="preserve">4.27009868621826</t>
   </si>
   <si>
     <t xml:space="preserve">4.12285375595093</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">4.01130437850952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91760301589966</t>
+    <t xml:space="preserve">3.91760349273682</t>
   </si>
   <si>
     <t xml:space="preserve">4.22547912597656</t>
@@ -1808,19 +1808,19 @@
     <t xml:space="preserve">4.00684213638306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83282613754272</t>
+    <t xml:space="preserve">3.8328263759613</t>
   </si>
   <si>
     <t xml:space="preserve">3.85513615608215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85959792137146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93098926544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83728814125061</t>
+    <t xml:space="preserve">3.8595974445343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93098974227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83728837966919</t>
   </si>
   <si>
     <t xml:space="preserve">4.01576662063599</t>
@@ -1832,13 +1832,13 @@
     <t xml:space="preserve">3.95776081085205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79266834259033</t>
+    <t xml:space="preserve">3.79266858100891</t>
   </si>
   <si>
     <t xml:space="preserve">3.74358701705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76143455505371</t>
+    <t xml:space="preserve">3.76143479347229</t>
   </si>
   <si>
     <t xml:space="preserve">3.61419010162354</t>
@@ -1853,13 +1853,13 @@
     <t xml:space="preserve">3.48479294776917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67219543457031</t>
+    <t xml:space="preserve">3.67219519615173</t>
   </si>
   <si>
     <t xml:space="preserve">3.59634208679199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5874183177948</t>
+    <t xml:space="preserve">3.58741807937622</t>
   </si>
   <si>
     <t xml:space="preserve">3.64096164703369</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">3.52495074272156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41786336898804</t>
+    <t xml:space="preserve">3.41786360740662</t>
   </si>
   <si>
     <t xml:space="preserve">3.44909739494324</t>
@@ -1895,19 +1895,19 @@
     <t xml:space="preserve">3.41340160369873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42678737640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36878228187561</t>
+    <t xml:space="preserve">3.42678761482239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36878204345703</t>
   </si>
   <si>
     <t xml:space="preserve">3.34647226333618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31523823738098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32862448692322</t>
+    <t xml:space="preserve">3.31523847579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32862424850464</t>
   </si>
   <si>
     <t xml:space="preserve">3.36432003974915</t>
@@ -1943,10 +1943,10 @@
     <t xml:space="preserve">3.33308601379395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35093426704407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52941250801086</t>
+    <t xml:space="preserve">3.35093402862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52941274642944</t>
   </si>
   <si>
     <t xml:space="preserve">3.65880942344666</t>
@@ -1955,10 +1955,10 @@
     <t xml:space="preserve">3.71235322952271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81051659584045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80605435371399</t>
+    <t xml:space="preserve">3.81051635742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80605411529541</t>
   </si>
   <si>
     <t xml:space="preserve">3.7658965587616</t>
@@ -1973,40 +1973,40 @@
     <t xml:space="preserve">3.4669451713562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62757611274719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78374433517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69004368782043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70789122581482</t>
+    <t xml:space="preserve">3.62757587432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78374409675598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69004344940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7078914642334</t>
   </si>
   <si>
     <t xml:space="preserve">3.67665719985962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73912501335144</t>
+    <t xml:space="preserve">3.73912477493286</t>
   </si>
   <si>
     <t xml:space="preserve">3.68558144569397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66773366928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69896721839905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72127723693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72573947906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62311363220215</t>
+    <t xml:space="preserve">3.66773343086243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69896697998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7212769985199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72573924064636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62311387062073</t>
   </si>
   <si>
     <t xml:space="preserve">3.60972809791565</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">3.96668481826782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73466277122498</t>
+    <t xml:space="preserve">3.73466300964355</t>
   </si>
   <si>
     <t xml:space="preserve">3.69450497627258</t>
@@ -2042,25 +2042,25 @@
     <t xml:space="preserve">3.57849431037903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56510829925537</t>
+    <t xml:space="preserve">3.56510806083679</t>
   </si>
   <si>
     <t xml:space="preserve">3.93991351127625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06038618087769</t>
+    <t xml:space="preserve">4.06038665771484</t>
   </si>
   <si>
     <t xml:space="preserve">3.91314196586609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98899483680725</t>
+    <t xml:space="preserve">3.98899435997009</t>
   </si>
   <si>
     <t xml:space="preserve">3.98007082939148</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12731552124023</t>
+    <t xml:space="preserve">4.12731599807739</t>
   </si>
   <si>
     <t xml:space="preserve">4.05146217346191</t>
@@ -2087,13 +2087,13 @@
     <t xml:space="preserve">3.93545150756836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8908314704895</t>
+    <t xml:space="preserve">3.89083194732666</t>
   </si>
   <si>
     <t xml:space="preserve">4.07823419570923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19424486160278</t>
+    <t xml:space="preserve">4.19424438476562</t>
   </si>
   <si>
     <t xml:space="preserve">4.00238084793091</t>
@@ -2105,13 +2105,13 @@
     <t xml:space="preserve">4.08715772628784</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21655511856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46196317672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53335380554199</t>
+    <t xml:space="preserve">4.21655464172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46196269989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53335428237915</t>
   </si>
   <si>
     <t xml:space="preserve">4.64044094085693</t>
@@ -2120,19 +2120,19 @@
     <t xml:space="preserve">4.58689785003662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64936542510986</t>
+    <t xml:space="preserve">4.64936494827271</t>
   </si>
   <si>
     <t xml:space="preserve">4.7564525604248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78322410583496</t>
+    <t xml:space="preserve">4.78322458267212</t>
   </si>
   <si>
     <t xml:space="preserve">4.68506097793579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83676767349243</t>
+    <t xml:space="preserve">4.83676815032959</t>
   </si>
   <si>
     <t xml:space="preserve">4.81892013549805</t>
@@ -2141,13 +2141,13 @@
     <t xml:space="preserve">4.90815925598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00632190704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89923524856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85461568832397</t>
+    <t xml:space="preserve">5.00632238388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89923477172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85461521148682</t>
   </si>
   <si>
     <t xml:space="preserve">4.9795503616333</t>
@@ -2171,10 +2171,10 @@
     <t xml:space="preserve">4.76537656784058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82784366607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80999565124512</t>
+    <t xml:space="preserve">4.82784414291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80999612808228</t>
   </si>
   <si>
     <t xml:space="preserve">4.94385480880737</t>
@@ -2183,13 +2183,13 @@
     <t xml:space="preserve">5.06878995895386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99739837646484</t>
+    <t xml:space="preserve">4.997398853302</t>
   </si>
   <si>
     <t xml:space="preserve">5.23834466934204</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45251893997192</t>
+    <t xml:space="preserve">5.45251846313477</t>
   </si>
   <si>
     <t xml:space="preserve">5.83624744415283</t>
@@ -2204,46 +2204,46 @@
     <t xml:space="preserve">5.15802955627441</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88138723373413</t>
+    <t xml:space="preserve">4.88138675689697</t>
   </si>
   <si>
     <t xml:space="preserve">4.70290899276733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71183347702026</t>
+    <t xml:space="preserve">4.71183300018311</t>
   </si>
   <si>
     <t xml:space="preserve">4.73860454559326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63151788711548</t>
+    <t xml:space="preserve">4.63151741027832</t>
   </si>
   <si>
     <t xml:space="preserve">4.67613697052002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56012582778931</t>
+    <t xml:space="preserve">4.56012630462646</t>
   </si>
   <si>
     <t xml:space="preserve">4.41734313964844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14516353607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02022838592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98453307151794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94883751869202</t>
+    <t xml:space="preserve">4.14516401290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02022886276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98453259468079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94883704185486</t>
   </si>
   <si>
     <t xml:space="preserve">3.8015923500061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12783575057983</t>
+    <t xml:space="preserve">3.12783598899841</t>
   </si>
   <si>
     <t xml:space="preserve">3.15906977653503</t>
@@ -2252,13 +2252,13 @@
     <t xml:space="preserve">3.25277090072632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72625946998596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.757493019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44961762428284</t>
+    <t xml:space="preserve">2.72625923156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75749325752258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44961738586426</t>
   </si>
   <si>
     <t xml:space="preserve">2.45854163169861</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">1.99895930290222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10604643821716</t>
+    <t xml:space="preserve">2.10604619979858</t>
   </si>
   <si>
     <t xml:space="preserve">2.2577531337738</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">2.45407962799072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46300363540649</t>
+    <t xml:space="preserve">2.46300339698792</t>
   </si>
   <si>
     <t xml:space="preserve">2.56116652488708</t>
@@ -2303,31 +2303,31 @@
     <t xml:space="preserve">2.73964524269104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23938536643982</t>
+    <t xml:space="preserve">3.23938512802124</t>
   </si>
   <si>
     <t xml:space="preserve">3.20368933677673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10998797416687</t>
+    <t xml:space="preserve">3.10998773574829</t>
   </si>
   <si>
     <t xml:space="preserve">2.91812372207642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85119438171387</t>
+    <t xml:space="preserve">2.85119414329529</t>
   </si>
   <si>
     <t xml:space="preserve">2.99843883514404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93597173690796</t>
+    <t xml:space="preserve">2.93597149848938</t>
   </si>
   <si>
     <t xml:space="preserve">2.94489550590515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8913516998291</t>
+    <t xml:space="preserve">2.89135193824768</t>
   </si>
   <si>
     <t xml:space="preserve">2.97612929344177</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">3.00290107727051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1322979927063</t>
+    <t xml:space="preserve">3.13229775428772</t>
   </si>
   <si>
     <t xml:space="preserve">3.0118248462677</t>
@@ -4194,6 +4194,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.67999982833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8899998664856</t>
   </si>
 </sst>
 </file>
@@ -69844,7 +69847,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.6910300926</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>270274</v>
@@ -69865,6 +69868,32 @@
         <v>1393</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.6910648148</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>244697</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>7.96000003814697</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>7.57000017166138</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>7.67999982833862</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>7.8899998664856</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>1394</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="1395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="1396">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95473086833954</t>
+    <t xml:space="preserve">1.95473074913025</t>
   </si>
   <si>
     <t xml:space="preserve">FM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95993399620056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90963470935822</t>
+    <t xml:space="preserve">1.95993411540985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9096348285675</t>
   </si>
   <si>
     <t xml:space="preserve">1.85586702823639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86453914642334</t>
+    <t xml:space="preserve">1.86453902721405</t>
   </si>
   <si>
     <t xml:space="preserve">1.68415582180023</t>
@@ -65,37 +65,37 @@
     <t xml:space="preserve">1.74486172199249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69542980194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61824667453766</t>
+    <t xml:space="preserve">1.69542992115021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61824655532837</t>
   </si>
   <si>
     <t xml:space="preserve">1.52285158634186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4794899225235</t>
+    <t xml:space="preserve">1.47949004173279</t>
   </si>
   <si>
     <t xml:space="preserve">1.34420263767242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45434045791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55233716964722</t>
+    <t xml:space="preserve">1.45434057712555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55233728885651</t>
   </si>
   <si>
     <t xml:space="preserve">1.48989689350128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54366505146027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59569871425629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51331210136414</t>
+    <t xml:space="preserve">1.54366493225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59569847583771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51331198215485</t>
   </si>
   <si>
     <t xml:space="preserve">1.53325819969177</t>
@@ -110,34 +110,34 @@
     <t xml:space="preserve">1.40751028060913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38582968711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28349661827087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17682754993439</t>
+    <t xml:space="preserve">1.38582956790924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28349673748016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17682778835297</t>
   </si>
   <si>
     <t xml:space="preserve">1.24186980724335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20718061923981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23059582710266</t>
+    <t xml:space="preserve">1.2071807384491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23059594631195</t>
   </si>
   <si>
     <t xml:space="preserve">1.43873059749603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39710354804993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50030374526978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48295903205872</t>
+    <t xml:space="preserve">1.39710342884064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50030362606049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48295915126801</t>
   </si>
   <si>
     <t xml:space="preserve">1.46561455726624</t>
@@ -149,34 +149,34 @@
     <t xml:space="preserve">1.51678085327148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49423289299011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47688853740692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47515404224396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50984311103821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56014239788055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58702623844147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55754065513611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52805483341217</t>
+    <t xml:space="preserve">1.4942330121994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47688841819763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47515392303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5098432302475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56014227867126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58702635765076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55754053592682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52805495262146</t>
   </si>
   <si>
     <t xml:space="preserve">1.54279780387878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51244473457336</t>
+    <t xml:space="preserve">1.51244461536407</t>
   </si>
   <si>
     <t xml:space="preserve">1.55147004127502</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">1.61651206016541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67374897003174</t>
+    <t xml:space="preserve">1.67374908924103</t>
   </si>
   <si>
     <t xml:space="preserve">1.70843815803528</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">1.65467011928558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63298952579498</t>
+    <t xml:space="preserve">1.63298940658569</t>
   </si>
   <si>
     <t xml:space="preserve">1.6061053276062</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">1.49683463573456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48122441768646</t>
+    <t xml:space="preserve">1.48122453689575</t>
   </si>
   <si>
     <t xml:space="preserve">1.41791689395905</t>
@@ -221,19 +221,19 @@
     <t xml:space="preserve">1.39970517158508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35200774669647</t>
+    <t xml:space="preserve">1.35200762748718</t>
   </si>
   <si>
     <t xml:space="preserve">1.39190018177032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46041119098663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57228338718414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62952041625977</t>
+    <t xml:space="preserve">1.46041107177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57228350639343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62952053546906</t>
   </si>
   <si>
     <t xml:space="preserve">1.60437095165253</t>
@@ -242,46 +242,46 @@
     <t xml:space="preserve">1.60870707035065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62518429756165</t>
+    <t xml:space="preserve">1.62518441677094</t>
   </si>
   <si>
     <t xml:space="preserve">1.65987348556519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58615911006927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55407166481018</t>
+    <t xml:space="preserve">1.58615899085999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55407178401947</t>
   </si>
   <si>
     <t xml:space="preserve">1.60090184211731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58876073360443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49249839782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4578093290329</t>
+    <t xml:space="preserve">1.58876085281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49249851703644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45780944824219</t>
   </si>
   <si>
     <t xml:space="preserve">1.47775566577911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47428679466248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46908330917358</t>
+    <t xml:space="preserve">1.47428691387177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46908342838287</t>
   </si>
   <si>
     <t xml:space="preserve">1.56794726848602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53932869434357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53065645694733</t>
+    <t xml:space="preserve">1.53932881355286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53065657615662</t>
   </si>
   <si>
     <t xml:space="preserve">1.54106318950653</t>
@@ -299,10 +299,10 @@
     <t xml:space="preserve">1.56708014011383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5740180015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5107102394104</t>
+    <t xml:space="preserve">1.57401788234711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51071012020111</t>
   </si>
   <si>
     <t xml:space="preserve">1.59136247634888</t>
@@ -311,10 +311,10 @@
     <t xml:space="preserve">1.56100940704346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54453217983246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45000445842743</t>
+    <t xml:space="preserve">1.54453229904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45000433921814</t>
   </si>
   <si>
     <t xml:space="preserve">1.38929855823517</t>
@@ -323,22 +323,22 @@
     <t xml:space="preserve">1.40057241916656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3875640630722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44740283489227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49163138866425</t>
+    <t xml:space="preserve">1.38756394386292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44740271568298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49163126945496</t>
   </si>
   <si>
     <t xml:space="preserve">1.4838262796402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32338905334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32945990562439</t>
+    <t xml:space="preserve">1.32338929176331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32945966720581</t>
   </si>
   <si>
     <t xml:space="preserve">1.3884311914444</t>
@@ -350,10 +350,10 @@
     <t xml:space="preserve">1.35981273651123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33726489543915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31124794483185</t>
+    <t xml:space="preserve">1.33726501464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31124806404114</t>
   </si>
   <si>
     <t xml:space="preserve">1.30084121227264</t>
@@ -368,13 +368,13 @@
     <t xml:space="preserve">1.37802445888519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3823606967926</t>
+    <t xml:space="preserve">1.38236057758331</t>
   </si>
   <si>
     <t xml:space="preserve">1.39623630046844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.377157330513</t>
+    <t xml:space="preserve">1.37715744972229</t>
   </si>
   <si>
     <t xml:space="preserve">1.4049084186554</t>
@@ -383,10 +383,10 @@
     <t xml:space="preserve">1.39450180530548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40404140949249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.393634557724</t>
+    <t xml:space="preserve">1.4040412902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39363467693329</t>
   </si>
   <si>
     <t xml:space="preserve">1.42225313186646</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">1.38062620162964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3658834695816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3563437461853</t>
+    <t xml:space="preserve">1.36588335037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35634386539459</t>
   </si>
   <si>
     <t xml:space="preserve">1.35460937023163</t>
@@ -413,28 +413,28 @@
     <t xml:space="preserve">1.34333539009094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33119428157806</t>
+    <t xml:space="preserve">1.33119416236877</t>
   </si>
   <si>
     <t xml:space="preserve">1.32685804367065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30170845985413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3077791929245</t>
+    <t xml:space="preserve">1.30170857906342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30777907371521</t>
   </si>
   <si>
     <t xml:space="preserve">1.34767150878906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34506988525391</t>
+    <t xml:space="preserve">1.34506976604462</t>
   </si>
   <si>
     <t xml:space="preserve">1.33379590511322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37108671665192</t>
+    <t xml:space="preserve">1.37108659744263</t>
   </si>
   <si>
     <t xml:space="preserve">1.35547661781311</t>
@@ -443,13 +443,13 @@
     <t xml:space="preserve">1.34940600395203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33813190460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34853863716125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41704964637756</t>
+    <t xml:space="preserve">1.33813202381134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34853875637054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41704976558685</t>
   </si>
   <si>
     <t xml:space="preserve">1.40317416191101</t>
@@ -458,10 +458,10 @@
     <t xml:space="preserve">1.39536905288696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41097915172577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36501610279083</t>
+    <t xml:space="preserve">1.41097903251648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36501598358154</t>
   </si>
   <si>
     <t xml:space="preserve">1.38322782516479</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">1.38149344921112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39797067642212</t>
+    <t xml:space="preserve">1.39797079563141</t>
   </si>
   <si>
     <t xml:space="preserve">1.37455558776855</t>
@@ -482,16 +482,16 @@
     <t xml:space="preserve">1.41358077526093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42138588428497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41271352767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40924477577209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42572224140167</t>
+    <t xml:space="preserve">1.42138600349426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41271364688873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40924465656281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42572200298309</t>
   </si>
   <si>
     <t xml:space="preserve">1.35114049911499</t>
@@ -509,25 +509,25 @@
     <t xml:space="preserve">1.36241436004639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33032715320587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32078754901886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31905317306519</t>
+    <t xml:space="preserve">1.33032703399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32078742980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3190530538559</t>
   </si>
   <si>
     <t xml:space="preserve">1.31992018222809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31298243999481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17942941188812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26181602478027</t>
+    <t xml:space="preserve">1.3129825592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17942929267883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26181614398956</t>
   </si>
   <si>
     <t xml:space="preserve">1.29216909408569</t>
@@ -560,19 +560,19 @@
     <t xml:space="preserve">1.12305963039398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13346648216248</t>
+    <t xml:space="preserve">1.13346636295319</t>
   </si>
   <si>
     <t xml:space="preserve">1.11438727378845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11612164974213</t>
+    <t xml:space="preserve">1.11612176895142</t>
   </si>
   <si>
     <t xml:space="preserve">1.11525464057922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09791004657745</t>
+    <t xml:space="preserve">1.09791016578674</t>
   </si>
   <si>
     <t xml:space="preserve">1.09270668029785</t>
@@ -581,10 +581,10 @@
     <t xml:space="preserve">1.07536220550537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07276034355164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10398054122925</t>
+    <t xml:space="preserve">1.07276046276093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10398042201996</t>
   </si>
   <si>
     <t xml:space="preserve">1.1542797088623</t>
@@ -593,37 +593,37 @@
     <t xml:space="preserve">1.16295206546783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16208481788635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17856204509735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18289828300476</t>
+    <t xml:space="preserve">1.16208493709564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17856216430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18289840221405</t>
   </si>
   <si>
     <t xml:space="preserve">1.20544612407684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23493182659149</t>
+    <t xml:space="preserve">1.23493194580078</t>
   </si>
   <si>
     <t xml:space="preserve">1.24533867835999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21845459938049</t>
+    <t xml:space="preserve">1.21845471858978</t>
   </si>
   <si>
     <t xml:space="preserve">1.19937562942505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20111012458801</t>
+    <t xml:space="preserve">1.20111000537872</t>
   </si>
   <si>
     <t xml:space="preserve">1.2279942035675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22192347049713</t>
+    <t xml:space="preserve">1.22192358970642</t>
   </si>
   <si>
     <t xml:space="preserve">1.23666632175446</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">1.38409507274628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39883804321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38669681549072</t>
+    <t xml:space="preserve">1.39883816242218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38669669628143</t>
   </si>
   <si>
     <t xml:space="preserve">1.35721111297607</t>
@@ -647,10 +647,10 @@
     <t xml:space="preserve">1.34593713283539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33292853832245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28869998455048</t>
+    <t xml:space="preserve">1.33292865753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28870010375977</t>
   </si>
   <si>
     <t xml:space="preserve">1.25747990608215</t>
@@ -662,16 +662,16 @@
     <t xml:space="preserve">1.2444714307785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22712683677673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25661253929138</t>
+    <t xml:space="preserve">1.22712695598602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25661265850067</t>
   </si>
   <si>
     <t xml:space="preserve">1.2236579656601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22279071807861</t>
+    <t xml:space="preserve">1.2227908372879</t>
   </si>
   <si>
     <t xml:space="preserve">1.25314378738403</t>
@@ -686,16 +686,16 @@
     <t xml:space="preserve">1.20891523361206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20457899570465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21585297584534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21672010421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19070327281952</t>
+    <t xml:space="preserve">1.20457911491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21585285663605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21672022342682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19070339202881</t>
   </si>
   <si>
     <t xml:space="preserve">1.20197737216949</t>
@@ -713,13 +713,13 @@
     <t xml:space="preserve">1.19243776798248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2340646982193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27742624282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27222263813019</t>
+    <t xml:space="preserve">1.23406457901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27742612361908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27222275733948</t>
   </si>
   <si>
     <t xml:space="preserve">1.2982394695282</t>
@@ -728,10 +728,10 @@
     <t xml:space="preserve">1.26355051994324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24273693561554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23579907417297</t>
+    <t xml:space="preserve">1.24273705482483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23579919338226</t>
   </si>
   <si>
     <t xml:space="preserve">1.22018897533417</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">1.24967479705811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29043459892273</t>
+    <t xml:space="preserve">1.29043447971344</t>
   </si>
   <si>
     <t xml:space="preserve">1.29303634166718</t>
@@ -755,16 +755,16 @@
     <t xml:space="preserve">1.30691194534302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27309000492096</t>
+    <t xml:space="preserve">1.27309012413025</t>
   </si>
   <si>
     <t xml:space="preserve">1.24013531208038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27916061878204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27048826217651</t>
+    <t xml:space="preserve">1.27916049957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2704883813858</t>
   </si>
   <si>
     <t xml:space="preserve">1.26528489589691</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">1.28523111343384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28696548938751</t>
+    <t xml:space="preserve">1.2869656085968</t>
   </si>
   <si>
     <t xml:space="preserve">1.33986639976501</t>
@@ -791,19 +791,19 @@
     <t xml:space="preserve">1.33899927139282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41184651851654</t>
+    <t xml:space="preserve">1.41184639930725</t>
   </si>
   <si>
     <t xml:space="preserve">1.57835412025452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51851534843445</t>
+    <t xml:space="preserve">1.51851546764374</t>
   </si>
   <si>
     <t xml:space="preserve">1.54019606113434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49856925010681</t>
+    <t xml:space="preserve">1.49856913089752</t>
   </si>
   <si>
     <t xml:space="preserve">1.50724148750305</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">1.40577578544617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38496232032776</t>
+    <t xml:space="preserve">1.38496220111847</t>
   </si>
   <si>
     <t xml:space="preserve">1.47168505191803</t>
@@ -830,10 +830,10 @@
     <t xml:space="preserve">1.48729526996613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47602128982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45694208145142</t>
+    <t xml:space="preserve">1.47602117061615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45694220066071</t>
   </si>
   <si>
     <t xml:space="preserve">1.4682160615921</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">1.45867669582367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45954382419586</t>
+    <t xml:space="preserve">1.45954394340515</t>
   </si>
   <si>
     <t xml:space="preserve">1.45607495307922</t>
@@ -878,22 +878,22 @@
     <t xml:space="preserve">1.49510014057159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51157760620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4890296459198</t>
+    <t xml:space="preserve">1.51157748699188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48902952671051</t>
   </si>
   <si>
     <t xml:space="preserve">1.48035728931427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48816239833832</t>
+    <t xml:space="preserve">1.48816251754761</t>
   </si>
   <si>
     <t xml:space="preserve">1.51591360569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5688145160675</t>
+    <t xml:space="preserve">1.56881463527679</t>
   </si>
   <si>
     <t xml:space="preserve">1.57054901123047</t>
@@ -902,10 +902,10 @@
     <t xml:space="preserve">1.64686512947083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78648853302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76047170162201</t>
+    <t xml:space="preserve">1.78648865222931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7604718208313</t>
   </si>
   <si>
     <t xml:space="preserve">1.85933589935303</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">1.84199130535126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15245866775513</t>
+    <t xml:space="preserve">2.15245890617371</t>
   </si>
   <si>
     <t xml:space="preserve">1.99982666969299</t>
@@ -938,73 +938,73 @@
     <t xml:space="preserve">2.01543641090393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98074758052826</t>
+    <t xml:space="preserve">1.98074769973755</t>
   </si>
   <si>
     <t xml:space="preserve">1.90443181991577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90790057182312</t>
+    <t xml:space="preserve">1.90790045261383</t>
   </si>
   <si>
     <t xml:space="preserve">1.91657280921936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90616595745087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84892892837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87321150302887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83158433437347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84719455242157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93218314647675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93738603591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92524516582489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94258952140808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97727882862091</t>
+    <t xml:space="preserve">1.90616583824158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84892904758453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87321138381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83158445358276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84719467163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93218290805817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93738627433777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9252450466156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94258987903595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97727859020233</t>
   </si>
   <si>
     <t xml:space="preserve">2.0206401348114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06920456886292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01196765899658</t>
+    <t xml:space="preserve">2.06920480728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01196789741516</t>
   </si>
   <si>
     <t xml:space="preserve">2.03971886634827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01370215415955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99462306499481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94432413578033</t>
+    <t xml:space="preserve">2.01370239257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99462330341339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94432425498962</t>
   </si>
   <si>
     <t xml:space="preserve">1.90269720554352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82117772102356</t>
+    <t xml:space="preserve">1.82117760181427</t>
   </si>
   <si>
     <t xml:space="preserve">1.91310381889343</t>
@@ -1013,34 +1013,34 @@
     <t xml:space="preserve">1.72144663333893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67114758491516</t>
+    <t xml:space="preserve">1.67114734649658</t>
   </si>
   <si>
     <t xml:space="preserve">1.69976603984833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68762469291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67895233631134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63992726802826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64773225784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62865316867828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62691867351532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60350370407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59656596183777</t>
+    <t xml:space="preserve">1.68762457370758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67895245552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63992714881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64773213863373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62865328788757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62691879272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60350358486176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59656572341919</t>
   </si>
   <si>
     <t xml:space="preserve">1.63905990123749</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">1.6485995054245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6650767326355</t>
+    <t xml:space="preserve">1.66507685184479</t>
   </si>
   <si>
     <t xml:space="preserve">1.6910936832428</t>
@@ -1061,28 +1061,28 @@
     <t xml:space="preserve">1.67548358440399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65640461444855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63038766384125</t>
+    <t xml:space="preserve">1.65640449523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63038778305054</t>
   </si>
   <si>
     <t xml:space="preserve">1.66681122779846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68155419826508</t>
+    <t xml:space="preserve">1.68155407905579</t>
   </si>
   <si>
     <t xml:space="preserve">1.68935918807983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67721796035767</t>
+    <t xml:space="preserve">1.67721807956696</t>
   </si>
   <si>
     <t xml:space="preserve">1.63385665416718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6217155456543</t>
+    <t xml:space="preserve">1.62171530723572</t>
   </si>
   <si>
     <t xml:space="preserve">1.65727174282074</t>
@@ -1094,64 +1094,64 @@
     <t xml:space="preserve">1.66854572296143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71711039543152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7067037820816</t>
+    <t xml:space="preserve">1.71711051464081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70670366287231</t>
   </si>
   <si>
     <t xml:space="preserve">1.72578275203705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72751724720001</t>
+    <t xml:space="preserve">1.72751700878143</t>
   </si>
   <si>
     <t xml:space="preserve">1.71190702915192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74312722682953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77781641483307</t>
+    <t xml:space="preserve">1.74312734603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77781629562378</t>
   </si>
   <si>
     <t xml:space="preserve">1.77348029613495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80383324623108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93391728401184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8818838596344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95559823513031</t>
+    <t xml:space="preserve">1.80383312702179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93391740322113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88188374042511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95559811592102</t>
   </si>
   <si>
     <t xml:space="preserve">1.88621973991394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81684172153473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89489221572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8081693649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8298499584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85153079032898</t>
+    <t xml:space="preserve">1.81684160232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89489197731018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80816924571991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82984983921051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85153067111969</t>
   </si>
   <si>
     <t xml:space="preserve">1.78215253353119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81250548362732</t>
+    <t xml:space="preserve">1.81250536441803</t>
   </si>
   <si>
     <t xml:space="preserve">1.79082489013672</t>
@@ -1160,16 +1160,16 @@
     <t xml:space="preserve">1.73445498943329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76480805873871</t>
+    <t xml:space="preserve">1.764808177948</t>
   </si>
   <si>
     <t xml:space="preserve">1.96860635280609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89922833442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89055585861206</t>
+    <t xml:space="preserve">1.89922845363617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89055609703064</t>
   </si>
   <si>
     <t xml:space="preserve">1.8775475025177</t>
@@ -1181,25 +1181,25 @@
     <t xml:space="preserve">1.84285831451416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82551383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83852219581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86020302772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97294235229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98161494731903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92958092689514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98595070838928</t>
+    <t xml:space="preserve">1.82551395893097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83852207660675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86020290851593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9729425907135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98161482810974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92958116531372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98595082759857</t>
   </si>
   <si>
     <t xml:space="preserve">2.04665684700012</t>
@@ -1211,31 +1211,31 @@
     <t xml:space="preserve">2.042320728302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07267379760742</t>
+    <t xml:space="preserve">2.072674036026</t>
   </si>
   <si>
     <t xml:space="preserve">2.08134603500366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1116988658905</t>
+    <t xml:space="preserve">2.11169862747192</t>
   </si>
   <si>
     <t xml:space="preserve">2.15072441101074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05532908439636</t>
+    <t xml:space="preserve">2.05532932281494</t>
   </si>
   <si>
     <t xml:space="preserve">2.1854133605957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33717799186707</t>
+    <t xml:space="preserve">2.33717823028564</t>
   </si>
   <si>
     <t xml:space="preserve">2.3024890422821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28080821037292</t>
+    <t xml:space="preserve">2.2808084487915</t>
   </si>
   <si>
     <t xml:space="preserve">2.21143007278442</t>
@@ -1247,25 +1247,25 @@
     <t xml:space="preserve">2.28514456748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44991755485535</t>
+    <t xml:space="preserve">2.44991779327393</t>
   </si>
   <si>
     <t xml:space="preserve">2.48894286155701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59300994873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38921189308167</t>
+    <t xml:space="preserve">2.59301018714905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38921213150024</t>
   </si>
   <si>
     <t xml:space="preserve">2.49761533737183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57566571235657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62769937515259</t>
+    <t xml:space="preserve">2.57566595077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62769961357117</t>
   </si>
   <si>
     <t xml:space="preserve">2.71442222595215</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">2.83583378791809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91388416290283</t>
+    <t xml:space="preserve">2.91388440132141</t>
   </si>
   <si>
     <t xml:space="preserve">2.92255663871765</t>
@@ -1295,16 +1295,16 @@
     <t xml:space="preserve">3.10033845901489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23909449577332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25210309028625</t>
+    <t xml:space="preserve">3.23909473419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25210285186768</t>
   </si>
   <si>
     <t xml:space="preserve">3.21741414070129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25643968582153</t>
+    <t xml:space="preserve">3.25643920898438</t>
   </si>
   <si>
     <t xml:space="preserve">3.36050653457642</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">3.36917877197266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26511144638062</t>
+    <t xml:space="preserve">3.26511168479919</t>
   </si>
   <si>
     <t xml:space="preserve">3.22175002098083</t>
@@ -1328,16 +1328,16 @@
     <t xml:space="preserve">3.27811980247498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34749794006348</t>
+    <t xml:space="preserve">3.34749817848206</t>
   </si>
   <si>
     <t xml:space="preserve">3.50793528556824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48625445365906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55563282966614</t>
+    <t xml:space="preserve">3.48625469207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55563259124756</t>
   </si>
   <si>
     <t xml:space="preserve">3.51227164268494</t>
@@ -1355,34 +1355,34 @@
     <t xml:space="preserve">3.80712842941284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90685963630676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07596921920776</t>
+    <t xml:space="preserve">3.90686011314392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07596874237061</t>
   </si>
   <si>
     <t xml:space="preserve">4.0456166267395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09765005111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86783456802368</t>
+    <t xml:space="preserve">4.09764957427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86783480644226</t>
   </si>
   <si>
     <t xml:space="preserve">4.0412802696228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94588470458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97190141677856</t>
+    <t xml:space="preserve">3.945885181427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97190165519714</t>
   </si>
   <si>
     <t xml:space="preserve">3.71173405647278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91986799240112</t>
+    <t xml:space="preserve">3.9198682308197</t>
   </si>
   <si>
     <t xml:space="preserve">4.07163333892822</t>
@@ -1391,16 +1391,16 @@
     <t xml:space="preserve">4.24941492080688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25375080108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.284104347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62232255935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57896184921265</t>
+    <t xml:space="preserve">4.25375127792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28410387039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62232303619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57896137237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.74373435974121</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">4.75240707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05593633651733</t>
+    <t xml:space="preserve">5.05593585968018</t>
   </si>
   <si>
     <t xml:space="preserve">4.98655796051025</t>
@@ -1418,13 +1418,13 @@
     <t xml:space="preserve">4.95186901092529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87381839752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31879281997681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80444049835205</t>
+    <t xml:space="preserve">4.87381887435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31879329681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80444002151489</t>
   </si>
   <si>
     <t xml:space="preserve">4.97788572311401</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">5.01257514953613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03859233856201</t>
+    <t xml:space="preserve">5.03859186172485</t>
   </si>
   <si>
     <t xml:space="preserve">4.91718006134033</t>
@@ -1445,16 +1445,16 @@
     <t xml:space="preserve">4.85647392272949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89116287231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83045768737793</t>
+    <t xml:space="preserve">4.89116334915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83045721054077</t>
   </si>
   <si>
     <t xml:space="preserve">4.76107883453369</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54427242279053</t>
+    <t xml:space="preserve">4.54427194595337</t>
   </si>
   <si>
     <t xml:space="preserve">4.70904541015625</t>
@@ -1463,64 +1463,64 @@
     <t xml:space="preserve">4.60497808456421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58763313293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64833927154541</t>
+    <t xml:space="preserve">4.58763360977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64833974838257</t>
   </si>
   <si>
     <t xml:space="preserve">4.61365032196045</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53559970855713</t>
+    <t xml:space="preserve">4.53560018539429</t>
   </si>
   <si>
     <t xml:space="preserve">4.47489356994629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40551519393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1843729019165</t>
+    <t xml:space="preserve">4.40551614761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18437242507935</t>
   </si>
   <si>
     <t xml:space="preserve">4.18870878219604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24074220657349</t>
+    <t xml:space="preserve">4.24074268341064</t>
   </si>
   <si>
     <t xml:space="preserve">4.084641456604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9285409450531</t>
+    <t xml:space="preserve">3.92854118347168</t>
   </si>
   <si>
     <t xml:space="preserve">3.91553211212158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85916185379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78111171722412</t>
+    <t xml:space="preserve">3.85916233062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78111219406128</t>
   </si>
   <si>
     <t xml:space="preserve">4.14101123809814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62501096725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31280922889709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28679227828979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14369964599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00927948951721</t>
+    <t xml:space="preserve">3.62501072883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31280899047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28679203987122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14369988441467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00927972793579</t>
   </si>
   <si>
     <t xml:space="preserve">3.09166598320007</t>
@@ -1529,13 +1529,13 @@
     <t xml:space="preserve">3.03529620170593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04830479621887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07865738868713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96158194541931</t>
+    <t xml:space="preserve">3.04830455780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07865762710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96158170700073</t>
   </si>
   <si>
     <t xml:space="preserve">2.89653992652893</t>
@@ -1544,7 +1544,7 @@
     <t xml:space="preserve">2.90521216392517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02662420272827</t>
+    <t xml:space="preserve">3.02662396430969</t>
   </si>
   <si>
     <t xml:space="preserve">2.75344729423523</t>
@@ -1553,40 +1553,40 @@
     <t xml:space="preserve">2.80548071861267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88786745071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04396867752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2607753276825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24343109130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19139742851257</t>
+    <t xml:space="preserve">2.88786768913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04396843910217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26077556610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24343061447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19139695167542</t>
   </si>
   <si>
     <t xml:space="preserve">3.42554879188538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43855714797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39519548416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20440554618835</t>
+    <t xml:space="preserve">3.43855667114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39519572257996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20440578460693</t>
   </si>
   <si>
     <t xml:space="preserve">3.06998538970947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86618685722351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93990135192871</t>
+    <t xml:space="preserve">2.86618709564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93990111351013</t>
   </si>
   <si>
     <t xml:space="preserve">2.88353157043457</t>
@@ -1601,37 +1601,37 @@
     <t xml:space="preserve">3.3821873664856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32148122787476</t>
+    <t xml:space="preserve">3.32148146629333</t>
   </si>
   <si>
     <t xml:space="preserve">3.15670824050903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11768269538879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08733010292053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06564927101135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81848955154419</t>
+    <t xml:space="preserve">3.11768293380737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08732986450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06564903259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81848931312561</t>
   </si>
   <si>
     <t xml:space="preserve">2.68840527534485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73176693916321</t>
+    <t xml:space="preserve">2.73176670074463</t>
   </si>
   <si>
     <t xml:space="preserve">2.63203549385071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98759889602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17405247688293</t>
+    <t xml:space="preserve">2.98759865760803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17405271530151</t>
   </si>
   <si>
     <t xml:space="preserve">3.3041365146637</t>
@@ -1640,25 +1640,25 @@
     <t xml:space="preserve">3.3084728717804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17838883399963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10467433929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16104412078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.330153465271</t>
+    <t xml:space="preserve">3.17838859558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10467457771301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16104435920715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33015370368958</t>
   </si>
   <si>
     <t xml:space="preserve">3.46023774147034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59032154083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88517904281616</t>
+    <t xml:space="preserve">3.5903217792511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8851797580719</t>
   </si>
   <si>
     <t xml:space="preserve">3.90252375602722</t>
@@ -1667,34 +1667,34 @@
     <t xml:space="preserve">3.85482621192932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11499404907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27543115615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10198640823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14534759521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1323390007019</t>
+    <t xml:space="preserve">4.11499500274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27543163299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10198593139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.145348072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13233947753906</t>
   </si>
   <si>
     <t xml:space="preserve">3.95889353752136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82447361946106</t>
+    <t xml:space="preserve">3.82447338104248</t>
   </si>
   <si>
     <t xml:space="preserve">3.9675657749176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9415488243103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99791860580444</t>
+    <t xml:space="preserve">3.94154906272888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9979190826416</t>
   </si>
   <si>
     <t xml:space="preserve">4.00659132003784</t>
@@ -1715,22 +1715,22 @@
     <t xml:space="preserve">4.03260803222656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98924612998962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92420482635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82880973815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7594313621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74642300605774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5686411857605</t>
+    <t xml:space="preserve">3.98924660682678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9242045879364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8288094997406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75943112373352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74642276763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56864094734192</t>
   </si>
   <si>
     <t xml:space="preserve">3.77677583694458</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">4.17136430740356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0889778137207</t>
+    <t xml:space="preserve">4.08897733688354</t>
   </si>
   <si>
     <t xml:space="preserve">4.06729698181152</t>
@@ -1751,7 +1751,7 @@
     <t xml:space="preserve">4.16269207000732</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21906137466431</t>
+    <t xml:space="preserve">4.21906185150146</t>
   </si>
   <si>
     <t xml:space="preserve">4.2320704460144</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">4.20171689987183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68302869796753</t>
+    <t xml:space="preserve">4.68302822113037</t>
   </si>
   <si>
     <t xml:space="preserve">4.88249111175537</t>
@@ -1769,25 +1769,25 @@
     <t xml:space="preserve">4.76975107192993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72638988494873</t>
+    <t xml:space="preserve">4.72638940811157</t>
   </si>
   <si>
     <t xml:space="preserve">4.63966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55294466018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44887685775757</t>
+    <t xml:space="preserve">4.55294418334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44887733459473</t>
   </si>
   <si>
     <t xml:space="preserve">4.39684343338013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91119647026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04995203018188</t>
+    <t xml:space="preserve">3.91119623184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04995250701904</t>
   </si>
   <si>
     <t xml:space="preserve">4.2700982093811</t>
@@ -1796,31 +1796,31 @@
     <t xml:space="preserve">4.12285375595093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01130437850952</t>
+    <t xml:space="preserve">4.01130485534668</t>
   </si>
   <si>
     <t xml:space="preserve">3.91760301589966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22547912597656</t>
+    <t xml:space="preserve">4.2254786491394</t>
   </si>
   <si>
     <t xml:space="preserve">4.00684213638306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83282613754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85513615608215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85959792137146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93098926544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83728814125061</t>
+    <t xml:space="preserve">3.8328263759613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85513591766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85959768295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93098950386047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83728790283203</t>
   </si>
   <si>
     <t xml:space="preserve">4.01576662063599</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">4.03807640075684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95776081085205</t>
+    <t xml:space="preserve">3.95776104927063</t>
   </si>
   <si>
     <t xml:space="preserve">3.79266834259033</t>
@@ -1838,22 +1838,22 @@
     <t xml:space="preserve">3.74358701705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76143455505371</t>
+    <t xml:space="preserve">3.76143503189087</t>
   </si>
   <si>
     <t xml:space="preserve">3.61419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6811192035675</t>
+    <t xml:space="preserve">3.68111944198608</t>
   </si>
   <si>
     <t xml:space="preserve">3.52048873901367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48479294776917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67219543457031</t>
+    <t xml:space="preserve">3.48479270935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67219519615173</t>
   </si>
   <si>
     <t xml:space="preserve">3.59634208679199</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">3.64096164703369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64988589286804</t>
+    <t xml:space="preserve">3.64988565444946</t>
   </si>
   <si>
     <t xml:space="preserve">3.5115647315979</t>
@@ -1886,10 +1886,10 @@
     <t xml:space="preserve">3.4223256111145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47140693664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50710296630859</t>
+    <t xml:space="preserve">3.47140717506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50710272789001</t>
   </si>
   <si>
     <t xml:space="preserve">3.41340160369873</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">3.42678737640381</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36878228187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34647226333618</t>
+    <t xml:space="preserve">3.36878204345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3464720249176</t>
   </si>
   <si>
     <t xml:space="preserve">3.31523823738098</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32862448692322</t>
+    <t xml:space="preserve">3.32862424850464</t>
   </si>
   <si>
     <t xml:space="preserve">3.36432003974915</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">3.39555382728577</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35539603233337</t>
+    <t xml:space="preserve">3.35539627075195</t>
   </si>
   <si>
     <t xml:space="preserve">3.31077647209167</t>
@@ -1934,16 +1934,16 @@
     <t xml:space="preserve">3.40001559257507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30631446838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28400492668152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33308601379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35093426704407</t>
+    <t xml:space="preserve">3.30631422996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28400468826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33308625221252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35093402862549</t>
   </si>
   <si>
     <t xml:space="preserve">3.52941250801086</t>
@@ -1952,34 +1952,34 @@
     <t xml:space="preserve">3.65880942344666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71235322952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81051659584045</t>
+    <t xml:space="preserve">3.71235299110413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8105161190033</t>
   </si>
   <si>
     <t xml:space="preserve">3.80605435371399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7658965587616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6008038520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55618405342102</t>
+    <t xml:space="preserve">3.76589632034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60080409049988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55618453025818</t>
   </si>
   <si>
     <t xml:space="preserve">3.4669451713562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62757611274719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78374433517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69004368782043</t>
+    <t xml:space="preserve">3.62757587432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78374409675598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69004344940186</t>
   </si>
   <si>
     <t xml:space="preserve">3.70789122581482</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">3.69896721839905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72127723693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72573947906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62311363220215</t>
+    <t xml:space="preserve">3.7212769985199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72573924064636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62311387062073</t>
   </si>
   <si>
     <t xml:space="preserve">3.60972809791565</t>
@@ -2018,13 +2018,13 @@
     <t xml:space="preserve">3.56957030296326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96668481826782</t>
+    <t xml:space="preserve">3.96668529510498</t>
   </si>
   <si>
     <t xml:space="preserve">3.73466277122498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69450497627258</t>
+    <t xml:space="preserve">3.69450521469116</t>
   </si>
   <si>
     <t xml:space="preserve">3.70342922210693</t>
@@ -2033,43 +2033,43 @@
     <t xml:space="preserve">3.63203811645508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60526609420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57849431037903</t>
+    <t xml:space="preserve">3.60526585578918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57849454879761</t>
   </si>
   <si>
     <t xml:space="preserve">3.56510829925537</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93991351127625</t>
+    <t xml:space="preserve">3.93991327285767</t>
   </si>
   <si>
     <t xml:space="preserve">4.06038618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91314196586609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98899483680725</t>
+    <t xml:space="preserve">3.91314172744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98899435997009</t>
   </si>
   <si>
     <t xml:space="preserve">3.98007082939148</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12731552124023</t>
+    <t xml:space="preserve">4.12731599807739</t>
   </si>
   <si>
     <t xml:space="preserve">4.05146217346191</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09161996841431</t>
+    <t xml:space="preserve">4.09161949157715</t>
   </si>
   <si>
     <t xml:space="preserve">4.03361415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92652750015259</t>
+    <t xml:space="preserve">3.92652726173401</t>
   </si>
   <si>
     <t xml:space="preserve">3.90867972373962</t>
@@ -2078,22 +2078,22 @@
     <t xml:space="preserve">3.90421748161316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0425386428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93545150756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8908314704895</t>
+    <t xml:space="preserve">4.04253911972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93545126914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89083194732666</t>
   </si>
   <si>
     <t xml:space="preserve">4.07823419570923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19424486160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00238084793091</t>
+    <t xml:space="preserve">4.19424438476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00238037109375</t>
   </si>
   <si>
     <t xml:space="preserve">4.1763973236084</t>
@@ -2102,16 +2102,16 @@
     <t xml:space="preserve">4.08715772628784</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21655511856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46196317672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53335380554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64044094085693</t>
+    <t xml:space="preserve">4.21655464172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46196269989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53335475921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64044141769409</t>
   </si>
   <si>
     <t xml:space="preserve">4.58689785003662</t>
@@ -2123,31 +2123,31 @@
     <t xml:space="preserve">4.7564525604248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78322410583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68506097793579</t>
+    <t xml:space="preserve">4.78322458267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68506050109863</t>
   </si>
   <si>
     <t xml:space="preserve">4.83676767349243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81892013549805</t>
+    <t xml:space="preserve">4.81891965866089</t>
   </si>
   <si>
     <t xml:space="preserve">4.90815925598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00632190704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89923524856567</t>
+    <t xml:space="preserve">5.00632238388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89923477172852</t>
   </si>
   <si>
     <t xml:space="preserve">4.85461568832397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9795503616333</t>
+    <t xml:space="preserve">4.97955083847046</t>
   </si>
   <si>
     <t xml:space="preserve">5.12233304977417</t>
@@ -2156,10 +2156,10 @@
     <t xml:space="preserve">5.04201793670654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8903112411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9527792930603</t>
+    <t xml:space="preserve">4.89031171798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95277881622314</t>
   </si>
   <si>
     <t xml:space="preserve">4.8456916809082</t>
@@ -2168,16 +2168,16 @@
     <t xml:space="preserve">4.76537656784058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82784366607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80999565124512</t>
+    <t xml:space="preserve">4.82784414291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80999612808228</t>
   </si>
   <si>
     <t xml:space="preserve">4.94385480880737</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06878995895386</t>
+    <t xml:space="preserve">5.0687894821167</t>
   </si>
   <si>
     <t xml:space="preserve">4.99739837646484</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">5.42574691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15802955627441</t>
+    <t xml:space="preserve">5.15802907943726</t>
   </si>
   <si>
     <t xml:space="preserve">4.88138723373413</t>
@@ -2207,43 +2207,43 @@
     <t xml:space="preserve">4.70290899276733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71183347702026</t>
+    <t xml:space="preserve">4.71183300018311</t>
   </si>
   <si>
     <t xml:space="preserve">4.73860454559326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63151788711548</t>
+    <t xml:space="preserve">4.63151741027832</t>
   </si>
   <si>
     <t xml:space="preserve">4.67613697052002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56012582778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41734313964844</t>
+    <t xml:space="preserve">4.56012630462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41734266281128</t>
   </si>
   <si>
     <t xml:space="preserve">4.14516353607178</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02022838592529</t>
+    <t xml:space="preserve">4.02022886276245</t>
   </si>
   <si>
     <t xml:space="preserve">3.98453307151794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94883751869202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8015923500061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12783575057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15906977653503</t>
+    <t xml:space="preserve">3.94883728027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80159282684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12783622741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15906953811646</t>
   </si>
   <si>
     <t xml:space="preserve">3.25277090072632</t>
@@ -2255,16 +2255,16 @@
     <t xml:space="preserve">2.757493019104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961762428284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45854163169861</t>
+    <t xml:space="preserve">2.44961738586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45854187011719</t>
   </si>
   <si>
     <t xml:space="preserve">2.14174222946167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99895930290222</t>
+    <t xml:space="preserve">1.9989595413208</t>
   </si>
   <si>
     <t xml:space="preserve">2.10604643821716</t>
@@ -2273,16 +2273,16 @@
     <t xml:space="preserve">2.2577531337738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34699249267578</t>
+    <t xml:space="preserve">2.34699273109436</t>
   </si>
   <si>
     <t xml:space="preserve">2.4228458404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54331851005554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40053606033325</t>
+    <t xml:space="preserve">2.54331874847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40053629875183</t>
   </si>
   <si>
     <t xml:space="preserve">2.48085117340088</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">2.45407962799072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46300363540649</t>
+    <t xml:space="preserve">2.46300339698792</t>
   </si>
   <si>
     <t xml:space="preserve">2.56116652488708</t>
@@ -2300,13 +2300,13 @@
     <t xml:space="preserve">2.73964524269104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23938536643982</t>
+    <t xml:space="preserve">3.23938488960266</t>
   </si>
   <si>
     <t xml:space="preserve">3.20368933677673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10998797416687</t>
+    <t xml:space="preserve">3.10998821258545</t>
   </si>
   <si>
     <t xml:space="preserve">2.91812372207642</t>
@@ -2315,34 +2315,34 @@
     <t xml:space="preserve">2.85119438171387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99843883514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93597173690796</t>
+    <t xml:space="preserve">2.99843907356262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93597149848938</t>
   </si>
   <si>
     <t xml:space="preserve">2.94489550590515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8913516998291</t>
+    <t xml:space="preserve">2.89135193824768</t>
   </si>
   <si>
     <t xml:space="preserve">2.97612929344177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85565638542175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98059129714966</t>
+    <t xml:space="preserve">2.85565614700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98059105873108</t>
   </si>
   <si>
     <t xml:space="preserve">3.00290107727051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1322979927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0118248462677</t>
+    <t xml:space="preserve">3.13229775428772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01182508468628</t>
   </si>
   <si>
     <t xml:space="preserve">2.98862147331238</t>
@@ -2357,22 +2357,22 @@
     <t xml:space="preserve">2.951495885849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87724423408508</t>
+    <t xml:space="preserve">2.8772439956665</t>
   </si>
   <si>
     <t xml:space="preserve">2.88652563095093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85404086112976</t>
+    <t xml:space="preserve">2.85404062271118</t>
   </si>
   <si>
     <t xml:space="preserve">2.7473042011261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71481919288635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96077728271484</t>
+    <t xml:space="preserve">2.71481895446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96077704429626</t>
   </si>
   <si>
     <t xml:space="preserve">2.75658559799194</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">2.78442978858948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83547782897949</t>
+    <t xml:space="preserve">2.83547806739807</t>
   </si>
   <si>
     <t xml:space="preserve">3.08607649803162</t>
@@ -2405,19 +2405,19 @@
     <t xml:space="preserve">3.31347155570984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3505973815918</t>
+    <t xml:space="preserve">3.35059714317322</t>
   </si>
   <si>
     <t xml:space="preserve">3.27634596824646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28098654747009</t>
+    <t xml:space="preserve">3.28098678588867</t>
   </si>
   <si>
     <t xml:space="preserve">3.34595656394958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07215452194214</t>
+    <t xml:space="preserve">3.07215428352356</t>
   </si>
   <si>
     <t xml:space="preserve">3.07679510116577</t>
@@ -2426,13 +2426,13 @@
     <t xml:space="preserve">3.09999847412109</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16032791137695</t>
+    <t xml:space="preserve">3.16032814979553</t>
   </si>
   <si>
     <t xml:space="preserve">3.09535789489746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05359148979187</t>
+    <t xml:space="preserve">3.05359125137329</t>
   </si>
   <si>
     <t xml:space="preserve">3.03502869606018</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">2.99326205253601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85868120193481</t>
+    <t xml:space="preserve">2.85868144035339</t>
   </si>
   <si>
     <t xml:space="preserve">2.83083701133728</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">2.82155561447144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84939980506897</t>
+    <t xml:space="preserve">2.84940004348755</t>
   </si>
   <si>
     <t xml:space="preserve">2.81227421760559</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">2.88188505172729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79371118545532</t>
+    <t xml:space="preserve">2.7937114238739</t>
   </si>
   <si>
     <t xml:space="preserve">2.76122617721558</t>
@@ -2480,13 +2480,13 @@
     <t xml:space="preserve">2.90972924232483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86332225799561</t>
+    <t xml:space="preserve">2.86332201957703</t>
   </si>
   <si>
     <t xml:space="preserve">2.78907084465027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69161581993103</t>
+    <t xml:space="preserve">2.69161558151245</t>
   </si>
   <si>
     <t xml:space="preserve">2.59416055679321</t>
@@ -2507,7 +2507,7 @@
     <t xml:space="preserve">2.16257381439209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13472962379456</t>
+    <t xml:space="preserve">2.13472938537598</t>
   </si>
   <si>
     <t xml:space="preserve">2.24610686302185</t>
@@ -2516,16 +2516,16 @@
     <t xml:space="preserve">2.40389108657837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.589519739151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55703473091125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60808277130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55239415168762</t>
+    <t xml:space="preserve">2.58951997756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55703496932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60808253288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55239391326904</t>
   </si>
   <si>
     <t xml:space="preserve">2.57559776306152</t>
@@ -2540,13 +2540,13 @@
     <t xml:space="preserve">2.40853190422058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35748386383057</t>
+    <t xml:space="preserve">2.35748410224915</t>
   </si>
   <si>
     <t xml:space="preserve">2.54311275482178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45029830932617</t>
+    <t xml:space="preserve">2.45029854774475</t>
   </si>
   <si>
     <t xml:space="preserve">2.41781330108643</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">2.45957970619202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44565773010254</t>
+    <t xml:space="preserve">2.44565749168396</t>
   </si>
   <si>
     <t xml:space="preserve">2.46422052383423</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">2.4317352771759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49670553207397</t>
+    <t xml:space="preserve">2.49670577049255</t>
   </si>
   <si>
     <t xml:space="preserve">2.47814273834229</t>
@@ -2576,28 +2576,28 @@
     <t xml:space="preserve">2.51990914344788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50134634971619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52919054031372</t>
+    <t xml:space="preserve">2.50134611129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52919030189514</t>
   </si>
   <si>
     <t xml:space="preserve">2.56167554855347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56631636619568</t>
+    <t xml:space="preserve">2.5663161277771</t>
   </si>
   <si>
     <t xml:space="preserve">2.3017954826355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29715466499329</t>
+    <t xml:space="preserve">2.29715442657471</t>
   </si>
   <si>
     <t xml:space="preserve">2.29251408576965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27859163284302</t>
+    <t xml:space="preserve">2.2785918712616</t>
   </si>
   <si>
     <t xml:space="preserve">2.23218464851379</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">2.19969964027405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17185521125793</t>
+    <t xml:space="preserve">2.17185544967651</t>
   </si>
   <si>
     <t xml:space="preserve">2.26931023597717</t>
@@ -2618,13 +2618,13 @@
     <t xml:space="preserve">2.24146604537964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22754406929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19505882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12544798851013</t>
+    <t xml:space="preserve">2.22754383087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19505906105042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12544822692871</t>
   </si>
   <si>
     <t xml:space="preserve">2.01407098770142</t>
@@ -2639,13 +2639,13 @@
     <t xml:space="preserve">2.0744001865387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97230458259583</t>
+    <t xml:space="preserve">1.97230446338654</t>
   </si>
   <si>
     <t xml:space="preserve">1.96766364574432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94446015357971</t>
+    <t xml:space="preserve">1.944460272789</t>
   </si>
   <si>
     <t xml:space="preserve">1.87020885944366</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">1.81730461120605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79688537120819</t>
+    <t xml:space="preserve">1.79688549041748</t>
   </si>
   <si>
     <t xml:space="preserve">1.80059802532196</t>
@@ -2669,7 +2669,7 @@
     <t xml:space="preserve">1.88413095474243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03263378143311</t>
+    <t xml:space="preserve">2.03263401985168</t>
   </si>
   <si>
     <t xml:space="preserve">2.50598692893982</t>
@@ -2690,10 +2690,10 @@
     <t xml:space="preserve">2.77978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71945977210999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70553779602051</t>
+    <t xml:space="preserve">2.71946001052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70553755760193</t>
   </si>
   <si>
     <t xml:space="preserve">2.7241005897522</t>
@@ -2705,10 +2705,10 @@
     <t xml:space="preserve">2.64056777954102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68233442306519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76586699485779</t>
+    <t xml:space="preserve">2.68233418464661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76586723327637</t>
   </si>
   <si>
     <t xml:space="preserve">2.58023834228516</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">2.6127233505249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59880137443542</t>
+    <t xml:space="preserve">2.59880113601685</t>
   </si>
   <si>
     <t xml:space="preserve">2.62664556503296</t>
@@ -2738,10 +2738,10 @@
     <t xml:space="preserve">2.39925050735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27395129203796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32963991165161</t>
+    <t xml:space="preserve">2.27395105361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32963967323303</t>
   </si>
   <si>
     <t xml:space="preserve">2.3482027053833</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">2.35284328460693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39460945129395</t>
+    <t xml:space="preserve">2.39460968971252</t>
   </si>
   <si>
     <t xml:space="preserve">2.46886134147644</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">2.64520835876465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70089721679688</t>
+    <t xml:space="preserve">2.7008969783783</t>
   </si>
   <si>
     <t xml:space="preserve">2.71017861366272</t>
@@ -2783,16 +2783,16 @@
     <t xml:space="preserve">2.93757343292236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99790287017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09071707725525</t>
+    <t xml:space="preserve">2.9979031085968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09071731567383</t>
   </si>
   <si>
     <t xml:space="preserve">3.04895091056824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10463929176331</t>
+    <t xml:space="preserve">3.10463953018188</t>
   </si>
   <si>
     <t xml:space="preserve">3.11392092704773</t>
@@ -2801,19 +2801,19 @@
     <t xml:space="preserve">3.2392201423645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24386096000671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2160165309906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25314235687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29026794433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29954934120178</t>
+    <t xml:space="preserve">3.24386072158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21601629257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25314259529114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29026818275452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29954957962036</t>
   </si>
   <si>
     <t xml:space="preserve">3.31811237335205</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">3.61975908279419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49910020828247</t>
+    <t xml:space="preserve">3.49910044670105</t>
   </si>
   <si>
     <t xml:space="preserve">3.62904047966003</t>
@@ -2843,19 +2843,19 @@
     <t xml:space="preserve">3.41092658042908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34131598472595</t>
+    <t xml:space="preserve">3.34131574630737</t>
   </si>
   <si>
     <t xml:space="preserve">3.3273937702179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44805240631104</t>
+    <t xml:space="preserve">3.44805216789246</t>
   </si>
   <si>
     <t xml:space="preserve">3.38772320747375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41556763648987</t>
+    <t xml:space="preserve">3.41556739807129</t>
   </si>
   <si>
     <t xml:space="preserve">3.29490876197815</t>
@@ -2870,19 +2870,19 @@
     <t xml:space="preserve">3.13248372077942</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17889094352722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18353152275085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2856273651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37380075454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43413043022156</t>
+    <t xml:space="preserve">3.17889070510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18353176116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28562712669373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3738009929657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43413019180298</t>
   </si>
   <si>
     <t xml:space="preserve">3.47589659690857</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">3.50838160514832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63368082046509</t>
+    <t xml:space="preserve">3.63368105888367</t>
   </si>
   <si>
     <t xml:space="preserve">3.60583686828613</t>
@@ -2903,28 +2903,28 @@
     <t xml:space="preserve">3.54550743103027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69865083694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55478882789612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53622579574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44341158866882</t>
+    <t xml:space="preserve">3.69865107536316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55478858947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53622603416443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4434118270874</t>
   </si>
   <si>
     <t xml:space="preserve">3.52230405807495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54086685180664</t>
+    <t xml:space="preserve">3.54086661338806</t>
   </si>
   <si>
     <t xml:space="preserve">3.46197438240051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47125577926636</t>
+    <t xml:space="preserve">3.47125601768494</t>
   </si>
   <si>
     <t xml:space="preserve">3.50374102592468</t>
@@ -2936,16 +2936,16 @@
     <t xml:space="preserve">3.22993874549866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26706433296204</t>
+    <t xml:space="preserve">3.26706457138062</t>
   </si>
   <si>
     <t xml:space="preserve">3.33203434944153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39236378669739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37844181060791</t>
+    <t xml:space="preserve">3.39236354827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37844157218933</t>
   </si>
   <si>
     <t xml:space="preserve">3.30883097648621</t>
@@ -2966,13 +2966,13 @@
     <t xml:space="preserve">3.05823230743408</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13712430000305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11856126785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9654176235199</t>
+    <t xml:space="preserve">3.13712453842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11856150627136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96541786193848</t>
   </si>
   <si>
     <t xml:space="preserve">3.30419015884399</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">3.17425012588501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12784266471863</t>
+    <t xml:space="preserve">3.12784290313721</t>
   </si>
   <si>
     <t xml:space="preserve">3.19745373725891</t>
@@ -3002,16 +3002,16 @@
     <t xml:space="preserve">3.36451935768127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45269298553467</t>
+    <t xml:space="preserve">3.45269322395325</t>
   </si>
   <si>
     <t xml:space="preserve">3.42020797729492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42484903335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32275295257568</t>
+    <t xml:space="preserve">3.42484879493713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32275319099426</t>
   </si>
   <si>
     <t xml:space="preserve">3.33667516708374</t>
@@ -3020,13 +3020,13 @@
     <t xml:space="preserve">3.38308238983154</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36916041374207</t>
+    <t xml:space="preserve">3.36916017532349</t>
   </si>
   <si>
     <t xml:space="preserve">3.16496872901917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01646590232849</t>
+    <t xml:space="preserve">3.01646566390991</t>
   </si>
   <si>
     <t xml:space="preserve">3.1696093082428</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">3.06751370429993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02110648155212</t>
+    <t xml:space="preserve">3.0211067199707</t>
   </si>
   <si>
     <t xml:space="preserve">3.15568733215332</t>
@@ -3044,10 +3044,10 @@
     <t xml:space="preserve">3.14176511764526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12320232391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03966951370239</t>
+    <t xml:space="preserve">3.123202085495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03966927528381</t>
   </si>
   <si>
     <t xml:space="preserve">3.14640593528748</t>
@@ -3062,10 +3062,10 @@
     <t xml:space="preserve">2.58487915992737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7705078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86796283721924</t>
+    <t xml:space="preserve">2.77050757408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86796259880066</t>
   </si>
   <si>
     <t xml:space="preserve">2.94685482978821</t>
@@ -3074,7 +3074,7 @@
     <t xml:space="preserve">2.98398065567017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02574729919434</t>
+    <t xml:space="preserve">3.02574706077576</t>
   </si>
   <si>
     <t xml:space="preserve">2.97934007644653</t>
@@ -3083,16 +3083,16 @@
     <t xml:space="preserve">2.80299282073975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84475946426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92829203605652</t>
+    <t xml:space="preserve">2.84475922584534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9282922744751</t>
   </si>
   <si>
     <t xml:space="preserve">2.87260365486145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89116644859314</t>
+    <t xml:space="preserve">2.89116621017456</t>
   </si>
   <si>
     <t xml:space="preserve">3.03038787841797</t>
@@ -3101,16 +3101,16 @@
     <t xml:space="preserve">2.8169150352478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68697476387024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69625616073608</t>
+    <t xml:space="preserve">2.68697500228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69625639915466</t>
   </si>
   <si>
     <t xml:space="preserve">2.62200474739075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79835224151611</t>
+    <t xml:space="preserve">2.79835200309753</t>
   </si>
   <si>
     <t xml:space="preserve">2.91901063919067</t>
@@ -3122,7 +3122,7 @@
     <t xml:space="preserve">2.9050886631012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95613622665405</t>
+    <t xml:space="preserve">2.95613646507263</t>
   </si>
   <si>
     <t xml:space="preserve">2.80763363838196</t>
@@ -3140,31 +3140,31 @@
     <t xml:space="preserve">2.74266338348389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63128614425659</t>
+    <t xml:space="preserve">2.63128638267517</t>
   </si>
   <si>
     <t xml:space="preserve">2.49206471443176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53847193717957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54775309562683</t>
+    <t xml:space="preserve">2.53847169876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54775333404541</t>
   </si>
   <si>
     <t xml:space="preserve">2.48742413520813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44101691246033</t>
+    <t xml:space="preserve">2.44101715087891</t>
   </si>
   <si>
     <t xml:space="preserve">2.47350192070007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43637633323669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38996911048889</t>
+    <t xml:space="preserve">2.43637609481812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38996887207031</t>
   </si>
   <si>
     <t xml:space="preserve">2.3249990940094</t>
@@ -3176,19 +3176,19 @@
     <t xml:space="preserve">2.31107687950134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28323268890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28787302970886</t>
+    <t xml:space="preserve">2.28323245048523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28787326812744</t>
   </si>
   <si>
     <t xml:space="preserve">2.26002883911133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33428049087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33892130851746</t>
+    <t xml:space="preserve">2.33428072929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33892107009888</t>
   </si>
   <si>
     <t xml:space="preserve">2.30643606185913</t>
@@ -3218,13 +3218,13 @@
     <t xml:space="preserve">2.18113660812378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22290301322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18577742576599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11616659164429</t>
+    <t xml:space="preserve">2.22290325164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18577766418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11616683006287</t>
   </si>
   <si>
     <t xml:space="preserve">2.0976037979126</t>
@@ -3242,22 +3242,22 @@
     <t xml:space="preserve">2.04191517829895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02335238456726</t>
+    <t xml:space="preserve">2.02335262298584</t>
   </si>
   <si>
     <t xml:space="preserve">2.00014877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98158597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97694528102875</t>
+    <t xml:space="preserve">1.98158586025238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97694540023804</t>
   </si>
   <si>
     <t xml:space="preserve">1.99086737632751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99550831317902</t>
+    <t xml:space="preserve">1.99550807476044</t>
   </si>
   <si>
     <t xml:space="preserve">2.00478959083557</t>
@@ -3272,10 +3272,10 @@
     <t xml:space="preserve">2.05119657516479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0094301700592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02799320220947</t>
+    <t xml:space="preserve">2.00943040847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02799296379089</t>
   </si>
   <si>
     <t xml:space="preserve">1.95838224887848</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">1.93981945514679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91197514533997</t>
+    <t xml:space="preserve">1.91197526454926</t>
   </si>
   <si>
     <t xml:space="preserve">1.90269374847412</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">1.75419080257416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73562788963318</t>
+    <t xml:space="preserve">1.73562800884247</t>
   </si>
   <si>
     <t xml:space="preserve">1.82472968101501</t>
@@ -3314,16 +3314,16 @@
     <t xml:space="preserve">1.80431056022644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77646636962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79317283630371</t>
+    <t xml:space="preserve">1.77646625041962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.793172955513</t>
   </si>
   <si>
     <t xml:space="preserve">1.7950291633606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76904106140137</t>
+    <t xml:space="preserve">1.76904118061066</t>
   </si>
   <si>
     <t xml:space="preserve">1.75047838687897</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">1.81916093826294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287347316742</t>
+    <t xml:space="preserve">1.82287335395813</t>
   </si>
   <si>
     <t xml:space="preserve">2.01871156692505</t>
@@ -3368,22 +3368,22 @@
     <t xml:space="preserve">2.37604665756226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3853280544281</t>
+    <t xml:space="preserve">2.38532829284668</t>
   </si>
   <si>
     <t xml:space="preserve">2.3714063167572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60344195365906</t>
+    <t xml:space="preserve">2.60344219207764</t>
   </si>
   <si>
     <t xml:space="preserve">3.56407022476196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64296221733093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5779926776886</t>
+    <t xml:space="preserve">3.64296245574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57799243927002</t>
   </si>
   <si>
     <t xml:space="preserve">3.55942964553833</t>
@@ -3392,19 +3392,19 @@
     <t xml:space="preserve">3.82859110832214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90748310089111</t>
+    <t xml:space="preserve">3.90748333930969</t>
   </si>
   <si>
     <t xml:space="preserve">4.00029754638672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81466889381409</t>
+    <t xml:space="preserve">3.81466913223267</t>
   </si>
   <si>
     <t xml:space="preserve">3.48517823219299</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42948937416077</t>
+    <t xml:space="preserve">3.42948961257935</t>
   </si>
   <si>
     <t xml:space="preserve">3.45733380317688</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">3.35987877845764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58727407455444</t>
+    <t xml:space="preserve">3.58727383613586</t>
   </si>
   <si>
     <t xml:space="preserve">3.52694439888</t>
@@ -4197,6 +4197,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.82999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98999977111816</t>
   </si>
 </sst>
 </file>
@@ -69951,7 +69954,7 @@
     </row>
     <row r="2517">
       <c r="A2517" s="1" t="n">
-        <v>45982.6909953704</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2517" t="n">
         <v>90354</v>
@@ -69972,6 +69975,32 @@
         <v>1385</v>
       </c>
       <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>45985.6912962963</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>69294</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>8.05000019073486</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>7.82999992370605</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>7.96000003814697</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>7.98999977111816</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>1395</v>
+      </c>
+      <c r="H2518" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="1396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1397" uniqueCount="1397">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95473074913025</t>
+    <t xml:space="preserve">1.95473098754883</t>
   </si>
   <si>
     <t xml:space="preserve">FM.MI</t>
@@ -50,10 +50,10 @@
     <t xml:space="preserve">1.9096348285675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85586702823639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86453902721405</t>
+    <t xml:space="preserve">1.8558669090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86453926563263</t>
   </si>
   <si>
     <t xml:space="preserve">1.68415582180023</t>
@@ -62,28 +62,28 @@
     <t xml:space="preserve">1.76914405822754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74486172199249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69542992115021</t>
+    <t xml:space="preserve">1.74486184120178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69542980194092</t>
   </si>
   <si>
     <t xml:space="preserve">1.61824655532837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52285158634186</t>
+    <t xml:space="preserve">1.52285146713257</t>
   </si>
   <si>
     <t xml:space="preserve">1.47949004173279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34420263767242</t>
+    <t xml:space="preserve">1.34420251846313</t>
   </si>
   <si>
     <t xml:space="preserve">1.45434057712555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55233728885651</t>
+    <t xml:space="preserve">1.55233716964722</t>
   </si>
   <si>
     <t xml:space="preserve">1.48989689350128</t>
@@ -92,22 +92,22 @@
     <t xml:space="preserve">1.54366493225098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59569847583771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51331198215485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53325819969177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.499436378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43005812168121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40751028060913</t>
+    <t xml:space="preserve">1.595698595047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51331210136414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53325831890106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49943625926971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4300582408905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40751016139984</t>
   </si>
   <si>
     <t xml:space="preserve">1.38582956790924</t>
@@ -116,37 +116,37 @@
     <t xml:space="preserve">1.28349673748016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17682778835297</t>
+    <t xml:space="preserve">1.17682766914368</t>
   </si>
   <si>
     <t xml:space="preserve">1.24186980724335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2071807384491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23059594631195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43873059749603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39710342884064</t>
+    <t xml:space="preserve">1.20718061923981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23059582710266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43873047828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39710354804993</t>
   </si>
   <si>
     <t xml:space="preserve">1.50030362606049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48295915126801</t>
+    <t xml:space="preserve">1.48295903205872</t>
   </si>
   <si>
     <t xml:space="preserve">1.46561455726624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5211169719696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51678085327148</t>
+    <t xml:space="preserve">1.52111709117889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51678073406219</t>
   </si>
   <si>
     <t xml:space="preserve">1.4942330121994</t>
@@ -167,10 +167,10 @@
     <t xml:space="preserve">1.58702635765076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55754053592682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52805495262146</t>
+    <t xml:space="preserve">1.55754041671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52805471420288</t>
   </si>
   <si>
     <t xml:space="preserve">1.54279780387878</t>
@@ -182,19 +182,19 @@
     <t xml:space="preserve">1.55147004127502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61651206016541</t>
+    <t xml:space="preserve">1.61651194095612</t>
   </si>
   <si>
     <t xml:space="preserve">1.67374908924103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70843815803528</t>
+    <t xml:space="preserve">1.70843827724457</t>
   </si>
   <si>
     <t xml:space="preserve">1.67808520793915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65467011928558</t>
+    <t xml:space="preserve">1.65467000007629</t>
   </si>
   <si>
     <t xml:space="preserve">1.63298940658569</t>
@@ -206,16 +206,16 @@
     <t xml:space="preserve">1.53499269485474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49770188331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49683463573456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48122453689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41791689395905</t>
+    <t xml:space="preserve">1.49770200252533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49683451652527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48122441768646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41791701316833</t>
   </si>
   <si>
     <t xml:space="preserve">1.39970517158508</t>
@@ -227,37 +227,37 @@
     <t xml:space="preserve">1.39190018177032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46041107177734</t>
+    <t xml:space="preserve">1.46041119098663</t>
   </si>
   <si>
     <t xml:space="preserve">1.57228350639343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62952053546906</t>
+    <t xml:space="preserve">1.62952041625977</t>
   </si>
   <si>
     <t xml:space="preserve">1.60437095165253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60870707035065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62518441677094</t>
+    <t xml:space="preserve">1.60870695114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62518429756165</t>
   </si>
   <si>
     <t xml:space="preserve">1.65987348556519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58615899085999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55407178401947</t>
+    <t xml:space="preserve">1.58615911006927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55407166481018</t>
   </si>
   <si>
     <t xml:space="preserve">1.60090184211731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58876085281372</t>
+    <t xml:space="preserve">1.58876073360443</t>
   </si>
   <si>
     <t xml:space="preserve">1.49249851703644</t>
@@ -269,52 +269,52 @@
     <t xml:space="preserve">1.47775566577911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47428691387177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46908342838287</t>
+    <t xml:space="preserve">1.47428679466248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46908330917358</t>
   </si>
   <si>
     <t xml:space="preserve">1.56794726848602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53932881355286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53065657615662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54106318950653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56968176364899</t>
+    <t xml:space="preserve">1.53932893276215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53065645694733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54106330871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5696816444397</t>
   </si>
   <si>
     <t xml:space="preserve">1.5471339225769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55060267448425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56708014011383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57401788234711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51071012020111</t>
+    <t xml:space="preserve">1.55060279369354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56708025932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5740180015564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5107102394104</t>
   </si>
   <si>
     <t xml:space="preserve">1.59136247634888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56100940704346</t>
+    <t xml:space="preserve">1.56100952625275</t>
   </si>
   <si>
     <t xml:space="preserve">1.54453229904175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45000433921814</t>
+    <t xml:space="preserve">1.45000445842743</t>
   </si>
   <si>
     <t xml:space="preserve">1.38929855823517</t>
@@ -326,19 +326,19 @@
     <t xml:space="preserve">1.38756394386292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44740271568298</t>
+    <t xml:space="preserve">1.44740283489227</t>
   </si>
   <si>
     <t xml:space="preserve">1.49163126945496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4838262796402</t>
+    <t xml:space="preserve">1.48382616043091</t>
   </si>
   <si>
     <t xml:space="preserve">1.32338929176331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32945966720581</t>
+    <t xml:space="preserve">1.3294597864151</t>
   </si>
   <si>
     <t xml:space="preserve">1.3884311914444</t>
@@ -347,22 +347,22 @@
     <t xml:space="preserve">1.39016568660736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35981273651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33726501464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31124806404114</t>
+    <t xml:space="preserve">1.35981261730194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33726489543915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31124794483185</t>
   </si>
   <si>
     <t xml:space="preserve">1.30084121227264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30257570743561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3615471124649</t>
+    <t xml:space="preserve">1.30257558822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36154723167419</t>
   </si>
   <si>
     <t xml:space="preserve">1.37802445888519</t>
@@ -374,19 +374,19 @@
     <t xml:space="preserve">1.39623630046844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37715744972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4049084186554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39450180530548</t>
+    <t xml:space="preserve">1.377157330513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40490853786469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39450192451477</t>
   </si>
   <si>
     <t xml:space="preserve">1.4040412902832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39363467693329</t>
+    <t xml:space="preserve">1.393634557724</t>
   </si>
   <si>
     <t xml:space="preserve">1.42225313186646</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">1.35460937023163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34333539009094</t>
+    <t xml:space="preserve">1.34333550930023</t>
   </si>
   <si>
     <t xml:space="preserve">1.33119416236877</t>
@@ -422,25 +422,25 @@
     <t xml:space="preserve">1.30170857906342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30777907371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34767150878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34506976604462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33379590511322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37108659744263</t>
+    <t xml:space="preserve">1.3077791929245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34767162799835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34506988525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33379578590393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37108671665192</t>
   </si>
   <si>
     <t xml:space="preserve">1.35547661781311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34940600395203</t>
+    <t xml:space="preserve">1.34940588474274</t>
   </si>
   <si>
     <t xml:space="preserve">1.33813202381134</t>
@@ -455,25 +455,25 @@
     <t xml:space="preserve">1.40317416191101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39536905288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41097903251648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36501598358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38322782516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36761784553528</t>
+    <t xml:space="preserve">1.39536893367767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41097915172577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36501610279083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38322794437408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36761772632599</t>
   </si>
   <si>
     <t xml:space="preserve">1.38149344921112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39797079563141</t>
+    <t xml:space="preserve">1.39797067642212</t>
   </si>
   <si>
     <t xml:space="preserve">1.37455558776855</t>
@@ -482,16 +482,16 @@
     <t xml:space="preserve">1.41358077526093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42138600349426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41271364688873</t>
+    <t xml:space="preserve">1.42138588428497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41271352767944</t>
   </si>
   <si>
     <t xml:space="preserve">1.40924465656281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42572200298309</t>
+    <t xml:space="preserve">1.42572212219238</t>
   </si>
   <si>
     <t xml:space="preserve">1.35114049911499</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">1.33032703399658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32078742980957</t>
+    <t xml:space="preserve">1.32078754901886</t>
   </si>
   <si>
     <t xml:space="preserve">1.3190530538559</t>
@@ -524,10 +524,10 @@
     <t xml:space="preserve">1.3129825592041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17942929267883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26181614398956</t>
+    <t xml:space="preserve">1.17942941188812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26181602478027</t>
   </si>
   <si>
     <t xml:space="preserve">1.29216909408569</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">1.2175874710083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24880766868591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22886145114899</t>
+    <t xml:space="preserve">1.2488077878952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22886157035828</t>
   </si>
   <si>
     <t xml:space="preserve">1.18550002574921</t>
@@ -557,34 +557,34 @@
     <t xml:space="preserve">1.13086462020874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12305963039398</t>
+    <t xml:space="preserve">1.12305951118469</t>
   </si>
   <si>
     <t xml:space="preserve">1.13346636295319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11438727378845</t>
+    <t xml:space="preserve">1.11438739299774</t>
   </si>
   <si>
     <t xml:space="preserve">1.11612176895142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11525464057922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09791016578674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09270668029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07536220550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07276046276093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10398042201996</t>
+    <t xml:space="preserve">1.11525452136993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09791004657745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09270656108856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07536208629608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07276034355164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10398066043854</t>
   </si>
   <si>
     <t xml:space="preserve">1.1542797088623</t>
@@ -593,40 +593,40 @@
     <t xml:space="preserve">1.16295206546783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16208493709564</t>
+    <t xml:space="preserve">1.16208481788635</t>
   </si>
   <si>
     <t xml:space="preserve">1.17856216430664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18289840221405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20544612407684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23493194580078</t>
+    <t xml:space="preserve">1.18289828300476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20544624328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23493206501007</t>
   </si>
   <si>
     <t xml:space="preserve">1.24533867835999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21845471858978</t>
+    <t xml:space="preserve">1.21845459938049</t>
   </si>
   <si>
     <t xml:space="preserve">1.19937562942505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20111000537872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2279942035675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22192358970642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23666632175446</t>
+    <t xml:space="preserve">1.20111012458801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22799408435822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22192347049713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23666656017303</t>
   </si>
   <si>
     <t xml:space="preserve">1.26875388622284</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">1.38409507274628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39883816242218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38669669628143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35721111297607</t>
+    <t xml:space="preserve">1.39883804321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38669681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35721099376678</t>
   </si>
   <si>
     <t xml:space="preserve">1.34593713283539</t>
@@ -650,49 +650,49 @@
     <t xml:space="preserve">1.33292865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28870010375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25747990608215</t>
+    <t xml:space="preserve">1.28869986534119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25747978687286</t>
   </si>
   <si>
     <t xml:space="preserve">1.23319756984711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2444714307785</t>
+    <t xml:space="preserve">1.24447154998779</t>
   </si>
   <si>
     <t xml:space="preserve">1.22712695598602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25661265850067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2236579656601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2227908372879</t>
+    <t xml:space="preserve">1.25661277770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22365808486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22279071807861</t>
   </si>
   <si>
     <t xml:space="preserve">1.25314378738403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22625982761383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21325135231018</t>
+    <t xml:space="preserve">1.22625970840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21325147151947</t>
   </si>
   <si>
     <t xml:space="preserve">1.20891523361206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20457911491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21585285663605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21672022342682</t>
+    <t xml:space="preserve">1.20457899570465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21585297584534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21672010421753</t>
   </si>
   <si>
     <t xml:space="preserve">1.19070339202881</t>
@@ -707,37 +707,37 @@
     <t xml:space="preserve">1.191570520401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20284461975098</t>
+    <t xml:space="preserve">1.20284450054169</t>
   </si>
   <si>
     <t xml:space="preserve">1.19243776798248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23406457901001</t>
+    <t xml:space="preserve">1.2340646982193</t>
   </si>
   <si>
     <t xml:space="preserve">1.27742612361908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27222275733948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2982394695282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26355051994324</t>
+    <t xml:space="preserve">1.27222287654877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29823958873749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26355040073395</t>
   </si>
   <si>
     <t xml:space="preserve">1.24273705482483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23579919338226</t>
+    <t xml:space="preserve">1.23579907417297</t>
   </si>
   <si>
     <t xml:space="preserve">1.22018897533417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24794042110443</t>
+    <t xml:space="preserve">1.24794030189514</t>
   </si>
   <si>
     <t xml:space="preserve">1.24967479705811</t>
@@ -746,19 +746,19 @@
     <t xml:space="preserve">1.29043447971344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29303634166718</t>
+    <t xml:space="preserve">1.2930361032486</t>
   </si>
   <si>
     <t xml:space="preserve">1.31818580627441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30691194534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27309012413025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24013531208038</t>
+    <t xml:space="preserve">1.30691182613373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27308988571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24013519287109</t>
   </si>
   <si>
     <t xml:space="preserve">1.27916049957275</t>
@@ -767,25 +767,25 @@
     <t xml:space="preserve">1.2704883813858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26528489589691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28436386585236</t>
+    <t xml:space="preserve">1.26528477668762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28436398506165</t>
   </si>
   <si>
     <t xml:space="preserve">1.27482438087463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26441764831543</t>
+    <t xml:space="preserve">1.26441776752472</t>
   </si>
   <si>
     <t xml:space="preserve">1.28523111343384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2869656085968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33986639976501</t>
+    <t xml:space="preserve">1.28696548938751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3398665189743</t>
   </si>
   <si>
     <t xml:space="preserve">1.33899927139282</t>
@@ -797,22 +797,22 @@
     <t xml:space="preserve">1.57835412025452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51851546764374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54019606113434</t>
+    <t xml:space="preserve">1.51851534843445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54019594192505</t>
   </si>
   <si>
     <t xml:space="preserve">1.49856913089752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50724148750305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50203800201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47862303256989</t>
+    <t xml:space="preserve">1.50724136829376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50203812122345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4786229133606</t>
   </si>
   <si>
     <t xml:space="preserve">1.43352711200714</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">1.40577578544617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38496220111847</t>
+    <t xml:space="preserve">1.38496232032776</t>
   </si>
   <si>
     <t xml:space="preserve">1.47168505191803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48729526996613</t>
+    <t xml:space="preserve">1.48729515075684</t>
   </si>
   <si>
     <t xml:space="preserve">1.47602117061615</t>
@@ -836,13 +836,13 @@
     <t xml:space="preserve">1.45694220066071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4682160615921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45867669582367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45954394340515</t>
+    <t xml:space="preserve">1.46821618080139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45867657661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45954382419586</t>
   </si>
   <si>
     <t xml:space="preserve">1.45607495307922</t>
@@ -854,22 +854,22 @@
     <t xml:space="preserve">1.47341954708099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52892208099365</t>
+    <t xml:space="preserve">1.52892220020294</t>
   </si>
   <si>
     <t xml:space="preserve">1.50637412071228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57488512992859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58269023895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56187677383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53585994243622</t>
+    <t xml:space="preserve">1.57488524913788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58269035816193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56187665462494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53585982322693</t>
   </si>
   <si>
     <t xml:space="preserve">1.48642790317535</t>
@@ -878,19 +878,19 @@
     <t xml:space="preserve">1.49510014057159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51157748699188</t>
+    <t xml:space="preserve">1.51157760620117</t>
   </si>
   <si>
     <t xml:space="preserve">1.48902952671051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48035728931427</t>
+    <t xml:space="preserve">1.48035740852356</t>
   </si>
   <si>
     <t xml:space="preserve">1.48816251754761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51591360569</t>
+    <t xml:space="preserve">1.51591372489929</t>
   </si>
   <si>
     <t xml:space="preserve">1.56881463527679</t>
@@ -899,10 +899,10 @@
     <t xml:space="preserve">1.57054901123047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64686512947083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78648865222931</t>
+    <t xml:space="preserve">1.64686501026154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78648853302002</t>
   </si>
   <si>
     <t xml:space="preserve">1.7604718208313</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">2.15245890617371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99982666969299</t>
+    <t xml:space="preserve">1.9998265504837</t>
   </si>
   <si>
     <t xml:space="preserve">2.05879807472229</t>
@@ -929,37 +929,37 @@
     <t xml:space="preserve">2.00329566001892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95126187801361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05186033248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01543641090393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98074769973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90443181991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90790045261383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91657280921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90616583824158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84892904758453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87321138381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83158445358276</t>
+    <t xml:space="preserve">1.9512619972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05186009407043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01543664932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98074758052826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90443193912506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90790057182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91657269001007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90616595745087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84892892837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87321150302887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83158457279205</t>
   </si>
   <si>
     <t xml:space="preserve">1.84719467163086</t>
@@ -968,25 +968,25 @@
     <t xml:space="preserve">1.93218290805817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93738627433777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9252450466156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94258987903595</t>
+    <t xml:space="preserve">1.93738615512848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92524492740631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94258952140808</t>
   </si>
   <si>
     <t xml:space="preserve">1.97727859020233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0206401348114</t>
+    <t xml:space="preserve">2.02063989639282</t>
   </si>
   <si>
     <t xml:space="preserve">2.06920480728149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01196789741516</t>
+    <t xml:space="preserve">2.011967420578</t>
   </si>
   <si>
     <t xml:space="preserve">2.03971886634827</t>
@@ -995,10 +995,10 @@
     <t xml:space="preserve">2.01370239257812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99462330341339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94432425498962</t>
+    <t xml:space="preserve">1.99462342262268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94432413578033</t>
   </si>
   <si>
     <t xml:space="preserve">1.90269720554352</t>
@@ -1007,31 +1007,31 @@
     <t xml:space="preserve">1.82117760181427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91310381889343</t>
+    <t xml:space="preserve">1.91310393810272</t>
   </si>
   <si>
     <t xml:space="preserve">1.72144663333893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67114734649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69976603984833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68762457370758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67895245552063</t>
+    <t xml:space="preserve">1.67114746570587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69976592063904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68762469291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67895257472992</t>
   </si>
   <si>
     <t xml:space="preserve">1.63992714881897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64773213863373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62865328788757</t>
+    <t xml:space="preserve">1.64773225784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62865316867828</t>
   </si>
   <si>
     <t xml:space="preserve">1.62691879272461</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">1.60350358486176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59656572341919</t>
+    <t xml:space="preserve">1.59656584262848</t>
   </si>
   <si>
     <t xml:space="preserve">1.63905990123749</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">1.6485995054245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66507685184479</t>
+    <t xml:space="preserve">1.6650767326355</t>
   </si>
   <si>
     <t xml:space="preserve">1.6910936832428</t>
@@ -1070,19 +1070,19 @@
     <t xml:space="preserve">1.66681122779846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68155407905579</t>
+    <t xml:space="preserve">1.68155419826508</t>
   </si>
   <si>
     <t xml:space="preserve">1.68935918807983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67721807956696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63385665416718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62171530723572</t>
+    <t xml:space="preserve">1.67721796035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63385653495789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62171542644501</t>
   </si>
   <si>
     <t xml:space="preserve">1.65727174282074</t>
@@ -1097,28 +1097,28 @@
     <t xml:space="preserve">1.71711051464081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70670366287231</t>
+    <t xml:space="preserve">1.7067037820816</t>
   </si>
   <si>
     <t xml:space="preserve">1.72578275203705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72751700878143</t>
+    <t xml:space="preserve">1.72751724720001</t>
   </si>
   <si>
     <t xml:space="preserve">1.71190702915192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74312734603882</t>
+    <t xml:space="preserve">1.74312722682953</t>
   </si>
   <si>
     <t xml:space="preserve">1.77781629562378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77348029613495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80383312702179</t>
+    <t xml:space="preserve">1.77348017692566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80383324623108</t>
   </si>
   <si>
     <t xml:space="preserve">1.93391740322113</t>
@@ -1127,31 +1127,31 @@
     <t xml:space="preserve">1.88188374042511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95559811592102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88621973991394</t>
+    <t xml:space="preserve">1.95559823513031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88621962070465</t>
   </si>
   <si>
     <t xml:space="preserve">1.81684160232544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89489197731018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80816924571991</t>
+    <t xml:space="preserve">1.89489221572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8081693649292</t>
   </si>
   <si>
     <t xml:space="preserve">1.82984983921051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85153067111969</t>
+    <t xml:space="preserve">1.85153090953827</t>
   </si>
   <si>
     <t xml:space="preserve">1.78215253353119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81250536441803</t>
+    <t xml:space="preserve">1.81250548362732</t>
   </si>
   <si>
     <t xml:space="preserve">1.79082489013672</t>
@@ -1166,13 +1166,13 @@
     <t xml:space="preserve">1.96860635280609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89922845363617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89055609703064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8775475025177</t>
+    <t xml:space="preserve">1.89922821521759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89055597782135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87754738330841</t>
   </si>
   <si>
     <t xml:space="preserve">1.83418619632721</t>
@@ -1184,25 +1184,25 @@
     <t xml:space="preserve">1.82551395893097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83852207660675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86020290851593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9729425907135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98161482810974</t>
+    <t xml:space="preserve">1.83852219581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86020302772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97294282913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98161494731903</t>
   </si>
   <si>
     <t xml:space="preserve">1.92958116531372</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98595082759857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04665684700012</t>
+    <t xml:space="preserve">1.98595094680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0466570854187</t>
   </si>
   <si>
     <t xml:space="preserve">2.03364849090576</t>
@@ -1211,31 +1211,31 @@
     <t xml:space="preserve">2.042320728302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.072674036026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08134603500366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11169862747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15072441101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05532932281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1854133605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33717823028564</t>
+    <t xml:space="preserve">2.07267379760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08134627342224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1116988658905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15072417259216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05532884597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18541312217712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33717799186707</t>
   </si>
   <si>
     <t xml:space="preserve">2.3024890422821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2808084487915</t>
+    <t xml:space="preserve">2.28080821037292</t>
   </si>
   <si>
     <t xml:space="preserve">2.21143007278442</t>
@@ -1244,43 +1244,43 @@
     <t xml:space="preserve">2.30682516098022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28514456748962</t>
+    <t xml:space="preserve">2.28514432907104</t>
   </si>
   <si>
     <t xml:space="preserve">2.44991779327393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48894286155701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59301018714905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38921213150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49761533737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57566595077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62769961357117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71442222595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76645565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83583378791809</t>
+    <t xml:space="preserve">2.48894309997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59300994873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38921189308167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49761557579041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57566571235657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62769937515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71442198753357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76645588874817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83583402633667</t>
   </si>
   <si>
     <t xml:space="preserve">2.91388440132141</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92255663871765</t>
+    <t xml:space="preserve">2.92255640029907</t>
   </si>
   <si>
     <t xml:space="preserve">2.93122911453247</t>
@@ -1298,13 +1298,13 @@
     <t xml:space="preserve">3.23909473419189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25210285186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21741414070129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25643920898438</t>
+    <t xml:space="preserve">3.25210309028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21741390228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25643944740295</t>
   </si>
   <si>
     <t xml:space="preserve">3.36050653457642</t>
@@ -1319,10 +1319,10 @@
     <t xml:space="preserve">3.26511168479919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22175002098083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33882594108582</t>
+    <t xml:space="preserve">3.22175025939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33882570266724</t>
   </si>
   <si>
     <t xml:space="preserve">3.27811980247498</t>
@@ -1331,16 +1331,16 @@
     <t xml:space="preserve">3.34749817848206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50793528556824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48625469207764</t>
+    <t xml:space="preserve">3.50793552398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48625445365906</t>
   </si>
   <si>
     <t xml:space="preserve">3.55563259124756</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51227164268494</t>
+    <t xml:space="preserve">3.51227140426636</t>
   </si>
   <si>
     <t xml:space="preserve">3.62934684753418</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">3.73341417312622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80712842941284</t>
+    <t xml:space="preserve">3.80712866783142</t>
   </si>
   <si>
     <t xml:space="preserve">3.90686011314392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07596874237061</t>
+    <t xml:space="preserve">4.07596921920776</t>
   </si>
   <si>
     <t xml:space="preserve">4.0456166267395</t>
@@ -1370,16 +1370,16 @@
     <t xml:space="preserve">3.86783480644226</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0412802696228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.945885181427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97190165519714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71173405647278</t>
+    <t xml:space="preserve">4.04127979278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94588565826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97190189361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7117338180542</t>
   </si>
   <si>
     <t xml:space="preserve">3.9198682308197</t>
@@ -1391,19 +1391,19 @@
     <t xml:space="preserve">4.24941492080688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25375127792358</t>
+    <t xml:space="preserve">4.25375080108643</t>
   </si>
   <si>
     <t xml:space="preserve">4.28410387039185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62232303619385</t>
+    <t xml:space="preserve">4.62232255935669</t>
   </si>
   <si>
     <t xml:space="preserve">4.57896137237549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74373435974121</t>
+    <t xml:space="preserve">4.74373388290405</t>
   </si>
   <si>
     <t xml:space="preserve">4.75240707397461</t>
@@ -1415,19 +1415,19 @@
     <t xml:space="preserve">4.98655796051025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95186901092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87381887435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31879329681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80444002151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97788572311401</t>
+    <t xml:space="preserve">4.95186948776245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87381839752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31879281997681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80444049835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97788619995117</t>
   </si>
   <si>
     <t xml:space="preserve">5.01257514953613</t>
@@ -1436,22 +1436,22 @@
     <t xml:space="preserve">5.03859186172485</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91718006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82178449630737</t>
+    <t xml:space="preserve">4.91717958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82178497314453</t>
   </si>
   <si>
     <t xml:space="preserve">4.85647392272949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89116334915161</t>
+    <t xml:space="preserve">4.89116287231445</t>
   </si>
   <si>
     <t xml:space="preserve">4.83045721054077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76107883453369</t>
+    <t xml:space="preserve">4.76107835769653</t>
   </si>
   <si>
     <t xml:space="preserve">4.54427194595337</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">4.60497808456421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58763360977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64833974838257</t>
+    <t xml:space="preserve">4.58763313293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64833927154541</t>
   </si>
   <si>
     <t xml:space="preserve">4.61365032196045</t>
@@ -1478,13 +1478,13 @@
     <t xml:space="preserve">4.47489356994629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40551614761353</t>
+    <t xml:space="preserve">4.40551567077637</t>
   </si>
   <si>
     <t xml:space="preserve">4.18437242507935</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18870878219604</t>
+    <t xml:space="preserve">4.1887092590332</t>
   </si>
   <si>
     <t xml:space="preserve">4.24074268341064</t>
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">4.084641456604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92854118347168</t>
+    <t xml:space="preserve">3.92854022979736</t>
   </si>
   <si>
     <t xml:space="preserve">3.91553211212158</t>
@@ -1502,58 +1502,58 @@
     <t xml:space="preserve">3.85916233062744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78111219406128</t>
+    <t xml:space="preserve">3.7811119556427</t>
   </si>
   <si>
     <t xml:space="preserve">4.14101123809814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62501072883606</t>
+    <t xml:space="preserve">3.62501096725464</t>
   </si>
   <si>
     <t xml:space="preserve">3.31280899047852</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28679203987122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14369988441467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00927972793579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09166598320007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03529620170593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04830455780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07865762710571</t>
+    <t xml:space="preserve">3.28679227828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14369964599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00927925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09166622161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03529644012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04830479621887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07865786552429</t>
   </si>
   <si>
     <t xml:space="preserve">2.96158170700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89653992652893</t>
+    <t xml:space="preserve">2.89653968811035</t>
   </si>
   <si>
     <t xml:space="preserve">2.90521216392517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02662396430969</t>
+    <t xml:space="preserve">3.02662420272827</t>
   </si>
   <si>
     <t xml:space="preserve">2.75344729423523</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80548071861267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88786768913269</t>
+    <t xml:space="preserve">2.80548095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88786745071411</t>
   </si>
   <si>
     <t xml:space="preserve">3.04396843910217</t>
@@ -1562,37 +1562,37 @@
     <t xml:space="preserve">3.26077556610107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24343061447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19139695167542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42554879188538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43855667114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39519572257996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20440578460693</t>
+    <t xml:space="preserve">3.24343085289001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19139719009399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4255485534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43855714797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39519596099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20440554618835</t>
   </si>
   <si>
     <t xml:space="preserve">3.06998538970947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86618709564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93990111351013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88353157043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97459053993225</t>
+    <t xml:space="preserve">2.86618685722351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93990135192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88353133201599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97459030151367</t>
   </si>
   <si>
     <t xml:space="preserve">3.02228784561157</t>
@@ -1601,31 +1601,31 @@
     <t xml:space="preserve">3.3821873664856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32148146629333</t>
+    <t xml:space="preserve">3.32148122787476</t>
   </si>
   <si>
     <t xml:space="preserve">3.15670824050903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11768293380737</t>
+    <t xml:space="preserve">3.11768269538879</t>
   </si>
   <si>
     <t xml:space="preserve">3.08732986450195</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06564903259277</t>
+    <t xml:space="preserve">3.06564927101135</t>
   </si>
   <si>
     <t xml:space="preserve">2.81848931312561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68840527534485</t>
+    <t xml:space="preserve">2.68840503692627</t>
   </si>
   <si>
     <t xml:space="preserve">2.73176670074463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63203549385071</t>
+    <t xml:space="preserve">2.63203573226929</t>
   </si>
   <si>
     <t xml:space="preserve">2.98759865760803</t>
@@ -1634,22 +1634,22 @@
     <t xml:space="preserve">3.17405271530151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3041365146637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3084728717804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17838859558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10467457771301</t>
+    <t xml:space="preserve">3.30413675308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30847311019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17838883399963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10467433929443</t>
   </si>
   <si>
     <t xml:space="preserve">3.16104435920715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33015370368958</t>
+    <t xml:space="preserve">3.330153465271</t>
   </si>
   <si>
     <t xml:space="preserve">3.46023774147034</t>
@@ -1658,16 +1658,16 @@
     <t xml:space="preserve">3.5903217792511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8851797580719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90252375602722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85482621192932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11499500274658</t>
+    <t xml:space="preserve">3.88517904281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9025239944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8548264503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11499452590942</t>
   </si>
   <si>
     <t xml:space="preserve">4.27543163299561</t>
@@ -1676,25 +1676,25 @@
     <t xml:space="preserve">4.10198593139648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.145348072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13233947753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95889353752136</t>
+    <t xml:space="preserve">4.14534759521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1323390007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95889377593994</t>
   </si>
   <si>
     <t xml:space="preserve">3.82447338104248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9675657749176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94154906272888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9979190826416</t>
+    <t xml:space="preserve">3.96756529808044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9415488243103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99791884422302</t>
   </si>
   <si>
     <t xml:space="preserve">4.00659132003784</t>
@@ -1709,46 +1709,46 @@
     <t xml:space="preserve">4.01526355743408</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09331369400024</t>
+    <t xml:space="preserve">4.0933141708374</t>
   </si>
   <si>
     <t xml:space="preserve">4.03260803222656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98924660682678</t>
+    <t xml:space="preserve">3.98924684524536</t>
   </si>
   <si>
     <t xml:space="preserve">3.9242045879364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8288094997406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75943112373352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74642276763916</t>
+    <t xml:space="preserve">3.82880926132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75943160057068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74642300605774</t>
   </si>
   <si>
     <t xml:space="preserve">3.56864094734192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77677583694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24507904052734</t>
+    <t xml:space="preserve">3.77677607536316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24507856369019</t>
   </si>
   <si>
     <t xml:space="preserve">4.17136430740356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08897733688354</t>
+    <t xml:space="preserve">4.0889778137207</t>
   </si>
   <si>
     <t xml:space="preserve">4.06729698181152</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16269207000732</t>
+    <t xml:space="preserve">4.16269254684448</t>
   </si>
   <si>
     <t xml:space="preserve">4.21906185150146</t>
@@ -1757,10 +1757,10 @@
     <t xml:space="preserve">4.2320704460144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20171689987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68302822113037</t>
+    <t xml:space="preserve">4.20171737670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68302869796753</t>
   </si>
   <si>
     <t xml:space="preserve">4.88249111175537</t>
@@ -1769,13 +1769,13 @@
     <t xml:space="preserve">4.76975107192993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72638940811157</t>
+    <t xml:space="preserve">4.72638988494873</t>
   </si>
   <si>
     <t xml:space="preserve">4.63966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55294418334961</t>
+    <t xml:space="preserve">4.55294466018677</t>
   </si>
   <si>
     <t xml:space="preserve">4.44887733459473</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">4.39684343338013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91119623184204</t>
+    <t xml:space="preserve">3.91119647026062</t>
   </si>
   <si>
     <t xml:space="preserve">4.04995250701904</t>
@@ -1799,22 +1799,22 @@
     <t xml:space="preserve">4.01130485534668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91760301589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2254786491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00684213638306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8328263759613</t>
+    <t xml:space="preserve">3.91760349273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22547912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00684261322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83282613754272</t>
   </si>
   <si>
     <t xml:space="preserve">3.85513591766357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85959768295288</t>
+    <t xml:space="preserve">3.85959792137146</t>
   </si>
   <si>
     <t xml:space="preserve">3.93098950386047</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">4.03807640075684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95776104927063</t>
+    <t xml:space="preserve">3.95776081085205</t>
   </si>
   <si>
     <t xml:space="preserve">3.79266834259033</t>
@@ -1856,16 +1856,16 @@
     <t xml:space="preserve">3.67219519615173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59634208679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5874183177948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64096164703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64988565444946</t>
+    <t xml:space="preserve">3.59634232521057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58741807937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64096140861511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64988589286804</t>
   </si>
   <si>
     <t xml:space="preserve">3.5115647315979</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">3.41786336898804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44909739494324</t>
+    <t xml:space="preserve">3.44909715652466</t>
   </si>
   <si>
     <t xml:space="preserve">3.4223256111145</t>
@@ -1889,7 +1889,7 @@
     <t xml:space="preserve">3.47140717506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50710272789001</t>
+    <t xml:space="preserve">3.50710296630859</t>
   </si>
   <si>
     <t xml:space="preserve">3.41340160369873</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">3.36878204345703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3464720249176</t>
+    <t xml:space="preserve">3.34647226333618</t>
   </si>
   <si>
     <t xml:space="preserve">3.31523823738098</t>
@@ -1910,16 +1910,16 @@
     <t xml:space="preserve">3.32862424850464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36432003974915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39555382728577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35539627075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31077647209167</t>
+    <t xml:space="preserve">3.36432027816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39555358886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35539603233337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31077671051025</t>
   </si>
   <si>
     <t xml:space="preserve">3.27954268455505</t>
@@ -1931,7 +1931,7 @@
     <t xml:space="preserve">3.38216781616211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40001559257507</t>
+    <t xml:space="preserve">3.40001583099365</t>
   </si>
   <si>
     <t xml:space="preserve">3.30631422996521</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">3.33308625221252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35093402862549</t>
+    <t xml:space="preserve">3.35093426704407</t>
   </si>
   <si>
     <t xml:space="preserve">3.52941250801086</t>
@@ -1958,16 +1958,16 @@
     <t xml:space="preserve">3.8105161190033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80605435371399</t>
+    <t xml:space="preserve">3.80605459213257</t>
   </si>
   <si>
     <t xml:space="preserve">3.76589632034302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60080409049988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55618453025818</t>
+    <t xml:space="preserve">3.6008038520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5561842918396</t>
   </si>
   <si>
     <t xml:space="preserve">3.4669451713562</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">3.70789122581482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67665719985962</t>
+    <t xml:space="preserve">3.6766574382782</t>
   </si>
   <si>
     <t xml:space="preserve">3.73912501335144</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">3.66773366928101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69896721839905</t>
+    <t xml:space="preserve">3.69896745681763</t>
   </si>
   <si>
     <t xml:space="preserve">3.7212769985199</t>
@@ -2018,13 +2018,13 @@
     <t xml:space="preserve">3.56957030296326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96668529510498</t>
+    <t xml:space="preserve">3.96668553352356</t>
   </si>
   <si>
     <t xml:space="preserve">3.73466277122498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69450521469116</t>
+    <t xml:space="preserve">3.69450497627258</t>
   </si>
   <si>
     <t xml:space="preserve">3.70342922210693</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">3.56510829925537</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93991327285767</t>
+    <t xml:space="preserve">3.93991351127625</t>
   </si>
   <si>
     <t xml:space="preserve">4.06038618087769</t>
@@ -2051,25 +2051,25 @@
     <t xml:space="preserve">3.91314172744751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98899435997009</t>
+    <t xml:space="preserve">3.98899459838867</t>
   </si>
   <si>
     <t xml:space="preserve">3.98007082939148</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12731599807739</t>
+    <t xml:space="preserve">4.12731552124023</t>
   </si>
   <si>
     <t xml:space="preserve">4.05146217346191</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09161949157715</t>
+    <t xml:space="preserve">4.09161996841431</t>
   </si>
   <si>
     <t xml:space="preserve">4.03361415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92652726173401</t>
+    <t xml:space="preserve">3.92652702331543</t>
   </si>
   <si>
     <t xml:space="preserve">3.90867972373962</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">3.90421748161316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04253911972046</t>
+    <t xml:space="preserve">4.0425386428833</t>
   </si>
   <si>
     <t xml:space="preserve">3.93545126914978</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">4.07823419570923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19424438476562</t>
+    <t xml:space="preserve">4.19424486160278</t>
   </si>
   <si>
     <t xml:space="preserve">4.00238037109375</t>
@@ -2099,7 +2099,7 @@
     <t xml:space="preserve">4.1763973236084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08715772628784</t>
+    <t xml:space="preserve">4.087158203125</t>
   </si>
   <si>
     <t xml:space="preserve">4.21655464172363</t>
@@ -2108,10 +2108,10 @@
     <t xml:space="preserve">4.46196269989014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53335475921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64044141769409</t>
+    <t xml:space="preserve">4.53335428237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64044094085693</t>
   </si>
   <si>
     <t xml:space="preserve">4.58689785003662</t>
@@ -2123,25 +2123,25 @@
     <t xml:space="preserve">4.7564525604248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78322458267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68506050109863</t>
+    <t xml:space="preserve">4.78322410583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68506097793579</t>
   </si>
   <si>
     <t xml:space="preserve">4.83676767349243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81891965866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90815925598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00632238388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89923477172852</t>
+    <t xml:space="preserve">4.81892013549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90815877914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00632286071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89923524856567</t>
   </si>
   <si>
     <t xml:space="preserve">4.85461568832397</t>
@@ -2171,19 +2171,19 @@
     <t xml:space="preserve">4.82784414291382</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80999612808228</t>
+    <t xml:space="preserve">4.80999565124512</t>
   </si>
   <si>
     <t xml:space="preserve">4.94385480880737</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0687894821167</t>
+    <t xml:space="preserve">5.06878995895386</t>
   </si>
   <si>
     <t xml:space="preserve">4.99739837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23834466934204</t>
+    <t xml:space="preserve">5.23834419250488</t>
   </si>
   <si>
     <t xml:space="preserve">5.45251893997192</t>
@@ -2201,10 +2201,10 @@
     <t xml:space="preserve">5.15802907943726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88138723373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70290899276733</t>
+    <t xml:space="preserve">4.88138675689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70290851593018</t>
   </si>
   <si>
     <t xml:space="preserve">4.71183300018311</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">4.63151741027832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67613697052002</t>
+    <t xml:space="preserve">4.67613649368286</t>
   </si>
   <si>
     <t xml:space="preserve">4.56012630462646</t>
@@ -2231,13 +2231,13 @@
     <t xml:space="preserve">4.02022886276245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98453307151794</t>
+    <t xml:space="preserve">3.98453330993652</t>
   </si>
   <si>
     <t xml:space="preserve">3.94883728027344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80159282684326</t>
+    <t xml:space="preserve">3.80159258842468</t>
   </si>
   <si>
     <t xml:space="preserve">3.12783622741699</t>
@@ -2252,25 +2252,25 @@
     <t xml:space="preserve">2.72625946998596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.757493019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44961738586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45854187011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14174222946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9989595413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10604643821716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2577531337738</t>
+    <t xml:space="preserve">2.75749278068542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44961762428284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45854163169861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14174199104309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99895942211151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10604619979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25775337219238</t>
   </si>
   <si>
     <t xml:space="preserve">2.34699273109436</t>
@@ -2285,13 +2285,13 @@
     <t xml:space="preserve">2.40053629875183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48085117340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45407962799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46300339698792</t>
+    <t xml:space="preserve">2.48085141181946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45407938957214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46300363540649</t>
   </si>
   <si>
     <t xml:space="preserve">2.56116652488708</t>
@@ -2300,13 +2300,13 @@
     <t xml:space="preserve">2.73964524269104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23938488960266</t>
+    <t xml:space="preserve">3.23938512802124</t>
   </si>
   <si>
     <t xml:space="preserve">3.20368933677673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10998821258545</t>
+    <t xml:space="preserve">3.10998797416687</t>
   </si>
   <si>
     <t xml:space="preserve">2.91812372207642</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">2.99843907356262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93597149848938</t>
+    <t xml:space="preserve">2.9359712600708</t>
   </si>
   <si>
     <t xml:space="preserve">2.94489550590515</t>
@@ -2330,13 +2330,13 @@
     <t xml:space="preserve">2.97612929344177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85565614700317</t>
+    <t xml:space="preserve">2.85565638542175</t>
   </si>
   <si>
     <t xml:space="preserve">2.98059105873108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00290107727051</t>
+    <t xml:space="preserve">3.00290083885193</t>
   </si>
   <si>
     <t xml:space="preserve">3.13229775428772</t>
@@ -4200,6 +4200,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.98999977111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86999988555908</t>
   </si>
 </sst>
 </file>
@@ -69980,7 +69983,7 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>45985.6912962963</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2518" t="n">
         <v>69294</v>
@@ -70001,6 +70004,32 @@
         <v>1395</v>
       </c>
       <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.6910763889</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>116979</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>8.05000019073486</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>8.05000019073486</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>7.86999988555908</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>1396</v>
+      </c>
+      <c r="H2519" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95473074913025</t>
+    <t xml:space="preserve">1.95473062992096</t>
   </si>
   <si>
     <t xml:space="preserve">FM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95993387699127</t>
+    <t xml:space="preserve">1.95993399620056</t>
   </si>
   <si>
     <t xml:space="preserve">1.9096348285675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85586678981781</t>
+    <t xml:space="preserve">1.8558669090271</t>
   </si>
   <si>
     <t xml:space="preserve">1.86453938484192</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">1.76914405822754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74486184120178</t>
+    <t xml:space="preserve">1.74486172199249</t>
   </si>
   <si>
     <t xml:space="preserve">1.69542980194092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61824655532837</t>
+    <t xml:space="preserve">1.61824667453766</t>
   </si>
   <si>
     <t xml:space="preserve">1.52285146713257</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">1.23059582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43873047828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39710330963135</t>
+    <t xml:space="preserve">1.43873059749603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39710342884064</t>
   </si>
   <si>
     <t xml:space="preserve">1.50030362606049</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">1.48295903205872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46561443805695</t>
+    <t xml:space="preserve">1.46561455726624</t>
   </si>
   <si>
     <t xml:space="preserve">1.5211169719696</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">1.51678085327148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4942330121994</t>
+    <t xml:space="preserve">1.49423289299011</t>
   </si>
   <si>
     <t xml:space="preserve">1.47688841819763</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">1.47515404224396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5098432302475</t>
+    <t xml:space="preserve">1.50984311103821</t>
   </si>
   <si>
     <t xml:space="preserve">1.56014227867126</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">1.51244461536407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55147004127502</t>
+    <t xml:space="preserve">1.55146992206573</t>
   </si>
   <si>
     <t xml:space="preserve">1.61651194095612</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">1.67374897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70843827724457</t>
+    <t xml:space="preserve">1.70843815803528</t>
   </si>
   <si>
     <t xml:space="preserve">1.67808520793915</t>
@@ -215,19 +215,19 @@
     <t xml:space="preserve">1.48122453689575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41791701316833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39970517158508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35200762748718</t>
+    <t xml:space="preserve">1.41791689395905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39970505237579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35200774669647</t>
   </si>
   <si>
     <t xml:space="preserve">1.39190006256104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46041107177734</t>
+    <t xml:space="preserve">1.46041119098663</t>
   </si>
   <si>
     <t xml:space="preserve">1.57228338718414</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">1.58876073360443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49249851703644</t>
+    <t xml:space="preserve">1.49249839782715</t>
   </si>
   <si>
     <t xml:space="preserve">1.4578093290329</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">1.55060267448425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56708014011383</t>
+    <t xml:space="preserve">1.56708002090454</t>
   </si>
   <si>
     <t xml:space="preserve">1.5740180015564</t>
@@ -317,10 +317,10 @@
     <t xml:space="preserve">1.45000445842743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38929843902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40057229995728</t>
+    <t xml:space="preserve">1.38929855823517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40057241916656</t>
   </si>
   <si>
     <t xml:space="preserve">1.3875640630722</t>
@@ -332,19 +332,19 @@
     <t xml:space="preserve">1.49163138866425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48382616043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32338929176331</t>
+    <t xml:space="preserve">1.4838262796402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32338917255402</t>
   </si>
   <si>
     <t xml:space="preserve">1.3294597864151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38843131065369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39016580581665</t>
+    <t xml:space="preserve">1.3884311914444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39016568660736</t>
   </si>
   <si>
     <t xml:space="preserve">1.35981273651123</t>
@@ -359,22 +359,22 @@
     <t xml:space="preserve">1.30084121227264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30257558822632</t>
+    <t xml:space="preserve">1.30257570743561</t>
   </si>
   <si>
     <t xml:space="preserve">1.36154723167419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37802457809448</t>
+    <t xml:space="preserve">1.37802445888519</t>
   </si>
   <si>
     <t xml:space="preserve">1.3823606967926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39623630046844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.377157330513</t>
+    <t xml:space="preserve">1.39623618125916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37715744972229</t>
   </si>
   <si>
     <t xml:space="preserve">1.40490865707397</t>
@@ -389,13 +389,13 @@
     <t xml:space="preserve">1.393634557724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42225301265717</t>
+    <t xml:space="preserve">1.42225313186646</t>
   </si>
   <si>
     <t xml:space="preserve">1.42832362651825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37889170646667</t>
+    <t xml:space="preserve">1.37889182567596</t>
   </si>
   <si>
     <t xml:space="preserve">1.38062620162964</t>
@@ -404,10 +404,10 @@
     <t xml:space="preserve">1.36588335037231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35634386539459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35460948944092</t>
+    <t xml:space="preserve">1.3563437461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35460937023163</t>
   </si>
   <si>
     <t xml:space="preserve">1.34333550930023</t>
@@ -419,28 +419,28 @@
     <t xml:space="preserve">1.32685804367065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30170857906342</t>
+    <t xml:space="preserve">1.30170845985413</t>
   </si>
   <si>
     <t xml:space="preserve">1.30777907371521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34767150878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3450700044632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33379578590393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37108659744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35547649860382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34940600395203</t>
+    <t xml:space="preserve">1.34767162799835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34506988525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33379590511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37108671665192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35547661781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34940612316132</t>
   </si>
   <si>
     <t xml:space="preserve">1.33813202381134</t>
@@ -449,13 +449,13 @@
     <t xml:space="preserve">1.34853875637054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41704964637756</t>
+    <t xml:space="preserve">1.41704976558685</t>
   </si>
   <si>
     <t xml:space="preserve">1.40317404270172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39536893367767</t>
+    <t xml:space="preserve">1.39536905288696</t>
   </si>
   <si>
     <t xml:space="preserve">1.41097915172577</t>
@@ -467,22 +467,22 @@
     <t xml:space="preserve">1.38322794437408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36761772632599</t>
+    <t xml:space="preserve">1.36761784553528</t>
   </si>
   <si>
     <t xml:space="preserve">1.38149344921112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39797079563141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37455570697784</t>
+    <t xml:space="preserve">1.39797067642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37455558776855</t>
   </si>
   <si>
     <t xml:space="preserve">1.41358077526093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42138600349426</t>
+    <t xml:space="preserve">1.42138588428497</t>
   </si>
   <si>
     <t xml:space="preserve">1.41271352767944</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">1.35894548892975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34680438041687</t>
+    <t xml:space="preserve">1.34680426120758</t>
   </si>
   <si>
     <t xml:space="preserve">1.36414873600006</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">1.36241436004639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33032691478729</t>
+    <t xml:space="preserve">1.33032703399658</t>
   </si>
   <si>
     <t xml:space="preserve">1.32078742980957</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">1.31992018222809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3129825592041</t>
+    <t xml:space="preserve">1.31298243999481</t>
   </si>
   <si>
     <t xml:space="preserve">1.17942941188812</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">1.12305963039398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1334662437439</t>
+    <t xml:space="preserve">1.13346636295319</t>
   </si>
   <si>
     <t xml:space="preserve">1.11438727378845</t>
@@ -569,22 +569,22 @@
     <t xml:space="preserve">1.11612164974213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11525452136993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09791016578674</t>
+    <t xml:space="preserve">1.11525464057922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09791004657745</t>
   </si>
   <si>
     <t xml:space="preserve">1.09270668029785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07536208629608</t>
+    <t xml:space="preserve">1.07536220550537</t>
   </si>
   <si>
     <t xml:space="preserve">1.07276034355164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10398066043854</t>
+    <t xml:space="preserve">1.10398054122925</t>
   </si>
   <si>
     <t xml:space="preserve">1.15427982807159</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">1.16208493709564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17856216430664</t>
+    <t xml:space="preserve">1.17856204509735</t>
   </si>
   <si>
     <t xml:space="preserve">1.18289828300476</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">1.20544612407684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23493206501007</t>
+    <t xml:space="preserve">1.23493194580078</t>
   </si>
   <si>
     <t xml:space="preserve">1.24533867835999</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">1.22192347049713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23666644096375</t>
+    <t xml:space="preserve">1.23666632175446</t>
   </si>
   <si>
     <t xml:space="preserve">1.26875388622284</t>
@@ -635,28 +635,28 @@
     <t xml:space="preserve">1.38409507274628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3988379240036</t>
+    <t xml:space="preserve">1.39883804321289</t>
   </si>
   <si>
     <t xml:space="preserve">1.38669669628143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35721099376678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34593713283539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33292865753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28869998455048</t>
+    <t xml:space="preserve">1.35721111297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34593725204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33292853832245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28870010375977</t>
   </si>
   <si>
     <t xml:space="preserve">1.25747990608215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2331976890564</t>
+    <t xml:space="preserve">1.23319756984711</t>
   </si>
   <si>
     <t xml:space="preserve">1.2444714307785</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">1.22712683677673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25661277770996</t>
+    <t xml:space="preserve">1.25661265850067</t>
   </si>
   <si>
     <t xml:space="preserve">1.22365808486938</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">1.27222275733948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29823958873749</t>
+    <t xml:space="preserve">1.2982394695282</t>
   </si>
   <si>
     <t xml:space="preserve">1.26355040073395</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">1.2496749162674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29043447971344</t>
+    <t xml:space="preserve">1.29043459892273</t>
   </si>
   <si>
     <t xml:space="preserve">1.29303622245789</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">1.27048826217651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26528477668762</t>
+    <t xml:space="preserve">1.26528489589691</t>
   </si>
   <si>
     <t xml:space="preserve">1.28436398506165</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">1.28523111343384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28696548938751</t>
+    <t xml:space="preserve">1.2869656085968</t>
   </si>
   <si>
     <t xml:space="preserve">1.3398665189743</t>
@@ -803,10 +803,10 @@
     <t xml:space="preserve">1.54019606113434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49856913089752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50724136829376</t>
+    <t xml:space="preserve">1.49856925010681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50724148750305</t>
   </si>
   <si>
     <t xml:space="preserve">1.50203800201416</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">1.4786229133606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43352711200714</t>
+    <t xml:space="preserve">1.43352699279785</t>
   </si>
   <si>
     <t xml:space="preserve">1.40577590465546</t>
@@ -827,13 +827,13 @@
     <t xml:space="preserve">1.47168517112732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48729515075684</t>
+    <t xml:space="preserve">1.48729526996613</t>
   </si>
   <si>
     <t xml:space="preserve">1.47602128982544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45694220066071</t>
+    <t xml:space="preserve">1.45694208145142</t>
   </si>
   <si>
     <t xml:space="preserve">1.46821618080139</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">1.53585994243622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48642802238464</t>
+    <t xml:space="preserve">1.48642790317535</t>
   </si>
   <si>
     <t xml:space="preserve">1.49510014057159</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">1.48816239833832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51591372489929</t>
+    <t xml:space="preserve">1.51591360569</t>
   </si>
   <si>
     <t xml:space="preserve">1.56881463527679</t>
@@ -899,10 +899,10 @@
     <t xml:space="preserve">1.57054901123047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64686512947083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78648865222931</t>
+    <t xml:space="preserve">1.64686501026154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78648853302002</t>
   </si>
   <si>
     <t xml:space="preserve">1.7604718208313</t>
@@ -917,10 +917,10 @@
     <t xml:space="preserve">1.84199118614197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15245890617371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9998265504837</t>
+    <t xml:space="preserve">2.15245866775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99982666969299</t>
   </si>
   <si>
     <t xml:space="preserve">2.05879807472229</t>
@@ -929,37 +929,37 @@
     <t xml:space="preserve">2.00329542160034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9512619972229</t>
+    <t xml:space="preserve">1.95126187801361</t>
   </si>
   <si>
     <t xml:space="preserve">2.05186033248901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01543664932251</t>
+    <t xml:space="preserve">2.01543641090393</t>
   </si>
   <si>
     <t xml:space="preserve">1.98074734210968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90443158149719</t>
+    <t xml:space="preserve">1.9044314622879</t>
   </si>
   <si>
     <t xml:space="preserve">1.90790057182312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91657269001007</t>
+    <t xml:space="preserve">1.91657257080078</t>
   </si>
   <si>
     <t xml:space="preserve">1.90616607666016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84892892837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87321150302887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83158445358276</t>
+    <t xml:space="preserve">1.84892904758453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87321138381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83158433437347</t>
   </si>
   <si>
     <t xml:space="preserve">1.84719455242157</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">1.93218290805817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93738615512848</t>
+    <t xml:space="preserve">1.93738627433777</t>
   </si>
   <si>
     <t xml:space="preserve">1.92524516582489</t>
@@ -977,13 +977,13 @@
     <t xml:space="preserve">1.94258975982666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97727859020233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02063989639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06920480728149</t>
+    <t xml:space="preserve">1.97727870941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0206401348114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06920456886292</t>
   </si>
   <si>
     <t xml:space="preserve">2.01196765899658</t>
@@ -992,16 +992,16 @@
     <t xml:space="preserve">2.03971910476685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01370215415955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99462342262268</t>
+    <t xml:space="preserve">2.01370239257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99462330341339</t>
   </si>
   <si>
     <t xml:space="preserve">1.94432413578033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90269708633423</t>
+    <t xml:space="preserve">1.90269696712494</t>
   </si>
   <si>
     <t xml:space="preserve">1.82117772102356</t>
@@ -1025,16 +1025,16 @@
     <t xml:space="preserve">1.67895245552063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63992726802826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64773213863373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62865328788757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6269189119339</t>
+    <t xml:space="preserve">1.63992738723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64773225784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62865316867828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62691879272461</t>
   </si>
   <si>
     <t xml:space="preserve">1.60350370407104</t>
@@ -1046,19 +1046,19 @@
     <t xml:space="preserve">1.63905990123749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6485995054245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66507685184479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6910936832428</t>
+    <t xml:space="preserve">1.64859938621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6650767326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69109380245209</t>
   </si>
   <si>
     <t xml:space="preserve">1.72925162315369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6754834651947</t>
+    <t xml:space="preserve">1.67548358440399</t>
   </si>
   <si>
     <t xml:space="preserve">1.65640461444855</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">1.63038766384125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66681134700775</t>
+    <t xml:space="preserve">1.66681122779846</t>
   </si>
   <si>
     <t xml:space="preserve">1.68155407905579</t>
@@ -1076,7 +1076,7 @@
     <t xml:space="preserve">1.68935918807983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67721784114838</t>
+    <t xml:space="preserve">1.67721796035767</t>
   </si>
   <si>
     <t xml:space="preserve">1.63385653495789</t>
@@ -1088,10 +1088,10 @@
     <t xml:space="preserve">1.65727186203003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71537601947784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66854584217072</t>
+    <t xml:space="preserve">1.71537590026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66854572296143</t>
   </si>
   <si>
     <t xml:space="preserve">1.71711039543152</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">1.72751724720001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71190714836121</t>
+    <t xml:space="preserve">1.71190702915192</t>
   </si>
   <si>
     <t xml:space="preserve">1.74312722682953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77781629562378</t>
+    <t xml:space="preserve">1.77781641483307</t>
   </si>
   <si>
     <t xml:space="preserve">1.77348029613495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80383324623108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93391740322113</t>
+    <t xml:space="preserve">1.80383312702179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93391752243042</t>
   </si>
   <si>
     <t xml:space="preserve">1.88188374042511</t>
@@ -1136,19 +1136,19 @@
     <t xml:space="preserve">1.81684160232544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89489209651947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8081693649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8298499584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85153079032898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78215253353119</t>
+    <t xml:space="preserve">1.89489197731018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80816924571991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82984983921051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85153067111969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7821524143219</t>
   </si>
   <si>
     <t xml:space="preserve">1.81250548362732</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">1.79082489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73445498943329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76480805873871</t>
+    <t xml:space="preserve">1.73445510864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76480793952942</t>
   </si>
   <si>
     <t xml:space="preserve">1.96860635280609</t>
@@ -1172,10 +1172,10 @@
     <t xml:space="preserve">1.89055597782135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87754738330841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83418619632721</t>
+    <t xml:space="preserve">1.8775475025177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8341863155365</t>
   </si>
   <si>
     <t xml:space="preserve">1.84285843372345</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">1.97294282913208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98161470890045</t>
+    <t xml:space="preserve">1.98161494731903</t>
   </si>
   <si>
     <t xml:space="preserve">1.92958116531372</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">2.072674036026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08134603500366</t>
+    <t xml:space="preserve">2.08134579658508</t>
   </si>
   <si>
     <t xml:space="preserve">2.1116988658905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15072417259216</t>
+    <t xml:space="preserve">2.15072441101074</t>
   </si>
   <si>
     <t xml:space="preserve">2.05532908439636</t>
@@ -1238,13 +1238,13 @@
     <t xml:space="preserve">2.2808084487915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21143007278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30682516098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28514432907104</t>
+    <t xml:space="preserve">2.21142983436584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3068253993988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28514456748962</t>
   </si>
   <si>
     <t xml:space="preserve">2.44991755485535</t>
@@ -1268,22 +1268,22 @@
     <t xml:space="preserve">2.62769937515259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71442198753357</t>
+    <t xml:space="preserve">2.71442222595215</t>
   </si>
   <si>
     <t xml:space="preserve">2.76645588874817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83583402633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91388440132141</t>
+    <t xml:space="preserve">2.83583378791809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91388416290283</t>
   </si>
   <si>
     <t xml:space="preserve">2.92255640029907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93122887611389</t>
+    <t xml:space="preserve">2.93122911453247</t>
   </si>
   <si>
     <t xml:space="preserve">2.87052297592163</t>
@@ -1295,16 +1295,16 @@
     <t xml:space="preserve">3.10033845901489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23909449577332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25210309028625</t>
+    <t xml:space="preserve">3.23909473419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25210332870483</t>
   </si>
   <si>
     <t xml:space="preserve">3.21741390228271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25643920898438</t>
+    <t xml:space="preserve">3.25643944740295</t>
   </si>
   <si>
     <t xml:space="preserve">3.36050653457642</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">3.20874190330505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36917877197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26511168479919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22175025939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33882570266724</t>
+    <t xml:space="preserve">3.36917901039124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26511144638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22175002098083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33882594108582</t>
   </si>
   <si>
     <t xml:space="preserve">3.27811980247498</t>
@@ -1337,10 +1337,10 @@
     <t xml:space="preserve">3.48625445365906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55563259124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51227164268494</t>
+    <t xml:space="preserve">3.55563282966614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51227188110352</t>
   </si>
   <si>
     <t xml:space="preserve">3.62934708595276</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">3.6640362739563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73341393470764</t>
+    <t xml:space="preserve">3.73341417312622</t>
   </si>
   <si>
     <t xml:space="preserve">3.80712866783142</t>
@@ -1361,16 +1361,16 @@
     <t xml:space="preserve">4.07596921920776</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04561614990234</t>
+    <t xml:space="preserve">4.0456166267395</t>
   </si>
   <si>
     <t xml:space="preserve">4.09765005111694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86783480644226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04127979278564</t>
+    <t xml:space="preserve">3.86783504486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0412802696228</t>
   </si>
   <si>
     <t xml:space="preserve">3.94588565826416</t>
@@ -1379,16 +1379,16 @@
     <t xml:space="preserve">3.97190189361572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71173357963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91986775398254</t>
+    <t xml:space="preserve">3.7117338180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91986799240112</t>
   </si>
   <si>
     <t xml:space="preserve">4.07163333892822</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24941492080688</t>
+    <t xml:space="preserve">4.24941444396973</t>
   </si>
   <si>
     <t xml:space="preserve">4.25375080108643</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">4.28410387039185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62232255935669</t>
+    <t xml:space="preserve">4.62232208251953</t>
   </si>
   <si>
     <t xml:space="preserve">4.57896137237549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74373388290405</t>
+    <t xml:space="preserve">4.74373435974121</t>
   </si>
   <si>
     <t xml:space="preserve">4.75240707397461</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">5.0385913848877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91717958450317</t>
+    <t xml:space="preserve">4.91718006134033</t>
   </si>
   <si>
     <t xml:space="preserve">4.82178449630737</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">4.89116334915161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83045721054077</t>
+    <t xml:space="preserve">4.83045768737793</t>
   </si>
   <si>
     <t xml:space="preserve">4.76107883453369</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">4.54427194595337</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70904541015625</t>
+    <t xml:space="preserve">4.70904493331909</t>
   </si>
   <si>
     <t xml:space="preserve">4.60497808456421</t>
@@ -1469,10 +1469,10 @@
     <t xml:space="preserve">4.64833974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61365032196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53559970855713</t>
+    <t xml:space="preserve">4.61365079879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53559923171997</t>
   </si>
   <si>
     <t xml:space="preserve">4.47489356994629</t>
@@ -1487,13 +1487,13 @@
     <t xml:space="preserve">4.1887092590332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24074220657349</t>
+    <t xml:space="preserve">4.24074268341064</t>
   </si>
   <si>
     <t xml:space="preserve">4.084641456604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92854118347168</t>
+    <t xml:space="preserve">3.9285409450531</t>
   </si>
   <si>
     <t xml:space="preserve">3.91553163528442</t>
@@ -1523,19 +1523,19 @@
     <t xml:space="preserve">3.00927948951721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09166622161865</t>
+    <t xml:space="preserve">3.09166598320007</t>
   </si>
   <si>
     <t xml:space="preserve">3.03529620170593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04830479621887</t>
+    <t xml:space="preserve">3.04830455780029</t>
   </si>
   <si>
     <t xml:space="preserve">3.07865762710571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96158194541931</t>
+    <t xml:space="preserve">2.96158170700073</t>
   </si>
   <si>
     <t xml:space="preserve">2.89653992652893</t>
@@ -1550,10 +1550,10 @@
     <t xml:space="preserve">2.75344729423523</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80548095703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88786745071411</t>
+    <t xml:space="preserve">2.80548071861267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88786768913269</t>
   </si>
   <si>
     <t xml:space="preserve">3.04396843910217</t>
@@ -1568,13 +1568,13 @@
     <t xml:space="preserve">3.19139719009399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4255485534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43855714797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39519572257996</t>
+    <t xml:space="preserve">3.42554879188538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43855690956116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39519548416138</t>
   </si>
   <si>
     <t xml:space="preserve">3.20440554618835</t>
@@ -1592,13 +1592,13 @@
     <t xml:space="preserve">2.88353133201599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97459030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02228784561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3821873664856</t>
+    <t xml:space="preserve">2.97459053993225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02228760719299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38218760490417</t>
   </si>
   <si>
     <t xml:space="preserve">3.32148122787476</t>
@@ -1625,10 +1625,10 @@
     <t xml:space="preserve">2.73176670074463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63203549385071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98759865760803</t>
+    <t xml:space="preserve">2.63203573226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98759889602661</t>
   </si>
   <si>
     <t xml:space="preserve">3.17405247688293</t>
@@ -1637,10 +1637,10 @@
     <t xml:space="preserve">3.3041365146637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30847311019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17838883399963</t>
+    <t xml:space="preserve">3.3084728717804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17838859558105</t>
   </si>
   <si>
     <t xml:space="preserve">3.10467433929443</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">3.16104435920715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33015370368958</t>
+    <t xml:space="preserve">3.330153465271</t>
   </si>
   <si>
     <t xml:space="preserve">3.46023774147034</t>
@@ -1661,16 +1661,16 @@
     <t xml:space="preserve">3.88517951965332</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9025239944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85482597351074</t>
+    <t xml:space="preserve">3.90252375602722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85482621192932</t>
   </si>
   <si>
     <t xml:space="preserve">4.11499404907227</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27543163299561</t>
+    <t xml:space="preserve">4.27543115615845</t>
   </si>
   <si>
     <t xml:space="preserve">4.10198640823364</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">4.1323390007019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95889329910278</t>
+    <t xml:space="preserve">3.95889353752136</t>
   </si>
   <si>
     <t xml:space="preserve">3.82447338104248</t>
@@ -1694,7 +1694,7 @@
     <t xml:space="preserve">3.9415488243103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99791884422302</t>
+    <t xml:space="preserve">3.99791860580444</t>
   </si>
   <si>
     <t xml:space="preserve">4.00659084320068</t>
@@ -1715,25 +1715,25 @@
     <t xml:space="preserve">4.03260803222656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98924684524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92420506477356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8288094997406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7594313621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74642300605774</t>
+    <t xml:space="preserve">3.98924660682678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92420482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82880926132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75943112373352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74642276763916</t>
   </si>
   <si>
     <t xml:space="preserve">3.56864094734192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.776775598526</t>
+    <t xml:space="preserve">3.77677583694458</t>
   </si>
   <si>
     <t xml:space="preserve">4.24507856369019</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">4.06729698181152</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16269207000732</t>
+    <t xml:space="preserve">4.16269159317017</t>
   </si>
   <si>
     <t xml:space="preserve">4.21906137466431</t>
@@ -1763,13 +1763,13 @@
     <t xml:space="preserve">4.68302822113037</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88249111175537</t>
+    <t xml:space="preserve">4.88249063491821</t>
   </si>
   <si>
     <t xml:space="preserve">4.76975107192993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72638940811157</t>
+    <t xml:space="preserve">4.72638988494873</t>
   </si>
   <si>
     <t xml:space="preserve">4.63966703414917</t>
@@ -1778,10 +1778,10 @@
     <t xml:space="preserve">4.55294466018677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44887733459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39684295654297</t>
+    <t xml:space="preserve">4.44887685775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39684343338013</t>
   </si>
   <si>
     <t xml:space="preserve">3.91119599342346</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">4.12285375595093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01130485534668</t>
+    <t xml:space="preserve">4.01130437850952</t>
   </si>
   <si>
     <t xml:space="preserve">3.91760349273682</t>
@@ -1805,19 +1805,19 @@
     <t xml:space="preserve">4.22547912597656</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00684261322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83282613754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85513591766357</t>
+    <t xml:space="preserve">4.00684213638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8328263759613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85513615608215</t>
   </si>
   <si>
     <t xml:space="preserve">3.8595974445343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93098950386047</t>
+    <t xml:space="preserve">3.93098974227905</t>
   </si>
   <si>
     <t xml:space="preserve">3.83728837966919</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">4.03807640075684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95776128768921</t>
+    <t xml:space="preserve">3.95776081085205</t>
   </si>
   <si>
     <t xml:space="preserve">3.79266858100891</t>
@@ -1841,22 +1841,22 @@
     <t xml:space="preserve">3.76143479347229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61419034004211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68111944198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52048850059509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48479270935059</t>
+    <t xml:space="preserve">3.61419010162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6811192035675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52048873901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48479294776917</t>
   </si>
   <si>
     <t xml:space="preserve">3.67219519615173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59634232521057</t>
+    <t xml:space="preserve">3.59634208679199</t>
   </si>
   <si>
     <t xml:space="preserve">3.58741807937622</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">3.64096164703369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64988565444946</t>
+    <t xml:space="preserve">3.64988589286804</t>
   </si>
   <si>
     <t xml:space="preserve">3.5115647315979</t>
@@ -1886,7 +1886,7 @@
     <t xml:space="preserve">3.4223256111145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47140717506409</t>
+    <t xml:space="preserve">3.47140693664551</t>
   </si>
   <si>
     <t xml:space="preserve">3.50710296630859</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">3.41340160369873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42678737640381</t>
+    <t xml:space="preserve">3.42678761482239</t>
   </si>
   <si>
     <t xml:space="preserve">3.36878204345703</t>
@@ -1934,40 +1934,40 @@
     <t xml:space="preserve">3.40001559257507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30631422996521</t>
+    <t xml:space="preserve">3.30631446838379</t>
   </si>
   <si>
     <t xml:space="preserve">3.28400492668152</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33308625221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35093426704407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52941250801086</t>
+    <t xml:space="preserve">3.33308601379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35093402862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52941274642944</t>
   </si>
   <si>
     <t xml:space="preserve">3.65880942344666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71235299110413</t>
+    <t xml:space="preserve">3.71235322952271</t>
   </si>
   <si>
     <t xml:space="preserve">3.81051635742188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80605435371399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76589632034302</t>
+    <t xml:space="preserve">3.80605411529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7658965587616</t>
   </si>
   <si>
     <t xml:space="preserve">3.6008038520813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5561842918396</t>
+    <t xml:space="preserve">3.55618405342102</t>
   </si>
   <si>
     <t xml:space="preserve">3.4669451713562</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">3.66773343086243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69896721839905</t>
+    <t xml:space="preserve">3.69896697998047</t>
   </si>
   <si>
     <t xml:space="preserve">3.7212769985199</t>
@@ -2018,10 +2018,10 @@
     <t xml:space="preserve">3.56957030296326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9666850566864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73466324806213</t>
+    <t xml:space="preserve">3.96668481826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73466300964355</t>
   </si>
   <si>
     <t xml:space="preserve">3.69450497627258</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">3.60526609420776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57849454879761</t>
+    <t xml:space="preserve">3.57849431037903</t>
   </si>
   <si>
     <t xml:space="preserve">3.56510806083679</t>
@@ -2048,10 +2048,10 @@
     <t xml:space="preserve">4.06038665771484</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91314172744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98899459838867</t>
+    <t xml:space="preserve">3.91314196586609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98899435997009</t>
   </si>
   <si>
     <t xml:space="preserve">3.98007082939148</t>
@@ -2069,10 +2069,10 @@
     <t xml:space="preserve">4.03361415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92652702331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90867924690247</t>
+    <t xml:space="preserve">3.92652750015259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90867972373962</t>
   </si>
   <si>
     <t xml:space="preserve">3.90421748161316</t>
@@ -2081,22 +2081,22 @@
     <t xml:space="preserve">4.0425386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93545126914978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8908314704895</t>
+    <t xml:space="preserve">3.93545150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89083194732666</t>
   </si>
   <si>
     <t xml:space="preserve">4.07823419570923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19424486160278</t>
+    <t xml:space="preserve">4.19424438476562</t>
   </si>
   <si>
     <t xml:space="preserve">4.00238084793091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17639684677124</t>
+    <t xml:space="preserve">4.1763973236084</t>
   </si>
   <si>
     <t xml:space="preserve">4.08715772628784</t>
@@ -2108,28 +2108,28 @@
     <t xml:space="preserve">4.46196269989014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53335380554199</t>
+    <t xml:space="preserve">4.53335428237915</t>
   </si>
   <si>
     <t xml:space="preserve">4.64044094085693</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58689737319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64936542510986</t>
+    <t xml:space="preserve">4.58689785003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64936494827271</t>
   </si>
   <si>
     <t xml:space="preserve">4.7564525604248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78322410583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68506145477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83676767349243</t>
+    <t xml:space="preserve">4.78322458267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68506097793579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83676815032959</t>
   </si>
   <si>
     <t xml:space="preserve">4.81892013549805</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">4.89923477172852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85461568832397</t>
+    <t xml:space="preserve">4.85461521148682</t>
   </si>
   <si>
     <t xml:space="preserve">4.9795503616333</t>
@@ -2156,10 +2156,10 @@
     <t xml:space="preserve">5.04201793670654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89031171798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95277881622314</t>
+    <t xml:space="preserve">4.8903112411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9527792930603</t>
   </si>
   <si>
     <t xml:space="preserve">4.8456916809082</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">4.997398853302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23834419250488</t>
+    <t xml:space="preserve">5.23834466934204</t>
   </si>
   <si>
     <t xml:space="preserve">5.45251846313477</t>
@@ -2201,13 +2201,13 @@
     <t xml:space="preserve">5.15802955627441</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88138723373413</t>
+    <t xml:space="preserve">4.88138675689697</t>
   </si>
   <si>
     <t xml:space="preserve">4.70290899276733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71183252334595</t>
+    <t xml:space="preserve">4.71183300018311</t>
   </si>
   <si>
     <t xml:space="preserve">4.73860454559326</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">4.63151741027832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67613649368286</t>
+    <t xml:space="preserve">4.67613697052002</t>
   </si>
   <si>
     <t xml:space="preserve">4.56012630462646</t>
@@ -2225,16 +2225,16 @@
     <t xml:space="preserve">4.41734313964844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14516353607178</t>
+    <t xml:space="preserve">4.14516401290894</t>
   </si>
   <si>
     <t xml:space="preserve">4.02022886276245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98453283309937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94883728027344</t>
+    <t xml:space="preserve">3.98453259468079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94883704185486</t>
   </si>
   <si>
     <t xml:space="preserve">3.8015923500061</t>
@@ -2252,25 +2252,25 @@
     <t xml:space="preserve">2.72625923156738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.757493019104</t>
+    <t xml:space="preserve">2.75749325752258</t>
   </si>
   <si>
     <t xml:space="preserve">2.44961738586426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45854139328003</t>
+    <t xml:space="preserve">2.45854163169861</t>
   </si>
   <si>
     <t xml:space="preserve">2.14174222946167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99895942211151</t>
+    <t xml:space="preserve">1.99895930290222</t>
   </si>
   <si>
     <t xml:space="preserve">2.10604619979858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25775337219238</t>
+    <t xml:space="preserve">2.2577531337738</t>
   </si>
   <si>
     <t xml:space="preserve">2.34699249267578</t>
@@ -2279,25 +2279,25 @@
     <t xml:space="preserve">2.4228458404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54331874847412</t>
+    <t xml:space="preserve">2.54331851005554</t>
   </si>
   <si>
     <t xml:space="preserve">2.40053606033325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48085141181946</t>
+    <t xml:space="preserve">2.48085117340088</t>
   </si>
   <si>
     <t xml:space="preserve">2.45407962799072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46300363540649</t>
+    <t xml:space="preserve">2.46300339698792</t>
   </si>
   <si>
     <t xml:space="preserve">2.56116652488708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73964500427246</t>
+    <t xml:space="preserve">2.73964524269104</t>
   </si>
   <si>
     <t xml:space="preserve">3.23938512802124</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">3.20368933677673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10998797416687</t>
+    <t xml:space="preserve">3.10998773574829</t>
   </si>
   <si>
     <t xml:space="preserve">2.91812372207642</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">2.94489550590515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89135217666626</t>
+    <t xml:space="preserve">2.89135193824768</t>
   </si>
   <si>
     <t xml:space="preserve">2.97612929344177</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">2.85565638542175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98059105873108</t>
+    <t xml:space="preserve">2.98059129714966</t>
   </si>
   <si>
     <t xml:space="preserve">3.00290107727051</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">3.13229775428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01182508468628</t>
+    <t xml:space="preserve">3.0118248462677</t>
   </si>
   <si>
     <t xml:space="preserve">2.98862147331238</t>
@@ -2795,9 +2795,6 @@
     <t xml:space="preserve">3.10463929176331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0118248462677</t>
-  </si>
-  <si>
     <t xml:space="preserve">3.11392092704773</t>
   </si>
   <si>
@@ -4221,6 +4218,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.13000011444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96999979019165</t>
   </si>
 </sst>
 </file>
@@ -39053,7 +39053,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1327" t="s">
-        <v>927</v>
+        <v>776</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -39131,7 +39131,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1330" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -39157,7 +39157,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1331" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -39183,7 +39183,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1332" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -39209,7 +39209,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1333" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -39235,7 +39235,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1334" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -39261,7 +39261,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1335" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -39313,7 +39313,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1337" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -39339,7 +39339,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1338" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -39365,7 +39365,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1339" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -39391,7 +39391,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G1340" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -39417,7 +39417,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1341" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -39443,7 +39443,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1342" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -39469,7 +39469,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1343" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -39495,7 +39495,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1344" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -39521,7 +39521,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1345" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -39547,7 +39547,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1346" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -39573,7 +39573,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1347" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -39599,7 +39599,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1348" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -39625,7 +39625,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1349" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -39651,7 +39651,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1350" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -39677,7 +39677,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1351" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -39703,7 +39703,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1352" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -39729,7 +39729,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1353" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -39755,7 +39755,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1354" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -39781,7 +39781,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1355" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -39833,7 +39833,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1357" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -39859,7 +39859,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1358" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -39885,7 +39885,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1359" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -39911,7 +39911,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1360" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -39937,7 +39937,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1361" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -39963,7 +39963,7 @@
         <v>3.375</v>
       </c>
       <c r="G1362" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -39989,7 +39989,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1363" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -40015,7 +40015,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1364" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -40041,7 +40041,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1365" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -40067,7 +40067,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1366" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -40093,7 +40093,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1367" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -40119,7 +40119,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1368" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -40145,7 +40145,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1369" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -40171,7 +40171,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1370" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -40223,7 +40223,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1372" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -40249,7 +40249,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1373" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -40275,7 +40275,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1374" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -40301,7 +40301,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1375" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -40327,7 +40327,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1376" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -40353,7 +40353,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1377" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -40379,7 +40379,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1378" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -40405,7 +40405,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G1379" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -40431,7 +40431,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G1380" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -40457,7 +40457,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1381" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -40483,7 +40483,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1382" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -40509,7 +40509,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1383" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -40535,7 +40535,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G1384" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -40561,7 +40561,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1385" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -40587,7 +40587,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1386" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -40613,7 +40613,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1387" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -40639,7 +40639,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1388" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -40665,7 +40665,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G1389" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -40691,7 +40691,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G1390" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -40717,7 +40717,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1391" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -40743,7 +40743,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1392" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -40769,7 +40769,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G1393" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -40795,7 +40795,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1394" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -40821,7 +40821,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1395" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -40847,7 +40847,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1396" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -40873,7 +40873,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1397" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -40899,7 +40899,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1398" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -40925,7 +40925,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1399" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -40951,7 +40951,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1400" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -40977,7 +40977,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1401" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -41003,7 +41003,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1402" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -41029,7 +41029,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1403" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -41055,7 +41055,7 @@
         <v>3.5</v>
       </c>
       <c r="G1404" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -41107,7 +41107,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1406" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -41185,7 +41185,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1409" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -41211,7 +41211,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1410" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -41237,7 +41237,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1411" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -41289,7 +41289,7 @@
         <v>3.375</v>
       </c>
       <c r="G1413" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -41367,7 +41367,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1416" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -41393,7 +41393,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1417" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -41523,7 +41523,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1422" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -41549,7 +41549,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1423" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -41575,7 +41575,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1424" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -41601,7 +41601,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1425" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -41627,7 +41627,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1426" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -41653,7 +41653,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1427" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -41679,7 +41679,7 @@
         <v>3.5</v>
       </c>
       <c r="G1428" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -41705,7 +41705,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1429" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -41731,7 +41731,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1430" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -41757,7 +41757,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1431" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -41783,7 +41783,7 @@
         <v>3.375</v>
       </c>
       <c r="G1432" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -41809,7 +41809,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1433" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -41835,7 +41835,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1434" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -41887,7 +41887,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1436" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -41913,7 +41913,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1437" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -41939,7 +41939,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1438" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -41965,7 +41965,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1439" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -41991,7 +41991,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1440" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -42017,7 +42017,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G1441" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -42043,7 +42043,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1442" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -42069,7 +42069,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1443" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -42095,7 +42095,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1444" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -42121,7 +42121,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1445" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -42173,7 +42173,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1447" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -42199,7 +42199,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1448" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -42225,7 +42225,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1449" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -42251,7 +42251,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1450" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -42277,7 +42277,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1451" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -42303,7 +42303,7 @@
         <v>3.625</v>
       </c>
       <c r="G1452" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -42329,7 +42329,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1453" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -42381,7 +42381,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1455" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -42407,7 +42407,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1456" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -42433,7 +42433,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1457" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -42459,7 +42459,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G1458" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -42485,7 +42485,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1459" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -42511,7 +42511,7 @@
         <v>3.625</v>
       </c>
       <c r="G1460" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -42537,7 +42537,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1461" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -42563,7 +42563,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1462" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -42589,7 +42589,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1463" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -42615,7 +42615,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1464" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -42641,7 +42641,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1465" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -42667,7 +42667,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1466" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -42693,7 +42693,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1467" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -42719,7 +42719,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1468" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -42745,7 +42745,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1469" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -42771,7 +42771,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1470" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -42797,7 +42797,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1471" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -42823,7 +42823,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1472" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -42849,7 +42849,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1473" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -42875,7 +42875,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1474" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -42901,7 +42901,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1475" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -42927,7 +42927,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1476" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -42953,7 +42953,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1477" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -42979,7 +42979,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1478" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -43005,7 +43005,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G1479" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -43057,7 +43057,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1481" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -43109,7 +43109,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1483" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -43135,7 +43135,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G1484" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -43161,7 +43161,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1485" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -43187,7 +43187,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1486" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -43213,7 +43213,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1487" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -43239,7 +43239,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1488" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -43265,7 +43265,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1489" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -43291,7 +43291,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1490" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -43317,7 +43317,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1491" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -43343,7 +43343,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1492" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -43369,7 +43369,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1493" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -43395,7 +43395,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1494" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -43421,7 +43421,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1495" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -43447,7 +43447,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1496" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -43473,7 +43473,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1497" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -43499,7 +43499,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1498" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -43525,7 +43525,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1499" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -43577,7 +43577,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1501" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -43629,7 +43629,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1503" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -43655,7 +43655,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1504" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -43681,7 +43681,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1505" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -43733,7 +43733,7 @@
         <v>3.25</v>
       </c>
       <c r="G1507" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -43811,7 +43811,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1510" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -43837,7 +43837,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1511" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -43863,7 +43863,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1512" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -43889,7 +43889,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1513" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -43941,7 +43941,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1515" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -43967,7 +43967,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1516" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -44045,7 +44045,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1519" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -44071,7 +44071,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1520" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -44097,7 +44097,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1521" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -44123,7 +44123,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1522" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -44149,7 +44149,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1523" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -44175,7 +44175,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1524" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -44201,7 +44201,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1525" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -44227,7 +44227,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1526" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -44253,7 +44253,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1527" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -44279,7 +44279,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -44331,7 +44331,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1530" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -44357,7 +44357,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1531" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -44435,7 +44435,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G1534" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -44461,7 +44461,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1535" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -44513,7 +44513,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1537" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -44539,7 +44539,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1538" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -44591,7 +44591,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1540" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -44617,7 +44617,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1541" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -44643,7 +44643,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1542" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -44825,7 +44825,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1549" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -44851,7 +44851,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1550" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -44903,7 +44903,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1552" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -44929,7 +44929,7 @@
         <v>3.375</v>
       </c>
       <c r="G1553" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -44955,7 +44955,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1554" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -45007,7 +45007,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1556" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -45059,7 +45059,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1558" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -45085,7 +45085,7 @@
         <v>3.375</v>
       </c>
       <c r="G1559" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -45163,7 +45163,7 @@
         <v>3.25</v>
       </c>
       <c r="G1562" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -45293,7 +45293,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1567" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -45319,7 +45319,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1568" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -45501,7 +45501,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G1575" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -45553,7 +45553,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1577" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -45605,7 +45605,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1579" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -45631,7 +45631,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1580" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -45735,7 +45735,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1584" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -45813,7 +45813,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G1587" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -45865,7 +45865,7 @@
         <v>3.375</v>
       </c>
       <c r="G1589" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -45891,7 +45891,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1590" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -46021,7 +46021,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1595" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -46125,7 +46125,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G1599" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -46203,7 +46203,7 @@
         <v>3.375</v>
       </c>
       <c r="G1602" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -46229,7 +46229,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1603" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -46307,7 +46307,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1606" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -46359,7 +46359,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1608" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -46411,7 +46411,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1610" t="s">
-        <v>927</v>
+        <v>776</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -46437,7 +46437,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1611" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -46463,7 +46463,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1612" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -46593,7 +46593,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1617" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -46645,7 +46645,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1619" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -46671,7 +46671,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1620" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -46697,7 +46697,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1621" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -46801,7 +46801,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1625" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -46827,7 +46827,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1626" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -46931,7 +46931,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1630" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -46957,7 +46957,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G1631" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -47113,7 +47113,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1637" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -47191,7 +47191,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1640" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -47243,7 +47243,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1642" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -47269,7 +47269,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1643" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -47321,7 +47321,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1645" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -47373,7 +47373,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1647" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -47425,7 +47425,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1649" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -47503,7 +47503,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1652" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -47555,7 +47555,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1654" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -47919,7 +47919,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1668" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -48075,7 +48075,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1674" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -48101,7 +48101,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1675" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -48257,7 +48257,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1681" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -48283,7 +48283,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1682" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -48309,7 +48309,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1683" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -48387,7 +48387,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1686" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -48543,7 +48543,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1692" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -48569,7 +48569,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1693" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -48647,7 +48647,7 @@
         <v>3.125</v>
       </c>
       <c r="G1696" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -48699,7 +48699,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1698" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -48751,7 +48751,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1700" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -48777,7 +48777,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1701" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -48829,7 +48829,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1703" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -48933,7 +48933,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1707" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -48959,7 +48959,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1708" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -48985,7 +48985,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1709" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -49037,7 +49037,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1711" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -49063,7 +49063,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G1712" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -49115,7 +49115,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1714" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -49271,7 +49271,7 @@
         <v>3.125</v>
       </c>
       <c r="G1720" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -49297,7 +49297,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1721" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -49349,7 +49349,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1723" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -49453,7 +49453,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1727" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -49635,7 +49635,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1734" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -49843,7 +49843,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1742" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -49921,7 +49921,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G1745" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -49973,7 +49973,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1747" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -49999,7 +49999,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1748" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -50129,7 +50129,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1753" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -50207,7 +50207,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1756" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -50285,7 +50285,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1759" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -50337,7 +50337,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1761" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -50467,7 +50467,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1766" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -50493,7 +50493,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1767" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -50545,7 +50545,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1769" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -50649,7 +50649,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1773" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -50701,7 +50701,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1775" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -50727,7 +50727,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1776" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -50753,7 +50753,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1777" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -50909,7 +50909,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1783" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -50935,7 +50935,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1784" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -50961,7 +50961,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1785" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -51013,7 +51013,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1787" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -51143,7 +51143,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1792" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -51247,7 +51247,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1796" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -51325,7 +51325,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1799" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -51455,7 +51455,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1804" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -51559,7 +51559,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1808" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -51585,7 +51585,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1809" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -51767,7 +51767,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1816" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -51845,7 +51845,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1819" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -51897,7 +51897,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1821" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -52105,7 +52105,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1829" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -52287,7 +52287,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1836" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -52339,7 +52339,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1838" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -52391,7 +52391,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1840" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -52443,7 +52443,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1842" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -52521,7 +52521,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1845" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -52599,7 +52599,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1848" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -52807,7 +52807,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1856" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -52833,7 +52833,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G1857" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -52885,7 +52885,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1859" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -52911,7 +52911,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1860" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -52963,7 +52963,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1862" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -52989,7 +52989,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1863" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -53145,7 +53145,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1869" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -53171,7 +53171,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1870" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -53197,7 +53197,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1871" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -53223,7 +53223,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1872" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -53353,7 +53353,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1877" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -53405,7 +53405,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1879" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -53483,7 +53483,7 @@
         <v>2.625</v>
       </c>
       <c r="G1882" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -53561,7 +53561,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G1885" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -53613,7 +53613,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G1887" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -53665,7 +53665,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1889" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -53691,7 +53691,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1890" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -53743,7 +53743,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1892" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -53769,7 +53769,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1893" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -53795,7 +53795,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G1894" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -53821,7 +53821,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G1895" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -53847,7 +53847,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1896" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -53873,7 +53873,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G1897" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -53899,7 +53899,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1898" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -53925,7 +53925,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1899" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -53951,7 +53951,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1900" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -53977,7 +53977,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G1901" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -54003,7 +54003,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G1902" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -54081,7 +54081,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1905" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -54107,7 +54107,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G1906" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -54159,7 +54159,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1908" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -54237,7 +54237,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1911" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -54289,7 +54289,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1913" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -54315,7 +54315,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1914" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -54341,7 +54341,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1915" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -54367,7 +54367,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1916" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -54393,7 +54393,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1917" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -54419,7 +54419,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1918" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -54445,7 +54445,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1919" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -54471,7 +54471,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1920" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -54497,7 +54497,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1921" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -54523,7 +54523,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G1922" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -54601,7 +54601,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1925" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -54627,7 +54627,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G1926" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -54705,7 +54705,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1929" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -54757,7 +54757,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1931" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -54809,7 +54809,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1933" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -54835,7 +54835,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1934" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -54861,7 +54861,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1935" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -54887,7 +54887,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1936" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -54913,7 +54913,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1937" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -54939,7 +54939,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1938" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -54965,7 +54965,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1939" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -54991,7 +54991,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1940" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -55017,7 +55017,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1941" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -55043,7 +55043,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1942" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -55069,7 +55069,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1943" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -55095,7 +55095,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1944" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -55121,7 +55121,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1945" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -55147,7 +55147,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G1946" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -55173,7 +55173,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1947" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -55199,7 +55199,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1948" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -55225,7 +55225,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1949" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -55277,7 +55277,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G1951" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -55303,7 +55303,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1952" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -55329,7 +55329,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1953" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -55355,7 +55355,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1954" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -55433,7 +55433,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1957" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -55459,7 +55459,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1958" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -55485,7 +55485,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1959" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -55511,7 +55511,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1960" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -55537,7 +55537,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1961" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -55589,7 +55589,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1963" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -55693,7 +55693,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1967" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -55745,7 +55745,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1969" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -55771,7 +55771,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1970" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -55797,7 +55797,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1971" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -55823,7 +55823,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1972" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -55849,7 +55849,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G1973" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -55875,7 +55875,7 @@
         <v>1.9539999961853</v>
       </c>
       <c r="G1974" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -55901,7 +55901,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1975" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -55927,7 +55927,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1976" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -55953,7 +55953,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1977" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -55979,7 +55979,7 @@
         <v>1.96599996089935</v>
       </c>
       <c r="G1978" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -56005,7 +56005,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G1979" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -56031,7 +56031,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1980" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -56057,7 +56057,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G1981" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -56083,7 +56083,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1982" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -56109,7 +56109,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G1983" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -56135,7 +56135,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1984" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -56161,7 +56161,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G1985" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -56187,7 +56187,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1986" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -56213,7 +56213,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1987" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -56239,7 +56239,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G1988" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -56265,7 +56265,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G1989" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -56291,7 +56291,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1990" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -56317,7 +56317,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1991" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -56343,7 +56343,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1992" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -56369,7 +56369,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G1993" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -56395,7 +56395,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G1994" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -56421,7 +56421,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1995" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -56447,7 +56447,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1996" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -56473,7 +56473,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G1997" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -56499,7 +56499,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1998" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -56525,7 +56525,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1999" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -56551,7 +56551,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2000" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -56577,7 +56577,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2001" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -56603,7 +56603,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G2002" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -56629,7 +56629,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2003" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -56655,7 +56655,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G2004" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -56681,7 +56681,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G2005" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -56863,7 +56863,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G2012" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -56889,7 +56889,7 @@
         <v>2.375</v>
       </c>
       <c r="G2013" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -56993,7 +56993,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G2017" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -57149,7 +57149,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2023" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -57201,7 +57201,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G2025" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -57279,7 +57279,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2028" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -57331,7 +57331,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G2030" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -57357,7 +57357,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G2031" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -57383,7 +57383,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G2032" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -57461,7 +57461,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G2035" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -57513,7 +57513,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G2037" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -57591,7 +57591,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G2040" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -57773,7 +57773,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G2047" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -57877,7 +57877,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G2051" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -57929,7 +57929,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G2053" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -58189,7 +58189,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G2063" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -58579,7 +58579,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2078" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -58605,7 +58605,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2079" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -58657,7 +58657,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G2081" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -58709,7 +58709,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2083" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -58735,7 +58735,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G2084" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -58761,7 +58761,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2085" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -58839,7 +58839,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G2088" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -58865,7 +58865,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2089" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -58891,7 +58891,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G2090" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -58917,7 +58917,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G2091" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -58943,7 +58943,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G2092" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -58969,7 +58969,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G2093" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -59021,7 +59021,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2095" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -59047,7 +59047,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G2096" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -59073,7 +59073,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G2097" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -59099,7 +59099,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G2098" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -59125,7 +59125,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G2099" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -59151,7 +59151,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G2100" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -59177,7 +59177,7 @@
         <v>4.125</v>
       </c>
       <c r="G2101" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -59203,7 +59203,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2102" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -59229,7 +59229,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2103" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -59255,7 +59255,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2104" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -59281,7 +59281,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2105" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -59307,7 +59307,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G2106" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -59333,7 +59333,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G2107" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -59359,7 +59359,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G2108" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -59385,7 +59385,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2109" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -59411,7 +59411,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G2110" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -59437,7 +59437,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G2111" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -59463,7 +59463,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G2112" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -59489,7 +59489,7 @@
         <v>3.625</v>
       </c>
       <c r="G2113" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -59515,7 +59515,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2114" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -59541,7 +59541,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G2115" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -59567,7 +59567,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2116" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -59593,7 +59593,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G2117" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -59619,7 +59619,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G2118" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -59645,7 +59645,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G2119" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -59671,7 +59671,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G2120" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -59697,7 +59697,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G2121" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -59723,7 +59723,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2122" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -59749,7 +59749,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G2123" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -59775,7 +59775,7 @@
         <v>3.75</v>
       </c>
       <c r="G2124" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -59801,7 +59801,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G2125" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -59827,7 +59827,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G2126" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -59853,7 +59853,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G2127" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -59879,7 +59879,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G2128" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -59905,7 +59905,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G2129" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -59931,7 +59931,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G2130" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -59957,7 +59957,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2131" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -59983,7 +59983,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G2132" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -60009,7 +60009,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G2133" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -60035,7 +60035,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G2134" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -60061,7 +60061,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G2135" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -60087,7 +60087,7 @@
         <v>3.75</v>
       </c>
       <c r="G2136" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -60113,7 +60113,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G2137" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -60139,7 +60139,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2138" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -60165,7 +60165,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G2139" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -60191,7 +60191,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G2140" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -60217,7 +60217,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2141" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -60243,7 +60243,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G2142" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -60269,7 +60269,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G2143" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -60295,7 +60295,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G2144" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -60321,7 +60321,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G2145" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -60347,7 +60347,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2146" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -60373,7 +60373,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G2147" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -60399,7 +60399,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G2148" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -60425,7 +60425,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G2149" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -60451,7 +60451,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G2150" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -60477,7 +60477,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G2151" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -60503,7 +60503,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G2152" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -60529,7 +60529,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G2153" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -60555,7 +60555,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G2154" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -60581,7 +60581,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G2155" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -60607,7 +60607,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2156" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -60633,7 +60633,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G2157" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -60659,7 +60659,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G2158" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -60685,7 +60685,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G2159" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -60711,7 +60711,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G2160" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -60737,7 +60737,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G2161" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -60763,7 +60763,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G2162" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -60789,7 +60789,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2163" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -60815,7 +60815,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2164" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -60841,7 +60841,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G2165" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -60867,7 +60867,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G2166" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -60893,7 +60893,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G2167" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -60919,7 +60919,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G2168" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -60945,7 +60945,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G2169" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -60971,7 +60971,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G2170" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -60997,7 +60997,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G2171" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -61023,7 +61023,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2172" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -61049,7 +61049,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G2173" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -61075,7 +61075,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G2174" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -61101,7 +61101,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2175" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -61127,7 +61127,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2176" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -61153,7 +61153,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2177" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -61179,7 +61179,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G2178" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -61205,7 +61205,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2179" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -61231,7 +61231,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G2180" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -61257,7 +61257,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2181" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -61283,7 +61283,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G2182" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -61309,7 +61309,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G2183" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -61335,7 +61335,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G2184" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -61361,7 +61361,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G2185" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -61387,7 +61387,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G2186" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -61413,7 +61413,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G2187" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -61439,7 +61439,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G2188" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -61465,7 +61465,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G2189" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -61491,7 +61491,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G2190" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -61517,7 +61517,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G2191" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -61543,7 +61543,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G2192" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -61569,7 +61569,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G2193" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -61595,7 +61595,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G2194" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -61621,7 +61621,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G2195" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -61647,7 +61647,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G2196" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -61673,7 +61673,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2197" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -61699,7 +61699,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G2198" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -61725,7 +61725,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G2199" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -61751,7 +61751,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2200" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -61777,7 +61777,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G2201" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -61803,7 +61803,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G2202" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -61829,7 +61829,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G2203" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -61855,7 +61855,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G2204" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -61881,7 +61881,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G2205" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -61907,7 +61907,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2206" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -61933,7 +61933,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G2207" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -61959,7 +61959,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G2208" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -61985,7 +61985,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G2209" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -62011,7 +62011,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G2210" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -62037,7 +62037,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G2211" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -62063,7 +62063,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G2212" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -62089,7 +62089,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G2213" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -62115,7 +62115,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G2214" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -62141,7 +62141,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G2215" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -62167,7 +62167,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G2216" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -62193,7 +62193,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G2217" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -62219,7 +62219,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G2218" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -62245,7 +62245,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G2219" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -62271,7 +62271,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G2220" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -62297,7 +62297,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G2221" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -62323,7 +62323,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G2222" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -62349,7 +62349,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G2223" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -62375,7 +62375,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G2224" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -62401,7 +62401,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G2225" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -62427,7 +62427,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G2226" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -62453,7 +62453,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G2227" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -62479,7 +62479,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G2228" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -62505,7 +62505,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G2229" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -62531,7 +62531,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2230" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -62557,7 +62557,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G2231" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -62583,7 +62583,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G2232" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -62609,7 +62609,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G2233" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -62635,7 +62635,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G2234" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -62661,7 +62661,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G2235" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -62687,7 +62687,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G2236" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -62713,7 +62713,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G2237" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -62739,7 +62739,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G2238" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -62765,7 +62765,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G2239" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -62791,7 +62791,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G2240" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -62817,7 +62817,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G2241" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -62843,7 +62843,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2242" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -62869,7 +62869,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2243" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -62895,7 +62895,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2244" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -62921,7 +62921,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2245" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -62947,7 +62947,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G2246" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -62973,7 +62973,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G2247" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -62999,7 +62999,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G2248" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -63025,7 +63025,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2249" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -63051,7 +63051,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2250" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -63077,7 +63077,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G2251" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -63103,7 +63103,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G2252" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -63129,7 +63129,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G2253" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -63155,7 +63155,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G2254" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -63181,7 +63181,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G2255" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -63207,7 +63207,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2256" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -63233,7 +63233,7 @@
         <v>4.125</v>
       </c>
       <c r="G2257" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -63259,7 +63259,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2258" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -63285,7 +63285,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G2259" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -63311,7 +63311,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G2260" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -63337,7 +63337,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G2261" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -63363,7 +63363,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G2262" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -63389,7 +63389,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2263" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -63415,7 +63415,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G2264" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -63441,7 +63441,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G2265" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -63467,7 +63467,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G2266" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -63493,7 +63493,7 @@
         <v>4</v>
       </c>
       <c r="G2267" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -63519,7 +63519,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2268" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63545,7 +63545,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2269" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63571,7 +63571,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2270" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63597,7 +63597,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G2271" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63623,7 +63623,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2272" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63649,7 +63649,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G2273" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -63675,7 +63675,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G2274" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63701,7 +63701,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2275" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -63727,7 +63727,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G2276" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -63753,7 +63753,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2277" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -63779,7 +63779,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2278" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -63805,7 +63805,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G2279" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -63831,7 +63831,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G2280" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -63857,7 +63857,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2281" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -63883,7 +63883,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G2282" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -63909,7 +63909,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G2283" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -63935,7 +63935,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2284" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -63961,7 +63961,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G2285" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -63987,7 +63987,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G2286" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -64013,7 +64013,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G2287" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -64039,7 +64039,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G2288" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -64065,7 +64065,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2289" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -64091,7 +64091,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2290" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -64117,7 +64117,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2291" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -64143,7 +64143,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2292" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64169,7 +64169,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G2293" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64195,7 +64195,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G2294" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64221,7 +64221,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G2295" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64247,7 +64247,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G2296" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64273,7 +64273,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2297" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64299,7 +64299,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2298" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64325,7 +64325,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G2299" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64351,7 +64351,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G2300" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64377,7 +64377,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2301" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64403,7 +64403,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2302" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64429,7 +64429,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G2303" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64455,7 +64455,7 @@
         <v>4.375</v>
       </c>
       <c r="G2304" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64481,7 +64481,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G2305" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64507,7 +64507,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G2306" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64533,7 +64533,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2307" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64559,7 +64559,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G2308" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64585,7 +64585,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2309" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64611,7 +64611,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G2310" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64637,7 +64637,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G2311" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64663,7 +64663,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G2312" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64689,7 +64689,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G2313" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64715,7 +64715,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G2314" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64741,7 +64741,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G2315" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -64767,7 +64767,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G2316" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -64793,7 +64793,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2317" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -64819,7 +64819,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G2318" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64845,7 +64845,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G2319" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64871,7 +64871,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G2320" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -64897,7 +64897,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2321" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -64923,7 +64923,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G2322" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -64949,7 +64949,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G2323" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -64975,7 +64975,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2324" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -65001,7 +65001,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G2325" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -65027,7 +65027,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2326" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -65053,7 +65053,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G2327" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -65079,7 +65079,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G2328" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -65105,7 +65105,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2329" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -65131,7 +65131,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G2330" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65157,7 +65157,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G2331" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65183,7 +65183,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G2332" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65209,7 +65209,7 @@
         <v>4.90500020980835</v>
       </c>
       <c r="G2333" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65235,7 +65235,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G2334" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65261,7 +65261,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G2335" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65287,7 +65287,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G2336" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65313,7 +65313,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G2337" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65339,7 +65339,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G2338" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65365,7 +65365,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G2339" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65391,7 +65391,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G2340" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65417,7 +65417,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G2341" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65443,7 +65443,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65469,7 +65469,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G2343" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65495,7 +65495,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G2344" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65521,7 +65521,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2345" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65547,7 +65547,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2346" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65573,7 +65573,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G2347" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65599,7 +65599,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2348" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65625,7 +65625,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2349" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65651,7 +65651,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G2350" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65677,7 +65677,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G2351" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65703,7 +65703,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2352" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65729,7 +65729,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G2353" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -65755,7 +65755,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G2354" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -65781,7 +65781,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G2355" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -65807,7 +65807,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2356" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -65833,7 +65833,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G2357" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -65859,7 +65859,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2358" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -65885,7 +65885,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2359" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -65911,7 +65911,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G2360" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -65937,7 +65937,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2361" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -65963,7 +65963,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G2362" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -65989,7 +65989,7 @@
         <v>4.91499996185303</v>
       </c>
       <c r="G2363" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -66015,7 +66015,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G2364" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -66041,7 +66041,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G2365" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -66067,7 +66067,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G2366" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -66093,7 +66093,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2367" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -66119,7 +66119,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G2368" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -66145,7 +66145,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G2369" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66171,7 +66171,7 @@
         <v>5.25</v>
       </c>
       <c r="G2370" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66197,7 +66197,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G2371" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66223,7 +66223,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G2372" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66249,7 +66249,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G2373" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66275,7 +66275,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G2374" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66301,7 +66301,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G2375" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66327,7 +66327,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2376" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66353,7 +66353,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G2377" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66379,7 +66379,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G2378" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66405,7 +66405,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G2379" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66431,7 +66431,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2380" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66457,7 +66457,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G2381" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66483,7 +66483,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G2382" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66509,7 +66509,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G2383" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66535,7 +66535,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G2384" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66561,7 +66561,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2385" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66587,7 +66587,7 @@
         <v>5.75</v>
       </c>
       <c r="G2386" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66613,7 +66613,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2387" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66639,7 +66639,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G2388" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66665,7 +66665,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2389" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66691,7 +66691,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2390" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66717,7 +66717,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G2391" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66743,7 +66743,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G2392" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66769,7 +66769,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G2393" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66795,7 +66795,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G2394" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66821,7 +66821,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G2395" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66847,7 +66847,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G2396" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66873,7 +66873,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G2397" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66899,7 +66899,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2398" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66925,7 +66925,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G2399" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66951,7 +66951,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G2400" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66977,7 +66977,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G2401" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -67003,7 +67003,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G2402" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -67029,7 +67029,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2403" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -67055,7 +67055,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G2404" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -67081,7 +67081,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G2405" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -67107,7 +67107,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G2406" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -67133,7 +67133,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2407" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67159,7 +67159,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G2408" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67185,7 +67185,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2409" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67211,7 +67211,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2410" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67237,7 +67237,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G2411" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67263,7 +67263,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G2412" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67289,7 +67289,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G2413" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67315,7 +67315,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G2414" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67341,7 +67341,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2415" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67367,7 +67367,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G2416" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67393,7 +67393,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G2417" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67419,7 +67419,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2418" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67445,7 +67445,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2419" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67471,7 +67471,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2420" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67497,7 +67497,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2421" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67523,7 +67523,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G2422" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67549,7 +67549,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G2423" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67575,7 +67575,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G2424" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67601,7 +67601,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2425" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67627,7 +67627,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G2426" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67653,7 +67653,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G2427" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67679,7 +67679,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G2428" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67705,7 +67705,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G2429" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67731,7 +67731,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G2430" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67757,7 +67757,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G2431" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67783,7 +67783,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G2432" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67809,7 +67809,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G2433" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67835,7 +67835,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G2434" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67861,7 +67861,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G2435" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67887,7 +67887,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G2436" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67913,7 +67913,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G2437" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67939,7 +67939,7 @@
         <v>6.5</v>
       </c>
       <c r="G2438" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67965,7 +67965,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G2439" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67991,7 +67991,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G2440" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -68017,7 +68017,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G2441" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -68043,7 +68043,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G2442" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -68069,7 +68069,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G2443" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -68095,7 +68095,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G2444" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -68121,7 +68121,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G2445" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -68147,7 +68147,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G2446" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68173,7 +68173,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G2447" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68199,7 +68199,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G2448" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68225,7 +68225,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G2449" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68251,7 +68251,7 @@
         <v>7</v>
       </c>
       <c r="G2450" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68277,7 +68277,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G2451" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68303,7 +68303,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G2452" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68329,7 +68329,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G2453" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68355,7 +68355,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2454" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68381,7 +68381,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G2455" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68407,7 +68407,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G2456" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68433,7 +68433,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G2457" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68459,7 +68459,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G2458" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68485,7 +68485,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G2459" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68511,7 +68511,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G2460" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68537,7 +68537,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G2461" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68563,7 +68563,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G2462" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68589,7 +68589,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G2463" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68615,7 +68615,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G2464" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68641,7 +68641,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2465" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68667,7 +68667,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2466" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68693,7 +68693,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G2467" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68719,7 +68719,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G2468" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68745,7 +68745,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G2469" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68771,7 +68771,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2470" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68797,7 +68797,7 @@
         <v>7.25</v>
       </c>
       <c r="G2471" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68823,7 +68823,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G2472" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68849,7 +68849,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G2473" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68875,7 +68875,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G2474" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68901,7 +68901,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G2475" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68927,7 +68927,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2476" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68953,7 +68953,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G2477" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68979,7 +68979,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G2478" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -69005,7 +69005,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G2479" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -69031,7 +69031,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G2480" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -69057,7 +69057,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G2481" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -69083,7 +69083,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2482" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -69109,7 +69109,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G2483" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -69135,7 +69135,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2484" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69161,7 +69161,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G2485" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69187,7 +69187,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G2486" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69213,7 +69213,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2487" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -69239,7 +69239,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2488" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -69265,7 +69265,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G2489" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -69291,7 +69291,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G2490" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -69317,7 +69317,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G2491" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -69343,7 +69343,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2492" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -69369,7 +69369,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G2493" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -69395,7 +69395,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G2494" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -69421,7 +69421,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2495" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -69447,7 +69447,7 @@
         <v>7.5</v>
       </c>
       <c r="G2496" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -69473,7 +69473,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G2497" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -69499,7 +69499,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G2498" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -69525,7 +69525,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G2499" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -69551,7 +69551,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G2500" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -69577,7 +69577,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G2501" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -69603,7 +69603,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G2502" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -69629,7 +69629,7 @@
         <v>8</v>
       </c>
       <c r="G2503" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -69655,7 +69655,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G2504" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -69681,7 +69681,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G2505" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -69707,7 +69707,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G2506" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -69733,7 +69733,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2507" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -69759,7 +69759,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G2508" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -69785,7 +69785,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G2509" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -69811,7 +69811,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G2510" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -69837,7 +69837,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G2511" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -69863,7 +69863,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2512" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -69889,7 +69889,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G2513" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -69915,7 +69915,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G2514" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -69941,7 +69941,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G2515" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -69967,7 +69967,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G2516" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -69993,7 +69993,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G2517" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -70019,7 +70019,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G2518" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -70045,7 +70045,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G2519" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -70071,7 +70071,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G2520" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -70097,7 +70097,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G2521" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -70123,7 +70123,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G2522" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -70149,7 +70149,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G2523" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -70157,7 +70157,7 @@
     </row>
     <row r="2524">
       <c r="A2524" s="1" t="n">
-        <v>45993.6912615741</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B2524" t="n">
         <v>49492</v>
@@ -70175,9 +70175,35 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G2524" t="s">
+        <v>1401</v>
+      </c>
+      <c r="H2524" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" s="1" t="n">
+        <v>45994.6912615741</v>
+      </c>
+      <c r="B2525" t="n">
+        <v>46966</v>
+      </c>
+      <c r="C2525" t="n">
+        <v>8.18000030517578</v>
+      </c>
+      <c r="D2525" t="n">
+        <v>7.96999979019165</v>
+      </c>
+      <c r="E2525" t="n">
+        <v>8.18000030517578</v>
+      </c>
+      <c r="F2525" t="n">
+        <v>7.96999979019165</v>
+      </c>
+      <c r="G2525" t="s">
         <v>1402</v>
       </c>
-      <c r="H2524" t="s">
+      <c r="H2525" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95473062992096</t>
+    <t xml:space="preserve">1.95473086833954</t>
   </si>
   <si>
     <t xml:space="preserve">FM.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">1.95993399620056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9096348285675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8558669090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86453938484192</t>
+    <t xml:space="preserve">1.90963470935822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85586702823639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86453914642334</t>
   </si>
   <si>
     <t xml:space="preserve">1.68415582180023</t>
@@ -71,16 +71,16 @@
     <t xml:space="preserve">1.61824667453766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52285146713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47949004173279</t>
+    <t xml:space="preserve">1.52285158634186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4794899225235</t>
   </si>
   <si>
     <t xml:space="preserve">1.34420263767242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45434057712555</t>
+    <t xml:space="preserve">1.45434045791626</t>
   </si>
   <si>
     <t xml:space="preserve">1.55233716964722</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">1.48989689350128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54366493225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.595698595047</t>
+    <t xml:space="preserve">1.54366505146027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59569871425629</t>
   </si>
   <si>
     <t xml:space="preserve">1.51331210136414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53325831890106</t>
+    <t xml:space="preserve">1.53325819969177</t>
   </si>
   <si>
     <t xml:space="preserve">1.499436378479</t>
@@ -110,16 +110,16 @@
     <t xml:space="preserve">1.40751028060913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38582956790924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28349673748016</t>
+    <t xml:space="preserve">1.38582968711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28349661827087</t>
   </si>
   <si>
     <t xml:space="preserve">1.17682754993439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24186968803406</t>
+    <t xml:space="preserve">1.24186980724335</t>
   </si>
   <si>
     <t xml:space="preserve">1.20718061923981</t>
@@ -131,10 +131,10 @@
     <t xml:space="preserve">1.43873059749603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39710342884064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50030362606049</t>
+    <t xml:space="preserve">1.39710354804993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50030374526978</t>
   </si>
   <si>
     <t xml:space="preserve">1.48295903205872</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">1.49423289299011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47688841819763</t>
+    <t xml:space="preserve">1.47688853740692</t>
   </si>
   <si>
     <t xml:space="preserve">1.47515404224396</t>
@@ -161,28 +161,28 @@
     <t xml:space="preserve">1.50984311103821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56014227867126</t>
+    <t xml:space="preserve">1.56014239788055</t>
   </si>
   <si>
     <t xml:space="preserve">1.58702623844147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55754053592682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52805471420288</t>
+    <t xml:space="preserve">1.55754065513611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52805483341217</t>
   </si>
   <si>
     <t xml:space="preserve">1.54279780387878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51244461536407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55146992206573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61651194095612</t>
+    <t xml:space="preserve">1.51244473457336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55147004127502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61651206016541</t>
   </si>
   <si>
     <t xml:space="preserve">1.67374897003174</t>
@@ -194,10 +194,10 @@
     <t xml:space="preserve">1.67808520793915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65467000007629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63298940658569</t>
+    <t xml:space="preserve">1.65467011928558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63298952579498</t>
   </si>
   <si>
     <t xml:space="preserve">1.6061053276062</t>
@@ -212,19 +212,19 @@
     <t xml:space="preserve">1.49683463573456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48122453689575</t>
+    <t xml:space="preserve">1.48122441768646</t>
   </si>
   <si>
     <t xml:space="preserve">1.41791689395905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39970505237579</t>
+    <t xml:space="preserve">1.39970517158508</t>
   </si>
   <si>
     <t xml:space="preserve">1.35200774669647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39190006256104</t>
+    <t xml:space="preserve">1.39190018177032</t>
   </si>
   <si>
     <t xml:space="preserve">1.46041119098663</t>
@@ -233,16 +233,16 @@
     <t xml:space="preserve">1.57228338718414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62952053546906</t>
+    <t xml:space="preserve">1.62952041625977</t>
   </si>
   <si>
     <t xml:space="preserve">1.60437095165253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60870695114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62518441677094</t>
+    <t xml:space="preserve">1.60870707035065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62518429756165</t>
   </si>
   <si>
     <t xml:space="preserve">1.65987348556519</t>
@@ -278,13 +278,13 @@
     <t xml:space="preserve">1.56794726848602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53932881355286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53065657615662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54106330871582</t>
+    <t xml:space="preserve">1.53932869434357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53065645694733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54106318950653</t>
   </si>
   <si>
     <t xml:space="preserve">1.56968176364899</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">1.55060267448425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56708002090454</t>
+    <t xml:space="preserve">1.56708014011383</t>
   </si>
   <si>
     <t xml:space="preserve">1.5740180015564</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">1.59136247634888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56100952625275</t>
+    <t xml:space="preserve">1.56100940704346</t>
   </si>
   <si>
     <t xml:space="preserve">1.54453217983246</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">1.4838262796402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32338917255402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3294597864151</t>
+    <t xml:space="preserve">1.32338905334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32945990562439</t>
   </si>
   <si>
     <t xml:space="preserve">1.3884311914444</t>
@@ -350,10 +350,10 @@
     <t xml:space="preserve">1.35981273651123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33726477622986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31124806404114</t>
+    <t xml:space="preserve">1.33726489543915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31124794483185</t>
   </si>
   <si>
     <t xml:space="preserve">1.30084121227264</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">1.30257570743561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36154723167419</t>
+    <t xml:space="preserve">1.3615471124649</t>
   </si>
   <si>
     <t xml:space="preserve">1.37802445888519</t>
@@ -371,13 +371,13 @@
     <t xml:space="preserve">1.3823606967926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39623618125916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37715744972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40490865707397</t>
+    <t xml:space="preserve">1.39623630046844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.377157330513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4049084186554</t>
   </si>
   <si>
     <t xml:space="preserve">1.39450180530548</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">1.38062620162964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36588335037231</t>
+    <t xml:space="preserve">1.3658834695816</t>
   </si>
   <si>
     <t xml:space="preserve">1.3563437461853</t>
@@ -410,10 +410,10 @@
     <t xml:space="preserve">1.35460937023163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34333550930023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33119416236877</t>
+    <t xml:space="preserve">1.34333539009094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33119428157806</t>
   </si>
   <si>
     <t xml:space="preserve">1.32685804367065</t>
@@ -422,10 +422,10 @@
     <t xml:space="preserve">1.30170845985413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30777907371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34767162799835</t>
+    <t xml:space="preserve">1.3077791929245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34767150878906</t>
   </si>
   <si>
     <t xml:space="preserve">1.34506988525391</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">1.35547661781311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34940612316132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33813202381134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34853875637054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41704976558685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40317404270172</t>
+    <t xml:space="preserve">1.34940600395203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33813190460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34853863716125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41704964637756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40317416191101</t>
   </si>
   <si>
     <t xml:space="preserve">1.39536905288696</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">1.36501610279083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38322794437408</t>
+    <t xml:space="preserve">1.38322782516479</t>
   </si>
   <si>
     <t xml:space="preserve">1.36761784553528</t>
@@ -491,31 +491,31 @@
     <t xml:space="preserve">1.40924477577209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42572212219238</t>
+    <t xml:space="preserve">1.42572224140167</t>
   </si>
   <si>
     <t xml:space="preserve">1.35114049911499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35894548892975</t>
+    <t xml:space="preserve">1.35894560813904</t>
   </si>
   <si>
     <t xml:space="preserve">1.34680426120758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36414873600006</t>
+    <t xml:space="preserve">1.36414885520935</t>
   </si>
   <si>
     <t xml:space="preserve">1.36241436004639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33032703399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32078742980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3190530538559</t>
+    <t xml:space="preserve">1.33032715320587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32078754901886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31905317306519</t>
   </si>
   <si>
     <t xml:space="preserve">1.31992018222809</t>
@@ -530,13 +530,13 @@
     <t xml:space="preserve">1.26181602478027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2921689748764</t>
+    <t xml:space="preserve">1.29216909408569</t>
   </si>
   <si>
     <t xml:space="preserve">1.23146307468414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21758759021759</t>
+    <t xml:space="preserve">1.2175874710083</t>
   </si>
   <si>
     <t xml:space="preserve">1.24880766868591</t>
@@ -554,13 +554,13 @@
     <t xml:space="preserve">1.11872339248657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13086473941803</t>
+    <t xml:space="preserve">1.13086462020874</t>
   </si>
   <si>
     <t xml:space="preserve">1.12305963039398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13346636295319</t>
+    <t xml:space="preserve">1.13346648216248</t>
   </si>
   <si>
     <t xml:space="preserve">1.11438727378845</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">1.10398054122925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15427982807159</t>
+    <t xml:space="preserve">1.1542797088623</t>
   </si>
   <si>
     <t xml:space="preserve">1.16295206546783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16208493709564</t>
+    <t xml:space="preserve">1.16208481788635</t>
   </si>
   <si>
     <t xml:space="preserve">1.17856204509735</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">1.20544612407684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23493194580078</t>
+    <t xml:space="preserve">1.23493182659149</t>
   </si>
   <si>
     <t xml:space="preserve">1.24533867835999</t>
@@ -638,19 +638,19 @@
     <t xml:space="preserve">1.39883804321289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38669669628143</t>
+    <t xml:space="preserve">1.38669681549072</t>
   </si>
   <si>
     <t xml:space="preserve">1.35721111297607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34593725204468</t>
+    <t xml:space="preserve">1.34593713283539</t>
   </si>
   <si>
     <t xml:space="preserve">1.33292853832245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28870010375977</t>
+    <t xml:space="preserve">1.28869998455048</t>
   </si>
   <si>
     <t xml:space="preserve">1.25747990608215</t>
@@ -665,25 +665,25 @@
     <t xml:space="preserve">1.22712683677673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25661265850067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22365808486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2227908372879</t>
+    <t xml:space="preserve">1.25661253929138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2236579656601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22279071807861</t>
   </si>
   <si>
     <t xml:space="preserve">1.25314378738403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22625970840454</t>
+    <t xml:space="preserve">1.22625982761383</t>
   </si>
   <si>
     <t xml:space="preserve">1.21325135231018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20891511440277</t>
+    <t xml:space="preserve">1.20891523361206</t>
   </si>
   <si>
     <t xml:space="preserve">1.20457899570465</t>
@@ -692,10 +692,10 @@
     <t xml:space="preserve">1.21585297584534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21672022342682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19070339202881</t>
+    <t xml:space="preserve">1.21672010421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19070327281952</t>
   </si>
   <si>
     <t xml:space="preserve">1.20197737216949</t>
@@ -704,10 +704,10 @@
     <t xml:space="preserve">1.18810176849365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19157063961029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20284450054169</t>
+    <t xml:space="preserve">1.191570520401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20284461975098</t>
   </si>
   <si>
     <t xml:space="preserve">1.19243776798248</t>
@@ -716,16 +716,16 @@
     <t xml:space="preserve">1.2340646982193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27742612361908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27222275733948</t>
+    <t xml:space="preserve">1.27742624282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27222263813019</t>
   </si>
   <si>
     <t xml:space="preserve">1.2982394695282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26355040073395</t>
+    <t xml:space="preserve">1.26355051994324</t>
   </si>
   <si>
     <t xml:space="preserve">1.24273693561554</t>
@@ -740,25 +740,25 @@
     <t xml:space="preserve">1.24794042110443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2496749162674</t>
+    <t xml:space="preserve">1.24967479705811</t>
   </si>
   <si>
     <t xml:space="preserve">1.29043459892273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29303622245789</t>
+    <t xml:space="preserve">1.29303634166718</t>
   </si>
   <si>
     <t xml:space="preserve">1.31818580627441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30691170692444</t>
+    <t xml:space="preserve">1.30691194534302</t>
   </si>
   <si>
     <t xml:space="preserve">1.27309000492096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24013519287109</t>
+    <t xml:space="preserve">1.24013531208038</t>
   </si>
   <si>
     <t xml:space="preserve">1.27916061878204</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">1.26528489589691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28436398506165</t>
+    <t xml:space="preserve">1.28436386585236</t>
   </si>
   <si>
     <t xml:space="preserve">1.27482438087463</t>
@@ -782,16 +782,16 @@
     <t xml:space="preserve">1.28523111343384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2869656085968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3398665189743</t>
+    <t xml:space="preserve">1.28696548938751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33986639976501</t>
   </si>
   <si>
     <t xml:space="preserve">1.33899927139282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41184639930725</t>
+    <t xml:space="preserve">1.41184651851654</t>
   </si>
   <si>
     <t xml:space="preserve">1.57835412025452</t>
@@ -812,19 +812,19 @@
     <t xml:space="preserve">1.50203800201416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4786229133606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43352699279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40577590465546</t>
+    <t xml:space="preserve">1.47862303256989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43352711200714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40577578544617</t>
   </si>
   <si>
     <t xml:space="preserve">1.38496232032776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47168517112732</t>
+    <t xml:space="preserve">1.47168505191803</t>
   </si>
   <si>
     <t xml:space="preserve">1.48729526996613</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">1.45694208145142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46821618080139</t>
+    <t xml:space="preserve">1.4682160615921</t>
   </si>
   <si>
     <t xml:space="preserve">1.45867669582367</t>
@@ -848,19 +848,19 @@
     <t xml:space="preserve">1.45607495307922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49076390266418</t>
+    <t xml:space="preserve">1.49076402187347</t>
   </si>
   <si>
     <t xml:space="preserve">1.47341954708099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52892196178436</t>
+    <t xml:space="preserve">1.52892208099365</t>
   </si>
   <si>
     <t xml:space="preserve">1.50637412071228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57488524913788</t>
+    <t xml:space="preserve">1.57488512992859</t>
   </si>
   <si>
     <t xml:space="preserve">1.58269023895264</t>
@@ -881,10 +881,10 @@
     <t xml:space="preserve">1.51157760620117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48902952671051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48035740852356</t>
+    <t xml:space="preserve">1.4890296459198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48035728931427</t>
   </si>
   <si>
     <t xml:space="preserve">1.48816239833832</t>
@@ -893,28 +893,28 @@
     <t xml:space="preserve">1.51591360569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56881463527679</t>
+    <t xml:space="preserve">1.5688145160675</t>
   </si>
   <si>
     <t xml:space="preserve">1.57054901123047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64686501026154</t>
+    <t xml:space="preserve">1.64686512947083</t>
   </si>
   <si>
     <t xml:space="preserve">1.78648853302002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7604718208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85933566093445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8662736415863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84199118614197</t>
+    <t xml:space="preserve">1.76047170162201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85933589935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86627352237701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84199130535126</t>
   </si>
   <si>
     <t xml:space="preserve">2.15245866775513</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">2.05879807472229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00329542160034</t>
+    <t xml:space="preserve">2.00329566001892</t>
   </si>
   <si>
     <t xml:space="preserve">1.95126187801361</t>
@@ -938,25 +938,25 @@
     <t xml:space="preserve">2.01543641090393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98074734210968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9044314622879</t>
+    <t xml:space="preserve">1.98074758052826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90443181991577</t>
   </si>
   <si>
     <t xml:space="preserve">1.90790057182312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91657257080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90616607666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84892904758453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87321138381958</t>
+    <t xml:space="preserve">1.91657280921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90616595745087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84892892837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87321150302887</t>
   </si>
   <si>
     <t xml:space="preserve">1.83158433437347</t>
@@ -965,19 +965,19 @@
     <t xml:space="preserve">1.84719455242157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93218290805817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93738627433777</t>
+    <t xml:space="preserve">1.93218314647675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93738603591919</t>
   </si>
   <si>
     <t xml:space="preserve">1.92524516582489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94258975982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97727870941162</t>
+    <t xml:space="preserve">1.94258952140808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97727882862091</t>
   </si>
   <si>
     <t xml:space="preserve">2.0206401348114</t>
@@ -989,19 +989,19 @@
     <t xml:space="preserve">2.01196765899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03971910476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01370239257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99462330341339</t>
+    <t xml:space="preserve">2.03971886634827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01370215415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99462306499481</t>
   </si>
   <si>
     <t xml:space="preserve">1.94432413578033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90269696712494</t>
+    <t xml:space="preserve">1.90269720554352</t>
   </si>
   <si>
     <t xml:space="preserve">1.82117772102356</t>
@@ -1013,19 +1013,19 @@
     <t xml:space="preserve">1.72144663333893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67114746570587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69976592063904</t>
+    <t xml:space="preserve">1.67114758491516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69976603984833</t>
   </si>
   <si>
     <t xml:space="preserve">1.68762469291687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67895245552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63992738723755</t>
+    <t xml:space="preserve">1.67895233631134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63992726802826</t>
   </si>
   <si>
     <t xml:space="preserve">1.64773225784302</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">1.62865316867828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62691879272461</t>
+    <t xml:space="preserve">1.62691867351532</t>
   </si>
   <si>
     <t xml:space="preserve">1.60350370407104</t>
@@ -1046,13 +1046,13 @@
     <t xml:space="preserve">1.63905990123749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64859938621521</t>
+    <t xml:space="preserve">1.6485995054245</t>
   </si>
   <si>
     <t xml:space="preserve">1.6650767326355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69109380245209</t>
+    <t xml:space="preserve">1.6910936832428</t>
   </si>
   <si>
     <t xml:space="preserve">1.72925162315369</t>
@@ -1070,7 +1070,7 @@
     <t xml:space="preserve">1.66681122779846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68155407905579</t>
+    <t xml:space="preserve">1.68155419826508</t>
   </si>
   <si>
     <t xml:space="preserve">1.68935918807983</t>
@@ -1079,16 +1079,16 @@
     <t xml:space="preserve">1.67721796035767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63385653495789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62171542644501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65727186203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71537590026855</t>
+    <t xml:space="preserve">1.63385665416718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6217155456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65727174282074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71537601947784</t>
   </si>
   <si>
     <t xml:space="preserve">1.66854572296143</t>
@@ -1118,37 +1118,37 @@
     <t xml:space="preserve">1.77348029613495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80383312702179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93391752243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88188374042511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95559799671173</t>
+    <t xml:space="preserve">1.80383324623108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93391728401184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8818838596344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95559823513031</t>
   </si>
   <si>
     <t xml:space="preserve">1.88621973991394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81684160232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89489197731018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80816924571991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82984983921051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85153067111969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7821524143219</t>
+    <t xml:space="preserve">1.81684172153473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89489221572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8081693649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8298499584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85153079032898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78215253353119</t>
   </si>
   <si>
     <t xml:space="preserve">1.81250548362732</t>
@@ -1157,28 +1157,28 @@
     <t xml:space="preserve">1.79082489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73445510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76480793952942</t>
+    <t xml:space="preserve">1.73445498943329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76480805873871</t>
   </si>
   <si>
     <t xml:space="preserve">1.96860635280609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89922821521759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89055597782135</t>
+    <t xml:space="preserve">1.89922833442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89055585861206</t>
   </si>
   <si>
     <t xml:space="preserve">1.8775475025177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8341863155365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84285843372345</t>
+    <t xml:space="preserve">1.83418619632721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84285831451416</t>
   </si>
   <si>
     <t xml:space="preserve">1.82551383972168</t>
@@ -1187,22 +1187,22 @@
     <t xml:space="preserve">1.83852219581604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86020290851593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97294282913208</t>
+    <t xml:space="preserve">1.86020302772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97294235229492</t>
   </si>
   <si>
     <t xml:space="preserve">1.98161494731903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92958116531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98595094680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04665660858154</t>
+    <t xml:space="preserve">1.92958092689514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98595070838928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04665684700012</t>
   </si>
   <si>
     <t xml:space="preserve">2.03364849090576</t>
@@ -1211,10 +1211,10 @@
     <t xml:space="preserve">2.042320728302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.072674036026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08134579658508</t>
+    <t xml:space="preserve">2.07267379760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08134603500366</t>
   </si>
   <si>
     <t xml:space="preserve">2.1116988658905</t>
@@ -1229,19 +1229,19 @@
     <t xml:space="preserve">2.1854133605957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33717823028564</t>
+    <t xml:space="preserve">2.33717799186707</t>
   </si>
   <si>
     <t xml:space="preserve">2.3024890422821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2808084487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21142983436584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3068253993988</t>
+    <t xml:space="preserve">2.28080821037292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21143007278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30682516098022</t>
   </si>
   <si>
     <t xml:space="preserve">2.28514456748962</t>
@@ -1253,10 +1253,10 @@
     <t xml:space="preserve">2.48894286155701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59301018714905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38921165466309</t>
+    <t xml:space="preserve">2.59300994873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38921189308167</t>
   </si>
   <si>
     <t xml:space="preserve">2.49761533737183</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">2.71442222595215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76645588874817</t>
+    <t xml:space="preserve">2.76645565032959</t>
   </si>
   <si>
     <t xml:space="preserve">2.83583378791809</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">2.91388416290283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92255640029907</t>
+    <t xml:space="preserve">2.92255663871765</t>
   </si>
   <si>
     <t xml:space="preserve">2.93122911453247</t>
@@ -1295,16 +1295,16 @@
     <t xml:space="preserve">3.10033845901489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23909473419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25210332870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21741390228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25643944740295</t>
+    <t xml:space="preserve">3.23909449577332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25210309028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21741414070129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25643968582153</t>
   </si>
   <si>
     <t xml:space="preserve">3.36050653457642</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">3.20874190330505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36917901039124</t>
+    <t xml:space="preserve">3.36917877197266</t>
   </si>
   <si>
     <t xml:space="preserve">3.26511144638062</t>
@@ -1340,10 +1340,10 @@
     <t xml:space="preserve">3.55563282966614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51227188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62934708595276</t>
+    <t xml:space="preserve">3.51227164268494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62934684753418</t>
   </si>
   <si>
     <t xml:space="preserve">3.6640362739563</t>
@@ -1352,10 +1352,10 @@
     <t xml:space="preserve">3.73341417312622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80712866783142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90686011314392</t>
+    <t xml:space="preserve">3.80712842941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90685963630676</t>
   </si>
   <si>
     <t xml:space="preserve">4.07596921920776</t>
@@ -1367,19 +1367,19 @@
     <t xml:space="preserve">4.09765005111694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86783504486084</t>
+    <t xml:space="preserve">3.86783456802368</t>
   </si>
   <si>
     <t xml:space="preserve">4.0412802696228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94588565826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97190189361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7117338180542</t>
+    <t xml:space="preserve">3.94588470458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97190141677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71173405647278</t>
   </si>
   <si>
     <t xml:space="preserve">3.91986799240112</t>
@@ -1388,19 +1388,19 @@
     <t xml:space="preserve">4.07163333892822</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24941444396973</t>
+    <t xml:space="preserve">4.24941492080688</t>
   </si>
   <si>
     <t xml:space="preserve">4.25375080108643</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28410387039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62232208251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57896137237549</t>
+    <t xml:space="preserve">4.284104347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62232255935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57896184921265</t>
   </si>
   <si>
     <t xml:space="preserve">4.74373435974121</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">4.87381839752197</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31879329681396</t>
+    <t xml:space="preserve">4.31879281997681</t>
   </si>
   <si>
     <t xml:space="preserve">4.80444049835205</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">5.01257514953613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0385913848877</t>
+    <t xml:space="preserve">5.03859233856201</t>
   </si>
   <si>
     <t xml:space="preserve">4.91718006134033</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">4.85647392272949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89116334915161</t>
+    <t xml:space="preserve">4.89116287231445</t>
   </si>
   <si>
     <t xml:space="preserve">4.83045768737793</t>
@@ -1454,40 +1454,40 @@
     <t xml:space="preserve">4.76107883453369</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54427194595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70904493331909</t>
+    <t xml:space="preserve">4.54427242279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70904541015625</t>
   </si>
   <si>
     <t xml:space="preserve">4.60497808456421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58763360977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64833974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61365079879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53559923171997</t>
+    <t xml:space="preserve">4.58763313293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64833927154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61365032196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53559970855713</t>
   </si>
   <si>
     <t xml:space="preserve">4.47489356994629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40551614761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18437242507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1887092590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24074268341064</t>
+    <t xml:space="preserve">4.40551519393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1843729019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18870878219604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24074220657349</t>
   </si>
   <si>
     <t xml:space="preserve">4.084641456604</t>
@@ -1496,13 +1496,13 @@
     <t xml:space="preserve">3.9285409450531</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91553163528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85916233062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7811119556427</t>
+    <t xml:space="preserve">3.91553211212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85916185379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78111171722412</t>
   </si>
   <si>
     <t xml:space="preserve">4.14101123809814</t>
@@ -1529,19 +1529,19 @@
     <t xml:space="preserve">3.03529620170593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04830455780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07865762710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96158170700073</t>
+    <t xml:space="preserve">3.04830479621887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07865738868713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96158194541931</t>
   </si>
   <si>
     <t xml:space="preserve">2.89653992652893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90521192550659</t>
+    <t xml:space="preserve">2.90521216392517</t>
   </si>
   <si>
     <t xml:space="preserve">3.02662420272827</t>
@@ -1553,25 +1553,25 @@
     <t xml:space="preserve">2.80548071861267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88786768913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04396843910217</t>
+    <t xml:space="preserve">2.88786745071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04396867752075</t>
   </si>
   <si>
     <t xml:space="preserve">3.2607753276825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24343085289001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19139719009399</t>
+    <t xml:space="preserve">3.24343109130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19139742851257</t>
   </si>
   <si>
     <t xml:space="preserve">3.42554879188538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43855690956116</t>
+    <t xml:space="preserve">3.43855714797974</t>
   </si>
   <si>
     <t xml:space="preserve">3.39519548416138</t>
@@ -1586,19 +1586,19 @@
     <t xml:space="preserve">2.86618685722351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93990159034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88353133201599</t>
+    <t xml:space="preserve">2.93990135192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88353157043457</t>
   </si>
   <si>
     <t xml:space="preserve">2.97459053993225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02228760719299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38218760490417</t>
+    <t xml:space="preserve">3.02228784561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3821873664856</t>
   </si>
   <si>
     <t xml:space="preserve">3.32148122787476</t>
@@ -1607,10 +1607,10 @@
     <t xml:space="preserve">3.15670824050903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11768293380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08732986450195</t>
+    <t xml:space="preserve">3.11768269538879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08733010292053</t>
   </si>
   <si>
     <t xml:space="preserve">3.06564927101135</t>
@@ -1622,10 +1622,10 @@
     <t xml:space="preserve">2.68840527534485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73176670074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63203573226929</t>
+    <t xml:space="preserve">2.73176693916321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63203549385071</t>
   </si>
   <si>
     <t xml:space="preserve">2.98759889602661</t>
@@ -1640,13 +1640,13 @@
     <t xml:space="preserve">3.3084728717804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17838859558105</t>
+    <t xml:space="preserve">3.17838883399963</t>
   </si>
   <si>
     <t xml:space="preserve">3.10467433929443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16104435920715</t>
+    <t xml:space="preserve">3.16104412078857</t>
   </si>
   <si>
     <t xml:space="preserve">3.330153465271</t>
@@ -1655,10 +1655,10 @@
     <t xml:space="preserve">3.46023774147034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5903217792511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88517951965332</t>
+    <t xml:space="preserve">3.59032154083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88517904281616</t>
   </si>
   <si>
     <t xml:space="preserve">3.90252375602722</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">4.10198640823364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.145348072052</t>
+    <t xml:space="preserve">4.14534759521484</t>
   </si>
   <si>
     <t xml:space="preserve">4.1323390007019</t>
@@ -1685,10 +1685,10 @@
     <t xml:space="preserve">3.95889353752136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82447338104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96756625175476</t>
+    <t xml:space="preserve">3.82447361946106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9675657749176</t>
   </si>
   <si>
     <t xml:space="preserve">3.9415488243103</t>
@@ -1697,10 +1697,10 @@
     <t xml:space="preserve">3.99791860580444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00659084320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06296110153198</t>
+    <t xml:space="preserve">4.00659132003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06296062469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.05862474441528</t>
@@ -1709,34 +1709,34 @@
     <t xml:space="preserve">4.01526355743408</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09331321716309</t>
+    <t xml:space="preserve">4.09331369400024</t>
   </si>
   <si>
     <t xml:space="preserve">4.03260803222656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98924660682678</t>
+    <t xml:space="preserve">3.98924612998962</t>
   </si>
   <si>
     <t xml:space="preserve">3.92420482635498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82880926132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75943112373352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74642276763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56864094734192</t>
+    <t xml:space="preserve">3.82880973815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7594313621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74642300605774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5686411857605</t>
   </si>
   <si>
     <t xml:space="preserve">3.77677583694458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24507856369019</t>
+    <t xml:space="preserve">4.24507904052734</t>
   </si>
   <si>
     <t xml:space="preserve">4.17136430740356</t>
@@ -1748,22 +1748,22 @@
     <t xml:space="preserve">4.06729698181152</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16269159317017</t>
+    <t xml:space="preserve">4.16269207000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.21906137466431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23207092285156</t>
+    <t xml:space="preserve">4.2320704460144</t>
   </si>
   <si>
     <t xml:space="preserve">4.20171689987183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68302822113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88249063491821</t>
+    <t xml:space="preserve">4.68302869796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88249111175537</t>
   </si>
   <si>
     <t xml:space="preserve">4.76975107192993</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">4.39684343338013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91119599342346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04995250701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27009868621826</t>
+    <t xml:space="preserve">3.91119647026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04995203018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2700982093811</t>
   </si>
   <si>
     <t xml:space="preserve">4.12285375595093</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">4.01130437850952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91760349273682</t>
+    <t xml:space="preserve">3.91760301589966</t>
   </si>
   <si>
     <t xml:space="preserve">4.22547912597656</t>
@@ -1808,19 +1808,19 @@
     <t xml:space="preserve">4.00684213638306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8328263759613</t>
+    <t xml:space="preserve">3.83282613754272</t>
   </si>
   <si>
     <t xml:space="preserve">3.85513615608215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8595974445343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93098974227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83728837966919</t>
+    <t xml:space="preserve">3.85959792137146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93098926544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83728814125061</t>
   </si>
   <si>
     <t xml:space="preserve">4.01576662063599</t>
@@ -1832,13 +1832,13 @@
     <t xml:space="preserve">3.95776081085205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79266858100891</t>
+    <t xml:space="preserve">3.79266834259033</t>
   </si>
   <si>
     <t xml:space="preserve">3.74358701705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76143479347229</t>
+    <t xml:space="preserve">3.76143455505371</t>
   </si>
   <si>
     <t xml:space="preserve">3.61419010162354</t>
@@ -1853,13 +1853,13 @@
     <t xml:space="preserve">3.48479294776917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67219519615173</t>
+    <t xml:space="preserve">3.67219543457031</t>
   </si>
   <si>
     <t xml:space="preserve">3.59634208679199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58741807937622</t>
+    <t xml:space="preserve">3.5874183177948</t>
   </si>
   <si>
     <t xml:space="preserve">3.64096164703369</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">3.52495074272156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41786360740662</t>
+    <t xml:space="preserve">3.41786336898804</t>
   </si>
   <si>
     <t xml:space="preserve">3.44909739494324</t>
@@ -1895,19 +1895,19 @@
     <t xml:space="preserve">3.41340160369873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42678761482239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36878204345703</t>
+    <t xml:space="preserve">3.42678737640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36878228187561</t>
   </si>
   <si>
     <t xml:space="preserve">3.34647226333618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31523847579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32862424850464</t>
+    <t xml:space="preserve">3.31523823738098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32862448692322</t>
   </si>
   <si>
     <t xml:space="preserve">3.36432003974915</t>
@@ -1943,10 +1943,10 @@
     <t xml:space="preserve">3.33308601379395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35093402862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52941274642944</t>
+    <t xml:space="preserve">3.35093426704407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52941250801086</t>
   </si>
   <si>
     <t xml:space="preserve">3.65880942344666</t>
@@ -1955,10 +1955,10 @@
     <t xml:space="preserve">3.71235322952271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81051635742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80605411529541</t>
+    <t xml:space="preserve">3.81051659584045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80605435371399</t>
   </si>
   <si>
     <t xml:space="preserve">3.7658965587616</t>
@@ -1973,40 +1973,40 @@
     <t xml:space="preserve">3.4669451713562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62757587432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78374409675598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69004344940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7078914642334</t>
+    <t xml:space="preserve">3.62757611274719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78374433517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69004368782043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70789122581482</t>
   </si>
   <si>
     <t xml:space="preserve">3.67665719985962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73912477493286</t>
+    <t xml:space="preserve">3.73912501335144</t>
   </si>
   <si>
     <t xml:space="preserve">3.68558144569397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66773343086243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69896697998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7212769985199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72573924064636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62311387062073</t>
+    <t xml:space="preserve">3.66773366928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69896721839905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72127723693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72573947906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62311363220215</t>
   </si>
   <si>
     <t xml:space="preserve">3.60972809791565</t>
@@ -2021,7 +2021,7 @@
     <t xml:space="preserve">3.96668481826782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73466300964355</t>
+    <t xml:space="preserve">3.73466277122498</t>
   </si>
   <si>
     <t xml:space="preserve">3.69450497627258</t>
@@ -2039,25 +2039,25 @@
     <t xml:space="preserve">3.57849431037903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56510806083679</t>
+    <t xml:space="preserve">3.56510829925537</t>
   </si>
   <si>
     <t xml:space="preserve">3.93991351127625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06038665771484</t>
+    <t xml:space="preserve">4.06038618087769</t>
   </si>
   <si>
     <t xml:space="preserve">3.91314196586609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98899435997009</t>
+    <t xml:space="preserve">3.98899483680725</t>
   </si>
   <si>
     <t xml:space="preserve">3.98007082939148</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12731599807739</t>
+    <t xml:space="preserve">4.12731552124023</t>
   </si>
   <si>
     <t xml:space="preserve">4.05146217346191</t>
@@ -2084,13 +2084,13 @@
     <t xml:space="preserve">3.93545150756836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89083194732666</t>
+    <t xml:space="preserve">3.8908314704895</t>
   </si>
   <si>
     <t xml:space="preserve">4.07823419570923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19424438476562</t>
+    <t xml:space="preserve">4.19424486160278</t>
   </si>
   <si>
     <t xml:space="preserve">4.00238084793091</t>
@@ -2102,13 +2102,13 @@
     <t xml:space="preserve">4.08715772628784</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21655464172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46196269989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53335428237915</t>
+    <t xml:space="preserve">4.21655511856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46196317672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53335380554199</t>
   </si>
   <si>
     <t xml:space="preserve">4.64044094085693</t>
@@ -2117,19 +2117,19 @@
     <t xml:space="preserve">4.58689785003662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64936494827271</t>
+    <t xml:space="preserve">4.64936542510986</t>
   </si>
   <si>
     <t xml:space="preserve">4.7564525604248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78322458267212</t>
+    <t xml:space="preserve">4.78322410583496</t>
   </si>
   <si>
     <t xml:space="preserve">4.68506097793579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83676815032959</t>
+    <t xml:space="preserve">4.83676767349243</t>
   </si>
   <si>
     <t xml:space="preserve">4.81892013549805</t>
@@ -2138,13 +2138,13 @@
     <t xml:space="preserve">4.90815925598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00632238388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89923477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85461521148682</t>
+    <t xml:space="preserve">5.00632190704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89923524856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85461568832397</t>
   </si>
   <si>
     <t xml:space="preserve">4.9795503616333</t>
@@ -2168,10 +2168,10 @@
     <t xml:space="preserve">4.76537656784058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82784414291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80999612808228</t>
+    <t xml:space="preserve">4.82784366607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80999565124512</t>
   </si>
   <si>
     <t xml:space="preserve">4.94385480880737</t>
@@ -2180,13 +2180,13 @@
     <t xml:space="preserve">5.06878995895386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.997398853302</t>
+    <t xml:space="preserve">4.99739837646484</t>
   </si>
   <si>
     <t xml:space="preserve">5.23834466934204</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45251846313477</t>
+    <t xml:space="preserve">5.45251893997192</t>
   </si>
   <si>
     <t xml:space="preserve">5.83624744415283</t>
@@ -2201,46 +2201,46 @@
     <t xml:space="preserve">5.15802955627441</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88138675689697</t>
+    <t xml:space="preserve">4.88138723373413</t>
   </si>
   <si>
     <t xml:space="preserve">4.70290899276733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71183300018311</t>
+    <t xml:space="preserve">4.71183347702026</t>
   </si>
   <si>
     <t xml:space="preserve">4.73860454559326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63151741027832</t>
+    <t xml:space="preserve">4.63151788711548</t>
   </si>
   <si>
     <t xml:space="preserve">4.67613697052002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56012630462646</t>
+    <t xml:space="preserve">4.56012582778931</t>
   </si>
   <si>
     <t xml:space="preserve">4.41734313964844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14516401290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02022886276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98453259468079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94883704185486</t>
+    <t xml:space="preserve">4.14516353607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02022838592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98453307151794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94883751869202</t>
   </si>
   <si>
     <t xml:space="preserve">3.8015923500061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12783598899841</t>
+    <t xml:space="preserve">3.12783575057983</t>
   </si>
   <si>
     <t xml:space="preserve">3.15906977653503</t>
@@ -2249,13 +2249,13 @@
     <t xml:space="preserve">3.25277090072632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72625923156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75749325752258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44961738586426</t>
+    <t xml:space="preserve">2.72625946998596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.757493019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44961762428284</t>
   </si>
   <si>
     <t xml:space="preserve">2.45854163169861</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">1.99895930290222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10604619979858</t>
+    <t xml:space="preserve">2.10604643821716</t>
   </si>
   <si>
     <t xml:space="preserve">2.2577531337738</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">2.45407962799072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46300339698792</t>
+    <t xml:space="preserve">2.46300363540649</t>
   </si>
   <si>
     <t xml:space="preserve">2.56116652488708</t>
@@ -2300,31 +2300,31 @@
     <t xml:space="preserve">2.73964524269104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23938512802124</t>
+    <t xml:space="preserve">3.23938536643982</t>
   </si>
   <si>
     <t xml:space="preserve">3.20368933677673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10998773574829</t>
+    <t xml:space="preserve">3.10998797416687</t>
   </si>
   <si>
     <t xml:space="preserve">2.91812372207642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85119414329529</t>
+    <t xml:space="preserve">2.85119438171387</t>
   </si>
   <si>
     <t xml:space="preserve">2.99843883514404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93597149848938</t>
+    <t xml:space="preserve">2.93597173690796</t>
   </si>
   <si>
     <t xml:space="preserve">2.94489550590515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89135193824768</t>
+    <t xml:space="preserve">2.8913516998291</t>
   </si>
   <si>
     <t xml:space="preserve">2.97612929344177</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">3.00290107727051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13229775428772</t>
+    <t xml:space="preserve">3.1322979927063</t>
   </si>
   <si>
     <t xml:space="preserve">3.0118248462677</t>
@@ -70183,7 +70183,7 @@
     </row>
     <row r="2525">
       <c r="A2525" s="1" t="n">
-        <v>45994.6912615741</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2525" t="n">
         <v>46966</v>
@@ -70204,6 +70204,32 @@
         <v>1402</v>
       </c>
       <c r="H2525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" s="1" t="n">
+        <v>45995.6912268518</v>
+      </c>
+      <c r="B2526" t="n">
+        <v>88599</v>
+      </c>
+      <c r="C2526" t="n">
+        <v>8.06999969482422</v>
+      </c>
+      <c r="D2526" t="n">
+        <v>7.8899998664856</v>
+      </c>
+      <c r="E2526" t="n">
+        <v>8.06999969482422</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>7.92000007629395</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>1385</v>
+      </c>
+      <c r="H2526" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="1405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="1406">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95473051071167</t>
+    <t xml:space="preserve">1.95473074913025</t>
   </si>
   <si>
     <t xml:space="preserve">FM.MI</t>
@@ -47,43 +47,43 @@
     <t xml:space="preserve">1.95993411540985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90963470935822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8558669090271</t>
+    <t xml:space="preserve">1.9096348285675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85586678981781</t>
   </si>
   <si>
     <t xml:space="preserve">1.86453914642334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68415570259094</t>
+    <t xml:space="preserve">1.68415582180023</t>
   </si>
   <si>
     <t xml:space="preserve">1.76914405822754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74486172199249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69542980194092</t>
+    <t xml:space="preserve">1.74486184120178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69542968273163</t>
   </si>
   <si>
     <t xml:space="preserve">1.61824655532837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52285158634186</t>
+    <t xml:space="preserve">1.52285146713257</t>
   </si>
   <si>
     <t xml:space="preserve">1.47949004173279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34420251846313</t>
+    <t xml:space="preserve">1.34420263767242</t>
   </si>
   <si>
     <t xml:space="preserve">1.45434057712555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55233728885651</t>
+    <t xml:space="preserve">1.55233716964722</t>
   </si>
   <si>
     <t xml:space="preserve">1.48989689350128</t>
@@ -95,16 +95,16 @@
     <t xml:space="preserve">1.595698595047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51331198215485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53325819969177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.499436378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43005812168121</t>
+    <t xml:space="preserve">1.51331210136414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53325831890106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49943625926971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4300582408905</t>
   </si>
   <si>
     <t xml:space="preserve">1.40751028060913</t>
@@ -122,13 +122,13 @@
     <t xml:space="preserve">1.24186968803406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2071807384491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23059594631195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43873047828674</t>
+    <t xml:space="preserve">1.20718061923981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23059582710266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43873035907745</t>
   </si>
   <si>
     <t xml:space="preserve">1.39710342884064</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">1.48295903205872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46561455726624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5211169719696</t>
+    <t xml:space="preserve">1.46561443805695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52111709117889</t>
   </si>
   <si>
     <t xml:space="preserve">1.51678085327148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4942330121994</t>
+    <t xml:space="preserve">1.49423313140869</t>
   </si>
   <si>
     <t xml:space="preserve">1.47688841819763</t>
@@ -158,13 +158,13 @@
     <t xml:space="preserve">1.47515392303467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50984311103821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56014227867126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58702635765076</t>
+    <t xml:space="preserve">1.5098432302475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56014239788055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58702623844147</t>
   </si>
   <si>
     <t xml:space="preserve">1.55754053592682</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">1.55147004127502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61651206016541</t>
+    <t xml:space="preserve">1.61651194095612</t>
   </si>
   <si>
     <t xml:space="preserve">1.67374897003174</t>
@@ -200,13 +200,13 @@
     <t xml:space="preserve">1.63298940658569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60610544681549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53499257564545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49770188331604</t>
+    <t xml:space="preserve">1.6061053276062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53499269485474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49770200252533</t>
   </si>
   <si>
     <t xml:space="preserve">1.49683463573456</t>
@@ -215,37 +215,37 @@
     <t xml:space="preserve">1.48122453689575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41791701316833</t>
+    <t xml:space="preserve">1.41791713237762</t>
   </si>
   <si>
     <t xml:space="preserve">1.39970517158508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35200774669647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39190018177032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46041119098663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57228350639343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62952053546906</t>
+    <t xml:space="preserve">1.35200762748718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39190006256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46041107177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57228338718414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62952041625977</t>
   </si>
   <si>
     <t xml:space="preserve">1.60437095165253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60870707035065</t>
+    <t xml:space="preserve">1.60870695114136</t>
   </si>
   <si>
     <t xml:space="preserve">1.62518429756165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6598733663559</t>
+    <t xml:space="preserve">1.65987348556519</t>
   </si>
   <si>
     <t xml:space="preserve">1.58615911006927</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">1.60090184211731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58876085281372</t>
+    <t xml:space="preserve">1.58876073360443</t>
   </si>
   <si>
     <t xml:space="preserve">1.49249851703644</t>
@@ -275,19 +275,19 @@
     <t xml:space="preserve">1.46908330917358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56794726848602</t>
+    <t xml:space="preserve">1.56794738769531</t>
   </si>
   <si>
     <t xml:space="preserve">1.53932881355286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53065657615662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54106318950653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56968176364899</t>
+    <t xml:space="preserve">1.53065645694733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54106330871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5696816444397</t>
   </si>
   <si>
     <t xml:space="preserve">1.5471339225769</t>
@@ -296,22 +296,22 @@
     <t xml:space="preserve">1.55060279369354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56708025932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57401788234711</t>
+    <t xml:space="preserve">1.56708014011383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5740180015564</t>
   </si>
   <si>
     <t xml:space="preserve">1.5107102394104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59136247634888</t>
+    <t xml:space="preserve">1.59136259555817</t>
   </si>
   <si>
     <t xml:space="preserve">1.56100952625275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54453217983246</t>
+    <t xml:space="preserve">1.54453229904175</t>
   </si>
   <si>
     <t xml:space="preserve">1.45000445842743</t>
@@ -320,22 +320,22 @@
     <t xml:space="preserve">1.38929843902588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40057253837585</t>
+    <t xml:space="preserve">1.40057241916656</t>
   </si>
   <si>
     <t xml:space="preserve">1.3875640630722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44740271568298</t>
+    <t xml:space="preserve">1.44740283489227</t>
   </si>
   <si>
     <t xml:space="preserve">1.49163126945496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4838262796402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32338917255402</t>
+    <t xml:space="preserve">1.48382616043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32338929176331</t>
   </si>
   <si>
     <t xml:space="preserve">1.3294597864151</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">1.3884311914444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39016568660736</t>
+    <t xml:space="preserve">1.39016580581665</t>
   </si>
   <si>
     <t xml:space="preserve">1.35981273651123</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">1.31124794483185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30084121227264</t>
+    <t xml:space="preserve">1.30084133148193</t>
   </si>
   <si>
     <t xml:space="preserve">1.30257558822632</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">1.36154723167419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37802457809448</t>
+    <t xml:space="preserve">1.37802445888519</t>
   </si>
   <si>
     <t xml:space="preserve">1.38236057758331</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">1.40490853786469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39450180530548</t>
+    <t xml:space="preserve">1.39450192451477</t>
   </si>
   <si>
     <t xml:space="preserve">1.4040412902832</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">1.393634557724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42225313186646</t>
+    <t xml:space="preserve">1.42225301265717</t>
   </si>
   <si>
     <t xml:space="preserve">1.42832362651825</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">1.35634386539459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35460948944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34333539009094</t>
+    <t xml:space="preserve">1.35460937023163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34333550930023</t>
   </si>
   <si>
     <t xml:space="preserve">1.33119428157806</t>
@@ -422,10 +422,10 @@
     <t xml:space="preserve">1.30170857906342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30777907371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34767150878906</t>
+    <t xml:space="preserve">1.3077791929245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34767162799835</t>
   </si>
   <si>
     <t xml:space="preserve">1.34506988525391</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">1.33379578590393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37108659744263</t>
+    <t xml:space="preserve">1.37108671665192</t>
   </si>
   <si>
     <t xml:space="preserve">1.35547649860382</t>
@@ -443,19 +443,19 @@
     <t xml:space="preserve">1.34940588474274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33813214302063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34853875637054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41704976558685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40317404270172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39536905288696</t>
+    <t xml:space="preserve">1.33813202381134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34853863716125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41704964637756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40317416191101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39536893367767</t>
   </si>
   <si>
     <t xml:space="preserve">1.41097915172577</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">1.36501610279083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38322782516479</t>
+    <t xml:space="preserve">1.38322794437408</t>
   </si>
   <si>
     <t xml:space="preserve">1.36761784553528</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">1.41358077526093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42138600349426</t>
+    <t xml:space="preserve">1.42138588428497</t>
   </si>
   <si>
     <t xml:space="preserve">1.41271352767944</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">1.40924465656281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42572200298309</t>
+    <t xml:space="preserve">1.42572212219238</t>
   </si>
   <si>
     <t xml:space="preserve">1.35114049911499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35894560813904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34680426120758</t>
+    <t xml:space="preserve">1.35894548892975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34680438041687</t>
   </si>
   <si>
     <t xml:space="preserve">1.36414885520935</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">1.33032703399658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32078742980957</t>
+    <t xml:space="preserve">1.32078754901886</t>
   </si>
   <si>
     <t xml:space="preserve">1.3190530538559</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">1.17942941188812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26181602478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29216909408569</t>
+    <t xml:space="preserve">1.26181590557098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2921689748764</t>
   </si>
   <si>
     <t xml:space="preserve">1.23146307468414</t>
@@ -539,22 +539,22 @@
     <t xml:space="preserve">1.2175874710083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2488077878952</t>
+    <t xml:space="preserve">1.24880766868591</t>
   </si>
   <si>
     <t xml:space="preserve">1.22886145114899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18550002574921</t>
+    <t xml:space="preserve">1.18549990653992</t>
   </si>
   <si>
     <t xml:space="preserve">1.15774869918823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11872351169586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13086473941803</t>
+    <t xml:space="preserve">1.11872339248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13086462020874</t>
   </si>
   <si>
     <t xml:space="preserve">1.12305963039398</t>
@@ -566,16 +566,16 @@
     <t xml:space="preserve">1.11438727378845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11612164974213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11525464057922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09791016578674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09270656108856</t>
+    <t xml:space="preserve">1.11612176895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11525452136993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09791004657745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09270668029785</t>
   </si>
   <si>
     <t xml:space="preserve">1.07536208629608</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">1.10398066043854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15427982807159</t>
+    <t xml:space="preserve">1.1542797088623</t>
   </si>
   <si>
     <t xml:space="preserve">1.16295206546783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16208493709564</t>
+    <t xml:space="preserve">1.16208481788635</t>
   </si>
   <si>
     <t xml:space="preserve">1.17856216430664</t>
@@ -605,19 +605,19 @@
     <t xml:space="preserve">1.20544624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23493194580078</t>
+    <t xml:space="preserve">1.23493206501007</t>
   </si>
   <si>
     <t xml:space="preserve">1.24533867835999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21845459938049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19937574863434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20111012458801</t>
+    <t xml:space="preserve">1.2184544801712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19937562942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20111000537872</t>
   </si>
   <si>
     <t xml:space="preserve">1.22799408435822</t>
@@ -626,19 +626,19 @@
     <t xml:space="preserve">1.22192347049713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23666644096375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26875400543213</t>
+    <t xml:space="preserve">1.23666656017303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26875388622284</t>
   </si>
   <si>
     <t xml:space="preserve">1.38409507274628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39883804321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38669669628143</t>
+    <t xml:space="preserve">1.3988379240036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38669681549072</t>
   </si>
   <si>
     <t xml:space="preserve">1.35721099376678</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">1.33292865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28869998455048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25747978687286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23319756984711</t>
+    <t xml:space="preserve">1.28869986534119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25747990608215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2331976890564</t>
   </si>
   <si>
     <t xml:space="preserve">1.2444714307785</t>
@@ -665,13 +665,13 @@
     <t xml:space="preserve">1.22712695598602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25661265850067</t>
+    <t xml:space="preserve">1.25661277770996</t>
   </si>
   <si>
     <t xml:space="preserve">1.22365808486938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2227908372879</t>
+    <t xml:space="preserve">1.22279071807861</t>
   </si>
   <si>
     <t xml:space="preserve">1.25314378738403</t>
@@ -680,10 +680,10 @@
     <t xml:space="preserve">1.22625970840454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21325135231018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20891523361206</t>
+    <t xml:space="preserve">1.21325147151947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20891511440277</t>
   </si>
   <si>
     <t xml:space="preserve">1.20457899570465</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">1.21672022342682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19070327281952</t>
+    <t xml:space="preserve">1.19070339202881</t>
   </si>
   <si>
     <t xml:space="preserve">1.20197737216949</t>
@@ -707,25 +707,25 @@
     <t xml:space="preserve">1.191570520401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20284461975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19243764877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23406457901001</t>
+    <t xml:space="preserve">1.20284450054169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19243776798248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2340646982193</t>
   </si>
   <si>
     <t xml:space="preserve">1.27742612361908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27222287654877</t>
+    <t xml:space="preserve">1.27222275733948</t>
   </si>
   <si>
     <t xml:space="preserve">1.29823958873749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26355051994324</t>
+    <t xml:space="preserve">1.26355040073395</t>
   </si>
   <si>
     <t xml:space="preserve">1.24273705482483</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">1.22018897533417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24794042110443</t>
+    <t xml:space="preserve">1.24794030189514</t>
   </si>
   <si>
     <t xml:space="preserve">1.24967479705811</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">1.29043447971344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29303634166718</t>
+    <t xml:space="preserve">1.29303622245789</t>
   </si>
   <si>
     <t xml:space="preserve">1.31818568706512</t>
@@ -758,34 +758,34 @@
     <t xml:space="preserve">1.27309000492096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24013531208038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27916061878204</t>
+    <t xml:space="preserve">1.24013519287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27916049957275</t>
   </si>
   <si>
     <t xml:space="preserve">1.2704883813858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26528489589691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28436386585236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27482426166534</t>
+    <t xml:space="preserve">1.26528477668762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28436398506165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27482438087463</t>
   </si>
   <si>
     <t xml:space="preserve">1.26441764831543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28523123264313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2869656085968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33986639976501</t>
+    <t xml:space="preserve">1.28523099422455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28696548938751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3398665189743</t>
   </si>
   <si>
     <t xml:space="preserve">1.33899927139282</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">1.41184639930725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57835400104523</t>
+    <t xml:space="preserve">1.57835412025452</t>
   </si>
   <si>
     <t xml:space="preserve">1.51851534843445</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">1.49856913089752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50724148750305</t>
+    <t xml:space="preserve">1.50724136829376</t>
   </si>
   <si>
     <t xml:space="preserve">1.50203800201416</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">1.47168505191803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48729526996613</t>
+    <t xml:space="preserve">1.48729515075684</t>
   </si>
   <si>
     <t xml:space="preserve">1.47602117061615</t>
@@ -836,10 +836,10 @@
     <t xml:space="preserve">1.45694220066071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4682160615921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45867669582367</t>
+    <t xml:space="preserve">1.46821618080139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45867657661438</t>
   </si>
   <si>
     <t xml:space="preserve">1.45954382419586</t>
@@ -857,19 +857,19 @@
     <t xml:space="preserve">1.52892208099365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50637423992157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57488512992859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58269035816193</t>
+    <t xml:space="preserve">1.50637412071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57488524913788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58269023895264</t>
   </si>
   <si>
     <t xml:space="preserve">1.56187665462494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53585994243622</t>
+    <t xml:space="preserve">1.53585982322693</t>
   </si>
   <si>
     <t xml:space="preserve">1.48642802238464</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">1.49510014057159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51157748699188</t>
+    <t xml:space="preserve">1.51157760620117</t>
   </si>
   <si>
     <t xml:space="preserve">1.48902952671051</t>
@@ -887,34 +887,34 @@
     <t xml:space="preserve">1.48035740852356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48816239833832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51591360569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56881463527679</t>
+    <t xml:space="preserve">1.48816251754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51591372489929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5688145160675</t>
   </si>
   <si>
     <t xml:space="preserve">1.57054901123047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64686501026154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7864887714386</t>
+    <t xml:space="preserve">1.64686512947083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78648853302002</t>
   </si>
   <si>
     <t xml:space="preserve">1.7604718208313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85933601856232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86627340316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84199118614197</t>
+    <t xml:space="preserve">1.85933589935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8662736415863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84199142456055</t>
   </si>
   <si>
     <t xml:space="preserve">2.15245890617371</t>
@@ -926,10 +926,10 @@
     <t xml:space="preserve">2.05879807472229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00329566001892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95126175880432</t>
+    <t xml:space="preserve">2.00329542160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9512619972229</t>
   </si>
   <si>
     <t xml:space="preserve">2.05186009407043</t>
@@ -941,34 +941,34 @@
     <t xml:space="preserve">1.98074758052826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90443193912506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90790045261383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91657269001007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90616595745087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84892904758453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87321150302887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83158445358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84719479084015</t>
+    <t xml:space="preserve">1.90443181991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90790033340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91657280921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90616607666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84892892837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87321162223816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83158457279205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84719467163086</t>
   </si>
   <si>
     <t xml:space="preserve">1.93218290805817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93738639354706</t>
+    <t xml:space="preserve">1.93738615512848</t>
   </si>
   <si>
     <t xml:space="preserve">1.92524516582489</t>
@@ -977,37 +977,37 @@
     <t xml:space="preserve">1.94258952140808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97727882862091</t>
+    <t xml:space="preserve">1.97727859020233</t>
   </si>
   <si>
     <t xml:space="preserve">2.02063989639282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06920504570007</t>
+    <t xml:space="preserve">2.06920480728149</t>
   </si>
   <si>
     <t xml:space="preserve">2.01196765899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03971886634827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01370215415955</t>
+    <t xml:space="preserve">2.03971910476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01370239257812</t>
   </si>
   <si>
     <t xml:space="preserve">1.9946231842041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94432437419891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90269720554352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82117748260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91310381889343</t>
+    <t xml:space="preserve">1.94432413578033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90269708633423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82117760181427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91310405731201</t>
   </si>
   <si>
     <t xml:space="preserve">1.72144663333893</t>
@@ -1022,22 +1022,22 @@
     <t xml:space="preserve">1.68762469291687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67895257472992</t>
+    <t xml:space="preserve">1.67895245552063</t>
   </si>
   <si>
     <t xml:space="preserve">1.63992714881897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64773213863373</t>
+    <t xml:space="preserve">1.64773225784302</t>
   </si>
   <si>
     <t xml:space="preserve">1.62865328788757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62691879272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60350358486176</t>
+    <t xml:space="preserve">1.6269189119339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60350370407104</t>
   </si>
   <si>
     <t xml:space="preserve">1.59656584262848</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">1.7292515039444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67548358440399</t>
+    <t xml:space="preserve">1.6754834651947</t>
   </si>
   <si>
     <t xml:space="preserve">1.65640449523926</t>
@@ -1070,7 +1070,7 @@
     <t xml:space="preserve">1.66681134700775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68155407905579</t>
+    <t xml:space="preserve">1.68155419826508</t>
   </si>
   <si>
     <t xml:space="preserve">1.68935906887054</t>
@@ -1079,37 +1079,37 @@
     <t xml:space="preserve">1.67721796035767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63385665416718</t>
+    <t xml:space="preserve">1.63385653495789</t>
   </si>
   <si>
     <t xml:space="preserve">1.6217155456543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65727186203003</t>
+    <t xml:space="preserve">1.65727174282074</t>
   </si>
   <si>
     <t xml:space="preserve">1.71537601947784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66854572296143</t>
+    <t xml:space="preserve">1.66854584217072</t>
   </si>
   <si>
     <t xml:space="preserve">1.71711039543152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70670366287231</t>
+    <t xml:space="preserve">1.7067037820816</t>
   </si>
   <si>
     <t xml:space="preserve">1.72578275203705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72751724720001</t>
+    <t xml:space="preserve">1.72751712799072</t>
   </si>
   <si>
     <t xml:space="preserve">1.71190714836121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74312734603882</t>
+    <t xml:space="preserve">1.74312722682953</t>
   </si>
   <si>
     <t xml:space="preserve">1.77781629562378</t>
@@ -1124,34 +1124,34 @@
     <t xml:space="preserve">1.93391740322113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88188362121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95559823513031</t>
+    <t xml:space="preserve">1.88188374042511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95559799671173</t>
   </si>
   <si>
     <t xml:space="preserve">1.88621973991394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81684160232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89489197731018</t>
+    <t xml:space="preserve">1.81684172153473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89489209651947</t>
   </si>
   <si>
     <t xml:space="preserve">1.8081693649292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8298499584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85153067111969</t>
+    <t xml:space="preserve">1.82984983921051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85153090953827</t>
   </si>
   <si>
     <t xml:space="preserve">1.78215253353119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81250548362732</t>
+    <t xml:space="preserve">1.81250536441803</t>
   </si>
   <si>
     <t xml:space="preserve">1.79082489013672</t>
@@ -1166,52 +1166,52 @@
     <t xml:space="preserve">1.96860635280609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89922833442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89055621623993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87754762172699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83418619632721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84285843372345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82551395893097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83852207660675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86020290851593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9729425907135</t>
+    <t xml:space="preserve">1.89922821521759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89055597782135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87754738330841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83418607711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84285831451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82551383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83852231502533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86020314693451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97294282913208</t>
   </si>
   <si>
     <t xml:space="preserve">1.98161470890045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92958092689514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98595094680786</t>
+    <t xml:space="preserve">1.92958116531372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98595118522644</t>
   </si>
   <si>
     <t xml:space="preserve">2.04665684700012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03364825248718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04232096672058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07267379760742</t>
+    <t xml:space="preserve">2.03364849090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04232048988342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.072674036026</t>
   </si>
   <si>
     <t xml:space="preserve">2.08134603500366</t>
@@ -1223,19 +1223,19 @@
     <t xml:space="preserve">2.15072417259216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05532908439636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18541312217712</t>
+    <t xml:space="preserve">2.05532884597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1854133605957</t>
   </si>
   <si>
     <t xml:space="preserve">2.33717799186707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3024890422821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28080868721008</t>
+    <t xml:space="preserve">2.30248880386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2808084487915</t>
   </si>
   <si>
     <t xml:space="preserve">2.21143007278442</t>
@@ -1253,13 +1253,13 @@
     <t xml:space="preserve">2.48894286155701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59300994873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38921189308167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49761557579041</t>
+    <t xml:space="preserve">2.59301018714905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38921165466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49761533737183</t>
   </si>
   <si>
     <t xml:space="preserve">2.57566571235657</t>
@@ -1271,10 +1271,10 @@
     <t xml:space="preserve">2.71442198753357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76645565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83583402633667</t>
+    <t xml:space="preserve">2.76645588874817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83583426475525</t>
   </si>
   <si>
     <t xml:space="preserve">2.91388440132141</t>
@@ -1283,13 +1283,13 @@
     <t xml:space="preserve">2.92255663871765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93122911453247</t>
+    <t xml:space="preserve">2.93122887611389</t>
   </si>
   <si>
     <t xml:space="preserve">2.87052297592163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92689299583435</t>
+    <t xml:space="preserve">2.92689275741577</t>
   </si>
   <si>
     <t xml:space="preserve">3.10033845901489</t>
@@ -1301,25 +1301,25 @@
     <t xml:space="preserve">3.25210309028625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21741414070129</t>
+    <t xml:space="preserve">3.21741390228271</t>
   </si>
   <si>
     <t xml:space="preserve">3.25643944740295</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36050629615784</t>
+    <t xml:space="preserve">3.36050653457642</t>
   </si>
   <si>
     <t xml:space="preserve">3.20874190330505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36917901039124</t>
+    <t xml:space="preserve">3.36917877197266</t>
   </si>
   <si>
     <t xml:space="preserve">3.26511168479919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22175002098083</t>
+    <t xml:space="preserve">3.22175025939941</t>
   </si>
   <si>
     <t xml:space="preserve">3.33882570266724</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">3.50793552398682</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48625469207764</t>
+    <t xml:space="preserve">3.48625445365906</t>
   </si>
   <si>
     <t xml:space="preserve">3.55563259124756</t>
@@ -1343,16 +1343,16 @@
     <t xml:space="preserve">3.51227140426636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62934684753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66403603553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73341417312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80712890625</t>
+    <t xml:space="preserve">3.62934708595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6640362739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7334144115448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80712866783142</t>
   </si>
   <si>
     <t xml:space="preserve">3.90686011314392</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">4.07596921920776</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0456166267395</t>
+    <t xml:space="preserve">4.04561614990234</t>
   </si>
   <si>
     <t xml:space="preserve">4.09764957427979</t>
@@ -1373,13 +1373,13 @@
     <t xml:space="preserve">4.04127979278564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.945885181427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97190189361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7117338180542</t>
+    <t xml:space="preserve">3.94588565826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97190237045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71173357963562</t>
   </si>
   <si>
     <t xml:space="preserve">3.9198682308197</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">4.62232255935669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57896184921265</t>
+    <t xml:space="preserve">4.57896137237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.74373388290405</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">4.75240707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05593585968018</t>
+    <t xml:space="preserve">5.05593633651733</t>
   </si>
   <si>
     <t xml:space="preserve">4.98655796051025</t>
@@ -1418,13 +1418,13 @@
     <t xml:space="preserve">4.95186901092529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87381839752197</t>
+    <t xml:space="preserve">4.87381792068481</t>
   </si>
   <si>
     <t xml:space="preserve">4.31879329681396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80444049835205</t>
+    <t xml:space="preserve">4.80444002151489</t>
   </si>
   <si>
     <t xml:space="preserve">4.97788572311401</t>
@@ -1433,40 +1433,40 @@
     <t xml:space="preserve">5.01257514953613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03859233856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91718006134033</t>
+    <t xml:space="preserve">5.03859186172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91717958450317</t>
   </si>
   <si>
     <t xml:space="preserve">4.82178497314453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85647344589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89116334915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83045721054077</t>
+    <t xml:space="preserve">4.85647392272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89116287231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83045673370361</t>
   </si>
   <si>
     <t xml:space="preserve">4.76107883453369</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54427146911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70904541015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60497808456421</t>
+    <t xml:space="preserve">4.54427194595337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70904588699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60497760772705</t>
   </si>
   <si>
     <t xml:space="preserve">4.58763360977173</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64833974838257</t>
+    <t xml:space="preserve">4.64833927154541</t>
   </si>
   <si>
     <t xml:space="preserve">4.61365032196045</t>
@@ -1475,40 +1475,40 @@
     <t xml:space="preserve">4.53560018539429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47489404678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40551614761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18437242507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18870878219604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24074220657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08464193344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92854118347168</t>
+    <t xml:space="preserve">4.47489356994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40551567077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1843729019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1887092590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24074268341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08464097976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92854070663452</t>
   </si>
   <si>
     <t xml:space="preserve">3.91553211212158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85916185379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78111243247986</t>
+    <t xml:space="preserve">3.85916233062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7811119556427</t>
   </si>
   <si>
     <t xml:space="preserve">4.14101123809814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62501096725464</t>
+    <t xml:space="preserve">3.62501072883606</t>
   </si>
   <si>
     <t xml:space="preserve">3.31280899047852</t>
@@ -1526,10 +1526,10 @@
     <t xml:space="preserve">3.09166622161865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03529620170593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04830479621887</t>
+    <t xml:space="preserve">3.03529644012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04830503463745</t>
   </si>
   <si>
     <t xml:space="preserve">3.07865762710571</t>
@@ -1544,19 +1544,19 @@
     <t xml:space="preserve">2.90521192550659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02662396430969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75344705581665</t>
+    <t xml:space="preserve">3.02662420272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75344729423523</t>
   </si>
   <si>
     <t xml:space="preserve">2.80548095703125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88786768913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04396867752075</t>
+    <t xml:space="preserve">2.88786745071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04396843910217</t>
   </si>
   <si>
     <t xml:space="preserve">3.2607753276825</t>
@@ -1571,16 +1571,16 @@
     <t xml:space="preserve">3.4255485534668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43855690956116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39519572257996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20440578460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06998515129089</t>
+    <t xml:space="preserve">3.43855714797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39519596099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20440554618835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06998538970947</t>
   </si>
   <si>
     <t xml:space="preserve">2.86618685722351</t>
@@ -1589,10 +1589,10 @@
     <t xml:space="preserve">2.93990135192871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88353157043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97459053993225</t>
+    <t xml:space="preserve">2.88353133201599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97459030151367</t>
   </si>
   <si>
     <t xml:space="preserve">3.02228784561157</t>
@@ -1601,10 +1601,10 @@
     <t xml:space="preserve">3.3821873664856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32148098945618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15670800209045</t>
+    <t xml:space="preserve">3.32148122787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15670824050903</t>
   </si>
   <si>
     <t xml:space="preserve">3.11768269538879</t>
@@ -1619,7 +1619,7 @@
     <t xml:space="preserve">2.81848931312561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68840503692627</t>
+    <t xml:space="preserve">2.68840527534485</t>
   </si>
   <si>
     <t xml:space="preserve">2.73176670074463</t>
@@ -1631,37 +1631,37 @@
     <t xml:space="preserve">2.98759865760803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17405271530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30413675308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3084728717804</t>
+    <t xml:space="preserve">3.17405247688293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3041365146637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30847311019897</t>
   </si>
   <si>
     <t xml:space="preserve">3.17838883399963</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10467457771301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16104412078857</t>
+    <t xml:space="preserve">3.10467433929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16104435920715</t>
   </si>
   <si>
     <t xml:space="preserve">3.33015370368958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46023750305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59032154083252</t>
+    <t xml:space="preserve">3.46023774147034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59032201766968</t>
   </si>
   <si>
     <t xml:space="preserve">3.88517904281616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90252351760864</t>
+    <t xml:space="preserve">3.9025239944458</t>
   </si>
   <si>
     <t xml:space="preserve">3.8548264503479</t>
@@ -1676,10 +1676,10 @@
     <t xml:space="preserve">4.10198640823364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14534759521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13233947753906</t>
+    <t xml:space="preserve">4.145348072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1323390007019</t>
   </si>
   <si>
     <t xml:space="preserve">3.95889377593994</t>
@@ -1694,13 +1694,13 @@
     <t xml:space="preserve">3.9415488243103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9979190826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00659132003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06296062469482</t>
+    <t xml:space="preserve">3.99791884422302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00659084320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06296110153198</t>
   </si>
   <si>
     <t xml:space="preserve">4.05862474441528</t>
@@ -1721,19 +1721,19 @@
     <t xml:space="preserve">3.9242045879364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82880973815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75943088531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74642300605774</t>
+    <t xml:space="preserve">3.82880902290344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75943160057068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74642324447632</t>
   </si>
   <si>
     <t xml:space="preserve">3.56864094734192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77677583694458</t>
+    <t xml:space="preserve">3.776775598526</t>
   </si>
   <si>
     <t xml:space="preserve">4.24507856369019</t>
@@ -1742,31 +1742,31 @@
     <t xml:space="preserve">4.17136430740356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08897733688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06729650497437</t>
+    <t xml:space="preserve">4.0889778137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06729698181152</t>
   </si>
   <si>
     <t xml:space="preserve">4.16269207000732</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21906185150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23207092285156</t>
+    <t xml:space="preserve">4.21906137466431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2320704460144</t>
   </si>
   <si>
     <t xml:space="preserve">4.20171737670898</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68302822113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88249111175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76975059509277</t>
+    <t xml:space="preserve">4.68302869796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88249158859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76975107192993</t>
   </si>
   <si>
     <t xml:space="preserve">4.72638940811157</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">4.39684343338013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91119647026062</t>
+    <t xml:space="preserve">3.91119599342346</t>
   </si>
   <si>
     <t xml:space="preserve">4.04995250701904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2700982093811</t>
+    <t xml:space="preserve">4.27009868621826</t>
   </si>
   <si>
     <t xml:space="preserve">4.12285375595093</t>
@@ -1814,13 +1814,13 @@
     <t xml:space="preserve">3.85513591766357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85959792137146</t>
+    <t xml:space="preserve">3.8595974445343</t>
   </si>
   <si>
     <t xml:space="preserve">3.93098950386047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83728790283203</t>
+    <t xml:space="preserve">3.83728837966919</t>
   </si>
   <si>
     <t xml:space="preserve">4.01576662063599</t>
@@ -1829,25 +1829,25 @@
     <t xml:space="preserve">4.03807640075684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95776081085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79266834259033</t>
+    <t xml:space="preserve">3.95776128768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79266858100891</t>
   </si>
   <si>
     <t xml:space="preserve">3.74358701705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76143503189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61419010162354</t>
+    <t xml:space="preserve">3.76143479347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61419034004211</t>
   </si>
   <si>
     <t xml:space="preserve">3.68111944198608</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52048873901367</t>
+    <t xml:space="preserve">3.52048850059509</t>
   </si>
   <si>
     <t xml:space="preserve">3.48479270935059</t>
@@ -1862,10 +1862,10 @@
     <t xml:space="preserve">3.58741807937622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64096140861511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64988589286804</t>
+    <t xml:space="preserve">3.64096164703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64988565444946</t>
   </si>
   <si>
     <t xml:space="preserve">3.5115647315979</t>
@@ -1877,10 +1877,10 @@
     <t xml:space="preserve">3.52495074272156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41786336898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44909715652466</t>
+    <t xml:space="preserve">3.41786360740662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44909739494324</t>
   </si>
   <si>
     <t xml:space="preserve">3.4223256111145</t>
@@ -1904,22 +1904,22 @@
     <t xml:space="preserve">3.34647226333618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31523823738098</t>
+    <t xml:space="preserve">3.31523847579956</t>
   </si>
   <si>
     <t xml:space="preserve">3.32862424850464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36432027816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39555358886719</t>
+    <t xml:space="preserve">3.36432003974915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39555382728577</t>
   </si>
   <si>
     <t xml:space="preserve">3.35539603233337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31077671051025</t>
+    <t xml:space="preserve">3.31077647209167</t>
   </si>
   <si>
     <t xml:space="preserve">3.27954268455505</t>
@@ -1931,13 +1931,13 @@
     <t xml:space="preserve">3.38216781616211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40001583099365</t>
+    <t xml:space="preserve">3.40001559257507</t>
   </si>
   <si>
     <t xml:space="preserve">3.30631422996521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28400468826294</t>
+    <t xml:space="preserve">3.28400492668152</t>
   </si>
   <si>
     <t xml:space="preserve">3.33308625221252</t>
@@ -1955,10 +1955,10 @@
     <t xml:space="preserve">3.71235299110413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8105161190033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80605459213257</t>
+    <t xml:space="preserve">3.81051635742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80605435371399</t>
   </si>
   <si>
     <t xml:space="preserve">3.76589632034302</t>
@@ -1982,22 +1982,22 @@
     <t xml:space="preserve">3.69004344940186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70789122581482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6766574382782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73912501335144</t>
+    <t xml:space="preserve">3.7078914642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67665719985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73912477493286</t>
   </si>
   <si>
     <t xml:space="preserve">3.68558144569397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66773366928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69896745681763</t>
+    <t xml:space="preserve">3.66773343086243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69896721839905</t>
   </si>
   <si>
     <t xml:space="preserve">3.7212769985199</t>
@@ -2018,13 +2018,10 @@
     <t xml:space="preserve">3.56957030296326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99791884422302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96668553352356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73466277122498</t>
+    <t xml:space="preserve">3.9666850566864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73466324806213</t>
   </si>
   <si>
     <t xml:space="preserve">3.69450497627258</t>
@@ -2036,19 +2033,19 @@
     <t xml:space="preserve">3.63203811645508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60526585578918</t>
+    <t xml:space="preserve">3.60526609420776</t>
   </si>
   <si>
     <t xml:space="preserve">3.57849454879761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56510829925537</t>
+    <t xml:space="preserve">3.56510806083679</t>
   </si>
   <si>
     <t xml:space="preserve">3.93991351127625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06038618087769</t>
+    <t xml:space="preserve">4.06038665771484</t>
   </si>
   <si>
     <t xml:space="preserve">3.91314172744751</t>
@@ -2060,7 +2057,7 @@
     <t xml:space="preserve">3.98007082939148</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12731552124023</t>
+    <t xml:space="preserve">4.12731599807739</t>
   </si>
   <si>
     <t xml:space="preserve">4.05146217346191</t>
@@ -2075,7 +2072,7 @@
     <t xml:space="preserve">3.92652702331543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90867972373962</t>
+    <t xml:space="preserve">3.90867924690247</t>
   </si>
   <si>
     <t xml:space="preserve">3.90421748161316</t>
@@ -2087,7 +2084,7 @@
     <t xml:space="preserve">3.93545126914978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89083194732666</t>
+    <t xml:space="preserve">3.8908314704895</t>
   </si>
   <si>
     <t xml:space="preserve">4.07823419570923</t>
@@ -2096,13 +2093,13 @@
     <t xml:space="preserve">4.19424486160278</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00238037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1763973236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.087158203125</t>
+    <t xml:space="preserve">4.00238084793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17639684677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08715772628784</t>
   </si>
   <si>
     <t xml:space="preserve">4.21655464172363</t>
@@ -2111,13 +2108,13 @@
     <t xml:space="preserve">4.46196269989014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53335428237915</t>
+    <t xml:space="preserve">4.53335380554199</t>
   </si>
   <si>
     <t xml:space="preserve">4.64044094085693</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58689785003662</t>
+    <t xml:space="preserve">4.58689737319946</t>
   </si>
   <si>
     <t xml:space="preserve">4.64936542510986</t>
@@ -2129,7 +2126,7 @@
     <t xml:space="preserve">4.78322410583496</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68506097793579</t>
+    <t xml:space="preserve">4.68506145477295</t>
   </si>
   <si>
     <t xml:space="preserve">4.83676767349243</t>
@@ -2138,19 +2135,19 @@
     <t xml:space="preserve">4.81892013549805</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90815877914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00632286071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89923524856567</t>
+    <t xml:space="preserve">4.90815925598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00632238388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89923477172852</t>
   </si>
   <si>
     <t xml:space="preserve">4.85461568832397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97955083847046</t>
+    <t xml:space="preserve">4.9795503616333</t>
   </si>
   <si>
     <t xml:space="preserve">5.12233304977417</t>
@@ -2174,7 +2171,7 @@
     <t xml:space="preserve">4.82784414291382</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80999565124512</t>
+    <t xml:space="preserve">4.80999612808228</t>
   </si>
   <si>
     <t xml:space="preserve">4.94385480880737</t>
@@ -2183,13 +2180,13 @@
     <t xml:space="preserve">5.06878995895386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99739837646484</t>
+    <t xml:space="preserve">4.997398853302</t>
   </si>
   <si>
     <t xml:space="preserve">5.23834419250488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45251893997192</t>
+    <t xml:space="preserve">5.45251846313477</t>
   </si>
   <si>
     <t xml:space="preserve">5.83624744415283</t>
@@ -2201,16 +2198,16 @@
     <t xml:space="preserve">5.42574691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15802907943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88138675689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70290851593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71183300018311</t>
+    <t xml:space="preserve">5.15802955627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88138723373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70290899276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71183252334595</t>
   </si>
   <si>
     <t xml:space="preserve">4.73860454559326</t>
@@ -2225,7 +2222,7 @@
     <t xml:space="preserve">4.56012630462646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41734266281128</t>
+    <t xml:space="preserve">4.41734313964844</t>
   </si>
   <si>
     <t xml:space="preserve">4.14516353607178</t>
@@ -2234,37 +2231,37 @@
     <t xml:space="preserve">4.02022886276245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98453330993652</t>
+    <t xml:space="preserve">3.98453283309937</t>
   </si>
   <si>
     <t xml:space="preserve">3.94883728027344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80159258842468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12783622741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15906953811646</t>
+    <t xml:space="preserve">3.8015923500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12783598899841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15906977653503</t>
   </si>
   <si>
     <t xml:space="preserve">3.25277090072632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72625946998596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75749278068542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44961762428284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45854163169861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14174199104309</t>
+    <t xml:space="preserve">2.72625923156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.757493019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44961738586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45854139328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14174222946167</t>
   </si>
   <si>
     <t xml:space="preserve">1.99895942211151</t>
@@ -2276,7 +2273,7 @@
     <t xml:space="preserve">2.25775337219238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34699273109436</t>
+    <t xml:space="preserve">2.34699249267578</t>
   </si>
   <si>
     <t xml:space="preserve">2.4228458404541</t>
@@ -2285,13 +2282,13 @@
     <t xml:space="preserve">2.54331874847412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40053629875183</t>
+    <t xml:space="preserve">2.40053606033325</t>
   </si>
   <si>
     <t xml:space="preserve">2.48085141181946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45407938957214</t>
+    <t xml:space="preserve">2.45407962799072</t>
   </si>
   <si>
     <t xml:space="preserve">2.46300363540649</t>
@@ -2300,7 +2297,7 @@
     <t xml:space="preserve">2.56116652488708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73964524269104</t>
+    <t xml:space="preserve">2.73964500427246</t>
   </si>
   <si>
     <t xml:space="preserve">3.23938512802124</t>
@@ -2315,19 +2312,19 @@
     <t xml:space="preserve">2.91812372207642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85119438171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99843907356262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9359712600708</t>
+    <t xml:space="preserve">2.85119414329529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99843883514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93597149848938</t>
   </si>
   <si>
     <t xml:space="preserve">2.94489550590515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89135193824768</t>
+    <t xml:space="preserve">2.89135217666626</t>
   </si>
   <si>
     <t xml:space="preserve">2.97612929344177</t>
@@ -2339,7 +2336,7 @@
     <t xml:space="preserve">2.98059105873108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00290083885193</t>
+    <t xml:space="preserve">3.00290107727051</t>
   </si>
   <si>
     <t xml:space="preserve">3.13229775428772</t>
@@ -2360,22 +2357,22 @@
     <t xml:space="preserve">2.951495885849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8772439956665</t>
+    <t xml:space="preserve">2.87724423408508</t>
   </si>
   <si>
     <t xml:space="preserve">2.88652563095093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85404062271118</t>
+    <t xml:space="preserve">2.85404086112976</t>
   </si>
   <si>
     <t xml:space="preserve">2.7473042011261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71481895446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96077704429626</t>
+    <t xml:space="preserve">2.71481919288635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96077728271484</t>
   </si>
   <si>
     <t xml:space="preserve">2.75658559799194</t>
@@ -2384,7 +2381,7 @@
     <t xml:space="preserve">2.78442978858948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83547806739807</t>
+    <t xml:space="preserve">2.83547782897949</t>
   </si>
   <si>
     <t xml:space="preserve">3.08607649803162</t>
@@ -2408,19 +2405,19 @@
     <t xml:space="preserve">3.31347155570984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35059714317322</t>
+    <t xml:space="preserve">3.3505973815918</t>
   </si>
   <si>
     <t xml:space="preserve">3.27634596824646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28098678588867</t>
+    <t xml:space="preserve">3.28098654747009</t>
   </si>
   <si>
     <t xml:space="preserve">3.34595656394958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07215428352356</t>
+    <t xml:space="preserve">3.07215452194214</t>
   </si>
   <si>
     <t xml:space="preserve">3.07679510116577</t>
@@ -2429,13 +2426,13 @@
     <t xml:space="preserve">3.09999847412109</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16032814979553</t>
+    <t xml:space="preserve">3.16032791137695</t>
   </si>
   <si>
     <t xml:space="preserve">3.09535789489746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05359125137329</t>
+    <t xml:space="preserve">3.05359148979187</t>
   </si>
   <si>
     <t xml:space="preserve">3.03502869606018</t>
@@ -2444,7 +2441,7 @@
     <t xml:space="preserve">2.99326205253601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85868144035339</t>
+    <t xml:space="preserve">2.85868120193481</t>
   </si>
   <si>
     <t xml:space="preserve">2.83083701133728</t>
@@ -2453,7 +2450,7 @@
     <t xml:space="preserve">2.82155561447144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84940004348755</t>
+    <t xml:space="preserve">2.84939980506897</t>
   </si>
   <si>
     <t xml:space="preserve">2.81227421760559</t>
@@ -2465,7 +2462,7 @@
     <t xml:space="preserve">2.88188505172729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7937114238739</t>
+    <t xml:space="preserve">2.79371118545532</t>
   </si>
   <si>
     <t xml:space="preserve">2.76122617721558</t>
@@ -2483,13 +2480,13 @@
     <t xml:space="preserve">2.90972924232483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86332201957703</t>
+    <t xml:space="preserve">2.86332225799561</t>
   </si>
   <si>
     <t xml:space="preserve">2.78907084465027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69161558151245</t>
+    <t xml:space="preserve">2.69161581993103</t>
   </si>
   <si>
     <t xml:space="preserve">2.59416055679321</t>
@@ -2510,7 +2507,7 @@
     <t xml:space="preserve">2.16257381439209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13472938537598</t>
+    <t xml:space="preserve">2.13472962379456</t>
   </si>
   <si>
     <t xml:space="preserve">2.24610686302185</t>
@@ -2519,16 +2516,16 @@
     <t xml:space="preserve">2.40389108657837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58951997756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55703496932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60808253288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55239391326904</t>
+    <t xml:space="preserve">2.589519739151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55703473091125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60808277130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55239415168762</t>
   </si>
   <si>
     <t xml:space="preserve">2.57559776306152</t>
@@ -2543,13 +2540,13 @@
     <t xml:space="preserve">2.40853190422058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35748410224915</t>
+    <t xml:space="preserve">2.35748386383057</t>
   </si>
   <si>
     <t xml:space="preserve">2.54311275482178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45029854774475</t>
+    <t xml:space="preserve">2.45029830932617</t>
   </si>
   <si>
     <t xml:space="preserve">2.41781330108643</t>
@@ -2558,7 +2555,7 @@
     <t xml:space="preserve">2.45957970619202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44565749168396</t>
+    <t xml:space="preserve">2.44565773010254</t>
   </si>
   <si>
     <t xml:space="preserve">2.46422052383423</t>
@@ -2570,7 +2567,7 @@
     <t xml:space="preserve">2.4317352771759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49670577049255</t>
+    <t xml:space="preserve">2.49670553207397</t>
   </si>
   <si>
     <t xml:space="preserve">2.47814273834229</t>
@@ -2579,28 +2576,28 @@
     <t xml:space="preserve">2.51990914344788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50134611129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52919030189514</t>
+    <t xml:space="preserve">2.50134634971619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52919054031372</t>
   </si>
   <si>
     <t xml:space="preserve">2.56167554855347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5663161277771</t>
+    <t xml:space="preserve">2.56631636619568</t>
   </si>
   <si>
     <t xml:space="preserve">2.3017954826355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29715442657471</t>
+    <t xml:space="preserve">2.29715466499329</t>
   </si>
   <si>
     <t xml:space="preserve">2.29251408576965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2785918712616</t>
+    <t xml:space="preserve">2.27859163284302</t>
   </si>
   <si>
     <t xml:space="preserve">2.23218464851379</t>
@@ -2609,7 +2606,7 @@
     <t xml:space="preserve">2.19969964027405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17185544967651</t>
+    <t xml:space="preserve">2.17185521125793</t>
   </si>
   <si>
     <t xml:space="preserve">2.26931023597717</t>
@@ -2621,13 +2618,13 @@
     <t xml:space="preserve">2.24146604537964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22754383087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19505906105042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12544822692871</t>
+    <t xml:space="preserve">2.22754406929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19505882263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12544798851013</t>
   </si>
   <si>
     <t xml:space="preserve">2.01407098770142</t>
@@ -2642,13 +2639,13 @@
     <t xml:space="preserve">2.0744001865387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97230446338654</t>
+    <t xml:space="preserve">1.97230458259583</t>
   </si>
   <si>
     <t xml:space="preserve">1.96766364574432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.944460272789</t>
+    <t xml:space="preserve">1.94446015357971</t>
   </si>
   <si>
     <t xml:space="preserve">1.87020885944366</t>
@@ -2663,7 +2660,7 @@
     <t xml:space="preserve">1.81730461120605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79688549041748</t>
+    <t xml:space="preserve">1.79688537120819</t>
   </si>
   <si>
     <t xml:space="preserve">1.80059802532196</t>
@@ -2672,7 +2669,7 @@
     <t xml:space="preserve">1.88413095474243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03263401985168</t>
+    <t xml:space="preserve">2.03263378143311</t>
   </si>
   <si>
     <t xml:space="preserve">2.50598692893982</t>
@@ -2693,10 +2690,10 @@
     <t xml:space="preserve">2.77978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71946001052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70553755760193</t>
+    <t xml:space="preserve">2.71945977210999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70553779602051</t>
   </si>
   <si>
     <t xml:space="preserve">2.7241005897522</t>
@@ -2708,10 +2705,10 @@
     <t xml:space="preserve">2.64056777954102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68233418464661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76586723327637</t>
+    <t xml:space="preserve">2.68233442306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76586699485779</t>
   </si>
   <si>
     <t xml:space="preserve">2.58023834228516</t>
@@ -2726,7 +2723,7 @@
     <t xml:space="preserve">2.6127233505249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59880113601685</t>
+    <t xml:space="preserve">2.59880137443542</t>
   </si>
   <si>
     <t xml:space="preserve">2.62664556503296</t>
@@ -2741,10 +2738,10 @@
     <t xml:space="preserve">2.39925050735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27395105361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32963967323303</t>
+    <t xml:space="preserve">2.27395129203796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32963991165161</t>
   </si>
   <si>
     <t xml:space="preserve">2.3482027053833</t>
@@ -2753,7 +2750,7 @@
     <t xml:space="preserve">2.35284328460693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39460968971252</t>
+    <t xml:space="preserve">2.39460945129395</t>
   </si>
   <si>
     <t xml:space="preserve">2.46886134147644</t>
@@ -2774,7 +2771,7 @@
     <t xml:space="preserve">2.64520835876465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7008969783783</t>
+    <t xml:space="preserve">2.70089721679688</t>
   </si>
   <si>
     <t xml:space="preserve">2.71017861366272</t>
@@ -2786,16 +2783,19 @@
     <t xml:space="preserve">2.93757343292236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9979031085968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09071731567383</t>
+    <t xml:space="preserve">2.99790287017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09071707725525</t>
   </si>
   <si>
     <t xml:space="preserve">3.04895091056824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10463953018188</t>
+    <t xml:space="preserve">3.10463929176331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0118248462677</t>
   </si>
   <si>
     <t xml:space="preserve">3.11392092704773</t>
@@ -2804,19 +2804,19 @@
     <t xml:space="preserve">3.2392201423645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24386072158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21601629257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25314259529114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29026818275452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29954957962036</t>
+    <t xml:space="preserve">3.24386096000671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2160165309906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25314235687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29026794433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29954934120178</t>
   </si>
   <si>
     <t xml:space="preserve">3.31811237335205</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">3.61975908279419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49910044670105</t>
+    <t xml:space="preserve">3.49910020828247</t>
   </si>
   <si>
     <t xml:space="preserve">3.62904047966003</t>
@@ -2846,19 +2846,19 @@
     <t xml:space="preserve">3.41092658042908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34131574630737</t>
+    <t xml:space="preserve">3.34131598472595</t>
   </si>
   <si>
     <t xml:space="preserve">3.3273937702179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44805216789246</t>
+    <t xml:space="preserve">3.44805240631104</t>
   </si>
   <si>
     <t xml:space="preserve">3.38772320747375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41556739807129</t>
+    <t xml:space="preserve">3.41556763648987</t>
   </si>
   <si>
     <t xml:space="preserve">3.29490876197815</t>
@@ -2873,19 +2873,19 @@
     <t xml:space="preserve">3.13248372077942</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17889070510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18353176116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28562712669373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3738009929657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43413019180298</t>
+    <t xml:space="preserve">3.17889094352722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18353152275085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2856273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37380075454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43413043022156</t>
   </si>
   <si>
     <t xml:space="preserve">3.47589659690857</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">3.50838160514832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63368105888367</t>
+    <t xml:space="preserve">3.63368082046509</t>
   </si>
   <si>
     <t xml:space="preserve">3.60583686828613</t>
@@ -2906,28 +2906,28 @@
     <t xml:space="preserve">3.54550743103027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69865107536316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55478858947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53622603416443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4434118270874</t>
+    <t xml:space="preserve">3.69865083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55478882789612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53622579574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44341158866882</t>
   </si>
   <si>
     <t xml:space="preserve">3.52230405807495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54086661338806</t>
+    <t xml:space="preserve">3.54086685180664</t>
   </si>
   <si>
     <t xml:space="preserve">3.46197438240051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47125601768494</t>
+    <t xml:space="preserve">3.47125577926636</t>
   </si>
   <si>
     <t xml:space="preserve">3.50374102592468</t>
@@ -2939,16 +2939,16 @@
     <t xml:space="preserve">3.22993874549866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26706457138062</t>
+    <t xml:space="preserve">3.26706433296204</t>
   </si>
   <si>
     <t xml:space="preserve">3.33203434944153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39236354827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37844157218933</t>
+    <t xml:space="preserve">3.39236378669739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37844181060791</t>
   </si>
   <si>
     <t xml:space="preserve">3.30883097648621</t>
@@ -2969,13 +2969,13 @@
     <t xml:space="preserve">3.05823230743408</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13712453842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11856150627136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96541786193848</t>
+    <t xml:space="preserve">3.13712430000305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11856126785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9654176235199</t>
   </si>
   <si>
     <t xml:space="preserve">3.30419015884399</t>
@@ -2984,7 +2984,7 @@
     <t xml:space="preserve">3.17425012588501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12784290313721</t>
+    <t xml:space="preserve">3.12784266471863</t>
   </si>
   <si>
     <t xml:space="preserve">3.19745373725891</t>
@@ -3005,16 +3005,16 @@
     <t xml:space="preserve">3.36451935768127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45269322395325</t>
+    <t xml:space="preserve">3.45269298553467</t>
   </si>
   <si>
     <t xml:space="preserve">3.42020797729492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42484879493713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32275319099426</t>
+    <t xml:space="preserve">3.42484903335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32275295257568</t>
   </si>
   <si>
     <t xml:space="preserve">3.33667516708374</t>
@@ -3023,13 +3023,13 @@
     <t xml:space="preserve">3.38308238983154</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36916017532349</t>
+    <t xml:space="preserve">3.36916041374207</t>
   </si>
   <si>
     <t xml:space="preserve">3.16496872901917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01646566390991</t>
+    <t xml:space="preserve">3.01646590232849</t>
   </si>
   <si>
     <t xml:space="preserve">3.1696093082428</t>
@@ -3038,7 +3038,7 @@
     <t xml:space="preserve">3.06751370429993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0211067199707</t>
+    <t xml:space="preserve">3.02110648155212</t>
   </si>
   <si>
     <t xml:space="preserve">3.15568733215332</t>
@@ -3047,10 +3047,10 @@
     <t xml:space="preserve">3.14176511764526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.123202085495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03966927528381</t>
+    <t xml:space="preserve">3.12320232391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03966951370239</t>
   </si>
   <si>
     <t xml:space="preserve">3.14640593528748</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">2.58487915992737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77050757408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86796259880066</t>
+    <t xml:space="preserve">2.7705078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86796283721924</t>
   </si>
   <si>
     <t xml:space="preserve">2.94685482978821</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">2.98398065567017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02574706077576</t>
+    <t xml:space="preserve">3.02574729919434</t>
   </si>
   <si>
     <t xml:space="preserve">2.97934007644653</t>
@@ -3086,16 +3086,16 @@
     <t xml:space="preserve">2.80299282073975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84475922584534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9282922744751</t>
+    <t xml:space="preserve">2.84475946426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92829203605652</t>
   </si>
   <si>
     <t xml:space="preserve">2.87260365486145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89116621017456</t>
+    <t xml:space="preserve">2.89116644859314</t>
   </si>
   <si>
     <t xml:space="preserve">3.03038787841797</t>
@@ -3104,16 +3104,16 @@
     <t xml:space="preserve">2.8169150352478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68697500228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69625639915466</t>
+    <t xml:space="preserve">2.68697476387024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69625616073608</t>
   </si>
   <si>
     <t xml:space="preserve">2.62200474739075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79835200309753</t>
+    <t xml:space="preserve">2.79835224151611</t>
   </si>
   <si>
     <t xml:space="preserve">2.91901063919067</t>
@@ -3125,7 +3125,7 @@
     <t xml:space="preserve">2.9050886631012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95613646507263</t>
+    <t xml:space="preserve">2.95613622665405</t>
   </si>
   <si>
     <t xml:space="preserve">2.80763363838196</t>
@@ -3143,31 +3143,31 @@
     <t xml:space="preserve">2.74266338348389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63128638267517</t>
+    <t xml:space="preserve">2.63128614425659</t>
   </si>
   <si>
     <t xml:space="preserve">2.49206471443176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53847169876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54775333404541</t>
+    <t xml:space="preserve">2.53847193717957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54775309562683</t>
   </si>
   <si>
     <t xml:space="preserve">2.48742413520813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44101715087891</t>
+    <t xml:space="preserve">2.44101691246033</t>
   </si>
   <si>
     <t xml:space="preserve">2.47350192070007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43637609481812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38996887207031</t>
+    <t xml:space="preserve">2.43637633323669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38996911048889</t>
   </si>
   <si>
     <t xml:space="preserve">2.3249990940094</t>
@@ -3179,19 +3179,19 @@
     <t xml:space="preserve">2.31107687950134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28323245048523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28787326812744</t>
+    <t xml:space="preserve">2.28323268890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28787302970886</t>
   </si>
   <si>
     <t xml:space="preserve">2.26002883911133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33428072929382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33892107009888</t>
+    <t xml:space="preserve">2.33428049087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33892130851746</t>
   </si>
   <si>
     <t xml:space="preserve">2.30643606185913</t>
@@ -3221,13 +3221,13 @@
     <t xml:space="preserve">2.18113660812378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22290325164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18577766418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11616683006287</t>
+    <t xml:space="preserve">2.22290301322937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18577742576599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11616659164429</t>
   </si>
   <si>
     <t xml:space="preserve">2.0976037979126</t>
@@ -3245,22 +3245,22 @@
     <t xml:space="preserve">2.04191517829895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02335262298584</t>
+    <t xml:space="preserve">2.02335238456726</t>
   </si>
   <si>
     <t xml:space="preserve">2.00014877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98158586025238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97694540023804</t>
+    <t xml:space="preserve">1.98158597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97694528102875</t>
   </si>
   <si>
     <t xml:space="preserve">1.99086737632751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99550807476044</t>
+    <t xml:space="preserve">1.99550831317902</t>
   </si>
   <si>
     <t xml:space="preserve">2.00478959083557</t>
@@ -3275,10 +3275,10 @@
     <t xml:space="preserve">2.05119657516479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00943040847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02799296379089</t>
+    <t xml:space="preserve">2.0094301700592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02799320220947</t>
   </si>
   <si>
     <t xml:space="preserve">1.95838224887848</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">1.93981945514679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91197526454926</t>
+    <t xml:space="preserve">1.91197514533997</t>
   </si>
   <si>
     <t xml:space="preserve">1.90269374847412</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">1.75419080257416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73562800884247</t>
+    <t xml:space="preserve">1.73562788963318</t>
   </si>
   <si>
     <t xml:space="preserve">1.82472968101501</t>
@@ -3317,16 +3317,16 @@
     <t xml:space="preserve">1.80431056022644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77646625041962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.793172955513</t>
+    <t xml:space="preserve">1.77646636962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79317283630371</t>
   </si>
   <si>
     <t xml:space="preserve">1.7950291633606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76904118061066</t>
+    <t xml:space="preserve">1.76904106140137</t>
   </si>
   <si>
     <t xml:space="preserve">1.75047838687897</t>
@@ -3356,7 +3356,7 @@
     <t xml:space="preserve">1.81916093826294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287335395813</t>
+    <t xml:space="preserve">1.82287347316742</t>
   </si>
   <si>
     <t xml:space="preserve">2.01871156692505</t>
@@ -3371,22 +3371,22 @@
     <t xml:space="preserve">2.37604665756226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38532829284668</t>
+    <t xml:space="preserve">2.3853280544281</t>
   </si>
   <si>
     <t xml:space="preserve">2.3714063167572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60344219207764</t>
+    <t xml:space="preserve">2.60344195365906</t>
   </si>
   <si>
     <t xml:space="preserve">3.56407022476196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64296245574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57799243927002</t>
+    <t xml:space="preserve">3.64296221733093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5779926776886</t>
   </si>
   <si>
     <t xml:space="preserve">3.55942964553833</t>
@@ -3395,19 +3395,19 @@
     <t xml:space="preserve">3.82859110832214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90748333930969</t>
+    <t xml:space="preserve">3.90748310089111</t>
   </si>
   <si>
     <t xml:space="preserve">4.00029754638672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81466913223267</t>
+    <t xml:space="preserve">3.81466889381409</t>
   </si>
   <si>
     <t xml:space="preserve">3.48517823219299</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42948961257935</t>
+    <t xml:space="preserve">3.42948937416077</t>
   </si>
   <si>
     <t xml:space="preserve">3.45733380317688</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">3.35987877845764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58727383613586</t>
+    <t xml:space="preserve">3.58727407455444</t>
   </si>
   <si>
     <t xml:space="preserve">3.52694439888</t>
@@ -4227,6 +4227,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.90000009536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92999982833862</t>
   </si>
 </sst>
 </file>
@@ -29075,7 +29078,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G943" t="s">
-        <v>668</v>
+        <v>560</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -29127,7 +29130,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G945" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -29153,7 +29156,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G946" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -29231,7 +29234,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G949" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -29257,7 +29260,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G950" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -29335,7 +29338,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G953" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -29361,7 +29364,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G954" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -29413,7 +29416,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G956" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -29465,7 +29468,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G958" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -29491,7 +29494,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G959" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -29517,7 +29520,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G960" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -29543,7 +29546,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G961" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -29647,7 +29650,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G965" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -29673,7 +29676,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G966" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -29699,7 +29702,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G967" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -29725,7 +29728,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G968" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -29751,7 +29754,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G969" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -29777,7 +29780,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G970" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -29803,7 +29806,7 @@
         <v>4.625</v>
       </c>
       <c r="G971" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -29829,7 +29832,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G972" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -29855,7 +29858,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G973" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -29881,7 +29884,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G974" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -29907,7 +29910,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G975" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -29933,7 +29936,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G976" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -29959,7 +29962,7 @@
         <v>4.375</v>
       </c>
       <c r="G977" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -29985,7 +29988,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G978" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -30011,7 +30014,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G979" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -30037,7 +30040,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G980" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -30063,7 +30066,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G981" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -30089,7 +30092,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G982" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -30141,7 +30144,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G984" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -30167,7 +30170,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G985" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -30193,7 +30196,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G986" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -30219,7 +30222,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G987" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -30245,7 +30248,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G988" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -30271,7 +30274,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G989" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -30297,7 +30300,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G990" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -30375,7 +30378,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G993" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -30401,7 +30404,7 @@
         <v>5</v>
       </c>
       <c r="G994" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -30427,7 +30430,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G995" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -30453,7 +30456,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G996" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -30479,7 +30482,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G997" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -30505,7 +30508,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G998" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -30531,7 +30534,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G999" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -30557,7 +30560,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1000" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -30583,7 +30586,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1001" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -30609,7 +30612,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1002" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -30635,7 +30638,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1003" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -30661,7 +30664,7 @@
         <v>5.25</v>
       </c>
       <c r="G1004" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -30687,7 +30690,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1005" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -30713,7 +30716,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1006" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -30739,7 +30742,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1007" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -30765,7 +30768,7 @@
         <v>5.5</v>
       </c>
       <c r="G1008" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -30791,7 +30794,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G1009" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -30817,7 +30820,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1010" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -30843,7 +30846,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1011" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -30869,7 +30872,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1012" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -30895,7 +30898,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1013" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -30921,7 +30924,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1014" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -30947,7 +30950,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1015" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -30973,7 +30976,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1016" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -30999,7 +31002,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1017" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -31025,7 +31028,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1018" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -31051,7 +31054,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1019" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -31077,7 +31080,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1020" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -31103,7 +31106,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1021" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -31129,7 +31132,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1022" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -31155,7 +31158,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1023" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -31181,7 +31184,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1024" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -31207,7 +31210,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1025" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -31233,7 +31236,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1026" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -31259,7 +31262,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1027" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -31285,7 +31288,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1028" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -31311,7 +31314,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1029" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -31337,7 +31340,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1030" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -31363,7 +31366,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1031" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -31389,7 +31392,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1032" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -31415,7 +31418,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1033" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -31441,7 +31444,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1034" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -31467,7 +31470,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1035" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -31493,7 +31496,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1036" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -31519,7 +31522,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1037" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -31545,7 +31548,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1038" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -31571,7 +31574,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1039" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -31597,7 +31600,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1040" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -31623,7 +31626,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G1041" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -31649,7 +31652,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1042" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -31675,7 +31678,7 @@
         <v>5.25</v>
       </c>
       <c r="G1043" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -31701,7 +31704,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1044" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -31727,7 +31730,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1045" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -31753,7 +31756,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1046" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -31779,7 +31782,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1047" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -31805,7 +31808,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1048" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -31831,7 +31834,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1049" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -31857,7 +31860,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1050" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -31883,7 +31886,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1051" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -31909,7 +31912,7 @@
         <v>5.25</v>
       </c>
       <c r="G1052" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -31935,7 +31938,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G1053" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -31961,7 +31964,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1054" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -31987,7 +31990,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1055" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -32013,7 +32016,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1056" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -32039,7 +32042,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1057" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -32091,7 +32094,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1059" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -32195,7 +32198,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1063" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -32221,7 +32224,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1064" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -32247,7 +32250,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1065" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -32273,7 +32276,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1066" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -32299,7 +32302,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1067" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -32325,7 +32328,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1068" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -32351,7 +32354,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1069" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -32377,7 +32380,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1070" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -32403,7 +32406,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1071" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -32429,7 +32432,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1072" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -32455,7 +32458,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1073" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -32481,7 +32484,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1074" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -32507,7 +32510,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1075" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -32533,7 +32536,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1076" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -32559,7 +32562,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1077" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -32585,7 +32588,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1078" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -32611,7 +32614,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1079" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -32637,7 +32640,7 @@
         <v>2.75</v>
       </c>
       <c r="G1080" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -32663,7 +32666,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1081" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -32689,7 +32692,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1082" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -32715,7 +32718,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1083" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -32741,7 +32744,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1084" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -32767,7 +32770,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1085" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -32793,7 +32796,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1086" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -32819,7 +32822,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1087" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -32845,7 +32848,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1088" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -32871,7 +32874,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1089" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -32897,7 +32900,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1090" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -32923,7 +32926,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1091" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -32949,7 +32952,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1092" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -32975,7 +32978,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1093" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -33001,7 +33004,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1094" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -33027,7 +33030,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1095" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -33053,7 +33056,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1096" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -33079,7 +33082,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1097" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -33105,7 +33108,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1098" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -33131,7 +33134,7 @@
         <v>3.375</v>
       </c>
       <c r="G1099" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -33157,7 +33160,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1100" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -33183,7 +33186,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1101" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -33209,7 +33212,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1102" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -33235,7 +33238,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1103" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -33261,7 +33264,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1104" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -33287,7 +33290,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1105" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -33313,7 +33316,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1106" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -33339,7 +33342,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1107" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -33365,7 +33368,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1108" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -33391,7 +33394,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1109" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -33417,7 +33420,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1110" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -33443,7 +33446,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1111" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -33469,7 +33472,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1112" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -33495,7 +33498,7 @@
         <v>3</v>
       </c>
       <c r="G1113" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -33521,7 +33524,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1114" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -33547,7 +33550,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1115" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -33573,7 +33576,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1116" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -33599,7 +33602,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1117" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -33625,7 +33628,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1118" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -33651,7 +33654,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1119" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -33677,7 +33680,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1120" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -33703,7 +33706,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1121" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -33729,7 +33732,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1122" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -33755,7 +33758,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1123" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -33781,7 +33784,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1124" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -33807,7 +33810,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1125" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -33833,7 +33836,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1126" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -33859,7 +33862,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1127" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -33885,7 +33888,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1128" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -33911,7 +33914,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1129" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -33937,7 +33940,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1130" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -33963,7 +33966,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1131" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -33989,7 +33992,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1132" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -34015,7 +34018,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1133" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -34041,7 +34044,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1134" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -34067,7 +34070,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1135" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -34093,7 +34096,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1136" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -34119,7 +34122,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1137" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -34145,7 +34148,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1138" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -34171,7 +34174,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1139" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -34197,7 +34200,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1140" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -34223,7 +34226,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1141" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -34249,7 +34252,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1142" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -34275,7 +34278,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1143" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -34301,7 +34304,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G1144" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -34327,7 +34330,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1145" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -34353,7 +34356,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1146" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -34379,7 +34382,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G1147" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -34405,7 +34408,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1148" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -34431,7 +34434,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1149" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -34457,7 +34460,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G1150" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -34483,7 +34486,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1151" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -34509,7 +34512,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1152" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -34535,7 +34538,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1153" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -34561,7 +34564,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1154" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -34587,7 +34590,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1155" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -34613,7 +34616,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1156" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -34639,7 +34642,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G1157" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -34665,7 +34668,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1158" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -34691,7 +34694,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1159" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -34717,7 +34720,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1160" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -34743,7 +34746,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G1161" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -34769,7 +34772,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1162" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -34795,7 +34798,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1163" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -34821,7 +34824,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1164" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -34847,7 +34850,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1165" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -34873,7 +34876,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1166" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -34899,7 +34902,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1167" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -34925,7 +34928,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1168" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -34951,7 +34954,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1169" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -34977,7 +34980,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1170" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -35003,7 +35006,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1171" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -35029,7 +35032,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1172" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -35055,7 +35058,7 @@
         <v>2.75</v>
       </c>
       <c r="G1173" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -35081,7 +35084,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G1174" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -35107,7 +35110,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1175" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -35133,7 +35136,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1176" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -35159,7 +35162,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1177" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -35185,7 +35188,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1178" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -35211,7 +35214,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1179" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -35237,7 +35240,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1180" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -35263,7 +35266,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1181" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -35289,7 +35292,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1182" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -35315,7 +35318,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G1183" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -35341,7 +35344,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1184" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -35367,7 +35370,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G1185" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -35393,7 +35396,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G1186" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -35419,7 +35422,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1187" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -35445,7 +35448,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1188" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -35471,7 +35474,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1189" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -35497,7 +35500,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1190" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -35523,7 +35526,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1191" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -35549,7 +35552,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1192" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -35575,7 +35578,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1193" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -35601,7 +35604,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1194" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -35627,7 +35630,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1195" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -35653,7 +35656,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1196" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -35679,7 +35682,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1197" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -35705,7 +35708,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1198" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -35731,7 +35734,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1199" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -35757,7 +35760,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1200" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -35783,7 +35786,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G1201" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -35809,7 +35812,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1202" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -35835,7 +35838,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1203" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -35861,7 +35864,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1204" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -35887,7 +35890,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1205" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -35913,7 +35916,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1206" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -35939,7 +35942,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1207" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -35965,7 +35968,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1208" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -35991,7 +35994,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1209" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -36017,7 +36020,7 @@
         <v>2.4449999332428</v>
       </c>
       <c r="G1210" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -36043,7 +36046,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1211" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -36069,7 +36072,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1212" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -36095,7 +36098,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1213" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -36121,7 +36124,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1214" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -36147,7 +36150,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G1215" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -36173,7 +36176,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1216" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -36199,7 +36202,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1217" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -36225,7 +36228,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1218" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -36251,7 +36254,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1219" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -36277,7 +36280,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G1220" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -36303,7 +36306,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G1221" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -36329,7 +36332,7 @@
         <v>2.125</v>
       </c>
       <c r="G1222" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -36355,7 +36358,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1223" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -36381,7 +36384,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1224" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -36407,7 +36410,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1225" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -36433,7 +36436,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1226" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -36459,7 +36462,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G1227" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -36485,7 +36488,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1228" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -36511,7 +36514,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G1229" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -36537,7 +36540,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1230" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -36563,7 +36566,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1231" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -36589,7 +36592,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1232" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -36615,7 +36618,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1233" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -36641,7 +36644,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1234" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -36667,7 +36670,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1235" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -36693,7 +36696,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1236" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -36719,7 +36722,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1237" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -36745,7 +36748,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1238" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -36771,7 +36774,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1239" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -36797,7 +36800,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1240" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -36823,7 +36826,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1241" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -36849,7 +36852,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G1242" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -36875,7 +36878,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1243" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -36901,7 +36904,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1244" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -36927,7 +36930,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1245" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -36953,7 +36956,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1246" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -36979,7 +36982,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1247" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -37005,7 +37008,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1248" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -37031,7 +37034,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1249" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -37057,7 +37060,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1250" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -37083,7 +37086,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1251" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -37109,7 +37112,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1252" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -37135,7 +37138,7 @@
         <v>3</v>
       </c>
       <c r="G1253" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -37161,7 +37164,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1254" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -37187,7 +37190,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1255" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -37213,7 +37216,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1256" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -37239,7 +37242,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1257" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -37265,7 +37268,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1258" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -37291,7 +37294,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G1259" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -37317,7 +37320,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1260" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -37343,7 +37346,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1261" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -37369,7 +37372,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1262" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -37395,7 +37398,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1263" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -37421,7 +37424,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1264" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -37447,7 +37450,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1265" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -37473,7 +37476,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1266" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -37499,7 +37502,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G1267" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -37525,7 +37528,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1268" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -37551,7 +37554,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1269" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -37577,7 +37580,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1270" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -37603,7 +37606,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1271" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -37629,7 +37632,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1272" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -37655,7 +37658,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1273" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -37681,7 +37684,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1274" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -37707,7 +37710,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1275" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -37733,7 +37736,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1276" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -37759,7 +37762,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1277" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -37785,7 +37788,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1278" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -37811,7 +37814,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1279" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -37837,7 +37840,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1280" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -37863,7 +37866,7 @@
         <v>2.75</v>
       </c>
       <c r="G1281" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -37889,7 +37892,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1282" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -37915,7 +37918,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1283" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -37941,7 +37944,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1284" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -37967,7 +37970,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1285" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -37993,7 +37996,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1286" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -38019,7 +38022,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1287" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -38045,7 +38048,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1288" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -38071,7 +38074,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1289" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -38097,7 +38100,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1290" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -38123,7 +38126,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1291" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -38149,7 +38152,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1292" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -38175,7 +38178,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1293" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -38201,7 +38204,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1294" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -38227,7 +38230,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1295" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -38253,7 +38256,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1296" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -38279,7 +38282,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1297" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -38305,7 +38308,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1298" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -38331,7 +38334,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1299" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -38357,7 +38360,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1300" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -38383,7 +38386,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1301" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -38409,7 +38412,7 @@
         <v>2.875</v>
       </c>
       <c r="G1302" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -38435,7 +38438,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G1303" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -38461,7 +38464,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1304" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -38487,7 +38490,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1305" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -38513,7 +38516,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1306" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -38539,7 +38542,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1307" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -38565,7 +38568,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1308" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -38591,7 +38594,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1309" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -38617,7 +38620,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1310" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -38643,7 +38646,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1311" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -38669,7 +38672,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1312" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -38695,7 +38698,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1313" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -38721,7 +38724,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1314" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -38747,7 +38750,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1315" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -38773,7 +38776,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1316" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -38799,7 +38802,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1317" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -38825,7 +38828,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G1318" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -38851,7 +38854,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1319" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -38877,7 +38880,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1320" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -38903,7 +38906,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1321" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -38929,7 +38932,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1322" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -38955,7 +38958,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1323" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -38981,7 +38984,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1324" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -39007,7 +39010,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1325" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -39033,7 +39036,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1326" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -39059,7 +39062,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1327" t="s">
-        <v>777</v>
+        <v>927</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -39085,7 +39088,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1328" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -39111,7 +39114,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1329" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -39293,7 +39296,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1336" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -39813,7 +39816,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1356" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -40203,7 +40206,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1371" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -41087,7 +41090,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1405" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -41139,7 +41142,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1407" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -41165,7 +41168,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1408" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -41269,7 +41272,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1412" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -41321,7 +41324,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1414" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -41347,7 +41350,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1415" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -41425,7 +41428,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1418" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -41451,7 +41454,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1419" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -41477,7 +41480,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1420" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -41503,7 +41506,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1421" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -41867,7 +41870,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1435" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -42153,7 +42156,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1446" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -42361,7 +42364,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1454" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -43037,7 +43040,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1480" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -43089,7 +43092,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1482" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -43557,7 +43560,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1500" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -43609,7 +43612,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1502" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -43713,7 +43716,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1506" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -43765,7 +43768,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1508" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -43791,7 +43794,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1509" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -43921,7 +43924,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1514" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -43999,7 +44002,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1517" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -44025,7 +44028,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1518" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -44311,7 +44314,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1529" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -44389,7 +44392,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1532" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -44415,7 +44418,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1533" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -44493,7 +44496,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1536" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -44571,7 +44574,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1539" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -44675,7 +44678,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1543" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -44701,7 +44704,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1544" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -44727,7 +44730,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1545" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -44753,7 +44756,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1546" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -44779,7 +44782,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1547" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -44805,7 +44808,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1548" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -44883,7 +44886,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1551" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -44987,7 +44990,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1555" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -45039,7 +45042,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1557" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -45117,7 +45120,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1560" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -45143,7 +45146,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1561" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -45195,7 +45198,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1563" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -45221,7 +45224,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G1564" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -45247,7 +45250,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1565" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -45273,7 +45276,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1566" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -45351,7 +45354,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1569" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -45377,7 +45380,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1570" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -45403,7 +45406,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1571" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -45429,7 +45432,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1572" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -45455,7 +45458,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1573" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -45481,7 +45484,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1574" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -45533,7 +45536,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1576" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -45585,7 +45588,7 @@
         <v>3</v>
       </c>
       <c r="G1578" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -45663,7 +45666,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1581" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -45689,7 +45692,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1582" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -45715,7 +45718,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1583" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -45767,7 +45770,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1585" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -45793,7 +45796,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1586" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -45845,7 +45848,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1588" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -45923,7 +45926,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1591" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -45949,7 +45952,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1592" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -45975,7 +45978,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1593" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -46001,7 +46004,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G1594" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -46053,7 +46056,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1596" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -46079,7 +46082,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1597" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -46105,7 +46108,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G1598" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -46157,7 +46160,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1600" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -46183,7 +46186,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1601" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -46261,7 +46264,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1604" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -46287,7 +46290,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1605" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -46339,7 +46342,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1607" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -46391,7 +46394,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1609" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -46417,7 +46420,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1610" t="s">
-        <v>777</v>
+        <v>927</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -46495,7 +46498,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G1613" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -46521,7 +46524,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G1614" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -46547,7 +46550,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1615" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -46573,7 +46576,7 @@
         <v>3</v>
       </c>
       <c r="G1616" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -46625,7 +46628,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1618" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -46729,7 +46732,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1622" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -46755,7 +46758,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1623" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -46781,7 +46784,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1624" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -46859,7 +46862,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1627" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -46885,7 +46888,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1628" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -46911,7 +46914,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1629" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -46989,7 +46992,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1632" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -47015,7 +47018,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1633" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -47041,7 +47044,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1634" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -47067,7 +47070,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1635" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -47093,7 +47096,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1636" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -47145,7 +47148,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1638" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -47171,7 +47174,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1639" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -47223,7 +47226,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G1641" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -47301,7 +47304,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1644" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -47353,7 +47356,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1646" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -47405,7 +47408,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1648" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47457,7 +47460,7 @@
         <v>3</v>
       </c>
       <c r="G1650" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -47483,7 +47486,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1651" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47535,7 +47538,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1653" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -47587,7 +47590,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1655" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -47613,7 +47616,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1656" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -47639,7 +47642,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1657" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -47665,7 +47668,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G1658" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -47691,7 +47694,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1659" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -47717,7 +47720,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1660" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -47743,7 +47746,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1661" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47769,7 +47772,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1662" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -47795,7 +47798,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1663" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -47821,7 +47824,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1664" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -47847,7 +47850,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1665" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -47873,7 +47876,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1666" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -47899,7 +47902,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1667" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -47951,7 +47954,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1669" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -47977,7 +47980,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1670" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -48003,7 +48006,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1671" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -48029,7 +48032,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1672" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -48055,7 +48058,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1673" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -48133,7 +48136,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1676" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -48159,7 +48162,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1677" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -48185,7 +48188,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1678" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -48211,7 +48214,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1679" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -48237,7 +48240,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1680" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -48341,7 +48344,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1684" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -48367,7 +48370,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G1685" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -48419,7 +48422,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1687" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -48445,7 +48448,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1688" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -48471,7 +48474,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1689" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -48497,7 +48500,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G1690" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -48523,7 +48526,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1691" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -48601,7 +48604,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1694" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -48627,7 +48630,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1695" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -48679,7 +48682,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1697" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -48731,7 +48734,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1699" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -48809,7 +48812,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1702" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -48861,7 +48864,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1704" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -48887,7 +48890,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1705" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -48913,7 +48916,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1706" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -49017,7 +49020,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1710" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -49095,7 +49098,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1713" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -49147,7 +49150,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1715" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -49173,7 +49176,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1716" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -49199,7 +49202,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1717" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -49225,7 +49228,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1718" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -49251,7 +49254,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1719" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -49329,7 +49332,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1722" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -49381,7 +49384,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1724" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -49407,7 +49410,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1725" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -49433,7 +49436,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1726" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -49485,7 +49488,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1728" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -49511,7 +49514,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1729" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -49537,7 +49540,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1730" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -49563,7 +49566,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1731" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -49589,7 +49592,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1732" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -49615,7 +49618,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1733" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -49667,7 +49670,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1735" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -49693,7 +49696,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G1736" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -49719,7 +49722,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1737" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -49745,7 +49748,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1738" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -49771,7 +49774,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1739" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -49797,7 +49800,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1740" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -49823,7 +49826,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1741" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -49875,7 +49878,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1743" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -49901,7 +49904,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1744" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -49953,7 +49956,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1746" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -50031,7 +50034,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1749" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -50057,7 +50060,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1750" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -50083,7 +50086,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1751" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -50109,7 +50112,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1752" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -50161,7 +50164,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1754" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -50187,7 +50190,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1755" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -50239,7 +50242,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1757" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -50265,7 +50268,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1758" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -50317,7 +50320,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1760" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -50369,7 +50372,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1762" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -50395,7 +50398,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1763" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -50421,7 +50424,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1764" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -50447,7 +50450,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1765" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50525,7 +50528,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G1768" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -50577,7 +50580,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1770" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -50603,7 +50606,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1771" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -50629,7 +50632,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1772" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -50681,7 +50684,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1774" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -50785,7 +50788,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1778" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -50811,7 +50814,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1779" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -50837,7 +50840,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1780" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -50863,7 +50866,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1781" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -50889,7 +50892,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1782" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -50993,7 +50996,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1786" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -51045,7 +51048,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1788" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -51071,7 +51074,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1789" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -51097,7 +51100,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1790" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -51123,7 +51126,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1791" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -51175,7 +51178,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1793" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -51201,7 +51204,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1794" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -51227,7 +51230,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -51279,7 +51282,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1797" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -51305,7 +51308,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G1798" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -51357,7 +51360,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1800" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -51383,7 +51386,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1801" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -51409,7 +51412,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1802" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -51435,7 +51438,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1803" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -51487,7 +51490,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1805" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -51513,7 +51516,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1806" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -51539,7 +51542,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1807" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -51617,7 +51620,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1810" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -51643,7 +51646,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1811" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -51669,7 +51672,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1812" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -51695,7 +51698,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1813" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -51721,7 +51724,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1814" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -51747,7 +51750,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1815" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -51799,7 +51802,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1817" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -51825,7 +51828,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1818" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -51877,7 +51880,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G1820" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -51929,7 +51932,7 @@
         <v>3</v>
       </c>
       <c r="G1822" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -51955,7 +51958,7 @@
         <v>3</v>
       </c>
       <c r="G1823" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -51981,7 +51984,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1824" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -52007,7 +52010,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1825" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -52033,7 +52036,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1826" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -52059,7 +52062,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1827" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -52085,7 +52088,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1828" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -52137,7 +52140,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1830" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -52163,7 +52166,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1831" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -52189,7 +52192,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1832" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -52215,7 +52218,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1833" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -52241,7 +52244,7 @@
         <v>3</v>
       </c>
       <c r="G1834" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -52267,7 +52270,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1835" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -52319,7 +52322,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G1837" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -52371,7 +52374,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1839" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -52423,7 +52426,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1841" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -52475,7 +52478,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1843" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -52501,7 +52504,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1844" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -52553,7 +52556,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1846" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -52579,7 +52582,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1847" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -52631,7 +52634,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1849" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -52657,7 +52660,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1850" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -52683,7 +52686,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1851" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -52709,7 +52712,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1852" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -52735,7 +52738,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1853" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -52761,7 +52764,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1854" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -52787,7 +52790,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1855" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -52865,7 +52868,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1858" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -52943,7 +52946,7 @@
         <v>2.75</v>
       </c>
       <c r="G1861" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -53021,7 +53024,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1864" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -53047,7 +53050,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1865" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -53073,7 +53076,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1866" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -53099,7 +53102,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1867" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -53125,7 +53128,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1868" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -53255,7 +53258,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1873" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -53281,7 +53284,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1874" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -53307,7 +53310,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1875" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -53333,7 +53336,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1876" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -53385,7 +53388,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1878" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -53437,7 +53440,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1880" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -53463,7 +53466,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1881" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -53515,7 +53518,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1883" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -53541,7 +53544,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1884" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -53593,7 +53596,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1886" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -53645,7 +53648,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1888" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -53723,7 +53726,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1891" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -54035,7 +54038,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1903" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -54061,7 +54064,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1904" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -54139,7 +54142,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1907" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -54191,7 +54194,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1909" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -54217,7 +54220,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1910" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -54269,7 +54272,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1912" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -54555,7 +54558,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1923" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -54581,7 +54584,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1924" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -54659,7 +54662,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1927" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -54685,7 +54688,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1928" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -54737,7 +54740,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G1930" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -54789,7 +54792,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1932" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -55257,7 +55260,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1950" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -55387,7 +55390,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1955" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -55413,7 +55416,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1956" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -55569,7 +55572,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1962" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -55621,7 +55624,7 @@
         <v>2.125</v>
       </c>
       <c r="G1964" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -55647,7 +55650,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1965" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -55673,7 +55676,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1966" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -55725,7 +55728,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1968" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -56713,7 +56716,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G2006" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -56739,7 +56742,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G2007" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -56765,7 +56768,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G2008" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -56791,7 +56794,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G2009" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -56817,7 +56820,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G2010" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -56843,7 +56846,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G2011" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -56921,7 +56924,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G2014" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -56947,7 +56950,7 @@
         <v>2.4449999332428</v>
       </c>
       <c r="G2015" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -56973,7 +56976,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2016" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -57025,7 +57028,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2018" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -57051,7 +57054,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G2019" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -57077,7 +57080,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2020" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -57103,7 +57106,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2021" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -57129,7 +57132,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G2022" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -57181,7 +57184,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2024" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -57233,7 +57236,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G2026" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -57259,7 +57262,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2027" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -57311,7 +57314,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G2029" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -57415,7 +57418,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2033" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -57441,7 +57444,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G2034" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -57493,7 +57496,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G2036" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -57545,7 +57548,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G2038" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -57571,7 +57574,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G2039" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -57623,7 +57626,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2041" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -57649,7 +57652,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2042" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -57675,7 +57678,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G2043" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -57701,7 +57704,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G2044" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -57727,7 +57730,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G2045" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -57753,7 +57756,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G2046" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -57805,7 +57808,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G2048" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -57831,7 +57834,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G2049" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -57857,7 +57860,7 @@
         <v>2.75</v>
       </c>
       <c r="G2050" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -57909,7 +57912,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G2052" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -57961,7 +57964,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G2054" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -57987,7 +57990,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G2055" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -58013,7 +58016,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2056" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -58039,7 +58042,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G2057" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -58065,7 +58068,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G2058" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -58091,7 +58094,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G2059" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -58117,7 +58120,7 @@
         <v>2.75</v>
       </c>
       <c r="G2060" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -58143,7 +58146,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G2061" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -58169,7 +58172,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2062" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -58221,7 +58224,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G2064" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -58247,7 +58250,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G2065" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -58273,7 +58276,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G2066" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -58299,7 +58302,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G2067" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -58325,7 +58328,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G2068" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -58351,7 +58354,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G2069" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -58377,7 +58380,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G2070" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -58403,7 +58406,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G2071" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -58429,7 +58432,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2072" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -58455,7 +58458,7 @@
         <v>2.875</v>
       </c>
       <c r="G2073" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -58481,7 +58484,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G2074" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -58507,7 +58510,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2075" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -58533,7 +58536,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2076" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -58559,7 +58562,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G2077" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -58637,7 +58640,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G2080" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -58689,7 +58692,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2082" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -58793,7 +58796,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G2086" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -58819,7 +58822,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2087" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -59001,7 +59004,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G2094" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -70241,7 +70244,7 @@
     </row>
     <row r="2527">
       <c r="A2527" s="1" t="n">
-        <v>45996.6912384259</v>
+        <v>45996.3333333333</v>
       </c>
       <c r="B2527" t="n">
         <v>28745</v>
@@ -70262,6 +70265,32 @@
         <v>1404</v>
       </c>
       <c r="H2527" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2528">
+      <c r="A2528" s="1" t="n">
+        <v>45999.6911226852</v>
+      </c>
+      <c r="B2528" t="n">
+        <v>28002</v>
+      </c>
+      <c r="C2528" t="n">
+        <v>7.98999977111816</v>
+      </c>
+      <c r="D2528" t="n">
+        <v>7.90999984741211</v>
+      </c>
+      <c r="E2528" t="n">
+        <v>7.92000007629395</v>
+      </c>
+      <c r="F2528" t="n">
+        <v>7.92999982833862</v>
+      </c>
+      <c r="G2528" t="s">
+        <v>1405</v>
+      </c>
+      <c r="H2528" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="1405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="1406">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95473062992096</t>
+    <t xml:space="preserve">1.95473086833954</t>
   </si>
   <si>
     <t xml:space="preserve">FM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95993399620056</t>
+    <t xml:space="preserve">1.95993423461914</t>
   </si>
   <si>
     <t xml:space="preserve">1.9096348285675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8558669090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86453938484192</t>
+    <t xml:space="preserve">1.85586702823639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86453902721405</t>
   </si>
   <si>
     <t xml:space="preserve">1.68415582180023</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">1.69542980194092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61824667453766</t>
+    <t xml:space="preserve">1.61824655532837</t>
   </si>
   <si>
     <t xml:space="preserve">1.52285146713257</t>
@@ -80,16 +80,16 @@
     <t xml:space="preserve">1.34420263767242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45434057712555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55233716964722</t>
+    <t xml:space="preserve">1.45434045791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55233728885651</t>
   </si>
   <si>
     <t xml:space="preserve">1.48989689350128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54366493225098</t>
+    <t xml:space="preserve">1.54366505146027</t>
   </si>
   <si>
     <t xml:space="preserve">1.595698595047</t>
@@ -101,22 +101,22 @@
     <t xml:space="preserve">1.53325831890106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.499436378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43005812168121</t>
+    <t xml:space="preserve">1.49943625926971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4300582408905</t>
   </si>
   <si>
     <t xml:space="preserve">1.40751028060913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38582956790924</t>
+    <t xml:space="preserve">1.38582968711853</t>
   </si>
   <si>
     <t xml:space="preserve">1.28349673748016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17682754993439</t>
+    <t xml:space="preserve">1.17682766914368</t>
   </si>
   <si>
     <t xml:space="preserve">1.24186968803406</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">1.23059582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43873059749603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39710342884064</t>
+    <t xml:space="preserve">1.43873047828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39710354804993</t>
   </si>
   <si>
     <t xml:space="preserve">1.50030362606049</t>
@@ -143,25 +143,25 @@
     <t xml:space="preserve">1.46561455726624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5211169719696</t>
+    <t xml:space="preserve">1.52111709117889</t>
   </si>
   <si>
     <t xml:space="preserve">1.51678085327148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49423289299011</t>
+    <t xml:space="preserve">1.4942330121994</t>
   </si>
   <si>
     <t xml:space="preserve">1.47688841819763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47515404224396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50984311103821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56014227867126</t>
+    <t xml:space="preserve">1.47515392303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5098432302475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56014239788055</t>
   </si>
   <si>
     <t xml:space="preserve">1.58702623844147</t>
@@ -170,16 +170,16 @@
     <t xml:space="preserve">1.55754053592682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52805471420288</t>
+    <t xml:space="preserve">1.52805483341217</t>
   </si>
   <si>
     <t xml:space="preserve">1.54279780387878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51244461536407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55146992206573</t>
+    <t xml:space="preserve">1.51244473457336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55147004127502</t>
   </si>
   <si>
     <t xml:space="preserve">1.61651194095612</t>
@@ -188,13 +188,13 @@
     <t xml:space="preserve">1.67374897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70843815803528</t>
+    <t xml:space="preserve">1.70843827724457</t>
   </si>
   <si>
     <t xml:space="preserve">1.67808520793915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65467000007629</t>
+    <t xml:space="preserve">1.65467011928558</t>
   </si>
   <si>
     <t xml:space="preserve">1.63298940658569</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">1.6061053276062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53499269485474</t>
+    <t xml:space="preserve">1.53499281406403</t>
   </si>
   <si>
     <t xml:space="preserve">1.49770188331604</t>
@@ -218,34 +218,34 @@
     <t xml:space="preserve">1.41791689395905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39970505237579</t>
+    <t xml:space="preserve">1.39970517158508</t>
   </si>
   <si>
     <t xml:space="preserve">1.35200774669647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39190006256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46041119098663</t>
+    <t xml:space="preserve">1.39190018177032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46041107177734</t>
   </si>
   <si>
     <t xml:space="preserve">1.57228338718414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62952053546906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60437095165253</t>
+    <t xml:space="preserve">1.62952041625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60437083244324</t>
   </si>
   <si>
     <t xml:space="preserve">1.60870695114136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62518441677094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65987348556519</t>
+    <t xml:space="preserve">1.62518429756165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65987360477448</t>
   </si>
   <si>
     <t xml:space="preserve">1.58615911006927</t>
@@ -260,28 +260,28 @@
     <t xml:space="preserve">1.58876073360443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49249839782715</t>
+    <t xml:space="preserve">1.49249851703644</t>
   </si>
   <si>
     <t xml:space="preserve">1.4578093290329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47775566577911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47428679466248</t>
+    <t xml:space="preserve">1.47775554656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47428667545319</t>
   </si>
   <si>
     <t xml:space="preserve">1.46908330917358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56794726848602</t>
+    <t xml:space="preserve">1.56794738769531</t>
   </si>
   <si>
     <t xml:space="preserve">1.53932881355286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53065657615662</t>
+    <t xml:space="preserve">1.53065645694733</t>
   </si>
   <si>
     <t xml:space="preserve">1.54106330871582</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">1.5471339225769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55060267448425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56708002090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5740180015564</t>
+    <t xml:space="preserve">1.55060279369354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56708014011383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57401788234711</t>
   </si>
   <si>
     <t xml:space="preserve">1.5107102394104</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">1.56100952625275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54453217983246</t>
+    <t xml:space="preserve">1.54453229904175</t>
   </si>
   <si>
     <t xml:space="preserve">1.45000445842743</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">1.38929855823517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40057241916656</t>
+    <t xml:space="preserve">1.40057253837585</t>
   </si>
   <si>
     <t xml:space="preserve">1.3875640630722</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">1.44740283489227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49163138866425</t>
+    <t xml:space="preserve">1.49163126945496</t>
   </si>
   <si>
     <t xml:space="preserve">1.4838262796402</t>
@@ -350,13 +350,13 @@
     <t xml:space="preserve">1.35981273651123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33726477622986</t>
+    <t xml:space="preserve">1.33726489543915</t>
   </si>
   <si>
     <t xml:space="preserve">1.31124806404114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30084121227264</t>
+    <t xml:space="preserve">1.30084133148193</t>
   </si>
   <si>
     <t xml:space="preserve">1.30257570743561</t>
@@ -371,22 +371,22 @@
     <t xml:space="preserve">1.3823606967926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39623618125916</t>
+    <t xml:space="preserve">1.39623630046844</t>
   </si>
   <si>
     <t xml:space="preserve">1.37715744972229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40490865707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39450180530548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40404140949249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.393634557724</t>
+    <t xml:space="preserve">1.40490853786469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39450192451477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4040412902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39363467693329</t>
   </si>
   <si>
     <t xml:space="preserve">1.42225313186646</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">1.38062620162964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36588335037231</t>
+    <t xml:space="preserve">1.3658834695816</t>
   </si>
   <si>
     <t xml:space="preserve">1.3563437461853</t>
@@ -410,10 +410,10 @@
     <t xml:space="preserve">1.35460937023163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34333550930023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33119416236877</t>
+    <t xml:space="preserve">1.34333539009094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33119428157806</t>
   </si>
   <si>
     <t xml:space="preserve">1.32685804367065</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">1.35547661781311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34940612316132</t>
+    <t xml:space="preserve">1.34940600395203</t>
   </si>
   <si>
     <t xml:space="preserve">1.33813202381134</t>
@@ -449,16 +449,16 @@
     <t xml:space="preserve">1.34853875637054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41704976558685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40317404270172</t>
+    <t xml:space="preserve">1.41704964637756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40317416191101</t>
   </si>
   <si>
     <t xml:space="preserve">1.39536905288696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41097915172577</t>
+    <t xml:space="preserve">1.41097903251648</t>
   </si>
   <si>
     <t xml:space="preserve">1.36501610279083</t>
@@ -482,13 +482,13 @@
     <t xml:space="preserve">1.41358077526093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42138588428497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41271352767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40924477577209</t>
+    <t xml:space="preserve">1.42138576507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41271340847015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40924465656281</t>
   </si>
   <si>
     <t xml:space="preserve">1.42572212219238</t>
@@ -503,16 +503,16 @@
     <t xml:space="preserve">1.34680426120758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36414873600006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36241436004639</t>
+    <t xml:space="preserve">1.36414885520935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36241447925568</t>
   </si>
   <si>
     <t xml:space="preserve">1.33032703399658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32078742980957</t>
+    <t xml:space="preserve">1.32078754901886</t>
   </si>
   <si>
     <t xml:space="preserve">1.3190530538559</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">1.17942941188812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26181602478027</t>
+    <t xml:space="preserve">1.26181590557098</t>
   </si>
   <si>
     <t xml:space="preserve">1.2921689748764</t>
@@ -545,40 +545,40 @@
     <t xml:space="preserve">1.22886145114899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18550002574921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15774881839752</t>
+    <t xml:space="preserve">1.18549990653992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15774869918823</t>
   </si>
   <si>
     <t xml:space="preserve">1.11872339248657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13086473941803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12305963039398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13346636295319</t>
+    <t xml:space="preserve">1.13086462020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12305951118469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13346648216248</t>
   </si>
   <si>
     <t xml:space="preserve">1.11438727378845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11612164974213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11525464057922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09791004657745</t>
+    <t xml:space="preserve">1.11612176895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11525452136993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09790992736816</t>
   </si>
   <si>
     <t xml:space="preserve">1.09270668029785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07536220550537</t>
+    <t xml:space="preserve">1.07536208629608</t>
   </si>
   <si>
     <t xml:space="preserve">1.07276034355164</t>
@@ -587,28 +587,28 @@
     <t xml:space="preserve">1.10398054122925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15427982807159</t>
+    <t xml:space="preserve">1.1542797088623</t>
   </si>
   <si>
     <t xml:space="preserve">1.16295206546783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16208493709564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17856204509735</t>
+    <t xml:space="preserve">1.16208481788635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17856216430664</t>
   </si>
   <si>
     <t xml:space="preserve">1.18289828300476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20544612407684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23493194580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24533867835999</t>
+    <t xml:space="preserve">1.20544624328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23493206501007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2453385591507</t>
   </si>
   <si>
     <t xml:space="preserve">1.21845459938049</t>
@@ -623,10 +623,10 @@
     <t xml:space="preserve">1.2279942035675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22192347049713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23666632175446</t>
+    <t xml:space="preserve">1.22192358970642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23666644096375</t>
   </si>
   <si>
     <t xml:space="preserve">1.26875388622284</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">1.39883804321289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38669669628143</t>
+    <t xml:space="preserve">1.38669681549072</t>
   </si>
   <si>
     <t xml:space="preserve">1.35721111297607</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">1.33292853832245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28870010375977</t>
+    <t xml:space="preserve">1.28869998455048</t>
   </si>
   <si>
     <t xml:space="preserve">1.25747990608215</t>
@@ -662,22 +662,22 @@
     <t xml:space="preserve">1.2444714307785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22712683677673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25661265850067</t>
+    <t xml:space="preserve">1.22712695598602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25661253929138</t>
   </si>
   <si>
     <t xml:space="preserve">1.22365808486938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2227908372879</t>
+    <t xml:space="preserve">1.22279071807861</t>
   </si>
   <si>
     <t xml:space="preserve">1.25314378738403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22625970840454</t>
+    <t xml:space="preserve">1.22625982761383</t>
   </si>
   <si>
     <t xml:space="preserve">1.21325135231018</t>
@@ -686,13 +686,13 @@
     <t xml:space="preserve">1.20891511440277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20457899570465</t>
+    <t xml:space="preserve">1.20457911491394</t>
   </si>
   <si>
     <t xml:space="preserve">1.21585297584534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21672022342682</t>
+    <t xml:space="preserve">1.21672010421753</t>
   </si>
   <si>
     <t xml:space="preserve">1.19070339202881</t>
@@ -704,13 +704,13 @@
     <t xml:space="preserve">1.18810176849365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19157063961029</t>
+    <t xml:space="preserve">1.191570520401</t>
   </si>
   <si>
     <t xml:space="preserve">1.20284450054169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19243776798248</t>
+    <t xml:space="preserve">1.19243788719177</t>
   </si>
   <si>
     <t xml:space="preserve">1.2340646982193</t>
@@ -731,46 +731,46 @@
     <t xml:space="preserve">1.24273693561554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23579907417297</t>
+    <t xml:space="preserve">1.23579919338226</t>
   </si>
   <si>
     <t xml:space="preserve">1.22018897533417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24794042110443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2496749162674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29043459892273</t>
+    <t xml:space="preserve">1.24794030189514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24967479705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29043447971344</t>
   </si>
   <si>
     <t xml:space="preserve">1.29303622245789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31818580627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30691170692444</t>
+    <t xml:space="preserve">1.31818568706512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30691182613373</t>
   </si>
   <si>
     <t xml:space="preserve">1.27309000492096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24013519287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27916061878204</t>
+    <t xml:space="preserve">1.24013531208038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27916049957275</t>
   </si>
   <si>
     <t xml:space="preserve">1.27048826217651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26528489589691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28436398506165</t>
+    <t xml:space="preserve">1.26528477668762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28436386585236</t>
   </si>
   <si>
     <t xml:space="preserve">1.27482438087463</t>
@@ -779,10 +779,10 @@
     <t xml:space="preserve">1.26441764831543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28523111343384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2869656085968</t>
+    <t xml:space="preserve">1.28523099422455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28696548938751</t>
   </si>
   <si>
     <t xml:space="preserve">1.3398665189743</t>
@@ -791,13 +791,13 @@
     <t xml:space="preserve">1.33899927139282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41184639930725</t>
+    <t xml:space="preserve">1.41184628009796</t>
   </si>
   <si>
     <t xml:space="preserve">1.57835412025452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51851534843445</t>
+    <t xml:space="preserve">1.51851546764374</t>
   </si>
   <si>
     <t xml:space="preserve">1.54019606113434</t>
@@ -809,34 +809,34 @@
     <t xml:space="preserve">1.50724148750305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50203800201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4786229133606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43352699279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40577590465546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38496232032776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47168517112732</t>
+    <t xml:space="preserve">1.50203812122345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47862303256989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43352711200714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40577578544617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38496243953705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47168505191803</t>
   </si>
   <si>
     <t xml:space="preserve">1.48729526996613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47602128982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45694208145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46821618080139</t>
+    <t xml:space="preserve">1.47602117061615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45694220066071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4682160615921</t>
   </si>
   <si>
     <t xml:space="preserve">1.45867669582367</t>
@@ -848,22 +848,22 @@
     <t xml:space="preserve">1.45607495307922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49076390266418</t>
+    <t xml:space="preserve">1.49076402187347</t>
   </si>
   <si>
     <t xml:space="preserve">1.47341954708099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52892196178436</t>
+    <t xml:space="preserve">1.52892208099365</t>
   </si>
   <si>
     <t xml:space="preserve">1.50637412071228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57488524913788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58269023895264</t>
+    <t xml:space="preserve">1.57488512992859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58269011974335</t>
   </si>
   <si>
     <t xml:space="preserve">1.56187677383423</t>
@@ -890,10 +890,10 @@
     <t xml:space="preserve">1.48816239833832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51591360569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56881463527679</t>
+    <t xml:space="preserve">1.51591372489929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5688145160675</t>
   </si>
   <si>
     <t xml:space="preserve">1.57054901123047</t>
@@ -902,19 +902,19 @@
     <t xml:space="preserve">1.64686501026154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78648853302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7604718208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85933566093445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8662736415863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84199118614197</t>
+    <t xml:space="preserve">1.78648841381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76047170162201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85933578014374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86627340316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84199142456055</t>
   </si>
   <si>
     <t xml:space="preserve">2.15245866775513</t>
@@ -932,37 +932,37 @@
     <t xml:space="preserve">1.95126187801361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05186033248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01543641090393</t>
+    <t xml:space="preserve">2.05186009407043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01543664932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.98074734210968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9044314622879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90790057182312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91657257080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90616607666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84892904758453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87321138381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83158433437347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84719455242157</t>
+    <t xml:space="preserve">1.90443170070648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90790033340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91657280921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90616595745087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84892892837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87321150302887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83158445358276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84719479084015</t>
   </si>
   <si>
     <t xml:space="preserve">1.93218290805817</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">1.93738627433777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92524516582489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94258975982666</t>
+    <t xml:space="preserve">1.9252450466156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94258952140808</t>
   </si>
   <si>
     <t xml:space="preserve">1.97727870941162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0206401348114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06920456886292</t>
+    <t xml:space="preserve">2.02063989639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06920480728149</t>
   </si>
   <si>
     <t xml:space="preserve">2.01196765899658</t>
@@ -1007,16 +1007,16 @@
     <t xml:space="preserve">1.82117772102356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91310381889343</t>
+    <t xml:space="preserve">1.91310393810272</t>
   </si>
   <si>
     <t xml:space="preserve">1.72144663333893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67114746570587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69976592063904</t>
+    <t xml:space="preserve">1.67114758491516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69976603984833</t>
   </si>
   <si>
     <t xml:space="preserve">1.68762469291687</t>
@@ -1025,13 +1025,13 @@
     <t xml:space="preserve">1.67895245552063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63992738723755</t>
+    <t xml:space="preserve">1.63992726802826</t>
   </si>
   <si>
     <t xml:space="preserve">1.64773225784302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62865316867828</t>
+    <t xml:space="preserve">1.62865328788757</t>
   </si>
   <si>
     <t xml:space="preserve">1.62691879272461</t>
@@ -1040,13 +1040,13 @@
     <t xml:space="preserve">1.60350370407104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59656596183777</t>
+    <t xml:space="preserve">1.59656572341919</t>
   </si>
   <si>
     <t xml:space="preserve">1.63905990123749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64859938621521</t>
+    <t xml:space="preserve">1.6485995054245</t>
   </si>
   <si>
     <t xml:space="preserve">1.6650767326355</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">1.67548358440399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65640461444855</t>
+    <t xml:space="preserve">1.65640449523926</t>
   </si>
   <si>
     <t xml:space="preserve">1.63038766384125</t>
@@ -1070,40 +1070,40 @@
     <t xml:space="preserve">1.66681122779846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68155407905579</t>
+    <t xml:space="preserve">1.68155419826508</t>
   </si>
   <si>
     <t xml:space="preserve">1.68935918807983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67721796035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63385653495789</t>
+    <t xml:space="preserve">1.67721807956696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6338564157486</t>
   </si>
   <si>
     <t xml:space="preserve">1.62171542644501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65727186203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71537590026855</t>
+    <t xml:space="preserve">1.65727174282074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71537601947784</t>
   </si>
   <si>
     <t xml:space="preserve">1.66854572296143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71711039543152</t>
+    <t xml:space="preserve">1.71711051464081</t>
   </si>
   <si>
     <t xml:space="preserve">1.7067037820816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72578275203705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72751724720001</t>
+    <t xml:space="preserve">1.72578287124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72751712799072</t>
   </si>
   <si>
     <t xml:space="preserve">1.71190702915192</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">1.74312722682953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77781641483307</t>
+    <t xml:space="preserve">1.77781629562378</t>
   </si>
   <si>
     <t xml:space="preserve">1.77348029613495</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">1.80383312702179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93391752243042</t>
+    <t xml:space="preserve">1.93391728401184</t>
   </si>
   <si>
     <t xml:space="preserve">1.88188374042511</t>
@@ -1130,13 +1130,13 @@
     <t xml:space="preserve">1.95559799671173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88621973991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81684160232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89489197731018</t>
+    <t xml:space="preserve">1.88621962070465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81684172153473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89489209651947</t>
   </si>
   <si>
     <t xml:space="preserve">1.80816924571991</t>
@@ -1145,13 +1145,13 @@
     <t xml:space="preserve">1.82984983921051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85153067111969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7821524143219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81250548362732</t>
+    <t xml:space="preserve">1.85153079032898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78215253353119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81250536441803</t>
   </si>
   <si>
     <t xml:space="preserve">1.79082489013672</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">1.73445510864258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76480793952942</t>
+    <t xml:space="preserve">1.76480805873871</t>
   </si>
   <si>
     <t xml:space="preserve">1.96860635280609</t>
@@ -1172,25 +1172,25 @@
     <t xml:space="preserve">1.89055597782135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8775475025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8341863155365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84285843372345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82551383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83852219581604</t>
+    <t xml:space="preserve">1.87754738330841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83418619632721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84285831451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82551395893097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83852231502533</t>
   </si>
   <si>
     <t xml:space="preserve">1.86020290851593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97294282913208</t>
+    <t xml:space="preserve">1.9729425907135</t>
   </si>
   <si>
     <t xml:space="preserve">1.98161494731903</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">1.98595094680786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04665660858154</t>
+    <t xml:space="preserve">2.04665684700012</t>
   </si>
   <si>
     <t xml:space="preserve">2.03364849090576</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">2.072674036026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08134579658508</t>
+    <t xml:space="preserve">2.08134603500366</t>
   </si>
   <si>
     <t xml:space="preserve">2.1116988658905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15072441101074</t>
+    <t xml:space="preserve">2.15072417259216</t>
   </si>
   <si>
     <t xml:space="preserve">2.05532908439636</t>
@@ -1229,13 +1229,13 @@
     <t xml:space="preserve">2.1854133605957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33717823028564</t>
+    <t xml:space="preserve">2.33717799186707</t>
   </si>
   <si>
     <t xml:space="preserve">2.3024890422821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2808084487915</t>
+    <t xml:space="preserve">2.28080821037292</t>
   </si>
   <si>
     <t xml:space="preserve">2.21142983436584</t>
@@ -1247,16 +1247,16 @@
     <t xml:space="preserve">2.28514456748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44991755485535</t>
+    <t xml:space="preserve">2.44991779327393</t>
   </si>
   <si>
     <t xml:space="preserve">2.48894286155701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59301018714905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38921165466309</t>
+    <t xml:space="preserve">2.59300994873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38921189308167</t>
   </si>
   <si>
     <t xml:space="preserve">2.49761533737183</t>
@@ -1277,16 +1277,16 @@
     <t xml:space="preserve">2.83583378791809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91388416290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92255640029907</t>
+    <t xml:space="preserve">2.91388440132141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92255663871765</t>
   </si>
   <si>
     <t xml:space="preserve">2.93122911453247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87052297592163</t>
+    <t xml:space="preserve">2.87052273750305</t>
   </si>
   <si>
     <t xml:space="preserve">2.92689275741577</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">3.23909473419189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25210332870483</t>
+    <t xml:space="preserve">3.25210309028625</t>
   </si>
   <si>
     <t xml:space="preserve">3.21741390228271</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">3.36050653457642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20874190330505</t>
+    <t xml:space="preserve">3.20874166488647</t>
   </si>
   <si>
     <t xml:space="preserve">3.36917901039124</t>
@@ -1337,19 +1337,19 @@
     <t xml:space="preserve">3.48625445365906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55563282966614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51227188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62934708595276</t>
+    <t xml:space="preserve">3.55563259124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51227164268494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62934684753418</t>
   </si>
   <si>
     <t xml:space="preserve">3.6640362739563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73341417312622</t>
+    <t xml:space="preserve">3.7334144115448</t>
   </si>
   <si>
     <t xml:space="preserve">3.80712866783142</t>
@@ -1364,37 +1364,37 @@
     <t xml:space="preserve">4.0456166267395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09765005111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86783504486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0412802696228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94588565826416</t>
+    <t xml:space="preserve">4.09764957427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86783456802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04127979278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.945885181427</t>
   </si>
   <si>
     <t xml:space="preserve">3.97190189361572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7117338180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91986799240112</t>
+    <t xml:space="preserve">3.71173405647278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91986846923828</t>
   </si>
   <si>
     <t xml:space="preserve">4.07163333892822</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24941444396973</t>
+    <t xml:space="preserve">4.24941492080688</t>
   </si>
   <si>
     <t xml:space="preserve">4.25375080108643</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28410387039185</t>
+    <t xml:space="preserve">4.284104347229</t>
   </si>
   <si>
     <t xml:space="preserve">4.62232208251953</t>
@@ -1409,10 +1409,10 @@
     <t xml:space="preserve">4.75240707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05593633651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98655796051025</t>
+    <t xml:space="preserve">5.05593585968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9865574836731</t>
   </si>
   <si>
     <t xml:space="preserve">4.95186901092529</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">4.87381839752197</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31879329681396</t>
+    <t xml:space="preserve">4.31879281997681</t>
   </si>
   <si>
     <t xml:space="preserve">4.80444049835205</t>
@@ -1433,70 +1433,70 @@
     <t xml:space="preserve">5.01257514953613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0385913848877</t>
+    <t xml:space="preserve">5.03859186172485</t>
   </si>
   <si>
     <t xml:space="preserve">4.91718006134033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82178449630737</t>
+    <t xml:space="preserve">4.82178497314453</t>
   </si>
   <si>
     <t xml:space="preserve">4.85647392272949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89116334915161</t>
+    <t xml:space="preserve">4.89116287231445</t>
   </si>
   <si>
     <t xml:space="preserve">4.83045768737793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76107883453369</t>
+    <t xml:space="preserve">4.76107835769653</t>
   </si>
   <si>
     <t xml:space="preserve">4.54427194595337</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70904493331909</t>
+    <t xml:space="preserve">4.70904541015625</t>
   </si>
   <si>
     <t xml:space="preserve">4.60497808456421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58763360977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64833974838257</t>
+    <t xml:space="preserve">4.58763313293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64833927154541</t>
   </si>
   <si>
     <t xml:space="preserve">4.61365079879761</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53559923171997</t>
+    <t xml:space="preserve">4.53559970855713</t>
   </si>
   <si>
     <t xml:space="preserve">4.47489356994629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40551614761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18437242507935</t>
+    <t xml:space="preserve">4.40551567077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1843729019165</t>
   </si>
   <si>
     <t xml:space="preserve">4.1887092590332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24074268341064</t>
+    <t xml:space="preserve">4.2407431602478</t>
   </si>
   <si>
     <t xml:space="preserve">4.084641456604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9285409450531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91553163528442</t>
+    <t xml:space="preserve">3.92854046821594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91553258895874</t>
   </si>
   <si>
     <t xml:space="preserve">3.85916233062744</t>
@@ -1505,13 +1505,13 @@
     <t xml:space="preserve">3.7811119556427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14101123809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62501096725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31280922889709</t>
+    <t xml:space="preserve">4.14101076126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62501072883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31280899047852</t>
   </si>
   <si>
     <t xml:space="preserve">3.28679227828979</t>
@@ -1523,13 +1523,13 @@
     <t xml:space="preserve">3.00927948951721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09166598320007</t>
+    <t xml:space="preserve">3.09166622161865</t>
   </si>
   <si>
     <t xml:space="preserve">3.03529620170593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04830455780029</t>
+    <t xml:space="preserve">3.04830479621887</t>
   </si>
   <si>
     <t xml:space="preserve">3.07865762710571</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">2.96158170700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89653992652893</t>
+    <t xml:space="preserve">2.89653968811035</t>
   </si>
   <si>
     <t xml:space="preserve">2.90521192550659</t>
@@ -1553,10 +1553,10 @@
     <t xml:space="preserve">2.80548071861267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88786768913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04396843910217</t>
+    <t xml:space="preserve">2.88786745071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04396867752075</t>
   </si>
   <si>
     <t xml:space="preserve">3.2607753276825</t>
@@ -1571,22 +1571,22 @@
     <t xml:space="preserve">3.42554879188538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43855690956116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39519548416138</t>
+    <t xml:space="preserve">3.43855714797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39519572257996</t>
   </si>
   <si>
     <t xml:space="preserve">3.20440554618835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06998538970947</t>
+    <t xml:space="preserve">3.06998562812805</t>
   </si>
   <si>
     <t xml:space="preserve">2.86618685722351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93990159034729</t>
+    <t xml:space="preserve">2.93990135192871</t>
   </si>
   <si>
     <t xml:space="preserve">2.88353133201599</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">2.97459053993225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02228760719299</t>
+    <t xml:space="preserve">3.02228784561157</t>
   </si>
   <si>
     <t xml:space="preserve">3.38218760490417</t>
@@ -1607,22 +1607,22 @@
     <t xml:space="preserve">3.15670824050903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11768293380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08732986450195</t>
+    <t xml:space="preserve">3.11768269538879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08733010292053</t>
   </si>
   <si>
     <t xml:space="preserve">3.06564927101135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81848955154419</t>
+    <t xml:space="preserve">2.81848931312561</t>
   </si>
   <si>
     <t xml:space="preserve">2.68840527534485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73176670074463</t>
+    <t xml:space="preserve">2.73176693916321</t>
   </si>
   <si>
     <t xml:space="preserve">2.63203573226929</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">3.17405247688293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3041365146637</t>
+    <t xml:space="preserve">3.30413675308228</t>
   </si>
   <si>
     <t xml:space="preserve">3.3084728717804</t>
@@ -1643,10 +1643,10 @@
     <t xml:space="preserve">3.17838859558105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10467433929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16104435920715</t>
+    <t xml:space="preserve">3.10467457771301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16104412078857</t>
   </si>
   <si>
     <t xml:space="preserve">3.330153465271</t>
@@ -1658,19 +1658,19 @@
     <t xml:space="preserve">3.5903217792511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88517951965332</t>
+    <t xml:space="preserve">3.88517904281616</t>
   </si>
   <si>
     <t xml:space="preserve">3.90252375602722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85482621192932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11499404907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27543115615845</t>
+    <t xml:space="preserve">3.8548264503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11499452590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27543163299561</t>
   </si>
   <si>
     <t xml:space="preserve">4.10198640823364</t>
@@ -1685,10 +1685,10 @@
     <t xml:space="preserve">3.95889353752136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82447338104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96756625175476</t>
+    <t xml:space="preserve">3.8244731426239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9675657749176</t>
   </si>
   <si>
     <t xml:space="preserve">3.9415488243103</t>
@@ -1700,16 +1700,16 @@
     <t xml:space="preserve">4.00659084320068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06296110153198</t>
+    <t xml:space="preserve">4.06296062469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.05862474441528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01526355743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09331321716309</t>
+    <t xml:space="preserve">4.01526403427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09331369400024</t>
   </si>
   <si>
     <t xml:space="preserve">4.03260803222656</t>
@@ -1724,19 +1724,19 @@
     <t xml:space="preserve">3.82880926132202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75943112373352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74642276763916</t>
+    <t xml:space="preserve">3.75943160057068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74642300605774</t>
   </si>
   <si>
     <t xml:space="preserve">3.56864094734192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77677583694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24507856369019</t>
+    <t xml:space="preserve">3.77677607536316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24507904052734</t>
   </si>
   <si>
     <t xml:space="preserve">4.17136430740356</t>
@@ -1748,31 +1748,31 @@
     <t xml:space="preserve">4.06729698181152</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16269159317017</t>
+    <t xml:space="preserve">4.16269207000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.21906137466431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23207092285156</t>
+    <t xml:space="preserve">4.2320704460144</t>
   </si>
   <si>
     <t xml:space="preserve">4.20171689987183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68302822113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88249063491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76975107192993</t>
+    <t xml:space="preserve">4.68302869796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88249111175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76975154876709</t>
   </si>
   <si>
     <t xml:space="preserve">4.72638988494873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63966703414917</t>
+    <t xml:space="preserve">4.63966751098633</t>
   </si>
   <si>
     <t xml:space="preserve">4.55294466018677</t>
@@ -1790,7 +1790,7 @@
     <t xml:space="preserve">4.04995250701904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27009868621826</t>
+    <t xml:space="preserve">4.2700982093811</t>
   </si>
   <si>
     <t xml:space="preserve">4.12285375595093</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">4.01130437850952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91760349273682</t>
+    <t xml:space="preserve">3.91760301589966</t>
   </si>
   <si>
     <t xml:space="preserve">4.22547912597656</t>
@@ -1808,19 +1808,19 @@
     <t xml:space="preserve">4.00684213638306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8328263759613</t>
+    <t xml:space="preserve">3.83282613754272</t>
   </si>
   <si>
     <t xml:space="preserve">3.85513615608215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8595974445343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93098974227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83728837966919</t>
+    <t xml:space="preserve">3.85959792137146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93098926544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83728814125061</t>
   </si>
   <si>
     <t xml:space="preserve">4.01576662063599</t>
@@ -1832,13 +1832,13 @@
     <t xml:space="preserve">3.95776081085205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79266858100891</t>
+    <t xml:space="preserve">3.79266834259033</t>
   </si>
   <si>
     <t xml:space="preserve">3.74358701705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76143479347229</t>
+    <t xml:space="preserve">3.76143455505371</t>
   </si>
   <si>
     <t xml:space="preserve">3.61419010162354</t>
@@ -1853,13 +1853,13 @@
     <t xml:space="preserve">3.48479294776917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67219519615173</t>
+    <t xml:space="preserve">3.67219543457031</t>
   </si>
   <si>
     <t xml:space="preserve">3.59634208679199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58741807937622</t>
+    <t xml:space="preserve">3.5874183177948</t>
   </si>
   <si>
     <t xml:space="preserve">3.64096164703369</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">3.52495074272156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41786360740662</t>
+    <t xml:space="preserve">3.41786336898804</t>
   </si>
   <si>
     <t xml:space="preserve">3.44909739494324</t>
@@ -1895,19 +1895,19 @@
     <t xml:space="preserve">3.41340160369873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42678761482239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36878204345703</t>
+    <t xml:space="preserve">3.42678737640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36878228187561</t>
   </si>
   <si>
     <t xml:space="preserve">3.34647226333618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31523847579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32862424850464</t>
+    <t xml:space="preserve">3.31523823738098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32862448692322</t>
   </si>
   <si>
     <t xml:space="preserve">3.36432003974915</t>
@@ -1943,10 +1943,10 @@
     <t xml:space="preserve">3.33308601379395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35093402862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52941274642944</t>
+    <t xml:space="preserve">3.35093426704407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52941250801086</t>
   </si>
   <si>
     <t xml:space="preserve">3.65880942344666</t>
@@ -1955,10 +1955,10 @@
     <t xml:space="preserve">3.71235322952271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81051635742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80605411529541</t>
+    <t xml:space="preserve">3.81051659584045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80605435371399</t>
   </si>
   <si>
     <t xml:space="preserve">3.7658965587616</t>
@@ -1973,40 +1973,40 @@
     <t xml:space="preserve">3.4669451713562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62757587432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78374409675598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69004344940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7078914642334</t>
+    <t xml:space="preserve">3.62757611274719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78374433517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69004368782043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70789122581482</t>
   </si>
   <si>
     <t xml:space="preserve">3.67665719985962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73912477493286</t>
+    <t xml:space="preserve">3.73912501335144</t>
   </si>
   <si>
     <t xml:space="preserve">3.68558144569397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66773343086243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69896697998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7212769985199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72573924064636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62311387062073</t>
+    <t xml:space="preserve">3.66773366928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69896721839905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72127723693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72573947906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62311363220215</t>
   </si>
   <si>
     <t xml:space="preserve">3.60972809791565</t>
@@ -2021,7 +2021,7 @@
     <t xml:space="preserve">3.96668481826782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73466300964355</t>
+    <t xml:space="preserve">3.73466277122498</t>
   </si>
   <si>
     <t xml:space="preserve">3.69450497627258</t>
@@ -2039,25 +2039,25 @@
     <t xml:space="preserve">3.57849431037903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56510806083679</t>
+    <t xml:space="preserve">3.56510829925537</t>
   </si>
   <si>
     <t xml:space="preserve">3.93991351127625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06038665771484</t>
+    <t xml:space="preserve">4.06038618087769</t>
   </si>
   <si>
     <t xml:space="preserve">3.91314196586609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98899435997009</t>
+    <t xml:space="preserve">3.98899483680725</t>
   </si>
   <si>
     <t xml:space="preserve">3.98007082939148</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12731599807739</t>
+    <t xml:space="preserve">4.12731552124023</t>
   </si>
   <si>
     <t xml:space="preserve">4.05146217346191</t>
@@ -2084,13 +2084,13 @@
     <t xml:space="preserve">3.93545150756836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89083194732666</t>
+    <t xml:space="preserve">3.8908314704895</t>
   </si>
   <si>
     <t xml:space="preserve">4.07823419570923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19424438476562</t>
+    <t xml:space="preserve">4.19424486160278</t>
   </si>
   <si>
     <t xml:space="preserve">4.00238084793091</t>
@@ -2102,13 +2102,13 @@
     <t xml:space="preserve">4.08715772628784</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21655464172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46196269989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53335428237915</t>
+    <t xml:space="preserve">4.21655511856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46196317672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53335380554199</t>
   </si>
   <si>
     <t xml:space="preserve">4.64044094085693</t>
@@ -2117,19 +2117,19 @@
     <t xml:space="preserve">4.58689785003662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64936494827271</t>
+    <t xml:space="preserve">4.64936542510986</t>
   </si>
   <si>
     <t xml:space="preserve">4.7564525604248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78322458267212</t>
+    <t xml:space="preserve">4.78322410583496</t>
   </si>
   <si>
     <t xml:space="preserve">4.68506097793579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83676815032959</t>
+    <t xml:space="preserve">4.83676767349243</t>
   </si>
   <si>
     <t xml:space="preserve">4.81892013549805</t>
@@ -2138,13 +2138,13 @@
     <t xml:space="preserve">4.90815925598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00632238388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89923477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85461521148682</t>
+    <t xml:space="preserve">5.00632190704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89923524856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85461568832397</t>
   </si>
   <si>
     <t xml:space="preserve">4.9795503616333</t>
@@ -2168,10 +2168,10 @@
     <t xml:space="preserve">4.76537656784058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82784414291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80999612808228</t>
+    <t xml:space="preserve">4.82784366607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80999565124512</t>
   </si>
   <si>
     <t xml:space="preserve">4.94385480880737</t>
@@ -2180,13 +2180,13 @@
     <t xml:space="preserve">5.06878995895386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.997398853302</t>
+    <t xml:space="preserve">4.99739837646484</t>
   </si>
   <si>
     <t xml:space="preserve">5.23834466934204</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45251846313477</t>
+    <t xml:space="preserve">5.45251893997192</t>
   </si>
   <si>
     <t xml:space="preserve">5.83624744415283</t>
@@ -2201,46 +2201,46 @@
     <t xml:space="preserve">5.15802955627441</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88138675689697</t>
+    <t xml:space="preserve">4.88138723373413</t>
   </si>
   <si>
     <t xml:space="preserve">4.70290899276733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71183300018311</t>
+    <t xml:space="preserve">4.71183347702026</t>
   </si>
   <si>
     <t xml:space="preserve">4.73860454559326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63151741027832</t>
+    <t xml:space="preserve">4.63151788711548</t>
   </si>
   <si>
     <t xml:space="preserve">4.67613697052002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56012630462646</t>
+    <t xml:space="preserve">4.56012582778931</t>
   </si>
   <si>
     <t xml:space="preserve">4.41734313964844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14516401290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02022886276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98453259468079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94883704185486</t>
+    <t xml:space="preserve">4.14516353607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02022838592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98453307151794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94883751869202</t>
   </si>
   <si>
     <t xml:space="preserve">3.8015923500061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12783598899841</t>
+    <t xml:space="preserve">3.12783575057983</t>
   </si>
   <si>
     <t xml:space="preserve">3.15906977653503</t>
@@ -2249,13 +2249,13 @@
     <t xml:space="preserve">3.25277090072632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72625923156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75749325752258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44961738586426</t>
+    <t xml:space="preserve">2.72625946998596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.757493019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44961762428284</t>
   </si>
   <si>
     <t xml:space="preserve">2.45854163169861</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">1.99895930290222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10604619979858</t>
+    <t xml:space="preserve">2.10604643821716</t>
   </si>
   <si>
     <t xml:space="preserve">2.2577531337738</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">2.45407962799072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46300339698792</t>
+    <t xml:space="preserve">2.46300363540649</t>
   </si>
   <si>
     <t xml:space="preserve">2.56116652488708</t>
@@ -2300,31 +2300,31 @@
     <t xml:space="preserve">2.73964524269104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23938512802124</t>
+    <t xml:space="preserve">3.23938536643982</t>
   </si>
   <si>
     <t xml:space="preserve">3.20368933677673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10998773574829</t>
+    <t xml:space="preserve">3.10998797416687</t>
   </si>
   <si>
     <t xml:space="preserve">2.91812372207642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85119414329529</t>
+    <t xml:space="preserve">2.85119438171387</t>
   </si>
   <si>
     <t xml:space="preserve">2.99843883514404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93597149848938</t>
+    <t xml:space="preserve">2.93597173690796</t>
   </si>
   <si>
     <t xml:space="preserve">2.94489550590515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89135193824768</t>
+    <t xml:space="preserve">2.8913516998291</t>
   </si>
   <si>
     <t xml:space="preserve">2.97612929344177</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">3.00290107727051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13229775428772</t>
+    <t xml:space="preserve">3.1322979927063</t>
   </si>
   <si>
     <t xml:space="preserve">3.0118248462677</t>
@@ -4227,6 +4227,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.92999982833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05000019073486</t>
   </si>
 </sst>
 </file>
@@ -70293,7 +70296,7 @@
     </row>
     <row r="2529">
       <c r="A2529" s="1" t="n">
-        <v>46000.6912384259</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B2529" t="n">
         <v>93753</v>
@@ -70314,6 +70317,32 @@
         <v>1397</v>
       </c>
       <c r="H2529" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" s="1" t="n">
+        <v>46001.6911574074</v>
+      </c>
+      <c r="B2530" t="n">
+        <v>84179</v>
+      </c>
+      <c r="C2530" t="n">
+        <v>8.05000019073486</v>
+      </c>
+      <c r="D2530" t="n">
+        <v>7.84000015258789</v>
+      </c>
+      <c r="E2530" t="n">
+        <v>8.02000045776367</v>
+      </c>
+      <c r="F2530" t="n">
+        <v>8.05000019073486</v>
+      </c>
+      <c r="G2530" t="s">
+        <v>1405</v>
+      </c>
+      <c r="H2530" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -70322,7 +70322,7 @@
     </row>
     <row r="2530">
       <c r="A2530" s="1" t="n">
-        <v>46001.6911574074</v>
+        <v>46001.3333333333</v>
       </c>
       <c r="B2530" t="n">
         <v>84179</v>
@@ -70343,6 +70343,32 @@
         <v>1405</v>
       </c>
       <c r="H2530" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2531">
+      <c r="A2531" s="1" t="n">
+        <v>46002.6911111111</v>
+      </c>
+      <c r="B2531" t="n">
+        <v>43740</v>
+      </c>
+      <c r="C2531" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="D2531" t="n">
+        <v>7.88000011444092</v>
+      </c>
+      <c r="E2531" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2531" t="n">
+        <v>7.88000011444092</v>
+      </c>
+      <c r="G2531" t="s">
+        <v>1388</v>
+      </c>
+      <c r="H2531" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95473086833954</t>
+    <t xml:space="preserve">1.95473062992096</t>
   </si>
   <si>
     <t xml:space="preserve">FM.MI</t>
@@ -50,10 +50,10 @@
     <t xml:space="preserve">1.9096348285675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85586702823639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86453902721405</t>
+    <t xml:space="preserve">1.8558669090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86453914642334</t>
   </si>
   <si>
     <t xml:space="preserve">1.68415582180023</t>
@@ -65,10 +65,10 @@
     <t xml:space="preserve">1.74486172199249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69542980194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61824655532837</t>
+    <t xml:space="preserve">1.69542968273163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61824667453766</t>
   </si>
   <si>
     <t xml:space="preserve">1.52285146713257</t>
@@ -80,16 +80,16 @@
     <t xml:space="preserve">1.34420263767242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45434045791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55233728885651</t>
+    <t xml:space="preserve">1.45434057712555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55233716964722</t>
   </si>
   <si>
     <t xml:space="preserve">1.48989689350128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54366505146027</t>
+    <t xml:space="preserve">1.54366493225098</t>
   </si>
   <si>
     <t xml:space="preserve">1.595698595047</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">1.40751028060913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38582968711853</t>
+    <t xml:space="preserve">1.38582956790924</t>
   </si>
   <si>
     <t xml:space="preserve">1.28349673748016</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">1.47515392303467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5098432302475</t>
+    <t xml:space="preserve">1.50984311103821</t>
   </si>
   <si>
     <t xml:space="preserve">1.56014239788055</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">1.54279780387878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51244473457336</t>
+    <t xml:space="preserve">1.51244461536407</t>
   </si>
   <si>
     <t xml:space="preserve">1.55147004127502</t>
@@ -203,10 +203,10 @@
     <t xml:space="preserve">1.6061053276062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53499281406403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49770188331604</t>
+    <t xml:space="preserve">1.53499269485474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49770200252533</t>
   </si>
   <si>
     <t xml:space="preserve">1.49683463573456</t>
@@ -215,19 +215,19 @@
     <t xml:space="preserve">1.48122453689575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41791689395905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39970517158508</t>
+    <t xml:space="preserve">1.41791701316833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39970505237579</t>
   </si>
   <si>
     <t xml:space="preserve">1.35200774669647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39190018177032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46041107177734</t>
+    <t xml:space="preserve">1.39190006256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46041119098663</t>
   </si>
   <si>
     <t xml:space="preserve">1.57228338718414</t>
@@ -236,16 +236,16 @@
     <t xml:space="preserve">1.62952041625977</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60437083244324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60870695114136</t>
+    <t xml:space="preserve">1.60437095165253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60870683193207</t>
   </si>
   <si>
     <t xml:space="preserve">1.62518429756165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65987360477448</t>
+    <t xml:space="preserve">1.65987348556519</t>
   </si>
   <si>
     <t xml:space="preserve">1.58615911006927</t>
@@ -260,16 +260,16 @@
     <t xml:space="preserve">1.58876073360443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49249851703644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4578093290329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47775554656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47428667545319</t>
+    <t xml:space="preserve">1.49249839782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45780944824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47775566577911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47428679466248</t>
   </si>
   <si>
     <t xml:space="preserve">1.46908330917358</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">1.54106330871582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56968176364899</t>
+    <t xml:space="preserve">1.5696816444397</t>
   </si>
   <si>
     <t xml:space="preserve">1.5471339225769</t>
@@ -296,16 +296,16 @@
     <t xml:space="preserve">1.55060279369354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56708014011383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57401788234711</t>
+    <t xml:space="preserve">1.56708002090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5740180015564</t>
   </si>
   <si>
     <t xml:space="preserve">1.5107102394104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59136247634888</t>
+    <t xml:space="preserve">1.59136259555817</t>
   </si>
   <si>
     <t xml:space="preserve">1.56100952625275</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">1.3294597864151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3884311914444</t>
+    <t xml:space="preserve">1.38843107223511</t>
   </si>
   <si>
     <t xml:space="preserve">1.39016568660736</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">1.33726489543915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31124806404114</t>
+    <t xml:space="preserve">1.31124794483185</t>
   </si>
   <si>
     <t xml:space="preserve">1.30084133148193</t>
@@ -365,13 +365,13 @@
     <t xml:space="preserve">1.36154723167419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37802445888519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3823606967926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39623630046844</t>
+    <t xml:space="preserve">1.3780243396759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38236057758331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39623618125916</t>
   </si>
   <si>
     <t xml:space="preserve">1.37715744972229</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">1.4040412902832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39363467693329</t>
+    <t xml:space="preserve">1.393634557724</t>
   </si>
   <si>
     <t xml:space="preserve">1.42225313186646</t>
@@ -401,13 +401,13 @@
     <t xml:space="preserve">1.38062620162964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3658834695816</t>
+    <t xml:space="preserve">1.36588335037231</t>
   </si>
   <si>
     <t xml:space="preserve">1.3563437461853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35460937023163</t>
+    <t xml:space="preserve">1.35460925102234</t>
   </si>
   <si>
     <t xml:space="preserve">1.34333539009094</t>
@@ -422,13 +422,13 @@
     <t xml:space="preserve">1.30170845985413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30777907371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34767162799835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34506988525391</t>
+    <t xml:space="preserve">1.3077791929245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34767174720764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34506976604462</t>
   </si>
   <si>
     <t xml:space="preserve">1.33379590511322</t>
@@ -446,10 +446,10 @@
     <t xml:space="preserve">1.33813202381134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34853875637054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41704964637756</t>
+    <t xml:space="preserve">1.34853863716125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41704976558685</t>
   </si>
   <si>
     <t xml:space="preserve">1.40317416191101</t>
@@ -458,16 +458,16 @@
     <t xml:space="preserve">1.39536905288696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41097903251648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36501610279083</t>
+    <t xml:space="preserve">1.41097915172577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36501598358154</t>
   </si>
   <si>
     <t xml:space="preserve">1.38322794437408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36761784553528</t>
+    <t xml:space="preserve">1.36761796474457</t>
   </si>
   <si>
     <t xml:space="preserve">1.38149344921112</t>
@@ -485,10 +485,10 @@
     <t xml:space="preserve">1.42138576507568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41271340847015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40924465656281</t>
+    <t xml:space="preserve">1.41271352767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40924477577209</t>
   </si>
   <si>
     <t xml:space="preserve">1.42572212219238</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">1.36414885520935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36241447925568</t>
+    <t xml:space="preserve">1.36241436004639</t>
   </si>
   <si>
     <t xml:space="preserve">1.33032703399658</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">1.23146307468414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21758759021759</t>
+    <t xml:space="preserve">1.2175874710083</t>
   </si>
   <si>
     <t xml:space="preserve">1.24880766868591</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">1.13086462020874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12305951118469</t>
+    <t xml:space="preserve">1.12305963039398</t>
   </si>
   <si>
     <t xml:space="preserve">1.13346648216248</t>
@@ -569,7 +569,7 @@
     <t xml:space="preserve">1.11612176895142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11525452136993</t>
+    <t xml:space="preserve">1.11525464057922</t>
   </si>
   <si>
     <t xml:space="preserve">1.09790992736816</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">1.09270668029785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07536208629608</t>
+    <t xml:space="preserve">1.07536220550537</t>
   </si>
   <si>
     <t xml:space="preserve">1.07276034355164</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">1.16208481788635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17856216430664</t>
+    <t xml:space="preserve">1.17856204509735</t>
   </si>
   <si>
     <t xml:space="preserve">1.18289828300476</t>
@@ -605,25 +605,25 @@
     <t xml:space="preserve">1.20544624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23493206501007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2453385591507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21845459938049</t>
+    <t xml:space="preserve">1.23493194580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24533867835999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2184544801712</t>
   </si>
   <si>
     <t xml:space="preserve">1.19937562942505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20111012458801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2279942035675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22192358970642</t>
+    <t xml:space="preserve">1.20111000537872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22799408435822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22192347049713</t>
   </si>
   <si>
     <t xml:space="preserve">1.23666644096375</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">1.22712695598602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25661253929138</t>
+    <t xml:space="preserve">1.25661265850067</t>
   </si>
   <si>
     <t xml:space="preserve">1.22365808486938</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">1.25314378738403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22625982761383</t>
+    <t xml:space="preserve">1.22625970840454</t>
   </si>
   <si>
     <t xml:space="preserve">1.21325135231018</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">1.20891511440277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20457911491394</t>
+    <t xml:space="preserve">1.20457899570465</t>
   </si>
   <si>
     <t xml:space="preserve">1.21585297584534</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">1.20284450054169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19243788719177</t>
+    <t xml:space="preserve">1.19243776798248</t>
   </si>
   <si>
     <t xml:space="preserve">1.2340646982193</t>
@@ -728,10 +728,10 @@
     <t xml:space="preserve">1.26355040073395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24273693561554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23579919338226</t>
+    <t xml:space="preserve">1.24273705482483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23579907417297</t>
   </si>
   <si>
     <t xml:space="preserve">1.22018897533417</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">1.24967479705811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29043447971344</t>
+    <t xml:space="preserve">1.29043459892273</t>
   </si>
   <si>
     <t xml:space="preserve">1.29303622245789</t>
@@ -758,19 +758,19 @@
     <t xml:space="preserve">1.27309000492096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24013531208038</t>
+    <t xml:space="preserve">1.24013519287109</t>
   </si>
   <si>
     <t xml:space="preserve">1.27916049957275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27048826217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26528477668762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28436386585236</t>
+    <t xml:space="preserve">1.2704883813858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26528489589691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28436398506165</t>
   </si>
   <si>
     <t xml:space="preserve">1.27482438087463</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">1.28523099422455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28696548938751</t>
+    <t xml:space="preserve">1.2869656085968</t>
   </si>
   <si>
     <t xml:space="preserve">1.3398665189743</t>
@@ -797,22 +797,22 @@
     <t xml:space="preserve">1.57835412025452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51851546764374</t>
+    <t xml:space="preserve">1.51851534843445</t>
   </si>
   <si>
     <t xml:space="preserve">1.54019606113434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49856925010681</t>
+    <t xml:space="preserve">1.49856913089752</t>
   </si>
   <si>
     <t xml:space="preserve">1.50724148750305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50203812122345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47862303256989</t>
+    <t xml:space="preserve">1.50203800201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4786229133606</t>
   </si>
   <si>
     <t xml:space="preserve">1.43352711200714</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">1.40577578544617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38496243953705</t>
+    <t xml:space="preserve">1.38496232032776</t>
   </si>
   <si>
     <t xml:space="preserve">1.47168505191803</t>
@@ -836,10 +836,10 @@
     <t xml:space="preserve">1.45694220066071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4682160615921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45867669582367</t>
+    <t xml:space="preserve">1.46821618080139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45867657661438</t>
   </si>
   <si>
     <t xml:space="preserve">1.45954382419586</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">1.50637412071228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57488512992859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58269011974335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56187677383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53585994243622</t>
+    <t xml:space="preserve">1.57488524913788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58269023895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56187665462494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53585982322693</t>
   </si>
   <si>
     <t xml:space="preserve">1.48642790317535</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">1.48816239833832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51591372489929</t>
+    <t xml:space="preserve">1.51591360569</t>
   </si>
   <si>
     <t xml:space="preserve">1.5688145160675</t>
@@ -908,10 +908,10 @@
     <t xml:space="preserve">1.76047170162201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85933578014374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86627340316772</t>
+    <t xml:space="preserve">1.85933589935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8662736415863</t>
   </si>
   <si>
     <t xml:space="preserve">1.84199142456055</t>
@@ -935,10 +935,10 @@
     <t xml:space="preserve">2.05186009407043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01543664932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98074734210968</t>
+    <t xml:space="preserve">2.01543641090393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98074758052826</t>
   </si>
   <si>
     <t xml:space="preserve">1.90443170070648</t>
@@ -950,19 +950,19 @@
     <t xml:space="preserve">1.91657280921936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90616595745087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84892892837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87321150302887</t>
+    <t xml:space="preserve">1.90616607666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84892904758453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87321162223816</t>
   </si>
   <si>
     <t xml:space="preserve">1.83158445358276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84719479084015</t>
+    <t xml:space="preserve">1.84719467163086</t>
   </si>
   <si>
     <t xml:space="preserve">1.93218290805817</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">1.93738627433777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9252450466156</t>
+    <t xml:space="preserve">1.92524516582489</t>
   </si>
   <si>
     <t xml:space="preserve">1.94258952140808</t>
@@ -980,10 +980,10 @@
     <t xml:space="preserve">1.97727870941162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02063989639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06920480728149</t>
+    <t xml:space="preserve">2.0206401348114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06920456886292</t>
   </si>
   <si>
     <t xml:space="preserve">2.01196765899658</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">2.01370239257812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99462330341339</t>
+    <t xml:space="preserve">1.99462306499481</t>
   </si>
   <si>
     <t xml:space="preserve">1.94432413578033</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">1.82117772102356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91310393810272</t>
+    <t xml:space="preserve">1.91310405731201</t>
   </si>
   <si>
     <t xml:space="preserve">1.72144663333893</t>
@@ -1016,7 +1016,7 @@
     <t xml:space="preserve">1.67114758491516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69976603984833</t>
+    <t xml:space="preserve">1.69976592063904</t>
   </si>
   <si>
     <t xml:space="preserve">1.68762469291687</t>
@@ -1028,10 +1028,10 @@
     <t xml:space="preserve">1.63992726802826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64773225784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62865328788757</t>
+    <t xml:space="preserve">1.64773237705231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62865316867828</t>
   </si>
   <si>
     <t xml:space="preserve">1.62691879272461</t>
@@ -1040,13 +1040,13 @@
     <t xml:space="preserve">1.60350370407104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59656572341919</t>
+    <t xml:space="preserve">1.59656584262848</t>
   </si>
   <si>
     <t xml:space="preserve">1.63905990123749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6485995054245</t>
+    <t xml:space="preserve">1.64859938621521</t>
   </si>
   <si>
     <t xml:space="preserve">1.6650767326355</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">1.69109380245209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72925162315369</t>
+    <t xml:space="preserve">1.7292515039444</t>
   </si>
   <si>
     <t xml:space="preserve">1.67548358440399</t>
@@ -1079,28 +1079,28 @@
     <t xml:space="preserve">1.67721807956696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6338564157486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62171542644501</t>
+    <t xml:space="preserve">1.63385653495789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6217155456543</t>
   </si>
   <si>
     <t xml:space="preserve">1.65727174282074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71537601947784</t>
+    <t xml:space="preserve">1.71537590026855</t>
   </si>
   <si>
     <t xml:space="preserve">1.66854572296143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71711051464081</t>
+    <t xml:space="preserve">1.71711039543152</t>
   </si>
   <si>
     <t xml:space="preserve">1.7067037820816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72578287124634</t>
+    <t xml:space="preserve">1.72578275203705</t>
   </si>
   <si>
     <t xml:space="preserve">1.72751712799072</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">1.74312722682953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77781629562378</t>
+    <t xml:space="preserve">1.77781641483307</t>
   </si>
   <si>
     <t xml:space="preserve">1.77348029613495</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">1.80383312702179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93391728401184</t>
+    <t xml:space="preserve">1.93391752243042</t>
   </si>
   <si>
     <t xml:space="preserve">1.88188374042511</t>
@@ -1130,25 +1130,25 @@
     <t xml:space="preserve">1.95559799671173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88621962070465</t>
+    <t xml:space="preserve">1.88621973991394</t>
   </si>
   <si>
     <t xml:space="preserve">1.81684172153473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89489209651947</t>
+    <t xml:space="preserve">1.89489197731018</t>
   </si>
   <si>
     <t xml:space="preserve">1.80816924571991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82984983921051</t>
+    <t xml:space="preserve">1.82984972000122</t>
   </si>
   <si>
     <t xml:space="preserve">1.85153079032898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78215253353119</t>
+    <t xml:space="preserve">1.7821524143219</t>
   </si>
   <si>
     <t xml:space="preserve">1.81250536441803</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">1.89055597782135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87754738330841</t>
+    <t xml:space="preserve">1.8775475025177</t>
   </si>
   <si>
     <t xml:space="preserve">1.83418619632721</t>
@@ -1181,16 +1181,16 @@
     <t xml:space="preserve">1.84285831451416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82551395893097</t>
+    <t xml:space="preserve">1.82551383972168</t>
   </si>
   <si>
     <t xml:space="preserve">1.83852231502533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86020290851593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9729425907135</t>
+    <t xml:space="preserve">1.86020314693451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97294282913208</t>
   </si>
   <si>
     <t xml:space="preserve">1.98161494731903</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">1.92958116531372</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98595094680786</t>
+    <t xml:space="preserve">1.98595118522644</t>
   </si>
   <si>
     <t xml:space="preserve">2.04665684700012</t>
@@ -1208,22 +1208,22 @@
     <t xml:space="preserve">2.03364849090576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.042320728302</t>
+    <t xml:space="preserve">2.04232048988342</t>
   </si>
   <si>
     <t xml:space="preserve">2.072674036026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08134603500366</t>
+    <t xml:space="preserve">2.08134579658508</t>
   </si>
   <si>
     <t xml:space="preserve">2.1116988658905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15072417259216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05532908439636</t>
+    <t xml:space="preserve">2.15072441101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05532884597778</t>
   </si>
   <si>
     <t xml:space="preserve">2.1854133605957</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.33717799186707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3024890422821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28080821037292</t>
+    <t xml:space="preserve">2.30248880386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2808084487915</t>
   </si>
   <si>
     <t xml:space="preserve">2.21142983436584</t>
@@ -1247,16 +1247,16 @@
     <t xml:space="preserve">2.28514456748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44991779327393</t>
+    <t xml:space="preserve">2.44991755485535</t>
   </si>
   <si>
     <t xml:space="preserve">2.48894286155701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59300994873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38921189308167</t>
+    <t xml:space="preserve">2.59301018714905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38921165466309</t>
   </si>
   <si>
     <t xml:space="preserve">2.49761533737183</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">2.76645588874817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83583378791809</t>
+    <t xml:space="preserve">2.83583402633667</t>
   </si>
   <si>
     <t xml:space="preserve">2.91388440132141</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">3.25210309028625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21741390228271</t>
+    <t xml:space="preserve">3.21741366386414</t>
   </si>
   <si>
     <t xml:space="preserve">3.25643944740295</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">3.36050653457642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20874166488647</t>
+    <t xml:space="preserve">3.20874190330505</t>
   </si>
   <si>
     <t xml:space="preserve">3.36917901039124</t>
@@ -1331,13 +1331,13 @@
     <t xml:space="preserve">3.34749794006348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50793528556824</t>
+    <t xml:space="preserve">3.50793552398682</t>
   </si>
   <si>
     <t xml:space="preserve">3.48625445365906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55563259124756</t>
+    <t xml:space="preserve">3.55563282966614</t>
   </si>
   <si>
     <t xml:space="preserve">3.51227164268494</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">3.6640362739563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7334144115448</t>
+    <t xml:space="preserve">3.73341464996338</t>
   </si>
   <si>
     <t xml:space="preserve">3.80712866783142</t>
@@ -1367,19 +1367,19 @@
     <t xml:space="preserve">4.09764957427979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86783456802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04127979278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.945885181427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97190189361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71173405647278</t>
+    <t xml:space="preserve">3.86783504486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0412802696228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94588565826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97190237045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7117338180542</t>
   </si>
   <si>
     <t xml:space="preserve">3.91986846923828</t>
@@ -1388,13 +1388,13 @@
     <t xml:space="preserve">4.07163333892822</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24941492080688</t>
+    <t xml:space="preserve">4.24941444396973</t>
   </si>
   <si>
     <t xml:space="preserve">4.25375080108643</t>
   </si>
   <si>
-    <t xml:space="preserve">4.284104347229</t>
+    <t xml:space="preserve">4.28410387039185</t>
   </si>
   <si>
     <t xml:space="preserve">4.62232208251953</t>
@@ -1409,22 +1409,22 @@
     <t xml:space="preserve">4.75240707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05593585968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9865574836731</t>
+    <t xml:space="preserve">5.05593633651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98655796051025</t>
   </si>
   <si>
     <t xml:space="preserve">4.95186901092529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87381839752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31879281997681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80444049835205</t>
+    <t xml:space="preserve">4.87381792068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31879329681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80444002151489</t>
   </si>
   <si>
     <t xml:space="preserve">4.97788572311401</t>
@@ -1448,10 +1448,10 @@
     <t xml:space="preserve">4.89116287231445</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83045768737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76107835769653</t>
+    <t xml:space="preserve">4.83045721054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76107883453369</t>
   </si>
   <si>
     <t xml:space="preserve">4.54427194595337</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">4.70904541015625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60497808456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58763313293457</t>
+    <t xml:space="preserve">4.60497760772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58763360977173</t>
   </si>
   <si>
     <t xml:space="preserve">4.64833927154541</t>
@@ -1487,16 +1487,16 @@
     <t xml:space="preserve">4.1887092590332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2407431602478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.084641456604</t>
+    <t xml:space="preserve">4.24074268341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08464097976685</t>
   </si>
   <si>
     <t xml:space="preserve">3.92854046821594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91553258895874</t>
+    <t xml:space="preserve">3.91553211212158</t>
   </si>
   <si>
     <t xml:space="preserve">3.85916233062744</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">3.7811119556427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14101076126099</t>
+    <t xml:space="preserve">4.14101123809814</t>
   </si>
   <si>
     <t xml:space="preserve">3.62501072883606</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">3.00927948951721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09166622161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03529620170593</t>
+    <t xml:space="preserve">3.09166598320007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03529644012451</t>
   </si>
   <si>
     <t xml:space="preserve">3.04830479621887</t>
@@ -1553,16 +1553,16 @@
     <t xml:space="preserve">2.80548071861267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88786745071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04396867752075</t>
+    <t xml:space="preserve">2.88786768913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04396843910217</t>
   </si>
   <si>
     <t xml:space="preserve">3.2607753276825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24343085289001</t>
+    <t xml:space="preserve">3.24343109130859</t>
   </si>
   <si>
     <t xml:space="preserve">3.19139719009399</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">3.42554879188538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43855714797974</t>
+    <t xml:space="preserve">3.43855690956116</t>
   </si>
   <si>
     <t xml:space="preserve">3.39519572257996</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">3.20440554618835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06998562812805</t>
+    <t xml:space="preserve">3.06998538970947</t>
   </si>
   <si>
     <t xml:space="preserve">2.86618685722351</t>
@@ -1610,19 +1610,19 @@
     <t xml:space="preserve">3.11768269538879</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08733010292053</t>
+    <t xml:space="preserve">3.08732986450195</t>
   </si>
   <si>
     <t xml:space="preserve">3.06564927101135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81848931312561</t>
+    <t xml:space="preserve">2.81848955154419</t>
   </si>
   <si>
     <t xml:space="preserve">2.68840527534485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73176693916321</t>
+    <t xml:space="preserve">2.73176670074463</t>
   </si>
   <si>
     <t xml:space="preserve">2.63203573226929</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">3.17405247688293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30413675308228</t>
+    <t xml:space="preserve">3.3041365146637</t>
   </si>
   <si>
     <t xml:space="preserve">3.3084728717804</t>
@@ -1643,10 +1643,10 @@
     <t xml:space="preserve">3.17838859558105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10467457771301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16104412078857</t>
+    <t xml:space="preserve">3.10467433929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16104435920715</t>
   </si>
   <si>
     <t xml:space="preserve">3.330153465271</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">3.46023774147034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5903217792511</t>
+    <t xml:space="preserve">3.59032201766968</t>
   </si>
   <si>
     <t xml:space="preserve">3.88517904281616</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">4.11499452590942</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27543163299561</t>
+    <t xml:space="preserve">4.27543115615845</t>
   </si>
   <si>
     <t xml:space="preserve">4.10198640823364</t>
@@ -1682,10 +1682,10 @@
     <t xml:space="preserve">4.1323390007019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95889353752136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8244731426239</t>
+    <t xml:space="preserve">3.95889401435852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82447338104248</t>
   </si>
   <si>
     <t xml:space="preserve">3.9675657749176</t>
@@ -1700,13 +1700,13 @@
     <t xml:space="preserve">4.00659084320068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06296062469482</t>
+    <t xml:space="preserve">4.06296110153198</t>
   </si>
   <si>
     <t xml:space="preserve">4.05862474441528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01526403427124</t>
+    <t xml:space="preserve">4.01526355743408</t>
   </si>
   <si>
     <t xml:space="preserve">4.09331369400024</t>
@@ -1715,28 +1715,28 @@
     <t xml:space="preserve">4.03260803222656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98924660682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92420482635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82880926132202</t>
+    <t xml:space="preserve">3.98924612998962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92420434951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82880878448486</t>
   </si>
   <si>
     <t xml:space="preserve">3.75943160057068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74642300605774</t>
+    <t xml:space="preserve">3.74642324447632</t>
   </si>
   <si>
     <t xml:space="preserve">3.56864094734192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77677607536316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24507904052734</t>
+    <t xml:space="preserve">3.77677583694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24507856369019</t>
   </si>
   <si>
     <t xml:space="preserve">4.17136430740356</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">4.06729698181152</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16269207000732</t>
+    <t xml:space="preserve">4.16269159317017</t>
   </si>
   <si>
     <t xml:space="preserve">4.21906137466431</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">4.2320704460144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20171689987183</t>
+    <t xml:space="preserve">4.20171737670898</t>
   </si>
   <si>
     <t xml:space="preserve">4.68302869796753</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">4.88249111175537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76975154876709</t>
+    <t xml:space="preserve">4.76975107192993</t>
   </si>
   <si>
     <t xml:space="preserve">4.72638988494873</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">4.44887685775757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39684343338013</t>
+    <t xml:space="preserve">4.39684391021729</t>
   </si>
   <si>
     <t xml:space="preserve">3.91119599342346</t>
@@ -1790,7 +1790,7 @@
     <t xml:space="preserve">4.04995250701904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2700982093811</t>
+    <t xml:space="preserve">4.27009868621826</t>
   </si>
   <si>
     <t xml:space="preserve">4.12285375595093</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">4.01130437850952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91760301589966</t>
+    <t xml:space="preserve">3.91760349273682</t>
   </si>
   <si>
     <t xml:space="preserve">4.22547912597656</t>
@@ -1808,19 +1808,19 @@
     <t xml:space="preserve">4.00684213638306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83282613754272</t>
+    <t xml:space="preserve">3.8328263759613</t>
   </si>
   <si>
     <t xml:space="preserve">3.85513615608215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85959792137146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93098926544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83728814125061</t>
+    <t xml:space="preserve">3.8595974445343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93098974227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83728837966919</t>
   </si>
   <si>
     <t xml:space="preserve">4.01576662063599</t>
@@ -1832,13 +1832,13 @@
     <t xml:space="preserve">3.95776081085205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79266834259033</t>
+    <t xml:space="preserve">3.79266858100891</t>
   </si>
   <si>
     <t xml:space="preserve">3.74358701705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76143455505371</t>
+    <t xml:space="preserve">3.76143479347229</t>
   </si>
   <si>
     <t xml:space="preserve">3.61419010162354</t>
@@ -1853,13 +1853,13 @@
     <t xml:space="preserve">3.48479294776917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67219543457031</t>
+    <t xml:space="preserve">3.67219519615173</t>
   </si>
   <si>
     <t xml:space="preserve">3.59634208679199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5874183177948</t>
+    <t xml:space="preserve">3.58741807937622</t>
   </si>
   <si>
     <t xml:space="preserve">3.64096164703369</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">3.52495074272156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41786336898804</t>
+    <t xml:space="preserve">3.41786360740662</t>
   </si>
   <si>
     <t xml:space="preserve">3.44909739494324</t>
@@ -1895,19 +1895,19 @@
     <t xml:space="preserve">3.41340160369873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42678737640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36878228187561</t>
+    <t xml:space="preserve">3.42678761482239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36878204345703</t>
   </si>
   <si>
     <t xml:space="preserve">3.34647226333618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31523823738098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32862448692322</t>
+    <t xml:space="preserve">3.31523847579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32862424850464</t>
   </si>
   <si>
     <t xml:space="preserve">3.36432003974915</t>
@@ -1943,10 +1943,10 @@
     <t xml:space="preserve">3.33308601379395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35093426704407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52941250801086</t>
+    <t xml:space="preserve">3.35093402862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52941274642944</t>
   </si>
   <si>
     <t xml:space="preserve">3.65880942344666</t>
@@ -1955,10 +1955,10 @@
     <t xml:space="preserve">3.71235322952271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81051659584045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80605435371399</t>
+    <t xml:space="preserve">3.81051635742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80605411529541</t>
   </si>
   <si>
     <t xml:space="preserve">3.7658965587616</t>
@@ -1973,40 +1973,40 @@
     <t xml:space="preserve">3.4669451713562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62757611274719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78374433517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69004368782043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70789122581482</t>
+    <t xml:space="preserve">3.62757587432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78374409675598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69004344940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7078914642334</t>
   </si>
   <si>
     <t xml:space="preserve">3.67665719985962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73912501335144</t>
+    <t xml:space="preserve">3.73912477493286</t>
   </si>
   <si>
     <t xml:space="preserve">3.68558144569397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66773366928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69896721839905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72127723693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72573947906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62311363220215</t>
+    <t xml:space="preserve">3.66773343086243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69896697998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7212769985199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72573924064636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62311387062073</t>
   </si>
   <si>
     <t xml:space="preserve">3.60972809791565</t>
@@ -2021,7 +2021,7 @@
     <t xml:space="preserve">3.96668481826782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73466277122498</t>
+    <t xml:space="preserve">3.73466300964355</t>
   </si>
   <si>
     <t xml:space="preserve">3.69450497627258</t>
@@ -2039,25 +2039,25 @@
     <t xml:space="preserve">3.57849431037903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56510829925537</t>
+    <t xml:space="preserve">3.56510806083679</t>
   </si>
   <si>
     <t xml:space="preserve">3.93991351127625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06038618087769</t>
+    <t xml:space="preserve">4.06038665771484</t>
   </si>
   <si>
     <t xml:space="preserve">3.91314196586609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98899483680725</t>
+    <t xml:space="preserve">3.98899435997009</t>
   </si>
   <si>
     <t xml:space="preserve">3.98007082939148</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12731552124023</t>
+    <t xml:space="preserve">4.12731599807739</t>
   </si>
   <si>
     <t xml:space="preserve">4.05146217346191</t>
@@ -2084,13 +2084,13 @@
     <t xml:space="preserve">3.93545150756836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8908314704895</t>
+    <t xml:space="preserve">3.89083194732666</t>
   </si>
   <si>
     <t xml:space="preserve">4.07823419570923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19424486160278</t>
+    <t xml:space="preserve">4.19424438476562</t>
   </si>
   <si>
     <t xml:space="preserve">4.00238084793091</t>
@@ -2102,13 +2102,13 @@
     <t xml:space="preserve">4.08715772628784</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21655511856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46196317672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53335380554199</t>
+    <t xml:space="preserve">4.21655464172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46196269989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53335428237915</t>
   </si>
   <si>
     <t xml:space="preserve">4.64044094085693</t>
@@ -2117,19 +2117,19 @@
     <t xml:space="preserve">4.58689785003662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64936542510986</t>
+    <t xml:space="preserve">4.64936494827271</t>
   </si>
   <si>
     <t xml:space="preserve">4.7564525604248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78322410583496</t>
+    <t xml:space="preserve">4.78322458267212</t>
   </si>
   <si>
     <t xml:space="preserve">4.68506097793579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83676767349243</t>
+    <t xml:space="preserve">4.83676815032959</t>
   </si>
   <si>
     <t xml:space="preserve">4.81892013549805</t>
@@ -2138,13 +2138,13 @@
     <t xml:space="preserve">4.90815925598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00632190704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89923524856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85461568832397</t>
+    <t xml:space="preserve">5.00632238388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89923477172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85461521148682</t>
   </si>
   <si>
     <t xml:space="preserve">4.9795503616333</t>
@@ -2168,10 +2168,10 @@
     <t xml:space="preserve">4.76537656784058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82784366607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80999565124512</t>
+    <t xml:space="preserve">4.82784414291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80999612808228</t>
   </si>
   <si>
     <t xml:space="preserve">4.94385480880737</t>
@@ -2180,13 +2180,13 @@
     <t xml:space="preserve">5.06878995895386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99739837646484</t>
+    <t xml:space="preserve">4.997398853302</t>
   </si>
   <si>
     <t xml:space="preserve">5.23834466934204</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45251893997192</t>
+    <t xml:space="preserve">5.45251846313477</t>
   </si>
   <si>
     <t xml:space="preserve">5.83624744415283</t>
@@ -2201,46 +2201,46 @@
     <t xml:space="preserve">5.15802955627441</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88138723373413</t>
+    <t xml:space="preserve">4.88138675689697</t>
   </si>
   <si>
     <t xml:space="preserve">4.70290899276733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71183347702026</t>
+    <t xml:space="preserve">4.71183300018311</t>
   </si>
   <si>
     <t xml:space="preserve">4.73860454559326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63151788711548</t>
+    <t xml:space="preserve">4.63151741027832</t>
   </si>
   <si>
     <t xml:space="preserve">4.67613697052002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56012582778931</t>
+    <t xml:space="preserve">4.56012630462646</t>
   </si>
   <si>
     <t xml:space="preserve">4.41734313964844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14516353607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02022838592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98453307151794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94883751869202</t>
+    <t xml:space="preserve">4.14516401290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02022886276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98453259468079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94883704185486</t>
   </si>
   <si>
     <t xml:space="preserve">3.8015923500061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12783575057983</t>
+    <t xml:space="preserve">3.12783598899841</t>
   </si>
   <si>
     <t xml:space="preserve">3.15906977653503</t>
@@ -2249,13 +2249,13 @@
     <t xml:space="preserve">3.25277090072632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72625946998596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.757493019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44961762428284</t>
+    <t xml:space="preserve">2.72625923156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75749325752258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44961738586426</t>
   </si>
   <si>
     <t xml:space="preserve">2.45854163169861</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">1.99895930290222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10604643821716</t>
+    <t xml:space="preserve">2.10604619979858</t>
   </si>
   <si>
     <t xml:space="preserve">2.2577531337738</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">2.45407962799072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46300363540649</t>
+    <t xml:space="preserve">2.46300339698792</t>
   </si>
   <si>
     <t xml:space="preserve">2.56116652488708</t>
@@ -2300,31 +2300,31 @@
     <t xml:space="preserve">2.73964524269104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23938536643982</t>
+    <t xml:space="preserve">3.23938512802124</t>
   </si>
   <si>
     <t xml:space="preserve">3.20368933677673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10998797416687</t>
+    <t xml:space="preserve">3.10998773574829</t>
   </si>
   <si>
     <t xml:space="preserve">2.91812372207642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85119438171387</t>
+    <t xml:space="preserve">2.85119414329529</t>
   </si>
   <si>
     <t xml:space="preserve">2.99843883514404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93597173690796</t>
+    <t xml:space="preserve">2.93597149848938</t>
   </si>
   <si>
     <t xml:space="preserve">2.94489550590515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8913516998291</t>
+    <t xml:space="preserve">2.89135193824768</t>
   </si>
   <si>
     <t xml:space="preserve">2.97612929344177</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">3.00290107727051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1322979927063</t>
+    <t xml:space="preserve">3.13229775428772</t>
   </si>
   <si>
     <t xml:space="preserve">3.0118248462677</t>
@@ -70348,7 +70348,7 @@
     </row>
     <row r="2531">
       <c r="A2531" s="1" t="n">
-        <v>46002.6911111111</v>
+        <v>46002.3333333333</v>
       </c>
       <c r="B2531" t="n">
         <v>43740</v>
@@ -70369,6 +70369,32 @@
         <v>1388</v>
       </c>
       <c r="H2531" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" s="1" t="n">
+        <v>46003.6912962963</v>
+      </c>
+      <c r="B2532" t="n">
+        <v>86984</v>
+      </c>
+      <c r="C2532" t="n">
+        <v>8.09000015258789</v>
+      </c>
+      <c r="D2532" t="n">
+        <v>7.84999990463257</v>
+      </c>
+      <c r="E2532" t="n">
+        <v>7.90999984741211</v>
+      </c>
+      <c r="F2532" t="n">
+        <v>7.8899998664856</v>
+      </c>
+      <c r="G2532" t="s">
+        <v>1393</v>
+      </c>
+      <c r="H2532" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="1407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="1408">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95473086833954</t>
+    <t xml:space="preserve">1.95473062992096</t>
   </si>
   <si>
     <t xml:space="preserve">FM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95993399620056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90963470935822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85586702823639</t>
+    <t xml:space="preserve">1.95993423461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9096348285675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8558669090271</t>
   </si>
   <si>
     <t xml:space="preserve">1.86453914642334</t>
@@ -65,22 +65,22 @@
     <t xml:space="preserve">1.74486172199249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69542980194092</t>
+    <t xml:space="preserve">1.69542968273163</t>
   </si>
   <si>
     <t xml:space="preserve">1.61824667453766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52285158634186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4794899225235</t>
+    <t xml:space="preserve">1.52285146713257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47949004173279</t>
   </si>
   <si>
     <t xml:space="preserve">1.34420263767242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45434045791626</t>
+    <t xml:space="preserve">1.45434057712555</t>
   </si>
   <si>
     <t xml:space="preserve">1.55233716964722</t>
@@ -89,37 +89,37 @@
     <t xml:space="preserve">1.48989689350128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54366505146027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59569871425629</t>
+    <t xml:space="preserve">1.54366493225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.595698595047</t>
   </si>
   <si>
     <t xml:space="preserve">1.51331210136414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53325819969177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.499436378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43005812168121</t>
+    <t xml:space="preserve">1.53325831890106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49943625926971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4300582408905</t>
   </si>
   <si>
     <t xml:space="preserve">1.40751028060913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38582968711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28349661827087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17682754993439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24186980724335</t>
+    <t xml:space="preserve">1.38582956790924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28349673748016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17682766914368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24186968803406</t>
   </si>
   <si>
     <t xml:space="preserve">1.20718061923981</t>
@@ -128,13 +128,13 @@
     <t xml:space="preserve">1.23059582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43873059749603</t>
+    <t xml:space="preserve">1.43873047828674</t>
   </si>
   <si>
     <t xml:space="preserve">1.39710354804993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50030374526978</t>
+    <t xml:space="preserve">1.50030362606049</t>
   </si>
   <si>
     <t xml:space="preserve">1.48295903205872</t>
@@ -143,19 +143,19 @@
     <t xml:space="preserve">1.46561455726624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5211169719696</t>
+    <t xml:space="preserve">1.52111709117889</t>
   </si>
   <si>
     <t xml:space="preserve">1.51678085327148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49423289299011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47688853740692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47515404224396</t>
+    <t xml:space="preserve">1.4942330121994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47688841819763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47515392303467</t>
   </si>
   <si>
     <t xml:space="preserve">1.50984311103821</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">1.58702623844147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55754065513611</t>
+    <t xml:space="preserve">1.55754053592682</t>
   </si>
   <si>
     <t xml:space="preserve">1.52805483341217</t>
@@ -176,19 +176,19 @@
     <t xml:space="preserve">1.54279780387878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51244473457336</t>
+    <t xml:space="preserve">1.51244461536407</t>
   </si>
   <si>
     <t xml:space="preserve">1.55147004127502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61651206016541</t>
+    <t xml:space="preserve">1.61651194095612</t>
   </si>
   <si>
     <t xml:space="preserve">1.67374897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70843815803528</t>
+    <t xml:space="preserve">1.70843827724457</t>
   </si>
   <si>
     <t xml:space="preserve">1.67808520793915</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">1.65467011928558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63298952579498</t>
+    <t xml:space="preserve">1.63298940658569</t>
   </si>
   <si>
     <t xml:space="preserve">1.6061053276062</t>
@@ -206,25 +206,25 @@
     <t xml:space="preserve">1.53499269485474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49770188331604</t>
+    <t xml:space="preserve">1.49770200252533</t>
   </si>
   <si>
     <t xml:space="preserve">1.49683463573456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48122441768646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41791689395905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39970517158508</t>
+    <t xml:space="preserve">1.48122453689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41791701316833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39970505237579</t>
   </si>
   <si>
     <t xml:space="preserve">1.35200774669647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39190018177032</t>
+    <t xml:space="preserve">1.39190006256104</t>
   </si>
   <si>
     <t xml:space="preserve">1.46041119098663</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">1.60437095165253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60870707035065</t>
+    <t xml:space="preserve">1.60870683193207</t>
   </si>
   <si>
     <t xml:space="preserve">1.62518429756165</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">1.49249839782715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4578093290329</t>
+    <t xml:space="preserve">1.45780944824219</t>
   </si>
   <si>
     <t xml:space="preserve">1.47775566577911</t>
@@ -275,28 +275,28 @@
     <t xml:space="preserve">1.46908330917358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56794726848602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53932869434357</t>
+    <t xml:space="preserve">1.56794738769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53932881355286</t>
   </si>
   <si>
     <t xml:space="preserve">1.53065645694733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54106318950653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56968176364899</t>
+    <t xml:space="preserve">1.54106330871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5696816444397</t>
   </si>
   <si>
     <t xml:space="preserve">1.5471339225769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55060267448425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56708014011383</t>
+    <t xml:space="preserve">1.55060279369354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56708002090454</t>
   </si>
   <si>
     <t xml:space="preserve">1.5740180015564</t>
@@ -305,13 +305,13 @@
     <t xml:space="preserve">1.5107102394104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59136247634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56100940704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54453217983246</t>
+    <t xml:space="preserve">1.59136259555817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56100952625275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54453229904175</t>
   </si>
   <si>
     <t xml:space="preserve">1.45000445842743</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">1.38929855823517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40057241916656</t>
+    <t xml:space="preserve">1.40057253837585</t>
   </si>
   <si>
     <t xml:space="preserve">1.3875640630722</t>
@@ -329,19 +329,19 @@
     <t xml:space="preserve">1.44740283489227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49163138866425</t>
+    <t xml:space="preserve">1.49163126945496</t>
   </si>
   <si>
     <t xml:space="preserve">1.4838262796402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32338905334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32945990562439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3884311914444</t>
+    <t xml:space="preserve">1.32338917255402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3294597864151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38843107223511</t>
   </si>
   <si>
     <t xml:space="preserve">1.39016568660736</t>
@@ -356,34 +356,34 @@
     <t xml:space="preserve">1.31124794483185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30084121227264</t>
+    <t xml:space="preserve">1.30084133148193</t>
   </si>
   <si>
     <t xml:space="preserve">1.30257570743561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3615471124649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37802445888519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3823606967926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39623630046844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.377157330513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4049084186554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39450180530548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40404140949249</t>
+    <t xml:space="preserve">1.36154723167419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3780243396759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38236057758331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39623618125916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37715744972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40490853786469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39450192451477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4040412902832</t>
   </si>
   <si>
     <t xml:space="preserve">1.393634557724</t>
@@ -401,13 +401,13 @@
     <t xml:space="preserve">1.38062620162964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3658834695816</t>
+    <t xml:space="preserve">1.36588335037231</t>
   </si>
   <si>
     <t xml:space="preserve">1.3563437461853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35460937023163</t>
+    <t xml:space="preserve">1.35460925102234</t>
   </si>
   <si>
     <t xml:space="preserve">1.34333539009094</t>
@@ -425,10 +425,10 @@
     <t xml:space="preserve">1.3077791929245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34767150878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34506988525391</t>
+    <t xml:space="preserve">1.34767174720764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34506976604462</t>
   </si>
   <si>
     <t xml:space="preserve">1.33379590511322</t>
@@ -443,13 +443,13 @@
     <t xml:space="preserve">1.34940600395203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33813190460205</t>
+    <t xml:space="preserve">1.33813202381134</t>
   </si>
   <si>
     <t xml:space="preserve">1.34853863716125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41704964637756</t>
+    <t xml:space="preserve">1.41704976558685</t>
   </si>
   <si>
     <t xml:space="preserve">1.40317416191101</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">1.41097915172577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36501610279083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38322782516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36761784553528</t>
+    <t xml:space="preserve">1.36501598358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38322794437408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36761796474457</t>
   </si>
   <si>
     <t xml:space="preserve">1.38149344921112</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">1.41358077526093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42138588428497</t>
+    <t xml:space="preserve">1.42138576507568</t>
   </si>
   <si>
     <t xml:space="preserve">1.41271352767944</t>
@@ -491,13 +491,13 @@
     <t xml:space="preserve">1.40924477577209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42572224140167</t>
+    <t xml:space="preserve">1.42572212219238</t>
   </si>
   <si>
     <t xml:space="preserve">1.35114049911499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35894560813904</t>
+    <t xml:space="preserve">1.35894548892975</t>
   </si>
   <si>
     <t xml:space="preserve">1.34680426120758</t>
@@ -509,13 +509,13 @@
     <t xml:space="preserve">1.36241436004639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33032715320587</t>
+    <t xml:space="preserve">1.33032703399658</t>
   </si>
   <si>
     <t xml:space="preserve">1.32078754901886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31905317306519</t>
+    <t xml:space="preserve">1.3190530538559</t>
   </si>
   <si>
     <t xml:space="preserve">1.31992018222809</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">1.17942941188812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26181602478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29216909408569</t>
+    <t xml:space="preserve">1.26181590557098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2921689748764</t>
   </si>
   <si>
     <t xml:space="preserve">1.23146307468414</t>
@@ -545,10 +545,10 @@
     <t xml:space="preserve">1.22886145114899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18550002574921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15774881839752</t>
+    <t xml:space="preserve">1.18549990653992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15774869918823</t>
   </si>
   <si>
     <t xml:space="preserve">1.11872339248657</t>
@@ -566,13 +566,13 @@
     <t xml:space="preserve">1.11438727378845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11612164974213</t>
+    <t xml:space="preserve">1.11612176895142</t>
   </si>
   <si>
     <t xml:space="preserve">1.11525464057922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09791004657745</t>
+    <t xml:space="preserve">1.09790992736816</t>
   </si>
   <si>
     <t xml:space="preserve">1.09270668029785</t>
@@ -602,31 +602,31 @@
     <t xml:space="preserve">1.18289828300476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20544612407684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23493182659149</t>
+    <t xml:space="preserve">1.20544624328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23493194580078</t>
   </si>
   <si>
     <t xml:space="preserve">1.24533867835999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21845459938049</t>
+    <t xml:space="preserve">1.2184544801712</t>
   </si>
   <si>
     <t xml:space="preserve">1.19937562942505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20111012458801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2279942035675</t>
+    <t xml:space="preserve">1.20111000537872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22799408435822</t>
   </si>
   <si>
     <t xml:space="preserve">1.22192347049713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23666632175446</t>
+    <t xml:space="preserve">1.23666644096375</t>
   </si>
   <si>
     <t xml:space="preserve">1.26875388622284</t>
@@ -644,7 +644,7 @@
     <t xml:space="preserve">1.35721111297607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34593713283539</t>
+    <t xml:space="preserve">1.34593725204468</t>
   </si>
   <si>
     <t xml:space="preserve">1.33292853832245</t>
@@ -662,13 +662,13 @@
     <t xml:space="preserve">1.2444714307785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22712683677673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25661253929138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2236579656601</t>
+    <t xml:space="preserve">1.22712695598602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25661265850067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22365808486938</t>
   </si>
   <si>
     <t xml:space="preserve">1.22279071807861</t>
@@ -677,13 +677,13 @@
     <t xml:space="preserve">1.25314378738403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22625982761383</t>
+    <t xml:space="preserve">1.22625970840454</t>
   </si>
   <si>
     <t xml:space="preserve">1.21325135231018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20891523361206</t>
+    <t xml:space="preserve">1.20891511440277</t>
   </si>
   <si>
     <t xml:space="preserve">1.20457899570465</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">1.21672010421753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19070327281952</t>
+    <t xml:space="preserve">1.19070339202881</t>
   </si>
   <si>
     <t xml:space="preserve">1.20197737216949</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">1.191570520401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20284461975098</t>
+    <t xml:space="preserve">1.20284450054169</t>
   </si>
   <si>
     <t xml:space="preserve">1.19243776798248</t>
@@ -716,19 +716,19 @@
     <t xml:space="preserve">1.2340646982193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27742624282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27222263813019</t>
+    <t xml:space="preserve">1.27742612361908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27222275733948</t>
   </si>
   <si>
     <t xml:space="preserve">1.2982394695282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26355051994324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24273693561554</t>
+    <t xml:space="preserve">1.26355040073395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24273705482483</t>
   </si>
   <si>
     <t xml:space="preserve">1.23579907417297</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">1.22018897533417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24794042110443</t>
+    <t xml:space="preserve">1.24794030189514</t>
   </si>
   <si>
     <t xml:space="preserve">1.24967479705811</t>
@@ -746,31 +746,31 @@
     <t xml:space="preserve">1.29043459892273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29303634166718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31818580627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30691194534302</t>
+    <t xml:space="preserve">1.29303622245789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31818568706512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30691182613373</t>
   </si>
   <si>
     <t xml:space="preserve">1.27309000492096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24013531208038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27916061878204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27048826217651</t>
+    <t xml:space="preserve">1.24013519287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27916049957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2704883813858</t>
   </si>
   <si>
     <t xml:space="preserve">1.26528489589691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28436386585236</t>
+    <t xml:space="preserve">1.28436398506165</t>
   </si>
   <si>
     <t xml:space="preserve">1.27482438087463</t>
@@ -779,19 +779,19 @@
     <t xml:space="preserve">1.26441764831543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28523111343384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28696548938751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33986639976501</t>
+    <t xml:space="preserve">1.28523099422455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2869656085968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3398665189743</t>
   </si>
   <si>
     <t xml:space="preserve">1.33899927139282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41184651851654</t>
+    <t xml:space="preserve">1.41184628009796</t>
   </si>
   <si>
     <t xml:space="preserve">1.57835412025452</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">1.54019606113434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49856925010681</t>
+    <t xml:space="preserve">1.49856913089752</t>
   </si>
   <si>
     <t xml:space="preserve">1.50724148750305</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">1.50203800201416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47862303256989</t>
+    <t xml:space="preserve">1.4786229133606</t>
   </si>
   <si>
     <t xml:space="preserve">1.43352711200714</t>
@@ -830,16 +830,16 @@
     <t xml:space="preserve">1.48729526996613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47602128982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45694208145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4682160615921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45867669582367</t>
+    <t xml:space="preserve">1.47602117061615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45694220066071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46821618080139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45867657661438</t>
   </si>
   <si>
     <t xml:space="preserve">1.45954382419586</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">1.50637412071228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57488512992859</t>
+    <t xml:space="preserve">1.57488524913788</t>
   </si>
   <si>
     <t xml:space="preserve">1.58269023895264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56187677383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53585994243622</t>
+    <t xml:space="preserve">1.56187665462494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53585982322693</t>
   </si>
   <si>
     <t xml:space="preserve">1.48642790317535</t>
@@ -881,10 +881,10 @@
     <t xml:space="preserve">1.51157760620117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4890296459198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48035728931427</t>
+    <t xml:space="preserve">1.48902952671051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48035740852356</t>
   </si>
   <si>
     <t xml:space="preserve">1.48816239833832</t>
@@ -899,10 +899,10 @@
     <t xml:space="preserve">1.57054901123047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64686512947083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78648853302002</t>
+    <t xml:space="preserve">1.64686501026154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78648841381073</t>
   </si>
   <si>
     <t xml:space="preserve">1.76047170162201</t>
@@ -911,10 +911,10 @@
     <t xml:space="preserve">1.85933589935303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86627352237701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84199130535126</t>
+    <t xml:space="preserve">1.8662736415863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84199142456055</t>
   </si>
   <si>
     <t xml:space="preserve">2.15245866775513</t>
@@ -926,13 +926,13 @@
     <t xml:space="preserve">2.05879807472229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00329566001892</t>
+    <t xml:space="preserve">2.00329542160034</t>
   </si>
   <si>
     <t xml:space="preserve">1.95126187801361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05186033248901</t>
+    <t xml:space="preserve">2.05186009407043</t>
   </si>
   <si>
     <t xml:space="preserve">2.01543641090393</t>
@@ -941,34 +941,34 @@
     <t xml:space="preserve">1.98074758052826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90443181991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90790057182312</t>
+    <t xml:space="preserve">1.90443170070648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90790033340454</t>
   </si>
   <si>
     <t xml:space="preserve">1.91657280921936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90616595745087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84892892837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87321150302887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83158433437347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84719455242157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93218314647675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93738603591919</t>
+    <t xml:space="preserve">1.90616607666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84892904758453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87321162223816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83158445358276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84719467163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93218290805817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93738627433777</t>
   </si>
   <si>
     <t xml:space="preserve">1.92524516582489</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">1.94258952140808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97727882862091</t>
+    <t xml:space="preserve">1.97727870941162</t>
   </si>
   <si>
     <t xml:space="preserve">2.0206401348114</t>
@@ -989,10 +989,10 @@
     <t xml:space="preserve">2.01196765899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03971886634827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01370215415955</t>
+    <t xml:space="preserve">2.03971910476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01370239257812</t>
   </si>
   <si>
     <t xml:space="preserve">1.99462306499481</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">1.94432413578033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90269720554352</t>
+    <t xml:space="preserve">1.90269696712494</t>
   </si>
   <si>
     <t xml:space="preserve">1.82117772102356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91310381889343</t>
+    <t xml:space="preserve">1.91310405731201</t>
   </si>
   <si>
     <t xml:space="preserve">1.72144663333893</t>
@@ -1016,52 +1016,52 @@
     <t xml:space="preserve">1.67114758491516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69976603984833</t>
+    <t xml:space="preserve">1.69976592063904</t>
   </si>
   <si>
     <t xml:space="preserve">1.68762469291687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67895233631134</t>
+    <t xml:space="preserve">1.67895245552063</t>
   </si>
   <si>
     <t xml:space="preserve">1.63992726802826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64773225784302</t>
+    <t xml:space="preserve">1.64773237705231</t>
   </si>
   <si>
     <t xml:space="preserve">1.62865316867828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62691867351532</t>
+    <t xml:space="preserve">1.62691879272461</t>
   </si>
   <si>
     <t xml:space="preserve">1.60350370407104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59656596183777</t>
+    <t xml:space="preserve">1.59656584262848</t>
   </si>
   <si>
     <t xml:space="preserve">1.63905990123749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6485995054245</t>
+    <t xml:space="preserve">1.64859938621521</t>
   </si>
   <si>
     <t xml:space="preserve">1.6650767326355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6910936832428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72925162315369</t>
+    <t xml:space="preserve">1.69109380245209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7292515039444</t>
   </si>
   <si>
     <t xml:space="preserve">1.67548358440399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65640461444855</t>
+    <t xml:space="preserve">1.65640449523926</t>
   </si>
   <si>
     <t xml:space="preserve">1.63038766384125</t>
@@ -1076,10 +1076,10 @@
     <t xml:space="preserve">1.68935918807983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67721796035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63385665416718</t>
+    <t xml:space="preserve">1.67721807956696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63385653495789</t>
   </si>
   <si>
     <t xml:space="preserve">1.6217155456543</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">1.65727174282074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71537601947784</t>
+    <t xml:space="preserve">1.71537590026855</t>
   </si>
   <si>
     <t xml:space="preserve">1.66854572296143</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">1.72578275203705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72751724720001</t>
+    <t xml:space="preserve">1.72751712799072</t>
   </si>
   <si>
     <t xml:space="preserve">1.71190702915192</t>
@@ -1118,16 +1118,16 @@
     <t xml:space="preserve">1.77348029613495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80383324623108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93391728401184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8818838596344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95559823513031</t>
+    <t xml:space="preserve">1.80383312702179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93391752243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88188374042511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95559799671173</t>
   </si>
   <si>
     <t xml:space="preserve">1.88621973991394</t>
@@ -1136,28 +1136,28 @@
     <t xml:space="preserve">1.81684172153473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89489221572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8081693649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8298499584198</t>
+    <t xml:space="preserve">1.89489197731018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80816924571991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82984972000122</t>
   </si>
   <si>
     <t xml:space="preserve">1.85153079032898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78215253353119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81250548362732</t>
+    <t xml:space="preserve">1.7821524143219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81250536441803</t>
   </si>
   <si>
     <t xml:space="preserve">1.79082489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73445498943329</t>
+    <t xml:space="preserve">1.73445510864258</t>
   </si>
   <si>
     <t xml:space="preserve">1.76480805873871</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">1.96860635280609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89922833442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89055585861206</t>
+    <t xml:space="preserve">1.89922821521759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89055597782135</t>
   </si>
   <si>
     <t xml:space="preserve">1.8775475025177</t>
@@ -1184,22 +1184,22 @@
     <t xml:space="preserve">1.82551383972168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83852219581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86020302772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97294235229492</t>
+    <t xml:space="preserve">1.83852231502533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86020314693451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97294282913208</t>
   </si>
   <si>
     <t xml:space="preserve">1.98161494731903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92958092689514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98595070838928</t>
+    <t xml:space="preserve">1.92958116531372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98595118522644</t>
   </si>
   <si>
     <t xml:space="preserve">2.04665684700012</t>
@@ -1208,13 +1208,13 @@
     <t xml:space="preserve">2.03364849090576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.042320728302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07267379760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08134603500366</t>
+    <t xml:space="preserve">2.04232048988342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.072674036026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08134579658508</t>
   </si>
   <si>
     <t xml:space="preserve">2.1116988658905</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">2.15072441101074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05532908439636</t>
+    <t xml:space="preserve">2.05532884597778</t>
   </si>
   <si>
     <t xml:space="preserve">2.1854133605957</t>
@@ -1232,16 +1232,16 @@
     <t xml:space="preserve">2.33717799186707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3024890422821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28080821037292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21143007278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30682516098022</t>
+    <t xml:space="preserve">2.30248880386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2808084487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21142983436584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3068253993988</t>
   </si>
   <si>
     <t xml:space="preserve">2.28514456748962</t>
@@ -1253,10 +1253,10 @@
     <t xml:space="preserve">2.48894286155701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59300994873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38921189308167</t>
+    <t xml:space="preserve">2.59301018714905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38921165466309</t>
   </si>
   <si>
     <t xml:space="preserve">2.49761533737183</t>
@@ -1271,13 +1271,13 @@
     <t xml:space="preserve">2.71442222595215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76645565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83583378791809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91388416290283</t>
+    <t xml:space="preserve">2.76645588874817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83583402633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91388440132141</t>
   </si>
   <si>
     <t xml:space="preserve">2.92255663871765</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">2.93122911453247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87052297592163</t>
+    <t xml:space="preserve">2.87052273750305</t>
   </si>
   <si>
     <t xml:space="preserve">2.92689275741577</t>
@@ -1295,16 +1295,16 @@
     <t xml:space="preserve">3.10033845901489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23909449577332</t>
+    <t xml:space="preserve">3.23909473419189</t>
   </si>
   <si>
     <t xml:space="preserve">3.25210309028625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21741414070129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25643968582153</t>
+    <t xml:space="preserve">3.21741366386414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25643944740295</t>
   </si>
   <si>
     <t xml:space="preserve">3.36050653457642</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">3.20874190330505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36917877197266</t>
+    <t xml:space="preserve">3.36917901039124</t>
   </si>
   <si>
     <t xml:space="preserve">3.26511144638062</t>
@@ -1331,7 +1331,7 @@
     <t xml:space="preserve">3.34749794006348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50793528556824</t>
+    <t xml:space="preserve">3.50793552398682</t>
   </si>
   <si>
     <t xml:space="preserve">3.48625445365906</t>
@@ -1349,13 +1349,13 @@
     <t xml:space="preserve">3.6640362739563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73341417312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80712842941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90685963630676</t>
+    <t xml:space="preserve">3.73341464996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80712866783142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90686011314392</t>
   </si>
   <si>
     <t xml:space="preserve">4.07596921920776</t>
@@ -1364,43 +1364,43 @@
     <t xml:space="preserve">4.0456166267395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09765005111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86783456802368</t>
+    <t xml:space="preserve">4.09764957427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86783504486084</t>
   </si>
   <si>
     <t xml:space="preserve">4.0412802696228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94588470458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97190141677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71173405647278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91986799240112</t>
+    <t xml:space="preserve">3.94588565826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97190237045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7117338180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91986846923828</t>
   </si>
   <si>
     <t xml:space="preserve">4.07163333892822</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24941492080688</t>
+    <t xml:space="preserve">4.24941444396973</t>
   </si>
   <si>
     <t xml:space="preserve">4.25375080108643</t>
   </si>
   <si>
-    <t xml:space="preserve">4.284104347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62232255935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57896184921265</t>
+    <t xml:space="preserve">4.28410387039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62232208251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57896137237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.74373435974121</t>
@@ -1418,13 +1418,13 @@
     <t xml:space="preserve">4.95186901092529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87381839752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31879281997681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80444049835205</t>
+    <t xml:space="preserve">4.87381792068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31879329681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80444002151489</t>
   </si>
   <si>
     <t xml:space="preserve">4.97788572311401</t>
@@ -1433,13 +1433,13 @@
     <t xml:space="preserve">5.01257514953613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03859233856201</t>
+    <t xml:space="preserve">5.03859186172485</t>
   </si>
   <si>
     <t xml:space="preserve">4.91718006134033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82178449630737</t>
+    <t xml:space="preserve">4.82178497314453</t>
   </si>
   <si>
     <t xml:space="preserve">4.85647392272949</t>
@@ -1448,28 +1448,28 @@
     <t xml:space="preserve">4.89116287231445</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83045768737793</t>
+    <t xml:space="preserve">4.83045721054077</t>
   </si>
   <si>
     <t xml:space="preserve">4.76107883453369</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54427242279053</t>
+    <t xml:space="preserve">4.54427194595337</t>
   </si>
   <si>
     <t xml:space="preserve">4.70904541015625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60497808456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58763313293457</t>
+    <t xml:space="preserve">4.60497760772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58763360977173</t>
   </si>
   <si>
     <t xml:space="preserve">4.64833927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61365032196045</t>
+    <t xml:space="preserve">4.61365079879761</t>
   </si>
   <si>
     <t xml:space="preserve">4.53559970855713</t>
@@ -1478,40 +1478,40 @@
     <t xml:space="preserve">4.47489356994629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40551519393921</t>
+    <t xml:space="preserve">4.40551567077637</t>
   </si>
   <si>
     <t xml:space="preserve">4.1843729019165</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18870878219604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24074220657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.084641456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9285409450531</t>
+    <t xml:space="preserve">4.1887092590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24074268341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08464097976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92854046821594</t>
   </si>
   <si>
     <t xml:space="preserve">3.91553211212158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85916185379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78111171722412</t>
+    <t xml:space="preserve">3.85916233062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7811119556427</t>
   </si>
   <si>
     <t xml:space="preserve">4.14101123809814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62501096725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31280922889709</t>
+    <t xml:space="preserve">3.62501072883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31280899047852</t>
   </si>
   <si>
     <t xml:space="preserve">3.28679227828979</t>
@@ -1526,22 +1526,22 @@
     <t xml:space="preserve">3.09166598320007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03529620170593</t>
+    <t xml:space="preserve">3.03529644012451</t>
   </si>
   <si>
     <t xml:space="preserve">3.04830479621887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07865738868713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96158194541931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89653992652893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90521216392517</t>
+    <t xml:space="preserve">3.07865762710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96158170700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89653968811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90521192550659</t>
   </si>
   <si>
     <t xml:space="preserve">3.02662420272827</t>
@@ -1553,10 +1553,10 @@
     <t xml:space="preserve">2.80548071861267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88786745071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04396867752075</t>
+    <t xml:space="preserve">2.88786768913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04396843910217</t>
   </si>
   <si>
     <t xml:space="preserve">3.2607753276825</t>
@@ -1565,16 +1565,16 @@
     <t xml:space="preserve">3.24343109130859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19139742851257</t>
+    <t xml:space="preserve">3.19139719009399</t>
   </si>
   <si>
     <t xml:space="preserve">3.42554879188538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43855714797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39519548416138</t>
+    <t xml:space="preserve">3.43855690956116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39519572257996</t>
   </si>
   <si>
     <t xml:space="preserve">3.20440554618835</t>
@@ -1589,7 +1589,7 @@
     <t xml:space="preserve">2.93990135192871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88353157043457</t>
+    <t xml:space="preserve">2.88353133201599</t>
   </si>
   <si>
     <t xml:space="preserve">2.97459053993225</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">3.02228784561157</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3821873664856</t>
+    <t xml:space="preserve">3.38218760490417</t>
   </si>
   <si>
     <t xml:space="preserve">3.32148122787476</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">3.11768269538879</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08733010292053</t>
+    <t xml:space="preserve">3.08732986450195</t>
   </si>
   <si>
     <t xml:space="preserve">3.06564927101135</t>
@@ -1622,10 +1622,10 @@
     <t xml:space="preserve">2.68840527534485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73176693916321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63203549385071</t>
+    <t xml:space="preserve">2.73176670074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63203573226929</t>
   </si>
   <si>
     <t xml:space="preserve">2.98759889602661</t>
@@ -1640,13 +1640,13 @@
     <t xml:space="preserve">3.3084728717804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17838883399963</t>
+    <t xml:space="preserve">3.17838859558105</t>
   </si>
   <si>
     <t xml:space="preserve">3.10467433929443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16104412078857</t>
+    <t xml:space="preserve">3.16104435920715</t>
   </si>
   <si>
     <t xml:space="preserve">3.330153465271</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">3.46023774147034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59032154083252</t>
+    <t xml:space="preserve">3.59032201766968</t>
   </si>
   <si>
     <t xml:space="preserve">3.88517904281616</t>
@@ -1664,10 +1664,10 @@
     <t xml:space="preserve">3.90252375602722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85482621192932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11499404907227</t>
+    <t xml:space="preserve">3.8548264503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11499452590942</t>
   </si>
   <si>
     <t xml:space="preserve">4.27543115615845</t>
@@ -1676,16 +1676,16 @@
     <t xml:space="preserve">4.10198640823364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14534759521484</t>
+    <t xml:space="preserve">4.145348072052</t>
   </si>
   <si>
     <t xml:space="preserve">4.1323390007019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95889353752136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82447361946106</t>
+    <t xml:space="preserve">3.95889401435852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82447338104248</t>
   </si>
   <si>
     <t xml:space="preserve">3.9675657749176</t>
@@ -1697,10 +1697,10 @@
     <t xml:space="preserve">3.99791860580444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00659132003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06296062469482</t>
+    <t xml:space="preserve">4.00659084320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06296110153198</t>
   </si>
   <si>
     <t xml:space="preserve">4.05862474441528</t>
@@ -1718,25 +1718,25 @@
     <t xml:space="preserve">3.98924612998962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92420482635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82880973815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7594313621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74642300605774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5686411857605</t>
+    <t xml:space="preserve">3.92420434951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82880878448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75943160057068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74642324447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56864094734192</t>
   </si>
   <si>
     <t xml:space="preserve">3.77677583694458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24507904052734</t>
+    <t xml:space="preserve">4.24507856369019</t>
   </si>
   <si>
     <t xml:space="preserve">4.17136430740356</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">4.06729698181152</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16269207000732</t>
+    <t xml:space="preserve">4.16269159317017</t>
   </si>
   <si>
     <t xml:space="preserve">4.21906137466431</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">4.2320704460144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20171689987183</t>
+    <t xml:space="preserve">4.20171737670898</t>
   </si>
   <si>
     <t xml:space="preserve">4.68302869796753</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">4.72638988494873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63966703414917</t>
+    <t xml:space="preserve">4.63966751098633</t>
   </si>
   <si>
     <t xml:space="preserve">4.55294466018677</t>
@@ -1781,16 +1781,16 @@
     <t xml:space="preserve">4.44887685775757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39684343338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91119647026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04995203018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2700982093811</t>
+    <t xml:space="preserve">4.39684391021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91119599342346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04995250701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27009868621826</t>
   </si>
   <si>
     <t xml:space="preserve">4.12285375595093</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">4.01130437850952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91760301589966</t>
+    <t xml:space="preserve">3.91760349273682</t>
   </si>
   <si>
     <t xml:space="preserve">4.22547912597656</t>
@@ -1808,19 +1808,19 @@
     <t xml:space="preserve">4.00684213638306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83282613754272</t>
+    <t xml:space="preserve">3.8328263759613</t>
   </si>
   <si>
     <t xml:space="preserve">3.85513615608215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85959792137146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93098926544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83728814125061</t>
+    <t xml:space="preserve">3.8595974445343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93098974227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83728837966919</t>
   </si>
   <si>
     <t xml:space="preserve">4.01576662063599</t>
@@ -1832,13 +1832,13 @@
     <t xml:space="preserve">3.95776081085205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79266834259033</t>
+    <t xml:space="preserve">3.79266858100891</t>
   </si>
   <si>
     <t xml:space="preserve">3.74358701705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76143455505371</t>
+    <t xml:space="preserve">3.76143479347229</t>
   </si>
   <si>
     <t xml:space="preserve">3.61419010162354</t>
@@ -1853,13 +1853,13 @@
     <t xml:space="preserve">3.48479294776917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67219543457031</t>
+    <t xml:space="preserve">3.67219519615173</t>
   </si>
   <si>
     <t xml:space="preserve">3.59634208679199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5874183177948</t>
+    <t xml:space="preserve">3.58741807937622</t>
   </si>
   <si>
     <t xml:space="preserve">3.64096164703369</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">3.52495074272156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41786336898804</t>
+    <t xml:space="preserve">3.41786360740662</t>
   </si>
   <si>
     <t xml:space="preserve">3.44909739494324</t>
@@ -1895,19 +1895,19 @@
     <t xml:space="preserve">3.41340160369873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42678737640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36878228187561</t>
+    <t xml:space="preserve">3.42678761482239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36878204345703</t>
   </si>
   <si>
     <t xml:space="preserve">3.34647226333618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31523823738098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32862448692322</t>
+    <t xml:space="preserve">3.31523847579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32862424850464</t>
   </si>
   <si>
     <t xml:space="preserve">3.36432003974915</t>
@@ -1943,10 +1943,10 @@
     <t xml:space="preserve">3.33308601379395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35093426704407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52941250801086</t>
+    <t xml:space="preserve">3.35093402862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52941274642944</t>
   </si>
   <si>
     <t xml:space="preserve">3.65880942344666</t>
@@ -1955,10 +1955,10 @@
     <t xml:space="preserve">3.71235322952271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81051659584045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80605435371399</t>
+    <t xml:space="preserve">3.81051635742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80605411529541</t>
   </si>
   <si>
     <t xml:space="preserve">3.7658965587616</t>
@@ -1973,40 +1973,40 @@
     <t xml:space="preserve">3.4669451713562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62757611274719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78374433517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69004368782043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70789122581482</t>
+    <t xml:space="preserve">3.62757587432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78374409675598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69004344940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7078914642334</t>
   </si>
   <si>
     <t xml:space="preserve">3.67665719985962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73912501335144</t>
+    <t xml:space="preserve">3.73912477493286</t>
   </si>
   <si>
     <t xml:space="preserve">3.68558144569397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66773366928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69896721839905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72127723693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72573947906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62311363220215</t>
+    <t xml:space="preserve">3.66773343086243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69896697998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7212769985199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72573924064636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62311387062073</t>
   </si>
   <si>
     <t xml:space="preserve">3.60972809791565</t>
@@ -2021,7 +2021,7 @@
     <t xml:space="preserve">3.96668481826782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73466277122498</t>
+    <t xml:space="preserve">3.73466300964355</t>
   </si>
   <si>
     <t xml:space="preserve">3.69450497627258</t>
@@ -2039,25 +2039,25 @@
     <t xml:space="preserve">3.57849431037903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56510829925537</t>
+    <t xml:space="preserve">3.56510806083679</t>
   </si>
   <si>
     <t xml:space="preserve">3.93991351127625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06038618087769</t>
+    <t xml:space="preserve">4.06038665771484</t>
   </si>
   <si>
     <t xml:space="preserve">3.91314196586609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98899483680725</t>
+    <t xml:space="preserve">3.98899435997009</t>
   </si>
   <si>
     <t xml:space="preserve">3.98007082939148</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12731552124023</t>
+    <t xml:space="preserve">4.12731599807739</t>
   </si>
   <si>
     <t xml:space="preserve">4.05146217346191</t>
@@ -2084,13 +2084,13 @@
     <t xml:space="preserve">3.93545150756836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8908314704895</t>
+    <t xml:space="preserve">3.89083194732666</t>
   </si>
   <si>
     <t xml:space="preserve">4.07823419570923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19424486160278</t>
+    <t xml:space="preserve">4.19424438476562</t>
   </si>
   <si>
     <t xml:space="preserve">4.00238084793091</t>
@@ -2102,13 +2102,13 @@
     <t xml:space="preserve">4.08715772628784</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21655511856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46196317672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53335380554199</t>
+    <t xml:space="preserve">4.21655464172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46196269989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53335428237915</t>
   </si>
   <si>
     <t xml:space="preserve">4.64044094085693</t>
@@ -2117,19 +2117,19 @@
     <t xml:space="preserve">4.58689785003662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64936542510986</t>
+    <t xml:space="preserve">4.64936494827271</t>
   </si>
   <si>
     <t xml:space="preserve">4.7564525604248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78322410583496</t>
+    <t xml:space="preserve">4.78322458267212</t>
   </si>
   <si>
     <t xml:space="preserve">4.68506097793579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83676767349243</t>
+    <t xml:space="preserve">4.83676815032959</t>
   </si>
   <si>
     <t xml:space="preserve">4.81892013549805</t>
@@ -2138,13 +2138,13 @@
     <t xml:space="preserve">4.90815925598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00632190704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89923524856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85461568832397</t>
+    <t xml:space="preserve">5.00632238388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89923477172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85461521148682</t>
   </si>
   <si>
     <t xml:space="preserve">4.9795503616333</t>
@@ -2168,10 +2168,10 @@
     <t xml:space="preserve">4.76537656784058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82784366607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80999565124512</t>
+    <t xml:space="preserve">4.82784414291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80999612808228</t>
   </si>
   <si>
     <t xml:space="preserve">4.94385480880737</t>
@@ -2180,13 +2180,13 @@
     <t xml:space="preserve">5.06878995895386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99739837646484</t>
+    <t xml:space="preserve">4.997398853302</t>
   </si>
   <si>
     <t xml:space="preserve">5.23834466934204</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45251893997192</t>
+    <t xml:space="preserve">5.45251846313477</t>
   </si>
   <si>
     <t xml:space="preserve">5.83624744415283</t>
@@ -2201,46 +2201,46 @@
     <t xml:space="preserve">5.15802955627441</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88138723373413</t>
+    <t xml:space="preserve">4.88138675689697</t>
   </si>
   <si>
     <t xml:space="preserve">4.70290899276733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71183347702026</t>
+    <t xml:space="preserve">4.71183300018311</t>
   </si>
   <si>
     <t xml:space="preserve">4.73860454559326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63151788711548</t>
+    <t xml:space="preserve">4.63151741027832</t>
   </si>
   <si>
     <t xml:space="preserve">4.67613697052002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56012582778931</t>
+    <t xml:space="preserve">4.56012630462646</t>
   </si>
   <si>
     <t xml:space="preserve">4.41734313964844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14516353607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02022838592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98453307151794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94883751869202</t>
+    <t xml:space="preserve">4.14516401290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02022886276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98453259468079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94883704185486</t>
   </si>
   <si>
     <t xml:space="preserve">3.8015923500061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12783575057983</t>
+    <t xml:space="preserve">3.12783598899841</t>
   </si>
   <si>
     <t xml:space="preserve">3.15906977653503</t>
@@ -2249,13 +2249,13 @@
     <t xml:space="preserve">3.25277090072632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72625946998596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.757493019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44961762428284</t>
+    <t xml:space="preserve">2.72625923156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75749325752258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44961738586426</t>
   </si>
   <si>
     <t xml:space="preserve">2.45854163169861</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">1.99895930290222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10604643821716</t>
+    <t xml:space="preserve">2.10604619979858</t>
   </si>
   <si>
     <t xml:space="preserve">2.2577531337738</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">2.45407962799072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46300363540649</t>
+    <t xml:space="preserve">2.46300339698792</t>
   </si>
   <si>
     <t xml:space="preserve">2.56116652488708</t>
@@ -2300,31 +2300,31 @@
     <t xml:space="preserve">2.73964524269104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23938536643982</t>
+    <t xml:space="preserve">3.23938512802124</t>
   </si>
   <si>
     <t xml:space="preserve">3.20368933677673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10998797416687</t>
+    <t xml:space="preserve">3.10998773574829</t>
   </si>
   <si>
     <t xml:space="preserve">2.91812372207642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85119438171387</t>
+    <t xml:space="preserve">2.85119414329529</t>
   </si>
   <si>
     <t xml:space="preserve">2.99843883514404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93597173690796</t>
+    <t xml:space="preserve">2.93597149848938</t>
   </si>
   <si>
     <t xml:space="preserve">2.94489550590515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8913516998291</t>
+    <t xml:space="preserve">2.89135193824768</t>
   </si>
   <si>
     <t xml:space="preserve">2.97612929344177</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">3.00290107727051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1322979927063</t>
+    <t xml:space="preserve">3.13229775428772</t>
   </si>
   <si>
     <t xml:space="preserve">3.0118248462677</t>
@@ -4233,6 +4233,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.76999998092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67000007629395</t>
   </si>
 </sst>
 </file>
@@ -70455,7 +70458,7 @@
     </row>
     <row r="2535">
       <c r="A2535" s="1" t="n">
-        <v>46008.6910069444</v>
+        <v>46008.3333333333</v>
       </c>
       <c r="B2535" t="n">
         <v>49074</v>
@@ -70476,6 +70479,32 @@
         <v>1390</v>
       </c>
       <c r="H2535" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2536">
+      <c r="A2536" s="1" t="n">
+        <v>46009.6909953704</v>
+      </c>
+      <c r="B2536" t="n">
+        <v>39533</v>
+      </c>
+      <c r="C2536" t="n">
+        <v>7.76000022888184</v>
+      </c>
+      <c r="D2536" t="n">
+        <v>7.6100001335144</v>
+      </c>
+      <c r="E2536" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="F2536" t="n">
+        <v>7.67000007629395</v>
+      </c>
+      <c r="G2536" t="s">
+        <v>1407</v>
+      </c>
+      <c r="H2536" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="1408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="1409">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">FM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95993423461914</t>
+    <t xml:space="preserve">1.95993399620056</t>
   </si>
   <si>
     <t xml:space="preserve">1.9096348285675</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">1.8558669090271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86453914642334</t>
+    <t xml:space="preserve">1.86453938484192</t>
   </si>
   <si>
     <t xml:space="preserve">1.68415582180023</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">1.74486172199249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69542968273163</t>
+    <t xml:space="preserve">1.69542980194092</t>
   </si>
   <si>
     <t xml:space="preserve">1.61824667453766</t>
@@ -101,10 +101,10 @@
     <t xml:space="preserve">1.53325831890106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49943625926971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4300582408905</t>
+    <t xml:space="preserve">1.499436378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43005812168121</t>
   </si>
   <si>
     <t xml:space="preserve">1.40751028060913</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">1.28349673748016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17682766914368</t>
+    <t xml:space="preserve">1.17682754993439</t>
   </si>
   <si>
     <t xml:space="preserve">1.24186968803406</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">1.23059582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43873047828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39710354804993</t>
+    <t xml:space="preserve">1.43873059749603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39710342884064</t>
   </si>
   <si>
     <t xml:space="preserve">1.50030362606049</t>
@@ -143,25 +143,25 @@
     <t xml:space="preserve">1.46561455726624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52111709117889</t>
+    <t xml:space="preserve">1.5211169719696</t>
   </si>
   <si>
     <t xml:space="preserve">1.51678085327148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4942330121994</t>
+    <t xml:space="preserve">1.49423289299011</t>
   </si>
   <si>
     <t xml:space="preserve">1.47688841819763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47515392303467</t>
+    <t xml:space="preserve">1.47515404224396</t>
   </si>
   <si>
     <t xml:space="preserve">1.50984311103821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56014239788055</t>
+    <t xml:space="preserve">1.56014227867126</t>
   </si>
   <si>
     <t xml:space="preserve">1.58702623844147</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">1.55754053592682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52805483341217</t>
+    <t xml:space="preserve">1.52805471420288</t>
   </si>
   <si>
     <t xml:space="preserve">1.54279780387878</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">1.51244461536407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55147004127502</t>
+    <t xml:space="preserve">1.55146992206573</t>
   </si>
   <si>
     <t xml:space="preserve">1.61651194095612</t>
@@ -188,13 +188,13 @@
     <t xml:space="preserve">1.67374897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70843827724457</t>
+    <t xml:space="preserve">1.70843815803528</t>
   </si>
   <si>
     <t xml:space="preserve">1.67808520793915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65467011928558</t>
+    <t xml:space="preserve">1.65467000007629</t>
   </si>
   <si>
     <t xml:space="preserve">1.63298940658569</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">1.53499269485474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49770200252533</t>
+    <t xml:space="preserve">1.49770188331604</t>
   </si>
   <si>
     <t xml:space="preserve">1.49683463573456</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">1.48122453689575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41791701316833</t>
+    <t xml:space="preserve">1.41791689395905</t>
   </si>
   <si>
     <t xml:space="preserve">1.39970505237579</t>
@@ -233,16 +233,16 @@
     <t xml:space="preserve">1.57228338718414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62952041625977</t>
+    <t xml:space="preserve">1.62952053546906</t>
   </si>
   <si>
     <t xml:space="preserve">1.60437095165253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60870683193207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62518429756165</t>
+    <t xml:space="preserve">1.60870695114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62518441677094</t>
   </si>
   <si>
     <t xml:space="preserve">1.65987348556519</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">1.49249839782715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45780944824219</t>
+    <t xml:space="preserve">1.4578093290329</t>
   </si>
   <si>
     <t xml:space="preserve">1.47775566577911</t>
@@ -275,25 +275,25 @@
     <t xml:space="preserve">1.46908330917358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56794738769531</t>
+    <t xml:space="preserve">1.56794726848602</t>
   </si>
   <si>
     <t xml:space="preserve">1.53932881355286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53065645694733</t>
+    <t xml:space="preserve">1.53065657615662</t>
   </si>
   <si>
     <t xml:space="preserve">1.54106330871582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5696816444397</t>
+    <t xml:space="preserve">1.56968176364899</t>
   </si>
   <si>
     <t xml:space="preserve">1.5471339225769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55060279369354</t>
+    <t xml:space="preserve">1.55060267448425</t>
   </si>
   <si>
     <t xml:space="preserve">1.56708002090454</t>
@@ -305,13 +305,13 @@
     <t xml:space="preserve">1.5107102394104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59136259555817</t>
+    <t xml:space="preserve">1.59136247634888</t>
   </si>
   <si>
     <t xml:space="preserve">1.56100952625275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54453229904175</t>
+    <t xml:space="preserve">1.54453217983246</t>
   </si>
   <si>
     <t xml:space="preserve">1.45000445842743</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">1.38929855823517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40057253837585</t>
+    <t xml:space="preserve">1.40057241916656</t>
   </si>
   <si>
     <t xml:space="preserve">1.3875640630722</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">1.44740283489227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49163126945496</t>
+    <t xml:space="preserve">1.49163138866425</t>
   </si>
   <si>
     <t xml:space="preserve">1.4838262796402</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">1.3294597864151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38843107223511</t>
+    <t xml:space="preserve">1.3884311914444</t>
   </si>
   <si>
     <t xml:space="preserve">1.39016568660736</t>
@@ -350,13 +350,13 @@
     <t xml:space="preserve">1.35981273651123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33726489543915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31124794483185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30084133148193</t>
+    <t xml:space="preserve">1.33726477622986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31124806404114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30084121227264</t>
   </si>
   <si>
     <t xml:space="preserve">1.30257570743561</t>
@@ -365,10 +365,10 @@
     <t xml:space="preserve">1.36154723167419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3780243396759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38236057758331</t>
+    <t xml:space="preserve">1.37802445888519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3823606967926</t>
   </si>
   <si>
     <t xml:space="preserve">1.39623618125916</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">1.37715744972229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40490853786469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39450192451477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4040412902832</t>
+    <t xml:space="preserve">1.40490865707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39450180530548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40404140949249</t>
   </si>
   <si>
     <t xml:space="preserve">1.393634557724</t>
@@ -407,13 +407,13 @@
     <t xml:space="preserve">1.3563437461853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35460925102234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34333539009094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33119428157806</t>
+    <t xml:space="preserve">1.35460937023163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34333550930023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33119416236877</t>
   </si>
   <si>
     <t xml:space="preserve">1.32685804367065</t>
@@ -422,13 +422,13 @@
     <t xml:space="preserve">1.30170845985413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3077791929245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34767174720764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34506976604462</t>
+    <t xml:space="preserve">1.30777907371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34767162799835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34506988525391</t>
   </si>
   <si>
     <t xml:space="preserve">1.33379590511322</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">1.35547661781311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34940600395203</t>
+    <t xml:space="preserve">1.34940612316132</t>
   </si>
   <si>
     <t xml:space="preserve">1.33813202381134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34853863716125</t>
+    <t xml:space="preserve">1.34853875637054</t>
   </si>
   <si>
     <t xml:space="preserve">1.41704976558685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40317416191101</t>
+    <t xml:space="preserve">1.40317404270172</t>
   </si>
   <si>
     <t xml:space="preserve">1.39536905288696</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">1.41097915172577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36501598358154</t>
+    <t xml:space="preserve">1.36501610279083</t>
   </si>
   <si>
     <t xml:space="preserve">1.38322794437408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36761796474457</t>
+    <t xml:space="preserve">1.36761784553528</t>
   </si>
   <si>
     <t xml:space="preserve">1.38149344921112</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">1.41358077526093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42138576507568</t>
+    <t xml:space="preserve">1.42138588428497</t>
   </si>
   <si>
     <t xml:space="preserve">1.41271352767944</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">1.34680426120758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36414885520935</t>
+    <t xml:space="preserve">1.36414873600006</t>
   </si>
   <si>
     <t xml:space="preserve">1.36241436004639</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">1.33032703399658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32078754901886</t>
+    <t xml:space="preserve">1.32078742980957</t>
   </si>
   <si>
     <t xml:space="preserve">1.3190530538559</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">1.17942941188812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26181590557098</t>
+    <t xml:space="preserve">1.26181602478027</t>
   </si>
   <si>
     <t xml:space="preserve">1.2921689748764</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">1.23146307468414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2175874710083</t>
+    <t xml:space="preserve">1.21758759021759</t>
   </si>
   <si>
     <t xml:space="preserve">1.24880766868591</t>
@@ -545,34 +545,34 @@
     <t xml:space="preserve">1.22886145114899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18549990653992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15774869918823</t>
+    <t xml:space="preserve">1.18550002574921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15774881839752</t>
   </si>
   <si>
     <t xml:space="preserve">1.11872339248657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13086462020874</t>
+    <t xml:space="preserve">1.13086473941803</t>
   </si>
   <si>
     <t xml:space="preserve">1.12305963039398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13346648216248</t>
+    <t xml:space="preserve">1.13346636295319</t>
   </si>
   <si>
     <t xml:space="preserve">1.11438727378845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11612176895142</t>
+    <t xml:space="preserve">1.11612164974213</t>
   </si>
   <si>
     <t xml:space="preserve">1.11525464057922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09790992736816</t>
+    <t xml:space="preserve">1.09791004657745</t>
   </si>
   <si>
     <t xml:space="preserve">1.09270668029785</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">1.10398054122925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1542797088623</t>
+    <t xml:space="preserve">1.15427982807159</t>
   </si>
   <si>
     <t xml:space="preserve">1.16295206546783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16208481788635</t>
+    <t xml:space="preserve">1.16208493709564</t>
   </si>
   <si>
     <t xml:space="preserve">1.17856204509735</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">1.18289828300476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20544624328613</t>
+    <t xml:space="preserve">1.20544612407684</t>
   </si>
   <si>
     <t xml:space="preserve">1.23493194580078</t>
@@ -611,22 +611,22 @@
     <t xml:space="preserve">1.24533867835999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2184544801712</t>
+    <t xml:space="preserve">1.21845459938049</t>
   </si>
   <si>
     <t xml:space="preserve">1.19937562942505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20111000537872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22799408435822</t>
+    <t xml:space="preserve">1.20111012458801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2279942035675</t>
   </si>
   <si>
     <t xml:space="preserve">1.22192347049713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23666644096375</t>
+    <t xml:space="preserve">1.23666632175446</t>
   </si>
   <si>
     <t xml:space="preserve">1.26875388622284</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">1.39883804321289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38669681549072</t>
+    <t xml:space="preserve">1.38669669628143</t>
   </si>
   <si>
     <t xml:space="preserve">1.35721111297607</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">1.33292853832245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28869998455048</t>
+    <t xml:space="preserve">1.28870010375977</t>
   </si>
   <si>
     <t xml:space="preserve">1.25747990608215</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">1.2444714307785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22712695598602</t>
+    <t xml:space="preserve">1.22712683677673</t>
   </si>
   <si>
     <t xml:space="preserve">1.25661265850067</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">1.22365808486938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22279071807861</t>
+    <t xml:space="preserve">1.2227908372879</t>
   </si>
   <si>
     <t xml:space="preserve">1.25314378738403</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">1.21585297584534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21672010421753</t>
+    <t xml:space="preserve">1.21672022342682</t>
   </si>
   <si>
     <t xml:space="preserve">1.19070339202881</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">1.18810176849365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.191570520401</t>
+    <t xml:space="preserve">1.19157063961029</t>
   </si>
   <si>
     <t xml:space="preserve">1.20284450054169</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">1.26355040073395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24273705482483</t>
+    <t xml:space="preserve">1.24273693561554</t>
   </si>
   <si>
     <t xml:space="preserve">1.23579907417297</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">1.22018897533417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24794030189514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24967479705811</t>
+    <t xml:space="preserve">1.24794042110443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2496749162674</t>
   </si>
   <si>
     <t xml:space="preserve">1.29043459892273</t>
@@ -749,10 +749,10 @@
     <t xml:space="preserve">1.29303622245789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31818568706512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30691182613373</t>
+    <t xml:space="preserve">1.31818580627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30691170692444</t>
   </si>
   <si>
     <t xml:space="preserve">1.27309000492096</t>
@@ -761,10 +761,10 @@
     <t xml:space="preserve">1.24013519287109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27916049957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2704883813858</t>
+    <t xml:space="preserve">1.27916061878204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27048826217651</t>
   </si>
   <si>
     <t xml:space="preserve">1.26528489589691</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">1.26441764831543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28523099422455</t>
+    <t xml:space="preserve">1.28523111343384</t>
   </si>
   <si>
     <t xml:space="preserve">1.2869656085968</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">1.33899927139282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41184628009796</t>
+    <t xml:space="preserve">1.41184639930725</t>
   </si>
   <si>
     <t xml:space="preserve">1.57835412025452</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">1.54019606113434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49856913089752</t>
+    <t xml:space="preserve">1.49856925010681</t>
   </si>
   <si>
     <t xml:space="preserve">1.50724148750305</t>
@@ -815,31 +815,31 @@
     <t xml:space="preserve">1.4786229133606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43352711200714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40577578544617</t>
+    <t xml:space="preserve">1.43352699279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40577590465546</t>
   </si>
   <si>
     <t xml:space="preserve">1.38496232032776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47168505191803</t>
+    <t xml:space="preserve">1.47168517112732</t>
   </si>
   <si>
     <t xml:space="preserve">1.48729526996613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47602117061615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45694220066071</t>
+    <t xml:space="preserve">1.47602128982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45694208145142</t>
   </si>
   <si>
     <t xml:space="preserve">1.46821618080139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45867657661438</t>
+    <t xml:space="preserve">1.45867669582367</t>
   </si>
   <si>
     <t xml:space="preserve">1.45954382419586</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">1.45607495307922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49076402187347</t>
+    <t xml:space="preserve">1.49076390266418</t>
   </si>
   <si>
     <t xml:space="preserve">1.47341954708099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52892208099365</t>
+    <t xml:space="preserve">1.52892196178436</t>
   </si>
   <si>
     <t xml:space="preserve">1.50637412071228</t>
@@ -866,10 +866,10 @@
     <t xml:space="preserve">1.58269023895264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56187665462494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53585982322693</t>
+    <t xml:space="preserve">1.56187677383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53585994243622</t>
   </si>
   <si>
     <t xml:space="preserve">1.48642790317535</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">1.51591360569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5688145160675</t>
+    <t xml:space="preserve">1.56881463527679</t>
   </si>
   <si>
     <t xml:space="preserve">1.57054901123047</t>
@@ -902,19 +902,19 @@
     <t xml:space="preserve">1.64686501026154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78648841381073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76047170162201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85933589935303</t>
+    <t xml:space="preserve">1.78648853302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7604718208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85933566093445</t>
   </si>
   <si>
     <t xml:space="preserve">1.8662736415863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84199142456055</t>
+    <t xml:space="preserve">1.84199118614197</t>
   </si>
   <si>
     <t xml:space="preserve">2.15245866775513</t>
@@ -932,22 +932,22 @@
     <t xml:space="preserve">1.95126187801361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05186009407043</t>
+    <t xml:space="preserve">2.05186033248901</t>
   </si>
   <si>
     <t xml:space="preserve">2.01543641090393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98074758052826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90443170070648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90790033340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91657280921936</t>
+    <t xml:space="preserve">1.98074734210968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9044314622879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90790057182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91657257080078</t>
   </si>
   <si>
     <t xml:space="preserve">1.90616607666016</t>
@@ -956,13 +956,13 @@
     <t xml:space="preserve">1.84892904758453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87321162223816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83158445358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84719467163086</t>
+    <t xml:space="preserve">1.87321138381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83158433437347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84719455242157</t>
   </si>
   <si>
     <t xml:space="preserve">1.93218290805817</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.92524516582489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94258952140808</t>
+    <t xml:space="preserve">1.94258975982666</t>
   </si>
   <si>
     <t xml:space="preserve">1.97727870941162</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">2.01370239257812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99462306499481</t>
+    <t xml:space="preserve">1.99462330341339</t>
   </si>
   <si>
     <t xml:space="preserve">1.94432413578033</t>
@@ -1007,13 +1007,13 @@
     <t xml:space="preserve">1.82117772102356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91310405731201</t>
+    <t xml:space="preserve">1.91310381889343</t>
   </si>
   <si>
     <t xml:space="preserve">1.72144663333893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67114758491516</t>
+    <t xml:space="preserve">1.67114746570587</t>
   </si>
   <si>
     <t xml:space="preserve">1.69976592063904</t>
@@ -1025,10 +1025,10 @@
     <t xml:space="preserve">1.67895245552063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63992726802826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64773237705231</t>
+    <t xml:space="preserve">1.63992738723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64773225784302</t>
   </si>
   <si>
     <t xml:space="preserve">1.62865316867828</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">1.60350370407104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59656584262848</t>
+    <t xml:space="preserve">1.59656596183777</t>
   </si>
   <si>
     <t xml:space="preserve">1.63905990123749</t>
@@ -1055,13 +1055,13 @@
     <t xml:space="preserve">1.69109380245209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7292515039444</t>
+    <t xml:space="preserve">1.72925162315369</t>
   </si>
   <si>
     <t xml:space="preserve">1.67548358440399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65640449523926</t>
+    <t xml:space="preserve">1.65640461444855</t>
   </si>
   <si>
     <t xml:space="preserve">1.63038766384125</t>
@@ -1070,22 +1070,22 @@
     <t xml:space="preserve">1.66681122779846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68155419826508</t>
+    <t xml:space="preserve">1.68155407905579</t>
   </si>
   <si>
     <t xml:space="preserve">1.68935918807983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67721807956696</t>
+    <t xml:space="preserve">1.67721796035767</t>
   </si>
   <si>
     <t xml:space="preserve">1.63385653495789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6217155456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65727174282074</t>
+    <t xml:space="preserve">1.62171542644501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65727186203003</t>
   </si>
   <si>
     <t xml:space="preserve">1.71537590026855</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">1.72578275203705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72751712799072</t>
+    <t xml:space="preserve">1.72751724720001</t>
   </si>
   <si>
     <t xml:space="preserve">1.71190702915192</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">1.88621973991394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81684172153473</t>
+    <t xml:space="preserve">1.81684160232544</t>
   </si>
   <si>
     <t xml:space="preserve">1.89489197731018</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">1.80816924571991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82984972000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85153079032898</t>
+    <t xml:space="preserve">1.82984983921051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85153067111969</t>
   </si>
   <si>
     <t xml:space="preserve">1.7821524143219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81250536441803</t>
+    <t xml:space="preserve">1.81250548362732</t>
   </si>
   <si>
     <t xml:space="preserve">1.79082489013672</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">1.73445510864258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76480805873871</t>
+    <t xml:space="preserve">1.76480793952942</t>
   </si>
   <si>
     <t xml:space="preserve">1.96860635280609</t>
@@ -1175,19 +1175,19 @@
     <t xml:space="preserve">1.8775475025177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83418619632721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84285831451416</t>
+    <t xml:space="preserve">1.8341863155365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84285843372345</t>
   </si>
   <si>
     <t xml:space="preserve">1.82551383972168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83852231502533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86020314693451</t>
+    <t xml:space="preserve">1.83852219581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86020290851593</t>
   </si>
   <si>
     <t xml:space="preserve">1.97294282913208</t>
@@ -1199,16 +1199,16 @@
     <t xml:space="preserve">1.92958116531372</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98595118522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04665684700012</t>
+    <t xml:space="preserve">1.98595094680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04665660858154</t>
   </si>
   <si>
     <t xml:space="preserve">2.03364849090576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04232048988342</t>
+    <t xml:space="preserve">2.042320728302</t>
   </si>
   <si>
     <t xml:space="preserve">2.072674036026</t>
@@ -1223,16 +1223,16 @@
     <t xml:space="preserve">2.15072441101074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05532884597778</t>
+    <t xml:space="preserve">2.05532908439636</t>
   </si>
   <si>
     <t xml:space="preserve">2.1854133605957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33717799186707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30248880386353</t>
+    <t xml:space="preserve">2.33717823028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3024890422821</t>
   </si>
   <si>
     <t xml:space="preserve">2.2808084487915</t>
@@ -1274,19 +1274,19 @@
     <t xml:space="preserve">2.76645588874817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83583402633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91388440132141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92255663871765</t>
+    <t xml:space="preserve">2.83583378791809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91388416290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92255640029907</t>
   </si>
   <si>
     <t xml:space="preserve">2.93122911453247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87052273750305</t>
+    <t xml:space="preserve">2.87052297592163</t>
   </si>
   <si>
     <t xml:space="preserve">2.92689275741577</t>
@@ -1298,10 +1298,10 @@
     <t xml:space="preserve">3.23909473419189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25210309028625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21741366386414</t>
+    <t xml:space="preserve">3.25210332870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21741390228271</t>
   </si>
   <si>
     <t xml:space="preserve">3.25643944740295</t>
@@ -1331,7 +1331,7 @@
     <t xml:space="preserve">3.34749794006348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50793552398682</t>
+    <t xml:space="preserve">3.50793528556824</t>
   </si>
   <si>
     <t xml:space="preserve">3.48625445365906</t>
@@ -1340,16 +1340,16 @@
     <t xml:space="preserve">3.55563282966614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51227164268494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62934684753418</t>
+    <t xml:space="preserve">3.51227188110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62934708595276</t>
   </si>
   <si>
     <t xml:space="preserve">3.6640362739563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73341464996338</t>
+    <t xml:space="preserve">3.73341417312622</t>
   </si>
   <si>
     <t xml:space="preserve">3.80712866783142</t>
@@ -1364,7 +1364,7 @@
     <t xml:space="preserve">4.0456166267395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09764957427979</t>
+    <t xml:space="preserve">4.09765005111694</t>
   </si>
   <si>
     <t xml:space="preserve">3.86783504486084</t>
@@ -1376,13 +1376,13 @@
     <t xml:space="preserve">3.94588565826416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97190237045288</t>
+    <t xml:space="preserve">3.97190189361572</t>
   </si>
   <si>
     <t xml:space="preserve">3.7117338180542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91986846923828</t>
+    <t xml:space="preserve">3.91986799240112</t>
   </si>
   <si>
     <t xml:space="preserve">4.07163333892822</t>
@@ -1418,13 +1418,13 @@
     <t xml:space="preserve">4.95186901092529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87381792068481</t>
+    <t xml:space="preserve">4.87381839752197</t>
   </si>
   <si>
     <t xml:space="preserve">4.31879329681396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80444002151489</t>
+    <t xml:space="preserve">4.80444049835205</t>
   </si>
   <si>
     <t xml:space="preserve">4.97788572311401</t>
@@ -1433,22 +1433,22 @@
     <t xml:space="preserve">5.01257514953613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03859186172485</t>
+    <t xml:space="preserve">5.0385913848877</t>
   </si>
   <si>
     <t xml:space="preserve">4.91718006134033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82178497314453</t>
+    <t xml:space="preserve">4.82178449630737</t>
   </si>
   <si>
     <t xml:space="preserve">4.85647392272949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89116287231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83045721054077</t>
+    <t xml:space="preserve">4.89116334915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83045768737793</t>
   </si>
   <si>
     <t xml:space="preserve">4.76107883453369</t>
@@ -1457,31 +1457,31 @@
     <t xml:space="preserve">4.54427194595337</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70904541015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60497760772705</t>
+    <t xml:space="preserve">4.70904493331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60497808456421</t>
   </si>
   <si>
     <t xml:space="preserve">4.58763360977173</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64833927154541</t>
+    <t xml:space="preserve">4.64833974838257</t>
   </si>
   <si>
     <t xml:space="preserve">4.61365079879761</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53559970855713</t>
+    <t xml:space="preserve">4.53559923171997</t>
   </si>
   <si>
     <t xml:space="preserve">4.47489356994629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40551567077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1843729019165</t>
+    <t xml:space="preserve">4.40551614761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18437242507935</t>
   </si>
   <si>
     <t xml:space="preserve">4.1887092590332</t>
@@ -1490,13 +1490,13 @@
     <t xml:space="preserve">4.24074268341064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08464097976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92854046821594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91553211212158</t>
+    <t xml:space="preserve">4.084641456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9285409450531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91553163528442</t>
   </si>
   <si>
     <t xml:space="preserve">3.85916233062744</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">4.14101123809814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62501072883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31280899047852</t>
+    <t xml:space="preserve">3.62501096725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31280922889709</t>
   </si>
   <si>
     <t xml:space="preserve">3.28679227828979</t>
@@ -1526,10 +1526,10 @@
     <t xml:space="preserve">3.09166598320007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03529644012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04830479621887</t>
+    <t xml:space="preserve">3.03529620170593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04830455780029</t>
   </si>
   <si>
     <t xml:space="preserve">3.07865762710571</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">2.96158170700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89653968811035</t>
+    <t xml:space="preserve">2.89653992652893</t>
   </si>
   <si>
     <t xml:space="preserve">2.90521192550659</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">3.2607753276825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24343109130859</t>
+    <t xml:space="preserve">3.24343085289001</t>
   </si>
   <si>
     <t xml:space="preserve">3.19139719009399</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">3.43855690956116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39519572257996</t>
+    <t xml:space="preserve">3.39519548416138</t>
   </si>
   <si>
     <t xml:space="preserve">3.20440554618835</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">2.86618685722351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93990135192871</t>
+    <t xml:space="preserve">2.93990159034729</t>
   </si>
   <si>
     <t xml:space="preserve">2.88353133201599</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">2.97459053993225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02228784561157</t>
+    <t xml:space="preserve">3.02228760719299</t>
   </si>
   <si>
     <t xml:space="preserve">3.38218760490417</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">3.15670824050903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11768269538879</t>
+    <t xml:space="preserve">3.11768293380737</t>
   </si>
   <si>
     <t xml:space="preserve">3.08732986450195</t>
@@ -1655,19 +1655,19 @@
     <t xml:space="preserve">3.46023774147034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59032201766968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88517904281616</t>
+    <t xml:space="preserve">3.5903217792511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88517951965332</t>
   </si>
   <si>
     <t xml:space="preserve">3.90252375602722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8548264503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11499452590942</t>
+    <t xml:space="preserve">3.85482621192932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11499404907227</t>
   </si>
   <si>
     <t xml:space="preserve">4.27543115615845</t>
@@ -1682,13 +1682,13 @@
     <t xml:space="preserve">4.1323390007019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95889401435852</t>
+    <t xml:space="preserve">3.95889353752136</t>
   </si>
   <si>
     <t xml:space="preserve">3.82447338104248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9675657749176</t>
+    <t xml:space="preserve">3.96756625175476</t>
   </si>
   <si>
     <t xml:space="preserve">3.9415488243103</t>
@@ -1709,25 +1709,25 @@
     <t xml:space="preserve">4.01526355743408</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09331369400024</t>
+    <t xml:space="preserve">4.09331321716309</t>
   </si>
   <si>
     <t xml:space="preserve">4.03260803222656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98924612998962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92420434951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82880878448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75943160057068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74642324447632</t>
+    <t xml:space="preserve">3.98924660682678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92420482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82880926132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75943112373352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74642276763916</t>
   </si>
   <si>
     <t xml:space="preserve">3.56864094734192</t>
@@ -1754,16 +1754,16 @@
     <t xml:space="preserve">4.21906137466431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2320704460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20171737670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68302869796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88249111175537</t>
+    <t xml:space="preserve">4.23207092285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20171689987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68302822113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88249063491821</t>
   </si>
   <si>
     <t xml:space="preserve">4.76975107192993</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">4.72638988494873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63966751098633</t>
+    <t xml:space="preserve">4.63966703414917</t>
   </si>
   <si>
     <t xml:space="preserve">4.55294466018677</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">4.44887685775757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39684391021729</t>
+    <t xml:space="preserve">4.39684343338013</t>
   </si>
   <si>
     <t xml:space="preserve">3.91119599342346</t>
@@ -4236,6 +4236,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.67000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53999996185303</t>
   </si>
 </sst>
 </file>
@@ -70484,7 +70487,7 @@
     </row>
     <row r="2536">
       <c r="A2536" s="1" t="n">
-        <v>46009.6909953704</v>
+        <v>46009.3333333333</v>
       </c>
       <c r="B2536" t="n">
         <v>39533</v>
@@ -70505,6 +70508,32 @@
         <v>1407</v>
       </c>
       <c r="H2536" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" s="1" t="n">
+        <v>46010.6912847222</v>
+      </c>
+      <c r="B2537" t="n">
+        <v>101171</v>
+      </c>
+      <c r="C2537" t="n">
+        <v>7.67000007629395</v>
+      </c>
+      <c r="D2537" t="n">
+        <v>7.51999998092651</v>
+      </c>
+      <c r="E2537" t="n">
+        <v>7.67000007629395</v>
+      </c>
+      <c r="F2537" t="n">
+        <v>7.53999996185303</v>
+      </c>
+      <c r="G2537" t="s">
+        <v>1408</v>
+      </c>
+      <c r="H2537" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="1409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="1410">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95473062992096</t>
+    <t xml:space="preserve">1.95473098754883</t>
   </si>
   <si>
     <t xml:space="preserve">FM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95993399620056</t>
+    <t xml:space="preserve">1.95993411540985</t>
   </si>
   <si>
     <t xml:space="preserve">1.9096348285675</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">1.8558669090271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86453938484192</t>
+    <t xml:space="preserve">1.86453926563263</t>
   </si>
   <si>
     <t xml:space="preserve">1.68415582180023</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">1.76914405822754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74486172199249</t>
+    <t xml:space="preserve">1.74486184120178</t>
   </si>
   <si>
     <t xml:space="preserve">1.69542980194092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61824667453766</t>
+    <t xml:space="preserve">1.61824655532837</t>
   </si>
   <si>
     <t xml:space="preserve">1.52285146713257</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">1.47949004173279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34420263767242</t>
+    <t xml:space="preserve">1.34420251846313</t>
   </si>
   <si>
     <t xml:space="preserve">1.45434057712555</t>
@@ -101,13 +101,13 @@
     <t xml:space="preserve">1.53325831890106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.499436378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43005812168121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40751028060913</t>
+    <t xml:space="preserve">1.49943625926971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4300582408905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40751016139984</t>
   </si>
   <si>
     <t xml:space="preserve">1.38582956790924</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">1.28349673748016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17682754993439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24186968803406</t>
+    <t xml:space="preserve">1.17682766914368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24186980724335</t>
   </si>
   <si>
     <t xml:space="preserve">1.20718061923981</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">1.23059582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43873059749603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39710342884064</t>
+    <t xml:space="preserve">1.43873047828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39710354804993</t>
   </si>
   <si>
     <t xml:space="preserve">1.50030362606049</t>
@@ -143,31 +143,31 @@
     <t xml:space="preserve">1.46561455726624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5211169719696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51678085327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49423289299011</t>
+    <t xml:space="preserve">1.52111709117889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51678073406219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4942330121994</t>
   </si>
   <si>
     <t xml:space="preserve">1.47688841819763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47515404224396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50984311103821</t>
+    <t xml:space="preserve">1.47515392303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5098432302475</t>
   </si>
   <si>
     <t xml:space="preserve">1.56014227867126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58702623844147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55754053592682</t>
+    <t xml:space="preserve">1.58702635765076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55754041671753</t>
   </si>
   <si>
     <t xml:space="preserve">1.52805471420288</t>
@@ -179,16 +179,16 @@
     <t xml:space="preserve">1.51244461536407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55146992206573</t>
+    <t xml:space="preserve">1.55147004127502</t>
   </si>
   <si>
     <t xml:space="preserve">1.61651194095612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67374897003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70843815803528</t>
+    <t xml:space="preserve">1.67374908924103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70843827724457</t>
   </si>
   <si>
     <t xml:space="preserve">1.67808520793915</t>
@@ -206,34 +206,34 @@
     <t xml:space="preserve">1.53499269485474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49770188331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49683463573456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48122453689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41791689395905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39970505237579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35200774669647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39190006256104</t>
+    <t xml:space="preserve">1.49770200252533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49683451652527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48122441768646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41791701316833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39970517158508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35200762748718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39190018177032</t>
   </si>
   <si>
     <t xml:space="preserve">1.46041119098663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57228338718414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62952053546906</t>
+    <t xml:space="preserve">1.57228350639343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62952041625977</t>
   </si>
   <si>
     <t xml:space="preserve">1.60437095165253</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">1.60870695114136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62518441677094</t>
+    <t xml:space="preserve">1.62518429756165</t>
   </si>
   <si>
     <t xml:space="preserve">1.65987348556519</t>
@@ -260,10 +260,10 @@
     <t xml:space="preserve">1.58876073360443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49249839782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4578093290329</t>
+    <t xml:space="preserve">1.49249851703644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45780944824219</t>
   </si>
   <si>
     <t xml:space="preserve">1.47775566577911</t>
@@ -278,25 +278,25 @@
     <t xml:space="preserve">1.56794726848602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53932881355286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53065657615662</t>
+    <t xml:space="preserve">1.53932893276215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53065645694733</t>
   </si>
   <si>
     <t xml:space="preserve">1.54106330871582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56968176364899</t>
+    <t xml:space="preserve">1.5696816444397</t>
   </si>
   <si>
     <t xml:space="preserve">1.5471339225769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55060267448425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56708002090454</t>
+    <t xml:space="preserve">1.55060279369354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56708025932312</t>
   </si>
   <si>
     <t xml:space="preserve">1.5740180015564</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">1.56100952625275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54453217983246</t>
+    <t xml:space="preserve">1.54453229904175</t>
   </si>
   <si>
     <t xml:space="preserve">1.45000445842743</t>
@@ -323,19 +323,19 @@
     <t xml:space="preserve">1.40057241916656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3875640630722</t>
+    <t xml:space="preserve">1.38756394386292</t>
   </si>
   <si>
     <t xml:space="preserve">1.44740283489227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49163138866425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4838262796402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32338917255402</t>
+    <t xml:space="preserve">1.49163126945496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48382616043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32338929176331</t>
   </si>
   <si>
     <t xml:space="preserve">1.3294597864151</t>
@@ -347,19 +347,19 @@
     <t xml:space="preserve">1.39016568660736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35981273651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33726477622986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31124806404114</t>
+    <t xml:space="preserve">1.35981261730194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33726489543915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31124794483185</t>
   </si>
   <si>
     <t xml:space="preserve">1.30084121227264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30257570743561</t>
+    <t xml:space="preserve">1.30257558822632</t>
   </si>
   <si>
     <t xml:space="preserve">1.36154723167419</t>
@@ -368,22 +368,22 @@
     <t xml:space="preserve">1.37802445888519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3823606967926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39623618125916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37715744972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40490865707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39450180530548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40404140949249</t>
+    <t xml:space="preserve">1.38236057758331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39623630046844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.377157330513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40490853786469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39450192451477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4040412902832</t>
   </si>
   <si>
     <t xml:space="preserve">1.393634557724</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">1.36588335037231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3563437461853</t>
+    <t xml:space="preserve">1.35634386539459</t>
   </si>
   <si>
     <t xml:space="preserve">1.35460937023163</t>
@@ -419,10 +419,10 @@
     <t xml:space="preserve">1.32685804367065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30170845985413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30777907371521</t>
+    <t xml:space="preserve">1.30170857906342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3077791929245</t>
   </si>
   <si>
     <t xml:space="preserve">1.34767162799835</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">1.34506988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33379590511322</t>
+    <t xml:space="preserve">1.33379578590393</t>
   </si>
   <si>
     <t xml:space="preserve">1.37108671665192</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">1.35547661781311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34940612316132</t>
+    <t xml:space="preserve">1.34940588474274</t>
   </si>
   <si>
     <t xml:space="preserve">1.33813202381134</t>
@@ -452,10 +452,10 @@
     <t xml:space="preserve">1.41704976558685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40317404270172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39536905288696</t>
+    <t xml:space="preserve">1.40317416191101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39536893367767</t>
   </si>
   <si>
     <t xml:space="preserve">1.41097915172577</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">1.38322794437408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36761784553528</t>
+    <t xml:space="preserve">1.36761772632599</t>
   </si>
   <si>
     <t xml:space="preserve">1.38149344921112</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">1.41271352767944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40924477577209</t>
+    <t xml:space="preserve">1.40924465656281</t>
   </si>
   <si>
     <t xml:space="preserve">1.42572212219238</t>
@@ -497,13 +497,13 @@
     <t xml:space="preserve">1.35114049911499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35894548892975</t>
+    <t xml:space="preserve">1.35894560813904</t>
   </si>
   <si>
     <t xml:space="preserve">1.34680426120758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36414873600006</t>
+    <t xml:space="preserve">1.36414885520935</t>
   </si>
   <si>
     <t xml:space="preserve">1.36241436004639</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">1.33032703399658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32078742980957</t>
+    <t xml:space="preserve">1.32078754901886</t>
   </si>
   <si>
     <t xml:space="preserve">1.3190530538559</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">1.31992018222809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31298243999481</t>
+    <t xml:space="preserve">1.3129825592041</t>
   </si>
   <si>
     <t xml:space="preserve">1.17942941188812</t>
@@ -530,19 +530,19 @@
     <t xml:space="preserve">1.26181602478027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2921689748764</t>
+    <t xml:space="preserve">1.29216909408569</t>
   </si>
   <si>
     <t xml:space="preserve">1.23146307468414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21758759021759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24880766868591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22886145114899</t>
+    <t xml:space="preserve">1.2175874710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2488077878952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22886157035828</t>
   </si>
   <si>
     <t xml:space="preserve">1.18550002574921</t>
@@ -554,58 +554,58 @@
     <t xml:space="preserve">1.11872339248657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13086473941803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12305963039398</t>
+    <t xml:space="preserve">1.13086462020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12305951118469</t>
   </si>
   <si>
     <t xml:space="preserve">1.13346636295319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11438727378845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11612164974213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11525464057922</t>
+    <t xml:space="preserve">1.11438739299774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11612176895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11525452136993</t>
   </si>
   <si>
     <t xml:space="preserve">1.09791004657745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09270668029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07536220550537</t>
+    <t xml:space="preserve">1.09270656108856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07536208629608</t>
   </si>
   <si>
     <t xml:space="preserve">1.07276034355164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10398054122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15427982807159</t>
+    <t xml:space="preserve">1.10398066043854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1542797088623</t>
   </si>
   <si>
     <t xml:space="preserve">1.16295206546783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16208493709564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17856204509735</t>
+    <t xml:space="preserve">1.16208481788635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17856216430664</t>
   </si>
   <si>
     <t xml:space="preserve">1.18289828300476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20544612407684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23493194580078</t>
+    <t xml:space="preserve">1.20544624328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23493206501007</t>
   </si>
   <si>
     <t xml:space="preserve">1.24533867835999</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">1.20111012458801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2279942035675</t>
+    <t xml:space="preserve">1.22799408435822</t>
   </si>
   <si>
     <t xml:space="preserve">1.22192347049713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23666632175446</t>
+    <t xml:space="preserve">1.23666656017303</t>
   </si>
   <si>
     <t xml:space="preserve">1.26875388622284</t>
@@ -638,40 +638,40 @@
     <t xml:space="preserve">1.39883804321289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38669669628143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35721111297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34593725204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33292853832245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28870010375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25747990608215</t>
+    <t xml:space="preserve">1.38669681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35721099376678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34593713283539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33292865753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28869986534119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25747978687286</t>
   </si>
   <si>
     <t xml:space="preserve">1.23319756984711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2444714307785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22712683677673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25661265850067</t>
+    <t xml:space="preserve">1.24447154998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22712695598602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25661277770996</t>
   </si>
   <si>
     <t xml:space="preserve">1.22365808486938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2227908372879</t>
+    <t xml:space="preserve">1.22279071807861</t>
   </si>
   <si>
     <t xml:space="preserve">1.25314378738403</t>
@@ -680,10 +680,10 @@
     <t xml:space="preserve">1.22625970840454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21325135231018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20891511440277</t>
+    <t xml:space="preserve">1.21325147151947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20891523361206</t>
   </si>
   <si>
     <t xml:space="preserve">1.20457899570465</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">1.21585297584534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21672022342682</t>
+    <t xml:space="preserve">1.21672010421753</t>
   </si>
   <si>
     <t xml:space="preserve">1.19070339202881</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">1.18810176849365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19157063961029</t>
+    <t xml:space="preserve">1.191570520401</t>
   </si>
   <si>
     <t xml:space="preserve">1.20284450054169</t>
@@ -719,16 +719,16 @@
     <t xml:space="preserve">1.27742612361908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27222275733948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2982394695282</t>
+    <t xml:space="preserve">1.27222287654877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29823958873749</t>
   </si>
   <si>
     <t xml:space="preserve">1.26355040073395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24273693561554</t>
+    <t xml:space="preserve">1.24273705482483</t>
   </si>
   <si>
     <t xml:space="preserve">1.23579907417297</t>
@@ -737,37 +737,37 @@
     <t xml:space="preserve">1.22018897533417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24794042110443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2496749162674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29043459892273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29303622245789</t>
+    <t xml:space="preserve">1.24794030189514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24967479705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29043447971344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2930361032486</t>
   </si>
   <si>
     <t xml:space="preserve">1.31818580627441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30691170692444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27309000492096</t>
+    <t xml:space="preserve">1.30691182613373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27308988571167</t>
   </si>
   <si>
     <t xml:space="preserve">1.24013519287109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27916061878204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27048826217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26528489589691</t>
+    <t xml:space="preserve">1.27916049957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2704883813858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26528477668762</t>
   </si>
   <si>
     <t xml:space="preserve">1.28436398506165</t>
@@ -776,13 +776,13 @@
     <t xml:space="preserve">1.27482438087463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26441764831543</t>
+    <t xml:space="preserve">1.26441776752472</t>
   </si>
   <si>
     <t xml:space="preserve">1.28523111343384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2869656085968</t>
+    <t xml:space="preserve">1.28696548938751</t>
   </si>
   <si>
     <t xml:space="preserve">1.3398665189743</t>
@@ -800,46 +800,46 @@
     <t xml:space="preserve">1.51851534843445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54019606113434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49856925010681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50724148750305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50203800201416</t>
+    <t xml:space="preserve">1.54019594192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49856913089752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50724136829376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50203812122345</t>
   </si>
   <si>
     <t xml:space="preserve">1.4786229133606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43352699279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40577590465546</t>
+    <t xml:space="preserve">1.43352711200714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40577578544617</t>
   </si>
   <si>
     <t xml:space="preserve">1.38496232032776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47168517112732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48729526996613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47602128982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45694208145142</t>
+    <t xml:space="preserve">1.47168505191803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48729515075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47602117061615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45694220066071</t>
   </si>
   <si>
     <t xml:space="preserve">1.46821618080139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45867669582367</t>
+    <t xml:space="preserve">1.45867657661438</t>
   </si>
   <si>
     <t xml:space="preserve">1.45954382419586</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">1.45607495307922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49076390266418</t>
+    <t xml:space="preserve">1.49076402187347</t>
   </si>
   <si>
     <t xml:space="preserve">1.47341954708099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52892196178436</t>
+    <t xml:space="preserve">1.52892220020294</t>
   </si>
   <si>
     <t xml:space="preserve">1.50637412071228</t>
@@ -863,13 +863,13 @@
     <t xml:space="preserve">1.57488524913788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58269023895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56187677383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53585994243622</t>
+    <t xml:space="preserve">1.58269035816193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56187665462494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53585982322693</t>
   </si>
   <si>
     <t xml:space="preserve">1.48642790317535</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">1.48035740852356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48816239833832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51591360569</t>
+    <t xml:space="preserve">1.48816251754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51591372489929</t>
   </si>
   <si>
     <t xml:space="preserve">1.56881463527679</t>
@@ -908,106 +908,106 @@
     <t xml:space="preserve">1.7604718208313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85933566093445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8662736415863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84199118614197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15245866775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99982666969299</t>
+    <t xml:space="preserve">1.85933589935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86627352237701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84199130535126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15245890617371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9998265504837</t>
   </si>
   <si>
     <t xml:space="preserve">2.05879807472229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00329542160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95126187801361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05186033248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01543641090393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98074734210968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9044314622879</t>
+    <t xml:space="preserve">2.00329566001892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9512619972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05186009407043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01543664932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98074758052826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90443193912506</t>
   </si>
   <si>
     <t xml:space="preserve">1.90790057182312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91657257080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90616607666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84892904758453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87321138381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83158433437347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84719455242157</t>
+    <t xml:space="preserve">1.91657269001007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90616595745087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84892892837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87321150302887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83158457279205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84719467163086</t>
   </si>
   <si>
     <t xml:space="preserve">1.93218290805817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93738627433777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92524516582489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94258975982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97727870941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0206401348114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06920456886292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01196765899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03971910476685</t>
+    <t xml:space="preserve">1.93738615512848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92524492740631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94258952140808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97727859020233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02063989639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06920480728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.011967420578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03971886634827</t>
   </si>
   <si>
     <t xml:space="preserve">2.01370239257812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99462330341339</t>
+    <t xml:space="preserve">1.99462342262268</t>
   </si>
   <si>
     <t xml:space="preserve">1.94432413578033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90269696712494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82117772102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91310381889343</t>
+    <t xml:space="preserve">1.90269720554352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82117760181427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91310393810272</t>
   </si>
   <si>
     <t xml:space="preserve">1.72144663333893</t>
@@ -1022,10 +1022,10 @@
     <t xml:space="preserve">1.68762469291687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67895245552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63992738723755</t>
+    <t xml:space="preserve">1.67895257472992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63992714881897</t>
   </si>
   <si>
     <t xml:space="preserve">1.64773225784302</t>
@@ -1037,22 +1037,22 @@
     <t xml:space="preserve">1.62691879272461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60350370407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59656596183777</t>
+    <t xml:space="preserve">1.60350358486176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59656584262848</t>
   </si>
   <si>
     <t xml:space="preserve">1.63905990123749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64859938621521</t>
+    <t xml:space="preserve">1.6485995054245</t>
   </si>
   <si>
     <t xml:space="preserve">1.6650767326355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69109380245209</t>
+    <t xml:space="preserve">1.6910936832428</t>
   </si>
   <si>
     <t xml:space="preserve">1.72925162315369</t>
@@ -1061,16 +1061,16 @@
     <t xml:space="preserve">1.67548358440399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65640461444855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63038766384125</t>
+    <t xml:space="preserve">1.65640449523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63038778305054</t>
   </si>
   <si>
     <t xml:space="preserve">1.66681122779846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68155407905579</t>
+    <t xml:space="preserve">1.68155419826508</t>
   </si>
   <si>
     <t xml:space="preserve">1.68935918807983</t>
@@ -1085,16 +1085,16 @@
     <t xml:space="preserve">1.62171542644501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65727186203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71537590026855</t>
+    <t xml:space="preserve">1.65727174282074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71537601947784</t>
   </si>
   <si>
     <t xml:space="preserve">1.66854572296143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71711039543152</t>
+    <t xml:space="preserve">1.71711051464081</t>
   </si>
   <si>
     <t xml:space="preserve">1.7067037820816</t>
@@ -1112,43 +1112,43 @@
     <t xml:space="preserve">1.74312722682953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77781641483307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77348029613495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80383312702179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93391752243042</t>
+    <t xml:space="preserve">1.77781629562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77348017692566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80383324623108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93391740322113</t>
   </si>
   <si>
     <t xml:space="preserve">1.88188374042511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95559799671173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88621973991394</t>
+    <t xml:space="preserve">1.95559823513031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88621962070465</t>
   </si>
   <si>
     <t xml:space="preserve">1.81684160232544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89489197731018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80816924571991</t>
+    <t xml:space="preserve">1.89489221572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8081693649292</t>
   </si>
   <si>
     <t xml:space="preserve">1.82984983921051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85153067111969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7821524143219</t>
+    <t xml:space="preserve">1.85153090953827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78215253353119</t>
   </si>
   <si>
     <t xml:space="preserve">1.81250548362732</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">1.79082489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73445510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76480793952942</t>
+    <t xml:space="preserve">1.73445498943329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.764808177948</t>
   </si>
   <si>
     <t xml:space="preserve">1.96860635280609</t>
@@ -1172,22 +1172,22 @@
     <t xml:space="preserve">1.89055597782135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8775475025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8341863155365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84285843372345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82551383972168</t>
+    <t xml:space="preserve">1.87754738330841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83418619632721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84285831451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82551395893097</t>
   </si>
   <si>
     <t xml:space="preserve">1.83852219581604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86020290851593</t>
+    <t xml:space="preserve">1.86020302772522</t>
   </si>
   <si>
     <t xml:space="preserve">1.97294282913208</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">1.98595094680786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04665660858154</t>
+    <t xml:space="preserve">2.0466570854187</t>
   </si>
   <si>
     <t xml:space="preserve">2.03364849090576</t>
@@ -1211,55 +1211,55 @@
     <t xml:space="preserve">2.042320728302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.072674036026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08134579658508</t>
+    <t xml:space="preserve">2.07267379760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08134627342224</t>
   </si>
   <si>
     <t xml:space="preserve">2.1116988658905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15072441101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05532908439636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1854133605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33717823028564</t>
+    <t xml:space="preserve">2.15072417259216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05532884597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18541312217712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33717799186707</t>
   </si>
   <si>
     <t xml:space="preserve">2.3024890422821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2808084487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21142983436584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3068253993988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28514456748962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44991755485535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48894286155701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59301018714905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38921165466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49761533737183</t>
+    <t xml:space="preserve">2.28080821037292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21143007278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30682516098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28514432907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44991779327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48894309997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59300994873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38921189308167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49761557579041</t>
   </si>
   <si>
     <t xml:space="preserve">2.57566571235657</t>
@@ -1268,16 +1268,16 @@
     <t xml:space="preserve">2.62769937515259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71442222595215</t>
+    <t xml:space="preserve">2.71442198753357</t>
   </si>
   <si>
     <t xml:space="preserve">2.76645588874817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83583378791809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91388416290283</t>
+    <t xml:space="preserve">2.83583402633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91388440132141</t>
   </si>
   <si>
     <t xml:space="preserve">2.92255640029907</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">3.23909473419189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25210332870483</t>
+    <t xml:space="preserve">3.25210309028625</t>
   </si>
   <si>
     <t xml:space="preserve">3.21741390228271</t>
@@ -1313,37 +1313,37 @@
     <t xml:space="preserve">3.20874190330505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36917901039124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26511144638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22175002098083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33882594108582</t>
+    <t xml:space="preserve">3.36917877197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26511168479919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22175025939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33882570266724</t>
   </si>
   <si>
     <t xml:space="preserve">3.27811980247498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34749794006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50793528556824</t>
+    <t xml:space="preserve">3.34749817848206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50793552398682</t>
   </si>
   <si>
     <t xml:space="preserve">3.48625445365906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55563282966614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51227188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62934708595276</t>
+    <t xml:space="preserve">3.55563259124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51227140426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62934684753418</t>
   </si>
   <si>
     <t xml:space="preserve">3.6640362739563</t>
@@ -1364,13 +1364,13 @@
     <t xml:space="preserve">4.0456166267395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09765005111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86783504486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0412802696228</t>
+    <t xml:space="preserve">4.09764957427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86783480644226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04127979278564</t>
   </si>
   <si>
     <t xml:space="preserve">3.94588565826416</t>
@@ -1382,13 +1382,13 @@
     <t xml:space="preserve">3.7117338180542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91986799240112</t>
+    <t xml:space="preserve">3.9198682308197</t>
   </si>
   <si>
     <t xml:space="preserve">4.07163333892822</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24941444396973</t>
+    <t xml:space="preserve">4.24941492080688</t>
   </si>
   <si>
     <t xml:space="preserve">4.25375080108643</t>
@@ -1397,88 +1397,88 @@
     <t xml:space="preserve">4.28410387039185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62232208251953</t>
+    <t xml:space="preserve">4.62232255935669</t>
   </si>
   <si>
     <t xml:space="preserve">4.57896137237549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74373435974121</t>
+    <t xml:space="preserve">4.74373388290405</t>
   </si>
   <si>
     <t xml:space="preserve">4.75240707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05593633651733</t>
+    <t xml:space="preserve">5.05593585968018</t>
   </si>
   <si>
     <t xml:space="preserve">4.98655796051025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95186901092529</t>
+    <t xml:space="preserve">4.95186948776245</t>
   </si>
   <si>
     <t xml:space="preserve">4.87381839752197</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31879329681396</t>
+    <t xml:space="preserve">4.31879281997681</t>
   </si>
   <si>
     <t xml:space="preserve">4.80444049835205</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97788572311401</t>
+    <t xml:space="preserve">4.97788619995117</t>
   </si>
   <si>
     <t xml:space="preserve">5.01257514953613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0385913848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91718006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82178449630737</t>
+    <t xml:space="preserve">5.03859186172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91717958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82178497314453</t>
   </si>
   <si>
     <t xml:space="preserve">4.85647392272949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89116334915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83045768737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76107883453369</t>
+    <t xml:space="preserve">4.89116287231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83045721054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76107835769653</t>
   </si>
   <si>
     <t xml:space="preserve">4.54427194595337</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70904493331909</t>
+    <t xml:space="preserve">4.70904541015625</t>
   </si>
   <si>
     <t xml:space="preserve">4.60497808456421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58763360977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64833974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61365079879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53559923171997</t>
+    <t xml:space="preserve">4.58763313293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64833927154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61365032196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53560018539429</t>
   </si>
   <si>
     <t xml:space="preserve">4.47489356994629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40551614761353</t>
+    <t xml:space="preserve">4.40551567077637</t>
   </si>
   <si>
     <t xml:space="preserve">4.18437242507935</t>
@@ -1493,10 +1493,10 @@
     <t xml:space="preserve">4.084641456604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9285409450531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91553163528442</t>
+    <t xml:space="preserve">3.92854022979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91553211212158</t>
   </si>
   <si>
     <t xml:space="preserve">3.85916233062744</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">3.62501096725464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31280922889709</t>
+    <t xml:space="preserve">3.31280899047852</t>
   </si>
   <si>
     <t xml:space="preserve">3.28679227828979</t>
@@ -1520,28 +1520,28 @@
     <t xml:space="preserve">3.14369964599609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00927948951721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09166598320007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03529620170593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04830455780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07865762710571</t>
+    <t xml:space="preserve">3.00927925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09166622161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03529644012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04830479621887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07865786552429</t>
   </si>
   <si>
     <t xml:space="preserve">2.96158170700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89653992652893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90521192550659</t>
+    <t xml:space="preserve">2.89653968811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90521216392517</t>
   </si>
   <si>
     <t xml:space="preserve">3.02662420272827</t>
@@ -1550,16 +1550,16 @@
     <t xml:space="preserve">2.75344729423523</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80548071861267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88786768913269</t>
+    <t xml:space="preserve">2.80548095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88786745071411</t>
   </si>
   <si>
     <t xml:space="preserve">3.04396843910217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2607753276825</t>
+    <t xml:space="preserve">3.26077556610107</t>
   </si>
   <si>
     <t xml:space="preserve">3.24343085289001</t>
@@ -1568,13 +1568,13 @@
     <t xml:space="preserve">3.19139719009399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42554879188538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43855690956116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39519548416138</t>
+    <t xml:space="preserve">3.4255485534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43855714797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39519596099854</t>
   </si>
   <si>
     <t xml:space="preserve">3.20440554618835</t>
@@ -1586,19 +1586,19 @@
     <t xml:space="preserve">2.86618685722351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93990159034729</t>
+    <t xml:space="preserve">2.93990135192871</t>
   </si>
   <si>
     <t xml:space="preserve">2.88353133201599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97459053993225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02228760719299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38218760490417</t>
+    <t xml:space="preserve">2.97459030151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02228784561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3821873664856</t>
   </si>
   <si>
     <t xml:space="preserve">3.32148122787476</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">3.15670824050903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11768293380737</t>
+    <t xml:space="preserve">3.11768269538879</t>
   </si>
   <si>
     <t xml:space="preserve">3.08732986450195</t>
@@ -1616,10 +1616,10 @@
     <t xml:space="preserve">3.06564927101135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81848955154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68840527534485</t>
+    <t xml:space="preserve">2.81848931312561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68840503692627</t>
   </si>
   <si>
     <t xml:space="preserve">2.73176670074463</t>
@@ -1628,19 +1628,19 @@
     <t xml:space="preserve">2.63203573226929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98759889602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17405247688293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3041365146637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3084728717804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17838859558105</t>
+    <t xml:space="preserve">2.98759865760803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17405271530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30413675308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30847311019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17838883399963</t>
   </si>
   <si>
     <t xml:space="preserve">3.10467433929443</t>
@@ -1658,49 +1658,49 @@
     <t xml:space="preserve">3.5903217792511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88517951965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90252375602722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85482621192932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11499404907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27543115615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10198640823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.145348072052</t>
+    <t xml:space="preserve">3.88517904281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9025239944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8548264503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11499452590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27543163299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10198593139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14534759521484</t>
   </si>
   <si>
     <t xml:space="preserve">4.1323390007019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95889353752136</t>
+    <t xml:space="preserve">3.95889377593994</t>
   </si>
   <si>
     <t xml:space="preserve">3.82447338104248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96756625175476</t>
+    <t xml:space="preserve">3.96756529808044</t>
   </si>
   <si>
     <t xml:space="preserve">3.9415488243103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99791860580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00659084320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06296110153198</t>
+    <t xml:space="preserve">3.99791884422302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00659132003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06296062469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.05862474441528</t>
@@ -1709,31 +1709,31 @@
     <t xml:space="preserve">4.01526355743408</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09331321716309</t>
+    <t xml:space="preserve">4.0933141708374</t>
   </si>
   <si>
     <t xml:space="preserve">4.03260803222656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98924660682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92420482635498</t>
+    <t xml:space="preserve">3.98924684524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9242045879364</t>
   </si>
   <si>
     <t xml:space="preserve">3.82880926132202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75943112373352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74642276763916</t>
+    <t xml:space="preserve">3.75943160057068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74642300605774</t>
   </si>
   <si>
     <t xml:space="preserve">3.56864094734192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77677583694458</t>
+    <t xml:space="preserve">3.77677607536316</t>
   </si>
   <si>
     <t xml:space="preserve">4.24507856369019</t>
@@ -1748,22 +1748,22 @@
     <t xml:space="preserve">4.06729698181152</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16269159317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21906137466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23207092285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20171689987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68302822113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88249063491821</t>
+    <t xml:space="preserve">4.16269254684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21906185150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2320704460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20171737670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68302869796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88249111175537</t>
   </si>
   <si>
     <t xml:space="preserve">4.76975107192993</t>
@@ -1778,25 +1778,25 @@
     <t xml:space="preserve">4.55294466018677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44887685775757</t>
+    <t xml:space="preserve">4.44887733459473</t>
   </si>
   <si>
     <t xml:space="preserve">4.39684343338013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91119599342346</t>
+    <t xml:space="preserve">3.91119647026062</t>
   </si>
   <si>
     <t xml:space="preserve">4.04995250701904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27009868621826</t>
+    <t xml:space="preserve">4.2700982093811</t>
   </si>
   <si>
     <t xml:space="preserve">4.12285375595093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01130437850952</t>
+    <t xml:space="preserve">4.01130485534668</t>
   </si>
   <si>
     <t xml:space="preserve">3.91760349273682</t>
@@ -1805,22 +1805,22 @@
     <t xml:space="preserve">4.22547912597656</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00684213638306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8328263759613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85513615608215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8595974445343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93098974227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83728837966919</t>
+    <t xml:space="preserve">4.00684261322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83282613754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85513591766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85959792137146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93098950386047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83728790283203</t>
   </si>
   <si>
     <t xml:space="preserve">4.01576662063599</t>
@@ -1832,37 +1832,37 @@
     <t xml:space="preserve">3.95776081085205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79266858100891</t>
+    <t xml:space="preserve">3.79266834259033</t>
   </si>
   <si>
     <t xml:space="preserve">3.74358701705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76143479347229</t>
+    <t xml:space="preserve">3.76143503189087</t>
   </si>
   <si>
     <t xml:space="preserve">3.61419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6811192035675</t>
+    <t xml:space="preserve">3.68111944198608</t>
   </si>
   <si>
     <t xml:space="preserve">3.52048873901367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48479294776917</t>
+    <t xml:space="preserve">3.48479270935059</t>
   </si>
   <si>
     <t xml:space="preserve">3.67219519615173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59634208679199</t>
+    <t xml:space="preserve">3.59634232521057</t>
   </si>
   <si>
     <t xml:space="preserve">3.58741807937622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64096164703369</t>
+    <t xml:space="preserve">3.64096140861511</t>
   </si>
   <si>
     <t xml:space="preserve">3.64988589286804</t>
@@ -1877,16 +1877,16 @@
     <t xml:space="preserve">3.52495074272156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41786360740662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44909739494324</t>
+    <t xml:space="preserve">3.41786336898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44909715652466</t>
   </si>
   <si>
     <t xml:space="preserve">3.4223256111145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47140693664551</t>
+    <t xml:space="preserve">3.47140717506409</t>
   </si>
   <si>
     <t xml:space="preserve">3.50710296630859</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">3.41340160369873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42678761482239</t>
+    <t xml:space="preserve">3.42678737640381</t>
   </si>
   <si>
     <t xml:space="preserve">3.36878204345703</t>
@@ -1904,22 +1904,22 @@
     <t xml:space="preserve">3.34647226333618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31523847579956</t>
+    <t xml:space="preserve">3.31523823738098</t>
   </si>
   <si>
     <t xml:space="preserve">3.32862424850464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36432003974915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39555382728577</t>
+    <t xml:space="preserve">3.36432027816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39555358886719</t>
   </si>
   <si>
     <t xml:space="preserve">3.35539603233337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31077647209167</t>
+    <t xml:space="preserve">3.31077671051025</t>
   </si>
   <si>
     <t xml:space="preserve">3.27954268455505</t>
@@ -1931,43 +1931,43 @@
     <t xml:space="preserve">3.38216781616211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40001559257507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30631446838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28400492668152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33308601379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35093402862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52941274642944</t>
+    <t xml:space="preserve">3.40001583099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30631422996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28400468826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33308625221252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35093426704407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52941250801086</t>
   </si>
   <si>
     <t xml:space="preserve">3.65880942344666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71235322952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81051635742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80605411529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7658965587616</t>
+    <t xml:space="preserve">3.71235299110413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8105161190033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80605459213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76589632034302</t>
   </si>
   <si>
     <t xml:space="preserve">3.6008038520813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55618405342102</t>
+    <t xml:space="preserve">3.5561842918396</t>
   </si>
   <si>
     <t xml:space="preserve">3.4669451713562</t>
@@ -1982,22 +1982,22 @@
     <t xml:space="preserve">3.69004344940186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7078914642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67665719985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73912477493286</t>
+    <t xml:space="preserve">3.70789122581482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6766574382782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73912501335144</t>
   </si>
   <si>
     <t xml:space="preserve">3.68558144569397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66773343086243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69896697998047</t>
+    <t xml:space="preserve">3.66773366928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69896745681763</t>
   </si>
   <si>
     <t xml:space="preserve">3.7212769985199</t>
@@ -2018,10 +2018,10 @@
     <t xml:space="preserve">3.56957030296326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96668481826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73466300964355</t>
+    <t xml:space="preserve">3.96668553352356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73466277122498</t>
   </si>
   <si>
     <t xml:space="preserve">3.69450497627258</t>
@@ -2033,31 +2033,31 @@
     <t xml:space="preserve">3.63203811645508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60526609420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57849431037903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56510806083679</t>
+    <t xml:space="preserve">3.60526585578918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57849454879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56510829925537</t>
   </si>
   <si>
     <t xml:space="preserve">3.93991351127625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06038665771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91314196586609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98899435997009</t>
+    <t xml:space="preserve">4.06038618087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91314172744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98899459838867</t>
   </si>
   <si>
     <t xml:space="preserve">3.98007082939148</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12731599807739</t>
+    <t xml:space="preserve">4.12731552124023</t>
   </si>
   <si>
     <t xml:space="preserve">4.05146217346191</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">4.03361415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92652750015259</t>
+    <t xml:space="preserve">3.92652702331543</t>
   </si>
   <si>
     <t xml:space="preserve">3.90867972373962</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">4.0425386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93545150756836</t>
+    <t xml:space="preserve">3.93545126914978</t>
   </si>
   <si>
     <t xml:space="preserve">3.89083194732666</t>
@@ -2090,16 +2090,16 @@
     <t xml:space="preserve">4.07823419570923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19424438476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00238084793091</t>
+    <t xml:space="preserve">4.19424486160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00238037109375</t>
   </si>
   <si>
     <t xml:space="preserve">4.1763973236084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08715772628784</t>
+    <t xml:space="preserve">4.087158203125</t>
   </si>
   <si>
     <t xml:space="preserve">4.21655464172363</t>
@@ -2117,37 +2117,37 @@
     <t xml:space="preserve">4.58689785003662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64936494827271</t>
+    <t xml:space="preserve">4.64936542510986</t>
   </si>
   <si>
     <t xml:space="preserve">4.7564525604248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78322458267212</t>
+    <t xml:space="preserve">4.78322410583496</t>
   </si>
   <si>
     <t xml:space="preserve">4.68506097793579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83676815032959</t>
+    <t xml:space="preserve">4.83676767349243</t>
   </si>
   <si>
     <t xml:space="preserve">4.81892013549805</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90815925598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00632238388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89923477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85461521148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9795503616333</t>
+    <t xml:space="preserve">4.90815877914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00632286071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89923524856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85461568832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97955083847046</t>
   </si>
   <si>
     <t xml:space="preserve">5.12233304977417</t>
@@ -2156,10 +2156,10 @@
     <t xml:space="preserve">5.04201793670654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8903112411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9527792930603</t>
+    <t xml:space="preserve">4.89031171798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95277881622314</t>
   </si>
   <si>
     <t xml:space="preserve">4.8456916809082</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">4.82784414291382</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80999612808228</t>
+    <t xml:space="preserve">4.80999565124512</t>
   </si>
   <si>
     <t xml:space="preserve">4.94385480880737</t>
@@ -2180,13 +2180,13 @@
     <t xml:space="preserve">5.06878995895386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.997398853302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23834466934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45251846313477</t>
+    <t xml:space="preserve">4.99739837646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23834419250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45251893997192</t>
   </si>
   <si>
     <t xml:space="preserve">5.83624744415283</t>
@@ -2198,13 +2198,13 @@
     <t xml:space="preserve">5.42574691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15802955627441</t>
+    <t xml:space="preserve">5.15802907943726</t>
   </si>
   <si>
     <t xml:space="preserve">4.88138675689697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70290899276733</t>
+    <t xml:space="preserve">4.70290851593018</t>
   </si>
   <si>
     <t xml:space="preserve">4.71183300018311</t>
@@ -2216,82 +2216,82 @@
     <t xml:space="preserve">4.63151741027832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67613697052002</t>
+    <t xml:space="preserve">4.67613649368286</t>
   </si>
   <si>
     <t xml:space="preserve">4.56012630462646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41734313964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14516401290894</t>
+    <t xml:space="preserve">4.41734266281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14516353607178</t>
   </si>
   <si>
     <t xml:space="preserve">4.02022886276245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98453259468079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94883704185486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8015923500061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12783598899841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15906977653503</t>
+    <t xml:space="preserve">3.98453330993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94883728027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80159258842468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12783622741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15906953811646</t>
   </si>
   <si>
     <t xml:space="preserve">3.25277090072632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72625923156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75749325752258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44961738586426</t>
+    <t xml:space="preserve">2.72625946998596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75749278068542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44961762428284</t>
   </si>
   <si>
     <t xml:space="preserve">2.45854163169861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14174222946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99895930290222</t>
+    <t xml:space="preserve">2.14174199104309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99895942211151</t>
   </si>
   <si>
     <t xml:space="preserve">2.10604619979858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2577531337738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34699249267578</t>
+    <t xml:space="preserve">2.25775337219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34699273109436</t>
   </si>
   <si>
     <t xml:space="preserve">2.4228458404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54331851005554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40053606033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48085117340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45407962799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46300339698792</t>
+    <t xml:space="preserve">2.54331874847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40053629875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48085141181946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45407938957214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46300363540649</t>
   </si>
   <si>
     <t xml:space="preserve">2.56116652488708</t>
@@ -2306,19 +2306,19 @@
     <t xml:space="preserve">3.20368933677673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10998773574829</t>
+    <t xml:space="preserve">3.10998797416687</t>
   </si>
   <si>
     <t xml:space="preserve">2.91812372207642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85119414329529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99843883514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93597149848938</t>
+    <t xml:space="preserve">2.85119438171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99843907356262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9359712600708</t>
   </si>
   <si>
     <t xml:space="preserve">2.94489550590515</t>
@@ -2333,16 +2333,16 @@
     <t xml:space="preserve">2.85565638542175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98059129714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00290107727051</t>
+    <t xml:space="preserve">2.98059105873108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00290083885193</t>
   </si>
   <si>
     <t xml:space="preserve">3.13229775428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0118248462677</t>
+    <t xml:space="preserve">3.01182508468628</t>
   </si>
   <si>
     <t xml:space="preserve">2.98862147331238</t>
@@ -2357,22 +2357,22 @@
     <t xml:space="preserve">2.951495885849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87724423408508</t>
+    <t xml:space="preserve">2.8772439956665</t>
   </si>
   <si>
     <t xml:space="preserve">2.88652563095093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85404086112976</t>
+    <t xml:space="preserve">2.85404062271118</t>
   </si>
   <si>
     <t xml:space="preserve">2.7473042011261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71481919288635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96077728271484</t>
+    <t xml:space="preserve">2.71481895446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96077704429626</t>
   </si>
   <si>
     <t xml:space="preserve">2.75658559799194</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">2.78442978858948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83547782897949</t>
+    <t xml:space="preserve">2.83547806739807</t>
   </si>
   <si>
     <t xml:space="preserve">3.08607649803162</t>
@@ -2405,19 +2405,19 @@
     <t xml:space="preserve">3.31347155570984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3505973815918</t>
+    <t xml:space="preserve">3.35059714317322</t>
   </si>
   <si>
     <t xml:space="preserve">3.27634596824646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28098654747009</t>
+    <t xml:space="preserve">3.28098678588867</t>
   </si>
   <si>
     <t xml:space="preserve">3.34595656394958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07215452194214</t>
+    <t xml:space="preserve">3.07215428352356</t>
   </si>
   <si>
     <t xml:space="preserve">3.07679510116577</t>
@@ -2426,13 +2426,13 @@
     <t xml:space="preserve">3.09999847412109</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16032791137695</t>
+    <t xml:space="preserve">3.16032814979553</t>
   </si>
   <si>
     <t xml:space="preserve">3.09535789489746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05359148979187</t>
+    <t xml:space="preserve">3.05359125137329</t>
   </si>
   <si>
     <t xml:space="preserve">3.03502869606018</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">2.99326205253601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85868120193481</t>
+    <t xml:space="preserve">2.85868144035339</t>
   </si>
   <si>
     <t xml:space="preserve">2.83083701133728</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">2.82155561447144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84939980506897</t>
+    <t xml:space="preserve">2.84940004348755</t>
   </si>
   <si>
     <t xml:space="preserve">2.81227421760559</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">2.88188505172729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79371118545532</t>
+    <t xml:space="preserve">2.7937114238739</t>
   </si>
   <si>
     <t xml:space="preserve">2.76122617721558</t>
@@ -2480,13 +2480,13 @@
     <t xml:space="preserve">2.90972924232483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86332225799561</t>
+    <t xml:space="preserve">2.86332201957703</t>
   </si>
   <si>
     <t xml:space="preserve">2.78907084465027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69161581993103</t>
+    <t xml:space="preserve">2.69161558151245</t>
   </si>
   <si>
     <t xml:space="preserve">2.59416055679321</t>
@@ -2507,7 +2507,7 @@
     <t xml:space="preserve">2.16257381439209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13472962379456</t>
+    <t xml:space="preserve">2.13472938537598</t>
   </si>
   <si>
     <t xml:space="preserve">2.24610686302185</t>
@@ -2516,16 +2516,16 @@
     <t xml:space="preserve">2.40389108657837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.589519739151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55703473091125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60808277130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55239415168762</t>
+    <t xml:space="preserve">2.58951997756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55703496932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60808253288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55239391326904</t>
   </si>
   <si>
     <t xml:space="preserve">2.57559776306152</t>
@@ -2540,13 +2540,13 @@
     <t xml:space="preserve">2.40853190422058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35748386383057</t>
+    <t xml:space="preserve">2.35748410224915</t>
   </si>
   <si>
     <t xml:space="preserve">2.54311275482178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45029830932617</t>
+    <t xml:space="preserve">2.45029854774475</t>
   </si>
   <si>
     <t xml:space="preserve">2.41781330108643</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">2.45957970619202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44565773010254</t>
+    <t xml:space="preserve">2.44565749168396</t>
   </si>
   <si>
     <t xml:space="preserve">2.46422052383423</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">2.4317352771759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49670553207397</t>
+    <t xml:space="preserve">2.49670577049255</t>
   </si>
   <si>
     <t xml:space="preserve">2.47814273834229</t>
@@ -2576,28 +2576,28 @@
     <t xml:space="preserve">2.51990914344788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50134634971619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52919054031372</t>
+    <t xml:space="preserve">2.50134611129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52919030189514</t>
   </si>
   <si>
     <t xml:space="preserve">2.56167554855347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56631636619568</t>
+    <t xml:space="preserve">2.5663161277771</t>
   </si>
   <si>
     <t xml:space="preserve">2.3017954826355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29715466499329</t>
+    <t xml:space="preserve">2.29715442657471</t>
   </si>
   <si>
     <t xml:space="preserve">2.29251408576965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27859163284302</t>
+    <t xml:space="preserve">2.2785918712616</t>
   </si>
   <si>
     <t xml:space="preserve">2.23218464851379</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">2.19969964027405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17185521125793</t>
+    <t xml:space="preserve">2.17185544967651</t>
   </si>
   <si>
     <t xml:space="preserve">2.26931023597717</t>
@@ -2618,13 +2618,13 @@
     <t xml:space="preserve">2.24146604537964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22754406929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19505882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12544798851013</t>
+    <t xml:space="preserve">2.22754383087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19505906105042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12544822692871</t>
   </si>
   <si>
     <t xml:space="preserve">2.01407098770142</t>
@@ -2639,13 +2639,13 @@
     <t xml:space="preserve">2.0744001865387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97230458259583</t>
+    <t xml:space="preserve">1.97230446338654</t>
   </si>
   <si>
     <t xml:space="preserve">1.96766364574432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94446015357971</t>
+    <t xml:space="preserve">1.944460272789</t>
   </si>
   <si>
     <t xml:space="preserve">1.87020885944366</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">1.81730461120605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79688537120819</t>
+    <t xml:space="preserve">1.79688549041748</t>
   </si>
   <si>
     <t xml:space="preserve">1.80059802532196</t>
@@ -2669,7 +2669,7 @@
     <t xml:space="preserve">1.88413095474243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03263378143311</t>
+    <t xml:space="preserve">2.03263401985168</t>
   </si>
   <si>
     <t xml:space="preserve">2.50598692893982</t>
@@ -2690,10 +2690,10 @@
     <t xml:space="preserve">2.77978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71945977210999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70553779602051</t>
+    <t xml:space="preserve">2.71946001052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70553755760193</t>
   </si>
   <si>
     <t xml:space="preserve">2.7241005897522</t>
@@ -2705,10 +2705,10 @@
     <t xml:space="preserve">2.64056777954102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68233442306519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76586699485779</t>
+    <t xml:space="preserve">2.68233418464661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76586723327637</t>
   </si>
   <si>
     <t xml:space="preserve">2.58023834228516</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">2.6127233505249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59880137443542</t>
+    <t xml:space="preserve">2.59880113601685</t>
   </si>
   <si>
     <t xml:space="preserve">2.62664556503296</t>
@@ -2738,10 +2738,10 @@
     <t xml:space="preserve">2.39925050735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27395129203796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32963991165161</t>
+    <t xml:space="preserve">2.27395105361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32963967323303</t>
   </si>
   <si>
     <t xml:space="preserve">2.3482027053833</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">2.35284328460693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39460945129395</t>
+    <t xml:space="preserve">2.39460968971252</t>
   </si>
   <si>
     <t xml:space="preserve">2.46886134147644</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">2.64520835876465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70089721679688</t>
+    <t xml:space="preserve">2.7008969783783</t>
   </si>
   <si>
     <t xml:space="preserve">2.71017861366272</t>
@@ -2783,16 +2783,16 @@
     <t xml:space="preserve">2.93757343292236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99790287017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09071707725525</t>
+    <t xml:space="preserve">2.9979031085968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09071731567383</t>
   </si>
   <si>
     <t xml:space="preserve">3.04895091056824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10463929176331</t>
+    <t xml:space="preserve">3.10463953018188</t>
   </si>
   <si>
     <t xml:space="preserve">3.11392092704773</t>
@@ -2801,19 +2801,19 @@
     <t xml:space="preserve">3.2392201423645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24386096000671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2160165309906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25314235687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29026794433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29954934120178</t>
+    <t xml:space="preserve">3.24386072158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21601629257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25314259529114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29026818275452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29954957962036</t>
   </si>
   <si>
     <t xml:space="preserve">3.31811237335205</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">3.61975908279419</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49910020828247</t>
+    <t xml:space="preserve">3.49910044670105</t>
   </si>
   <si>
     <t xml:space="preserve">3.62904047966003</t>
@@ -2843,19 +2843,19 @@
     <t xml:space="preserve">3.41092658042908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34131598472595</t>
+    <t xml:space="preserve">3.34131574630737</t>
   </si>
   <si>
     <t xml:space="preserve">3.3273937702179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44805240631104</t>
+    <t xml:space="preserve">3.44805216789246</t>
   </si>
   <si>
     <t xml:space="preserve">3.38772320747375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41556763648987</t>
+    <t xml:space="preserve">3.41556739807129</t>
   </si>
   <si>
     <t xml:space="preserve">3.29490876197815</t>
@@ -2870,19 +2870,19 @@
     <t xml:space="preserve">3.13248372077942</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17889094352722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18353152275085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2856273651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37380075454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43413043022156</t>
+    <t xml:space="preserve">3.17889070510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18353176116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28562712669373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3738009929657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43413019180298</t>
   </si>
   <si>
     <t xml:space="preserve">3.47589659690857</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">3.50838160514832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63368082046509</t>
+    <t xml:space="preserve">3.63368105888367</t>
   </si>
   <si>
     <t xml:space="preserve">3.60583686828613</t>
@@ -2903,28 +2903,28 @@
     <t xml:space="preserve">3.54550743103027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69865083694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55478882789612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53622579574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44341158866882</t>
+    <t xml:space="preserve">3.69865107536316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55478858947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53622603416443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4434118270874</t>
   </si>
   <si>
     <t xml:space="preserve">3.52230405807495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54086685180664</t>
+    <t xml:space="preserve">3.54086661338806</t>
   </si>
   <si>
     <t xml:space="preserve">3.46197438240051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47125577926636</t>
+    <t xml:space="preserve">3.47125601768494</t>
   </si>
   <si>
     <t xml:space="preserve">3.50374102592468</t>
@@ -2936,16 +2936,16 @@
     <t xml:space="preserve">3.22993874549866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26706433296204</t>
+    <t xml:space="preserve">3.26706457138062</t>
   </si>
   <si>
     <t xml:space="preserve">3.33203434944153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39236378669739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37844181060791</t>
+    <t xml:space="preserve">3.39236354827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37844157218933</t>
   </si>
   <si>
     <t xml:space="preserve">3.30883097648621</t>
@@ -2966,13 +2966,13 @@
     <t xml:space="preserve">3.05823230743408</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13712430000305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11856126785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9654176235199</t>
+    <t xml:space="preserve">3.13712453842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11856150627136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96541786193848</t>
   </si>
   <si>
     <t xml:space="preserve">3.30419015884399</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">3.17425012588501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12784266471863</t>
+    <t xml:space="preserve">3.12784290313721</t>
   </si>
   <si>
     <t xml:space="preserve">3.19745373725891</t>
@@ -3002,16 +3002,16 @@
     <t xml:space="preserve">3.36451935768127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45269298553467</t>
+    <t xml:space="preserve">3.45269322395325</t>
   </si>
   <si>
     <t xml:space="preserve">3.42020797729492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42484903335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32275295257568</t>
+    <t xml:space="preserve">3.42484879493713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32275319099426</t>
   </si>
   <si>
     <t xml:space="preserve">3.33667516708374</t>
@@ -3020,13 +3020,13 @@
     <t xml:space="preserve">3.38308238983154</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36916041374207</t>
+    <t xml:space="preserve">3.36916017532349</t>
   </si>
   <si>
     <t xml:space="preserve">3.16496872901917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01646590232849</t>
+    <t xml:space="preserve">3.01646566390991</t>
   </si>
   <si>
     <t xml:space="preserve">3.1696093082428</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">3.06751370429993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02110648155212</t>
+    <t xml:space="preserve">3.0211067199707</t>
   </si>
   <si>
     <t xml:space="preserve">3.15568733215332</t>
@@ -3044,10 +3044,10 @@
     <t xml:space="preserve">3.14176511764526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12320232391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03966951370239</t>
+    <t xml:space="preserve">3.123202085495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03966927528381</t>
   </si>
   <si>
     <t xml:space="preserve">3.14640593528748</t>
@@ -3062,10 +3062,10 @@
     <t xml:space="preserve">2.58487915992737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7705078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86796283721924</t>
+    <t xml:space="preserve">2.77050757408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86796259880066</t>
   </si>
   <si>
     <t xml:space="preserve">2.94685482978821</t>
@@ -3074,7 +3074,7 @@
     <t xml:space="preserve">2.98398065567017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02574729919434</t>
+    <t xml:space="preserve">3.02574706077576</t>
   </si>
   <si>
     <t xml:space="preserve">2.97934007644653</t>
@@ -3083,16 +3083,16 @@
     <t xml:space="preserve">2.80299282073975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84475946426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92829203605652</t>
+    <t xml:space="preserve">2.84475922584534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9282922744751</t>
   </si>
   <si>
     <t xml:space="preserve">2.87260365486145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89116644859314</t>
+    <t xml:space="preserve">2.89116621017456</t>
   </si>
   <si>
     <t xml:space="preserve">3.03038787841797</t>
@@ -3101,16 +3101,16 @@
     <t xml:space="preserve">2.8169150352478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68697476387024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69625616073608</t>
+    <t xml:space="preserve">2.68697500228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69625639915466</t>
   </si>
   <si>
     <t xml:space="preserve">2.62200474739075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79835224151611</t>
+    <t xml:space="preserve">2.79835200309753</t>
   </si>
   <si>
     <t xml:space="preserve">2.91901063919067</t>
@@ -3122,7 +3122,7 @@
     <t xml:space="preserve">2.9050886631012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95613622665405</t>
+    <t xml:space="preserve">2.95613646507263</t>
   </si>
   <si>
     <t xml:space="preserve">2.80763363838196</t>
@@ -3140,31 +3140,31 @@
     <t xml:space="preserve">2.74266338348389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63128614425659</t>
+    <t xml:space="preserve">2.63128638267517</t>
   </si>
   <si>
     <t xml:space="preserve">2.49206471443176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53847193717957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54775309562683</t>
+    <t xml:space="preserve">2.53847169876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54775333404541</t>
   </si>
   <si>
     <t xml:space="preserve">2.48742413520813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44101691246033</t>
+    <t xml:space="preserve">2.44101715087891</t>
   </si>
   <si>
     <t xml:space="preserve">2.47350192070007</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43637633323669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38996911048889</t>
+    <t xml:space="preserve">2.43637609481812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38996887207031</t>
   </si>
   <si>
     <t xml:space="preserve">2.3249990940094</t>
@@ -3176,19 +3176,19 @@
     <t xml:space="preserve">2.31107687950134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28323268890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28787302970886</t>
+    <t xml:space="preserve">2.28323245048523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28787326812744</t>
   </si>
   <si>
     <t xml:space="preserve">2.26002883911133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33428049087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33892130851746</t>
+    <t xml:space="preserve">2.33428072929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33892107009888</t>
   </si>
   <si>
     <t xml:space="preserve">2.30643606185913</t>
@@ -3218,13 +3218,13 @@
     <t xml:space="preserve">2.18113660812378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22290301322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18577742576599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11616659164429</t>
+    <t xml:space="preserve">2.22290325164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18577766418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11616683006287</t>
   </si>
   <si>
     <t xml:space="preserve">2.0976037979126</t>
@@ -3242,22 +3242,22 @@
     <t xml:space="preserve">2.04191517829895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02335238456726</t>
+    <t xml:space="preserve">2.02335262298584</t>
   </si>
   <si>
     <t xml:space="preserve">2.00014877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98158597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97694528102875</t>
+    <t xml:space="preserve">1.98158586025238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97694540023804</t>
   </si>
   <si>
     <t xml:space="preserve">1.99086737632751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99550831317902</t>
+    <t xml:space="preserve">1.99550807476044</t>
   </si>
   <si>
     <t xml:space="preserve">2.00478959083557</t>
@@ -3272,10 +3272,10 @@
     <t xml:space="preserve">2.05119657516479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0094301700592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02799320220947</t>
+    <t xml:space="preserve">2.00943040847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02799296379089</t>
   </si>
   <si>
     <t xml:space="preserve">1.95838224887848</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">1.93981945514679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91197514533997</t>
+    <t xml:space="preserve">1.91197526454926</t>
   </si>
   <si>
     <t xml:space="preserve">1.90269374847412</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">1.75419080257416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73562788963318</t>
+    <t xml:space="preserve">1.73562800884247</t>
   </si>
   <si>
     <t xml:space="preserve">1.82472968101501</t>
@@ -3314,16 +3314,16 @@
     <t xml:space="preserve">1.80431056022644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77646636962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79317283630371</t>
+    <t xml:space="preserve">1.77646625041962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.793172955513</t>
   </si>
   <si>
     <t xml:space="preserve">1.7950291633606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76904106140137</t>
+    <t xml:space="preserve">1.76904118061066</t>
   </si>
   <si>
     <t xml:space="preserve">1.75047838687897</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">1.81916093826294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287347316742</t>
+    <t xml:space="preserve">1.82287335395813</t>
   </si>
   <si>
     <t xml:space="preserve">2.01871156692505</t>
@@ -3368,22 +3368,22 @@
     <t xml:space="preserve">2.37604665756226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3853280544281</t>
+    <t xml:space="preserve">2.38532829284668</t>
   </si>
   <si>
     <t xml:space="preserve">2.3714063167572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60344195365906</t>
+    <t xml:space="preserve">2.60344219207764</t>
   </si>
   <si>
     <t xml:space="preserve">3.56407022476196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64296221733093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5779926776886</t>
+    <t xml:space="preserve">3.64296245574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57799243927002</t>
   </si>
   <si>
     <t xml:space="preserve">3.55942964553833</t>
@@ -3392,19 +3392,19 @@
     <t xml:space="preserve">3.82859110832214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90748310089111</t>
+    <t xml:space="preserve">3.90748333930969</t>
   </si>
   <si>
     <t xml:space="preserve">4.00029754638672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81466889381409</t>
+    <t xml:space="preserve">3.81466913223267</t>
   </si>
   <si>
     <t xml:space="preserve">3.48517823219299</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42948937416077</t>
+    <t xml:space="preserve">3.42948961257935</t>
   </si>
   <si>
     <t xml:space="preserve">3.45733380317688</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">3.35987877845764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58727407455444</t>
+    <t xml:space="preserve">3.58727383613586</t>
   </si>
   <si>
     <t xml:space="preserve">3.52694439888</t>
@@ -4239,6 +4239,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.53999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57000017166138</t>
   </si>
 </sst>
 </file>
@@ -70513,7 +70516,7 @@
     </row>
     <row r="2537">
       <c r="A2537" s="1" t="n">
-        <v>46010.6912847222</v>
+        <v>46010.3333333333</v>
       </c>
       <c r="B2537" t="n">
         <v>101171</v>
@@ -70534,6 +70537,32 @@
         <v>1408</v>
       </c>
       <c r="H2537" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2538">
+      <c r="A2538" s="1" t="n">
+        <v>46013.6912962963</v>
+      </c>
+      <c r="B2538" t="n">
+        <v>112208</v>
+      </c>
+      <c r="C2538" t="n">
+        <v>7.61999988555908</v>
+      </c>
+      <c r="D2538" t="n">
+        <v>7.44999980926514</v>
+      </c>
+      <c r="E2538" t="n">
+        <v>7.53999996185303</v>
+      </c>
+      <c r="F2538" t="n">
+        <v>7.57000017166138</v>
+      </c>
+      <c r="G2538" t="s">
+        <v>1409</v>
+      </c>
+      <c r="H2538" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -38,52 +38,52 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95473074913025</t>
+    <t xml:space="preserve">1.95473062992096</t>
   </si>
   <si>
     <t xml:space="preserve">FM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95993411540985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9096348285675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85586702823639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86453914642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68415582180023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76914405822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74486184120178</t>
+    <t xml:space="preserve">1.95993399620056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90963470935822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8558669090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86453902721405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68415570259094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76914393901825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74486172199249</t>
   </si>
   <si>
     <t xml:space="preserve">1.69542992115021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61824655532837</t>
+    <t xml:space="preserve">1.61824667453766</t>
   </si>
   <si>
     <t xml:space="preserve">1.52285158634186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47949004173279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34420263767242</t>
+    <t xml:space="preserve">1.47949016094208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34420251846313</t>
   </si>
   <si>
     <t xml:space="preserve">1.45434057712555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55233716964722</t>
+    <t xml:space="preserve">1.55233728885651</t>
   </si>
   <si>
     <t xml:space="preserve">1.48989689350128</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">1.595698595047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51331210136414</t>
+    <t xml:space="preserve">1.51331198215485</t>
   </si>
   <si>
     <t xml:space="preserve">1.53325819969177</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">1.38582956790924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28349685668945</t>
+    <t xml:space="preserve">1.28349673748016</t>
   </si>
   <si>
     <t xml:space="preserve">1.17682766914368</t>
@@ -122,22 +122,22 @@
     <t xml:space="preserve">1.24186980724335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20718061923981</t>
+    <t xml:space="preserve">1.2071807384491</t>
   </si>
   <si>
     <t xml:space="preserve">1.23059582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43873059749603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39710354804993</t>
+    <t xml:space="preserve">1.43873047828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39710342884064</t>
   </si>
   <si>
     <t xml:space="preserve">1.50030362606049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48295915126801</t>
+    <t xml:space="preserve">1.48295903205872</t>
   </si>
   <si>
     <t xml:space="preserve">1.46561455726624</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">1.5211169719696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51678073406219</t>
+    <t xml:space="preserve">1.51678085327148</t>
   </si>
   <si>
     <t xml:space="preserve">1.4942330121994</t>
@@ -158,10 +158,10 @@
     <t xml:space="preserve">1.47515392303467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5098432302475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56014239788055</t>
+    <t xml:space="preserve">1.50984311103821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56014227867126</t>
   </si>
   <si>
     <t xml:space="preserve">1.58702635765076</t>
@@ -170,13 +170,13 @@
     <t xml:space="preserve">1.55754065513611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52805495262146</t>
+    <t xml:space="preserve">1.52805483341217</t>
   </si>
   <si>
     <t xml:space="preserve">1.54279780387878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51244473457336</t>
+    <t xml:space="preserve">1.51244461536407</t>
   </si>
   <si>
     <t xml:space="preserve">1.55147004127502</t>
@@ -185,13 +185,13 @@
     <t xml:space="preserve">1.61651206016541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67374908924103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70843827724457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67808520793915</t>
+    <t xml:space="preserve">1.67374897003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70843815803528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67808532714844</t>
   </si>
   <si>
     <t xml:space="preserve">1.65467011928558</t>
@@ -200,19 +200,19 @@
     <t xml:space="preserve">1.63298940658569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60610520839691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53499269485474</t>
+    <t xml:space="preserve">1.6061053276062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53499257564545</t>
   </si>
   <si>
     <t xml:space="preserve">1.49770188331604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49683463573456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48122441768646</t>
+    <t xml:space="preserve">1.49683475494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48122453689575</t>
   </si>
   <si>
     <t xml:space="preserve">1.41791701316833</t>
@@ -224,22 +224,22 @@
     <t xml:space="preserve">1.35200774669647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39190006256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46041107177734</t>
+    <t xml:space="preserve">1.39190018177032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46041119098663</t>
   </si>
   <si>
     <t xml:space="preserve">1.57228350639343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62952053546906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60437095165253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60870707035065</t>
+    <t xml:space="preserve">1.62952041625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60437083244324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60870718955994</t>
   </si>
   <si>
     <t xml:space="preserve">1.62518441677094</t>
@@ -248,31 +248,31 @@
     <t xml:space="preserve">1.65987348556519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58615899085999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55407178401947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60090184211731</t>
+    <t xml:space="preserve">1.58615911006927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55407166481018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6009019613266</t>
   </si>
   <si>
     <t xml:space="preserve">1.58876085281372</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49249863624573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4578093290329</t>
+    <t xml:space="preserve">1.49249839782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45780944824219</t>
   </si>
   <si>
     <t xml:space="preserve">1.47775566577911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47428691387177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46908342838287</t>
+    <t xml:space="preserve">1.47428679466248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46908330917358</t>
   </si>
   <si>
     <t xml:space="preserve">1.56794726848602</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">1.53932881355286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53065645694733</t>
+    <t xml:space="preserve">1.53065657615662</t>
   </si>
   <si>
     <t xml:space="preserve">1.54106318950653</t>
@@ -290,46 +290,46 @@
     <t xml:space="preserve">1.56968176364899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54713380336761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55060267448425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56708025932312</t>
+    <t xml:space="preserve">1.5471339225769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55060279369354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56708014011383</t>
   </si>
   <si>
     <t xml:space="preserve">1.5740180015564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51071012020111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59136235713959</t>
+    <t xml:space="preserve">1.5107102394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59136259555817</t>
   </si>
   <si>
     <t xml:space="preserve">1.56100940704346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54453229904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45000433921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38929855823517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40057229995728</t>
+    <t xml:space="preserve">1.54453217983246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45000445842743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38929843902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40057253837585</t>
   </si>
   <si>
     <t xml:space="preserve">1.3875640630722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44740283489227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49163138866425</t>
+    <t xml:space="preserve">1.44740271568298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49163126945496</t>
   </si>
   <si>
     <t xml:space="preserve">1.4838262796402</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">1.32338917255402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32945966720581</t>
+    <t xml:space="preserve">1.3294597864151</t>
   </si>
   <si>
     <t xml:space="preserve">1.3884311914444</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">1.35981273651123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33726501464844</t>
+    <t xml:space="preserve">1.33726489543915</t>
   </si>
   <si>
     <t xml:space="preserve">1.31124794483185</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">1.30257570743561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3615471124649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37802445888519</t>
+    <t xml:space="preserve">1.36154723167419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37802457809448</t>
   </si>
   <si>
     <t xml:space="preserve">1.38236057758331</t>
@@ -377,19 +377,19 @@
     <t xml:space="preserve">1.377157330513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4049084186554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39450180530548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40404140949249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39363467693329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42225301265717</t>
+    <t xml:space="preserve">1.40490853786469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39450192451477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4040412902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.393634557724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42225313186646</t>
   </si>
   <si>
     <t xml:space="preserve">1.42832362651825</t>
@@ -404,16 +404,16 @@
     <t xml:space="preserve">1.36588335037231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3563437461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35460937023163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34333550930023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33119416236877</t>
+    <t xml:space="preserve">1.35634386539459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35460948944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34333539009094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33119428157806</t>
   </si>
   <si>
     <t xml:space="preserve">1.32685804367065</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">1.30170857906342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30777907371521</t>
+    <t xml:space="preserve">1.30777895450592</t>
   </si>
   <si>
     <t xml:space="preserve">1.34767150878906</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">1.33379590511322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37108659744263</t>
+    <t xml:space="preserve">1.37108671665192</t>
   </si>
   <si>
     <t xml:space="preserve">1.35547661781311</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">1.34940600395203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33813190460205</t>
+    <t xml:space="preserve">1.33813214302063</t>
   </si>
   <si>
     <t xml:space="preserve">1.34853875637054</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">1.41704976558685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40317416191101</t>
+    <t xml:space="preserve">1.40317404270172</t>
   </si>
   <si>
     <t xml:space="preserve">1.39536905288696</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">1.41097915172577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36501598358154</t>
+    <t xml:space="preserve">1.36501610279083</t>
   </si>
   <si>
     <t xml:space="preserve">1.38322782516479</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">1.36761772632599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38149356842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39797067642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37455558776855</t>
+    <t xml:space="preserve">1.38149344921112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39797079563141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37455570697784</t>
   </si>
   <si>
     <t xml:space="preserve">1.41358077526093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42138588428497</t>
+    <t xml:space="preserve">1.42138600349426</t>
   </si>
   <si>
     <t xml:space="preserve">1.41271352767944</t>
@@ -491,19 +491,19 @@
     <t xml:space="preserve">1.40924465656281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42572212219238</t>
+    <t xml:space="preserve">1.42572200298309</t>
   </si>
   <si>
     <t xml:space="preserve">1.35114049911499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35894560813904</t>
+    <t xml:space="preserve">1.35894548892975</t>
   </si>
   <si>
     <t xml:space="preserve">1.34680426120758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36414897441864</t>
+    <t xml:space="preserve">1.36414885520935</t>
   </si>
   <si>
     <t xml:space="preserve">1.36241436004639</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">1.17942941188812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26181614398956</t>
+    <t xml:space="preserve">1.26181602478027</t>
   </si>
   <si>
     <t xml:space="preserve">1.29216909408569</t>
@@ -536,16 +536,16 @@
     <t xml:space="preserve">1.23146307468414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21758759021759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24880766868591</t>
+    <t xml:space="preserve">1.2175874710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2488077878952</t>
   </si>
   <si>
     <t xml:space="preserve">1.2288613319397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18550002574921</t>
+    <t xml:space="preserve">1.18549990653992</t>
   </si>
   <si>
     <t xml:space="preserve">1.15774881839752</t>
@@ -554,28 +554,28 @@
     <t xml:space="preserve">1.11872339248657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13086462020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12305951118469</t>
+    <t xml:space="preserve">1.13086473941803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12305963039398</t>
   </si>
   <si>
     <t xml:space="preserve">1.13346636295319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11438727378845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11612176895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11525464057922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09791016578674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09270679950714</t>
+    <t xml:space="preserve">1.11438739299774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11612164974213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11525452136993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09791004657745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09270656108856</t>
   </si>
   <si>
     <t xml:space="preserve">1.07536208629608</t>
@@ -584,52 +584,52 @@
     <t xml:space="preserve">1.07276034355164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10398054122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1542797088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16295206546783</t>
+    <t xml:space="preserve">1.10398066043854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15427982807159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16295218467712</t>
   </si>
   <si>
     <t xml:space="preserve">1.16208481788635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17856216430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18289828300476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20544612407684</t>
+    <t xml:space="preserve">1.17856204509735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18289840221405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20544624328613</t>
   </si>
   <si>
     <t xml:space="preserve">1.23493194580078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2453385591507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21845471858978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19937562942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20111000537872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22799408435822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22192358970642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23666632175446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26875388622284</t>
+    <t xml:space="preserve">1.24533867835999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21845459938049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19937574863434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20111012458801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2279942035675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22192347049713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23666644096375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26875400543213</t>
   </si>
   <si>
     <t xml:space="preserve">1.38409507274628</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">1.34593713283539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33292865753174</t>
+    <t xml:space="preserve">1.33292853832245</t>
   </si>
   <si>
     <t xml:space="preserve">1.28870010375977</t>
@@ -668,19 +668,19 @@
     <t xml:space="preserve">1.25661265850067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2236579656601</t>
+    <t xml:space="preserve">1.22365808486938</t>
   </si>
   <si>
     <t xml:space="preserve">1.2227908372879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25314390659332</t>
+    <t xml:space="preserve">1.25314378738403</t>
   </si>
   <si>
     <t xml:space="preserve">1.22625982761383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21325135231018</t>
+    <t xml:space="preserve">1.21325123310089</t>
   </si>
   <si>
     <t xml:space="preserve">1.20891523361206</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">1.20457899570465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21585285663605</t>
+    <t xml:space="preserve">1.21585297584534</t>
   </si>
   <si>
     <t xml:space="preserve">1.21672022342682</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">1.191570520401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20284461975098</t>
+    <t xml:space="preserve">1.20284450054169</t>
   </si>
   <si>
     <t xml:space="preserve">1.19243776798248</t>
@@ -716,19 +716,19 @@
     <t xml:space="preserve">1.2340646982193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27742624282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27222263813019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29823958873749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26355051994324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24273693561554</t>
+    <t xml:space="preserve">1.27742612361908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27222275733948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2982394695282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26355040073395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24273705482483</t>
   </si>
   <si>
     <t xml:space="preserve">1.23579919338226</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">1.22018897533417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24794054031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24967467784882</t>
+    <t xml:space="preserve">1.24794042110443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2496749162674</t>
   </si>
   <si>
     <t xml:space="preserve">1.29043447971344</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">1.31818580627441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30691194534302</t>
+    <t xml:space="preserve">1.30691170692444</t>
   </si>
   <si>
     <t xml:space="preserve">1.27309000492096</t>
@@ -761,25 +761,25 @@
     <t xml:space="preserve">1.24013531208038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27916049957275</t>
+    <t xml:space="preserve">1.27916061878204</t>
   </si>
   <si>
     <t xml:space="preserve">1.2704883813858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26528489589691</t>
+    <t xml:space="preserve">1.2652850151062</t>
   </si>
   <si>
     <t xml:space="preserve">1.28436386585236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27482450008392</t>
+    <t xml:space="preserve">1.27482438087463</t>
   </si>
   <si>
     <t xml:space="preserve">1.26441752910614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28523111343384</t>
+    <t xml:space="preserve">1.28523123264313</t>
   </si>
   <si>
     <t xml:space="preserve">1.2869656085968</t>
@@ -791,28 +791,28 @@
     <t xml:space="preserve">1.33899927139282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41184651851654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57835412025452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51851546764374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54019606113434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49856925010681</t>
+    <t xml:space="preserve">1.41184639930725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57835400104523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51851534843445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54019618034363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49856913089752</t>
   </si>
   <si>
     <t xml:space="preserve">1.50724148750305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50203788280487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47862303256989</t>
+    <t xml:space="preserve">1.50203800201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4786229133606</t>
   </si>
   <si>
     <t xml:space="preserve">1.43352711200714</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">1.40577578544617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38496232032776</t>
+    <t xml:space="preserve">1.38496220111847</t>
   </si>
   <si>
     <t xml:space="preserve">1.47168505191803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48729515075684</t>
+    <t xml:space="preserve">1.48729526996613</t>
   </si>
   <si>
     <t xml:space="preserve">1.47602117061615</t>
@@ -836,16 +836,16 @@
     <t xml:space="preserve">1.45694220066071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46821618080139</t>
+    <t xml:space="preserve">1.4682160615921</t>
   </si>
   <si>
     <t xml:space="preserve">1.45867669582367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45954394340515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45607507228851</t>
+    <t xml:space="preserve">1.45954382419586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45607495307922</t>
   </si>
   <si>
     <t xml:space="preserve">1.49076402187347</t>
@@ -857,13 +857,13 @@
     <t xml:space="preserve">1.52892208099365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50637412071228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57488524913788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58269011974335</t>
+    <t xml:space="preserve">1.50637423992157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57488512992859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58269035816193</t>
   </si>
   <si>
     <t xml:space="preserve">1.56187665462494</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">1.53585994243622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48642790317535</t>
+    <t xml:space="preserve">1.48642802238464</t>
   </si>
   <si>
     <t xml:space="preserve">1.49510014057159</t>
@@ -881,25 +881,25 @@
     <t xml:space="preserve">1.51157748699188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4890296459198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48035728931427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48816239833832</t>
+    <t xml:space="preserve">1.48902952671051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48035740852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48816251754761</t>
   </si>
   <si>
     <t xml:space="preserve">1.51591360569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5688145160675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57054889202118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64686512947083</t>
+    <t xml:space="preserve">1.56881463527679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57054901123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64686501026154</t>
   </si>
   <si>
     <t xml:space="preserve">1.78648865222931</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">1.84199130535126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15245890617371</t>
+    <t xml:space="preserve">2.15245866775513</t>
   </si>
   <si>
     <t xml:space="preserve">1.99982666969299</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.05186033248901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01543641090393</t>
+    <t xml:space="preserve">2.01543664932251</t>
   </si>
   <si>
     <t xml:space="preserve">1.98074746131897</t>
@@ -944,31 +944,31 @@
     <t xml:space="preserve">1.90443181991577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90790045261383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91657304763794</t>
+    <t xml:space="preserve">1.90790033340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91657269001007</t>
   </si>
   <si>
     <t xml:space="preserve">1.90616583824158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84892892837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87321150302887</t>
+    <t xml:space="preserve">1.84892904758453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87321138381958</t>
   </si>
   <si>
     <t xml:space="preserve">1.83158445358276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84719455242157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93218290805817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93738603591919</t>
+    <t xml:space="preserve">1.84719467163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93218278884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93738639354706</t>
   </si>
   <si>
     <t xml:space="preserve">1.9252450466156</t>
@@ -977,16 +977,16 @@
     <t xml:space="preserve">1.94258964061737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97727859020233</t>
+    <t xml:space="preserve">1.97727870941162</t>
   </si>
   <si>
     <t xml:space="preserve">2.0206401348114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06920456886292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01196789741516</t>
+    <t xml:space="preserve">2.06920504570007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01196765899658</t>
   </si>
   <si>
     <t xml:space="preserve">2.03971886634827</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">2.01370215415955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99462330341339</t>
+    <t xml:space="preserve">1.99462294578552</t>
   </si>
   <si>
     <t xml:space="preserve">1.94432425498962</t>
@@ -1004,43 +1004,43 @@
     <t xml:space="preserve">1.90269720554352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82117760181427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91310381889343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72144663333893</t>
+    <t xml:space="preserve">1.82117748260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91310393810272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72144675254822</t>
   </si>
   <si>
     <t xml:space="preserve">1.67114746570587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69976603984833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68762457370758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67895233631134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63992726802826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64773225784302</t>
+    <t xml:space="preserve">1.69976592063904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68762481212616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67895257472992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63992714881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64773213863373</t>
   </si>
   <si>
     <t xml:space="preserve">1.62865328788757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62691867351532</t>
+    <t xml:space="preserve">1.6269189119339</t>
   </si>
   <si>
     <t xml:space="preserve">1.60350358486176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59656584262848</t>
+    <t xml:space="preserve">1.59656572341919</t>
   </si>
   <si>
     <t xml:space="preserve">1.63905990123749</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">1.6485995054245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66507685184479</t>
+    <t xml:space="preserve">1.6650767326355</t>
   </si>
   <si>
     <t xml:space="preserve">1.6910936832428</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">1.68155407905579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68935918807983</t>
+    <t xml:space="preserve">1.68935906887054</t>
   </si>
   <si>
     <t xml:space="preserve">1.67721807956696</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">1.63385665416718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62171530723572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65727162361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71537613868713</t>
+    <t xml:space="preserve">1.62171542644501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65727174282074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71537601947784</t>
   </si>
   <si>
     <t xml:space="preserve">1.66854584217072</t>
@@ -1097,58 +1097,58 @@
     <t xml:space="preserve">1.71711039543152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7067037820816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72578275203705</t>
+    <t xml:space="preserve">1.70670366287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72578263282776</t>
   </si>
   <si>
     <t xml:space="preserve">1.72751712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71190702915192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74312734603882</t>
+    <t xml:space="preserve">1.71190714836121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74312722682953</t>
   </si>
   <si>
     <t xml:space="preserve">1.77781629562378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77348029613495</t>
+    <t xml:space="preserve">1.77348041534424</t>
   </si>
   <si>
     <t xml:space="preserve">1.80383312702179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93391764163971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88188374042511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9555983543396</t>
+    <t xml:space="preserve">1.93391728401184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88188362121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95559811592102</t>
   </si>
   <si>
     <t xml:space="preserve">1.88621973991394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81684160232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89489221572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80816948413849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8298499584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85153079032898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78215253353119</t>
+    <t xml:space="preserve">1.81684172153473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89489197731018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8081693649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82984983921051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85153067111969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78215265274048</t>
   </si>
   <si>
     <t xml:space="preserve">1.81250536441803</t>
@@ -1160,94 +1160,94 @@
     <t xml:space="preserve">1.73445498943329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76480805873871</t>
+    <t xml:space="preserve">1.764808177948</t>
   </si>
   <si>
     <t xml:space="preserve">1.96860635280609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89922845363617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89055597782135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8775475025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83418619632721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84285831451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82551383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83852219581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86020290851593</t>
+    <t xml:space="preserve">1.89922833442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89055609703064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87754774093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8341863155365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84285843372345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82551395893097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83852207660675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86020302772522</t>
   </si>
   <si>
     <t xml:space="preserve">1.9729425907135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98161482810974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92958116531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98595082759857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04665684700012</t>
+    <t xml:space="preserve">1.98161494731903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92958092689514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98595106601715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04665660858154</t>
   </si>
   <si>
     <t xml:space="preserve">2.03364849090576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.042320728302</t>
+    <t xml:space="preserve">2.04232096672058</t>
   </si>
   <si>
     <t xml:space="preserve">2.072674036026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08134627342224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11169862747192</t>
+    <t xml:space="preserve">2.08134579658508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1116988658905</t>
   </si>
   <si>
     <t xml:space="preserve">2.15072417259216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05532908439636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18541359901428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33717823028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30248880386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2808084487915</t>
+    <t xml:space="preserve">2.05532932281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18541312217712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33717799186707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3024890422821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28080868721008</t>
   </si>
   <si>
     <t xml:space="preserve">2.21143007278442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30682492256165</t>
+    <t xml:space="preserve">2.30682516098022</t>
   </si>
   <si>
     <t xml:space="preserve">2.28514432907104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44991779327393</t>
+    <t xml:space="preserve">2.44991755485535</t>
   </si>
   <si>
     <t xml:space="preserve">2.48894286155701</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">2.38921189308167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49761533737183</t>
+    <t xml:space="preserve">2.49761557579041</t>
   </si>
   <si>
     <t xml:space="preserve">2.57566571235657</t>
@@ -1289,19 +1289,19 @@
     <t xml:space="preserve">2.87052297592163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92689275741577</t>
+    <t xml:space="preserve">2.92689299583435</t>
   </si>
   <si>
     <t xml:space="preserve">3.10033845901489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23909449577332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25210309028625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21741414070129</t>
+    <t xml:space="preserve">3.23909473419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25210332870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21741437911987</t>
   </si>
   <si>
     <t xml:space="preserve">3.25643944740295</t>
@@ -1310,13 +1310,13 @@
     <t xml:space="preserve">3.36050653457642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20874190330505</t>
+    <t xml:space="preserve">3.20874166488647</t>
   </si>
   <si>
     <t xml:space="preserve">3.36917877197266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26511168479919</t>
+    <t xml:space="preserve">3.26511144638062</t>
   </si>
   <si>
     <t xml:space="preserve">3.22175002098083</t>
@@ -1328,13 +1328,13 @@
     <t xml:space="preserve">3.27811980247498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34749817848206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50793504714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48625469207764</t>
+    <t xml:space="preserve">3.34749794006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50793528556824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48625445365906</t>
   </si>
   <si>
     <t xml:space="preserve">3.55563259124756</t>
@@ -1343,19 +1343,19 @@
     <t xml:space="preserve">3.51227164268494</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62934708595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6640362739563</t>
+    <t xml:space="preserve">3.62934684753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66403603553772</t>
   </si>
   <si>
     <t xml:space="preserve">3.73341417312622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80712842941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90685963630676</t>
+    <t xml:space="preserve">3.80712890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90686011314392</t>
   </si>
   <si>
     <t xml:space="preserve">4.07596921920776</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">4.09764957427979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86783528327942</t>
+    <t xml:space="preserve">3.86783456802368</t>
   </si>
   <si>
     <t xml:space="preserve">4.0412802696228</t>
@@ -1376,19 +1376,19 @@
     <t xml:space="preserve">3.945885181427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97190165519714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71173405647278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9198682308197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07163286209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24941539764404</t>
+    <t xml:space="preserve">3.9719021320343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7117338180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91986799240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07163333892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24941492080688</t>
   </si>
   <si>
     <t xml:space="preserve">4.25375127792358</t>
@@ -1397,40 +1397,40 @@
     <t xml:space="preserve">4.284104347229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62232303619385</t>
+    <t xml:space="preserve">4.62232255935669</t>
   </si>
   <si>
     <t xml:space="preserve">4.57896137237549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74373435974121</t>
+    <t xml:space="preserve">4.74373388290405</t>
   </si>
   <si>
     <t xml:space="preserve">4.75240707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05593633651733</t>
+    <t xml:space="preserve">5.05593585968018</t>
   </si>
   <si>
     <t xml:space="preserve">4.98655796051025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95186853408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87381887435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31879281997681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80444002151489</t>
+    <t xml:space="preserve">4.95186901092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87381839752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31879329681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80444049835205</t>
   </si>
   <si>
     <t xml:space="preserve">4.97788572311401</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01257562637329</t>
+    <t xml:space="preserve">5.01257514953613</t>
   </si>
   <si>
     <t xml:space="preserve">5.03859186172485</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">4.91718006134033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82178449630737</t>
+    <t xml:space="preserve">4.82178497314453</t>
   </si>
   <si>
     <t xml:space="preserve">4.85647392272949</t>
@@ -1448,19 +1448,19 @@
     <t xml:space="preserve">4.89116334915161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83045768737793</t>
+    <t xml:space="preserve">4.83045721054077</t>
   </si>
   <si>
     <t xml:space="preserve">4.76107883453369</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54427194595337</t>
+    <t xml:space="preserve">4.54427146911621</t>
   </si>
   <si>
     <t xml:space="preserve">4.70904541015625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60497760772705</t>
+    <t xml:space="preserve">4.60497808456421</t>
   </si>
   <si>
     <t xml:space="preserve">4.58763360977173</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">4.64833927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61364984512329</t>
+    <t xml:space="preserve">4.61365032196045</t>
   </si>
   <si>
     <t xml:space="preserve">4.53560018539429</t>
@@ -1481,28 +1481,28 @@
     <t xml:space="preserve">4.40551567077637</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18437242507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18870830535889</t>
+    <t xml:space="preserve">4.1843729019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18870878219604</t>
   </si>
   <si>
     <t xml:space="preserve">4.24074220657349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.084641456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92854070663452</t>
+    <t xml:space="preserve">4.08464193344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9285409450531</t>
   </si>
   <si>
     <t xml:space="preserve">3.91553211212158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85916233062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7811119556427</t>
+    <t xml:space="preserve">3.85916185379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78111219406128</t>
   </si>
   <si>
     <t xml:space="preserve">4.14101123809814</t>
@@ -1514,10 +1514,10 @@
     <t xml:space="preserve">3.31280899047852</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28679203987122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14369964599609</t>
+    <t xml:space="preserve">3.28679227828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14369940757751</t>
   </si>
   <si>
     <t xml:space="preserve">3.00927948951721</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">3.03529620170593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04830455780029</t>
+    <t xml:space="preserve">3.04830479621887</t>
   </si>
   <si>
     <t xml:space="preserve">3.07865762710571</t>
@@ -1538,31 +1538,31 @@
     <t xml:space="preserve">2.96158194541931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89653992652893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90521216392517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02662420272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75344753265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80548071861267</t>
+    <t xml:space="preserve">2.89653968811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90521192550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02662396430969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75344729423523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80548095703125</t>
   </si>
   <si>
     <t xml:space="preserve">2.88786768913269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04396867752075</t>
+    <t xml:space="preserve">3.04396843910217</t>
   </si>
   <si>
     <t xml:space="preserve">3.2607753276825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24343061447144</t>
+    <t xml:space="preserve">3.24343085289001</t>
   </si>
   <si>
     <t xml:space="preserve">3.19139719009399</t>
@@ -1571,16 +1571,16 @@
     <t xml:space="preserve">3.42554879188538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43855690956116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39519548416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20440554618835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06998538970947</t>
+    <t xml:space="preserve">3.43855667114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39519572257996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20440578460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06998515129089</t>
   </si>
   <si>
     <t xml:space="preserve">2.86618685722351</t>
@@ -1589,22 +1589,22 @@
     <t xml:space="preserve">2.93990135192871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88353157043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97459030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02228784561157</t>
+    <t xml:space="preserve">2.88353133201599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97459053993225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02228760719299</t>
   </si>
   <si>
     <t xml:space="preserve">3.3821873664856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32148146629333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15670824050903</t>
+    <t xml:space="preserve">3.32148122787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15670800209045</t>
   </si>
   <si>
     <t xml:space="preserve">3.11768293380737</t>
@@ -1613,13 +1613,13 @@
     <t xml:space="preserve">3.08732986450195</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06564927101135</t>
+    <t xml:space="preserve">3.06564950942993</t>
   </si>
   <si>
     <t xml:space="preserve">2.81848931312561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68840527534485</t>
+    <t xml:space="preserve">2.68840503692627</t>
   </si>
   <si>
     <t xml:space="preserve">2.73176670074463</t>
@@ -1634,28 +1634,28 @@
     <t xml:space="preserve">3.17405271530151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3041365146637</t>
+    <t xml:space="preserve">3.30413699150085</t>
   </si>
   <si>
     <t xml:space="preserve">3.3084728717804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17838883399963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10467433929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16104435920715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33015370368958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46023797988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5903217792511</t>
+    <t xml:space="preserve">3.17838859558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10467457771301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16104412078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.330153465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46023774147034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59032154083252</t>
   </si>
   <si>
     <t xml:space="preserve">3.88517928123474</t>
@@ -1664,16 +1664,16 @@
     <t xml:space="preserve">3.90252375602722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85482621192932</t>
+    <t xml:space="preserve">3.85482668876648</t>
   </si>
   <si>
     <t xml:space="preserve">4.11499452590942</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27543115615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10198593139648</t>
+    <t xml:space="preserve">4.27543163299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10198640823364</t>
   </si>
   <si>
     <t xml:space="preserve">4.145348072052</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">4.1323390007019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95889353752136</t>
+    <t xml:space="preserve">3.95889329910278</t>
   </si>
   <si>
     <t xml:space="preserve">3.82447338104248</t>
@@ -1691,16 +1691,16 @@
     <t xml:space="preserve">3.9675657749176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94154858589172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9979190826416</t>
+    <t xml:space="preserve">3.94154906272888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99791932106018</t>
   </si>
   <si>
     <t xml:space="preserve">4.00659132003784</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06296062469482</t>
+    <t xml:space="preserve">4.06296014785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.05862474441528</t>
@@ -1709,25 +1709,25 @@
     <t xml:space="preserve">4.01526355743408</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09331369400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0326075553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98924660682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9242045879364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8288094997406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75943112373352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74642300605774</t>
+    <t xml:space="preserve">4.09331321716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03260803222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98924589157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92420434951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82880973815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75943088531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74642276763916</t>
   </si>
   <si>
     <t xml:space="preserve">3.56864094734192</t>
@@ -1736,7 +1736,7 @@
     <t xml:space="preserve">3.77677583694458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24507904052734</t>
+    <t xml:space="preserve">4.24507856369019</t>
   </si>
   <si>
     <t xml:space="preserve">4.17136430740356</t>
@@ -1748,22 +1748,22 @@
     <t xml:space="preserve">4.06729698181152</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16269254684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21906137466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23206996917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20171737670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68302822113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88249111175537</t>
+    <t xml:space="preserve">4.16269159317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21906185150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2320704460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20171689987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68302869796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88249063491821</t>
   </si>
   <si>
     <t xml:space="preserve">4.76975107192993</t>
@@ -1772,10 +1772,10 @@
     <t xml:space="preserve">4.72638940811157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63966751098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55294466018677</t>
+    <t xml:space="preserve">4.63966703414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55294418334961</t>
   </si>
   <si>
     <t xml:space="preserve">4.44887733459473</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">4.39684343338013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9111967086792</t>
+    <t xml:space="preserve">3.91119623184204</t>
   </si>
   <si>
     <t xml:space="preserve">4.04995250701904</t>
@@ -1799,28 +1799,28 @@
     <t xml:space="preserve">4.01130485534668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91760301589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2254786491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00684213638306</t>
+    <t xml:space="preserve">3.91760349273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22547912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00684261322021</t>
   </si>
   <si>
     <t xml:space="preserve">3.83282613754272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85513615608215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85959768295288</t>
+    <t xml:space="preserve">3.85513591766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85959792137146</t>
   </si>
   <si>
     <t xml:space="preserve">3.93098950386047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83728814125061</t>
+    <t xml:space="preserve">3.83728790283203</t>
   </si>
   <si>
     <t xml:space="preserve">4.01576662063599</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">4.03807640075684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95776104927063</t>
+    <t xml:space="preserve">3.95776081085205</t>
   </si>
   <si>
     <t xml:space="preserve">3.79266834259033</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">3.74358701705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76143479347229</t>
+    <t xml:space="preserve">3.76143503189087</t>
   </si>
   <si>
     <t xml:space="preserve">3.61419010162354</t>
@@ -1850,25 +1850,25 @@
     <t xml:space="preserve">3.52048873901367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48479294776917</t>
+    <t xml:space="preserve">3.48479270935059</t>
   </si>
   <si>
     <t xml:space="preserve">3.67219519615173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59634208679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5874183177948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64096164703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64988565444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51156449317932</t>
+    <t xml:space="preserve">3.59634232521057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58741807937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64096140861511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64988589286804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5115647315979</t>
   </si>
   <si>
     <t xml:space="preserve">3.49817895889282</t>
@@ -1880,13 +1880,13 @@
     <t xml:space="preserve">3.41786336898804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44909739494324</t>
+    <t xml:space="preserve">3.44909715652466</t>
   </si>
   <si>
     <t xml:space="preserve">3.4223256111145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47140693664551</t>
+    <t xml:space="preserve">3.47140717506409</t>
   </si>
   <si>
     <t xml:space="preserve">3.50710296630859</t>
@@ -1898,7 +1898,7 @@
     <t xml:space="preserve">3.42678737640381</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36878228187561</t>
+    <t xml:space="preserve">3.36878204345703</t>
   </si>
   <si>
     <t xml:space="preserve">3.34647226333618</t>
@@ -1907,19 +1907,19 @@
     <t xml:space="preserve">3.31523823738098</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32862448692322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36431980133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39555382728577</t>
+    <t xml:space="preserve">3.32862424850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36432027816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39555358886719</t>
   </si>
   <si>
     <t xml:space="preserve">3.35539603233337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31077647209167</t>
+    <t xml:space="preserve">3.31077671051025</t>
   </si>
   <si>
     <t xml:space="preserve">3.27954268455505</t>
@@ -1931,16 +1931,16 @@
     <t xml:space="preserve">3.38216781616211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40001559257507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30631446838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28400492668152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33308601379395</t>
+    <t xml:space="preserve">3.40001583099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30631422996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28400468826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33308625221252</t>
   </si>
   <si>
     <t xml:space="preserve">3.35093426704407</t>
@@ -1955,13 +1955,13 @@
     <t xml:space="preserve">3.71235299110413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81051635742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80605435371399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7658965587616</t>
+    <t xml:space="preserve">3.8105161190033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80605459213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76589632034302</t>
   </si>
   <si>
     <t xml:space="preserve">3.6008038520813</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">3.62757587432861</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78374433517456</t>
+    <t xml:space="preserve">3.78374409675598</t>
   </si>
   <si>
     <t xml:space="preserve">3.69004344940186</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">3.70789122581482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67665719985962</t>
+    <t xml:space="preserve">3.6766574382782</t>
   </si>
   <si>
     <t xml:space="preserve">3.73912501335144</t>
@@ -1997,10 +1997,10 @@
     <t xml:space="preserve">3.66773366928101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69896721839905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72127747535706</t>
+    <t xml:space="preserve">3.69896745681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7212769985199</t>
   </si>
   <si>
     <t xml:space="preserve">3.72573924064636</t>
@@ -2009,43 +2009,43 @@
     <t xml:space="preserve">3.62311387062073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60972785949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58295631408691</t>
+    <t xml:space="preserve">3.60972809791565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58295607566833</t>
   </si>
   <si>
     <t xml:space="preserve">3.56957030296326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99791860580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96668529510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73466300964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69450521469116</t>
+    <t xml:space="preserve">3.99791884422302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96668553352356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73466277122498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69450497627258</t>
   </si>
   <si>
     <t xml:space="preserve">3.70342922210693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6320378780365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60526609420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57849431037903</t>
+    <t xml:space="preserve">3.63203811645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60526585578918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57849454879761</t>
   </si>
   <si>
     <t xml:space="preserve">3.56510829925537</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93991327285767</t>
+    <t xml:space="preserve">3.93991351127625</t>
   </si>
   <si>
     <t xml:space="preserve">4.06038618087769</t>
@@ -2054,25 +2054,25 @@
     <t xml:space="preserve">3.91314172744751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98899483680725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98007130622864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12731599807739</t>
+    <t xml:space="preserve">3.98899459838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98007082939148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12731552124023</t>
   </si>
   <si>
     <t xml:space="preserve">4.05146217346191</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09161949157715</t>
+    <t xml:space="preserve">4.09161996841431</t>
   </si>
   <si>
     <t xml:space="preserve">4.03361415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92652726173401</t>
+    <t xml:space="preserve">3.92652702331543</t>
   </si>
   <si>
     <t xml:space="preserve">3.90867972373962</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">3.93545126914978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8908314704895</t>
+    <t xml:space="preserve">3.89083194732666</t>
   </si>
   <si>
     <t xml:space="preserve">4.07823419570923</t>
@@ -2096,25 +2096,25 @@
     <t xml:space="preserve">4.19424486160278</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00238084793091</t>
+    <t xml:space="preserve">4.00238037109375</t>
   </si>
   <si>
     <t xml:space="preserve">4.1763973236084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08715772628784</t>
+    <t xml:space="preserve">4.087158203125</t>
   </si>
   <si>
     <t xml:space="preserve">4.21655464172363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46196317672729</t>
+    <t xml:space="preserve">4.46196269989014</t>
   </si>
   <si>
     <t xml:space="preserve">4.53335428237915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64044141769409</t>
+    <t xml:space="preserve">4.64044094085693</t>
   </si>
   <si>
     <t xml:space="preserve">4.58689785003662</t>
@@ -2135,22 +2135,22 @@
     <t xml:space="preserve">4.83676767349243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81891965866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90815925598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00632238388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89923477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85461616516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9795503616333</t>
+    <t xml:space="preserve">4.81892013549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90815877914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00632286071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89923524856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85461568832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97955083847046</t>
   </si>
   <si>
     <t xml:space="preserve">5.12233304977417</t>
@@ -2171,28 +2171,28 @@
     <t xml:space="preserve">4.76537656784058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82784366607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80999612808228</t>
+    <t xml:space="preserve">4.82784414291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80999565124512</t>
   </si>
   <si>
     <t xml:space="preserve">4.94385480880737</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0687894821167</t>
+    <t xml:space="preserve">5.06878995895386</t>
   </si>
   <si>
     <t xml:space="preserve">4.99739837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23834466934204</t>
+    <t xml:space="preserve">5.23834419250488</t>
   </si>
   <si>
     <t xml:space="preserve">5.45251893997192</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83624792098999</t>
+    <t xml:space="preserve">5.83624744415283</t>
   </si>
   <si>
     <t xml:space="preserve">5.67561721801758</t>
@@ -2201,10 +2201,10 @@
     <t xml:space="preserve">5.42574691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15802955627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88138771057129</t>
+    <t xml:space="preserve">5.15802907943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88138675689697</t>
   </si>
   <si>
     <t xml:space="preserve">4.70290851593018</t>
@@ -2213,28 +2213,28 @@
     <t xml:space="preserve">4.71183300018311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7386040687561</t>
+    <t xml:space="preserve">4.73860454559326</t>
   </si>
   <si>
     <t xml:space="preserve">4.63151741027832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67613697052002</t>
+    <t xml:space="preserve">4.67613649368286</t>
   </si>
   <si>
     <t xml:space="preserve">4.56012630462646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41734313964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14516305923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02022838592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98453307151794</t>
+    <t xml:space="preserve">4.41734266281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14516353607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02022886276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98453330993652</t>
   </si>
   <si>
     <t xml:space="preserve">3.94883728027344</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">3.80159258842468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12783598899841</t>
+    <t xml:space="preserve">3.12783622741699</t>
   </si>
   <si>
     <t xml:space="preserve">3.15906953811646</t>
@@ -2255,25 +2255,25 @@
     <t xml:space="preserve">2.72625946998596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.757493019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44961738586426</t>
+    <t xml:space="preserve">2.75749278068542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44961762428284</t>
   </si>
   <si>
     <t xml:space="preserve">2.45854163169861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14174246788025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99895930290222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10604643821716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2577531337738</t>
+    <t xml:space="preserve">2.14174199104309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99895942211151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10604619979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25775337219238</t>
   </si>
   <si>
     <t xml:space="preserve">2.34699273109436</t>
@@ -2288,10 +2288,10 @@
     <t xml:space="preserve">2.40053629875183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48085117340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45407962799072</t>
+    <t xml:space="preserve">2.48085141181946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45407938957214</t>
   </si>
   <si>
     <t xml:space="preserve">2.46300363540649</t>
@@ -2309,10 +2309,10 @@
     <t xml:space="preserve">3.20368933677673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10998821258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.918123960495</t>
+    <t xml:space="preserve">3.10998797416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91812372207642</t>
   </si>
   <si>
     <t xml:space="preserve">2.85119438171387</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">2.99843907356262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93597173690796</t>
+    <t xml:space="preserve">2.9359712600708</t>
   </si>
   <si>
     <t xml:space="preserve">2.94489550590515</t>
@@ -2339,10 +2339,10 @@
     <t xml:space="preserve">2.98059105873108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00290107727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1322979927063</t>
+    <t xml:space="preserve">3.00290083885193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13229775428772</t>
   </si>
   <si>
     <t xml:space="preserve">3.01182508468628</t>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95473062992096</t>
+    <t xml:space="preserve">1.95473086833954</t>
   </si>
   <si>
     <t xml:space="preserve">FM.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">1.95993399620056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9096348285675</t>
+    <t xml:space="preserve">1.90963470935822</t>
   </si>
   <si>
     <t xml:space="preserve">1.8558669090271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86453938484192</t>
+    <t xml:space="preserve">1.86453926563263</t>
   </si>
   <si>
     <t xml:space="preserve">1.68415582180023</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">1.69542980194092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61824667453766</t>
+    <t xml:space="preserve">1.61824655532837</t>
   </si>
   <si>
     <t xml:space="preserve">1.52285146713257</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">1.34420263767242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45434057712555</t>
+    <t xml:space="preserve">1.45434045791626</t>
   </si>
   <si>
     <t xml:space="preserve">1.55233716964722</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">1.48989689350128</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54366493225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.595698595047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51331210136414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53325831890106</t>
+    <t xml:space="preserve">1.54366505146027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59569871425629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51331198215485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53325819969177</t>
   </si>
   <si>
     <t xml:space="preserve">1.499436378479</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">1.43005812168121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40751028060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38582956790924</t>
+    <t xml:space="preserve">1.40751039981842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38582968711853</t>
   </si>
   <si>
     <t xml:space="preserve">1.28349673748016</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">1.17682754993439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24186968803406</t>
+    <t xml:space="preserve">1.24186980724335</t>
   </si>
   <si>
     <t xml:space="preserve">1.20718061923981</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">1.39710342884064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50030362606049</t>
+    <t xml:space="preserve">1.50030374526978</t>
   </si>
   <si>
     <t xml:space="preserve">1.48295903205872</t>
@@ -143,10 +143,10 @@
     <t xml:space="preserve">1.46561455726624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5211169719696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51678085327148</t>
+    <t xml:space="preserve">1.52111685276031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51678097248077</t>
   </si>
   <si>
     <t xml:space="preserve">1.49423289299011</t>
@@ -170,19 +170,19 @@
     <t xml:space="preserve">1.55754053592682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52805471420288</t>
+    <t xml:space="preserve">1.52805483341217</t>
   </si>
   <si>
     <t xml:space="preserve">1.54279780387878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51244461536407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55146992206573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61651194095612</t>
+    <t xml:space="preserve">1.51244473457336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55147004127502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61651206016541</t>
   </si>
   <si>
     <t xml:space="preserve">1.67374897003174</t>
@@ -191,13 +191,13 @@
     <t xml:space="preserve">1.70843815803528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67808520793915</t>
+    <t xml:space="preserve">1.67808508872986</t>
   </si>
   <si>
     <t xml:space="preserve">1.65467000007629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63298940658569</t>
+    <t xml:space="preserve">1.63298952579498</t>
   </si>
   <si>
     <t xml:space="preserve">1.6061053276062</t>
@@ -206,25 +206,25 @@
     <t xml:space="preserve">1.53499269485474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49770188331604</t>
+    <t xml:space="preserve">1.49770176410675</t>
   </si>
   <si>
     <t xml:space="preserve">1.49683463573456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48122453689575</t>
+    <t xml:space="preserve">1.48122441768646</t>
   </si>
   <si>
     <t xml:space="preserve">1.41791689395905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39970505237579</t>
+    <t xml:space="preserve">1.39970517158508</t>
   </si>
   <si>
     <t xml:space="preserve">1.35200774669647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39190006256104</t>
+    <t xml:space="preserve">1.39190018177032</t>
   </si>
   <si>
     <t xml:space="preserve">1.46041119098663</t>
@@ -233,28 +233,28 @@
     <t xml:space="preserve">1.57228338718414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62952053546906</t>
+    <t xml:space="preserve">1.62952041625977</t>
   </si>
   <si>
     <t xml:space="preserve">1.60437095165253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60870695114136</t>
+    <t xml:space="preserve">1.60870707035065</t>
   </si>
   <si>
     <t xml:space="preserve">1.62518441677094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65987348556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58615911006927</t>
+    <t xml:space="preserve">1.65987360477448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58615899085999</t>
   </si>
   <si>
     <t xml:space="preserve">1.55407166481018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60090184211731</t>
+    <t xml:space="preserve">1.6009019613266</t>
   </si>
   <si>
     <t xml:space="preserve">1.58876073360443</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">1.46908330917358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56794726848602</t>
+    <t xml:space="preserve">1.56794738769531</t>
   </si>
   <si>
     <t xml:space="preserve">1.53932881355286</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">1.53065657615662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54106330871582</t>
+    <t xml:space="preserve">1.54106318950653</t>
   </si>
   <si>
     <t xml:space="preserve">1.56968176364899</t>
@@ -296,10 +296,10 @@
     <t xml:space="preserve">1.55060267448425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56708002090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5740180015564</t>
+    <t xml:space="preserve">1.56708014011383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57401788234711</t>
   </si>
   <si>
     <t xml:space="preserve">1.5107102394104</t>
@@ -317,10 +317,10 @@
     <t xml:space="preserve">1.45000445842743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38929855823517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40057241916656</t>
+    <t xml:space="preserve">1.38929843902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40057229995728</t>
   </si>
   <si>
     <t xml:space="preserve">1.3875640630722</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">1.3294597864151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3884311914444</t>
+    <t xml:space="preserve">1.38843107223511</t>
   </si>
   <si>
     <t xml:space="preserve">1.39016568660736</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">1.30257570743561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36154723167419</t>
+    <t xml:space="preserve">1.3615471124649</t>
   </si>
   <si>
     <t xml:space="preserve">1.37802445888519</t>
@@ -371,13 +371,13 @@
     <t xml:space="preserve">1.3823606967926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39623618125916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37715744972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40490865707397</t>
+    <t xml:space="preserve">1.39623630046844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.377157330513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40490853786469</t>
   </si>
   <si>
     <t xml:space="preserve">1.39450180530548</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">1.34333550930023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33119416236877</t>
+    <t xml:space="preserve">1.33119428157806</t>
   </si>
   <si>
     <t xml:space="preserve">1.32685804367065</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">1.30170845985413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30777907371521</t>
+    <t xml:space="preserve">1.3077791929245</t>
   </si>
   <si>
     <t xml:space="preserve">1.34767162799835</t>
@@ -440,16 +440,16 @@
     <t xml:space="preserve">1.35547661781311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34940612316132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33813202381134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34853875637054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41704976558685</t>
+    <t xml:space="preserve">1.34940600395203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33813190460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34853863716125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41704964637756</t>
   </si>
   <si>
     <t xml:space="preserve">1.40317404270172</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">1.41097915172577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36501610279083</t>
+    <t xml:space="preserve">1.36501598358154</t>
   </si>
   <si>
     <t xml:space="preserve">1.38322794437408</t>
@@ -497,13 +497,13 @@
     <t xml:space="preserve">1.35114049911499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35894548892975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34680426120758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36414873600006</t>
+    <t xml:space="preserve">1.35894560813904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34680438041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36414885520935</t>
   </si>
   <si>
     <t xml:space="preserve">1.36241436004639</t>
@@ -512,19 +512,19 @@
     <t xml:space="preserve">1.33032703399658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32078742980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3190530538559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31992018222809</t>
+    <t xml:space="preserve">1.32078754901886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31905317306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31992030143738</t>
   </si>
   <si>
     <t xml:space="preserve">1.31298243999481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17942941188812</t>
+    <t xml:space="preserve">1.17942929267883</t>
   </si>
   <si>
     <t xml:space="preserve">1.26181602478027</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">1.23146307468414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21758759021759</t>
+    <t xml:space="preserve">1.2175874710083</t>
   </si>
   <si>
     <t xml:space="preserve">1.24880766868591</t>
@@ -557,10 +557,10 @@
     <t xml:space="preserve">1.13086473941803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12305963039398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13346636295319</t>
+    <t xml:space="preserve">1.12305974960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13346648216248</t>
   </si>
   <si>
     <t xml:space="preserve">1.11438727378845</t>
@@ -569,7 +569,7 @@
     <t xml:space="preserve">1.11612164974213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11525464057922</t>
+    <t xml:space="preserve">1.11525452136993</t>
   </si>
   <si>
     <t xml:space="preserve">1.09791004657745</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">1.09270668029785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07536220550537</t>
+    <t xml:space="preserve">1.07536208629608</t>
   </si>
   <si>
     <t xml:space="preserve">1.07276034355164</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">1.15427982807159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16295206546783</t>
+    <t xml:space="preserve">1.16295218467712</t>
   </si>
   <si>
     <t xml:space="preserve">1.16208493709564</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">1.17856204509735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18289828300476</t>
+    <t xml:space="preserve">1.18289840221405</t>
   </si>
   <si>
     <t xml:space="preserve">1.20544612407684</t>
@@ -608,13 +608,13 @@
     <t xml:space="preserve">1.23493194580078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24533867835999</t>
+    <t xml:space="preserve">1.2453385591507</t>
   </si>
   <si>
     <t xml:space="preserve">1.21845459938049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19937562942505</t>
+    <t xml:space="preserve">1.19937574863434</t>
   </si>
   <si>
     <t xml:space="preserve">1.20111012458801</t>
@@ -623,22 +623,22 @@
     <t xml:space="preserve">1.2279942035675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22192347049713</t>
+    <t xml:space="preserve">1.22192358970642</t>
   </si>
   <si>
     <t xml:space="preserve">1.23666632175446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26875388622284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38409507274628</t>
+    <t xml:space="preserve">1.26875376701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38409519195557</t>
   </si>
   <si>
     <t xml:space="preserve">1.39883804321289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38669669628143</t>
+    <t xml:space="preserve">1.38669681549072</t>
   </si>
   <si>
     <t xml:space="preserve">1.35721111297607</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">1.33292853832245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28870010375977</t>
+    <t xml:space="preserve">1.28869998455048</t>
   </si>
   <si>
     <t xml:space="preserve">1.25747990608215</t>
@@ -659,16 +659,16 @@
     <t xml:space="preserve">1.23319756984711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2444714307785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22712683677673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25661265850067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22365808486938</t>
+    <t xml:space="preserve">1.24447131156921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22712695598602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25661253929138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2236579656601</t>
   </si>
   <si>
     <t xml:space="preserve">1.2227908372879</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">1.25314378738403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22625970840454</t>
+    <t xml:space="preserve">1.22625982761383</t>
   </si>
   <si>
     <t xml:space="preserve">1.21325135231018</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">1.21585297584534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21672022342682</t>
+    <t xml:space="preserve">1.21672010421753</t>
   </si>
   <si>
     <t xml:space="preserve">1.19070339202881</t>
@@ -704,10 +704,10 @@
     <t xml:space="preserve">1.18810176849365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19157063961029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20284450054169</t>
+    <t xml:space="preserve">1.191570520401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20284461975098</t>
   </si>
   <si>
     <t xml:space="preserve">1.19243776798248</t>
@@ -719,13 +719,13 @@
     <t xml:space="preserve">1.27742612361908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27222275733948</t>
+    <t xml:space="preserve">1.27222263813019</t>
   </si>
   <si>
     <t xml:space="preserve">1.2982394695282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26355040073395</t>
+    <t xml:space="preserve">1.26355051994324</t>
   </si>
   <si>
     <t xml:space="preserve">1.24273693561554</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">1.31818580627441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30691170692444</t>
+    <t xml:space="preserve">1.30691182613373</t>
   </si>
   <si>
     <t xml:space="preserve">1.27309000492096</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">1.24013519287109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27916061878204</t>
+    <t xml:space="preserve">1.27916073799133</t>
   </si>
   <si>
     <t xml:space="preserve">1.27048826217651</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">1.26528489589691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28436398506165</t>
+    <t xml:space="preserve">1.28436386585236</t>
   </si>
   <si>
     <t xml:space="preserve">1.27482438087463</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">1.33899927139282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41184639930725</t>
+    <t xml:space="preserve">1.41184651851654</t>
   </si>
   <si>
     <t xml:space="preserve">1.57835412025452</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">1.51851534843445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54019606113434</t>
+    <t xml:space="preserve">1.54019618034363</t>
   </si>
   <si>
     <t xml:space="preserve">1.49856925010681</t>
@@ -809,10 +809,10 @@
     <t xml:space="preserve">1.50724148750305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50203800201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4786229133606</t>
+    <t xml:space="preserve">1.50203812122345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47862303256989</t>
   </si>
   <si>
     <t xml:space="preserve">1.43352699279785</t>
@@ -848,19 +848,19 @@
     <t xml:space="preserve">1.45607495307922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49076390266418</t>
+    <t xml:space="preserve">1.49076402187347</t>
   </si>
   <si>
     <t xml:space="preserve">1.47341954708099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52892196178436</t>
+    <t xml:space="preserve">1.52892208099365</t>
   </si>
   <si>
     <t xml:space="preserve">1.50637412071228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57488524913788</t>
+    <t xml:space="preserve">1.57488512992859</t>
   </si>
   <si>
     <t xml:space="preserve">1.58269023895264</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">1.48816239833832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51591360569</t>
+    <t xml:space="preserve">1.51591372489929</t>
   </si>
   <si>
     <t xml:space="preserve">1.56881463527679</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">1.7604718208313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85933566093445</t>
+    <t xml:space="preserve">1.85933578014374</t>
   </si>
   <si>
     <t xml:space="preserve">1.8662736415863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84199118614197</t>
+    <t xml:space="preserve">1.84199130535126</t>
   </si>
   <si>
     <t xml:space="preserve">2.15245866775513</t>
@@ -923,10 +923,10 @@
     <t xml:space="preserve">1.99982666969299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05879807472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00329542160034</t>
+    <t xml:space="preserve">2.05879831314087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00329566001892</t>
   </si>
   <si>
     <t xml:space="preserve">1.95126187801361</t>
@@ -938,34 +938,34 @@
     <t xml:space="preserve">2.01543641090393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98074734210968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9044314622879</t>
+    <t xml:space="preserve">1.98074758052826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90443158149719</t>
   </si>
   <si>
     <t xml:space="preserve">1.90790057182312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91657257080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90616607666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84892904758453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87321138381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83158433437347</t>
+    <t xml:space="preserve">1.91657280921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90616595745087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84892892837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87321150302887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83158445358276</t>
   </si>
   <si>
     <t xml:space="preserve">1.84719455242157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93218290805817</t>
+    <t xml:space="preserve">1.93218314647675</t>
   </si>
   <si>
     <t xml:space="preserve">1.93738627433777</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.92524516582489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94258975982666</t>
+    <t xml:space="preserve">1.94258952140808</t>
   </si>
   <si>
     <t xml:space="preserve">1.97727870941162</t>
@@ -983,16 +983,16 @@
     <t xml:space="preserve">2.0206401348114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06920456886292</t>
+    <t xml:space="preserve">2.06920480728149</t>
   </si>
   <si>
     <t xml:space="preserve">2.01196765899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03971910476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01370239257812</t>
+    <t xml:space="preserve">2.03971886634827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01370215415955</t>
   </si>
   <si>
     <t xml:space="preserve">1.99462330341339</t>
@@ -1010,28 +1010,28 @@
     <t xml:space="preserve">1.91310381889343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72144663333893</t>
+    <t xml:space="preserve">1.72144675254822</t>
   </si>
   <si>
     <t xml:space="preserve">1.67114746570587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69976592063904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68762469291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67895245552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63992738723755</t>
+    <t xml:space="preserve">1.69976603984833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68762481212616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67895233631134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63992726802826</t>
   </si>
   <si>
     <t xml:space="preserve">1.64773225784302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62865316867828</t>
+    <t xml:space="preserve">1.62865328788757</t>
   </si>
   <si>
     <t xml:space="preserve">1.62691879272461</t>
@@ -1046,13 +1046,13 @@
     <t xml:space="preserve">1.63905990123749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64859938621521</t>
+    <t xml:space="preserve">1.6485995054245</t>
   </si>
   <si>
     <t xml:space="preserve">1.6650767326355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69109380245209</t>
+    <t xml:space="preserve">1.6910936832428</t>
   </si>
   <si>
     <t xml:space="preserve">1.72925162315369</t>
@@ -1070,7 +1070,7 @@
     <t xml:space="preserve">1.66681122779846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68155407905579</t>
+    <t xml:space="preserve">1.68155419826508</t>
   </si>
   <si>
     <t xml:space="preserve">1.68935918807983</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">1.65727186203003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71537590026855</t>
+    <t xml:space="preserve">1.71537601947784</t>
   </si>
   <si>
     <t xml:space="preserve">1.66854572296143</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">1.71711039543152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7067037820816</t>
+    <t xml:space="preserve">1.70670366287231</t>
   </si>
   <si>
     <t xml:space="preserve">1.72578275203705</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">1.77348029613495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80383312702179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93391752243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88188374042511</t>
+    <t xml:space="preserve">1.80383324623108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93391728401184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8818838596344</t>
   </si>
   <si>
     <t xml:space="preserve">1.95559799671173</t>
@@ -1136,13 +1136,13 @@
     <t xml:space="preserve">1.81684160232544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89489197731018</t>
+    <t xml:space="preserve">1.89489221572876</t>
   </si>
   <si>
     <t xml:space="preserve">1.80816924571991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82984983921051</t>
+    <t xml:space="preserve">1.8298499584198</t>
   </si>
   <si>
     <t xml:space="preserve">1.85153067111969</t>
@@ -1157,25 +1157,25 @@
     <t xml:space="preserve">1.79082489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73445510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76480793952942</t>
+    <t xml:space="preserve">1.73445498943329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76480805873871</t>
   </si>
   <si>
     <t xml:space="preserve">1.96860635280609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89922821521759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89055597782135</t>
+    <t xml:space="preserve">1.89922833442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89055609703064</t>
   </si>
   <si>
     <t xml:space="preserve">1.8775475025177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8341863155365</t>
+    <t xml:space="preserve">1.83418619632721</t>
   </si>
   <si>
     <t xml:space="preserve">1.84285843372345</t>
@@ -1184,22 +1184,22 @@
     <t xml:space="preserve">1.82551383972168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83852219581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86020290851593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97294282913208</t>
+    <t xml:space="preserve">1.83852207660675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86020302772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9729425907135</t>
   </si>
   <si>
     <t xml:space="preserve">1.98161494731903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92958116531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98595094680786</t>
+    <t xml:space="preserve">1.92958092689514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98595070838928</t>
   </si>
   <si>
     <t xml:space="preserve">2.04665660858154</t>
@@ -1211,16 +1211,16 @@
     <t xml:space="preserve">2.042320728302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.072674036026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08134579658508</t>
+    <t xml:space="preserve">2.07267379760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08134603500366</t>
   </si>
   <si>
     <t xml:space="preserve">2.1116988658905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15072441101074</t>
+    <t xml:space="preserve">2.15072417259216</t>
   </si>
   <si>
     <t xml:space="preserve">2.05532908439636</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">2.3024890422821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2808084487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21142983436584</t>
+    <t xml:space="preserve">2.28080821037292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21143007278442</t>
   </si>
   <si>
     <t xml:space="preserve">2.3068253993988</t>
@@ -1250,13 +1250,13 @@
     <t xml:space="preserve">2.44991755485535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48894286155701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59301018714905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38921165466309</t>
+    <t xml:space="preserve">2.48894262313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59300994873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38921189308167</t>
   </si>
   <si>
     <t xml:space="preserve">2.49761533737183</t>
@@ -1286,22 +1286,22 @@
     <t xml:space="preserve">2.93122911453247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87052297592163</t>
+    <t xml:space="preserve">2.87052321434021</t>
   </si>
   <si>
     <t xml:space="preserve">2.92689275741577</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10033845901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23909473419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25210332870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21741390228271</t>
+    <t xml:space="preserve">3.10033869743347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23909449577332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25210309028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21741414070129</t>
   </si>
   <si>
     <t xml:space="preserve">3.25643944740295</t>
@@ -1313,13 +1313,13 @@
     <t xml:space="preserve">3.20874190330505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36917901039124</t>
+    <t xml:space="preserve">3.36917877197266</t>
   </si>
   <si>
     <t xml:space="preserve">3.26511144638062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22175002098083</t>
+    <t xml:space="preserve">3.22175025939941</t>
   </si>
   <si>
     <t xml:space="preserve">3.33882594108582</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">3.55563282966614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51227188110352</t>
+    <t xml:space="preserve">3.51227164268494</t>
   </si>
   <si>
     <t xml:space="preserve">3.62934708595276</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">3.73341417312622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80712866783142</t>
+    <t xml:space="preserve">3.80712890625</t>
   </si>
   <si>
     <t xml:space="preserve">3.90686011314392</t>
@@ -1364,19 +1364,19 @@
     <t xml:space="preserve">4.0456166267395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09765005111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86783504486084</t>
+    <t xml:space="preserve">4.09764957427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86783456802368</t>
   </si>
   <si>
     <t xml:space="preserve">4.0412802696228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94588565826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97190189361572</t>
+    <t xml:space="preserve">3.945885181427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97190141677856</t>
   </si>
   <si>
     <t xml:space="preserve">3.7117338180542</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">4.07163333892822</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24941444396973</t>
+    <t xml:space="preserve">4.24941492080688</t>
   </si>
   <si>
     <t xml:space="preserve">4.25375080108643</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">4.28410387039185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62232208251953</t>
+    <t xml:space="preserve">4.62232255935669</t>
   </si>
   <si>
     <t xml:space="preserve">4.57896137237549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74373435974121</t>
+    <t xml:space="preserve">4.74373388290405</t>
   </si>
   <si>
     <t xml:space="preserve">4.75240707397461</t>
@@ -1421,19 +1421,19 @@
     <t xml:space="preserve">4.87381839752197</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31879329681396</t>
+    <t xml:space="preserve">4.31879281997681</t>
   </si>
   <si>
     <t xml:space="preserve">4.80444049835205</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97788572311401</t>
+    <t xml:space="preserve">4.97788524627686</t>
   </si>
   <si>
     <t xml:space="preserve">5.01257514953613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0385913848877</t>
+    <t xml:space="preserve">5.03859186172485</t>
   </si>
   <si>
     <t xml:space="preserve">4.91718006134033</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">4.82178449630737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85647392272949</t>
+    <t xml:space="preserve">4.85647439956665</t>
   </si>
   <si>
     <t xml:space="preserve">4.89116334915161</t>
@@ -1451,19 +1451,19 @@
     <t xml:space="preserve">4.83045768737793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76107883453369</t>
+    <t xml:space="preserve">4.76107835769653</t>
   </si>
   <si>
     <t xml:space="preserve">4.54427194595337</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70904493331909</t>
+    <t xml:space="preserve">4.70904541015625</t>
   </si>
   <si>
     <t xml:space="preserve">4.60497808456421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58763360977173</t>
+    <t xml:space="preserve">4.58763313293457</t>
   </si>
   <si>
     <t xml:space="preserve">4.64833974838257</t>
@@ -1478,10 +1478,10 @@
     <t xml:space="preserve">4.47489356994629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40551614761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18437242507935</t>
+    <t xml:space="preserve">4.40551567077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1843729019165</t>
   </si>
   <si>
     <t xml:space="preserve">4.1887092590332</t>
@@ -1499,10 +1499,10 @@
     <t xml:space="preserve">3.91553163528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85916233062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7811119556427</t>
+    <t xml:space="preserve">3.85916185379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78111219406128</t>
   </si>
   <si>
     <t xml:space="preserve">4.14101123809814</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">3.14369964599609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00927948951721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09166598320007</t>
+    <t xml:space="preserve">3.00927972793579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09166622161865</t>
   </si>
   <si>
     <t xml:space="preserve">3.03529620170593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04830455780029</t>
+    <t xml:space="preserve">3.04830479621887</t>
   </si>
   <si>
     <t xml:space="preserve">3.07865762710571</t>
@@ -1541,10 +1541,10 @@
     <t xml:space="preserve">2.89653992652893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90521192550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02662420272827</t>
+    <t xml:space="preserve">2.90521216392517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02662396430969</t>
   </si>
   <si>
     <t xml:space="preserve">2.75344729423523</t>
@@ -1565,13 +1565,13 @@
     <t xml:space="preserve">3.24343085289001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19139719009399</t>
+    <t xml:space="preserve">3.19139742851257</t>
   </si>
   <si>
     <t xml:space="preserve">3.42554879188538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43855690956116</t>
+    <t xml:space="preserve">3.43855714797974</t>
   </si>
   <si>
     <t xml:space="preserve">3.39519548416138</t>
@@ -1586,10 +1586,10 @@
     <t xml:space="preserve">2.86618685722351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93990159034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88353133201599</t>
+    <t xml:space="preserve">2.93990135192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88353157043457</t>
   </si>
   <si>
     <t xml:space="preserve">2.97459053993225</t>
@@ -1598,10 +1598,10 @@
     <t xml:space="preserve">3.02228760719299</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38218760490417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32148122787476</t>
+    <t xml:space="preserve">3.3821873664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32148146629333</t>
   </si>
   <si>
     <t xml:space="preserve">3.15670824050903</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">3.11768293380737</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08732986450195</t>
+    <t xml:space="preserve">3.08733010292053</t>
   </si>
   <si>
     <t xml:space="preserve">3.06564927101135</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">2.73176670074463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63203573226929</t>
+    <t xml:space="preserve">2.63203549385071</t>
   </si>
   <si>
     <t xml:space="preserve">2.98759889602661</t>
@@ -1637,28 +1637,28 @@
     <t xml:space="preserve">3.3041365146637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3084728717804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17838859558105</t>
+    <t xml:space="preserve">3.30847311019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17838883399963</t>
   </si>
   <si>
     <t xml:space="preserve">3.10467433929443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16104435920715</t>
+    <t xml:space="preserve">3.16104412078857</t>
   </si>
   <si>
     <t xml:space="preserve">3.330153465271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46023774147034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5903217792511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88517951965332</t>
+    <t xml:space="preserve">3.46023750305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59032154083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88517904281616</t>
   </si>
   <si>
     <t xml:space="preserve">3.90252375602722</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">4.10198640823364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.145348072052</t>
+    <t xml:space="preserve">4.14534759521484</t>
   </si>
   <si>
     <t xml:space="preserve">4.1323390007019</t>
@@ -1685,10 +1685,10 @@
     <t xml:space="preserve">3.95889353752136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82447338104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96756625175476</t>
+    <t xml:space="preserve">3.82447361946106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9675657749176</t>
   </si>
   <si>
     <t xml:space="preserve">3.9415488243103</t>
@@ -1697,10 +1697,10 @@
     <t xml:space="preserve">3.99791860580444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00659084320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06296110153198</t>
+    <t xml:space="preserve">4.00659132003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06296062469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.05862474441528</t>
@@ -1721,13 +1721,13 @@
     <t xml:space="preserve">3.92420482635498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82880926132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75943112373352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74642276763916</t>
+    <t xml:space="preserve">3.82880973815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7594313621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74642300605774</t>
   </si>
   <si>
     <t xml:space="preserve">3.56864094734192</t>
@@ -1736,7 +1736,7 @@
     <t xml:space="preserve">3.77677583694458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24507856369019</t>
+    <t xml:space="preserve">4.24507904052734</t>
   </si>
   <si>
     <t xml:space="preserve">4.17136430740356</t>
@@ -1748,22 +1748,22 @@
     <t xml:space="preserve">4.06729698181152</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16269159317017</t>
+    <t xml:space="preserve">4.16269207000732</t>
   </si>
   <si>
     <t xml:space="preserve">4.21906137466431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23207092285156</t>
+    <t xml:space="preserve">4.2320704460144</t>
   </si>
   <si>
     <t xml:space="preserve">4.20171689987183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68302822113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88249063491821</t>
+    <t xml:space="preserve">4.68302869796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88249111175537</t>
   </si>
   <si>
     <t xml:space="preserve">4.76975107192993</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">4.55294466018677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44887685775757</t>
+    <t xml:space="preserve">4.44887733459473</t>
   </si>
   <si>
     <t xml:space="preserve">4.39684343338013</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">3.91119599342346</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04995250701904</t>
+    <t xml:space="preserve">4.04995203018188</t>
   </si>
   <si>
     <t xml:space="preserve">4.27009868621826</t>
@@ -70681,7 +70681,7 @@
     </row>
     <row r="2543">
       <c r="A2543" s="1" t="n">
-        <v>46027.6911342593</v>
+        <v>46027.3333333333</v>
       </c>
       <c r="B2543" t="n">
         <v>52603</v>
@@ -70702,6 +70702,32 @@
         <v>1412</v>
       </c>
       <c r="H2543" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2544">
+      <c r="A2544" s="1" t="n">
+        <v>46028.6861574074</v>
+      </c>
+      <c r="B2544" t="n">
+        <v>34472</v>
+      </c>
+      <c r="C2544" t="n">
+        <v>7.94000005722046</v>
+      </c>
+      <c r="D2544" t="n">
+        <v>7.84000015258789</v>
+      </c>
+      <c r="E2544" t="n">
+        <v>7.88000011444092</v>
+      </c>
+      <c r="F2544" t="n">
+        <v>7.8600001335144</v>
+      </c>
+      <c r="G2544" t="s">
+        <v>1386</v>
+      </c>
+      <c r="H2544" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95473074913025</t>
+    <t xml:space="preserve">1.95473086833954</t>
   </si>
   <si>
     <t xml:space="preserve">FM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95993411540985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9096348285675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85586678981781</t>
+    <t xml:space="preserve">1.95993399620056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90963470935822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8558669090271</t>
   </si>
   <si>
     <t xml:space="preserve">1.86453914642334</t>
@@ -65,46 +65,46 @@
     <t xml:space="preserve">1.74486184120178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69542968273163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61824655532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52285146713257</t>
+    <t xml:space="preserve">1.69542992115021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61824667453766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52285158634186</t>
   </si>
   <si>
     <t xml:space="preserve">1.47949004173279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34420263767242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45434057712555</t>
+    <t xml:space="preserve">1.34420251846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45434045791626</t>
   </si>
   <si>
     <t xml:space="preserve">1.55233716964722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48989689350128</t>
+    <t xml:space="preserve">1.48989677429199</t>
   </si>
   <si>
     <t xml:space="preserve">1.54366493225098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.595698595047</t>
+    <t xml:space="preserve">1.59569871425629</t>
   </si>
   <si>
     <t xml:space="preserve">1.51331210136414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53325831890106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49943625926971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4300582408905</t>
+    <t xml:space="preserve">1.53325819969177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.499436378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43005812168121</t>
   </si>
   <si>
     <t xml:space="preserve">1.40751028060913</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">1.38582956790924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28349673748016</t>
+    <t xml:space="preserve">1.28349661827087</t>
   </si>
   <si>
     <t xml:space="preserve">1.17682766914368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24186968803406</t>
+    <t xml:space="preserve">1.24186980724335</t>
   </si>
   <si>
     <t xml:space="preserve">1.20718061923981</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">1.23059582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43873035907745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39710342884064</t>
+    <t xml:space="preserve">1.43873047828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39710354804993</t>
   </si>
   <si>
     <t xml:space="preserve">1.50030362606049</t>
@@ -146,28 +146,28 @@
     <t xml:space="preserve">1.52111709117889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51678085327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49423313140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47688841819763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47515392303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5098432302475</t>
+    <t xml:space="preserve">1.51678073406219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4942330121994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47688853740692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47515404224396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50984311103821</t>
   </si>
   <si>
     <t xml:space="preserve">1.56014239788055</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58702623844147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55754053592682</t>
+    <t xml:space="preserve">1.58702635765076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55754065513611</t>
   </si>
   <si>
     <t xml:space="preserve">1.52805483341217</t>
@@ -176,19 +176,19 @@
     <t xml:space="preserve">1.54279780387878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51244461536407</t>
+    <t xml:space="preserve">1.51244485378265</t>
   </si>
   <si>
     <t xml:space="preserve">1.55147004127502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61651194095612</t>
+    <t xml:space="preserve">1.61651206016541</t>
   </si>
   <si>
     <t xml:space="preserve">1.67374897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70843827724457</t>
+    <t xml:space="preserve">1.70843815803528</t>
   </si>
   <si>
     <t xml:space="preserve">1.67808520793915</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">1.65467011928558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63298940658569</t>
+    <t xml:space="preserve">1.63298952579498</t>
   </si>
   <si>
     <t xml:space="preserve">1.6061053276062</t>
@@ -206,31 +206,31 @@
     <t xml:space="preserve">1.53499269485474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49770200252533</t>
+    <t xml:space="preserve">1.49770188331604</t>
   </si>
   <si>
     <t xml:space="preserve">1.49683463573456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48122453689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41791713237762</t>
+    <t xml:space="preserve">1.48122441768646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41791701316833</t>
   </si>
   <si>
     <t xml:space="preserve">1.39970517158508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35200762748718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39190006256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46041107177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57228338718414</t>
+    <t xml:space="preserve">1.35200774669647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39190018177032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46041119098663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57228350639343</t>
   </si>
   <si>
     <t xml:space="preserve">1.62952041625977</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">1.60437095165253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60870695114136</t>
+    <t xml:space="preserve">1.60870707035065</t>
   </si>
   <si>
     <t xml:space="preserve">1.62518429756165</t>
@@ -254,16 +254,16 @@
     <t xml:space="preserve">1.55407166481018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60090184211731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58876073360443</t>
+    <t xml:space="preserve">1.6009019613266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58876085281372</t>
   </si>
   <si>
     <t xml:space="preserve">1.49249851703644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45780944824219</t>
+    <t xml:space="preserve">1.4578093290329</t>
   </si>
   <si>
     <t xml:space="preserve">1.47775566577911</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">1.47428679466248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46908330917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56794738769531</t>
+    <t xml:space="preserve">1.46908342838287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56794714927673</t>
   </si>
   <si>
     <t xml:space="preserve">1.53932881355286</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">1.53065645694733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54106330871582</t>
+    <t xml:space="preserve">1.54106318950653</t>
   </si>
   <si>
     <t xml:space="preserve">1.5696816444397</t>
@@ -293,22 +293,22 @@
     <t xml:space="preserve">1.5471339225769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55060279369354</t>
+    <t xml:space="preserve">1.55060267448425</t>
   </si>
   <si>
     <t xml:space="preserve">1.56708014011383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5740180015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5107102394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59136259555817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56100952625275</t>
+    <t xml:space="preserve">1.57401812076569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51071035861969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59136247634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56100940704346</t>
   </si>
   <si>
     <t xml:space="preserve">1.54453229904175</t>
@@ -317,34 +317,34 @@
     <t xml:space="preserve">1.45000445842743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38929843902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40057241916656</t>
+    <t xml:space="preserve">1.38929855823517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40057253837585</t>
   </si>
   <si>
     <t xml:space="preserve">1.3875640630722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44740283489227</t>
+    <t xml:space="preserve">1.44740271568298</t>
   </si>
   <si>
     <t xml:space="preserve">1.49163126945496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48382616043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32338929176331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3294597864151</t>
+    <t xml:space="preserve">1.4838262796402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32338917255402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32945990562439</t>
   </si>
   <si>
     <t xml:space="preserve">1.3884311914444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39016580581665</t>
+    <t xml:space="preserve">1.39016568660736</t>
   </si>
   <si>
     <t xml:space="preserve">1.35981273651123</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">1.31124794483185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30084133148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30257558822632</t>
+    <t xml:space="preserve">1.30084121227264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30257570743561</t>
   </si>
   <si>
     <t xml:space="preserve">1.36154723167419</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">1.37802445888519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38236057758331</t>
+    <t xml:space="preserve">1.3823606967926</t>
   </si>
   <si>
     <t xml:space="preserve">1.39623630046844</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">1.377157330513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40490853786469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39450192451477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4040412902832</t>
+    <t xml:space="preserve">1.4049084186554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39450180530548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40404140949249</t>
   </si>
   <si>
     <t xml:space="preserve">1.393634557724</t>
@@ -395,22 +395,22 @@
     <t xml:space="preserve">1.42832362651825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37889170646667</t>
+    <t xml:space="preserve">1.37889182567596</t>
   </si>
   <si>
     <t xml:space="preserve">1.38062620162964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36588335037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35634386539459</t>
+    <t xml:space="preserve">1.3658834695816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3563437461853</t>
   </si>
   <si>
     <t xml:space="preserve">1.35460937023163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34333550930023</t>
+    <t xml:space="preserve">1.34333539009094</t>
   </si>
   <si>
     <t xml:space="preserve">1.33119428157806</t>
@@ -419,13 +419,13 @@
     <t xml:space="preserve">1.32685804367065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30170857906342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3077791929245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34767162799835</t>
+    <t xml:space="preserve">1.30170845985413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30777907371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34767150878906</t>
   </si>
   <si>
     <t xml:space="preserve">1.34506988525391</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">1.33379578590393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37108671665192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35547649860382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34940588474274</t>
+    <t xml:space="preserve">1.37108659744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35547661781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34940600395203</t>
   </si>
   <si>
     <t xml:space="preserve">1.33813202381134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34853863716125</t>
+    <t xml:space="preserve">1.34853875637054</t>
   </si>
   <si>
     <t xml:space="preserve">1.41704964637756</t>
@@ -455,25 +455,25 @@
     <t xml:space="preserve">1.40317416191101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39536893367767</t>
+    <t xml:space="preserve">1.39536905288696</t>
   </si>
   <si>
     <t xml:space="preserve">1.41097915172577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36501610279083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38322794437408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36761784553528</t>
+    <t xml:space="preserve">1.36501622200012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38322782516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36761772632599</t>
   </si>
   <si>
     <t xml:space="preserve">1.38149344921112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39797079563141</t>
+    <t xml:space="preserve">1.39797067642212</t>
   </si>
   <si>
     <t xml:space="preserve">1.37455570697784</t>
@@ -488,19 +488,19 @@
     <t xml:space="preserve">1.41271352767944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40924465656281</t>
+    <t xml:space="preserve">1.40924477577209</t>
   </si>
   <si>
     <t xml:space="preserve">1.42572212219238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35114049911499</t>
+    <t xml:space="preserve">1.3511403799057</t>
   </si>
   <si>
     <t xml:space="preserve">1.35894548892975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34680438041687</t>
+    <t xml:space="preserve">1.34680426120758</t>
   </si>
   <si>
     <t xml:space="preserve">1.36414885520935</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">1.36241436004639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33032703399658</t>
+    <t xml:space="preserve">1.33032715320587</t>
   </si>
   <si>
     <t xml:space="preserve">1.32078754901886</t>
@@ -527,28 +527,28 @@
     <t xml:space="preserve">1.17942941188812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26181590557098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2921689748764</t>
+    <t xml:space="preserve">1.26181614398956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29216909408569</t>
   </si>
   <si>
     <t xml:space="preserve">1.23146307468414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2175874710083</t>
+    <t xml:space="preserve">1.21758759021759</t>
   </si>
   <si>
     <t xml:space="preserve">1.24880766868591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22886145114899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18549990653992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15774869918823</t>
+    <t xml:space="preserve">1.2288613319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18550002574921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15774881839752</t>
   </si>
   <si>
     <t xml:space="preserve">1.11872339248657</t>
@@ -563,10 +563,10 @@
     <t xml:space="preserve">1.13346636295319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11438727378845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11612176895142</t>
+    <t xml:space="preserve">1.11438739299774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11612164974213</t>
   </si>
   <si>
     <t xml:space="preserve">1.11525452136993</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">1.09270668029785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07536208629608</t>
+    <t xml:space="preserve">1.07536220550537</t>
   </si>
   <si>
     <t xml:space="preserve">1.07276034355164</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">1.1542797088623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16295206546783</t>
+    <t xml:space="preserve">1.16295194625854</t>
   </si>
   <si>
     <t xml:space="preserve">1.16208481788635</t>
@@ -602,55 +602,55 @@
     <t xml:space="preserve">1.18289828300476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20544624328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23493206501007</t>
+    <t xml:space="preserve">1.20544612407684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23493194580078</t>
   </si>
   <si>
     <t xml:space="preserve">1.24533867835999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2184544801712</t>
+    <t xml:space="preserve">1.21845471858978</t>
   </si>
   <si>
     <t xml:space="preserve">1.19937562942505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20111000537872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22799408435822</t>
+    <t xml:space="preserve">1.20111012458801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2279942035675</t>
   </si>
   <si>
     <t xml:space="preserve">1.22192347049713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23666656017303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26875388622284</t>
+    <t xml:space="preserve">1.23666644096375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26875400543213</t>
   </si>
   <si>
     <t xml:space="preserve">1.38409507274628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3988379240036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38669681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35721099376678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34593713283539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33292865753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28869986534119</t>
+    <t xml:space="preserve">1.39883804321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38669669628143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35721111297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3459370136261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33292853832245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28870010375977</t>
   </si>
   <si>
     <t xml:space="preserve">1.25747990608215</t>
@@ -662,28 +662,28 @@
     <t xml:space="preserve">1.2444714307785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22712695598602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25661277770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22365808486938</t>
+    <t xml:space="preserve">1.22712683677673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25661265850067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2236579656601</t>
   </si>
   <si>
     <t xml:space="preserve">1.22279071807861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25314378738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22625970840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21325147151947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20891511440277</t>
+    <t xml:space="preserve">1.25314390659332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22625982761383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21325123310089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20891523361206</t>
   </si>
   <si>
     <t xml:space="preserve">1.20457899570465</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">1.20197737216949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18810176849365</t>
+    <t xml:space="preserve">1.18810164928436</t>
   </si>
   <si>
     <t xml:space="preserve">1.191570520401</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">1.20284450054169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19243776798248</t>
+    <t xml:space="preserve">1.19243788719177</t>
   </si>
   <si>
     <t xml:space="preserve">1.2340646982193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27742612361908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27222275733948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29823958873749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26355040073395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24273705482483</t>
+    <t xml:space="preserve">1.27742624282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27222263813019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2982394695282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26355051994324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24273693561554</t>
   </si>
   <si>
     <t xml:space="preserve">1.23579907417297</t>
@@ -737,52 +737,52 @@
     <t xml:space="preserve">1.22018897533417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24794030189514</t>
+    <t xml:space="preserve">1.24794042110443</t>
   </si>
   <si>
     <t xml:space="preserve">1.24967479705811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29043447971344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29303622245789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31818568706512</t>
+    <t xml:space="preserve">1.29043459892273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29303634166718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31818580627441</t>
   </si>
   <si>
     <t xml:space="preserve">1.30691182613373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27309000492096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24013519287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27916049957275</t>
+    <t xml:space="preserve">1.27308988571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24013531208038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27916061878204</t>
   </si>
   <si>
     <t xml:space="preserve">1.2704883813858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26528477668762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28436398506165</t>
+    <t xml:space="preserve">1.26528489589691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28436386585236</t>
   </si>
   <si>
     <t xml:space="preserve">1.27482438087463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26441764831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28523099422455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28696548938751</t>
+    <t xml:space="preserve">1.26441752910614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28523123264313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2869656085968</t>
   </si>
   <si>
     <t xml:space="preserve">1.3398665189743</t>
@@ -806,13 +806,13 @@
     <t xml:space="preserve">1.49856913089752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50724136829376</t>
+    <t xml:space="preserve">1.50724148750305</t>
   </si>
   <si>
     <t xml:space="preserve">1.50203800201416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4786229133606</t>
+    <t xml:space="preserve">1.47862303256989</t>
   </si>
   <si>
     <t xml:space="preserve">1.43352711200714</t>
@@ -821,25 +821,25 @@
     <t xml:space="preserve">1.40577578544617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38496232032776</t>
+    <t xml:space="preserve">1.38496220111847</t>
   </si>
   <si>
     <t xml:space="preserve">1.47168505191803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48729515075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47602117061615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45694220066071</t>
+    <t xml:space="preserve">1.48729526996613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47602128982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45694208145142</t>
   </si>
   <si>
     <t xml:space="preserve">1.46821618080139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45867657661438</t>
+    <t xml:space="preserve">1.45867669582367</t>
   </si>
   <si>
     <t xml:space="preserve">1.45954382419586</t>
@@ -860,19 +860,19 @@
     <t xml:space="preserve">1.50637412071228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57488524913788</t>
+    <t xml:space="preserve">1.57488512992859</t>
   </si>
   <si>
     <t xml:space="preserve">1.58269023895264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56187665462494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53585982322693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48642802238464</t>
+    <t xml:space="preserve">1.56187677383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53585994243622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48642790317535</t>
   </si>
   <si>
     <t xml:space="preserve">1.49510014057159</t>
@@ -881,16 +881,16 @@
     <t xml:space="preserve">1.51157760620117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48902952671051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48035740852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48816251754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51591372489929</t>
+    <t xml:space="preserve">1.4890296459198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48035728931427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48816239833832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51591360569</t>
   </si>
   <si>
     <t xml:space="preserve">1.5688145160675</t>
@@ -905,82 +905,82 @@
     <t xml:space="preserve">1.78648853302002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7604718208313</t>
+    <t xml:space="preserve">1.76047170162201</t>
   </si>
   <si>
     <t xml:space="preserve">1.85933589935303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8662736415863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84199142456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15245890617371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9998265504837</t>
+    <t xml:space="preserve">1.86627352237701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84199130535126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15245866775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99982666969299</t>
   </si>
   <si>
     <t xml:space="preserve">2.05879807472229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00329542160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9512619972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05186009407043</t>
+    <t xml:space="preserve">2.00329566001892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95126187801361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05186033248901</t>
   </si>
   <si>
     <t xml:space="preserve">2.01543664932251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98074758052826</t>
+    <t xml:space="preserve">1.98074769973755</t>
   </si>
   <si>
     <t xml:space="preserve">1.90443181991577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90790033340454</t>
+    <t xml:space="preserve">1.90790057182312</t>
   </si>
   <si>
     <t xml:space="preserve">1.91657280921936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90616607666016</t>
+    <t xml:space="preserve">1.90616595745087</t>
   </si>
   <si>
     <t xml:space="preserve">1.84892892837524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87321162223816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83158457279205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84719467163086</t>
+    <t xml:space="preserve">1.87321150302887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83158433437347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84719455242157</t>
   </si>
   <si>
     <t xml:space="preserve">1.93218290805817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93738615512848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92524516582489</t>
+    <t xml:space="preserve">1.93738603591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9252450466156</t>
   </si>
   <si>
     <t xml:space="preserve">1.94258952140808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97727859020233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02063989639282</t>
+    <t xml:space="preserve">1.97727870941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0206401348114</t>
   </si>
   <si>
     <t xml:space="preserve">2.06920480728149</t>
@@ -989,25 +989,25 @@
     <t xml:space="preserve">2.01196765899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03971910476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01370239257812</t>
+    <t xml:space="preserve">2.03971886634827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01370215415955</t>
   </si>
   <si>
     <t xml:space="preserve">1.9946231842041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94432413578033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90269708633423</t>
+    <t xml:space="preserve">1.94432425498962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90269732475281</t>
   </si>
   <si>
     <t xml:space="preserve">1.82117760181427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91310405731201</t>
+    <t xml:space="preserve">1.91310393810272</t>
   </si>
   <si>
     <t xml:space="preserve">1.72144663333893</t>
@@ -1025,19 +1025,19 @@
     <t xml:space="preserve">1.67895245552063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63992714881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64773225784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62865328788757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6269189119339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60350370407104</t>
+    <t xml:space="preserve">1.63992726802826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64773213863373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62865316867828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62691879272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60350358486176</t>
   </si>
   <si>
     <t xml:space="preserve">1.59656584262848</t>
@@ -1049,19 +1049,19 @@
     <t xml:space="preserve">1.6485995054245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66507685184479</t>
+    <t xml:space="preserve">1.6650767326355</t>
   </si>
   <si>
     <t xml:space="preserve">1.6910936832428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7292515039444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6754834651947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65640449523926</t>
+    <t xml:space="preserve">1.72925174236298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67548358440399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65640461444855</t>
   </si>
   <si>
     <t xml:space="preserve">1.63038766384125</t>
@@ -1070,19 +1070,19 @@
     <t xml:space="preserve">1.66681134700775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68155419826508</t>
+    <t xml:space="preserve">1.68155407905579</t>
   </si>
   <si>
     <t xml:space="preserve">1.68935906887054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67721796035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63385653495789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6217155456543</t>
+    <t xml:space="preserve">1.67721807956696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63385665416718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62171542644501</t>
   </si>
   <si>
     <t xml:space="preserve">1.65727174282074</t>
@@ -1103,31 +1103,31 @@
     <t xml:space="preserve">1.72578275203705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72751712799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71190714836121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74312722682953</t>
+    <t xml:space="preserve">1.72751724720001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71190702915192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74312734603882</t>
   </si>
   <si>
     <t xml:space="preserve">1.77781629562378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77348029613495</t>
+    <t xml:space="preserve">1.77348041534424</t>
   </si>
   <si>
     <t xml:space="preserve">1.80383324623108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93391740322113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88188374042511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95559799671173</t>
+    <t xml:space="preserve">1.93391728401184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8818838596344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9555983543396</t>
   </si>
   <si>
     <t xml:space="preserve">1.88621973991394</t>
@@ -1136,22 +1136,22 @@
     <t xml:space="preserve">1.81684172153473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89489209651947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8081693649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82984983921051</t>
+    <t xml:space="preserve">1.89489221572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80816948413849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8298499584198</t>
   </si>
   <si>
     <t xml:space="preserve">1.85153090953827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78215253353119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81250536441803</t>
+    <t xml:space="preserve">1.78215265274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81250548362732</t>
   </si>
   <si>
     <t xml:space="preserve">1.79082489013672</t>
@@ -1166,40 +1166,40 @@
     <t xml:space="preserve">1.96860635280609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89922821521759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89055597782135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87754738330841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83418607711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84285831451416</t>
+    <t xml:space="preserve">1.89922833442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89055585861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8775475025177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83418619632721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84285843372345</t>
   </si>
   <si>
     <t xml:space="preserve">1.82551383972168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83852231502533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86020314693451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97294282913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98161470890045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92958116531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98595118522644</t>
+    <t xml:space="preserve">1.83852219581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86020302772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9729425907135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98161494731903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92958104610443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98595082759857</t>
   </si>
   <si>
     <t xml:space="preserve">2.04665684700012</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">2.03364849090576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04232048988342</t>
+    <t xml:space="preserve">2.042320728302</t>
   </si>
   <si>
     <t xml:space="preserve">2.072674036026</t>
@@ -1217,13 +1217,13 @@
     <t xml:space="preserve">2.08134603500366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1116988658905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15072417259216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05532884597778</t>
+    <t xml:space="preserve">2.11169910430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15072441101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05532932281494</t>
   </si>
   <si>
     <t xml:space="preserve">2.1854133605957</t>
@@ -1232,19 +1232,19 @@
     <t xml:space="preserve">2.33717799186707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30248880386353</t>
+    <t xml:space="preserve">2.3024890422821</t>
   </si>
   <si>
     <t xml:space="preserve">2.2808084487915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21143007278442</t>
+    <t xml:space="preserve">2.211430311203</t>
   </si>
   <si>
     <t xml:space="preserve">2.30682516098022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28514432907104</t>
+    <t xml:space="preserve">2.28514456748962</t>
   </si>
   <si>
     <t xml:space="preserve">2.44991755485535</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">2.59301018714905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38921165466309</t>
+    <t xml:space="preserve">2.38921189308167</t>
   </si>
   <si>
     <t xml:space="preserve">2.49761533737183</t>
@@ -1268,16 +1268,16 @@
     <t xml:space="preserve">2.62769937515259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71442198753357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76645588874817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83583426475525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91388440132141</t>
+    <t xml:space="preserve">2.71442222595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76645565032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83583402633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91388416290283</t>
   </si>
   <si>
     <t xml:space="preserve">2.92255663871765</t>
@@ -1292,16 +1292,16 @@
     <t xml:space="preserve">2.92689275741577</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10033845901489</t>
+    <t xml:space="preserve">3.10033822059631</t>
   </si>
   <si>
     <t xml:space="preserve">3.23909449577332</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25210309028625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21741390228271</t>
+    <t xml:space="preserve">3.25210332870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21741414070129</t>
   </si>
   <si>
     <t xml:space="preserve">3.25643944740295</t>
@@ -1316,13 +1316,13 @@
     <t xml:space="preserve">3.36917877197266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26511168479919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22175025939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33882570266724</t>
+    <t xml:space="preserve">3.26511144638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22175002098083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33882594108582</t>
   </si>
   <si>
     <t xml:space="preserve">3.27811980247498</t>
@@ -1331,82 +1331,82 @@
     <t xml:space="preserve">3.34749794006348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50793552398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48625445365906</t>
+    <t xml:space="preserve">3.50793528556824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48625469207764</t>
   </si>
   <si>
     <t xml:space="preserve">3.55563259124756</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51227140426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62934708595276</t>
+    <t xml:space="preserve">3.51227164268494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62934684753418</t>
   </si>
   <si>
     <t xml:space="preserve">3.6640362739563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7334144115448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80712866783142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90686011314392</t>
+    <t xml:space="preserve">3.73341393470764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80712842941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90685963630676</t>
   </si>
   <si>
     <t xml:space="preserve">4.07596921920776</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04561614990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09764957427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86783480644226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04127979278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94588565826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97190237045288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71173357963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9198682308197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07163333892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24941492080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25375080108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28410387039185</t>
+    <t xml:space="preserve">4.0456166267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09765005111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86783456802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0412802696228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.945885181427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97190165519714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7117338180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91986799240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07163286209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24941539764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25375127792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.284104347229</t>
   </si>
   <si>
     <t xml:space="preserve">4.62232255935669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57896137237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74373388290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75240707397461</t>
+    <t xml:space="preserve">4.57896184921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74373435974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75240659713745</t>
   </si>
   <si>
     <t xml:space="preserve">5.05593633651733</t>
@@ -1418,28 +1418,28 @@
     <t xml:space="preserve">4.95186901092529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87381792068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31879329681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80444002151489</t>
+    <t xml:space="preserve">4.87381887435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31879281997681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80444049835205</t>
   </si>
   <si>
     <t xml:space="preserve">4.97788572311401</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01257514953613</t>
+    <t xml:space="preserve">5.01257562637329</t>
   </si>
   <si>
     <t xml:space="preserve">5.03859186172485</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91717958450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82178497314453</t>
+    <t xml:space="preserve">4.91718006134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82178449630737</t>
   </si>
   <si>
     <t xml:space="preserve">4.85647392272949</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">4.89116287231445</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83045673370361</t>
+    <t xml:space="preserve">4.83045721054077</t>
   </si>
   <si>
     <t xml:space="preserve">4.76107883453369</t>
@@ -1457,13 +1457,13 @@
     <t xml:space="preserve">4.54427194595337</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70904588699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60497760772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58763360977173</t>
+    <t xml:space="preserve">4.70904541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60497808456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58763313293457</t>
   </si>
   <si>
     <t xml:space="preserve">4.64833927154541</t>
@@ -1478,58 +1478,58 @@
     <t xml:space="preserve">4.47489356994629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40551567077637</t>
+    <t xml:space="preserve">4.40551519393921</t>
   </si>
   <si>
     <t xml:space="preserve">4.1843729019165</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1887092590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24074268341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08464097976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92854070663452</t>
+    <t xml:space="preserve">4.18870878219604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24074172973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.084641456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9285409450531</t>
   </si>
   <si>
     <t xml:space="preserve">3.91553211212158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85916233062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7811119556427</t>
+    <t xml:space="preserve">3.85916209220886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78111171722412</t>
   </si>
   <si>
     <t xml:space="preserve">4.14101123809814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62501072883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31280899047852</t>
+    <t xml:space="preserve">3.62501096725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31280922889709</t>
   </si>
   <si>
     <t xml:space="preserve">3.28679227828979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14369964599609</t>
+    <t xml:space="preserve">3.14369940757751</t>
   </si>
   <si>
     <t xml:space="preserve">3.00927948951721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09166622161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03529644012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04830503463745</t>
+    <t xml:space="preserve">3.09166598320007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03529620170593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04830479621887</t>
   </si>
   <si>
     <t xml:space="preserve">3.07865762710571</t>
@@ -1538,10 +1538,10 @@
     <t xml:space="preserve">2.96158194541931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89653968811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90521192550659</t>
+    <t xml:space="preserve">2.89653992652893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90521216392517</t>
   </si>
   <si>
     <t xml:space="preserve">3.02662420272827</t>
@@ -1550,31 +1550,31 @@
     <t xml:space="preserve">2.75344729423523</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80548095703125</t>
+    <t xml:space="preserve">2.80548071861267</t>
   </si>
   <si>
     <t xml:space="preserve">2.88786745071411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04396843910217</t>
+    <t xml:space="preserve">3.04396867752075</t>
   </si>
   <si>
     <t xml:space="preserve">3.2607753276825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24343109130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19139719009399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4255485534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43855714797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39519596099854</t>
+    <t xml:space="preserve">3.24343085289001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19139742851257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42554879188538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43855690956116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39519548416138</t>
   </si>
   <si>
     <t xml:space="preserve">3.20440554618835</t>
@@ -1586,16 +1586,16 @@
     <t xml:space="preserve">2.86618685722351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93990135192871</t>
+    <t xml:space="preserve">2.93990159034729</t>
   </si>
   <si>
     <t xml:space="preserve">2.88353133201599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97459030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02228784561157</t>
+    <t xml:space="preserve">2.97459053993225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02228760719299</t>
   </si>
   <si>
     <t xml:space="preserve">3.3821873664856</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">3.15670824050903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11768269538879</t>
+    <t xml:space="preserve">3.11768293380737</t>
   </si>
   <si>
     <t xml:space="preserve">3.08732986450195</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">3.06564927101135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81848931312561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68840527534485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73176670074463</t>
+    <t xml:space="preserve">2.81848955154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68840503692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73176693916321</t>
   </si>
   <si>
     <t xml:space="preserve">2.63203549385071</t>
@@ -1631,49 +1631,49 @@
     <t xml:space="preserve">2.98759865760803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17405247688293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3041365146637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30847311019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17838883399963</t>
+    <t xml:space="preserve">3.17405271530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30413675308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3084728717804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17838859558105</t>
   </si>
   <si>
     <t xml:space="preserve">3.10467433929443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16104435920715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33015370368958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46023774147034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59032201766968</t>
+    <t xml:space="preserve">3.16104412078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.330153465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46023797988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59032154083252</t>
   </si>
   <si>
     <t xml:space="preserve">3.88517904281616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9025239944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8548264503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11499452590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27543163299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10198640823364</t>
+    <t xml:space="preserve">3.90252375602722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85482597351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11499404907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27543115615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10198593139648</t>
   </si>
   <si>
     <t xml:space="preserve">4.145348072052</t>
@@ -1682,25 +1682,25 @@
     <t xml:space="preserve">4.1323390007019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95889377593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82447338104248</t>
+    <t xml:space="preserve">3.95889329910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82447361946106</t>
   </si>
   <si>
     <t xml:space="preserve">3.9675657749176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9415488243103</t>
+    <t xml:space="preserve">3.94154906272888</t>
   </si>
   <si>
     <t xml:space="preserve">3.99791884422302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00659084320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06296110153198</t>
+    <t xml:space="preserve">4.00659132003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06296062469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.05862474441528</t>
@@ -1712,28 +1712,28 @@
     <t xml:space="preserve">4.09331369400024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03260803222656</t>
+    <t xml:space="preserve">4.0326075553894</t>
   </si>
   <si>
     <t xml:space="preserve">3.9892463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9242045879364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82880902290344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75943160057068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74642324447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56864094734192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.776775598526</t>
+    <t xml:space="preserve">3.92420434951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82880973815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7594313621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74642300605774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5686411857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77677583694458</t>
   </si>
   <si>
     <t xml:space="preserve">4.24507856369019</t>
@@ -1751,22 +1751,22 @@
     <t xml:space="preserve">4.16269207000732</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21906137466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2320704460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20171737670898</t>
+    <t xml:space="preserve">4.21906185150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23206996917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20171689987183</t>
   </si>
   <si>
     <t xml:space="preserve">4.68302869796753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88249158859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76975107192993</t>
+    <t xml:space="preserve">4.88249111175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76975154876709</t>
   </si>
   <si>
     <t xml:space="preserve">4.72638940811157</t>
@@ -1775,52 +1775,52 @@
     <t xml:space="preserve">4.63966703414917</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55294466018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44887733459473</t>
+    <t xml:space="preserve">4.55294418334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44887685775757</t>
   </si>
   <si>
     <t xml:space="preserve">4.39684343338013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91119599342346</t>
+    <t xml:space="preserve">3.9111967086792</t>
   </si>
   <si>
     <t xml:space="preserve">4.04995250701904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27009868621826</t>
+    <t xml:space="preserve">4.2700982093811</t>
   </si>
   <si>
     <t xml:space="preserve">4.12285375595093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01130485534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91760349273682</t>
+    <t xml:space="preserve">4.01130437850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91760301589966</t>
   </si>
   <si>
     <t xml:space="preserve">4.22547912597656</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00684261322021</t>
+    <t xml:space="preserve">4.00684213638306</t>
   </si>
   <si>
     <t xml:space="preserve">3.83282613754272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85513591766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8595974445343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93098950386047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83728837966919</t>
+    <t xml:space="preserve">3.85513615608215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85959792137146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93098926544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83728814125061</t>
   </si>
   <si>
     <t xml:space="preserve">4.01576662063599</t>
@@ -1829,43 +1829,43 @@
     <t xml:space="preserve">4.03807640075684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95776128768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79266858100891</t>
+    <t xml:space="preserve">3.95776081085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79266834259033</t>
   </si>
   <si>
     <t xml:space="preserve">3.74358701705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76143479347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61419034004211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68111944198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52048850059509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48479270935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67219519615173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59634232521057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58741807937622</t>
+    <t xml:space="preserve">3.76143455505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61419010162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6811192035675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52048873901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48479294776917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67219543457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59634208679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5874183177948</t>
   </si>
   <si>
     <t xml:space="preserve">3.64096164703369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64988565444946</t>
+    <t xml:space="preserve">3.64988589286804</t>
   </si>
   <si>
     <t xml:space="preserve">3.5115647315979</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">3.52495074272156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41786360740662</t>
+    <t xml:space="preserve">3.41786336898804</t>
   </si>
   <si>
     <t xml:space="preserve">3.44909739494324</t>
@@ -1886,7 +1886,7 @@
     <t xml:space="preserve">3.4223256111145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47140717506409</t>
+    <t xml:space="preserve">3.47140693664551</t>
   </si>
   <si>
     <t xml:space="preserve">3.50710296630859</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">3.42678737640381</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36878204345703</t>
+    <t xml:space="preserve">3.36878228187561</t>
   </si>
   <si>
     <t xml:space="preserve">3.34647226333618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31523847579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32862424850464</t>
+    <t xml:space="preserve">3.31523823738098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32862448692322</t>
   </si>
   <si>
     <t xml:space="preserve">3.36432003974915</t>
@@ -1934,13 +1934,13 @@
     <t xml:space="preserve">3.40001559257507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30631422996521</t>
+    <t xml:space="preserve">3.30631446838379</t>
   </si>
   <si>
     <t xml:space="preserve">3.28400492668152</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33308625221252</t>
+    <t xml:space="preserve">3.33308601379395</t>
   </si>
   <si>
     <t xml:space="preserve">3.35093426704407</t>
@@ -1952,61 +1952,61 @@
     <t xml:space="preserve">3.65880942344666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71235299110413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81051635742188</t>
+    <t xml:space="preserve">3.71235322952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81051659584045</t>
   </si>
   <si>
     <t xml:space="preserve">3.80605435371399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76589632034302</t>
+    <t xml:space="preserve">3.7658965587616</t>
   </si>
   <si>
     <t xml:space="preserve">3.6008038520813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5561842918396</t>
+    <t xml:space="preserve">3.55618405342102</t>
   </si>
   <si>
     <t xml:space="preserve">3.4669451713562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62757587432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78374409675598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69004344940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7078914642334</t>
+    <t xml:space="preserve">3.62757611274719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78374433517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69004368782043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70789122581482</t>
   </si>
   <si>
     <t xml:space="preserve">3.67665719985962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73912477493286</t>
+    <t xml:space="preserve">3.73912501335144</t>
   </si>
   <si>
     <t xml:space="preserve">3.68558144569397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66773343086243</t>
+    <t xml:space="preserve">3.66773366928101</t>
   </si>
   <si>
     <t xml:space="preserve">3.69896721839905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7212769985199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72573924064636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62311387062073</t>
+    <t xml:space="preserve">3.72127723693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72573947906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62311363220215</t>
   </si>
   <si>
     <t xml:space="preserve">3.60972809791565</t>
@@ -2018,10 +2018,13 @@
     <t xml:space="preserve">3.56957030296326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9666850566864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73466324806213</t>
+    <t xml:space="preserve">3.99791860580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96668481826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73466277122498</t>
   </si>
   <si>
     <t xml:space="preserve">3.69450497627258</t>
@@ -2036,28 +2039,28 @@
     <t xml:space="preserve">3.60526609420776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57849454879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56510806083679</t>
+    <t xml:space="preserve">3.57849431037903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56510829925537</t>
   </si>
   <si>
     <t xml:space="preserve">3.93991351127625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06038665771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91314172744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98899459838867</t>
+    <t xml:space="preserve">4.06038618087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91314196586609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98899483680725</t>
   </si>
   <si>
     <t xml:space="preserve">3.98007082939148</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12731599807739</t>
+    <t xml:space="preserve">4.12731552124023</t>
   </si>
   <si>
     <t xml:space="preserve">4.05146217346191</t>
@@ -2069,10 +2072,10 @@
     <t xml:space="preserve">4.03361415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92652702331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90867924690247</t>
+    <t xml:space="preserve">3.92652750015259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90867972373962</t>
   </si>
   <si>
     <t xml:space="preserve">3.90421748161316</t>
@@ -2081,7 +2084,7 @@
     <t xml:space="preserve">4.0425386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93545126914978</t>
+    <t xml:space="preserve">3.93545150756836</t>
   </si>
   <si>
     <t xml:space="preserve">3.8908314704895</t>
@@ -2096,16 +2099,16 @@
     <t xml:space="preserve">4.00238084793091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17639684677124</t>
+    <t xml:space="preserve">4.1763973236084</t>
   </si>
   <si>
     <t xml:space="preserve">4.08715772628784</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21655464172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46196269989014</t>
+    <t xml:space="preserve">4.21655511856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46196317672729</t>
   </si>
   <si>
     <t xml:space="preserve">4.53335380554199</t>
@@ -2114,7 +2117,7 @@
     <t xml:space="preserve">4.64044094085693</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58689737319946</t>
+    <t xml:space="preserve">4.58689785003662</t>
   </si>
   <si>
     <t xml:space="preserve">4.64936542510986</t>
@@ -2126,7 +2129,7 @@
     <t xml:space="preserve">4.78322410583496</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68506145477295</t>
+    <t xml:space="preserve">4.68506097793579</t>
   </si>
   <si>
     <t xml:space="preserve">4.83676767349243</t>
@@ -2138,10 +2141,10 @@
     <t xml:space="preserve">4.90815925598145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00632238388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89923477172852</t>
+    <t xml:space="preserve">5.00632190704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89923524856567</t>
   </si>
   <si>
     <t xml:space="preserve">4.85461568832397</t>
@@ -2156,10 +2159,10 @@
     <t xml:space="preserve">5.04201793670654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89031171798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95277881622314</t>
+    <t xml:space="preserve">4.8903112411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9527792930603</t>
   </si>
   <si>
     <t xml:space="preserve">4.8456916809082</t>
@@ -2168,10 +2171,10 @@
     <t xml:space="preserve">4.76537656784058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82784414291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80999612808228</t>
+    <t xml:space="preserve">4.82784366607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80999565124512</t>
   </si>
   <si>
     <t xml:space="preserve">4.94385480880737</t>
@@ -2180,13 +2183,13 @@
     <t xml:space="preserve">5.06878995895386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.997398853302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23834419250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45251846313477</t>
+    <t xml:space="preserve">4.99739837646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23834466934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45251893997192</t>
   </si>
   <si>
     <t xml:space="preserve">5.83624744415283</t>
@@ -2207,19 +2210,19 @@
     <t xml:space="preserve">4.70290899276733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71183252334595</t>
+    <t xml:space="preserve">4.71183347702026</t>
   </si>
   <si>
     <t xml:space="preserve">4.73860454559326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63151741027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67613649368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56012630462646</t>
+    <t xml:space="preserve">4.63151788711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67613697052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56012582778931</t>
   </si>
   <si>
     <t xml:space="preserve">4.41734313964844</t>
@@ -2228,19 +2231,19 @@
     <t xml:space="preserve">4.14516353607178</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02022886276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98453283309937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94883728027344</t>
+    <t xml:space="preserve">4.02022838592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98453307151794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94883751869202</t>
   </si>
   <si>
     <t xml:space="preserve">3.8015923500061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12783598899841</t>
+    <t xml:space="preserve">3.12783575057983</t>
   </si>
   <si>
     <t xml:space="preserve">3.15906977653503</t>
@@ -2249,28 +2252,28 @@
     <t xml:space="preserve">3.25277090072632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72625923156738</t>
+    <t xml:space="preserve">2.72625946998596</t>
   </si>
   <si>
     <t xml:space="preserve">2.757493019104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961738586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45854139328003</t>
+    <t xml:space="preserve">2.44961762428284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45854163169861</t>
   </si>
   <si>
     <t xml:space="preserve">2.14174222946167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99895942211151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10604619979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25775337219238</t>
+    <t xml:space="preserve">1.99895930290222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10604643821716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2577531337738</t>
   </si>
   <si>
     <t xml:space="preserve">2.34699249267578</t>
@@ -2279,13 +2282,13 @@
     <t xml:space="preserve">2.4228458404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54331874847412</t>
+    <t xml:space="preserve">2.54331851005554</t>
   </si>
   <si>
     <t xml:space="preserve">2.40053606033325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48085141181946</t>
+    <t xml:space="preserve">2.48085117340088</t>
   </si>
   <si>
     <t xml:space="preserve">2.45407962799072</t>
@@ -2297,10 +2300,10 @@
     <t xml:space="preserve">2.56116652488708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73964500427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23938512802124</t>
+    <t xml:space="preserve">2.73964524269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23938536643982</t>
   </si>
   <si>
     <t xml:space="preserve">3.20368933677673</t>
@@ -2312,19 +2315,19 @@
     <t xml:space="preserve">2.91812372207642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85119414329529</t>
+    <t xml:space="preserve">2.85119438171387</t>
   </si>
   <si>
     <t xml:space="preserve">2.99843883514404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93597149848938</t>
+    <t xml:space="preserve">2.93597173690796</t>
   </si>
   <si>
     <t xml:space="preserve">2.94489550590515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89135217666626</t>
+    <t xml:space="preserve">2.8913516998291</t>
   </si>
   <si>
     <t xml:space="preserve">2.97612929344177</t>
@@ -2333,16 +2336,16 @@
     <t xml:space="preserve">2.85565638542175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98059105873108</t>
+    <t xml:space="preserve">2.98059129714966</t>
   </si>
   <si>
     <t xml:space="preserve">3.00290107727051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13229775428772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01182508468628</t>
+    <t xml:space="preserve">3.1322979927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0118248462677</t>
   </si>
   <si>
     <t xml:space="preserve">2.98862147331238</t>
@@ -2793,9 +2796,6 @@
   </si>
   <si>
     <t xml:space="preserve">3.10463929176331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0118248462677</t>
   </si>
   <si>
     <t xml:space="preserve">3.11392092704773</t>
@@ -29108,7 +29108,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G943" t="s">
-        <v>560</v>
+        <v>668</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -29160,7 +29160,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G945" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -29186,7 +29186,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G946" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -29264,7 +29264,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G949" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -29290,7 +29290,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G950" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -29368,7 +29368,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G953" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -29394,7 +29394,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G954" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -29446,7 +29446,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G956" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -29498,7 +29498,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G958" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -29524,7 +29524,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G959" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -29550,7 +29550,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G960" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -29576,7 +29576,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G961" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -29680,7 +29680,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G965" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -29706,7 +29706,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G966" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -29732,7 +29732,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G967" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -29758,7 +29758,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G968" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -29784,7 +29784,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G969" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -29810,7 +29810,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G970" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -29836,7 +29836,7 @@
         <v>4.625</v>
       </c>
       <c r="G971" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -29862,7 +29862,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G972" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -29888,7 +29888,7 @@
         <v>4.58500003814697</v>
       </c>
       <c r="G973" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -29914,7 +29914,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G974" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -29940,7 +29940,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G975" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -29966,7 +29966,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G976" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -29992,7 +29992,7 @@
         <v>4.375</v>
       </c>
       <c r="G977" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -30018,7 +30018,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G978" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -30044,7 +30044,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G979" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -30070,7 +30070,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G980" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -30096,7 +30096,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G981" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -30122,7 +30122,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G982" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -30174,7 +30174,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G984" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -30200,7 +30200,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G985" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -30226,7 +30226,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G986" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -30252,7 +30252,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G987" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -30278,7 +30278,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G988" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -30304,7 +30304,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G989" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -30330,7 +30330,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G990" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -30408,7 +30408,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G993" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -30434,7 +30434,7 @@
         <v>5</v>
       </c>
       <c r="G994" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -30460,7 +30460,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G995" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -30486,7 +30486,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G996" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -30512,7 +30512,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G997" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -30538,7 +30538,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G998" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -30564,7 +30564,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G999" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -30590,7 +30590,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1000" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -30616,7 +30616,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1001" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -30642,7 +30642,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1002" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -30668,7 +30668,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1003" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -30694,7 +30694,7 @@
         <v>5.25</v>
       </c>
       <c r="G1004" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -30720,7 +30720,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1005" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -30746,7 +30746,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1006" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -30772,7 +30772,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1007" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -30798,7 +30798,7 @@
         <v>5.5</v>
       </c>
       <c r="G1008" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -30824,7 +30824,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G1009" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -30850,7 +30850,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1010" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -30876,7 +30876,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1011" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -30902,7 +30902,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1012" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -30928,7 +30928,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1013" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -30954,7 +30954,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1014" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -30980,7 +30980,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1015" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -31006,7 +31006,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1016" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -31032,7 +31032,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1017" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -31058,7 +31058,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1018" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -31084,7 +31084,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1019" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -31110,7 +31110,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1020" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -31136,7 +31136,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1021" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -31162,7 +31162,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1022" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -31188,7 +31188,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1023" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -31214,7 +31214,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1024" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -31240,7 +31240,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1025" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -31266,7 +31266,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1026" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -31292,7 +31292,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1027" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -31318,7 +31318,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1028" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -31344,7 +31344,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1029" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -31370,7 +31370,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1030" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -31396,7 +31396,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1031" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -31422,7 +31422,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1032" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -31448,7 +31448,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1033" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -31474,7 +31474,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1034" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -31500,7 +31500,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1035" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -31526,7 +31526,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1036" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -31552,7 +31552,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1037" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -31578,7 +31578,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1038" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -31604,7 +31604,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1039" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -31630,7 +31630,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1040" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -31656,7 +31656,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G1041" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -31682,7 +31682,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1042" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -31708,7 +31708,7 @@
         <v>5.25</v>
       </c>
       <c r="G1043" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -31734,7 +31734,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1044" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -31760,7 +31760,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1045" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -31786,7 +31786,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1046" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -31812,7 +31812,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1047" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -31838,7 +31838,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1048" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -31864,7 +31864,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1049" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -31890,7 +31890,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1050" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -31916,7 +31916,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1051" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -31942,7 +31942,7 @@
         <v>5.25</v>
       </c>
       <c r="G1052" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -31968,7 +31968,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G1053" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -31994,7 +31994,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1054" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -32020,7 +32020,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1055" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -32046,7 +32046,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1056" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -32072,7 +32072,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1057" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -32124,7 +32124,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1059" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -32228,7 +32228,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1063" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -32254,7 +32254,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1064" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -32280,7 +32280,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1065" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -32306,7 +32306,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1066" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -32332,7 +32332,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1067" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -32358,7 +32358,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1068" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -32384,7 +32384,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1069" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -32410,7 +32410,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1070" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -32436,7 +32436,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1071" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -32462,7 +32462,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1072" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -32488,7 +32488,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1073" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -32514,7 +32514,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1074" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -32540,7 +32540,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1075" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -32566,7 +32566,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1076" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -32592,7 +32592,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1077" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -32618,7 +32618,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1078" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -32644,7 +32644,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1079" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -32670,7 +32670,7 @@
         <v>2.75</v>
       </c>
       <c r="G1080" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -32696,7 +32696,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1081" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -32722,7 +32722,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1082" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -32748,7 +32748,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1083" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -32774,7 +32774,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1084" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -32800,7 +32800,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1085" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -32826,7 +32826,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1086" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -32852,7 +32852,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1087" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -32878,7 +32878,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1088" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -32904,7 +32904,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1089" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -32930,7 +32930,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1090" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -32956,7 +32956,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1091" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -32982,7 +32982,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1092" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -33008,7 +33008,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1093" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -33034,7 +33034,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1094" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -33060,7 +33060,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1095" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -33086,7 +33086,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1096" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -33112,7 +33112,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1097" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -33138,7 +33138,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1098" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -33164,7 +33164,7 @@
         <v>3.375</v>
       </c>
       <c r="G1099" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -33190,7 +33190,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1100" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -33216,7 +33216,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1101" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -33242,7 +33242,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1102" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -33268,7 +33268,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1103" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -33294,7 +33294,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1104" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -33320,7 +33320,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1105" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -33346,7 +33346,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1106" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -33372,7 +33372,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1107" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -33398,7 +33398,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1108" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -33424,7 +33424,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1109" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -33450,7 +33450,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1110" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -33476,7 +33476,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1111" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -33502,7 +33502,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1112" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -33528,7 +33528,7 @@
         <v>3</v>
       </c>
       <c r="G1113" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -33554,7 +33554,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1114" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -33580,7 +33580,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1115" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -33606,7 +33606,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1116" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -33632,7 +33632,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1117" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -33658,7 +33658,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1118" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -33684,7 +33684,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1119" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -33710,7 +33710,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1120" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -33736,7 +33736,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1121" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -33762,7 +33762,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1122" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -33788,7 +33788,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1123" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -33814,7 +33814,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1124" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -33840,7 +33840,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1125" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -33866,7 +33866,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1126" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -33892,7 +33892,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1127" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -33918,7 +33918,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1128" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -33944,7 +33944,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1129" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -33970,7 +33970,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1130" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -33996,7 +33996,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1131" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -34022,7 +34022,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1132" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -34048,7 +34048,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1133" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -34074,7 +34074,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1134" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -34100,7 +34100,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1135" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -34126,7 +34126,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1136" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -34152,7 +34152,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1137" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -34178,7 +34178,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1138" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -34204,7 +34204,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1139" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -34230,7 +34230,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1140" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -34256,7 +34256,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1141" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -34282,7 +34282,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1142" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -34308,7 +34308,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1143" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -34334,7 +34334,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G1144" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -34360,7 +34360,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1145" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -34386,7 +34386,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1146" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -34412,7 +34412,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G1147" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -34438,7 +34438,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1148" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -34464,7 +34464,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1149" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -34490,7 +34490,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G1150" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -34516,7 +34516,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1151" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -34542,7 +34542,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1152" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -34568,7 +34568,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1153" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -34594,7 +34594,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1154" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -34620,7 +34620,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1155" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -34646,7 +34646,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1156" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -34672,7 +34672,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G1157" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -34698,7 +34698,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1158" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -34724,7 +34724,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1159" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -34750,7 +34750,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1160" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -34776,7 +34776,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G1161" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -34802,7 +34802,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1162" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -34828,7 +34828,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1163" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -34854,7 +34854,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1164" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -34880,7 +34880,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1165" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -34906,7 +34906,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1166" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -34932,7 +34932,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1167" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -34958,7 +34958,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1168" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -34984,7 +34984,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1169" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -35010,7 +35010,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1170" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -35036,7 +35036,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1171" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -35062,7 +35062,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1172" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -35088,7 +35088,7 @@
         <v>2.75</v>
       </c>
       <c r="G1173" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -35114,7 +35114,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G1174" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -35140,7 +35140,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1175" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -35166,7 +35166,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1176" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -35192,7 +35192,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1177" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -35218,7 +35218,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1178" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -35244,7 +35244,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1179" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -35270,7 +35270,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1180" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -35296,7 +35296,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1181" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -35322,7 +35322,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1182" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -35348,7 +35348,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G1183" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -35374,7 +35374,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1184" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -35400,7 +35400,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G1185" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -35426,7 +35426,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G1186" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -35452,7 +35452,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1187" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -35478,7 +35478,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1188" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -35504,7 +35504,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1189" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -35530,7 +35530,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1190" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -35556,7 +35556,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1191" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -35582,7 +35582,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1192" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -35608,7 +35608,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1193" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -35634,7 +35634,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1194" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -35660,7 +35660,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1195" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -35686,7 +35686,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1196" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -35712,7 +35712,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1197" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -35738,7 +35738,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1198" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -35764,7 +35764,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1199" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -35790,7 +35790,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1200" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -35816,7 +35816,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G1201" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -35842,7 +35842,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1202" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -35868,7 +35868,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1203" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -35894,7 +35894,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1204" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -35920,7 +35920,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1205" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -35946,7 +35946,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1206" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -35972,7 +35972,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1207" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -35998,7 +35998,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1208" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -36024,7 +36024,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1209" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -36050,7 +36050,7 @@
         <v>2.4449999332428</v>
       </c>
       <c r="G1210" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -36076,7 +36076,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1211" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -36102,7 +36102,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1212" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -36128,7 +36128,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1213" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -36154,7 +36154,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1214" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -36180,7 +36180,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G1215" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -36206,7 +36206,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1216" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -36232,7 +36232,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1217" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -36258,7 +36258,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1218" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -36284,7 +36284,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1219" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -36310,7 +36310,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G1220" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -36336,7 +36336,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G1221" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -36362,7 +36362,7 @@
         <v>2.125</v>
       </c>
       <c r="G1222" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -36388,7 +36388,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1223" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -36414,7 +36414,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1224" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -36440,7 +36440,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1225" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -36466,7 +36466,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1226" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -36492,7 +36492,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G1227" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -36518,7 +36518,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1228" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -36544,7 +36544,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G1229" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -36570,7 +36570,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1230" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -36596,7 +36596,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1231" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -36622,7 +36622,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1232" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -36648,7 +36648,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1233" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -36674,7 +36674,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1234" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -36700,7 +36700,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1235" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -36726,7 +36726,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1236" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -36752,7 +36752,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1237" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -36778,7 +36778,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1238" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -36804,7 +36804,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1239" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -36830,7 +36830,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1240" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -36856,7 +36856,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1241" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -36882,7 +36882,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G1242" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -36908,7 +36908,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1243" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -36934,7 +36934,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1244" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -36960,7 +36960,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1245" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -36986,7 +36986,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1246" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -37012,7 +37012,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1247" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -37038,7 +37038,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1248" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -37064,7 +37064,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1249" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -37090,7 +37090,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1250" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -37116,7 +37116,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1251" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -37142,7 +37142,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1252" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -37168,7 +37168,7 @@
         <v>3</v>
       </c>
       <c r="G1253" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -37194,7 +37194,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1254" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -37220,7 +37220,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1255" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -37246,7 +37246,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1256" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -37272,7 +37272,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1257" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -37298,7 +37298,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1258" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -37324,7 +37324,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G1259" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -37350,7 +37350,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1260" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -37376,7 +37376,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1261" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -37402,7 +37402,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1262" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -37428,7 +37428,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1263" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -37454,7 +37454,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1264" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -37480,7 +37480,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1265" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -37506,7 +37506,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1266" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -37532,7 +37532,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G1267" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -37558,7 +37558,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1268" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -37584,7 +37584,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1269" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -37610,7 +37610,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1270" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -37636,7 +37636,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1271" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -37662,7 +37662,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1272" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -37688,7 +37688,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1273" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -37714,7 +37714,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1274" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -37740,7 +37740,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1275" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -37766,7 +37766,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1276" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -37792,7 +37792,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1277" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -37818,7 +37818,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1278" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -37844,7 +37844,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1279" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -37870,7 +37870,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1280" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -37896,7 +37896,7 @@
         <v>2.75</v>
       </c>
       <c r="G1281" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -37922,7 +37922,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1282" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -37948,7 +37948,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1283" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -37974,7 +37974,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1284" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -38000,7 +38000,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1285" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -38026,7 +38026,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1286" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -38052,7 +38052,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1287" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -38078,7 +38078,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1288" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -38104,7 +38104,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1289" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -38130,7 +38130,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1290" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -38156,7 +38156,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1291" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -38182,7 +38182,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1292" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -38208,7 +38208,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1293" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -38234,7 +38234,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1294" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -38260,7 +38260,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1295" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -38286,7 +38286,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1296" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -38312,7 +38312,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1297" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -38338,7 +38338,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1298" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -38364,7 +38364,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1299" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -38390,7 +38390,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1300" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -38416,7 +38416,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1301" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -38442,7 +38442,7 @@
         <v>2.875</v>
       </c>
       <c r="G1302" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -38468,7 +38468,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G1303" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -38494,7 +38494,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1304" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -38520,7 +38520,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1305" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -38546,7 +38546,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1306" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -38572,7 +38572,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1307" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -38598,7 +38598,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1308" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -38624,7 +38624,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1309" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -38650,7 +38650,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1310" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -38676,7 +38676,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1311" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -38702,7 +38702,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1312" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -38728,7 +38728,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1313" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -38754,7 +38754,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1314" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -38780,7 +38780,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1315" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -38806,7 +38806,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1316" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -38832,7 +38832,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1317" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -38858,7 +38858,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G1318" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -38884,7 +38884,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1319" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -38910,7 +38910,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1320" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -38936,7 +38936,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1321" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -38962,7 +38962,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1322" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -38988,7 +38988,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1323" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -39014,7 +39014,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1324" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -39040,7 +39040,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1325" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -39066,7 +39066,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1326" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -39092,7 +39092,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1327" t="s">
-        <v>927</v>
+        <v>777</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -39118,7 +39118,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1328" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -39144,7 +39144,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1329" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -39326,7 +39326,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1336" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -39846,7 +39846,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1356" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -40236,7 +40236,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1371" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -41120,7 +41120,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1405" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -41172,7 +41172,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1407" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -41198,7 +41198,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1408" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -41302,7 +41302,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1412" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -41354,7 +41354,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1414" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -41380,7 +41380,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1415" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -41458,7 +41458,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1418" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -41484,7 +41484,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1419" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -41510,7 +41510,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1420" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -41536,7 +41536,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1421" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -41900,7 +41900,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1435" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -42186,7 +42186,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1446" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -42394,7 +42394,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1454" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -43070,7 +43070,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1480" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -43122,7 +43122,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1482" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -43590,7 +43590,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1500" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -43642,7 +43642,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1502" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -43746,7 +43746,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1506" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -43798,7 +43798,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1508" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -43824,7 +43824,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1509" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -43954,7 +43954,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1514" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -44032,7 +44032,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1517" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -44058,7 +44058,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1518" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -44344,7 +44344,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1529" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -44422,7 +44422,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1532" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -44448,7 +44448,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1533" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -44526,7 +44526,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1536" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -44604,7 +44604,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1539" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -44708,7 +44708,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1543" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -44734,7 +44734,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1544" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -44760,7 +44760,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1545" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -44786,7 +44786,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1546" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -44812,7 +44812,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1547" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -44838,7 +44838,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1548" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -44916,7 +44916,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1551" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -45020,7 +45020,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1555" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -45072,7 +45072,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1557" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -45150,7 +45150,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1560" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -45176,7 +45176,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1561" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -45228,7 +45228,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1563" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -45254,7 +45254,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G1564" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -45280,7 +45280,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1565" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -45306,7 +45306,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1566" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -45384,7 +45384,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1569" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -45410,7 +45410,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1570" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -45436,7 +45436,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1571" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -45462,7 +45462,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1572" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -45488,7 +45488,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1573" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -45514,7 +45514,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1574" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -45566,7 +45566,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1576" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -45618,7 +45618,7 @@
         <v>3</v>
       </c>
       <c r="G1578" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -45696,7 +45696,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1581" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -45722,7 +45722,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1582" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -45748,7 +45748,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1583" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -45800,7 +45800,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1585" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -45826,7 +45826,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1586" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -45878,7 +45878,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1588" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -45956,7 +45956,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1591" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -45982,7 +45982,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1592" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -46008,7 +46008,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1593" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -46034,7 +46034,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G1594" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -46086,7 +46086,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1596" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -46112,7 +46112,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1597" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -46138,7 +46138,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G1598" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -46190,7 +46190,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1600" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -46216,7 +46216,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1601" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -46294,7 +46294,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1604" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -46320,7 +46320,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1605" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -46372,7 +46372,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1607" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -46424,7 +46424,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1609" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -46450,7 +46450,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1610" t="s">
-        <v>927</v>
+        <v>777</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -46528,7 +46528,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G1613" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -46554,7 +46554,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G1614" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -46580,7 +46580,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1615" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -46606,7 +46606,7 @@
         <v>3</v>
       </c>
       <c r="G1616" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -46658,7 +46658,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1618" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -46762,7 +46762,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1622" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -46788,7 +46788,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1623" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -46814,7 +46814,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1624" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -46892,7 +46892,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1627" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -46918,7 +46918,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1628" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -46944,7 +46944,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1629" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -47022,7 +47022,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1632" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -47048,7 +47048,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1633" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -47074,7 +47074,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1634" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -47100,7 +47100,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1635" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -47126,7 +47126,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1636" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -47178,7 +47178,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1638" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -47204,7 +47204,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1639" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -47256,7 +47256,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G1641" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -47334,7 +47334,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1644" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -47386,7 +47386,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1646" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -47438,7 +47438,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1648" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47490,7 +47490,7 @@
         <v>3</v>
       </c>
       <c r="G1650" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -47516,7 +47516,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1651" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47568,7 +47568,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1653" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -47620,7 +47620,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1655" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -47646,7 +47646,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1656" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -47672,7 +47672,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1657" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -47698,7 +47698,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G1658" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -47724,7 +47724,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1659" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -47750,7 +47750,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1660" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -47776,7 +47776,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1661" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47802,7 +47802,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1662" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -47828,7 +47828,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1663" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -47854,7 +47854,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1664" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -47880,7 +47880,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1665" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -47906,7 +47906,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1666" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -47932,7 +47932,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1667" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -47984,7 +47984,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1669" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -48010,7 +48010,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1670" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -48036,7 +48036,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1671" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -48062,7 +48062,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1672" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -48088,7 +48088,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1673" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -48166,7 +48166,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1676" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -48192,7 +48192,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1677" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -48218,7 +48218,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1678" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -48244,7 +48244,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1679" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -48270,7 +48270,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1680" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -48374,7 +48374,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1684" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -48400,7 +48400,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G1685" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -48452,7 +48452,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1687" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -48478,7 +48478,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1688" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -48504,7 +48504,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1689" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -48530,7 +48530,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G1690" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -48556,7 +48556,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1691" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -48634,7 +48634,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1694" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -48660,7 +48660,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1695" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -48712,7 +48712,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1697" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -48764,7 +48764,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1699" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -48842,7 +48842,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1702" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -48894,7 +48894,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1704" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -48920,7 +48920,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1705" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -48946,7 +48946,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1706" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -49050,7 +49050,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1710" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -49128,7 +49128,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1713" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -49180,7 +49180,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1715" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -49206,7 +49206,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1716" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -49232,7 +49232,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1717" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -49258,7 +49258,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1718" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -49284,7 +49284,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1719" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -49362,7 +49362,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1722" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -49414,7 +49414,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1724" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -49440,7 +49440,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1725" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -49466,7 +49466,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1726" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -49518,7 +49518,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1728" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -49544,7 +49544,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1729" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -49570,7 +49570,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1730" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -49596,7 +49596,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1731" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -49622,7 +49622,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1732" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -49648,7 +49648,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1733" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -49700,7 +49700,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1735" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -49726,7 +49726,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G1736" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -49752,7 +49752,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1737" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -49778,7 +49778,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1738" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -49804,7 +49804,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1739" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -49830,7 +49830,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1740" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -49856,7 +49856,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1741" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -49908,7 +49908,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1743" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -49934,7 +49934,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1744" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -49986,7 +49986,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1746" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -50064,7 +50064,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1749" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -50090,7 +50090,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1750" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -50116,7 +50116,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1751" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -50142,7 +50142,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1752" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -50194,7 +50194,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1754" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -50220,7 +50220,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1755" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -50272,7 +50272,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1757" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -50298,7 +50298,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1758" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -50350,7 +50350,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1760" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -50402,7 +50402,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1762" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -50428,7 +50428,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1763" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -50454,7 +50454,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1764" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -50480,7 +50480,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1765" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50558,7 +50558,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G1768" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -50610,7 +50610,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1770" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -50636,7 +50636,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1771" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -50662,7 +50662,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1772" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -50714,7 +50714,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1774" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -50818,7 +50818,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1778" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -50844,7 +50844,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1779" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -50870,7 +50870,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1780" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -50896,7 +50896,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1781" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -50922,7 +50922,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1782" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -51026,7 +51026,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1786" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -51078,7 +51078,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1788" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -51104,7 +51104,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1789" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -51130,7 +51130,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1790" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -51156,7 +51156,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1791" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -51208,7 +51208,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1793" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -51234,7 +51234,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1794" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -51260,7 +51260,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -51312,7 +51312,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1797" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -51338,7 +51338,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G1798" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -51390,7 +51390,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1800" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -51416,7 +51416,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1801" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -51442,7 +51442,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1802" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -51468,7 +51468,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1803" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -51520,7 +51520,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1805" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -51546,7 +51546,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1806" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -51572,7 +51572,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1807" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -51650,7 +51650,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1810" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -51676,7 +51676,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1811" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -51702,7 +51702,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1812" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -51728,7 +51728,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1813" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -51754,7 +51754,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1814" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -51780,7 +51780,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1815" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -51832,7 +51832,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1817" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -51858,7 +51858,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1818" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -51910,7 +51910,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G1820" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -51962,7 +51962,7 @@
         <v>3</v>
       </c>
       <c r="G1822" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -51988,7 +51988,7 @@
         <v>3</v>
       </c>
       <c r="G1823" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -52014,7 +52014,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1824" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -52040,7 +52040,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1825" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -52066,7 +52066,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1826" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -52092,7 +52092,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1827" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -52118,7 +52118,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1828" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -52170,7 +52170,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1830" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -52196,7 +52196,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1831" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -52222,7 +52222,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1832" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -52248,7 +52248,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1833" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -52274,7 +52274,7 @@
         <v>3</v>
       </c>
       <c r="G1834" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -52300,7 +52300,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1835" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -52352,7 +52352,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G1837" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -52404,7 +52404,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1839" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -52456,7 +52456,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1841" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -52508,7 +52508,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1843" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -52534,7 +52534,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1844" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -52586,7 +52586,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1846" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -52612,7 +52612,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1847" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -52664,7 +52664,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1849" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -52690,7 +52690,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1850" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -52716,7 +52716,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1851" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -52742,7 +52742,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1852" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -52768,7 +52768,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1853" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -52794,7 +52794,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1854" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -52820,7 +52820,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1855" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -52898,7 +52898,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1858" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -52976,7 +52976,7 @@
         <v>2.75</v>
       </c>
       <c r="G1861" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -53054,7 +53054,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1864" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -53080,7 +53080,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1865" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -53106,7 +53106,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1866" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -53132,7 +53132,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1867" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -53158,7 +53158,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1868" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -53288,7 +53288,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1873" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -53314,7 +53314,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1874" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -53340,7 +53340,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1875" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -53366,7 +53366,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1876" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -53418,7 +53418,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1878" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -53470,7 +53470,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1880" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -53496,7 +53496,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1881" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -53548,7 +53548,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1883" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -53574,7 +53574,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1884" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -53626,7 +53626,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1886" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -53678,7 +53678,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1888" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -53756,7 +53756,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1891" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -54068,7 +54068,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1903" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -54094,7 +54094,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1904" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -54172,7 +54172,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1907" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -54224,7 +54224,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1909" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -54250,7 +54250,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1910" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -54302,7 +54302,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1912" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -54588,7 +54588,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1923" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -54614,7 +54614,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1924" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -54692,7 +54692,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1927" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -54718,7 +54718,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1928" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -54770,7 +54770,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G1930" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -54822,7 +54822,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1932" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -55290,7 +55290,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1950" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -55420,7 +55420,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1955" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -55446,7 +55446,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1956" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -55602,7 +55602,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1962" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -55654,7 +55654,7 @@
         <v>2.125</v>
       </c>
       <c r="G1964" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -55680,7 +55680,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1965" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -55706,7 +55706,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1966" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -55758,7 +55758,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1968" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -56746,7 +56746,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G2006" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -56772,7 +56772,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G2007" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -56798,7 +56798,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G2008" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -56824,7 +56824,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G2009" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -56850,7 +56850,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G2010" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -56876,7 +56876,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G2011" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -56954,7 +56954,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G2014" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -56980,7 +56980,7 @@
         <v>2.4449999332428</v>
       </c>
       <c r="G2015" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -57006,7 +57006,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2016" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -57058,7 +57058,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2018" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -57084,7 +57084,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G2019" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -57110,7 +57110,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2020" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -57136,7 +57136,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2021" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -57162,7 +57162,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G2022" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -57214,7 +57214,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2024" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -57266,7 +57266,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G2026" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -57292,7 +57292,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2027" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -57344,7 +57344,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G2029" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -57448,7 +57448,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2033" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -57474,7 +57474,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G2034" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -57526,7 +57526,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G2036" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -57578,7 +57578,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G2038" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -57604,7 +57604,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G2039" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -57656,7 +57656,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2041" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -57682,7 +57682,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2042" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -57708,7 +57708,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G2043" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -57734,7 +57734,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G2044" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -57760,7 +57760,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G2045" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -57786,7 +57786,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G2046" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -57838,7 +57838,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G2048" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -57864,7 +57864,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G2049" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -57890,7 +57890,7 @@
         <v>2.75</v>
       </c>
       <c r="G2050" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -57942,7 +57942,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G2052" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -57994,7 +57994,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G2054" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -58020,7 +58020,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G2055" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -58046,7 +58046,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2056" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -58072,7 +58072,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G2057" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -58098,7 +58098,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G2058" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -58124,7 +58124,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G2059" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -58150,7 +58150,7 @@
         <v>2.75</v>
       </c>
       <c r="G2060" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -58176,7 +58176,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G2061" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -58202,7 +58202,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2062" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -58254,7 +58254,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G2064" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -58280,7 +58280,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G2065" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -58306,7 +58306,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G2066" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -58332,7 +58332,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G2067" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -58358,7 +58358,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G2068" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -58384,7 +58384,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G2069" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -58410,7 +58410,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G2070" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -58436,7 +58436,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G2071" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -58462,7 +58462,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2072" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -58488,7 +58488,7 @@
         <v>2.875</v>
       </c>
       <c r="G2073" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -58514,7 +58514,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G2074" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -58540,7 +58540,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2075" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -58566,7 +58566,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2076" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -58592,7 +58592,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G2077" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -58670,7 +58670,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G2080" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -58722,7 +58722,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2082" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -58826,7 +58826,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G2086" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -58852,7 +58852,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2087" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -59034,7 +59034,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G2094" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -70768,7 +70768,7 @@
     </row>
     <row r="2546">
       <c r="A2546" s="1" t="n">
-        <v>46030.6910300926</v>
+        <v>46030.3333333333</v>
       </c>
       <c r="B2546" t="n">
         <v>48176</v>
@@ -70789,6 +70789,32 @@
         <v>1415</v>
       </c>
       <c r="H2546" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2547">
+      <c r="A2547" s="1" t="n">
+        <v>46031.6911921296</v>
+      </c>
+      <c r="B2547" t="n">
+        <v>67886</v>
+      </c>
+      <c r="C2547" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="D2547" t="n">
+        <v>7.51000022888184</v>
+      </c>
+      <c r="E2547" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="F2547" t="n">
+        <v>7.55999994277954</v>
+      </c>
+      <c r="G2547" t="s">
+        <v>1374</v>
+      </c>
+      <c r="H2547" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="1416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="1417">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95473086833954</t>
+    <t xml:space="preserve">1.95473062992096</t>
   </si>
   <si>
     <t xml:space="preserve">FM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95993399620056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90963470935822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8558669090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86453914642334</t>
+    <t xml:space="preserve">1.95993423461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9096348285675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85586702823639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86453926563263</t>
   </si>
   <si>
     <t xml:space="preserve">1.68415582180023</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">1.74486184120178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69542992115021</t>
+    <t xml:space="preserve">1.69542968273163</t>
   </si>
   <si>
     <t xml:space="preserve">1.61824667453766</t>
@@ -77,22 +77,22 @@
     <t xml:space="preserve">1.47949004173279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34420251846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45434045791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55233716964722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48989677429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54366493225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59569871425629</t>
+    <t xml:space="preserve">1.34420263767242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45434057712555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55233728885651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48989689350128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54366505146027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.595698595047</t>
   </si>
   <si>
     <t xml:space="preserve">1.51331210136414</t>
@@ -104,22 +104,22 @@
     <t xml:space="preserve">1.499436378479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43005812168121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40751028060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38582956790924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28349661827087</t>
+    <t xml:space="preserve">1.4300582408905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40751039981842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38582968711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28349673748016</t>
   </si>
   <si>
     <t xml:space="preserve">1.17682766914368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24186980724335</t>
+    <t xml:space="preserve">1.24186968803406</t>
   </si>
   <si>
     <t xml:space="preserve">1.20718061923981</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">1.23059582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43873047828674</t>
+    <t xml:space="preserve">1.43873059749603</t>
   </si>
   <si>
     <t xml:space="preserve">1.39710354804993</t>
@@ -140,22 +140,22 @@
     <t xml:space="preserve">1.48295903205872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46561443805695</t>
+    <t xml:space="preserve">1.46561455726624</t>
   </si>
   <si>
     <t xml:space="preserve">1.52111709117889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51678073406219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4942330121994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47688853740692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47515404224396</t>
+    <t xml:space="preserve">1.51678085327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49423289299011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47688841819763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47515392303467</t>
   </si>
   <si>
     <t xml:space="preserve">1.50984311103821</t>
@@ -167,16 +167,16 @@
     <t xml:space="preserve">1.58702635765076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55754065513611</t>
+    <t xml:space="preserve">1.55754053592682</t>
   </si>
   <si>
     <t xml:space="preserve">1.52805483341217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54279780387878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51244485378265</t>
+    <t xml:space="preserve">1.54279768466949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51244473457336</t>
   </si>
   <si>
     <t xml:space="preserve">1.55147004127502</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">1.67374897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70843815803528</t>
+    <t xml:space="preserve">1.70843827724457</t>
   </si>
   <si>
     <t xml:space="preserve">1.67808520793915</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">1.65467011928558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63298952579498</t>
+    <t xml:space="preserve">1.63298940658569</t>
   </si>
   <si>
     <t xml:space="preserve">1.6061053276062</t>
@@ -212,10 +212,10 @@
     <t xml:space="preserve">1.49683463573456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48122441768646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41791701316833</t>
+    <t xml:space="preserve">1.48122453689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41791689395905</t>
   </si>
   <si>
     <t xml:space="preserve">1.39970517158508</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">1.46041119098663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57228350639343</t>
+    <t xml:space="preserve">1.57228338718414</t>
   </si>
   <si>
     <t xml:space="preserve">1.62952041625977</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">1.62518429756165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65987348556519</t>
+    <t xml:space="preserve">1.65987360477448</t>
   </si>
   <si>
     <t xml:space="preserve">1.58615911006927</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">1.6009019613266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58876085281372</t>
+    <t xml:space="preserve">1.58876073360443</t>
   </si>
   <si>
     <t xml:space="preserve">1.49249851703644</t>
@@ -269,16 +269,16 @@
     <t xml:space="preserve">1.47775566577911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47428679466248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46908342838287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56794714927673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53932881355286</t>
+    <t xml:space="preserve">1.47428667545319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46908330917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56794726848602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53932869434357</t>
   </si>
   <si>
     <t xml:space="preserve">1.53065645694733</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">1.54106318950653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5696816444397</t>
+    <t xml:space="preserve">1.56968176364899</t>
   </si>
   <si>
     <t xml:space="preserve">1.5471339225769</t>
@@ -299,10 +299,10 @@
     <t xml:space="preserve">1.56708014011383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57401812076569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51071035861969</t>
+    <t xml:space="preserve">1.57401788234711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5107102394104</t>
   </si>
   <si>
     <t xml:space="preserve">1.59136247634888</t>
@@ -320,16 +320,16 @@
     <t xml:space="preserve">1.38929855823517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40057253837585</t>
+    <t xml:space="preserve">1.40057241916656</t>
   </si>
   <si>
     <t xml:space="preserve">1.3875640630722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44740271568298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49163126945496</t>
+    <t xml:space="preserve">1.44740283489227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49163138866425</t>
   </si>
   <si>
     <t xml:space="preserve">1.4838262796402</t>
@@ -338,13 +338,13 @@
     <t xml:space="preserve">1.32338917255402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32945990562439</t>
+    <t xml:space="preserve">1.3294597864151</t>
   </si>
   <si>
     <t xml:space="preserve">1.3884311914444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39016568660736</t>
+    <t xml:space="preserve">1.39016556739807</t>
   </si>
   <si>
     <t xml:space="preserve">1.35981273651123</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">1.33726489543915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31124794483185</t>
+    <t xml:space="preserve">1.31124806404114</t>
   </si>
   <si>
     <t xml:space="preserve">1.30084121227264</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">1.30257570743561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36154723167419</t>
+    <t xml:space="preserve">1.3615471124649</t>
   </si>
   <si>
     <t xml:space="preserve">1.37802445888519</t>
@@ -377,25 +377,25 @@
     <t xml:space="preserve">1.377157330513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4049084186554</t>
+    <t xml:space="preserve">1.40490853786469</t>
   </si>
   <si>
     <t xml:space="preserve">1.39450180530548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40404140949249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.393634557724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42225301265717</t>
+    <t xml:space="preserve">1.4040412902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39363467693329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42225313186646</t>
   </si>
   <si>
     <t xml:space="preserve">1.42832362651825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37889182567596</t>
+    <t xml:space="preserve">1.37889170646667</t>
   </si>
   <si>
     <t xml:space="preserve">1.38062620162964</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">1.30170845985413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30777907371521</t>
+    <t xml:space="preserve">1.3077791929245</t>
   </si>
   <si>
     <t xml:space="preserve">1.34767150878906</t>
@@ -431,25 +431,25 @@
     <t xml:space="preserve">1.34506988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33379578590393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37108659744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35547661781311</t>
+    <t xml:space="preserve">1.33379590511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37108671665192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35547649860382</t>
   </si>
   <si>
     <t xml:space="preserve">1.34940600395203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33813202381134</t>
+    <t xml:space="preserve">1.33813190460205</t>
   </si>
   <si>
     <t xml:space="preserve">1.34853875637054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41704964637756</t>
+    <t xml:space="preserve">1.41704976558685</t>
   </si>
   <si>
     <t xml:space="preserve">1.40317416191101</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">1.41097915172577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36501622200012</t>
+    <t xml:space="preserve">1.36501610279083</t>
   </si>
   <si>
     <t xml:space="preserve">1.38322782516479</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">1.39797067642212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37455570697784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41358077526093</t>
+    <t xml:space="preserve">1.37455558776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41358089447021</t>
   </si>
   <si>
     <t xml:space="preserve">1.42138588428497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41271352767944</t>
+    <t xml:space="preserve">1.41271340847015</t>
   </si>
   <si>
     <t xml:space="preserve">1.40924477577209</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">1.42572212219238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3511403799057</t>
+    <t xml:space="preserve">1.35114049911499</t>
   </si>
   <si>
     <t xml:space="preserve">1.35894548892975</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">1.36414885520935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36241436004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33032715320587</t>
+    <t xml:space="preserve">1.36241447925568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33032703399658</t>
   </si>
   <si>
     <t xml:space="preserve">1.32078754901886</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">1.31992018222809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3129825592041</t>
+    <t xml:space="preserve">1.31298243999481</t>
   </si>
   <si>
     <t xml:space="preserve">1.17942941188812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26181614398956</t>
+    <t xml:space="preserve">1.26181602478027</t>
   </si>
   <si>
     <t xml:space="preserve">1.29216909408569</t>
@@ -539,16 +539,16 @@
     <t xml:space="preserve">1.21758759021759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24880766868591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2288613319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18550002574921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15774881839752</t>
+    <t xml:space="preserve">1.2488077878952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22886145114899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18549990653992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15774869918823</t>
   </si>
   <si>
     <t xml:space="preserve">1.11872339248657</t>
@@ -557,19 +557,19 @@
     <t xml:space="preserve">1.13086462020874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12305963039398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13346636295319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11438739299774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11612164974213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11525452136993</t>
+    <t xml:space="preserve">1.12305951118469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13346648216248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11438727378845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11612176895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11525464057922</t>
   </si>
   <si>
     <t xml:space="preserve">1.09791004657745</t>
@@ -578,19 +578,19 @@
     <t xml:space="preserve">1.09270668029785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07536220550537</t>
+    <t xml:space="preserve">1.07536208629608</t>
   </si>
   <si>
     <t xml:space="preserve">1.07276034355164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10398066043854</t>
+    <t xml:space="preserve">1.10398054122925</t>
   </si>
   <si>
     <t xml:space="preserve">1.1542797088623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16295194625854</t>
+    <t xml:space="preserve">1.16295206546783</t>
   </si>
   <si>
     <t xml:space="preserve">1.16208481788635</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">1.17856216430664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18289828300476</t>
+    <t xml:space="preserve">1.18289816379547</t>
   </si>
   <si>
     <t xml:space="preserve">1.20544612407684</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">1.24533867835999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21845471858978</t>
+    <t xml:space="preserve">1.21845459938049</t>
   </si>
   <si>
     <t xml:space="preserve">1.19937562942505</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">1.20111012458801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2279942035675</t>
+    <t xml:space="preserve">1.22799408435822</t>
   </si>
   <si>
     <t xml:space="preserve">1.22192347049713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23666644096375</t>
+    <t xml:space="preserve">1.23666632175446</t>
   </si>
   <si>
     <t xml:space="preserve">1.26875400543213</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">1.38409507274628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39883804321289</t>
+    <t xml:space="preserve">1.3988379240036</t>
   </si>
   <si>
     <t xml:space="preserve">1.38669669628143</t>
@@ -644,19 +644,19 @@
     <t xml:space="preserve">1.35721111297607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3459370136261</t>
+    <t xml:space="preserve">1.34593713283539</t>
   </si>
   <si>
     <t xml:space="preserve">1.33292853832245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28870010375977</t>
+    <t xml:space="preserve">1.28869998455048</t>
   </si>
   <si>
     <t xml:space="preserve">1.25747990608215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2331976890564</t>
+    <t xml:space="preserve">1.23319756984711</t>
   </si>
   <si>
     <t xml:space="preserve">1.2444714307785</t>
@@ -665,25 +665,25 @@
     <t xml:space="preserve">1.22712683677673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25661265850067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2236579656601</t>
+    <t xml:space="preserve">1.25661253929138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22365808486938</t>
   </si>
   <si>
     <t xml:space="preserve">1.22279071807861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25314390659332</t>
+    <t xml:space="preserve">1.25314378738403</t>
   </si>
   <si>
     <t xml:space="preserve">1.22625982761383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21325123310089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20891523361206</t>
+    <t xml:space="preserve">1.21325135231018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20891511440277</t>
   </si>
   <si>
     <t xml:space="preserve">1.20457899570465</t>
@@ -692,16 +692,16 @@
     <t xml:space="preserve">1.21585297584534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21672022342682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19070339202881</t>
+    <t xml:space="preserve">1.21672010421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19070327281952</t>
   </si>
   <si>
     <t xml:space="preserve">1.20197737216949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18810164928436</t>
+    <t xml:space="preserve">1.18810176849365</t>
   </si>
   <si>
     <t xml:space="preserve">1.191570520401</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">1.27742624282837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27222263813019</t>
+    <t xml:space="preserve">1.27222275733948</t>
   </si>
   <si>
     <t xml:space="preserve">1.2982394695282</t>
@@ -743,49 +743,49 @@
     <t xml:space="preserve">1.24967479705811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29043459892273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29303634166718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31818580627441</t>
+    <t xml:space="preserve">1.29043447971344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29303622245789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31818568706512</t>
   </si>
   <si>
     <t xml:space="preserve">1.30691182613373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27308988571167</t>
+    <t xml:space="preserve">1.27309000492096</t>
   </si>
   <si>
     <t xml:space="preserve">1.24013531208038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27916061878204</t>
+    <t xml:space="preserve">1.27916049957275</t>
   </si>
   <si>
     <t xml:space="preserve">1.2704883813858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26528489589691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28436386585236</t>
+    <t xml:space="preserve">1.26528477668762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28436398506165</t>
   </si>
   <si>
     <t xml:space="preserve">1.27482438087463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26441752910614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28523123264313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2869656085968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3398665189743</t>
+    <t xml:space="preserve">1.26441764831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28523111343384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28696548938751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33986639976501</t>
   </si>
   <si>
     <t xml:space="preserve">1.33899927139282</t>
@@ -797,13 +797,13 @@
     <t xml:space="preserve">1.57835412025452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51851534843445</t>
+    <t xml:space="preserve">1.51851546764374</t>
   </si>
   <si>
     <t xml:space="preserve">1.54019606113434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49856913089752</t>
+    <t xml:space="preserve">1.49856925010681</t>
   </si>
   <si>
     <t xml:space="preserve">1.50724148750305</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">1.40577578544617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38496220111847</t>
+    <t xml:space="preserve">1.38496232032776</t>
   </si>
   <si>
     <t xml:space="preserve">1.47168505191803</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">1.45954382419586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45607495307922</t>
+    <t xml:space="preserve">1.45607507228851</t>
   </si>
   <si>
     <t xml:space="preserve">1.49076402187347</t>
@@ -860,10 +860,10 @@
     <t xml:space="preserve">1.50637412071228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57488512992859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58269023895264</t>
+    <t xml:space="preserve">1.57488524913788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58269011974335</t>
   </si>
   <si>
     <t xml:space="preserve">1.56187677383423</t>
@@ -872,34 +872,34 @@
     <t xml:space="preserve">1.53585994243622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48642790317535</t>
+    <t xml:space="preserve">1.48642778396606</t>
   </si>
   <si>
     <t xml:space="preserve">1.49510014057159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51157760620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4890296459198</t>
+    <t xml:space="preserve">1.51157748699188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48902952671051</t>
   </si>
   <si>
     <t xml:space="preserve">1.48035728931427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48816239833832</t>
+    <t xml:space="preserve">1.48816227912903</t>
   </si>
   <si>
     <t xml:space="preserve">1.51591360569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5688145160675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57054901123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64686512947083</t>
+    <t xml:space="preserve">1.56881439685822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57054889202118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64686501026154</t>
   </si>
   <si>
     <t xml:space="preserve">1.78648853302002</t>
@@ -911,13 +911,13 @@
     <t xml:space="preserve">1.85933589935303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86627352237701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84199130535126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15245866775513</t>
+    <t xml:space="preserve">1.86627340316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84199142456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15245890617371</t>
   </si>
   <si>
     <t xml:space="preserve">1.99982666969299</t>
@@ -926,10 +926,10 @@
     <t xml:space="preserve">2.05879807472229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00329566001892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95126187801361</t>
+    <t xml:space="preserve">2.00329542160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95126163959503</t>
   </si>
   <si>
     <t xml:space="preserve">2.05186033248901</t>
@@ -938,13 +938,13 @@
     <t xml:space="preserve">2.01543664932251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98074769973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90443181991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90790057182312</t>
+    <t xml:space="preserve">1.98074734210968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90443170070648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90790033340454</t>
   </si>
   <si>
     <t xml:space="preserve">1.91657280921936</t>
@@ -962,49 +962,49 @@
     <t xml:space="preserve">1.83158433437347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84719455242157</t>
+    <t xml:space="preserve">1.84719467163086</t>
   </si>
   <si>
     <t xml:space="preserve">1.93218290805817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93738603591919</t>
+    <t xml:space="preserve">1.93738627433777</t>
   </si>
   <si>
     <t xml:space="preserve">1.9252450466156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94258952140808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97727870941162</t>
+    <t xml:space="preserve">1.94258975982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97727882862091</t>
   </si>
   <si>
     <t xml:space="preserve">2.0206401348114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06920480728149</t>
+    <t xml:space="preserve">2.06920456886292</t>
   </si>
   <si>
     <t xml:space="preserve">2.01196765899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03971886634827</t>
+    <t xml:space="preserve">2.03971910476685</t>
   </si>
   <si>
     <t xml:space="preserve">2.01370215415955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9946231842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94432425498962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90269732475281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82117760181427</t>
+    <t xml:space="preserve">1.99462306499481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94432413578033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90269720554352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82117772102356</t>
   </si>
   <si>
     <t xml:space="preserve">1.91310393810272</t>
@@ -1013,31 +1013,31 @@
     <t xml:space="preserve">1.72144663333893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67114746570587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69976592063904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68762469291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67895245552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63992726802826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64773213863373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62865316867828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62691879272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60350358486176</t>
+    <t xml:space="preserve">1.67114758491516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69976603984833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68762457370758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67895233631134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63992738723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64773225784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62865328788757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62691867351532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60350370407104</t>
   </si>
   <si>
     <t xml:space="preserve">1.59656584262848</t>
@@ -1052,34 +1052,34 @@
     <t xml:space="preserve">1.6650767326355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6910936832428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72925174236298</t>
+    <t xml:space="preserve">1.69109380245209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72925162315369</t>
   </si>
   <si>
     <t xml:space="preserve">1.67548358440399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65640461444855</t>
+    <t xml:space="preserve">1.65640449523926</t>
   </si>
   <si>
     <t xml:space="preserve">1.63038766384125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66681134700775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68155407905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68935906887054</t>
+    <t xml:space="preserve">1.66681122779846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68155419826508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68935918807983</t>
   </si>
   <si>
     <t xml:space="preserve">1.67721807956696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63385665416718</t>
+    <t xml:space="preserve">1.63385653495789</t>
   </si>
   <si>
     <t xml:space="preserve">1.62171542644501</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">1.71537601947784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66854584217072</t>
+    <t xml:space="preserve">1.66854572296143</t>
   </si>
   <si>
     <t xml:space="preserve">1.71711039543152</t>
@@ -1103,13 +1103,13 @@
     <t xml:space="preserve">1.72578275203705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72751724720001</t>
+    <t xml:space="preserve">1.72751712799072</t>
   </si>
   <si>
     <t xml:space="preserve">1.71190702915192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74312734603882</t>
+    <t xml:space="preserve">1.74312722682953</t>
   </si>
   <si>
     <t xml:space="preserve">1.77781629562378</t>
@@ -1118,34 +1118,34 @@
     <t xml:space="preserve">1.77348041534424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80383324623108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93391728401184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8818838596344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9555983543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88621973991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81684172153473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89489221572876</t>
+    <t xml:space="preserve">1.80383312702179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93391752243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88188374042511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95559823513031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88621962070465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81684160232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89489209651947</t>
   </si>
   <si>
     <t xml:space="preserve">1.80816948413849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8298499584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85153090953827</t>
+    <t xml:space="preserve">1.82985007762909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85153079032898</t>
   </si>
   <si>
     <t xml:space="preserve">1.78215265274048</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">1.79082489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73445498943329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.764808177948</t>
+    <t xml:space="preserve">1.73445510864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76480805873871</t>
   </si>
   <si>
     <t xml:space="preserve">1.96860635280609</t>
@@ -1169,16 +1169,16 @@
     <t xml:space="preserve">1.89922833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89055585861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8775475025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83418619632721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84285843372345</t>
+    <t xml:space="preserve">1.89055597782135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87754762172699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8341863155365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84285831451416</t>
   </si>
   <si>
     <t xml:space="preserve">1.82551383972168</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">1.83852219581604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86020302772522</t>
+    <t xml:space="preserve">1.86020290851593</t>
   </si>
   <si>
     <t xml:space="preserve">1.9729425907135</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">1.98161494731903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92958104610443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98595082759857</t>
+    <t xml:space="preserve">1.92958092689514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98595070838928</t>
   </si>
   <si>
     <t xml:space="preserve">2.04665684700012</t>
@@ -1208,22 +1208,22 @@
     <t xml:space="preserve">2.03364849090576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.042320728302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.072674036026</t>
+    <t xml:space="preserve">2.04232096672058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07267379760742</t>
   </si>
   <si>
     <t xml:space="preserve">2.08134603500366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11169910430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15072441101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05532932281494</t>
+    <t xml:space="preserve">2.1116988658905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15072417259216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05532908439636</t>
   </si>
   <si>
     <t xml:space="preserve">2.1854133605957</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">2.3024890422821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2808084487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.211430311203</t>
+    <t xml:space="preserve">2.28080821037292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21143007278442</t>
   </si>
   <si>
     <t xml:space="preserve">2.30682516098022</t>
@@ -1253,13 +1253,13 @@
     <t xml:space="preserve">2.48894286155701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59301018714905</t>
+    <t xml:space="preserve">2.59300994873047</t>
   </si>
   <si>
     <t xml:space="preserve">2.38921189308167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49761533737183</t>
+    <t xml:space="preserve">2.49761557579041</t>
   </si>
   <si>
     <t xml:space="preserve">2.57566571235657</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">2.76645565032959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83583402633667</t>
+    <t xml:space="preserve">2.83583378791809</t>
   </si>
   <si>
     <t xml:space="preserve">2.91388416290283</t>
@@ -1283,19 +1283,19 @@
     <t xml:space="preserve">2.92255663871765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93122887611389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87052297592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92689275741577</t>
+    <t xml:space="preserve">2.93122911453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87052273750305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92689299583435</t>
   </si>
   <si>
     <t xml:space="preserve">3.10033822059631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23909449577332</t>
+    <t xml:space="preserve">3.23909473419189</t>
   </si>
   <si>
     <t xml:space="preserve">3.25210332870483</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">3.20874190330505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36917877197266</t>
+    <t xml:space="preserve">3.36917901039124</t>
   </si>
   <si>
     <t xml:space="preserve">3.26511144638062</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">3.50793528556824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48625469207764</t>
+    <t xml:space="preserve">3.48625445365906</t>
   </si>
   <si>
     <t xml:space="preserve">3.55563259124756</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">3.51227164268494</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62934684753418</t>
+    <t xml:space="preserve">3.62934708595276</t>
   </si>
   <si>
     <t xml:space="preserve">3.6640362739563</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">3.73341393470764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80712842941284</t>
+    <t xml:space="preserve">3.80712866783142</t>
   </si>
   <si>
     <t xml:space="preserve">3.90685963630676</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">4.09765005111694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86783456802368</t>
+    <t xml:space="preserve">3.86783504486084</t>
   </si>
   <si>
     <t xml:space="preserve">4.0412802696228</t>
@@ -1376,19 +1376,19 @@
     <t xml:space="preserve">3.945885181427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97190165519714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7117338180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91986799240112</t>
+    <t xml:space="preserve">3.97190141677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71173405647278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91986846923828</t>
   </si>
   <si>
     <t xml:space="preserve">4.07163286209106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24941539764404</t>
+    <t xml:space="preserve">4.24941492080688</t>
   </si>
   <si>
     <t xml:space="preserve">4.25375127792358</t>
@@ -1406,19 +1406,19 @@
     <t xml:space="preserve">4.74373435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75240659713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05593633651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98655796051025</t>
+    <t xml:space="preserve">4.75240707397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05593585968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9865574836731</t>
   </si>
   <si>
     <t xml:space="preserve">4.95186901092529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87381887435913</t>
+    <t xml:space="preserve">4.87381839752197</t>
   </si>
   <si>
     <t xml:space="preserve">4.31879281997681</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">4.97788572311401</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01257562637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03859186172485</t>
+    <t xml:space="preserve">5.01257514953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03859233856201</t>
   </si>
   <si>
     <t xml:space="preserve">4.91718006134033</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">4.82178449630737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85647392272949</t>
+    <t xml:space="preserve">4.85647344589233</t>
   </si>
   <si>
     <t xml:space="preserve">4.89116287231445</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83045721054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76107883453369</t>
+    <t xml:space="preserve">4.83045768737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76107835769653</t>
   </si>
   <si>
     <t xml:space="preserve">4.54427194595337</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">4.47489356994629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40551519393921</t>
+    <t xml:space="preserve">4.40551567077637</t>
   </si>
   <si>
     <t xml:space="preserve">4.1843729019165</t>
@@ -1487,10 +1487,10 @@
     <t xml:space="preserve">4.18870878219604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24074172973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.084641456604</t>
+    <t xml:space="preserve">4.24074268341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08464193344116</t>
   </si>
   <si>
     <t xml:space="preserve">3.9285409450531</t>
@@ -1499,10 +1499,10 @@
     <t xml:space="preserve">3.91553211212158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85916209220886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78111171722412</t>
+    <t xml:space="preserve">3.85916185379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7811119556427</t>
   </si>
   <si>
     <t xml:space="preserve">4.14101123809814</t>
@@ -1511,13 +1511,13 @@
     <t xml:space="preserve">3.62501096725464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31280922889709</t>
+    <t xml:space="preserve">3.31280899047852</t>
   </si>
   <si>
     <t xml:space="preserve">3.28679227828979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14369940757751</t>
+    <t xml:space="preserve">3.14369964599609</t>
   </si>
   <si>
     <t xml:space="preserve">3.00927948951721</t>
@@ -1526,13 +1526,13 @@
     <t xml:space="preserve">3.09166598320007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03529620170593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04830479621887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07865762710571</t>
+    <t xml:space="preserve">3.03529596328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04830455780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07865738868713</t>
   </si>
   <si>
     <t xml:space="preserve">2.96158194541931</t>
@@ -1541,7 +1541,7 @@
     <t xml:space="preserve">2.89653992652893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90521216392517</t>
+    <t xml:space="preserve">2.90521192550659</t>
   </si>
   <si>
     <t xml:space="preserve">3.02662420272827</t>
@@ -1565,13 +1565,13 @@
     <t xml:space="preserve">3.24343085289001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19139742851257</t>
+    <t xml:space="preserve">3.19139719009399</t>
   </si>
   <si>
     <t xml:space="preserve">3.42554879188538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43855690956116</t>
+    <t xml:space="preserve">3.43855714797974</t>
   </si>
   <si>
     <t xml:space="preserve">3.39519548416138</t>
@@ -1589,16 +1589,16 @@
     <t xml:space="preserve">2.93990159034729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88353133201599</t>
+    <t xml:space="preserve">2.88353157043457</t>
   </si>
   <si>
     <t xml:space="preserve">2.97459053993225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02228760719299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3821873664856</t>
+    <t xml:space="preserve">3.02228784561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38218760490417</t>
   </si>
   <si>
     <t xml:space="preserve">3.32148122787476</t>
@@ -1607,10 +1607,10 @@
     <t xml:space="preserve">3.15670824050903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11768293380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08732986450195</t>
+    <t xml:space="preserve">3.11768269538879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08733010292053</t>
   </si>
   <si>
     <t xml:space="preserve">3.06564927101135</t>
@@ -1619,16 +1619,16 @@
     <t xml:space="preserve">2.81848955154419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68840503692627</t>
+    <t xml:space="preserve">2.68840527534485</t>
   </si>
   <si>
     <t xml:space="preserve">2.73176693916321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63203549385071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98759865760803</t>
+    <t xml:space="preserve">2.63203573226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98759889602661</t>
   </si>
   <si>
     <t xml:space="preserve">3.17405271530151</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">3.17838859558105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10467433929443</t>
+    <t xml:space="preserve">3.10467457771301</t>
   </si>
   <si>
     <t xml:space="preserve">3.16104412078857</t>
@@ -1652,19 +1652,19 @@
     <t xml:space="preserve">3.330153465271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46023797988892</t>
+    <t xml:space="preserve">3.46023774147034</t>
   </si>
   <si>
     <t xml:space="preserve">3.59032154083252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88517904281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90252375602722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85482597351074</t>
+    <t xml:space="preserve">3.88517951965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90252327919006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8548264503479</t>
   </si>
   <si>
     <t xml:space="preserve">4.11499404907227</t>
@@ -1676,13 +1676,13 @@
     <t xml:space="preserve">4.10198593139648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.145348072052</t>
+    <t xml:space="preserve">4.14534759521484</t>
   </si>
   <si>
     <t xml:space="preserve">4.1323390007019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95889329910278</t>
+    <t xml:space="preserve">3.95889353752136</t>
   </si>
   <si>
     <t xml:space="preserve">3.82447361946106</t>
@@ -1691,19 +1691,19 @@
     <t xml:space="preserve">3.9675657749176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94154906272888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99791884422302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00659132003784</t>
+    <t xml:space="preserve">3.9415488243103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9979190826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00659084320068</t>
   </si>
   <si>
     <t xml:space="preserve">4.06296062469482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05862474441528</t>
+    <t xml:space="preserve">4.05862426757812</t>
   </si>
   <si>
     <t xml:space="preserve">4.01526355743408</t>
@@ -1715,16 +1715,16 @@
     <t xml:space="preserve">4.0326075553894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9892463684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92420434951782</t>
+    <t xml:space="preserve">3.98924612998962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92420482635498</t>
   </si>
   <si>
     <t xml:space="preserve">3.82880973815918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7594313621521</t>
+    <t xml:space="preserve">3.75943112373352</t>
   </si>
   <si>
     <t xml:space="preserve">3.74642300605774</t>
@@ -1733,13 +1733,13 @@
     <t xml:space="preserve">3.5686411857605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77677583694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24507856369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17136430740356</t>
+    <t xml:space="preserve">3.776775598526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24507904052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17136383056641</t>
   </si>
   <si>
     <t xml:space="preserve">4.0889778137207</t>
@@ -1751,7 +1751,7 @@
     <t xml:space="preserve">4.16269207000732</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21906185150146</t>
+    <t xml:space="preserve">4.21906137466431</t>
   </si>
   <si>
     <t xml:space="preserve">4.23206996917725</t>
@@ -1769,13 +1769,13 @@
     <t xml:space="preserve">4.76975154876709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72638940811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63966703414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55294418334961</t>
+    <t xml:space="preserve">4.72638988494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63966751098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55294466018677</t>
   </si>
   <si>
     <t xml:space="preserve">4.44887685775757</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">4.39684343338013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9111967086792</t>
+    <t xml:space="preserve">3.91119647026062</t>
   </si>
   <si>
     <t xml:space="preserve">4.04995250701904</t>
@@ -4260,6 +4260,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.63000011444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53000020980835</t>
   </si>
 </sst>
 </file>
@@ -70794,7 +70797,7 @@
     </row>
     <row r="2547">
       <c r="A2547" s="1" t="n">
-        <v>46031.6911921296</v>
+        <v>46031.3333333333</v>
       </c>
       <c r="B2547" t="n">
         <v>67886</v>
@@ -70815,6 +70818,32 @@
         <v>1374</v>
       </c>
       <c r="H2547" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2548">
+      <c r="A2548" s="1" t="n">
+        <v>46034.6910416667</v>
+      </c>
+      <c r="B2548" t="n">
+        <v>63626</v>
+      </c>
+      <c r="C2548" t="n">
+        <v>7.61999988555908</v>
+      </c>
+      <c r="D2548" t="n">
+        <v>7.46000003814697</v>
+      </c>
+      <c r="E2548" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F2548" t="n">
+        <v>7.53000020980835</v>
+      </c>
+      <c r="G2548" t="s">
+        <v>1416</v>
+      </c>
+      <c r="H2548" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FM.MI.xlsx
+++ b/data/FM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="1417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="1418">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95473062992096</t>
+    <t xml:space="preserve">1.95473086833954</t>
   </si>
   <si>
     <t xml:space="preserve">FM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95993423461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9096348285675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85586702823639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86453926563263</t>
+    <t xml:space="preserve">1.95993399620056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90963470935822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8558669090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86453914642334</t>
   </si>
   <si>
     <t xml:space="preserve">1.68415582180023</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">1.74486184120178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69542968273163</t>
+    <t xml:space="preserve">1.69542992115021</t>
   </si>
   <si>
     <t xml:space="preserve">1.61824667453766</t>
@@ -77,22 +77,22 @@
     <t xml:space="preserve">1.47949004173279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34420263767242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45434057712555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55233728885651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48989689350128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54366505146027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.595698595047</t>
+    <t xml:space="preserve">1.34420251846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45434045791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55233716964722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48989677429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54366493225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59569871425629</t>
   </si>
   <si>
     <t xml:space="preserve">1.51331210136414</t>
@@ -104,22 +104,22 @@
     <t xml:space="preserve">1.499436378479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4300582408905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40751039981842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38582968711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28349673748016</t>
+    <t xml:space="preserve">1.43005812168121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40751028060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38582956790924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28349661827087</t>
   </si>
   <si>
     <t xml:space="preserve">1.17682766914368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24186968803406</t>
+    <t xml:space="preserve">1.24186980724335</t>
   </si>
   <si>
     <t xml:space="preserve">1.20718061923981</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">1.23059582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43873059749603</t>
+    <t xml:space="preserve">1.43873047828674</t>
   </si>
   <si>
     <t xml:space="preserve">1.39710354804993</t>
@@ -140,22 +140,22 @@
     <t xml:space="preserve">1.48295903205872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46561455726624</t>
+    <t xml:space="preserve">1.46561443805695</t>
   </si>
   <si>
     <t xml:space="preserve">1.52111709117889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51678085327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49423289299011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47688841819763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47515392303467</t>
+    <t xml:space="preserve">1.51678073406219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4942330121994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47688853740692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47515404224396</t>
   </si>
   <si>
     <t xml:space="preserve">1.50984311103821</t>
@@ -167,16 +167,16 @@
     <t xml:space="preserve">1.58702635765076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55754053592682</t>
+    <t xml:space="preserve">1.55754065513611</t>
   </si>
   <si>
     <t xml:space="preserve">1.52805483341217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54279768466949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51244473457336</t>
+    <t xml:space="preserve">1.54279780387878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51244485378265</t>
   </si>
   <si>
     <t xml:space="preserve">1.55147004127502</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">1.67374897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70843827724457</t>
+    <t xml:space="preserve">1.70843815803528</t>
   </si>
   <si>
     <t xml:space="preserve">1.67808520793915</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">1.65467011928558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63298940658569</t>
+    <t xml:space="preserve">1.63298952579498</t>
   </si>
   <si>
     <t xml:space="preserve">1.6061053276062</t>
@@ -212,10 +212,10 @@
     <t xml:space="preserve">1.49683463573456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48122453689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41791689395905</t>
+    <t xml:space="preserve">1.48122441768646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41791701316833</t>
   </si>
   <si>
     <t xml:space="preserve">1.39970517158508</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">1.46041119098663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57228338718414</t>
+    <t xml:space="preserve">1.57228350639343</t>
   </si>
   <si>
     <t xml:space="preserve">1.62952041625977</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">1.62518429756165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65987360477448</t>
+    <t xml:space="preserve">1.65987348556519</t>
   </si>
   <si>
     <t xml:space="preserve">1.58615911006927</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">1.6009019613266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58876073360443</t>
+    <t xml:space="preserve">1.58876085281372</t>
   </si>
   <si>
     <t xml:space="preserve">1.49249851703644</t>
@@ -269,16 +269,16 @@
     <t xml:space="preserve">1.47775566577911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47428667545319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46908330917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56794726848602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53932869434357</t>
+    <t xml:space="preserve">1.47428679466248</t>
